--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q209"/>
+  <dimension ref="A1:Q210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14603,6 +14603,75 @@
         </is>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Consumer Strategy &amp; Intelligence Manager</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55748/consumer-strategy-intelligence-manager</t>
+        </is>
+      </c>
+      <c r="G210" t="n">
+        <v>1</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>1</v>
+      </c>
+      <c r="M210" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" t="n">
+        <v>1</v>
+      </c>
+      <c r="O210" t="n">
+        <v>0</v>
+      </c>
+      <c r="P210" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>¿Te apasiona entender al consumidor a partir de los datos y transformar ese conocimiento en estrategias de alto impacto? Buscamos un/aConsumer Strategy &amp; Intelligence Managerque lidere la evolución de la inteligencia de clientes y contribuya a fortalecer la relación entre nuestras marcas y millones de consumidores en Latinoamérica.En este rol tendrás la oportunidad de impulsar iniciativas regionales, trabajar con equipos multidisciplinarios y convertir los datos en decisiones que generen valor para el negocio y una mejor experiencia para nuestros clientes.Desafío:Serás responsable de liderar la estrategia de inteligencia de clientes y gestión de CRM, potenciando el conocimiento del consumidor para apoyar la toma de decisiones comerciales y de marketing. Tu foco estará en desarrollar estrategias de segmentación, fidelización y automatización que permitan construir relaciones de largo plazo con nuestros clientes en los distintos mercados donde operamos.Principales responsabilidades:Liderar la estrategia de segmentación de clientes y gestión de su ciclo de vida, utilizando metodologías como RFM y nuevas fuentes de información.Diseñar y coordinar campañas de captación, retención y fidelización junto a las distintas marcas y equipos regionales.Administrar y optimizar la plataforma CRM, asegurando la correcta implementación de automatizaciones y flujos de comunicación.Generar análisis e insights estratégicos que apoyen la planificación de campañas, promociones y comunicaciones orientadas al cliente.Promover el uso de herramientas de inteligencia de clientes dentro de la organización, capacitando y acompañando a los equipos internos en su adopción.Trabajar de manera transversal con Marketing, Comercial, Atención al Cliente, Tecnología y otras áreas clave para asegurar una visión integral del consumidor.Compartir aprendizajes y mejores prácticas entre los distintos países, impulsando la mejora continua de las estrategias de relacionamiento.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q210"/>
+  <dimension ref="A1:Q215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14672,6 +14672,351 @@
         </is>
       </c>
     </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Auxiliar de Servicios Transaccionales (Temporal)</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Mibanco</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55765/auxiliar-de-servicios-transaccionales-temporal</t>
+        </is>
+      </c>
+      <c r="G211" t="n">
+        <v>5</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>python, excel</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>1</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="n">
+        <v>0</v>
+      </c>
+      <c r="O211" t="n">
+        <v>0</v>
+      </c>
+      <c r="P211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAuxiliar de Servicios Transaccionales (Temporal).¿Cuáles serían tus principales responsabilidades?Atender requerimientos de regularizaciones creados en el JIRA.Verifica que el expediente se encuentre creado en Onbase.Validar el contenido del expediente creado en Onbase.Seguimiento a la subsanación de las observaciones encontradas.Informa a Negocios sobre las observaciones encontradas diariamente por correo electrónico.¿Qué necesitamos?Estudiante o Egresado en Administración, Ing. Industrial o Sistemas, afines.Al menos 6 meses de experiencia en gestión de información.Capacidad para trabajo bajo presión por la importancia de los plazos de entrega.Consultas y creación de querys en PLSQL a nivel intermedio.Excel nivel avanzado (Macros) (deseable)Creación y mantenimiento de Dashboards en PowerBI nivel básico/intermedio.Python, Powerplatform nivel Intermedio (deseable).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Analista de Monitoreo (Fraudes)</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Mibanco</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55764/analista-de-monitoreo-fraudes</t>
+        </is>
+      </c>
+      <c r="G212" t="n">
+        <v>4</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>excel, cloud</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>1</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" t="n">
+        <v>0</v>
+      </c>
+      <c r="O212" t="n">
+        <v>0</v>
+      </c>
+      <c r="P212" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAnalista de Monitoreo.¿Cuáles serían tus principales responsabilidades?Realizar el monitoreo continuo de las herramientas de prevención del fraudeAnalizar, coordinar, comunicar y realizar el seguimiento a los eventos reportados.Gestionar los eventos y alertas de las herramientas de monitoreo y el contacto con el cliente.Consolidar información y emitir el reporte de la gestión realizada por durante el monitoreo.Evaluar el cumplimiento los indicadores de monitoreo y brindar retroalimentación para la mejora de las herramientas.¿Qué necesitamos?Bachiller o Titulado en Administración bancaria o empresas, Economía, Derecho, Ingenierías.Mínimo 1 año de experiencia en el área de monitoreo en los sectores de banca, retail, seguros o telcoms.Creacción de reportes en Excel nivel Intermedio (Graficos) (Indispensable)Herramientas de Monitoreo nivel intermedio (Orion, CGR, PRTG, Monitor Plus, entre otros) (Indispensable).Conocimiento de MS Office a nivel Intermedio (Deseable).Creación de tickets Smart Cloud o JIRA nivel Intermedio (Deseable)Conocimientos en estructura de Red de Agencias y/o del sector financiero.Herramientas de Automatización - nivel Intermedio (Deseable).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Analista de Alianzas Estratégicas y Growth</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Mibanco</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55762/analista-de-alianzas-estrategicas-y-growth</t>
+        </is>
+      </c>
+      <c r="G213" t="n">
+        <v>12</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>python, sql, modelo, analisis, tableu</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>1</v>
+      </c>
+      <c r="L213" t="n">
+        <v>1</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" t="n">
+        <v>0</v>
+      </c>
+      <c r="O213" t="n">
+        <v>0</v>
+      </c>
+      <c r="P213" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAnalista de Alianzas Estratégicas y Growth.¿Cuáles serían tus principales responsabilidades?Construir y mantener reportes de performance comercial de alianzas y growth (leads, funnel, conversión, desembolsos, rentabilidad).Analizar data comercial y operativa con foco en crecimiento, eficiencia y rentabilidad, incorporando contexto de negocio.Generar insights accionables orientados a impacto (qué escalar, qué corregir, qué optimizar).Realizar seguimiento end‑to‑end al desempeño del funnel de prospectos provenientes de alianzas estratégicas y growth.Automatización de reportería generada para la generación más rápida y eficiente de insightsEjecutar y apoyar en tareas de soporte al modelo de alianzas (presentaciones, comunicaciones,validación de documentos, control de comisiones, atención de consultas de aliados y canales de venta).¿Qué necesitamos?Bachiller de Administración, Ing Industrial, Marketing, Economía, Ing Sistemas o afines.Experiencia mínima de 1-2 años en análisis comercial, reporting, producto o negocioExperiencia trabajando con data de ventas, canales o alianzas (deseable). De 1 a 2 añosExcel Avanzado (tablas dinámicas, programación de macros)SQL (consulta, cruce y análisis de datos, construcción de queries para reportería –Intermedio/Avanzado) (Indispensable).Herramientas de BI, visualización y automatización de datos.Power BI – Avanzado (Indispensable).Power Automate – básico (Deseable).Tableu – básico (Deseable).Python básico (automatización y análisis de datos) (Deseable).Conocimiento básico de framework ágil Scrum (Deseable).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>WHOLESALE RISK ANALYST I</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>BBVA Perú</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55761/wholesale-risk-analyst-i</t>
+        </is>
+      </c>
+      <c r="G214" t="n">
+        <v>1</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" t="n">
+        <v>1</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="n">
+        <v>0</v>
+      </c>
+      <c r="O214" t="n">
+        <v>0</v>
+      </c>
+      <c r="P214" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>¿Qué estamos buscando?Funciones:Elaborar programas financieros (informes de riesgo de crédito) y evaluación técnica de líneas de crédito y reestructuraciones de deuda, mediante bilaterales/sindicados de mediana empresa, gran empresa o empresas corporativasPresentar el Programa Financiero u Operación puntual, a las Jefaturas o comités de crédito.Visitar a clientes y dar soporte a la estructuración de las transacciones y programas financieros.Atender y asesorar a los Gerentes de Oficinas, Ejecutivos y Gestores sobre las operaciones presentadas y por presentarse.Cumplir los tiempo de respuesta en la evaluación de operaciones de acuerdo a ANS establecidoValidar correctamente el Rating , para poder ejercer delegación o refrendar las propuestas con jefes directos o comitesCumplir las normativas y procedimientos internos( facilidades crediticias, delegaciones y protocolos de Admisión)Presentar Propuestas para ingresos de clientes en Comite WLRequisitos:Profesional de las carreras de Economía, Administración, Ing. Industrial y/o afines.2 años de experiencia en análisis de estados financieros, evaluación de riesgos crediticios de grandes empresas , evaluación de créditos de medianos plazos.Experiencia en el sector de Banca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Analista de Control de Gestión y Presupuesto</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Mibanco</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55763/analista-de-control-de-gestion-y-presupuesto</t>
+        </is>
+      </c>
+      <c r="G215" t="n">
+        <v>9</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>python, sql, analisis, excel</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>1</v>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="n">
+        <v>1</v>
+      </c>
+      <c r="O215" t="n">
+        <v>0</v>
+      </c>
+      <c r="P215" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAnalista de Control de Gestión y Presupuesto.¿Cuáles serían tus principales responsabilidades?Participa en el proceso de planeamiento financiero y proyecciones durante el año, retando analíticamente a los equipos responsables de las principales líneas del GyP del banco.Mensualmente elabora presentaciones a los foros más senior de la organización (Comité Ejecutivo y Directorio), incorporando información de diferentes líneas del GyP mediante una buena dinámica con equipos del banco para su consolidación.Propone y desarrolla modelos financieros eficientes y automatizados, que nutran el análisis más granular de los drivers de crecimiento del negocio y que sirva como input tanto para el entendimiento de la ejecución real como insight looking forward hacia las proyecciones.¿Qué necesitamos?Bachiller en Economía, Administración, Ingeniería Industrial, Ingeniería de Sistemas, o a fines.Experiencia de mínimo 1 año en prácticas pre-profesionales en equipos de planeamiento financiero, planeamiento estratégico, tesorería o pricing.Excel Avanzado (Tablas Dinámicas y Macros) (Indispensable).Conocimiento Intermedio de PowerPoint (Indispensable).Conocimiento de nivel intermedio de lenguajes de programación para manejo de data (SQL, Power Query, Python u otros) (Indispensable al menos 1).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q215"/>
+  <dimension ref="A1:Q218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15017,6 +15017,201 @@
         </is>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Project Manager Office (PMO)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Murex Chile</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Presencial Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55792/project-manager-office-pmo</t>
+        </is>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="n">
+        <v>1</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>1</v>
+      </c>
+      <c r="L216" t="n">
+        <v>1</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" t="n">
+        <v>1</v>
+      </c>
+      <c r="O216" t="n">
+        <v>0</v>
+      </c>
+      <c r="P216" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>🌍 ¿Quiénes somos?Somos Murex, líder global en tecnología financiera (fintech) especializada en soluciones de trading, gestión de riesgo y procesamiento para mercados de capitales.Con presencia en 19 oficinas alrededor del mundo y más de 3.500 colaboradores de más de 60 nacionalidades, desarrollamos, implementamos y damos soporte a una plataforma utilizada por bancos, asset managers, corporaciones y utilities a nivel global.En Murex trabajarás en una industria que está a la vanguardia de la innovación, en un entorno centrado en las personas, donde podrás crecer rápidamente sin dejar de ser tú mismo/a. Formarás parte de un equipo global, diverso y altamente colaborativo.👥 El equipoEl área deProject Managementes responsable de la implementación y entrega de las soluciones de Murex. Gestionamos a los clientes desde la firma de los acuerdos contractuales hasta la puesta en marcha (go-live) del producto. ElProject Manageres el responsable integral del proyecto de implementación de Murex, liderando al equipo hacia una entrega exitosa del alcance y los servicios acordados, siguiendo los estándares de Murex, respetando las restricciones del proyecto y consolidando una sólida relación de largo plazo con el cliente🚀 ¿Qué harás?Liderar al equipo del proyecto hacia el cumplimiento de los objetivos, contribuyendo al desarrollo y la motivación a largo plazo de sus miembros, en colaboración con sus respectivos gerentes.Comunicar y reportar el estado del proyecto, proporcionando una visión clara y compartida a la dirección de Murex y al equipo del proyecto (incluidos los integradores).Definir el plan del proyecto: estimar esfuerzos, elaborar planes de alto nivel y detallados, incluyendo dotación de personal y aspectos logísticos (perfil de recursos, gobierno y organización).Coordinar con clientes e integradores, asegurando su preparación para el proyecto y construyendo una relación basada en el respeto y la confianza mutua.Identificar riesgos e incidencias del proyecto y garantizar la implementación de planes de mitigación.Asegurar el cumplimiento del cronograma, alcance, presupuesto y expectativas de calidad, gestionando además el proceso de solicitudes de cambio y monitoreando los KPI asociados.Adoptar y promover las metodologías, herramientas y mejores prácticas de gestión de proyectos de Murex, alineándolas con clientes e integradores.Contribuir a la definición y mantenimiento de metodologías.Preparar y ejecutar el cierre del proyecto y la transferencia de responsabilidades.Documentar y compartir las lecciones aprendidas.Reportar al Director de Proyecto y colaborar estrechamente con las distintas áreas de Murex (Client Services, departamentos de Producto y Administración de Proyectos).Asegurar que el espíritu de colaboración entre los distintos departamentos de Murex se promueva y difunda dentro de todo el equipo del proyecto.🎯 ¿Qué buscamos?Entre 6 y 10 años de experiencia relevante en gestión de proyectos dentro de los sectores de software, tecnología o banca.Experiencia previa en mercados de inversión o mercados financieros.Experiencia previa en actividades de cara al cliente.Se valorará el conocimiento de la industria y las soluciones de software de Murex.Capacidad para trabajar en múltiples tareas simultáneamente y manejar situaciones de presión.Enfoque demostrado, organizado, analítico y metodológico.Certificación PMI deseable.Nivel avanzado de inglés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Directora de arte</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>KiosClub</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55777/director-a-de-arte</t>
+        </is>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>1</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" t="n">
+        <v>0</v>
+      </c>
+      <c r="O217" t="n">
+        <v>0</v>
+      </c>
+      <c r="P217" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>KiosClub American SupermarketSomos una empresa que surge en 2017 con el propósito de acercar productos internacionales al mercado chileno, con una propuesta diferenciada basada en marcas norteamericanas. Nuestro foco está en la variedad, la innovación y un servicio cercano.Hoy contamos con más de 50 tiendas a lo largo de todo el país y seguimos creciendo. Nuestra misión es ofrecer una experiencia de compra dinámica y entretenida, manteniendo estándares claros en nuestros productos y en la forma en que operamos.¡Estamos buscando a nuestro/a próximo/aDirector/a de Arte!Si te apasiona el mundo del diseño y quieres desarrollarte en el área de Marketing dentro de una empresa en crecimiento, esta oportunidad es para ti.Tus principales responsabilidades serán:Diseñar, desarrollar y liderar propuestas de diseño gráfico e integral desde una perspectiva de branding 360°, fortaleciendo la identidad visual de la marca en todos sus puntos de contacto.Revisar, y entregar feedback sobre las piezas desarrolladas por el equipo creativo, asegurando el cumplimiento de los estándares de diseño y comunicación.Diseñar y Desarrollar piezas gráficas de alta complejidad  para distintos proyectos y canales de la compañíaConceptualizar, coordinar y participar activamente en sesiones fotográficas y producciones audiovisuales para campañas, e-commerce, redes sociales y otros canales.Realizar fotografías de productos, ambientes y contenido de marca, asegurando material visual de alta calidad para el sitio web, campañas y comunicaciones.Supervisar y optimizar la calidad visual del sitio web, proponiendo mejoras en imágenes, banners, recursos gráficos y presentación de productos para fortalecer la experiencia de compra.Apoyar al equipo de Visual Merchandising en terreno, levantando oportunidades y desarrollando materiales gráficos para una correcta implementación en tienda.Administrar y mantener actualizados los recursos gráficos, bibliotecas de imágenes, plantillas y activos visuales de la marca.Requisitos para postular:Formación en Diseño Gráfico o carrera afin1 año de experiencia en dirección de arte, branding y campañas creativasManejo avanzado de Adobe Creative Suite (Photoshop, Illustrator, InDesign, etc.).Experiencia en producción fotográfica y audiovisual (dirección de arte en shoots)Experiencia en dirección de arte, planificación y ejecución de sesiones fotográficas y producciones audiovisuales.Conocimiento en fotografía de producto, composición, iluminación y criterios visuales para e-commerce y redes sociales.Conocimiento en branding, identidad visual, desarrollo de key visuals y aplicación de brandbooks.Deseable experiencia en retail, visual merchandising y desarrollo de materiales para punto de venta.BeneficiosDías libres adicionales, sin límite anual, orientados a la flexibilidad laboral, sin goce de sueldo y previa coordinación con el equipo y la jefatura.Acceso a beneficios de la Asociación Chilena de Seguridad y Caja Los Andes.Seguro de salud complementario, aplicable a partir de la contratación indefinida.Beneficios para el hogar, con descuentos preferenciales en productos y servicios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>💼  Finance &amp; Administration Specialist</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Milimetrix</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Callao 2911, Las Condes, Chile</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/53554/finance-administration-specialist</t>
+        </is>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>1</v>
+      </c>
+      <c r="K218" t="n">
+        <v>1</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" t="n">
+        <v>0</v>
+      </c>
+      <c r="P218" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>Buscamos a nuestro/a próximo/aAnalista de Administración y Finanzaspara sumarse al equipo y apoyar el orden y control financiero de una empresa en etapa de crecimiento.Somos una consultora del rubromarketing digital &amp; e-commerce, que trabaja con marcas reconocidas a nivel nacional e internacional. Este rol será clave para asegurar una operación ordenada y mantener claridad en la información financiera para la toma de decisiones.Buscamos un perfil ordenado, confiable y con ganas de aprender, que quiera involucrarse en el día a día del área y entender cómo funciona la gestión financiera de una empresa dinámica.💼Principales responsabilidadesApoyar la gestión y control de contratos (clientes y proveedores)Llevar seguimiento del flujo de caja y apoyar en proyeccionesEjecutar y coordinar pagosApoyar la relación con contabilidad externa y procesos de cierrePreparar reportes básicos para el Gerente GeneralMantener orden y control de procesos administrativos internosApoyar en tareas financieras y operativas del día a día💡Lo que buscamosFormación en Contabilidad o carrera afínAl menos 1 año de experiencia en áreas de administración y/o finanzasAlto nivel de orden, responsabilidad y atención al detalleGanas de aprender y crecer en el áreaBuen manejo de ExcelCapacidad para trabajar de forma autónoma y organizadaBeneficiosModalidad: Híbrida 3x2 (Lunes, Miércoles y Jueves en oficina / Martes y Viernes remoto).Días libres por ocasión: Cumpleaños, mudanza, titulaciónFamilia: Licencias maternales y paternales extendidas (15 días adicionales). Los nuevos padres podrán trabajar de manera remota todas las tardes del primer medio año de vida de su nuevo integrante.Work from Anywhere: 3 semanas al año para trabajar 100% remoto; dos semanas son fijas (septiembre y Navidad/Año Nuevo) y una semana adicional es de libre elección.Vacaciones Premium: Si programas y te tomas 10 días de vacaciones consecutivos, ¡nosotros te regalamos un 11° día libre!Experiencia de equipo: actividades de equipo mensuales para fortalecer la colaboración y cultura interna.Make the dream: Después de cierto tiempo en la empresa, disfruta de hasta 6 meses sin goce de sueldo para perseguir ese sueño pendiente.Luna de miel prolongada: Añade 5 días extra a tu licencia matrimonial.Acompañamiento: Dos semanas libres en caso de pérdida de embarazo. Estamos contigo.Salud: Seguro complementario de salud, catastrófico y de vida sin costo.Convenio preferencial con MindFit Advanced, centro de entrenamiento ubicado en nuestro mismo edificio.Detalles del cargoUbicación: Las Condes, Santiago.Horario: Lun-Jue 09:00 - 18:15 hrs; Vie: 8:30 -16:30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q218"/>
+  <dimension ref="A1:Q222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15212,6 +15212,282 @@
         </is>
       </c>
     </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Práctica Riesgo de Crédito (Perfil Computacional) - Advisory</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>KPMG Chile</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Las Condes, Metropolitana, Chile, Chile</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55808/practica-riesgo-de-credito-perfil-computacional-advisory</t>
+        </is>
+      </c>
+      <c r="G219" t="n">
+        <v>10</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>machine learning, estadistica, matematica, informatica</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>1</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>1</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" t="n">
+        <v>1</v>
+      </c>
+      <c r="O219" t="n">
+        <v>0</v>
+      </c>
+      <c r="P219" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>¿A quién buscamos?Buscamos un/a estudiante proactivo/a y con marcada orientación tecnológica para unirse a nuestro equipo de Riesgo de Crédito en KPMG.El rol se enfoca en la automatización de procesos, scripting y manejo de datos, siendo fundamental para el desarrollo tecnológico y la optimización de flujos de trabajo.Formación AcadémicaEstudiantes de:Ingeniería Informática.Ingeniería en Computación.Ingeniería Matemática.Estadística.Ingeniería Industrial con fuerte orientación tecnológica.Habilidades TécnicasConocimientos prácticos enPython y/o Rpara desarrollo de scripts.Conocimiento enSQL(valorado).Interés y conocimientos básicos enautomatización, data pipelines y scripting.Conocimientos básicos enmachine learning(deseable).Competencias PersonalesProactividad.Curiosidad técnica.Capacidad de aprendizaje.Habilidad para resolver problemas.IdiomasInglés intermedio (deseable).¿Qué ofrecemos?Este puesto ofrece la oportunidad de aplicar y expandir tus habilidades en un entorno dinámico, contribuyendo a la mejora continua de procesos y al desarrollo de soluciones innovadoras en el área de Riesgo de Crédito.BeneficiosAprendizaje técnico avanzado y práctico.Exposición a herramientas de riesgo, automatización y analítica.Mentores y profesionales experimentados que te guiarán durante tu práctica.Desarrollar competencias tanto técnicas como interpersonales.Pertenecer a una organización de prestigio y trayectoria internacional. Ambiente laboral grato y profesional.Práctica Profesional remunerada.También podrás asistir a los “Meetings Point KPMG”, el cual es un encuentro exclusivo para profesionales de KPMG diseñado para pasarlo bien después del horario de oficina.🔎 Detalles de la práctica:Ubicación:Las Condes, Santiago Modalidad híbrida Horario: Lun–Jue: 9:00 a 18:00 Viernes: 9:00 a 13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Práctica Riesgo de Crédito (Perfil Analítico) - Advisory</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>KPMG Chile</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Las Condes, Metropolitana, Chile, Chile</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55807/practica-riesgo-de-credito-perfil-analitico-advisory</t>
+        </is>
+      </c>
+      <c r="G220" t="n">
+        <v>6</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>python, analisis, excel</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>1</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>1</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" t="n">
+        <v>1</v>
+      </c>
+      <c r="O220" t="n">
+        <v>0</v>
+      </c>
+      <c r="P220" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>¿A quién buscamos?Buscamos un/a estudiante proactivo/a y con un marcado interés por el análisis cuantitativo para unirse a nuestro equipo de Riesgo de Crédito en KPMG Chile.El/la candidato/a ideal será estudiante de:Ingeniería MatemáticaEstadísticaIngeniería IndustrialEconomíaIngeniería Comercial mención cuantitativaCarreras afinesCon un fuerte enfoque en la interpretación de datos y el entendimiento del negocio financiero.Principales responsabilidadesLas responsabilidades principales incluirán:Apoyo en análisis estadísticos.Exploración de datos.Preparación de bases para validación de modelos de riesgo.Participación en análisis macroeconómicos.Colaboración en proyectos de provisiones normativas (CMF, Basilea III, IFRS 9).Conocimientos deseablesSe valorará:Conocimiento básico en Python, R o software estadístico.Manejo intermedio de Excel.Competencias claveHabilidades analíticas sólidas.Capacidad de aprendizaje continuo.Motivación por el trabajo en equipo.Se considerará un nivel intermedio de inglés como un plus.¿Qué ofrecemos?Esta es una excelente oportunidad para desarrollar experiencia práctica en un entorno desafiante y de aprendizaje constante.BeneficiosOportunidad de trabajar en un entorno empresarial dinámico y colaborativo.Mentores y profesionales experimentados que te guiarán durante tu práctica.Desarrollar competencias tanto técnicas como interpersonales.Pertenecer a una organización de prestigio y trayectoria internacional. Ambiente laboral grato y profesional.Práctica Profesional remunerada.También podrás asistir a los “Meetings Point KPMG”, el cual es un encuentro exclusivo para profesionales de KPMG diseñado para pasarlo bien después del horario de oficina.🔎 Detalles de la práctica:Ubicación: Las Condes, Santiago Modalidad híbrida Horario: Lun–Jue: 9:00 a 18:00 Viernes: 9:00 a 13:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Práctica Profesional - Estudios y Clientes Marketing</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Ofi Cerro Colorado 5240 - Comercial, Chile</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55813/practica-profesional-estudios-y-clientes-marketing</t>
+        </is>
+      </c>
+      <c r="G221" t="n">
+        <v>2</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>1</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" t="n">
+        <v>1</v>
+      </c>
+      <c r="O221" t="n">
+        <v>0</v>
+      </c>
+      <c r="P221" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>Práctica Profesional - Estudios y Clientes Marketing🚀 ¡Buscamos a nuestro/a próximo/a practicante de Estudios y Clientes Marketing en la Gerencia de Marketing de Ripley!Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro.Ser parte de Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te motiva ser parte de un negocio desafiante y que tu práctica tenga impacto real? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Entender las necesidades, preferencias y comportamiento de los clientes de retail, permitiendo de esta forma segmentar y personalizar la experiencia, a la vez de levantar insights que permitan la toma de decisiones basadas en datos sólidos y actualizados para perfeccionar la oferta de valor, la propuesta comercial y la imagen de la marca.Funciones: 🤩Recopilar, limpiar, analizar e interpretar datos, para transformarlos en información de valor.Preparar instrumentos de medición (pautas) y supervisar terrenos de estudios de mercado, para que se ejecuten en calidad y tiempos esperados (cualitativos y cuantitativos)Levantar información de clientes al cierre de cada campaña (perfil de clientes, clientes nuevos, fuga, recurrentes, dormidos, etc).¿Qué estamos buscando? 💡Estudiante de Estudiante de Ingeniería Comercial, Estadístico, Civil o carrera afínContar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)Disponibilidad de 6 meses. (deseable posibilidad de extensión)Conocimiento en Excel.¿Por qué trabajar en Ripley? 🩷Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Administrador de Catálogo Web - Colina (Híbrido)</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Rosen</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55802/administrador-de-catalogo-web-colina-hibrido</t>
+        </is>
+      </c>
+      <c r="G222" t="n">
+        <v>2</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>1</v>
+      </c>
+      <c r="L222" t="n">
+        <v>1</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="n">
+        <v>0</v>
+      </c>
+      <c r="O222" t="n">
+        <v>0</v>
+      </c>
+      <c r="P222" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>📢¡Si te gusta la decoración, el mundo del descanso familiar, Rosen es para ti!Estamos buscando nuevos y nuevas RosenLovers que quieran ser parte de una de las mejores empresas para trabajar en Chile, ranking GPTW 2024. Buscamos el ADN Rosen en cada uno de nuestros/as colaboradores/as, potenciando la Excelencia, Integridad, Compromiso e Innovación.En Rosen creemos en el valor de las personas y en la riqueza de equipos diversos. Por eso, promovemos procesos de selección inclusivos y si necesitas algún ajuste para participar en el proceso, puedes indicarlo en tu postulación. Esta vacante se enmarca en nuestro compromiso con la inclusión laboral y la Ley 21.015.Actualmente nos encontramos en búsqueda de un/aAdministrador(a) de Catálogosa trabajar para nuestraGerencia de E-commerceen Modalidad Híbrida, en nuestras oficinas ubicadas en la comuna de Colina, Región Metropolitana.🔍¿Cuál es la misión de este rol?Gestionar la creación, actualización y publicación de productos y contenido comercial en los canales digitales de la compañía, velando por la calidad de la información y la correcta exhibición de la oferta de productos Rosen.💡¿Qué harás en este cargo?Gestionar la creación, actualización y publicación de productos y contenido comercial en los canales digitales de la compañía.Mantener actualizado el catálogo online, asegurando la correcta exhibición de productos, fichas técnicas, imágenes y categorías.Coordinar la actualización de contenidos y publicaciones con distintas áreas internas para garantizar una experiencia de compra consistente.Monitorear la correcta visualización y disponibilidad de los productos en el sitio web, realizando ajustes y mejoras cuando sea necesario.Detectar, reportar y dar seguimiento a incidencias del sitio web, contribuyendo a su correcto funcionamiento y a una óptima experiencia de usuario.📌¿Cuáles son los requisitos para rol?Título Técnico Profesional o estudios/cursos relacionados con canales digitales, eCommerce o gestión de contenidos web.Deseable experiencia en funciones relacionadas con canales digitales, eCommerce, administración de contenidos o gestión de información.Manejo de Excel nivel intermedio.Disponibilidad para trabajar en modalidad híbrida en Colina (4 días presencial, contamos con estacionamiento y buses de acercamiento).¡Te invitamos a ser parte de una compañía comprometida con sus colaboradores y la sustentabilidad!🌱🙌BeneficiosJornada laboral de 40 horas.Bono de vacaciones 🏝Aguinaldos.30% de descuentos en Productos Rosen.Seguro Complementario de Salud (desde contrato indefinido).Día Libre de Cumpleaños 🎈Regalos Corporativos 🎁Casino corporativo 🍝 y Buses de acercamiento.¡Entre muchos otros!</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q222"/>
+  <dimension ref="A1:Q228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15488,6 +15488,420 @@
         </is>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>ANALISTA DE EVALUACION DELITOS FINANCIEROS – PROYECTO</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>BCP</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55823/analista-de-evaluacion-delitos-financieros-proyecto</t>
+        </is>
+      </c>
+      <c r="G223" t="n">
+        <v>7</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>sql, excel, power bi</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="n">
+        <v>1</v>
+      </c>
+      <c r="M223" t="n">
+        <v>0</v>
+      </c>
+      <c r="N223" t="n">
+        <v>0</v>
+      </c>
+      <c r="O223" t="n">
+        <v>0</v>
+      </c>
+      <c r="P223" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>En el BCP todo lo hacemos distinto, lo hacemos al #ModoBCP. Por eso buscamos personas con tengan ganas de transformar el país y que disfruten desafiarse en grande para impactar en grande. Si eres una de ellas, podría ser nuestro siguienteANALISTA DE EVA. DELITOS FINANCIEROS.¿Cuál es el reto?Analizar las alertas de clientes BCP en base a un enfoque de riesgos considerando la normativa vigente en materia de Prevención de Lavado de Activos y Financiamiento del Terrorismo (PLAFT).¿Cómo impactarás en grande?Descartar e identificar nuevas señales de alertas de operaciones y transacciones monetarias inusuales de clientes, obtenidas mediante los sistemas automáticos o reportes de oficinas a nivel nacional, identificando patrones de comportamiento que se encuentran fuera del perfil habitual del cliente, teniendo en cuenta las autonomías del puesto.Evaluar las operaciones de clientes realizadas en cuentas y ventanilla, elaborando un informe que sustente la evaluación realizada.Consultar a clientes, funcionarios de negocios y otras áreas de la organización sobre operaciones inusuales de clientes con el objetivo de obtener información adicional y sustento documentario sobre las transacciones realizas a través de la institución.Revisar la documentación proporcionada por el cliente con el objetivo de hacer la debida diligencia y descartar la alerta generada.Administración a nivel usuario de aplicativos que contiene información de los clientes y las operaciones/transacciones bancarias que estos han realizado, como mecanismo o herramienta de consulta para la obtención de información relevante.¿Qué necesitamos de ti?Egresados(as) de las carreras de Administración, Economía, Contabilidad, a fines.Experiencia mínima de 1 año, como Asistentes o Analistas del equipo de PLAFT, Fraudes, Gestión Operativa, Auditoría y/o Riesgos.Conocimiento de Plaft, y herramientas de gestión de data.Manejo de Office Intermedio (Excel y Outlook).Manejo de Power BI, u otra herramienta de gestión de datos (SQL u otras)Beneficios¿Por qué unirte a nuestro equipo?Sé parte de la empresa #1 en Merco Talento 2026.Ambiente de trabajo retador: Únete a un entorno de trabajo donde tu voz importa y tus ideas impulsan el cambio.Recompensa a la medida: Disfruta de descuentos en productos financieros y +100 beneficios corporativos exclusivos para disfrutar con tu familia.Cultura que inspira: Vive una cultura constante de reconocimiento, donde tu talento impacta en grande desde el primer día.Crecimiento profesional: Disfruta de oportunidades de desarrollo continúo, respaldadas por un equipo comprometido con tu éxito.Accede a incentivos por tu esfuerzo/desempeño.¿Qué esperas? Postula hoy y ¡Únete al equipo BCP!“Somos una organización comprometida con la igualdad de derechos y oportunidades. Nuestros procesos de selección se rigen bajo una política donde nuestras/os postulantes son consideradas/os sin importar su origen, género, raza o cualquier otra característica, condición o preferencia, promoviendo así una cultura de respeto mutuo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Abogado</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>BCP</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55822/abogado</t>
+        </is>
+      </c>
+      <c r="G224" t="n">
+        <v>1</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>1</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="n">
+        <v>0</v>
+      </c>
+      <c r="O224" t="n">
+        <v>0</v>
+      </c>
+      <c r="P224" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>Buscamos a los que tienen ganas de transformar el país. A los que quieren llegar lejos. Por qué esto no es solo un trabajo. Esto es desafiarte en grande para impactar en grande. Esto es el BCP y te estamos buscando para que formes parte de nuestro equipo comoAbogado de la Unidad de Retenciones Judiciales de la Gerencia Procesal¿Cuál es el reto?Analizar y gestionar los requerimientos judiciales vinculados a embargos en forma de retención sobre cuentas y productos del Banco, identificando riesgos legales, definiendo criterios de actuación y proponiendo soluciones que aseguren el adecuado cumplimiento de los mandatos judiciales, protegiendo los intereses de la organización y contribuyendo a la mejora contínua de los procesos de la Unidad.¿Cómo impactarás en grande?Analizar requerimientos judiciales vinculados a medidas cautelares, especialmente embargos en forma de retención, determinando su alcance jurídico y operativo.Identificar, evaluar y mitigar riesgos legales derivados de la atención y ejecución de requerimientos judiciales notificados al Banco.Emitir instrucciones para la correcta ejecución de órdenes judiciales por parte de las áreas operativas involucradas.Absolver consultas especializadas relacionadas con cuentas y productos embargados.Dar soporte legal al equipo de embargos coactivos en temas vinculados a embargos amparados en la Ley de Procedimiento de ejecución coactiva, Código tributario, etc. y/o demanda de revisión judicial de legalidad.Hacer seguimiento al cumplimiento oportuno de los requerimientos judiciales.Contribuir a proyectos de automatización, transformación digital e inteligencia artificial del área¿Qué necesitamos de ti?Universitario Titulado en la carrera de Derecho2 años de experiencia profesionalcomo abogado en materias vinculadas a Derecho Procesal CivilExperiencia en análisis y gestión procesos judiciales civiles, preferentemente relacionados con Obligaciones de Dar Suma de Dinero, Medidas Cautelares y Ejecución de Garantías (incluyendo la elaboración de medidas cautelares, demandas, apelaciones, recurso extraordinario de casación, etc.)Experiencia en interpretación y análisis de resoluciones judiciales, identificación de riesgos legales y emisión de criterios jurídicos para la toma de decisiones.Experiencia en atención de consultas legales.Deseable experiencia en entidades bancarias, estudios de abogados especializados en litigios o área de asesoría legal con componente procesalDeseable experiencia participando en iniciativas de mejora de procesos, automatización y/o transformación digital.Office nivel intermedio o avanzado (deseable)Conocimiento en IA (deseable)Deseable maestría en Derecho Civil y/o Procesal Civil.Beneficios¿Por qué unirte a nuestro equipo?Ser parte de la empresa #1 en Merco Talento 2024.Ingreso a planilla BCP desde tu primer día.Accede a incentivos por tu esfuerzo/desempeñoAcompañamiento de líderes expertos y referentes en la banca.Acceso a descuentos en productos financieros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Analista Comex (reemplazoplazo fijo)</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Arcor</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Cerrillos, Chile</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55820/analista-comex-reemplazo-plazo-fijo</t>
+        </is>
+      </c>
+      <c r="G225" t="n">
+        <v>3</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>1</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" t="n">
+        <v>0</v>
+      </c>
+      <c r="O225" t="n">
+        <v>0</v>
+      </c>
+      <c r="P225" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>¿Te apasiona la logística, la coordinación de operaciones globales y el desafío de conectar mercados a través de una gestión eficiente y estratégica?EnArcorbuscamos unAnalista de Comex, quien será responsable de asegurar la correcta operación de los procesos de importación y exportación, coordinando múltiples actores internos y externos para garantizar el cumplimiento de los plazos, la normativa vigente y los estándares de servicio del negocio. Esta posición se basa en los perfiles de Importaciones y Exportaciones¿Cuál será tu misión?Gestionar integralmente las operaciones de comercio exterior, coordinando embarques, trámites aduaneros, documentación legal y comercial, proveedores logísticos, organismos reguladores y áreas internas, contribuyendo al abastecimiento y distribución internacional de productos de manera eficiente y oportuna.Principales desafíos:Coordinar procesos de importación y exportación, asegurando el cumplimiento de requisitos legales, aduaneros y documentales.Gestionar la emisión, revisión y control de documentación comercial y logística asociada a operaciones internacionales.Coordinar embarques con proveedores, agentes de aduana, navieras, transportistas y clientes internos.Realizar seguimiento de cargas desde origen hasta destino, monitoreando hitos críticos de cada operación.Mantener comunicación permanente con áreas comerciales, logística, programación, calidad y abastecimiento para asegurar el nivel de servicio comprometido.Elaborar reportes de gestión, indicadores y control de operaciones de comercio exterior.Gestionar contingencias operativas, reclamos, siniestros y requerimientos asociados a la cadena logística internacional.Requisitos:Formación en Comercio Exterior, Logística, Negocios Internacionales o carreras afines.Al menos 2 años de experiencia en operaciones de importación, exportación o logística internacional.Manejo de documentación aduanera, embarques marítimos y coordinación con proveedores logísticos.Excel avanzado como herramienta de análisis y control.Capacidad para organizar múltiples procesos simultáneamente y trabajar con un alto nivel de precisión.Orientación al cliente, habilidades de comunicación y capacidad para coordinar distintos stakeholders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Coordinador(a) de Atracción de Talento y Experiencia de Ingreso</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55835/coordinador-a-de-atraccion-de-talento-y-experiencia-de-ingreso</t>
+        </is>
+      </c>
+      <c r="G226" t="n">
+        <v>2</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>1</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0</v>
+      </c>
+      <c r="N226" t="n">
+        <v>0</v>
+      </c>
+      <c r="O226" t="n">
+        <v>0</v>
+      </c>
+      <c r="P226" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>Nos encontramos en búsqueda de un(a) profesional para integrarse al área de Personas de una compañía en constante crecimiento y transformación.La posición tendrá un rol clave en la gestión integral de los procesos de atracción de talento y experiencia de ingreso, asegurando una experiencia positiva para candidatos, nuevos colaboradores y clientes internos.Buscamos una persona autónoma, proactiva y orientada a la mejora continua, capaz de desenvolverse en entornos dinámicos, impulsar iniciativas y coordinar múltiples stakeholders de manera simultánea.Principales responsabilidadesCoordinar procesos de reclutamiento y selección para posiciones operativas y profesionales.Gestionar la relación y seguimiento con proveedores externos de reclutamiento.Asegurar una experiencia de selección ágil y positiva para candidatos y líderes.Coordinar integralmente el proceso de onboarding de nuevos ingresos.Gestionar actividades asociadas a ingresos, inducciones, equipamiento, beneficios y coordinación con áreas de soporte.Desarrollar y ejecutar iniciativas de marca empleadora.Proponer mejoras, automatizaciones y optimizaciones de procesos relacionados con atracción de talento y experiencia colaborador.Generar seguimiento de indicadores y métricas asociadas a los procesos bajo su responsabilidad.¿Qué buscamos?Profesionales titulados de Psicología, Ingeniería Comercial, Ingeniería en Administración o carreras afines.1-2 años de experiencia.Experiencia coordinando procesos de onboarding y gestión de ingresos.Experiencia trabajando con clientes internos y múltiples áreas.Manejo de Excel intermedio o avanzado.Deseable experiencia en iniciativas de marca empleadora, experiencia colaborador o mejora continua.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Ingeniero(a) de estudios actuariales</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>BNP Paribas Cardif</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Las Condes, Chile</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55825/ingeniero-a-de-estudios-actuariales</t>
+        </is>
+      </c>
+      <c r="G227" t="n">
+        <v>5</v>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>analisis, estadistica, power bi</t>
+        </is>
+      </c>
+      <c r="I227" t="n">
+        <v>1</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" t="n">
+        <v>1</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="n">
+        <v>0</v>
+      </c>
+      <c r="O227" t="n">
+        <v>0</v>
+      </c>
+      <c r="P227" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>Hoy BNP Paribas Cardif busca un(a) Ingeniero(a) de estudios actuariales quién será responsable de garantizar la rentabilidad de la compañía mediante análisis de negocios desarrollado en base a análisis económicos, de datos y evaluaciones técnico-financieras, respetando las políticas y procedimientos de la compañía.¿Cuáles son los principales desafíos del cargo?Analizar la rentabilidad de la cartera de productos y generar proyecciones de los diferentes negocios para entregar a la gerencia Comercial y técnico financiera las herramientas e informes para una correcta toma de decisiones.Seguimiento, estudio y control, de los diferentes riesgos que enfrenta la compañíaTarificar los diferentes seguros que vende la compañíaAsegurar, conocer y comprender las normas de cálculos de pasivos y márgenes de solvencia que afectan la rentabilidad de los productosProponer y mejorar las herramientas y modelos utilizados para la tarificación.Responsable de velar por la aplicación de los controles de Seguridad Financiera, establecidos en los diversos procedimientos operacionales del área.Perfil deseado¿Cómo saber si hago match con esta vacante? Buscamos a alguien que:Requisitos:a. Formación:Ingeniería civil industrial o comercial, estadística o afínb. Experiencia RequeridaNo necesita experiencia previac. Conocimientos y HabilidadesIngles avanzadoExcel avanzadoPower BI básico - medioPython medioAlta capacidad de análisis.Beneficios¿Cuáles son los beneficios y ventajas de trabajar con nosotros?Trabajamos eficientemente: 40 horas semanales en horarios flexibles y los viernes salimos a las 14:00.¡Tenemos más vacaciones y días libres! Una semana adicional de vacaciones + 1 día libre considerando tu cumpleaños y quehaceres personales.Apoyamos tu formación profesional: Acceso ilimitado a nuestra plataforma Coursera y dos días libres al año por estudios.Cardif te cuida: Contarás con telemedicina gratis, seguro de vida, de salud y dental.Queremos que seas tú mismo: Contamos con política de vestimenta flexible.Y muchos otros beneficios que podrás conocer al avanzar en nuestro proceso de selección¿Te sumas a la revolución de la industria del seguro?Esperamos tu postulación ¡seguro y con todo!Todas las contrataciones están sujetas a la ley 21015. En BNP Paribas Cardif creemos en lugares de trabajos inclusivos y diversos, donde todas las personas son bienvenidas. En caso de necesitar adaptaciones para ser parte de nuestro proceso de selección, favor comunicarlo en la sección de preguntas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Analista Suppy Chain</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Arcor</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Cerrillos, Chile</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55819/analista-suppy-chain</t>
+        </is>
+      </c>
+      <c r="G228" t="n">
+        <v>1</v>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="n">
+        <v>1</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" t="n">
+        <v>0</v>
+      </c>
+      <c r="O228" t="n">
+        <v>0</v>
+      </c>
+      <c r="P228" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>En Arcor buscamos un Analista Supply Chain para trabajar en nuestro Centro de Distribución ubicado en Cerrillos:Objetivo del cargo:El Analista de Supply Chain es responsable de crear, mantener y controlar indicadores clave de desempeño (KPIs) relacionados con logística y planificación, liderando además el proceso de revisión, control y seguimiento de los procesos del área para asegurar la eficiencia operativa y el cumplimiento de los objetivos estratégicos.Responsabilidades:Generar reportes de abastecimiento y gestión logística.Mantener actualizados los estados y maestros de productos.Crear, controlar y dar seguimiento a indicadores de Logística y Planeamiento.Revisar niveles de servicio y caducidad de productos.Calcular y mantener stocks de seguridad.Mantener actualizados los procesos del área.Liderar reuniones de revisión de nivel de servicio.Administración de KPIs de logística y planificación.Análisis de datos operacionales y generación de reportes para la toma de decisiones.Seguimiento de procesos logísticos y de planificación.Coordinación con Compras, Logística, Producción y Ventas.Identificación de oportunidades de mejora continua y automatización.Elaboración de reportes de abastecimiento nacional y comercio exterior.Seguimiento de stock, programación versus fabricación real y movimientos entre bodegas.Perfil deseadoCarreras requeridas:Ingeniería CivilIngeniería IndustrialIngeniería Comercial o carrera afínExperiencia:Entre 0 y 1 año.Competencias técnicasMicrosoft Office: Nivel 5 (avanzado)Manejo ERP: Nivel 3 (intermedio)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q228"/>
+  <dimension ref="A1:Q235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15902,6 +15902,481 @@
         </is>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Práctica profesional - Gerencia Riesgo y Cobranza - Área de Diseño Gráfico</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Ofi. Estado 91 - Producto Financiero, Chile</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55846/practica-profesional-gerencia-riesgo-y-cobranza-area-de-diseno-grafico</t>
+        </is>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" t="n">
+        <v>1</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0</v>
+      </c>
+      <c r="M229" t="n">
+        <v>0</v>
+      </c>
+      <c r="N229" t="n">
+        <v>1</v>
+      </c>
+      <c r="O229" t="n">
+        <v>0</v>
+      </c>
+      <c r="P229" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>🚀 ¡Buscamos a nuestro/a próximo/a Practicante de Diseño Gráfico para la Gerencia de Riesgo y Cobranzas de Banco Ripley! 💜Si te apasiona el diseño, la creatividad y la comunicación visual, esta es una excelente oportunidad para desarrollar tu talento y aportar a proyectos con impacto organizacional.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo:Apoyar la comunicación de iniciativas, proyectos y resultados de la gerencia mediante el desarrollo de piezas gráficas y materiales visuales que faciliten la comprensión y el impacto de los mensajes.Funciones: 🤩Diseñar propuestas gráficas para presentaciones ejecutivas y proyectos de la gerencia.Crear piezas visuales para comunicaciones digitales internas.Investigar tendencias y buenas prácticas de diseño para incorporar nuevas ideas y formatos.Apoyar la construcción de material visual para iniciativas estratégicas del área.Velar por la calidad gráfica y consistencia visual de las comunicaciones desarrolladas.¿Qué estamos buscando?💡Estudiante de Diseño Gráfico.Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)Disponibilidad mínima de 3 o 6 meses para realizar la práctica.Conocimientos de Adobe Illustrator e InDesign. (Excluyente)Creatividad, atención al detalle y habilidades de comunicación visual.Interés por el diseño corporativo y la presentación efectiva de información.¿Por qué trabajar en Banco Ripley? 💜Porque tendrás la oportunidad de desarrollar proyectos visibles, aportar nuevas ideas y potenciar tu creatividad en un entorno dinámico y colaborativo.En Ripley y Banco Ripley valoramos la diversidad e inclusión. En el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Práctica profesional - Gerencia Riesgo Financiero</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Ofi. Alonso De Cordova 5320 - Operaciones, Chile</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55865/practica-profesional-gerencia-riesgo-financiero</t>
+        </is>
+      </c>
+      <c r="G230" t="n">
+        <v>11</v>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>python, sql, analisis, estadistica, excel</t>
+        </is>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="n">
+        <v>1</v>
+      </c>
+      <c r="L230" t="n">
+        <v>0</v>
+      </c>
+      <c r="M230" t="n">
+        <v>0</v>
+      </c>
+      <c r="N230" t="n">
+        <v>1</v>
+      </c>
+      <c r="O230" t="n">
+        <v>0</v>
+      </c>
+      <c r="P230" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>🚀 ¡Buscamos a nuestro/a próximo/a Practicante para la Gerencia de Riesgo Financiero de Banco Ripley! 💜Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Banco Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro.Ser parte de Banco Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te interesa desarrollar modelos analíticos, trabajar con información financiera y participar en la gestión de riesgos de una institución financiera? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Apoyar al equipo de Riesgo Financiero en el análisis y monitoreo de riesgos de liquidez y mercado, participando en el desarrollo de metodologías internas, seguimiento de indicadores clave y validación de información regulatoria, contribuyendo a una gestión eficiente de los riesgos y a la sostenibilidad financiera del Banco.Funciones: 🤩• Apoyar en el desarrollo y mejora de metodologías internas para la medición y gestión de riesgos financieros.• Realizar seguimiento y análisis de los Indicadores Clave de Riesgo (KRI), apoyando el monitoreo de la exposición del Banco.• Colaborar en la validación y revisión de informes regulatorios y normativos.• Analizar bases de datos y generar reportes que apoyen la toma de decisiones del área.• Participar en iniciativas de mejora continua, automatización y optimización de procesos relacionados con la gestión de riesgos.¿Qué estamos buscando? 💡• Estudiante de Ingeniería Comercial, Ingeniería Civil, Estadística, Sociología o carrera afín.• Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)• Disponibilidad mínima de 3 meses para realizar la práctica.• Manejo de Excel.• Conocimientos de SQL.• Conocimientos de Python.• Interés por el análisis de datos, riesgo financiero, modelos analíticos y normativa bancaria.• Capacidad analítica, atención al detalle y orientación a la mejora continua.¿Por qué trabajar en Banco Ripley? 💜Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo. 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y, si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Práctica Profesional - Gerencia Control de Gestión y Medios - Planificación Financiera</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Ofi. Alonso De Cordova 5320 - Gerencia, Chile</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55859/practica-profesional-gerencia-control-de-gestion-y-medios-planificacion-financiera</t>
+        </is>
+      </c>
+      <c r="G231" t="n">
+        <v>5</v>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>analisis, excel, power bi</t>
+        </is>
+      </c>
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="n">
+        <v>1</v>
+      </c>
+      <c r="L231" t="n">
+        <v>0</v>
+      </c>
+      <c r="M231" t="n">
+        <v>0</v>
+      </c>
+      <c r="N231" t="n">
+        <v>1</v>
+      </c>
+      <c r="O231" t="n">
+        <v>0</v>
+      </c>
+      <c r="P231" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>🚀 ¡Buscamos a nuestro/a próximo/a Practicante para la Gerencia de Control de Gestión y Medios de Banco Ripley! 💜Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Banco Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro. Ser parte de Banco Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te motiva participar en la planificación financiera de una organización, analizar información clave para la toma de decisiones y generar impacto real en el negocio? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Apoyar al equipo de Control de Gestión y Medios en la planificación y control de costos operativos, participando en la elaboración presupuestaria, el monitoreo de indicadores y la generación de reportes de gestión que contribuyan a optimizar la eficiencia y apoyar la toma de decisiones estratégicas.Funciones: 🤩• Apoyar en la elaboración y consolidación del presupuesto 2027, recopilando, ordenando y analizando información proveniente de distintas áreas.• Realizar seguimiento y análisis de costos de servicios, identificando desviaciones y oportunidades de mejora en la gestión de gastos.• Generar reportes periódicos de gestión, indicadores de desempeño y control presupuestario para apoyar la toma de decisiones.• Colaborar en la automatización y mejora continua de reportes mediante herramientas como Excel y Power BI.• Participar en análisis financieros y en la elaboración de presentaciones de resultados para clientes internos.• Apoyar en el levantamiento, análisis y validación de información relevante para proyectos e iniciativas del área.• Contribuir a la optimización de procesos y generación de eficiencias mediante el análisis de datos y propuestas de mejora.¿Qué estamos buscando? 💡• Estudiante de Ingeniería Comercial, Ingeniería en Control de Gestión, Ingeniería en Administración y Finanzas, Contador Auditor o carrera afín.• Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)• Disponibilidad para realizar una práctica de 3 a 4 meses.• Manejo intermedio de Excel (tablas dinámicas, fórmulas y análisis de datos).• Conocimientos intermedios de Power BI.• Conocimientos en análisis de datos y control de gestión.¿Por qué trabajar en Banco Ripley? 💜Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo. 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y, si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Head of Sales</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>eDarkstore</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55858/head-of-sales</t>
+        </is>
+      </c>
+      <c r="G232" t="n">
+        <v>2</v>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" t="n">
+        <v>1</v>
+      </c>
+      <c r="L232" t="n">
+        <v>0</v>
+      </c>
+      <c r="M232" t="n">
+        <v>0</v>
+      </c>
+      <c r="N232" t="n">
+        <v>0</v>
+      </c>
+      <c r="O232" t="n">
+        <v>0</v>
+      </c>
+      <c r="P232" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>🚀 eDarkstore es una empresa de logística y tecnología que está revolucionando el mercado y la industria. Potenciamos los e-commerce a través de high tech y un equipo joven, entretenido y, por sobre todo, excepcional 🌟. Tenemos una fuerte cultura de innovación, y nos caracterizamos por una constante búsqueda de la excelencia y nuestra pasión por ofrecer un servicio extraordinario 💪. Si quieres tener una experiencia llena de aprendizajes 📚 y la oportunidad de generar cambios, ¡esta es tu oportunidad! 🙌 Súmate a esta empresa rupturista y buena onda 😎. Buscamos a un(a)Head of Salescon liderazgo, visión comercial y pasión por los resultados.🎯FuncionesProspectar y captar nuevos clientes y oportunidades de negocioLiderar y coordinar al equipo comercial para asegurar la ejecución de estrategias de ventaDesarrollar e implementar estrategias comerciales alineadas con los objetivos de la empresaGenerar reportes de cumplimiento de objetivos y rentabilidad de clientesAlinear los objetivos comerciales con las áreas de operaciones y tecnología (TI)Gestionar contratos con proveedores clave y distribuidoresApoyar la toma de decisiones estratégicas e identificar oportunidades de mejora continua✅Serás un buen match si eres/tienesTítulo en Ingeniería Comercial, Ingeniería Civil Industrial o carrera afín5 años de experiencia en roles de venta, liderando equipos comerciales y trabajando con metas.Dominio avanzado de Excel y manejo de CRM (Hubspot)Conocimiento en estrategias comerciales y negociación (deseable)Alta orientación a resultados, liderazgo, pensamiento analítico y proactividadBeneficios🌟 Hasta un 40% de descuento en Wild Lama, Wild Foods y Casa Nativa.🌟 1 día de home office a la semana de libre elección.🌟 Vestimenta informal.🌟 Y muchos más!</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Recién tituladoa para Coordinador hipotecario (PLAZO FIJO 3 Meses)</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Scotiabank</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55863/recien-titulado-a-para-coordinador-hipotecario-plazo-fijo-3-meses</t>
+        </is>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" t="n">
+        <v>1</v>
+      </c>
+      <c r="M233" t="n">
+        <v>0</v>
+      </c>
+      <c r="N233" t="n">
+        <v>1</v>
+      </c>
+      <c r="O233" t="n">
+        <v>0</v>
+      </c>
+      <c r="P233" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>Propósito:Ejecutar estrategias comerciales dirigidas a las inmobiliarias con las cuales se generan convenios, con la finalidad de entregar condiciones por volúmenes de operaciones dirigido a los distintos segmentos de negocios Retail Banking del Banco. Implementación, control, mantención, seguimiento y actualización de los convenios efectuados en su zona, administrando y fortaleciendo las relaciones de los convenios con las inmobiliarias. Asegurar la coordinación y calidad de atención de los Canales a las Inmobiliarias en Convenio.Responsabilidades:Apoyar y asesorar en la gestión de venta a los ejecutivos de Red de Sucursales y Fuerza de Ventas, mediante la oportuna entrega de listados de referidos campañables y el direccionamiento y asesoría ante consultas específicas relativas al producto.Seguimiento comercial y operativo de los proyectos financiados por el Banco.Concreción de nuevos convenios inmobiliarios. Coordinación, control y seguimiento de los convenios inmobiliarios vigentes locales como regionales.Coordinación con áreas de curse de las operaciones hipotecarias. (seguimiento para asegurar el correcto curse de las operaciones hipotecarias meta 99 días E2E, desde visado hasta la entrega de la escritura a la inmobiliaria)Trabajo en terreno con las inmobiliarias, visitar proyectos, visualizar sus potencialidades de cruce y calidad del servicio ofrecido sean estos proyectos encadenados y no encadenados, asegurando una atención y nivel de servicio excepcional que incluya las salas de ventas y en permanente coordinación con Sucursales y FFVV.Preparar información para controlar y efectuar el seguimiento de metas de convenios inmobiliarios y proyectos encadenados. Generación de Informes de visita y control de gestión.Analizar periódicamente la competencia regional investigando los productos y servicios que tienen respecto a los nuestros, buscando ofertas, nuevos productos, nuevos atributos y nuevas prácticas que mejoren nuestro servicio (incorporar Bench en las planillas de seguimiento y control de proyectos).Participar en reuniones con los ejecutivos de la banca inmobiliaria.Realizar actividades de capacitación periódicas tanto en canales internos como externos del banco sobre los productos y servicios a cargo.Contribuir al clima laboral dentro de la unidad, aplicando los valores del grupo Scotiabank facilitando el trabajo en equipo y contribuyendo a su desarrollo de carrera.Participar activamente en sesiones de coaching programadas por su jefatura.Participación en ferias inmobiliarias y eventos de la industria, así como en eventos del área con las inmobiliarias.Adecuado manejo del presupuesto y control de gastos de la operación sobre cada convenio.Requisitos:Titulado/a de Ingeniería Comercial o carrera a fin.Interés y motivación por el área comercial en banca.Manejo de Office nivel usuarioBeneficios¿Por qué elegirnos? 👀👀💻 Somos un Banco en proceso de modernización y digitalización.⏱ Equilibrio de vida personal y laboral. ¡Primer banco en reducir la jornada a 39 horas!💡 Grandes oportunidades de movilidad interna. ¡Queremos que crezcas y te desarrolles profesionalmente!📚 Educación y aprendizaje continuo: participa en proyectos, conferencias y eventos para desarrollar nuevas habilidades y conocimientos relevantes.🛫 Posibilidad de trabajar en proyectos con equipos de otros países, ya que potenciamos el intercambio de ideas.🎁 Excelentes beneficios: elige tus días libres, elige cómo distribuir tus bonos, convenios de salud y educación.🌈 Somos diversos e inclusivos.En Scotiabank, la inclusión es parte de nuestra forma de hacer banca 💜. Esta postulación está abierta conforme a la Ley 21.015. Si necesitas algún ajuste razonable para participar en el proceso, cuéntanos 🤝.¡No dudes en postular, únete a este viaje y sé nuestro próximo/a Scotiabanker!</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Talent &amp; Culture Assistant Retail</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Belcorp</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Quilicura, Chile</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55845/talent-culture-assistant-retail</t>
+        </is>
+      </c>
+      <c r="G234" t="n">
+        <v>2</v>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" t="n">
+        <v>1</v>
+      </c>
+      <c r="M234" t="n">
+        <v>0</v>
+      </c>
+      <c r="N234" t="n">
+        <v>0</v>
+      </c>
+      <c r="O234" t="n">
+        <v>0</v>
+      </c>
+      <c r="P234" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>¿Buscas un nuevo desafío en el mundo del Retail? ¿Te apasiona la coordinación, el trabajo en equipo y brindar una excelente experiencia a las personas? ¡Entonces esta oportunidad es para ti!Somos una empresa omnicanal y líder en el rubro de la venta directa, con presencia en 14 países de la región. Nos dedicamos a la comercialización de cosméticos a través de nuestras marcasL'BEL, Ésika y Cyzone, presentes en los canales de Venta Directa, E-commerce y Retail.En esta oportunidad buscamos un(a)Asistente Retailpara integrarse a nuestro equipo en unproyecto a plazo fijo de 3 meses, apoyando la gestión administrativa y operacional del área, y contribuyendo al cumplimiento de nuestros objetivos de negocio.Como parte de nuestro equipo de Retail, tendrás un rol clave en el soporte y coordinación de los principales procesos del área. Entre tus principales responsabilidades estarán:Liderar los procesos de reclutamiento, selección y contratación de posiciones de Retail. Apoyar el proceso de incorporación y la gestión administrativa de los nuevos colaboradores de Retail.Gestionar solicitudes administrativasCoordinar y dar seguimiento a la gestión de proveedores, cotizaciones y órdenes de compra.Elaborar, analizar y dar seguimiento a los principales indicadores de gestión del área, tales como rotación, headcount, dotación, vacantes, cobertura de posiciones y otros KPI de Retail, generando reportes que apoyen la toma de decisiones.Perfil deseadoTítulo Técnico o Profesional en Administración de Empresas, Ingeniería en Administración, Ingeniería Comercial o carrera afín.Deseable manejo de Excel nivel intermedio.Deseable experiencia utilizando SAP u otro ERP.Alta capacidad de organización, planificación y seguimiento.Proactividad, orientación al cliente interno y excelentes habilidades de coordinación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Trainee de Inversiones AFP PlanVital 2026</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>AFP Plan Vital</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Las Condes, Metropolitana, Chile</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55844/trainee-de-inversiones-afp-planvital-2026</t>
+        </is>
+      </c>
+      <c r="G235" t="n">
+        <v>16</v>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>python, sql, analisis, trainee, excel</t>
+        </is>
+      </c>
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="n">
+        <v>1</v>
+      </c>
+      <c r="L235" t="n">
+        <v>0</v>
+      </c>
+      <c r="M235" t="n">
+        <v>0</v>
+      </c>
+      <c r="N235" t="n">
+        <v>0</v>
+      </c>
+      <c r="O235" t="n">
+        <v>1</v>
+      </c>
+      <c r="P235" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>¡Invierte en tu carrera con nosotros!Si eres recién egresado/a y te apasionan los mercados financieros, el análisis y la toma de decisiones basada en datos, queremos ayudarte a explorar tu potencial.En AFP PlanVital estamos buscando a jóvenes profesionales (recién egresados) que quieran desarrollar su carrera en una de las gerencias más estratégicas de nuestro negocio.Diseñamos este programa para acelerar tu aprendizaje, exponerte a desafíos reales y entregarte las herramientas para construir una carrera de largo plazo en inversiones.Durante tus primeros 12 meses conocerás de cerca cómo funciona una de las áreas más desafiantes del negocio, participando en procesos vinculados a Renta Fija y Renta Variable. Aprenderás junto a especialistas del área, conocerás distintas perspectivas del proceso de inversión y desarrollarás habilidades técnicas que te permitirán acelerar tu crecimiento profesional.Más que experiencia previa, buscamos personas con:Curiosidad por entender cómo funcionan los mercadosCapacidad analítica y pensamiento críticoGanas de aprender, desafiarse y crecer profesionalmenteMotivación por construir una carrera en inversiones¡La próxima generación de inversiones comienza aquí!Requisitos Candidato/aIng. Comercial o Civil con mención en economía o finanzasManejo de Office (Word, Excel, Power Point)Ideal conocimientos en programación (Python, SQL u otros)Esta oferta es apta para personas en situación de discapacidad.Beneficios¿Qué hace diferente a este programa?Contrato indefinido desde tu ingresoAprendizaje en procesos de distintas áreasAcompañamiento permanente a través de mentoríaFormación especializada en mercado financiero, Bloomberg, Python y herramientas de análisisParticipación en proyectos reales que están transformando la industria previsionalPosibilidad de especializarte y proyectar tu carrera dentro de la Gerencia de Inversiones</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q235"/>
+  <dimension ref="A1:Q240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16377,6 +16377,347 @@
         </is>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Analista de Gestión Comercial</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Entel Perú</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55895/analista-de-gestion-comercial</t>
+        </is>
+      </c>
+      <c r="G236" t="n">
+        <v>5</v>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>modelo, excel</t>
+        </is>
+      </c>
+      <c r="I236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0</v>
+      </c>
+      <c r="L236" t="n">
+        <v>1</v>
+      </c>
+      <c r="M236" t="n">
+        <v>0</v>
+      </c>
+      <c r="N236" t="n">
+        <v>0</v>
+      </c>
+      <c r="O236" t="n">
+        <v>0</v>
+      </c>
+      <c r="P236" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>¿Te mueve colaborar, desafiar y crecer con propósito? Conoce que desafíos te esperan como Analista de Gestión ComercialGestión Comercial: Monitorear diariamente el embudo de ventas desde la prospección hasta la conversión (instalación) para identificar oportunidades de mejora en la gestión de los socios de negocio e implementarlas.Soporte y Capacitación al Canal Externo: Ser el punto de contacto para los dueños y supervisores de las fuerzas de ventas terceras, resolviendo dudas sobre el proceso de ventas y modelo de negocio.Optimización y Automatización de Flujos: Implementar soluciones que nos ayuden a optimizar los flujos operacionales con herramientas de tecnología o propuestas de flujos.Control de Gestión (BI): Apoyar y coordinar la elaboración de dashboards para el seguimiento de ventas e instalaciones para optimizar la toma de decisiones en el día a día.Coordinación con las áreas de agendamiento e instalaciones para la correcta conversión de las órdenes de venta.Validación de la actividad comisional de los socios de negocio.Garantizar el cumplimiento del marco normativo de seguridad de la información definido dentro de la organización.Brindar los recursos necesarios para el cumplimiento del modelo de prevención de delitos y facilitar la información requerida para la identificación de riesgos del MPD en su área correspondiente.Cumplir y hacer cumplir, por sus equipos de trabajo, los lineamientos establecidos en los sistemas de gestión implementados y/o certificados.Participar activamente en el desarrollo, implementación y mejora de los sistemas de gestión, y fomentarlo en sus equipos de trabajo.RequisitosBachiller o egresado en Ing. Industrial, Administración o afinesConocimiento de Excel a nivel avanzadoManejo de herramientas de IA generativaExperiencia en áreas comerciales, planeamiento u operaciones (deseable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Ejecutivo de Negocios  Banca Persona</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>BCP</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55891/ejecutivo-de-negocios-banca-persona</t>
+        </is>
+      </c>
+      <c r="G237" t="n">
+        <v>2</v>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" t="n">
+        <v>0</v>
+      </c>
+      <c r="L237" t="n">
+        <v>1</v>
+      </c>
+      <c r="M237" t="n">
+        <v>0</v>
+      </c>
+      <c r="N237" t="n">
+        <v>0</v>
+      </c>
+      <c r="O237" t="n">
+        <v>0</v>
+      </c>
+      <c r="P237" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>Buscamos a los que tienen ganas de transformar el país. A los que quieren llegar lejos. Por qué esto no es solo un trabajo. Esto es desafiarte en grande para impactar en grande. Esto es el BCP y te estamos buscando para que formes parte de nuestro equipo comoEjecutivo de Negocios Bex Digital.¿Cuál es el reto?Construir relaciones a largo plazo con los clientes a través de la efectiva gestión comercial de su cartera. Es responsable de interactuar con los clientes a través del servicio ágil y construir relaciones duraderas.¿Cómo impactarás en grande?Gestionar y desarrollar una cartera de clientes, identificando oportunidades de negocio y fortaleciendo relaciones de largo plazo.Brindar atención y asesoría remota, ofreciendo soluciones financieras de acuerdo con las necesidades de cada cliente.Impulsar la venta cruzada de productos y servicios para incrementar la vinculación y fidelización del clienteRealizar seguimiento permanente a la cartera, asegurando una experiencia ágil, una atención oportuna y altos niveles de satisfacción.Elaborar propuestas comerciales y resolver consultas o requerimientos, cumpliendo las políticas y lineamientos del banco.¿Qué necesitamos de ti?Egresado(a) universitario(a) de carreras afines a Banca, Administración, Economía, Negocios o similares.Experiencia mínima de 1 año en posiciones comerciales dentro de banca, financieras, cajas, seguros, fintech o empresas relacionadas.Experiencia en gestión de cartera de clientes, venta de productos financieros y cumplimiento de metas comerciales.Disponibilidad para laborar de manera presencial en Surquillo o San Isidro, de lunes a viernes de 8:30 a.m. a 6:00 p.m. y sábados de 8:30 a.m. a 1:00 p.mManejo de Excel a nivel intermedio¿Por qué unirte a nuestro equipo?Ser parte de la empresa #1 en Merco Talento 2025.Ingreso a planilla BCP desde tu primer día.Accede a incentivos por tu esfuerzo/desempeñoAcompañamiento de líderes expertos y referentes en la banca.Acceso a descuentos en productos financieros.Beneficios corporativos exclusivos por provincia para disfrutar con tu familia.Formarás parte de una cultura constante de reconocimientosSí, a ti. Te estamos buscando ¡Únete al equipo BCP!“Somos una organización comprometida con la igualdad de derechos y oportunidades. Nuestros procesos de selección se rigen bajo una política donde nuestras/os postulantes son consideradas/os sin importar su origen, género, raza o cualquier otra característica, condición o preferencia, promoviendo así una cultura de respeto mutuo"</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Ejecutivoa de Gestión y Ahorro UBM</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Clickie</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55897/ejecutivo-a-de-gestion-y-ahorro-ubm</t>
+        </is>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" t="n">
+        <v>1</v>
+      </c>
+      <c r="M238" t="n">
+        <v>0</v>
+      </c>
+      <c r="N238" t="n">
+        <v>0</v>
+      </c>
+      <c r="O238" t="n">
+        <v>0</v>
+      </c>
+      <c r="P238" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>¡Estamos contratando! Ejecutivo/a de Gestión y Ahorro UBMUbicación:PresencialEquipo:Utility Bill Management (UBM)Tipo de contrato:Jornada completaReporta a:Responsable del Servicio de UBMSobre ClickieEn Clickie ayudamos a nuestros clientes a tomar el control de sus servicios públicos, generando ahorros reales y tangibles a través de la gestión inteligente de sus datos y contratos. Somos un equipo que combina tecnología congestión en terreno de alto impacto— y buscamos sumar a alguien que disfrute salir a resolver, negociar y conseguir resultados concretos cara a cara con los actores que hacen posible el ahorro.El rolBuscamos un/aEjecutivo/a de Gestión y Ahorro UBMpara sumarse a nuestro equipo de Utility Bill Management. Este rol es, ante todo, unrol de campo: la persona será responsable de ejecutar las gestiones administrativas y comerciales —cambios de titularidad, optimización de tarifas y potencia, reclamos, entre otras— mediantepresencia activa y negociación directa in situcon tres actores clave de la operación:Distribuidorasde servicios públicosInmobiliariasMalls y centros comercialesEn Clickie tenemos una convicción clara:los ahorros significativos no se generan desde un escritorio, se generan en terreno.Cada nudo de gestión que se destraba, cada tarifa que se optimiza y cada reclamo que se resuelve es el resultado directo de estar físicamente presentes, construyendo relación y negociando cara a cara con quienes toman las decisiones del otro lado de la mesa.Si te motiva salir a terreno, tienes carácter para negociar en persona y sabes que los resultados se construyen con presencia y persistencia, este rol es para ti.¿Qué harás?Desplegarte activamente en terreno para gestionar directamente condistribuidoras, inmobiliarias y malls/centros comerciales, construyendo relaciones de confianza que faciliten cada negociación.Analizar información de clientes (ya digitalizada y validada por nuestro equipo de Datos) para identificar oportunidades concretas de ahorro y priorizar tu agenda de gestión en terreno.Ejecutar negociaciones cara a cara e in situ ante compañías proveedoras y actores clave, complementando —cuando corresponda— con llamadas, portales de gestión y comunicaciones formales.Dar seguimiento activo y presencial a cada gestión iniciada hasta su cierre efectivo, destrabando nudos operativos que solo se resuelven con presencia física y persistencia en el lugar.Presentar y gestionar reclamos directamente ante proveedores, inmobiliarias y malls cuando se detecten cobros indebidos o incumplimientos contractuales, escalando la conversación en terreno cuando sea necesario.Validar y reportar el ahorro real generado en cada caso cerrado, dejando trazabilidad de cómo la gestión en terreno se tradujo en resultado económico.Mantener actualizado el estado de cada cliente/caso en nuestros sistemas de gestión.Escalar oportunamente casos complejos o bloqueos regulatorios a la Responsable de UBM, con el contexto directo que solo da estar presente en la operación.Colaborar de cerca con el equipo de Digitalización y Calidad de Datos para resolver inconsistencias que puedan frenar una gestión en terreno.Lo que buscamos en tiExperiencia previa en gestión comercial, administrativa o de trámitescon trabajo de campo/terreno: visitas, negociación presencial, relacionamiento con proveedores, inmobiliarias, administraciones de malls o actores similares.Disposición real y disfrute genuino por el trabajo en terreno: esto no es un rol de oficina, es un rol de presencia activa en la operación.Excelente capacidad de negociación presencial y manejo de objeciones cara a cara.Firmeza, proactividad y capacidad de generar y sostener relaciones con contrapartes clave (distribuidoras, inmobiliarias, malls).Organización y capacidad de gestionar múltiples casos y visitas en paralelo sin perder el detalle de cada uno.Comunicación asertiva, tanto en la negociación in situ como en la redacción formal de reclamos y comunicaciones.Orientación a resultados: te motiva cumplir metas y ver el impacto de tu gestión en terreno reflejado en números concretos de ahorro.Persistencia y buena tolerancia a la frustración — las gestiones con proveedores externos no siempre son rápidas, y saber sostener el seguimiento en terreno sin perder el foco.Disponibilidad para desplazamiento frecuenteManejo de herramientas de gestión/CRM (deseable, no excluyente).Deseable (no excluyente):Conocimiento previo del mercado de servicios públicos (tarifas, actores del sector, regulación).Experiencia previa relacionándote en terreno con distribuidoras, inmobiliarias o administraciones de malls/centros comerciales.Experiencia en roles comerciales o de negociación B2B/B2C con componente presencial.¿Te interesa?Envíanos tu CV a[email protected]</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Product Onboarding Analyst</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Keirón</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55893/product-onboarding-analyst</t>
+        </is>
+      </c>
+      <c r="G239" t="n">
+        <v>7</v>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>sql, informatica, excel</t>
+        </is>
+      </c>
+      <c r="I239" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" t="n">
+        <v>1</v>
+      </c>
+      <c r="L239" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" t="n">
+        <v>0</v>
+      </c>
+      <c r="N239" t="n">
+        <v>0</v>
+      </c>
+      <c r="O239" t="n">
+        <v>0</v>
+      </c>
+      <c r="P239" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>Sobre Keirón 🩺En Keirón trabajamos para que ningún paciente se pierda en el sistema de salud. Somos unaHealthTechlatinoamericana que acompaña a clínicas, hospitales y centros de salud en cada etapa del viaje del paciente, desde que agenda una hora hasta que resuelve su problema de salud, reduciendo esperas, errores y desgaste tanto para los pacientes como para los equipos clínicos.Con presencia en Chile, México, Colombia y Perú, y millones de atenciones coordinadas a través de nuestra plataforma. Detrás de cada mejora en un proceso hay algo muy concreto: menos tiempo de espera, más claridad para un paciente, y un equipo clínico que puede enfocarse en dar la mejor atención.Nuestro equipo de OnboardingEn Onboarding traducimos el producto en una implementación exitosa: levantamos los flujos de cada cliente, los configuramos en la plataforma y validamos que funcionen en la operación real.En el equipo estamos buscando a nuestr@ siguienteProduct Onboarding Analyst:  alguien organizado/a, con mirada de proceso completo, cómodo/a manejando varios proyectos en paralelo y conversando tanto con clientes como con equipos de Producto y Tecnología, y con ojo analítico para detectar mejoras y automatizar procesos 🚀.¿Qué tendrás que hacer? 👀Levantar y modelarflujos operativos de nuevos clientes, configurándolos y adaptándolos correctamente en la plataforma.Diseñar y ejecutarel proceso de onboarding end-to-end, asegurando una implementación correcta y oportuna (levantamiento, configuración y capacitación).Detectar, documentar y escalarincidencias y oportunidades de mejora, tanto de implementación como de producto.Comunicaraprendizajes y feedback de clientes hacia los equipos de Producto y Tecnología, contribuyendo a la evolución del producto.Analizar, estandarizar y automatizarinformación y procesos de onboarding, proponiendo mejoras continuas en eficiencia y adopción.Habilidades técnicas deseadas ✨Conocimientos básicos en bases de datos (PostgreSQL, MySQL o similares).Capacidad para realizar consultas SQL simples (SELECT, JOIN, filtros, validaciones).Manejo intermedio de Excel / Google Sheets (tablas dinámicas, fórmulas, filtros).Deseable familiaridad con herramientas de gestión de proyectos y CRM (Jira, HubSpot u otras).Deseable conocimiento en APIs, Webhooks e integraciones con sistemas externos (CRM, ERP, etc.) o interés en aprender y profundizar en estos conceptos.¿Qué esperamos de ti?Formación en Ingeniería Industrial, Informática, Gestión de Proyectos TI o carreras afines (a partir de 1 año de experiencia en roles similares).Deseable experiencia previa enstartupsoentornos de rápido crecimiento.Habilidades decomunicación efectiva,con foco en interacción con clientes y equipos internos.Capacidad deorganización, planificación y gestión del tiempopara manejar múltiples onboardings en paralelo.Perfil analíticoy orientado al detalle, con capacidad para detectar incidencias y oportunidades de mejora.Proactividadyautonomíapara ejecutar tareas y dar seguimiento.Capacidad para trabajarcolaborativamentecon equipos de Producto, Tecnología y Customer Success.BeneficiosAl pasar a contrato indefinido podrás acceder a:Seguro complementario de saludHerramienta de trabajo7 viernes libres al añoMedio día de cumpleaños (más otros detallitos)3 primeros días de licencia pagadosCultura de innovación, impacto y colaboración</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Analista de Normas y Análisis Financiero</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>BICE</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55886/analista-de-normas-y-analisis-financiero</t>
+        </is>
+      </c>
+      <c r="G240" t="n">
+        <v>1</v>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I240" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>1</v>
+      </c>
+      <c r="L240" t="n">
+        <v>1</v>
+      </c>
+      <c r="M240" t="n">
+        <v>0</v>
+      </c>
+      <c r="N240" t="n">
+        <v>0</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0</v>
+      </c>
+      <c r="P240" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>¡En BICE te estamos buscando!Creemos firmemente que los colaboradores son nuestro principal activo. Por eso, nos preocupamos de ofrecer oportunidades que potencien su desarrollo integral. Apostamos por profesionales apasionados, innovadores, creativos y con ganas de aprender y crecer.¿Nuestro propósito? Impulsamos tu bienestar creando una experiencia financiera única con sello humano.Te invitamos a ser parte de BICE, donde buscamos a un Analista de Normas y Análisis Financiero para nuestra División de Planificación y Control Financiero.¿Cuáles serán tus principales responsabilidades?Elaborar explicaciones “de negocio” para las principales variaciones de los EEFF, tanto a nivel mensual, trimestral y anual.Comprender y explicar los efectos de mercado (inflación, alzas y bajas de tasas de interés, variaciones del valor razonable de instrumentos financieros, etc).Elaborar presentaciones ejecutivas a requerimiento específicos sobre temas propios del área.Realizar exposiciones internas a la Gerencia de Contabilidad.Analizar y estudiar la estrategia de fondeo e inversión del Banco y sus impactos contables.Apoyar la revisión de EEFF trimestrales y anuales.Elaborar documentos técnicos a requerimiento de la jefatura.¿Qué buscamos?Título de Contador auditor o Ingeniero Comercial, deseable especialización en finanzas corporativas.Ideal experiencia de 1 a 2 años en cargos similares dentro de la industria bancaria (también podría ser recién titulado).Ideal conocimientos en norma IFRS, CMF y del BCCh (deseable).Ideal conocimientos sobre regulación de la industria bancaria como por ejemplo Recopilación Actualizada de Normas, Compendio de Normas Contables para bancos, Basilea III, entre otros. (excluyente)Ideal conocimientos sobre valoración de instrumentos financieros y finanzas corporativas (deseable).Capacidad analítica, trabajo en equipo y bajo presión.Orientación al cumplimiento de tareas y logro de objetivos.Conocimiento SAP (deseable).Postula con nosotros!!Beneficios🏢 Modalidad de trabajo según rol: Algunas posiciones acceden a un sistema híbrido, mientras que las áreas comerciales operan 100% de forma presencial.🍽️ Almuerzo diario cubierto: Si trabajas en casa matriz, accedes al casino corporativo con almuerzo gratuito. Si estás en una sucursal, se te asigna un monto diario para cubrir este gasto.🛍️ Descuentos exclusivos y convenios: Acceso a beneficios con diversas empresas asociadas en áreas como salud, retail, entretenimiento y más.⚽ Actividades internas: Participación en torneos deportivos, actividades lúdicas, operativos oftalmológicos y otras instancias que promueven el bienestar.🤝 Cultura cercana y participativa: Ser parte activa de un entorno laboral colaborativo, donde se vive la cultura organizacional día a día.🩺 Seguros complementarios: Cobertura en salud, dental y de vida, para que cuentes con mayor respaldo y tranquilidad.🐾 Seguro para mascotas: Protección adicional para tus compañeros de cuatro patas.🏋️ Convenio con gimnasios: Accede a tarifas preferenciales para mantenerte activo y saludable.🎓 Formación continua: Convenios y descuentos con instituciones educativas para diplomados, cursos y otros programas de desarrollo profesional.🚲 Acceso a bicicletero: Estacionamiento seguro para bicicletas en casa matriz.🅿️ Convenio de estacionamientos: Tarifas preferenciales en estacionamientos cercanos.📱 Convenio con Entel: Descuentos en planes y equipos móviles.🦷 Red de centros odontológicos: Acceso a múltiples convenios para atención dental.🎁 Bonos diversos: Incluye bonos por escolaridad, fallecimiento, vacaciones, invierno, excelencia académica, aguinaldos de Fiestas Patrias y Navidad, entre otros.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q240"/>
+  <dimension ref="A1:Q248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16718,6 +16718,558 @@
         </is>
       </c>
     </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Ingeniero BI Tecnología Minera</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Ferreyros</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55911/ingeniero-bi-tecnologia-minera</t>
+        </is>
+      </c>
+      <c r="G241" t="n">
+        <v>12</v>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>python, sql, estadistica, cloud, gcp</t>
+        </is>
+      </c>
+      <c r="I241" t="n">
+        <v>1</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0</v>
+      </c>
+      <c r="L241" t="n">
+        <v>1</v>
+      </c>
+      <c r="M241" t="n">
+        <v>0</v>
+      </c>
+      <c r="N241" t="n">
+        <v>0</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
+      <c r="P241" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>Misión del puestoEjecutar actividades de implementación y soporte a los procesos de flujos y entrega de datos operacionales para facilitar la toma de decisiones, mediante el trabajo coordinado con las áreas operativas y de desarrollo, asegurando siempre los estándares técnicos de la organización.FuncionesGestión de Datos Operacionales: Limpieza, integración y contextualización de datos de campo para garantizar información confiable a Ferreyros y sus clientes.Modelado y Visualización: Analizar la lógica de negocio para implementar flujos de datos y dashboards bajo estándares de la empresa.Diseño y Soporte: Apoyar en el diseño de soluciones de datos, brindando soporte preventivo y correctivo a las herramientas desplegadas para asegurar la continuidad operativa.Capacitación y Adopción: Asistir en la creación y ejecución de capacitaciones técnicas para usuarios finales.Cumplir con la normativa legal y estándares internos en materia de SSMA (Seguridad, Salud y Medio Ambiente).RequisitosBachiller o Titulado/a en Ing. Electrónica, Mecatrónica, Sistemas, Industrial, Minas, Estadística o carreras afines.2 años de experiencia de laboral.Dominio Técnico Sólido en Python para Data Engineering, SQL avanzado y  Power BI u otras herramientas de visualización de Business Intelligence.Conocimiento de Google Cloud Platform (GCP) orientado a arquitectura e integración de datos.Manejo de Inglés (intermedio/avanzado).Disponibilidad para laborar de forma presencial en Cercado de Lima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>GESTOR COMERCIAL BANCA EMPRESAS I PER</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>BBVA Perú</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Huancayo, Perú</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55910/gestor-comercial-banca-empresas-i-per</t>
+        </is>
+      </c>
+      <c r="G242" t="n">
+        <v>3</v>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I242" t="n">
+        <v>1</v>
+      </c>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" t="n">
+        <v>1</v>
+      </c>
+      <c r="M242" t="n">
+        <v>0</v>
+      </c>
+      <c r="N242" t="n">
+        <v>0</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+      <c r="P242" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>¿Quieres desarrollar tu carrera profesional?BBVA es una empresa global con más de 160 años de historia que opera en más de 25 países en los que damos servicio a más de 80 millones de clientes. Somos más de 121.000 profesionales que trabajamos en equipos multidisciplinares y de perfiles tan diversos como financieros, expertos jurídicos, científicos de datos, desarrolladores, ingenieros o diseñadores.Nuestra gente marca la diferencia en nuestro éxito.Tipo de Contrato:Regular (Indefinido)¿Qué estamos buscando?Lo que harás:Solicitar información actualizada de los balances, estados de pérdidas y ganancias, conformación de la empresa, accionistas, ejecutivos, y otros documentos a los clientes para la posterior evaluación de riesgos.Obtener información sobre la competencia, proveedores, formas de pago, créditos, etc.Efectuar el análisis del mercado, proyecciones, comportamiento productivo, ventas, créditos otorgados, etc.Efectuar el análisis de su posición en el sistema financiero, responsabilidad con el Banco, etc.Presentar al Ejecutivo de Cuenta el Programa Financiero preliminar, para su respectivo contraste.Gestión de firmas y poderes para la apertura de cuentas corrientes de personas jurídicas.Mantener actualizado y en orden el file comercial, contactos y base de datos.Gestionar y hacer seguimiento de la evolución de tarifas preferenciales (tasas y comisiones).Apoyo en el análisis de oportunidades y gestión del portafolio de clientes del segmento Banca Empresa y Corporativa.Otras funciones asignadas por su jefe inmediato.Requisitos:Nivel de Estudios: Egresado o Bachiller en Administración, Ingeniería Industrial, Ingeniería de Sistemas, Economía o afines.Experiencia previa como analista comercial en los rubros de banca, financieras o afines.MS Excel (avanzado), MS Visio y MS Word (Intermedio), MS Access, MS Power Point y MS Project (Básico).Ingles: Avanzado (no indispensable)Competencias: Orientación al cliente, comunicación asertiva, proactividad y dinamismo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Analista de Datos de Desarrollo del Emprendedor</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Mibanco</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55909/analista-de-datos-de-desarrollo-del-emprendedor</t>
+        </is>
+      </c>
+      <c r="G243" t="n">
+        <v>11</v>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>python, sql, analisis, excel, power bi</t>
+        </is>
+      </c>
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
+        <v>1</v>
+      </c>
+      <c r="L243" t="n">
+        <v>1</v>
+      </c>
+      <c r="M243" t="n">
+        <v>0</v>
+      </c>
+      <c r="N243" t="n">
+        <v>1</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+      <c r="P243" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAnalista de Datos de Desarrollo del Emprendedor.¿Cuáles serían tus principales responsabilidades?Organizar, recopilar y gestionar la información de los distintos canales y su consolidación en un solo repositorio.Analizar los indicadores de performance de cada canal de difusión de contenidos en cada etapa del funnel.Elaborar reportería que ayude a medir alcance, impacto y satisfacción de los canales y contenido.Proponer mejoras o nuevas iniciativas en función al análisis de la información.Identificar la correlación de la capacitación y su impacto en el negocio.Generar reportería y rankings continuos para la red de agencia.Perfilar a los clientes que reciben los programa por cada canal.Proporcionar información de los clientes que son captados a través de las alianzas.¿Qué necesitamos?Bachiller en Administración, Economía, Ingeniería industrial o afines.Estudios de postgrado Gestión de proyectos, Análisis de datos, Metodologías ágiles, Innovación (deseable no excluyente).01 año de experiencia en la gestión de información y análisis de datos (incluyendo prácticas).Experiencia en elaboración de análisis predictivos, dashboards y reportería.Conocimiento de indicadores de medición de plataformas digitales (intermedio).Excel avanzado (Tablas Dinámicas, macros no excluyentes).Power BI (Dashboards intermedio).SQL/PL-SQL (intermedio).Python básico (deseable).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Asistente TAX Compliance</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Forvis Mazars</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55922/asistente-tax-compliance</t>
+        </is>
+      </c>
+      <c r="G244" t="n">
+        <v>3</v>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" t="n">
+        <v>1</v>
+      </c>
+      <c r="L244" t="n">
+        <v>0</v>
+      </c>
+      <c r="M244" t="n">
+        <v>0</v>
+      </c>
+      <c r="N244" t="n">
+        <v>0</v>
+      </c>
+      <c r="O244" t="n">
+        <v>0</v>
+      </c>
+      <c r="P244" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>Acerca del empleoCon nosotros tienes la oportunidad de pertenecer a una firma internacional con un importante potencial de crecimiento y un equipo de más de 40.000 profesionales altamente capacitados, que brinda servicios profesionales generando alto impacto en todos nuestros clientes en más de 100 países en los cinco continentes.Podrás formar parte de un equipo que valorará tus ideas, apoyará tus ambiciones y celebrará tus éxitos. En Forvis Mazars nos proponemos impulsar la colaboración y la flexibilidad, las diversas perspectivas de nuestros colaboradores y el progreso.Hoy nuestro equipo de TAX Compliance está buscando un (a) Asistente, el cual tiene como principal objetivo apoyar la correcta gestión y cumplimiento de las obligaciones tributarias de las empresas en su cartera asignada, asegurando la precisión, oportunidad y veracidad en los procesos de declaración y presentación de impuestos, así como el resguardo del cumplimiento normativo vigente.Principales ResponsabilidadesPreparar y recopilar la documentación necesaria para la presentación de declaraciones de impuestos mensuales y anuales.Colaborar en la revisión y análisis de los registros contables relacionados con impuestos, verificando su correcta imputación y clasificación.Apoyar en la elaboración de informes tributarios y reportes solicitados por su jefatura.Realizar seguimiento a las actualizaciones normativas y cambios en la legislación tributaria que puedan afectar a la empresa.Gestionar la comunicación y coordinación con entidades externas, como el Servicio de Impuestos Internos (SII) y asesores fiscales.Mantener actualizada la documentación y archivos vinculados a los procesos de TAX Compliances.Perfil RequeridoTítulo universitario en Contabilidad, Auditoría, Administración o carrera afín.Experiencia de 1 año lo menos en cargos similares o en áreas de cumplimiento tributario.Conocimiento actualizado de la normativa tributaria chilena y manejo de plataformas digitales del SII.Manejo de herramientas ofimáticas, especialmente Excel.Capacidad analítica, organización, atención al detalle y orientación al cumplimiento de plazos.Habilidades de comunicación y trabajo en equipo.Este cargo es compatible para personas con discapacidad, se enmarca en la ley 21.015, que incentiva la inclusión de personas con discapacidad al mundo laboral.BeneficiosOfrecemosPaquete de compensaciones de mercadoSeguro Complementarios de salud y Dental, además de seguro de VidaUna experiencia dinámica, diversa e inclusiva, en una Firma con orientación en las personas, desarrollo y crecimientoEducación continua, tanto de programas internos, corporativos y externosDías adicionales de vacaciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Analista Experto área de Rezagos Gerencia de Operaciones</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>AFP Modelo</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Avda de valle 614 Huechuraba, Chile, Chile</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55914/analista-experto-area-de-rezagos-gerencia-de-operaciones</t>
+        </is>
+      </c>
+      <c r="G245" t="n">
+        <v>5</v>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>sql, excel</t>
+        </is>
+      </c>
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" t="n">
+        <v>0</v>
+      </c>
+      <c r="L245" t="n">
+        <v>1</v>
+      </c>
+      <c r="M245" t="n">
+        <v>0</v>
+      </c>
+      <c r="N245" t="n">
+        <v>0</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+      <c r="P245" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>¿Quiénes somos?Somos una AFP orientada a las personas, comprometida con su bienestar presente y futuro. Destacamos que, en línea con nuestra cultura organizacional, nuestras búsquedas se enmarcan bajo la ley 21.015, la cual promueve la inclusión laboral de las personas con discapacidad.¿Quieres sumarte a cientos de profesionales que buscan contribuir con entusiasmo y responsabilidad al bienestar de las personas? ¡Esta es tu oportunidad!¿Cuáles serán los desafíos del cargo?Ejecutar los procesos necesarios del área de rezagos, a fin, de aportar a la gestión operacional de la misma, teniendo una visión crítica de los procesos que maneja, ideando e implementando soluciones orientadas a la mejora continua siempre de acuerdo a los protocolos y procedimientos vigentes, así como también políticas externas relacionadas al rubro, con el fin de dar cumplimiento al plan de operaciones, a la normativa vigente y a los estándares de servicio al cliente establecidos.¿Qué buscamos?Formación Académica: Egresado o Titulado de carrera Profesional o Técnico de carreras de ingenierías, administración, finanzas, marketing y demás carreras afines.Conocimientos técnicos:Manejo de Excel avanzado, SQL intermedio.Experiencia mínima/deseable: 1 año de experiencia en cargos similares.BeneficiosBus de acercamientoDía de CumpleañosSeguro complementarioy muchos beneficios más¡Te esperamos!</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Práctica Profesional - Gerencia Analytics y BI - Data Science</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Ofi. Alonso De Cordova 5320 - Producto Financiero, Chile</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55913/practica-profesional-gerencia-analytics-y-bi-data-science</t>
+        </is>
+      </c>
+      <c r="G246" t="n">
+        <v>18</v>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>python, sql, machine learning, estadistica, informatica, cloud, aws</t>
+        </is>
+      </c>
+      <c r="I246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" t="n">
+        <v>1</v>
+      </c>
+      <c r="L246" t="n">
+        <v>0</v>
+      </c>
+      <c r="M246" t="n">
+        <v>0</v>
+      </c>
+      <c r="N246" t="n">
+        <v>1</v>
+      </c>
+      <c r="O246" t="n">
+        <v>0</v>
+      </c>
+      <c r="P246" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>🚀 ¡Buscamos a nuestro/a próximo/a Practicante de Analítica y Automatización para la Gerencia de Analytics y BI en Banco Ripley! 💜Si estás buscando un lugar donde puedas aprender, desarrollar tus habilidades técnicas y participar en proyectos con impacto real en el negocio, llegaste al lugar indicado. En Banco Ripley te integrarás a un equipo dinámico, donde los datos, la innovación y la mejora continua son parte del día a día.Ser parte de Banco Ripley es vivir una cultura que impulsa el desarrollo, la colaboración y el aprendizaje constante, en un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te apasiona la programación, la analítica de datos y la automatización de procesos? ¿Te gustaría trabajar con modelos analíticos y contribuir a hacer más eficientes los procesos del negocio? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Apoyar la ejecución, monitoreo y optimización de los procesos analíticos de la gerencia, participando en el diseño e implementación de soluciones que permitan automatizar, calendarizar y mejorar los flujos de trabajo actuales, contribuyendo a una operación más eficiente y escalable.Funciones: 🤩• Ejecutar y monitorear los procesos analíticos vigentes para asegurar la continuidad operacional.• Garantizar la entrega oportuna de información y resultados generados por los procesos actuales.• Identificar oportunidades de automatización y mejora en procesos manuales.• Diseñar e implementar soluciones para automatizar y calendarizar procesos analíticos.• Revisar y optimizar el código de modelos analíticos, proponiendo mejoras en su estructura y eficiencia.• Validar el desempeño de modelos y procedimientos almacenados (Stored Procedures) en entornos AWS.• Colaborar en iniciativas de mejora continua que fortalezcan la eficiencia de los procesos del área.¿Qué estamos buscando? 💡• Estudiante de Ingeniería Civil, Ingeniería Informática, Ingeniería Industrial, Estadística, Ciencia de Datos o carrera afín.• Contar con seguro escolar vigente otorgado por la casa de estudios. (Excluyente).• Disponibilidad inmediata para realizar la práctica.• Conocimientos de programación en Python, R y SQL.• Conocimientos en estadística, machine learning y técnicas de clusterización.• Deseable conocimiento de entornos cloud, especialmente AWS SageMaker.• Interés por la analítica, la automatización de procesos y la optimización continua.• Capacidad analítica, proactividad y ganas de aprender en un entorno desafiante.¿Por qué trabajar en Banco Ripley? 💜Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo. 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y, si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Profesional de Proyectos de Packaging</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Difem Laboratorios S.A.</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55908/profesional-de-proyectos-de-packaging</t>
+        </is>
+      </c>
+      <c r="G247" t="n">
+        <v>5</v>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>analisis, excel, power bi</t>
+        </is>
+      </c>
+      <c r="I247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J247" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" t="n">
+        <v>0</v>
+      </c>
+      <c r="L247" t="n">
+        <v>1</v>
+      </c>
+      <c r="M247" t="n">
+        <v>0</v>
+      </c>
+      <c r="N247" t="n">
+        <v>0</v>
+      </c>
+      <c r="O247" t="n">
+        <v>0</v>
+      </c>
+      <c r="P247" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>EnDifem Laboratoriosbuscamos un/a profesional para liderar un proyecto de optimización de cajas de embalaje, participando en el análisis, diseño y desarrollo de soluciones que contribuyan a mejorar nuestros procesos y estandarizar el portafolio de packaging.¿Cuáles serán tus principales desafios?Analizar y optimizar el portafolio de cajas de embalaje.Desarrollar y validar propuestas de packaging mediante maquetas y troqueles.Elaborar fichas técnicas de productos y materiales de marketing.Crear instructivos y documentación técnica para la estandarización de procesos.Coordinar pruebas e implementación de mejoras, trabajando de manera transversal con distintas áreas de la compañía.Buscamos a un profesional con:Título de Diseño Industrial, Ingeniería Civil Industrial, Ingeniería en Packaging o carrera afín.Experiencia en desarrollo de packaging, mejora de procesos o gestión de proyectos.Manejo avanzado de Excel.Power BI (deseable).Perfil analítico, organizado y orientado a resultados.Te ofrecemos:Participar en un proyecto estratégico con impacto directo en la organización.🤝 Trabajo colaborativo con equipos multidisciplinarios.📅 Contrato por proyecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>KPMG Chile</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Las Condes, Metropolitana, Chile, Chile</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55912/data-analyst</t>
+        </is>
+      </c>
+      <c r="G248" t="n">
+        <v>5</v>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>analisis, estadistica, excel</t>
+        </is>
+      </c>
+      <c r="I248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J248" t="n">
+        <v>0</v>
+      </c>
+      <c r="K248" t="n">
+        <v>1</v>
+      </c>
+      <c r="L248" t="n">
+        <v>0</v>
+      </c>
+      <c r="M248" t="n">
+        <v>0</v>
+      </c>
+      <c r="N248" t="n">
+        <v>0</v>
+      </c>
+      <c r="O248" t="n">
+        <v>0</v>
+      </c>
+      <c r="P248" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>Perfil Ideal: Analista de DatosBuscamos un profesional proactivo y analítico para unirse a nuestro equipo en KPMG Chile. El candidato ideal poseerá una sólida orientación hacia la gestión y calidad de datos, con el objetivo de optimizar la información y respaldar la toma de decisiones estratégicas.Responsabilidades Clave:Administración y manejo de sistemas CRM, con énfasis en Salesforce.Ejecución de procesos de segmentación de datos para diversas iniciativas de negocio.Apoyo en la gestión, mantenimiento y aseguramiento de la calidad de bases de datos.Monitoreo y seguimiento riguroso de la calidad de la información registrada.Gestión y control de la calidad del pipeline de datos.Requisitos Fundamentales:Título profesional en Ingeniería Comercial, Ingeniería Civil Industrial, Ingeniería en Información y Control de Gestión, Estadística, Administración o carreras afines.Experiencia demostrable en gestión y calidad de datos.Manejo de CRM, preferentemente Salesforce.Conocimientos sólidos en segmentación, administración y análisis de bases de datos.Dominio de Excel a nivel intermedio o avanzado. Este rol es ideal para profesionales que buscan un entorno dinámico donde aplicar sus habilidades analíticas y contribuir directamente al éxito de la organización.Beneficios¿Qué ganas tú?:🚑Seguro complementario de Salud🌎Ser parte de una de las principales compañías de Auditoría y Consultoría a nivel mundial.🚀 Oportunidades de desarrollo profesional.💻Jornada de trabajo Hibrida (flexible según el cliente y el equipo con que se esté trabajando)🏢Oficinas de primer nivel ubicadas en Las Condes, frente al Parque Araucano💯Múltiples convenios corporativos🎉Actividades como fiestas, Meeting Points y encuentros de área para disfrutar con compañerosEn KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas, con un propósito claro, para una mejor sociedad. Valoramos las diversas habilidades y fortalezas, tanto personales como profesionales, que cada persona aporta. En KPMG estamos comprometidos con la Diversidad e inclusión, nuestras ofertas de empleo están disponibles con los ajustes razonables necesarios para tu proceso . Juntos, estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. ¡Anímate y ven a descubrir por qué somos la opción más clara! 🥇</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q248"/>
+  <dimension ref="A1:Q256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17270,6 +17270,542 @@
         </is>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Asesor de Financiamiento Automotriz Temuco</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Tanner</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Región de la Araucanía, Chile</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55939/asesor-de-financiamiento-automotriz-temuco</t>
+        </is>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" t="n">
+        <v>0</v>
+      </c>
+      <c r="L249" t="n">
+        <v>1</v>
+      </c>
+      <c r="M249" t="n">
+        <v>0</v>
+      </c>
+      <c r="N249" t="n">
+        <v>0</v>
+      </c>
+      <c r="O249" t="n">
+        <v>0</v>
+      </c>
+      <c r="P249" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>Asesor de Financiamiento Automotriz TemucoTanner Servicios FinancierosEn Tanner buscamos personas con energía comercial, foco en resultados y pasión por el mundo automotriz. Si te motiva el contacto con clientes y quieres potenciar tu desarrollo en una compañía del rubro financiero, esta oportunidad es para ti.¿Cuál será tu desafío?Serás responsable de gestionar la venta y refinanciamiento de créditos automotrices y productos asociados, contribuyendo directamente al cumplimiento de metas comerciales de la unidadEn el día a día esto implica:Venta de financiamiento automotriz en distintos canales (especialmente telefónicos)Comercialización de productos asociados (principalmente seguros)Gestión de cartera de clientes y seguimiento comercialCumplimiento de metas y presupuesto comercial¿Por qué Tanner?Aquí no solo vendes productos,generas soluciones reales para los clientesy eres protagonista de su proceso de financiamiento. Trabajarás en un entorno cercano, con foco en resultados y donde tu desempeño impacta directamente en tu crecimiento.Compromiso con la Inclusión:Nuestras ofertas están bajo el marco contextual de laLey 21.015, que incentiva la inclusión laboral de personas con discapacidad. En Tanner, valoramos el talento único de cada persona.Requisitos¿Qué buscamos?Recién titulados o personas con1 año de experiencia en ventas, idealmente en seguros, créditos o rubro automotrizOrientación comercial y foco en resultadosHabilidades de comunicación y cercanía con clientesProactividad y autonomíaDisponibilidad para trabajarfull presencial en Temuco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Analista Capacity Planning (1 a 2 años de experiencia)</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Polpaico Soluciones</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>san bernardo, Chile</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55942/analista-capacity-planning-1-a-2-anos-de-experiencia</t>
+        </is>
+      </c>
+      <c r="G250" t="n">
+        <v>8</v>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>python, analisis, excel, power bi</t>
+        </is>
+      </c>
+      <c r="I250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" t="n">
+        <v>0</v>
+      </c>
+      <c r="L250" t="n">
+        <v>1</v>
+      </c>
+      <c r="M250" t="n">
+        <v>0</v>
+      </c>
+      <c r="N250" t="n">
+        <v>0</v>
+      </c>
+      <c r="O250" t="n">
+        <v>0</v>
+      </c>
+      <c r="P250" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>Polpaico Soluciones, es una compañía líder en el mercado nacional de la fabricación y comercialización de cemento, hormigón y áridos. Como empresa estamos convencidos que tener un equipo de trabajo diverso y una cultura inclusiva genera beneficios para las personas y el negocio. No sólo aceptamos la diversidad, sino que la valoramos y promovemos activamente.Actualmente nos encontramos en la búsqueda deAnalista de capacity Planningcuyo propósito es la planificación de Capacity en la producción de los análisis, modelos y reportes que sustentan las decisiones de planificación de flota y operadores mixer. Procesa los datos del rolling forecast, construye los modelos de capacity por zona, elabora el calendario de turnos y la asignación de camiones, y monitorea las desviaciones entre la demanda proyectada y la real.¿Cuáles serán tus principales funciones en este cargo?1. Procesar los datos del rolling forecast mensual y construir los modelos de proyección de demanda por zona geográfica y planta, como insumo para el plan de capacity.2. Calcular los requerimientos de flota y operadores necesarios para cubrir la demanda proyectada, identificando brechas de capacidad por zona y período.3. Elaborar y mantener actualizado el calendario mensual de turnos de operadores mixer por planta y zona.4. Construir la propuesta de asignación mensual de camiones por planta y zona, integrando la disponibilidad de flota confirmada por el área de mantenimiento.5. Monitorear mensualmente la evolución de la demanda real versus la proyectada, identificando desviaciones y alertando al superar los umbrales definidos.6. Mantener actualizadas las bases de datos de capacity, demanda histórica, flota, disponibilidad de flota, dotación de operadores,eficiencia de operadores y asegurando calidad e integridad de los datos.7. Preparar los reportes y presentaciones del plan de capacity para la reunión mensual de rolling forecast con Planificación Comercial y el Área Comercial de Hormigones.8. Prepararse analizando distintos escenarios ante variaciones de demanda, disponibilidad de flota u otra variable que pueda afectar la correcta planificación de la operaciónRequisitos:Título profesional en Ingeniería Civil Industrial, Ingeniería Comercial o carrera afínAl menos un año de experiencia en el áreaConocimiento en Forecast de demandas, Proyecciones, Supply chain y/o Gestión de flota.Excel avanzado (Excluyente)Power Bi / Python (Deseable)Formación en metodologías de planificación de operaciones o supply chain (deseable).Polpaico Soluciones garantiza igualdad de condiciones en el acceso al empleo, es decir, esta oferta de trabajo es consciente con el medio y las diversas realidades, por lo que se enmarca en la ley de inclusión laboral N°21.015.Si tu objetivo es asumir nuevos desafíos en una compañía líder del mercado, ¡Postula con nosotros!BeneficiosComo colaborador/a de Polpaico Soluciones, te ofrecemos:Seguro de vida 100% financiado por la compañía.Seguro complementario de salud, dental y catastrófico.Oportunidades de crecimiento y desarrollo profesional a través de becas de estudio.Excelente ambiente de trabajo.Alguna de nuestras principales alianzas son: Caja compensación los Andes y FALP (Fundación Arturo López Perez).</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Analista Operaciones Logística</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Polpaico Soluciones</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Presencial Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55941/analista-operaciones-logistica</t>
+        </is>
+      </c>
+      <c r="G251" t="n">
+        <v>7</v>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>analisis, informatica, excel, power bi</t>
+        </is>
+      </c>
+      <c r="I251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" t="n">
+        <v>1</v>
+      </c>
+      <c r="L251" t="n">
+        <v>1</v>
+      </c>
+      <c r="M251" t="n">
+        <v>0</v>
+      </c>
+      <c r="N251" t="n">
+        <v>0</v>
+      </c>
+      <c r="O251" t="n">
+        <v>0</v>
+      </c>
+      <c r="P251" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>Polpaico Soluciones,es una compañía líder en el mercado nacional de la fabricación y comercialización de cemento, hormigón y áridos. Como empresa estamos convencidos que tener un equipo de trabajo diverso y una cultura inclusiva genera beneficios para las personas y el negocio.Actualmente nos encontramos en búsqueda de:Analista de operaciones Logísticas.Objetivo Principal:Proveer inteligencia analítica y de gestión a la Red Logística de Polpaico, liderando la reportabilidad de cierres de mes, el análisis de desviaciones en costos de distribución y el desarrollo de paneles de control en Power BI para la toma de decisiones operativas y estratégicas. Apoya el proceso S&amp;OP garantizando visibilidad end-to-end del desempeño logístico mediante datos confiables, oportunos y accionables.Principales Responsabilidades:1.- Preparar y consolidar el cierre de mes logístico: costos de distribución, volúmenes despachados, rendimientos de flota y cumplimiento de servicio en toda la Red Logística de Chile.2.- Analizar desviaciones de costos de distribución versus presupuesto y forecast, identificando causas raíz y proponiendo acciones correctivas a la jefatura.3.- Diseñar, desarrollar y mantener paneles de Power BI con indicadores clave para la gestión diaria (KPIs de costo, servicio, eficiencia de flota, fill rate, OTIF, cobertura de stock).4.- Gestionar y validar la información proveniente de SAP para asegurar consistencia y calidad de datos en los reportes logísticos.5.- Apoyar el proceso S&amp;OP mensual con análisis de demanda, capacidad logística y alertas de riesgo en el cumplimiento del plan.6.- Automatizar reportes recurrentes mediante Excel avanzado (Power Query, tablas dinámicas, macros) y conectores de datos para reducir tiempos de cierre.7.- Elaborar presentaciones ejecutivas con análisis de resultados logísticos para reuniones de gerencia y comités de gestión.8.- Colaborar con las áreas de Finanzas, Operaciones y Comercial en la validación de información y la alineación de definiciones de KPIs.RequisitosFormación:Ingeniería en Logística, Ingeniería Industrial, Ingeniería en informática ó carrera afín.Experiencia:- 2 años de experiencia en roles de control de gestión logística, planificación, S&amp;OP o analítica de operaciones en industrias de consumo masivo, cemento, materiales de construcción o afines.- Experiencia comprobable en desarrollo de reportes de cierre de mes y análisis de desviaciones de costos.- Historial demostrable en diseño e implementación de dashboards de gestión en Power BI con impacto real en la toma de decisiones operativas.-Deseable experiencia trabajando con datos de SAP en entornos logísticos o de supply chain.Conocimientos:Procesos logísticos y operacionales (transporte, distribución).Excluyente: Manejo de sistemas ERP (SAP), Excel avanzado, Power BI.BeneficiosComo colaborador/a de Polpaico Soluciones, te ofrecemos:Seguro de vida 100% financiado por la compañía.Seguro complementario de salud, dental y catastrófico.Oportunidades de crecimiento y desarrollo profesional a través de becas de estudio.Excelente ambiente de trabajo.Alguna de nuestras principales alianzas son: Caja compensación los Andes y FALP (Fundación Arturo López Pérez).</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Asesor de Financiamiento Automotriz Concepción</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Tanner</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Región del Biobío, Chile</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55940/asesor-de-financiamiento-automotriz-concepcion</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" t="n">
+        <v>0</v>
+      </c>
+      <c r="L252" t="n">
+        <v>1</v>
+      </c>
+      <c r="M252" t="n">
+        <v>0</v>
+      </c>
+      <c r="N252" t="n">
+        <v>0</v>
+      </c>
+      <c r="O252" t="n">
+        <v>0</v>
+      </c>
+      <c r="P252" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>Asesor de Financiamiento Automotriz TemucoTanner Servicios FinancierosEn Tanner buscamos personas con energía comercial, foco en resultados y pasión por el mundo automotriz. Si te motiva el contacto con clientes y quieres potenciar tu desarrollo en una compañía del rubro financiero, esta oportunidad es para ti.¿Cuál será tu desafío?Serás responsable de gestionar la venta y refinanciamiento de créditos automotrices y productos asociados, contribuyendo directamente al cumplimiento de metas comerciales de la unidadEn el día a día esto implica:Venta de financiamiento automotriz en distintos canales (especialmente telefónicos)Comercialización de productos asociados (principalmente seguros)Gestión de cartera de clientes y seguimiento comercialCumplimiento de metas y presupuesto comercial¿Por qué Tanner?Aquí no solo vendes productos,generas soluciones reales para los clientesy eres protagonista de su proceso de financiamiento. Trabajarás en un entorno cercano, con foco en resultados y donde tu desempeño impacta directamente en tu crecimiento.Compromiso con la Inclusión:Nuestras ofertas están bajo el marco contextual de laLey 21.015, que incentiva la inclusión laboral de personas con discapacidad. En Tanner, valoramos el talento único de cada persona.Requisitos¿Qué buscamos?Recién titulados o personas con1 año de experiencia en ventas, idealmente en seguros, créditos o rubro automotrizOrientación comercial y foco en resultadosHabilidades de comunicación y cercanía con clientesProactividad y autonomíaDisponibilidad para trabajarfull presencial en Temuco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Customer Success Manager – TGP</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>TGP</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55926/customer-success-manager-tgp</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" t="n">
+        <v>0</v>
+      </c>
+      <c r="K253" t="n">
+        <v>1</v>
+      </c>
+      <c r="L253" t="n">
+        <v>1</v>
+      </c>
+      <c r="M253" t="n">
+        <v>0</v>
+      </c>
+      <c r="N253" t="n">
+        <v>0</v>
+      </c>
+      <c r="O253" t="n">
+        <v>0</v>
+      </c>
+      <c r="P253" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>En TGP estamos buscando a nuestro/a próximo/a Customer Success ManagerBuscamos a una persona con experiencia en gestión de clientes B2B que quiera convertirse en un socio estratégico para las cuentas de su cartera. Si te motiva construir relaciones de largo plazo, analizar métricas, detectar oportunidades de crecimiento y generar un impacto directo en la retención y expansión de clientes, esta oportunidad puede ser para ti.¿Cuál será tu foco?Gestionar la relación comercial con una cartera de clientes activos.Analizar métricas de desempeño para identificar oportunidades de mejora y riesgos de churn.Reportar al Customer Success Lead el estado de cada cliente y diseñar en conjunto acciones operativas para mejorar el rendimiento.Diseñar estrategias de retención y expansión junto al Business Partner.Detectar oportunidades de cross-sell y upsell dentro de las cuentas.Liderar reuniones con clientes, presentar reportes y proponer acciones estratégicas.Coordinar con los equipos internos la correcta ejecución de los planes definidos para cada cliente.Buscamos personas que:Cuenten con experiencia en Customer Success, Account Management, KAM o gestión de clientes B2B.Tengan una fuerte orientación comercial y disfruten construir relaciones de largo plazo.Sean analíticas y capaces de interpretar métricas para tomar decisiones.Sean proactivas, organizadas y orientadas a resultados. Disfruten trabajar de forma autónoma y colaborativa con equipos multidisciplinarios.Modalidad: Híbrida (3 días presencial, 2 online)Ubicación:Las Condes, SantiagoSi te interesa esta oportunidad o conoces a alguien que pueda encajar, ¡nos encantaría conversar contigo!Beneficios¿Qué hace atractiva esta oportunidad?Tendrás autonomía para liderar la estrategia comercial de una cartera de clientes. Trabajarás directamente con clientes estratégicos, convirtiéndote en su principal socio comercial dentro de TGP.Serás protagonista en la retención y expansión de cuentas, generando un impacto directo en el crecimiento de la empresa.Contarás con oportunidades reales de crecimiento y desarrollo profesional dentro de TGP.Tendrás un esquema de incentivos asociado a oportunidades de upsell y expansión comercial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Coordinador Planificación y Abastecimiento Repuestos</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Polpaico Soluciones</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55925/coordinador-planificacion-y-abastecimiento-repuestos</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>0</v>
+      </c>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" t="n">
+        <v>0</v>
+      </c>
+      <c r="L254" t="n">
+        <v>1</v>
+      </c>
+      <c r="M254" t="n">
+        <v>0</v>
+      </c>
+      <c r="N254" t="n">
+        <v>0</v>
+      </c>
+      <c r="O254" t="n">
+        <v>0</v>
+      </c>
+      <c r="P254" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>Polpaico Soluciones, es una compañía líder en el mercado nacional de la fabricación y comercialización de cemento, hormigón y áridos. Como empresa estamos convencidos que tener un equipo de trabajo diverso y una cultura inclusiva genera beneficios para las personas y el negocio. No sólo aceptamos la diversidad, sino que la valoramos y promovemos activamente.Actualmente nos encontramos en la búsqueda de un/unaCoordinador(a) de Planificación y Abastecimiento de RepuestosObjetivo:Liderar la planificación de la demanda y la gestión técnica del inventario de repuestos para camiones y plantas. Es responsable de asegurar que el negocio cuente con las definiciones de stock necesarias (mínimos, máximos y criticidad) para garantizar la disponibilidad y continuidad operativa, entregando requerimientos validados al área de abastecimiento para las posterior búsqueda y negociación.Además, debe asegurar la gobernanza integral del ciclo de vida de materiales y repuestos, mediante la creación, estandarización y mantención de códigos maestros, la planificación eficiente de repuestos y el control del abastecimiento, articulando de manera coordinada las necesidades del área de Mantenimiento Planta con los procesos del área de Compras, con el fin de garantizar continuidad operacional, optimizar niveles de inventario y contribuir a la toma de decisiones confiables y oportunas para la operación.Funciones:1.- Analizar consumos históricos, criticidad de equipos y planes de mantenimiento para planificar el abastecimiento de repuestos, definiendo parámetros MRP, stocks de seguridad y puntos de reposición.2.- Administrar y asegurar la calidad de los datos maestros de materiales en SAP, garantizando información estandarizada, actualizada y confiable.3.- Coordinar requerimientos entre Mantenimiento, Operaciones, Compras y Bodega, realizando seguimiento al proceso de abastecimiento y apoyando la resolución de desviaciones, devoluciones y diferencias de compras.4.- Gestionar y optimizar los niveles de inventario, identificando sobrestock, obsolescencia y oportunidades de mejora para asegurar la disponibilidad de repuestos críticos.5.- Elaborar reportes e indicadores de planificación, inventarios y abastecimiento, detectando desviaciones y proponiendo acciones de mejora para apoyar la toma de decisiones.BeneficiosSeguro de vida 100% financiado por la compañía.Seguro complementario de salud, dental y catastrófico.Oportunidades de crecimiento y desarrollo profesional a través de becas de estudio.Excelente ambiente de trabajo.Alguna de nuestras principales alianzas son: Caja compensación los Andes y FALP (Fundación Arturo López Pérez).</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Analista Planificación Comercial</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Polpaico Soluciones</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55927/analista-planificacion-comercial</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>1</v>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" t="n">
+        <v>0</v>
+      </c>
+      <c r="L255" t="n">
+        <v>1</v>
+      </c>
+      <c r="M255" t="n">
+        <v>0</v>
+      </c>
+      <c r="N255" t="n">
+        <v>0</v>
+      </c>
+      <c r="O255" t="n">
+        <v>0</v>
+      </c>
+      <c r="P255" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>Polpaico Soluciones,es una compañía líder en el mercado nacional de la fabricación y comercialización de cemento, hormigón y áridos. Como empresa estamos convencidos que tener un equipo de trabajo diverso y una cultura inclusiva genera beneficios para las personas y el negocio. Actualmente nos encontramos en búsqueda de:Analista de Planificación Comercial.La persona que ocupa el cargo, deberá generar análisis, proyecciones y reportes estratégicos que permitan optimizar la planificación comercial, apoyar la toma de decisiones y contribuir al cumplimiento de metas de venta, rentabilidad y eficiencia operativa.Entre sus principales funciones se encuentran:Elaborar reportes de gestión comercial, análisis de ventas, márgenes, mix de productos y canales.Proyectar demanda y planificar escenarios comerciales.Monitorear KPIs (ventas, forecast accuracy, fill rate, rotación, etc.).Apoyar la definición de presupuestos y metas comerciales.Coordinar con áreas de ventas, marketing, operaciones y finanzas.Identificar oportunidades de mejora en procesos comerciales.Participar en comités de planificación y revisión de resultados.Mantener actualizados los tableros de control y bases de datos comerciales.BeneficiosComo colaborador/a de Polpaico Soluciones, te ofrecemos los siguientes beneficios:- Seguro de vida 100% financiado por la compañía.- Seguro complementario de salud, dental y catastrófico.- Oportunidades de crecimiento y desarrollo profesional a través de becas de estudio.- Excelente ambiente de trabajo.- Algunas de nuestras principales alianzas son: Caja compensación los Andes y FALP (Fundación Arturo López Pérez).</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Ingenieroa de Planificación Demanda - Las Condes</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>CCU</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55928/ingeniero-a-de-planificacion-demanda-las-condes</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>5</v>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>sql, excel</t>
+        </is>
+      </c>
+      <c r="I256" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" t="n">
+        <v>0</v>
+      </c>
+      <c r="L256" t="n">
+        <v>1</v>
+      </c>
+      <c r="M256" t="n">
+        <v>0</v>
+      </c>
+      <c r="N256" t="n">
+        <v>0</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+      <c r="P256" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>¡En CCU nos apasiona crear experiencias para compartir juntos un mejor vivir!Estamos buscando a nuestro/a próximo/aIngeniero/a de Planificación Demandapara nuestra Gerencia de Planificación Integrada (PPI) en el Edificio Corporativo deLas Condes.Principales funciones:Planificar la demanda de los Centros de Distribución (CDs) para la categoría asignada (Analcoholes), con el objetivo de contar con stock para Canal Tradicional (almacenes y botillerías).Monitorear y analizar KPIs de forecast accuracy, generando reportería para la toma de decisiones.Desarrollar el proceso de planificación de la demanda a fin de generar información para el área de producción, logística, aprovisionamiento, etc.Relacionarse con el área de ventas para recopilar la información de los distintos distritos comerciales con el objetivo de entregar input al equipo de Demanda.Requisitos:Título de Ingeniería Civil Industrial, Ingeniería Comercial o carrera afín.0 - 6 meses de experiencia.Manejo de Excel nivel intermedio y herramientas de Google.Manejo de BBDD SQL deseable.Disponibilidad para trabajar en modalidad presencial en Las Condes y disponibilidad para ir a ruta.Nuestro SER CCU nos inspira a trabajar con aceptación y respeto a las diferencias de las personas, promoviendo un entorno diverso e integrador, para así contribuir a un mejor vivir. Por esto, te agradecemos que nos compartas si necesitas adaptación en alguna etapa del proceso de postulación.¡Te invitamos a SER CCU!</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q256"/>
+  <dimension ref="A1:Q269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17806,6 +17806,859 @@
         </is>
       </c>
     </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Ingenieroa Proyectos Innovación y Desarrollo de Productos</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Enaex</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Las Condes, Metropolitana, Chile</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55982/ingeniero-a-proyectos-innovacion-y-desarrollo-de-productos</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>0</v>
+      </c>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="n">
+        <v>1</v>
+      </c>
+      <c r="J257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0</v>
+      </c>
+      <c r="L257" t="n">
+        <v>1</v>
+      </c>
+      <c r="M257" t="n">
+        <v>0</v>
+      </c>
+      <c r="N257" t="n">
+        <v>0</v>
+      </c>
+      <c r="O257" t="n">
+        <v>0</v>
+      </c>
+      <c r="P257" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>Nuestra empresa:Enaex es una empresa filial del grupo Sigdo Koppers, con más de 105 años de trayectoria en el mercado de explosivos. Nos hemos consolidado como el tercer productor mundial de Nitrato de Amonio de baja densidad y el principal prestador de servicios integrales de fragmentación de roca para la minería en Chile y Latinoamérica.Queremos invitarte a crecer con nosotros y desafiarte día a día en una compañía cuyo propósito es Humanizar la minería. Si para ti la prioridad es la vida, tu obsesión es la excelencia, tu vocación son los clientes y tienes como fortaleza la innovación y el emprendimiento, ¡este es tu lugar!Misión del cargo:Asegurar la validación en terreno de soluciones innovadoras, conectando la necesidad del cliente con el desarrollo de productos.Descripción del cargo:Propósito del cargo: Asegurar la validación en terreno de soluciones innovadoras, conectando la necesidad del cliente con el desarrollo de productos, para garantizar implementaciones exitosas que generen valor y continuidad operacional.Principales responsabilidades:- Definir pruebas de pilotaje de proyectos de Innovación para ejecutarlas en ambiente controlado y en terreno con clientes.- Articular pruebas de terreno de proyectos de Innovación con diferentes áreas involucradas.- Construir protocolos y reportes de pruebas.- Elaborar documentación de pilotaje y escalamiento de proyectos.- Hacer la conexión de la demanda del usuário y visión del cliente hacia el equipo de desarrollo de productos para articular modificaciones, generando un producto conforme la expectativa y que cumpla con la necesidad del cliente.- Garantizar que la implementación de un nuevo producto alcance continuidad operacional y agregue valor al cliente.- Organizar la primera implementación de productos en escalamiento, y sus posibles adaptaciones, en filiales (otros países) de Enaex.Responde las preguntas en Aira y carga tu currículum actualizado. ¡Esperamos contar contigo!Nuestro Candidato Ideal:Título Ingeniero Civil en Minas o EjecuciónAl menos 2 años de Experiencia en operaciones Mineras implementando nuevos productos; SIE, EMTSDisponibilidad para viajarTurnos 5x2Contar con residencia en Santiago, en Calama o Antofagasta (Deseable)Inglés IntermedioDiscapacidad: Esta vacante es apta para personas con discapacidad.Proceso de selección:El proceso de selección se realiza a través de Aira - plataforma de reclutamiento diseñado para mejorar tu experiencia de postulación.Para postular solo necesitas:1. Postular a la oferta2. Revisar tu email3. Ingresar a Aira y contestar las preguntas y/o pruebas solicitadasLuego, si vemos que tu perfil se ajusta a lo que estamos buscando, te contactaremos por email (a través de Aira) para seguir a la etapa presencial.BeneficiosBeneficios generales</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Supervisora de Oficina en Castro</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Fondo Esperanza</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Región de Los Lagos, Chile</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55981/supervisor-a-de-oficina-en-castro</t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="n">
+        <v>0</v>
+      </c>
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" t="n">
+        <v>1</v>
+      </c>
+      <c r="L258" t="n">
+        <v>1</v>
+      </c>
+      <c r="M258" t="n">
+        <v>0</v>
+      </c>
+      <c r="N258" t="n">
+        <v>0</v>
+      </c>
+      <c r="O258" t="n">
+        <v>0</v>
+      </c>
+      <c r="P258" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>Impulsa tu talento en un lugar donde la inclusión laboral es prioridadTe proyectas trabajando en una organización apasionada por la superación de la pobreza, donde el foco está en inspirar el desarrollo social de emprendedores de sectores vulnerables, sus familias y comunidades, ampliando sus oportunidades mediante servicios financieros, capacitación y redes.En Fondo Esperanza nos encontramos en búsqueda de un/aSupervisor/a de Oficina(Trabajador/a Social) para integrarse en nuestra oficina ubicada enCastro. Su principal objetivo será supervisar la gestión de los colaboradores de la oficina en coordinación con la jefatura, para el mejoramiento de las condiciones de vida de emprendedores vulnerables, sus familias y comunidades, asegurando la entrega del servicio microfinanciero integral alineado con los valores, misión y visión de Fondo Esperanza🌍 Compromiso con la inclusiónEn Fondo Esperanza valoramos profundamente ladiversidad y la equidadcomo pilares fundamentales de nuestro quehacer. Esta vacante se publica en el marco de laLey 21.015, que promueve la inclusión laboral de personas con discapacidad. Queremos que cada persona encuentre un espacio donde pueda aportar sus talentos y desarrollarse plenamente.Si durante el proceso de postulación o en tu futura experiencia laboral necesitasajustes razonables, te invitamos a informarlo con toda confianza. Promovemos un ambiente derespeto, colaboración y reconocimiento, donde cada persona es valorada por lo que aporta.🎯Principales responsabilidades:Asegurar la entrega del servicio integral de Fondo Esperanza, supervisando la gestión del equipo de acuerdo a los estándares establecidos.Promover en el equipo de trabajo la adecuada utilización de los recursos de la oficina (materiales. humanos, tecnológicos y financieros).Apoyar el cumplimiento de las metas de la oficina y los lineamientos estratégicos de la organización (visión, misión y valores), a través del acompañamiento de los colaboradores y la revisión permanente de los indicadoresCondiciones del cargo:Modalidad semi presencial (Oficina, Terreno y Teletrabajo).Flexibilidad horaria. (Artículo 22, inciso 2)💡Buscamos personas con:Orientación al servicio y trabajo en terreno.Compromiso con la transformación social.Capacidad de planificación, gestión y autonomía.Disponibilidad de viaje.Flexibilidad horaria (se recomienda)Reuniones y Gestiones dentro y fuera de la Oficina¿Y los beneficios?En esta organización, ¡tu bienestar también importa!Te compartimos algunos de los beneficios que entregamos a nuestro equipo:🎁Beneficios:Días administrativosAlianza con Caja de Compensación Los AndesDía libre por cumpleañosConvenio con clínica dentalConvenio con centro de salud mentalConvenio con gimnasioAguinaldos en Fiestas Patrias y Fin de Año🛡Y una vez con contrato indefinido, también accedes a:Seguro complementario Vida CámaraExtensión de vacacionesGift Cards de Escolaridad y NavidadReconocimiento por excelencia académicaReincorporación gradual para mamás y papásFondo de apoyo a la vivienda🌟¿Por qué postular a Fondo Esperanza?Porque trabajamos con propósito, en un entorno colaborativo, transparente y flexible, generando impacto social real. Queremos que tu talento y compromiso sean parte de este camino.BeneficiosTítulo:Trabajador Social y/o Profesional del Área Social.Experiencia:2 años de experiencia laboral:-      Ojalá liderando equipos de personas.-      Gestionando metodologías grupales de intervención  comunitariaFormación:Deseable curso o diplomado en Gestión de PersonasConocimientos Específicos-      Educación de Adultos.-      Conocimiento de gestión de redes.-      Administración de personas.-      Office Intermedio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Especialista de Estudios e Impacto</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Fondo Esperanza</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55980/especialista-de-estudios-e-impacto</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>4</v>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>python, analisis</t>
+        </is>
+      </c>
+      <c r="I259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" t="n">
+        <v>1</v>
+      </c>
+      <c r="L259" t="n">
+        <v>0</v>
+      </c>
+      <c r="M259" t="n">
+        <v>0</v>
+      </c>
+      <c r="N259" t="n">
+        <v>0</v>
+      </c>
+      <c r="O259" t="n">
+        <v>0</v>
+      </c>
+      <c r="P259" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>Impulsa tu talento en un lugar donde la inclusión laboral es prioridadTe proyectas trabajando en una organización apasionada por la superación de la pobreza, donde el foco está en inspirar el desarrollo social de emprendedores de sectores vulnerables, sus familias y comunidades, ampliando sus oportunidades mediante servicios financieros, capacitación y redes.En Fondo Esperanza nos encontramos en búsqueda de un/aEspecialista de Estudios e Impactopara sumarse a la Gerencia Comercial y Social. Su principal objetivo será impulsar y desarrollar estudios de diversa índole, colaborando con universidades y otras instituciones para generar conocimiento útil. La finalidad es aportar evidencia sólida que fortalezca la toma de decisiones estratégicas, la incidencia pública y la creación de valor para nuestras socias y la industria de las microfinanzas.🌍 Compromiso con la inclusiónEn Fondo Esperanza valoramos profundamente ladiversidad y la equidadcomo pilares fundamentales de nuestro quehacer. Esta vacante se publica en el marco de laLey 21.015, que promueve la inclusión laboral de personas con discapacidad. Queremos que cada persona encuentre un espacio donde pueda aportar sus talentos y desarrollarse plenamente.Si durante el proceso de postulación o en tu futura experiencia laboral necesitasajustes razonables, te invitamos a informarlo con toda confianza. Promovemos un ambiente derespeto, colaboración y reconocimiento, donde cada persona es valorada por lo que aporta.¿Te proyectas trabajando en una organización apasionada por la superación de la pobreza? En Fondo Esperanza, nuestro foco está en inspirar el desarrollo social de emprendedores de sectores vulnerables, sus familias y comunidades, ampliando sus oportunidades mediante servicios financieros, capacitación y redes.🎯 Principales responsabilidades:Impulsar, coordinar y desarrollar estudios de evaluación de impacto e innovación metodológica a partir del análisis de datos internos y externos.Definir y validar metodologías, instrumentos y modelos de análisis, asegurando su calidad técnica para medir el impacto de los productos y servicios de Fondo Esperanza.Gestionar y asegurar la calidad y robustez de los datos utilizados en los estudios, proponiendo mejoras continuas en su generación y administración.Acompañar a las distintas áreas en la interpretación de hallazgos y en la incorporación de evidencia para la toma de decisiones.Articular y supervisar el trabajo con actores externos como consultores, universidades y centros de investigación, asegurando la alineación con los objetivos institucionales.Proponer nuevas líneas de investigación y mejoras en la gestión de indicadores sociales para identificar oportunidades de innovación.🧠 Requisitos:Formación académica:Sociología, Economía, Ingeniería Comercial, Políticas Públicas, Ciencias Políticas u otras carreras afines.Experiencia laboral:Al menos 3 años en estudios o evaluación de impacto dentro de las políticas públicas, investigación ampliada.Conocimientos técnicos específicos:Métodos avanzados de análisis cuantitativo y cualitativo. (Se requiere cuantitativo)Programación en R, Python o STATA.Manejo de bases de datos relacionales y herramientas de visualización.Conocimiento en evaluación de programas y políticas públicas.Competencias:Pensamiento estratégico y analítico.Capacidad de generar incidencia con evidencia.Comunicación clara de hallazgos a públicos técnicos y no técnicos.Liderazgo técnico y trabajo colaborativo.Innovación metodológica.Condiciones del cargo:Modalidad:Híbrida.Ubicación:Oficina Central.🎁 Beneficios:Días administrativos.Alianza con Caja de Compensación Los Andes.Día libre por cumpleaños.Convenio con clínica dental.Convenio con centro de salud mental.Convenio con gimnasio.Aguinaldos en Fiestas Patrias y Fin de Año.🛡Y una vez con contrato indefinido, también accedes a:Seguro complementario Vida Cámara.Gift Cards de Escolaridad y Navidad.Reconocimiento por excelencia académica.Reincorporación gradual para mamás y papás.Fondo de apoyo a la vivienda.🌟 ¿Por qué postular a Fondo Esperanza?Porque trabajamos con propósito y vivimos nuestros valores día a día. Ponemos a la socia en el centro, enfocándonos en su desarrollo. Creemos que somos un equipo, por eso fomentamos un ambiente colaborativo, positivo y flexible. Promovemos relaciones transparentes, con comunicación abierta y retroalimentación constante. Generamos impacto social real a través de nuestro trabajo ético y comprometido, y siempre aspiramos a más, innovando para llegar más lejos.BeneficiosFormación académica:Sociología, Economía, Ingeniería Comercial, Políticas Públicas, Ciencias Políticas u otras carreras afines.Experiencia laboral:Al menos 3 años en estudios o evaluación de impacto dentro de las políticas públicas, investigación ampliada.Conocimientos técnicos específicos:Métodos avanzados de análisis cuantitativo y cualitativo. (Se requiere cuantitativo)Programación en R, Python o STATA.Manejo de bases de datos relacionales y herramientas de visualización.Conocimiento en evaluación de programas y políticas públicas.Competencias:Pensamiento estratégico y analítico.Capacidad de generar incidencia con evidencia.Comunicación clara de hallazgos a públicos técnicos y no técnicos.Liderazgo técnico y trabajo colaborativo.Innovación metodológica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Químico Farmacéutico Full Time, Santiago</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Cencosud</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55970/quimico-farmaceutico-full-time-santiago</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>0</v>
+      </c>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" t="n">
+        <v>0</v>
+      </c>
+      <c r="L260" t="n">
+        <v>1</v>
+      </c>
+      <c r="M260" t="n">
+        <v>0</v>
+      </c>
+      <c r="N260" t="n">
+        <v>0</v>
+      </c>
+      <c r="O260" t="n">
+        <v>0</v>
+      </c>
+      <c r="P260" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>Si piensas como nosotros que las funciones y el rol del Químico Farmacéutico debe tener estrecha relación con su formación profesional, poniendo como eje central la atención… Entonces este desafío laboral y profesional es para ti!!😀Nos encontramos en búsqueda del mejor Químico Farmacéutico Full Time para nuestra Farmacia Jumbo en nuestro local ubicado en Santiago. Todas las funciones tienen estrecha relación con la formación académica y profesional del Químico Farmacéutico, respetando al 100% la normativa legal y profesional¿Qué esperamos de ti?Elevada ética profesional en el ejercicio de tus funciones.Que te apasione y disfrutes de la atención de clientesTítulo profesional de Químico Farmacéutico (excluyente)Registro al día en la Superintendencia de SaludDisponibilidad para trabajar en turnos rotativosRequisitos de PostulaciónTítulo profesional de Químico Farmacéutico(excluyente)Registro al día en la Superintendencia de SaludDisponibilidad para trabajar Sábado, Domingo y Festivos en turnos rotativosBeneficios¿Qué otras cosas puedes obtener con nosotros?Descuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Seguridad y tranquilidad: todas nuestras Farmacias se encuentran en el interior de nuestros SupermercadosAguinaldo de navidad y fiestas patrias.ColaciónEl mejor lugar para trabajar y estabilidad a toda pruebaY podrás optar a muchos otros beneficios !!¡¡No lo pienses más y sé parte de nuestras Farmacias Jumbo 🐘💚!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Químico Farmacéutico Full time, Jumbo Rancagua</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Cencosud</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Loc Jumbo 504- Rancagua (Mall), Chile</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55960/quimico-farmaceutico-full-time-jumbo-rancagua</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>0</v>
+      </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" t="n">
+        <v>0</v>
+      </c>
+      <c r="L261" t="n">
+        <v>1</v>
+      </c>
+      <c r="M261" t="n">
+        <v>0</v>
+      </c>
+      <c r="N261" t="n">
+        <v>0</v>
+      </c>
+      <c r="O261" t="n">
+        <v>0</v>
+      </c>
+      <c r="P261" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>Si piensas como nosotros que las funciones y el rol del Químico Farmacéutico debe tener estrecha relación con su formación profesional, poniendo como eje central la atención… Entonces este desafío laboral y profesional es para ti!!😀Nos encontramos en búsqueda del mejor Químico Farmacéutico Full Time para nuestra Farmacia Jumbo en nuestro local ubicado en Rancagua. Todas las funciones tienen estrecha relación con la formación académica y profesional del Químico Farmacéutico, respetando al 100% la normativa legal y profesional¿Qué esperamos de ti?Elevada ética profesional en el ejercicio de tus funciones.Que te apasione y disfrutes de la atención de clientesTítulo profesional de Químico Farmacéutico (excluyente)Registro al día en la Superintendencia de SaludDisponibilidad para trabajar en turnos rotativosRequisitos de PostulaciónTítulo profesional de Químico Farmacéutico(excluyente)Registro al dia en la Superintendencia de SaludDisponibilidad para trabajar Sábado, Domingo y Festivos en turnos rotativosBeneficios¿Qué otras cosas puedes obtener con nosotros?Descuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Seguridad y tranquilidad: todas nuestras Farmacias se encuentran en el interior de nuestros SupermercadosAguinaldo de navidad y fiestas patrias.ColaciónEl mejor lugar para trabajar y estabilidad a toda pruebaY podrás optar a muchos otros beneficios !!¡¡No lo pienses más y sé parte de nuestras Farmacias Jumbo 🐘💚!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Químico Farmacéutico Part Time Fines de Semana, Jumbo Rancagua</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Cencosud</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Loc Jumbo 504- Rancagua (Mall), Chile</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55959/quimico-farmaceutico-part-time-fines-de-semana-jumbo-rancagua</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" t="n">
+        <v>0</v>
+      </c>
+      <c r="L262" t="n">
+        <v>1</v>
+      </c>
+      <c r="M262" t="n">
+        <v>1</v>
+      </c>
+      <c r="N262" t="n">
+        <v>0</v>
+      </c>
+      <c r="O262" t="n">
+        <v>0</v>
+      </c>
+      <c r="P262" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>Si piensas como nosotros que las funciones y el rol del Químico Farmacéutico debe tener estrecha relación con su formación profesional, poniendo como eje central la atención… Entonces este desafío laboral y profesional es para ti!!😀Nos encontramos en búsqueda del mejor Químico Farmacéutico Part Time (Fines de semana, 20 horas) para nuestra Farmacia Jumbo Rancagua. Todas las funciones tienen estrecha relación con la formación académica y profesional del Químico Farmacéutico, respetando al 100% la normativa legal y profesionalRequisitos de PostulaciónElevada ética profesional en el ejercicio de tus funciones.Que te apasione y disfrutes de la atención de clientesTítulo profesional de Químico Farmacéutico (excluyente)Registro al día en la Superintendencia de SaludDisponibilidad para trabajar en turnos rotativosBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Seguridad y tranquilidad: todas nuestras Farmacias se encuentran en el interior de nuestros SupermercadosAguinaldo de navidad y fiestas patrias.ColaciónEl mejor lugar para trabajar y estabilidad a toda pruebaY podrás optar a muchos otros beneficios !!¡¡No lo pienses más y sé parte de nuestras Farmacias Jumbo 🐘💚!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Quimico Farmacéutico Part Time fines de semana, Santiago</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Cencosud</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55958/quimico-farmaceutico-part-time-fines-de-semana-santiago</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>0</v>
+      </c>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="n">
+        <v>0</v>
+      </c>
+      <c r="L263" t="n">
+        <v>1</v>
+      </c>
+      <c r="M263" t="n">
+        <v>1</v>
+      </c>
+      <c r="N263" t="n">
+        <v>0</v>
+      </c>
+      <c r="O263" t="n">
+        <v>0</v>
+      </c>
+      <c r="P263" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>Si piensas como nosotros que las funciones y el rol del Químico Farmacéutico debe tener estrecha relación con su formación profesional, poniendo como eje central la atención… Entonces este desafío laboral y profesional es para ti!!😀Nos encontramos en búsqueda del mejor Químico Farmacéutico Part Time (Fines de semana, 20 horas) para nuestra Farmacia Jumbo, Santiago. Todas las funciones tienen estrecha relación con la formación académica y profesional del Químico Farmacéutico, respetando al 100% la normativa legal y profesionalRequisitos de PostulaciónElevada ética profesional en el ejercicio de tus funciones.Que te apasione y disfrutes de la atención de clientesTítulo profesional de Químico Farmacéutico (excluyente)Registro al día en la Superintendencia de SaludDisponibilidad para trabajar en turnos rotativosBeneficios¿Qué otras cosas puedes obtener con nosotros?Descuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Seguridad y tranquilidad: todas nuestras Farmacias se encuentran en el interior de nuestros SupermercadosAguinaldo de navidad y fiestas patrias.ColaciónEl mejor lugar para trabajar y estabilidad a toda pruebaY podrás optar a muchos otros beneficios !!¡¡No lo pienses más y sé parte de nuestras Farmacias Jumbo 🐘💚!!</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Auxiliar de Farmacia PT 20 hrs. (Fines de semana) - Jumbo El Belloto</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Cencosud</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Lc Jumbo 781-El Belloto (Mall), Chile</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55946/auxiliar-de-farmacia-pt-20-hrs-fines-de-semana-jumbo-el-belloto</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>0</v>
+      </c>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" t="n">
+        <v>1</v>
+      </c>
+      <c r="M264" t="n">
+        <v>0</v>
+      </c>
+      <c r="N264" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>¡Porque en Jumbo somos expertos en brindar una buena atención, sabemos que tú eres el indicado para formar parte de nuestro equipo como nuestro nuevo Auxiliar de Farmacia PartTime 20 hrs (FIN DE SEMANA) para apoyar en nuestro Jumbo el Belloto.Las Principales funciones del cargo son colaborar en la dispensación, expendio y/o venta, gestión de almacenamiento, y todo lo concerniente a los medicamentos en la Farmacia.Requisitos de PostulaciónCarnét o Certificado de Auxiliar de Farmacia otorgado por el MINSAL o SEREMI (excluyente)Técnico medio/ colegio técnicoDominio ComputacionalBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Aguinaldo de navidad y fiestas patrias.Bono por vacaciones.Y podrás optar a muchos otros, como un completo Seguro Complementario de Salud, Bono por Escolaridad, Bono por nacimiento de hijo(a), entre otros.Te invitamos a vivir una gran experiencia, donde existen espacios INCLUSIVOS en los que se valoran tus capacidades, convicciones, competencias, experiencia y te desafiamos a desarrollarte constantemente junto a nosotros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Auxiliar de Farmacia Full Time - Jumbo El Belloto</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Cencosud</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Lc Jumbo 781-El Belloto (Mall), Chile</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55945/auxiliar-de-farmacia-full-time-jumbo-el-belloto</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>0</v>
+      </c>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" t="n">
+        <v>0</v>
+      </c>
+      <c r="L265" t="n">
+        <v>1</v>
+      </c>
+      <c r="M265" t="n">
+        <v>0</v>
+      </c>
+      <c r="N265" t="n">
+        <v>0</v>
+      </c>
+      <c r="O265" t="n">
+        <v>0</v>
+      </c>
+      <c r="P265" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>¡Porque en Jumbo somos expertos en brindar una buena atención, sabemos que tú eres el indicado para formar parte de nuestro equipo como nuestro nuevo Auxiliar de Farmacia Full Time para apoyar en nuestro Jumbo El BellotoLas Principales funciones del cargo son colaborar en la dispensación, expendio y/o venta, gestión de almacenamiento, y todo lo concerniente a los medicamentos en la Farmacia.Requisitos de PostulaciónCarnét o Certificado de Auxiliar de Farmacia otorgado por el MINSAL o SEREMI (excluyente)Técnico medio/ colegio técnicoDominio ComputacionalBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Aguinaldo de navidad y fiestas patrias.Bono por vacaciones.Y podrás optar a muchos otros, como un completo Seguro Complementario de Salud, Bono por Escolaridad, Bono por nacimiento de hijo(a), entre otros.Te invitamos a vivir una gran experiencia, donde existen espacios INCLUSIVOS en los que se valoran tus capacidades, convicciones, competencias, experiencia y te desafiamos a desarrollarte constantemente junto a nosotros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Auxiliar de Farmacia Full Time - Jumbo La Reina</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Cencosud</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Loc Jumbo 512-La Reina (Mall), Chile</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55944/auxiliar-de-farmacia-full-time-jumbo-la-reina</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="n">
+        <v>0</v>
+      </c>
+      <c r="L266" t="n">
+        <v>1</v>
+      </c>
+      <c r="M266" t="n">
+        <v>0</v>
+      </c>
+      <c r="N266" t="n">
+        <v>0</v>
+      </c>
+      <c r="O266" t="n">
+        <v>0</v>
+      </c>
+      <c r="P266" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>¡Porque en Jumbo somos expertos en brindar una buena atención, sabemos que tú eres el indicado para formar parte de nuestro equipo como nuestro nuevo Auxiliar de Farmacia Full Time para apoyar en nuestro Jumbo La Reina.Las Principales funciones del cargo son colaborar en la dispensación, expendio y/o venta, gestión de almacenamiento, y todo lo concerniente a los medicamentos en la Farmacia.Requisitos de PostulaciónCarnét o Certificado de Auxiliar de Farmacia otorgado por el MINSAL o SEREMI (excluyente)Técnico medio/ colegio técnicoDominio ComputacionalBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Aguinaldo de navidad y fiestas patrias.Bono por vacaciones.Y podrás optar a muchos otros, como un completo Seguro Complementario de Salud, Bono por Escolaridad, Bono por nacimiento de hijo(a), entre otros.Te invitamos a vivir una gran experiencia, donde existen espacios INCLUSIVOS en los que se valoran tus capacidades, convicciones, competencias, experiencia y te desafiamos a desarrollarte constantemente junto a nosotros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Práctica Profesional - Auditoría TI</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Ofi. Alonso De Cordova 5320 - Auditoria, Chile</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55979/practica-profesional-auditoria-ti</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>3</v>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>analisis, informatica</t>
+        </is>
+      </c>
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="n">
+        <v>1</v>
+      </c>
+      <c r="L267" t="n">
+        <v>0</v>
+      </c>
+      <c r="M267" t="n">
+        <v>0</v>
+      </c>
+      <c r="N267" t="n">
+        <v>1</v>
+      </c>
+      <c r="O267" t="n">
+        <v>0</v>
+      </c>
+      <c r="P267" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>🚀 ¡Buscamos a nuestro/a próximo/a Practicante para Auditoría TI en la Gerencia de Contraloría de Banco Ripley! 💜Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Banco Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro.Ser parte de Banco Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te motiva ser parte de un negocio desafiante y que tu práctica tenga impacto real? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Apoyar al equipo de Auditoría TI en la evaluación independiente y objetiva de los controles tecnológicos, la gestión de riesgos y el cumplimiento normativo del Banco, contribuyendo al fortalecimiento del sistema de control interno, la seguridad de la información y la protección de los activos tecnológicos mediante el uso de herramientas innovadoras y tecnologías emergentes.Funciones: 🤩• Apoyar en la revisión y evaluación de controles de seguridad tecnológica, identificando oportunidades de mejora y fortalecimiento del ambiente de control.• Colaborar en la creación y desarrollo de agentes y soluciones basadas en Inteligencia Artificial para optimizar procesos de auditoría y análisis.• Participar en el seguimiento de planes de acción derivados de auditorías, asegurando la correcta implementación de medidas correctivas.• Apoyar en la evaluación de controles generales de tecnología (ITGC) y prácticas relacionadas con ciberseguridad.• Colaborar en iniciativas de mejora continua relacionadas con auditoría tecnológica, gestión de riesgos y control interno.¿Qué estamos buscando? 💡• Estudiante de Ingeniería en Informática, Ingeniería en Ciberseguridad, Auditoría en Sistemas de Información o carrera afín.• Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)• Disponibilidad de 3 a 6 meses para realizar la práctica.• Conocimientos en estándares de seguridad de la información y ciberseguridad.• Conocimientos de controles generales de tecnología (ITGC).• Interés por auditoría tecnológica, gestión de riesgos, seguridad de la información e Inteligencia Artificial.• Deseable conocimiento o experiencia en herramientas de IA y automatización.• Capacidad analítica, curiosidad tecnológica y orientación al aprendizaje continuo.¿Por qué trabajar en Banco Ripley? 💜Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Auxiliar de farmacia Full Time Jumbo Santiago</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Cencosud</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55969/auxiliar-de-farmacia-full-time-jumbo-santiago</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>0</v>
+      </c>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="n">
+        <v>0</v>
+      </c>
+      <c r="L268" t="n">
+        <v>1</v>
+      </c>
+      <c r="M268" t="n">
+        <v>0</v>
+      </c>
+      <c r="N268" t="n">
+        <v>0</v>
+      </c>
+      <c r="O268" t="n">
+        <v>0</v>
+      </c>
+      <c r="P268" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>¡Porque en Jumbo somos expertos en brindar una buena atención, sabemos que tú eres el indicado para formar parte de nuestro equipo como nuestro nuevo Auxiliar de Farmacia Full Time para apoyar en nuestro Jumbo Santiago.Las Principales funciones del cargo son colaborar en la dispensación, expendio y/o venta, gestión de almacenamiento, y todo lo concerniente a los medicamentos en la Farmacia.Requisitos de PostulaciónCarnét o Certificado de Auxiliar de Farmacia otorgado por el MINSAL o SEREMI (excluyente)Técnico medio/ colegio técnicoDominio ComputacionalBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Aguinaldo de navidad y fiestas patrias.Bono por vacaciones.Y podrás optar a muchos otros, como un completo Seguro Complementario de Salud, Bono por Escolaridad, Bono por nacimiento de hijo(a), entre otros.Te invitamos a vivir una gran experiencia, donde existen espacios INCLUSIVOS en los que se valoran tus capacidades, convicciones, competencias, experiencia y te desafiamos a desarrollarte constantemente junto a nosotros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Auxiliar de Farmacia PT 20 hrs. (Fines de semana) - Jumbo Santiago</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Cencosud</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55948/auxiliar-de-farmacia-pt-20-hrs-fines-de-semana-jumbo-santiago</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>0</v>
+      </c>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" t="n">
+        <v>0</v>
+      </c>
+      <c r="L269" t="n">
+        <v>1</v>
+      </c>
+      <c r="M269" t="n">
+        <v>0</v>
+      </c>
+      <c r="N269" t="n">
+        <v>0</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0</v>
+      </c>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>¡Porque en Jumbo somos expertos en brindar una buena atención, sabemos que tú eres el indicado para formar parte de nuestro equipo como nuestro nuevo Auxiliar de Farmacia PartTime 20 hrs (FIN DE SEMANA) para apoyar en un Jumbo en Santiago.Las Principales funciones del cargo son colaborar en la dispensación, expendio y/o venta, gestión de almacenamiento, y todo lo concerniente a los medicamentos en la Farmacia.Requisitos de PostulaciónCarnét o Certificado de Auxiliar de Farmacia otorgado por el MINSAL o SEREMI (excluyente)Técnico medio/ colegio técnicoDominio ComputacionalBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Aguinaldo de navidad y fiestas patrias.Bono por vacaciones.Y podrás optar a muchos otros, como un completo Seguro Complementario de Salud, Bono por Escolaridad, Bono por nacimiento de hijo(a), entre otros.Te invitamos a vivir una gran experiencia, donde existen espacios INCLUSIVOS en los que se valoran tus capacidades, convicciones, competencias, experiencia y te desafiamos a desarrollarte constantemente junto a nosotros.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q269"/>
+  <dimension ref="A1:Q272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18659,6 +18659,209 @@
         </is>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Analista Jr Calidad Plantas</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Alsea Colombia</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Medellín, Colombia</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56010/analista-jr-calidad-plantas</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>2</v>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L270" t="n">
+        <v>1</v>
+      </c>
+      <c r="M270" t="n">
+        <v>0</v>
+      </c>
+      <c r="N270" t="n">
+        <v>0</v>
+      </c>
+      <c r="O270" t="n">
+        <v>0</v>
+      </c>
+      <c r="P270" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>💥¿Quieres ser parte de nuestro equipo?Nos encontramos en busqueda de nuestro proximo/a Analista de Calidad Plantas que quiera ser parte de una compañía líder en el sector de restaurantes y food service, aportando al fortalecimiento de nuestros estándares de calidad e inocuidad alimentaria.Si te apasiona la mejora continua, los procesos productivos y el desarrollo de culturas de calidad, esta oportunidad es para ti.¿Cuál será tu proposito?Asegurar el cumplimiento de los estándares de calidad e inocuidad alimentaria en nuestras plantas de producción, contribuyendo a la implementación, mantenimiento y mejora continua de los sistemas de gestión, garantizando productos seguros y procesos alineados con la normativa vigente.📍 Medellín / Bello, Colombia🌟 Responsabilidades:Velar por el cumplimiento de los estándares de calidad e inocuidad en las plantas de producción.Implementar y fortalecer los sistemas de gestión de calidad y seguridad alimentaria.Realizar seguimiento a indicadores, auditorías y planes de acción asociados a la mejora continua.Capacitar y acompañar a los equipos operativos en materias de calidad e inocuidad.Promover una cultura de calidad, colaborando transversalmente con las distintas áreas de la operación.Capacitar y acompañar a los equipos de planta en materias de seguridad alimentaria.Promover el fortalecimiento de la cultura de calidad dentro de la operación.Coordinar acciones con áreas de Producción, Mantenimiento, Compras, SST, Logística y Recursos Humanos.Identificar oportunidades de mejora y proponer cambios que fortalezcan los procesos productivos y el sistema de gestión.RequisitosProfesional en Ingeniería en Alimentos, Microbiología o carreras afines.Al menos 2 años de experiencia en calidad dentro de plantas de producción de alimentos.Conocimiento de BPM, HACCP y sistemas de gestión de inocuidad alimentaria.Experiencia en auditorías y seguimiento de planes de acción.Manejo de Excel intermedio.Beneficios👪 En nuestro equipo:👉 Demostramos pasión por la excelencia y buscamos superar cada desafío.👉 Impulsamos una cultura de reconocimiento y gratitud en todo lo que hacemos.👉 Creamos experiencias únicas, llenas de sabor y cercanía.👉 Somos impacto positivo, comprometidos con el negocio, las personas y el entorno.¿Cuál es nuestro compromiso? Te sumas a una compañía con una cultura diversa e inclusiva, donde promovemos un ambiente de respeto, colaboración y oportunidades de desarrollo, valorando el aporte único de cada persona.❤️ En Alsea somos la suma de experiencias únicas y espacios para ser felices. ¿Te unes? 😎</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Asistente contable (Outsourcing)</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Forvis Mazars</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56003/asistente-contable-outsourcing</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="n">
+        <v>1</v>
+      </c>
+      <c r="L271" t="n">
+        <v>0</v>
+      </c>
+      <c r="M271" t="n">
+        <v>0</v>
+      </c>
+      <c r="N271" t="n">
+        <v>0</v>
+      </c>
+      <c r="O271" t="n">
+        <v>0</v>
+      </c>
+      <c r="P271" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>Con nosotros tienes la oportunidad de pertenecer a una firma internacional con un importante potencial de crecimiento y un equipo de más de 40.000 profesionales altamente capacitados, que brinda servicios profesionales generando alto impacto en todos nuestros clientes en más de 100 países en los cinco continentes.Podrás formar parte de un equipo que valorará tus ideas, apoyará tus ambiciones y celebrará tus éxitos. En Forvis Mazars nos proponemos impulsar la colaboración y la flexibilidad, las diversas perspectivas de nuestros colaboradores y el progreso.Hoy buscamos un/aAsistente Contablepara integrarse a nuestro equipo de Outsourcing. La persona será responsable de apoyar la gestión contable y administrativa de una cartera de clientes, asegurando el registro oportuno y correcto de la información financiera, el cumplimiento de procedimientos internos y el apoyo en procesos tributarios y administrativos.Tareas y ResponsabilidadesRegistrar transacciones contables de clientes en los sistemas definidos.Preparar y mantener actualizados los registros contables de la cartera de clientes asignada.Gestionar y mantener la documentación contable y administrativa, tanto física como digital.Revisar y actualizar información contable en ERP y sistemas de gestión.Apoyar en la elaboración de reportes e informes requeridos por clientes y la jefatura.Cumplir con los procedimientos, políticas internas y estándares de calidad establecidos para el servicio.RequisitosTécnico de Nivel Superior en Contabilidad General, Contador Auditor o carrera afín.Hasta 2 años de experiencia.Deseable experiencia en funciones administrativas y/o contables.Manejo de Microsoft Office.Conocimientos de ERP contables.Conocimientos básicos de normativa contable y tributaria.Capacidad de organización y atención al detalle.Deseable experiencia trabajando con carteras de clientes o servicios de outsourcing.OfrecemosPaquete de compensaciones de mercadoSeguro Complementarios de salud y Dental, además de seguro de VidaUna experiencia dinámica, diversa e inclusiva, en una Firma con orientación en las personas, desarrollo y crecimientoEducación continua, tanto de programas internos, corporativos y externosDías adicionales de vacaciones.Este cargo es compatible para personas con discapacidad, se enmarca en la ley 21.015, que incentiva la inclusión de personas con discapacidad al mundo laboral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Analista Actuarial</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56011/analista-actuarial</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>8</v>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>python, analisis, estadistica, matematica</t>
+        </is>
+      </c>
+      <c r="I272" t="n">
+        <v>1</v>
+      </c>
+      <c r="J272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K272" t="n">
+        <v>1</v>
+      </c>
+      <c r="L272" t="n">
+        <v>0</v>
+      </c>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+      <c r="N272" t="n">
+        <v>0</v>
+      </c>
+      <c r="O272" t="n">
+        <v>0</v>
+      </c>
+      <c r="P272" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>Importante empresa de servicios financieros se encuentra en búsqueda de un Analista Actuarial Junior, que será responsable de contribuir a la generación de análisis estratégicos, desarrollo de modelos y proyecciones financieras, apoyando la toma de decisiones en una organización líder del sector financiero.Principales responsabilidades:Apoyar el desarrollo, actualización y validación de modelos actuariales utilizados para análisis, medición y proyecciones del negocio.Crear análisis y reportes que contribuyan a la evaluación de resultados, tendencias y desempeño de productos.Supervisar la calidad, consistencia e integridad de la información utilizada en los procesos actuariales.Gestionar análisis relacionados con tarifas, reservas, rentabilidad, experiencia de siniestralidad y métricas de riesgo.Desarrollar proyecciones financieras y escenarios de negocio para apoyar la planificación y la toma de decisiones.Coordinar con áreas de Finanzas, Riesgos, Productos, Operaciones y otras funciones relacionadas para asegurar una adecuada implementación de modelos y análisis.Requisitos:Título profesional en Ingeniería Matemática o Ingeniería Estadística.Un año de experiencia en funciones similares y/o interés en desarrollarte en esta área.Inglés avanzado o fluido, tanto oral como escrito.Experiencia en programación y análisis de datos utilizando Python.Interés o experiencia en herramientas de inteligencia artificial generativa y automatización (Copilot u otras soluciones similares).Competencias que buscamos:Sólida capacidad analítica y estadística.Orientado a resultadosAutonomíaRelacionamientoComunicación a todo nivelBeneficiosTe ofrecemos:Trabajo colaborativo con equipos multidisciplinarios.Acceso a tecnologías, herramientas analíticas e iniciativas de innovación.Oportunidades de desarrollo profesional en un entorno desafiante.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q272"/>
+  <dimension ref="A1:Q279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18862,6 +18862,481 @@
         </is>
       </c>
     </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Consultor de Proyecto | Matrix Consulting</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Matrix Consulting</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Av. presidente Riesco 5435, Multipaís</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56058/consultor-de-proyecto-matrix-consulting</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>1</v>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I273" t="n">
+        <v>1</v>
+      </c>
+      <c r="J273" t="n">
+        <v>0</v>
+      </c>
+      <c r="K273" t="n">
+        <v>1</v>
+      </c>
+      <c r="L273" t="n">
+        <v>0</v>
+      </c>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+      <c r="N273" t="n">
+        <v>1</v>
+      </c>
+      <c r="O273" t="n">
+        <v>0</v>
+      </c>
+      <c r="P273" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>¡¡Te invitamos a formar parte de nuestro equipo de Matrixianos!! Estamos buscando personas como tú, apasionadas, enfocadas y con todas las ganas de crecer.Misión del cargoComo Consultor, podrá desarrollar junto al equipo de consultoría de proyectos labores de investigación y análisis, colaborando en el desarrollo de soluciones y recomendaciones de negocio para los clientes. El consultor deberá profundizar sus conocimientos en distintas industrias, clientes y áreas de práctica (estrategia, organización, operaciones, finanzas corporativas, transformación digital etc.) creando valor mediante la entrega de propuestas que se ajusten a las necesidades de los clientes.FuncionesDesarrollar diagnósticos y propuestas, acordes a los desafíos y problemáticas planteadas por los clientes.Realizar investigación y búsqueda de información relevante para el proyecto; estructurando y ejecutando los análisis de información.Anticipar requerimientos del proyecto, proponer lineamientos y objetivos para la generación de material de apoyo.Preparar presentaciones y otros documentos para clientes, liderando algunas reuniones en entornos de bajo riesgo.Ejecutar estrategia y planes diseñados, con foco en la mejora continua.RequisitosProfesión: Ing. Civil Industrial, Ing. Comercial, Ing. Industrial o Economista; Administración de Empresas o similaresIdioma: Inglés avanzado (oral y escrito) - B2/C1Experiencia laboral: 0 a 2 años - Entry levelExperiencia valorada: Experiencia relacionada con la consultoría como finanzas, control de gestión, estudios, evaluación de proyectos, desarrollo, nuevos negocios o similar (deseable, no excluyente).Otros: Participación en actividades que demuestran compromiso y liderazgo como: centro de alumnos, organizaciones sin fines de lucro, deportes, etc.Esta vacante tendrá como base Chile, Colombia o Perú (con viajes incluidos) y Argentina con posibilidad de traslado.BeneficiosDías adicionales de vacacionesDesarrollo profesional aceleradoTrabajar en una firma líder en consultoría.Ambiente de trabajo colaborativo y dinámicoCofinanciamiento con Wellhub para que puedas hacer deporte¡Celebramos todo! nuestros logros, cumpleaños, festividades y más</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Desarrollador(a) de Automatización e Inteligencia Artificial</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Postedin</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Multipaís</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Remoto Trabajo</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56051/desarrollador-a-de-automatizacion-e-inteligencia-artificial</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>17</v>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>python, analisis, informatica, javascript, gemini, zapier, n8n</t>
+        </is>
+      </c>
+      <c r="I274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" t="n">
+        <v>1</v>
+      </c>
+      <c r="K274" t="n">
+        <v>0</v>
+      </c>
+      <c r="L274" t="n">
+        <v>0</v>
+      </c>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+      <c r="N274" t="n">
+        <v>1</v>
+      </c>
+      <c r="O274" t="n">
+        <v>0</v>
+      </c>
+      <c r="P274" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>Modalidad:RemotoTipo de contrato:A convenirUbicación:LATAMSobre PostedinEn Postedin ayudamos a marcas líderes de Latinoamérica a mejorar su visibilidad orgánica en buscadores, asistentes de inteligencia artificial y plataformas digitales. Combinamos estrategia, tecnología, datos y automatización para entender cómo las personas encuentran información y cómo las marcas pueden ser relevantes dentro de ese proceso.Hoy estamos buscando una persona para integrarse a nuestro equipo de Desarrollo e Inteligencia Artificial, donde trabajará en la creación de automatizaciones, herramientas internas, análisis de datos y proyectos de investigación relacionados con el funcionamiento de los modelos de IA y los motores de búsqueda.¿Qué harás?Diseñar e implementar automatizaciones utilizando herramientas low-code y desarrollo personalizado.Crear integraciones entre plataformas mediante APIs.Participar en el desarrollo de herramientas internas impulsadas por inteligencia artificial.Construir dashboards y sistemas de visualización para equipos técnicos, ejecutivos y clientes.Investigar cómo los motores de búsqueda y los modelos de IA descubren, interpretan y priorizan información.Analizar patrones de visibilidad de marcas, conceptos y contenidos en Google, ChatGPT, Gemini, Claude y otras plataformas de IA.Apoyar el desarrollo de procesos de captura, transformación y análisis de datos.Colaborar con equipos de SEO, contenido, estrategia y analítica para convertir hallazgos en soluciones escalables.Experimentar constantemente con nuevas tecnologías, frameworks y herramientas impulsadas por IA.Lo que buscamosMás que un especialista en marketing digital, buscamos una persona con mentalidad técnica, curiosidad y ganas de aprender.Nos interesa alguien que:Disfrute investigando cómo funcionan las cosas.Tenga interés genuino por la inteligencia artificial y sus aplicaciones.Utilice herramientas de IA dentro de su flujo diario de trabajo.Se sienta cómodo construyendo soluciones, automatizando procesos y conectando sistemas.Tenga iniciativa para aprender tecnologías nuevas de manera autónoma.RequisitosFormación en Ingeniería Informática, Desarrollo de Software, Ciencia de Datos o carrera afín.Experiencia desarrollando software o automatizaciones.Conocimientos de programación en al menos un lenguaje moderno (Python, JavaScript, TypeScript u otro equivalente).Experiencia consumiendo e integrando APIs.Familiaridad con herramientas como N8N, Make, Zapier o similares.Manejo de bases de datos y procesamiento de información.Capacidad para analizar problemas y proponer soluciones técnicas.DeseablesConocimientos sobre LLMs (Large Language Models) y técnicas de prompting.Experiencia utilizando APIs de modelos de IA.Conocimientos de scraping, extracción y procesamiento de datos.Experiencia en herramientas de visualización y dashboards.Familiaridad con Google Analytics, Google Search Console, Ahrefs, Semrush o plataformas similares.Interés por SEO, GEO (Generative Engine Optimization), AEO (Answer Engine Optimization) y búsqueda impulsada por IA.Lo que aprenderásCómo funcionan los motores de búsqueda modernos y los asistentes de IA.Técnicas para analizar y mejorar la visibilidad de marcas en entornos de inteligencia artificial.Desarrollo de herramientas basadas en LLMs.Automatización avanzada de procesos de marketing y análisis de datos.Construcción de sistemas de monitoreo, dashboards e inteligencia de negocio.Aplicación práctica de IA en proyectos reales para empresas líderes de Latinoamérica.Lo que valoramos especialmenteNo esperamos que llegues sabiendo todo.Valoramos más la capacidad de aprender rápido, la curiosidad técnica, la pasión por construir soluciones y el interés por entender uno de los desafíos más interesantes de la industria hoy: descubrir cómo los motores de búsqueda y los modelos de inteligencia artificial encuentran, interpretan y recomiendan información.Si te entusiasma investigar, experimentar y construir herramientas que ayuden a entender las nuevas reglas de Internet, nos gustaría conocerte.BeneficiosAfiliación a Caja Los Andes.Acceso a Seguro de Salud Complementario al pasar a contrato indefinido.Previsión según topes legales.Tipo de trabajo: remotoSeguro de salud.Día de cumpleaños libre.Oportunidades de desarrollo y crecimiento profesional.Ambiente de trabajo dinámico y colaborativo.Acceso a capacitaciones continuas en marketing digital y SEO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Asistente de Ventas Full Time – Tanner Servicios Financieros</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Tanner</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56079/asistente-de-ventas-full-time-tanner-servicios-financieros</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>0</v>
+      </c>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" t="n">
+        <v>0</v>
+      </c>
+      <c r="L275" t="n">
+        <v>1</v>
+      </c>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+      <c r="N275" t="n">
+        <v>0</v>
+      </c>
+      <c r="O275" t="n">
+        <v>0</v>
+      </c>
+      <c r="P275" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>En Tanner seguimos creciendo y queremos que tú también seas parte de este equipo.Buscamos a nuestro próximo/aAsistente de Ventas Full Time, quien tendrá la misión de brindar un servicio de excelencia a nuestros clientes en el punto de venta, asesorándolos en productos financieros y seguros automotrices.¿Qué harás?Asesorar y apoyar en la venta de productos financieros y seguros automotrices.Entregar una experiencia de atención cercana y de calidad, ayudando a cada cliente a encontrar la mejor alternativa según sus necesidades.Validar documentación y respaldos asociados a los cierres de financiamiento.Representar a Tanner con una actitud proactiva, empática y orientada al servicio.En Tanner valoramos el compromiso, la cercanía y el trabajo colaborativo, ofreciendo un espacio donde podrás desarrollarte y generar impacto en la experiencia de nuestros clientes.¡Te invitamos a postular y ser parte de Tanner!Requisitos🔎 ¿Qué buscamos?Deseable contar con estudios técnicos o profesionales en áreas comerciales, administración o afines.Al menos 1 año de experiencia en atención al cliente o ventas (idealmente en retail o servicios financieros).Habilidades comunicacionales y orientación al cliente.Disponibilidad para trabajar en modalidad presencial 5x2, 3 días en la semana, incluyendo sábado y domingo de forma fija</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Práctica profesional - Comunicaciones internas</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56047/practica-profesional-comunicaciones-internas</t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>0</v>
+      </c>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" t="n">
+        <v>0</v>
+      </c>
+      <c r="K276" t="n">
+        <v>1</v>
+      </c>
+      <c r="L276" t="n">
+        <v>0</v>
+      </c>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+      <c r="N276" t="n">
+        <v>1</v>
+      </c>
+      <c r="O276" t="n">
+        <v>0</v>
+      </c>
+      <c r="P276" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>Práctica profesional - Comunicaciones internas 🚀 ¡Buscamos a nuestro/a próximo/a practicante para el Área de Comunicaciones Internas y Eventos Estratégicos en la Gerencia Corporativa de Personas de Ripley!Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Ripley/Banco Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro.Ser parte de Ripley/Banco Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te motiva ser parte de un negocio desafiante y que tu práctica tenga impacto real? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Ser parte activa de distintos proyectos del área, apoyando su coordinación, seguimiento y visibilidad comunicacional.Funciones: 🤩Ser parte activa de distintos proyectos del área, apoyando su coordinación, seguimiento y visibilidad comunicacional.Crear, proponer y ejecutar contenido para nuestro Instagram interno, potenciando iniciativas, cultura y experiencias de marca interna.¿Qué estamos buscando? 💡Estudiante de Publicidad o Periodismo.Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)Disponibilidad de 6 meses. (deseable posibilidad de extensión)Conocimiento en canva y suite de adobe, además de conocimiento de edición de videos.¿Por qué trabajar en Ripley/Banco Ripley? 💗Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.   ¡TRABAJA CON NOSOTROS!BeneficiosDescripción de los beneficios de la vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Practica profesional - Desarrollo Organizacional</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Ofi. Alonso De Cordova 5320 - RECURSOS HUMANO, Chile</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56044/practica-profesional-desarrollo-organizacional</t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>2</v>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I277" t="n">
+        <v>0</v>
+      </c>
+      <c r="J277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" t="n">
+        <v>1</v>
+      </c>
+      <c r="L277" t="n">
+        <v>0</v>
+      </c>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+      <c r="N277" t="n">
+        <v>1</v>
+      </c>
+      <c r="O277" t="n">
+        <v>0</v>
+      </c>
+      <c r="P277" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>Practica profesional - Desarrollo Organizacional 🚀 ¡Buscamos a nuestro/a próximo/a practicante para el Área de Desarrollo Organizacional en la Gerencia de Gestión de personas de Ripley!Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Ripley/Banco Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro.Ser parte de Ripley/Banco Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te motiva ser parte de un negocio desafiante y que tu práctica tenga impacto real? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Impulsar el desarrollo del talento interno y acompañar a cada colaborador en su viaje profesional, mediante iniciativas y procesos que fortalezcan su crecimiento, fomenten su compromiso y estén alineados con nuestra cultura corporativa. Buscamos crear experiencias significativas, simples y humanas que potencien el valor de las personas dentro de Ripley.Funciones: 🤩Levantar y mapear los procesos del área de Desarrollo Organizacional desde la perspectiva del colaborador, identificando puntos de fricción y oportunidades de mejora.Analizar la experiencia de usuario en los distintos procesos de desarrollo de talento, mediante herramientas de diagnóstico como entrevistas, encuestas u observación directa.Diseñar propuestas de mejora centradas en el usuario, que simplifiquen la experiencia y estén alineadas con la cultura organizacional.Trabajar en conjunto con el área de Datos y el equipo de desarrollo de la plataforma externa para crear, diseñar y realizar las modificaciones necesarias en los procesos definidos.¿Qué estamos buscando? 💡Estudiante de último año de la carrera de Psicología, Ingeniería/Técnico en administración de empresas, ingeniería comercial.Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)Disponibilidad de 6 meses. (deseable posibilidad de extensión)Conocimiento en Excel.¿Por qué trabajar en Ripley/Banco Ripley? 💗Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.   ¡TRABAJA CON NOSOTROS!BeneficiosDescripción de los beneficios de la vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Category Manager Tecno</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Ofi Cerro Colorado 5240 - Comercial, Chile</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56032/category-manager-tecno</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>1</v>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I278" t="n">
+        <v>1</v>
+      </c>
+      <c r="J278" t="n">
+        <v>0</v>
+      </c>
+      <c r="K278" t="n">
+        <v>1</v>
+      </c>
+      <c r="L278" t="n">
+        <v>0</v>
+      </c>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
+      <c r="P278" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>Category Manager Tecno¡En Ripley Chile, lo tenemos todo! ¡Solo nos falta tu talento! 🤩🩷Somos un equipo diverso, ágil y colaborativo, enfocado en mejorar constantemente la experiencia de nuestros clientes a través de la innovación y una sólida cultura de servicio. Si te apasiona el análisis de datos, el trabajo en equipo y enfrentar nuevos desafíos, esta oportunidad es para ti.¡Postula para ser parte de nuestro equipo!Estamos en búsqueda de nuestro/a nuevo/a Category Manager Tecno - Electro Menor y Audio para nuestra Gerencia Comercial.¿Cuáles serán tus principales desafíos? 🚀Apoyar la definición de estrategia comercial del departamento: Electro menor y AudioGenerar órdenes de compra.Ejecutar cambio de precios y costos.Realizar la gestión operacional del departamento.Apoyar al área en negociaciones con las marcas involucradas.Ser el contacto directo entre Product Manager y las tiendas¿Qué valoramos en tu postulación? 🎯Título Profesional en Ingeniería Comercial/Civil Industrial (Excluyente)Microsoft Office Avanzado (Excluyente)Dominio Inglés IntermedioExperiencia de al menos 1 año en cargos similares o áreas comerciales.Deseable experiencia en retail.¿Por qué trabajar en Ripley?🩷Pensamos en el bienestar de nuestros colaboradores, es por esto que contamos con atractivos beneficios corporativos como:Capacitaciones y entrenamiento enfocado a tu desarrollo de carrera.Tasa Preferencial en Productos Banco Ripley.Seguro Complementario Gratuito.Descuento en Tiendas Ripley.Desarrollo Profesional.Entre otros.En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarloBeneficiosDescripción de los beneficios de la vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Analista de riesgo financiero (foco quant)</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>AFP Modelo</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Avda de valle 614 Huechuraba, Chile, Chile</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56049/analista-de-riesgo-financiero-foco-quant</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>10</v>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>python, sql, estadistica, matematica</t>
+        </is>
+      </c>
+      <c r="I279" t="n">
+        <v>0</v>
+      </c>
+      <c r="J279" t="n">
+        <v>0</v>
+      </c>
+      <c r="K279" t="n">
+        <v>1</v>
+      </c>
+      <c r="L279" t="n">
+        <v>0</v>
+      </c>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
+        <v>0</v>
+      </c>
+      <c r="P279" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>¿Quiénes somos?Somos una AFP orientada a las personas, comprometida con su bienestar presente y futuro. Destacamos que, en línea con nuestra cultura organizacional, nuestras búsquedas se enmarcan bajo la ley 21.015, la cual promueve la inclusión laboral de las personas con discapacidad.¿Quieres sumarte a cientos de profesionales que buscan contribuir con entusiasmo y responsabilidad al bienestar de las personas? ¡Esta es tu oportunidad!¿Cuáles serán los desafíos del cargo?Analizar, desarrollar e implementar herramientas tecnológicas y financieras, usando modelos con enfoques principalmente matemáticos y estadísticos que permitan monitorear y aportar información relevante para la toma de decisiones y el control de riesgos financieros. Lo anterior, acorde a la normativa vigente y futuros cambios relevantes de la industria.Funciones principales:Analizar, desarrollar e implementar herramientas y modelos que complementen los vigentes y mejoren en sistema de control de riesgos financieros.Aportar información relevante para la toma de decisiones de inversiones y el control de riesgos financieros, particularmente riesgos de mercado y liquidez.Desarrollo de nuevas herramientas tecnológicas que apunten a hacer más eficiente y eficaz el control de riesgos financieros.¿Qué buscamos?Profesionales de Ingeniería Civil Matemática, en Computación, Estadística o carreras afines con fuerte base cuantitativa.Interés y/o conocimiento en mercados financieros, métricas y modelos de riesgos financieros.Manejo de SQL y Python excluyenteExperiencia: Deseable 1 año en cargos similares.¡Te esperamos!BeneficiosBus de acercamientoDía de CumpleañosSeguro complementarioy muchos beneficios más</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q279"/>
+  <dimension ref="A1:Q284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19337,6 +19337,343 @@
         </is>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Auditor Tributario - Tax &amp; Legal</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>KPMG Chile</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Las Condes, Metropolitana, Chile, Chile</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56087/auditor-tributario-tax-legal</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>0</v>
+      </c>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="n">
+        <v>1</v>
+      </c>
+      <c r="J280" t="n">
+        <v>0</v>
+      </c>
+      <c r="K280" t="n">
+        <v>1</v>
+      </c>
+      <c r="L280" t="n">
+        <v>0</v>
+      </c>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>**Perfil Ideal: Auditor Tributario - Tax &amp; Legal** Buscamos un **Auditor Tributario** con un mínimo de **2 años de experiencia** en cumplimiento tributario, para unirse a nuestro equipo de Tax &amp; Legal. El candidato ideal poseerá un título universitario en **Contador Auditor** (titulado o egresado) y un sólido interés en los procesos contables, financieros y tributarios. Las responsabilidades clave incluirán la preparación y presentación de impuestos mensuales (IVA e Impuesto Adicional), la determinación de Renta Líquida Imponible y Capital Propio Tributario, la elaboración de Registros de Rentas Empresariales para grandes empresas, y la determinación de provisiones de impuesto a la Renta e Impuestos Diferidos. Se espera un profundo conocimiento y aplicación de la normativa tributaria vigente. Se valorará el dominio **básico-intermedio de Microsoft Office** y, deseablemente, un nivel **intermedio-avanzado de inglés**. Este rol, de nivel **Junior**, es una excelente oportunidad para profesionales que buscan crecer en una de las cuatro consultoras auditoras más grandes del mundo y contribuir activamente al futuro de los negocios.Beneficios¿Qué ganas tú? 🌎Ser parte de una de las principales compañías de Auditoría y Consultoría a nivel mundial. 🚀 Oportunidades de desarrollo profesional. 🚑 Seguro de salud complementario con contrato indefinido. 💻 Jornada de trabajo híbrida. 🏢 Oficinas de primer nivel ubicadas en Las Condes, frente al Parque Araucano. 💯 Múltiples convenios corporativos. 🎉 Actividades como fiestas, Meeting Points y encuentros de área para disfrutar con compañeros. 🎂 16 horas anuales a libre disposición y tu día de cumpleaños es completamente libre para que lo disfrutes como desees. En KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas , con un propósito claro, para una mejor sociedad. Valoramos las diversas habilidades y fortalezas, tanto personales como profesionales, que cada persona aporta. En KPMG estamos comprometidos con la Diversidad e inclusión , nuestras ofertas de empleo están disponibles con los ajustes razonables necesarios para tu proceso. Juntos, estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. ¡Anímate y ven a descubrir por qué somos la opción más clara! 🥇</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Analista Siniestros RV</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Fid seguros</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56096/analista-siniestros-rv</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>0</v>
+      </c>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="n">
+        <v>0</v>
+      </c>
+      <c r="J281" t="n">
+        <v>0</v>
+      </c>
+      <c r="K281" t="n">
+        <v>1</v>
+      </c>
+      <c r="L281" t="n">
+        <v>0</v>
+      </c>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+      <c r="N281" t="n">
+        <v>0</v>
+      </c>
+      <c r="O281" t="n">
+        <v>0</v>
+      </c>
+      <c r="P281" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>FID Seguros es una compañía diseñada para integrar la tecnología como base de la experiencia de corredores y clientes. Nos definimos como una insurtech de seguros generales, que utiliza la digitalización para ofrecer experiencias simples, ágiles y transparentes, apalancado en la innovación, en el uso de la tecnología, en el trabajo en equipo y el compromiso.Actualmente nos encontramos en búsqueda de un/a Analista de Siniestros RV.¿Qué harás en este rol?Controlar y gestionar el ingreso de pérdidas probables en el plazo establecido en el procedimiento.Analizar y gestionar, según corresponda, requerimientos contenidos en pre-informes de liquidación emitido por liquidadores oficiales de seguros.Analizar la propuesta contenida en el informe de liquidación y gestionar, pago, rechazo o impugnación según corresponda. Para liquidadores oficiales a nivel nacionalVelar por el correcto pago al beneficiario en el plazo establecido en el procedimiento de la Compañía y en la norma.Gestionar el cobro y controlar el estado de pago de siniestros que afecten a pólizas con cláusula de libre pacto.Administrar y controlar la gestión de recupero legal y material.Mantener al día nómina de profesionales externos con la respectiva tabla de honorarios y comunicar su aplicación a nivel nacional.Desarrollar y mantener versión vigente de Manuales.Liquidar en forma directa.Participar en el desarrollo e implementación del sistema informático del área y de las modificaciones o cambios futuros.Desarrollar procedimiento de mejora continua.Desarrollar y comunicar sistemáticamente informes de gestión del área.¿Qué buscamos en ti?Titulado/a de Ingeniería en Construcción, Contador Auditor, Derecho, Ing Comercial, Civil Industrial.Experiencia de 1 año en roles similares.BeneficiosLo que ofrecemosModalidad de trabajo híbrida.Horario flexibleBeneficios como bono por desempeño, ajustes semestrales por IPC, seguro complementario y de vida, días administrativos, acuerdos de descuentos varios, entre otros.Esta oferta laboral se rige bajo la Ley Nº 21.015 que incentiva la inclusión de personas con discapacidad al mundo laboral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Analista de Coordinación Siniestros (técnicoingeniería en administración o carrera afín)</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Fid seguros</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56095/analista-de-coordinacion-siniestros-tecnico-ingenieria-en-administracion-o-carrera-afin</t>
+        </is>
+      </c>
+      <c r="G282" t="n">
+        <v>1</v>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I282" t="n">
+        <v>0</v>
+      </c>
+      <c r="J282" t="n">
+        <v>0</v>
+      </c>
+      <c r="K282" t="n">
+        <v>1</v>
+      </c>
+      <c r="L282" t="n">
+        <v>0</v>
+      </c>
+      <c r="M282" t="n">
+        <v>0</v>
+      </c>
+      <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="P282" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>EnFID Seguros, no solo somos una compañía de seguros generales; Somos el equipo que construye confianza, innova en servicio y transforma desafíos en soluciones. Buscamos a aquellos apasionados por aprender, crecer y contribuir desde el primer día.Actualmente nos encontramos en búsqueda Analista de Coordinación Siniestros a plazo fijo 3 meses,¿Qué harás en este rol?Realizar el ingreso de información/documentación relevante en sistemas para agilizar el proceso de liquidación de siniestros.Realizar la Cargar de documentación (CAV, Inspección de Riesgo, entre otros) en el sistema de siniestros para facilitar el análisis en el proceso de liquidación por parte de liquidador y analista de siniestros.Realizar la Validación e ingreso de denuncios de compañías coaseguradoras en sistema de siniestros para lograr registrar el siniestro en sistema de siniestros con su debida reserva.Coordinar y realizar reuniones con contrapartes internas y externas  para proveer de información sobre desempeño de gestión Intercompañía, coaseguro y carga de documentación.Realizar reportes de control y gestión en área de siniestros para contribuir el cumplimiento de indicadores de servicio y realizar feedback.RequisitosConocimientos de:  Técnico y/o Ingeniero en Administración, carrera afín. Normativa de seguros Manejo de office intermedioExperiencia en gestión y control de Información.Beneficios- Modalidad híbrida</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Category Manager Nuevos Negocios</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Ofi Cerro Colorado 5240 - Comercial, Chile</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56091/category-manager-nuevos-negocios</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>1</v>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I283" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" t="n">
+        <v>0</v>
+      </c>
+      <c r="K283" t="n">
+        <v>1</v>
+      </c>
+      <c r="L283" t="n">
+        <v>0</v>
+      </c>
+      <c r="M283" t="n">
+        <v>0</v>
+      </c>
+      <c r="N283" t="n">
+        <v>1</v>
+      </c>
+      <c r="O283" t="n">
+        <v>0</v>
+      </c>
+      <c r="P283" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>Category Manager Nuevos NegociosEn Ripley Chile, lo tenemos todo ¡Solo nos falta tu talento! 🤩Promovemos equipos diversos y colaborativos, buscando mejorar la experiencia de nuestros clientes a través de la innovación y la cultura de servicio. ¡Súmate a una industria ágil y desafiante!¡Postula para ser parte de nuestro equipo!Estamos en búsqueda de nuestro nuevo Category Manager para la Gerencia de Nuevos Negocios, de nuestra Gerencia Comercial.¿Cuáles serán tus principales desafíos?Encargado de apoyar al comprador en rentabilizar las categorías de Garantía y Rphone de todas las tiendas Ripley y Ripley.com. Para ello deberá poner en práctica todos sus conocimientos comerciales, venta y de marketing para poder crear acciones que generen el crecimiento del negocio. Parte de su responsabilidad será reunirse con proveedores (marcas), buscar nuevos productos, rentabilizar los actuales, visitar tiendas. Si eres una persona que se apasiona por el trabajo dinámico y el desafío constante ¡Esta es tu oportunidad de hacer que las cosas pasen!Tus principales funciones:🚀Estrategias Comerciales: Crear estrategias comerciales y de precios para llegar a las metas de venta y contribución presupuestadas por temporada.Mix de Compra: Presupuestar la compra de marcas y productos nacionales e importados, y en base a ello, generar el mix adecuado de productos y definir la carga de estos, en tiendas de cuerdo a capacidades, de manera de rentabilizar el metro cuadrado.Administrar la Compra: Revisar los abiertos de compra con los Planificadores de Compras, y seguir el comportamiento de las ventas, a fin de mantener volumen y stock suficientes para asegurar el óptimo desarrollo comercial por categoría y ubicación, y/o definir liquidaciones.Análisis de Tendencias de Mercado: Analizar e investigar los mercados internos y externos en cuanto a sus tendencias, competencia y cambios en la moda para así generar atractivas colecciones.Administración de Inventario: Negociar y coordinar constantemente con proveedores para definir precios, calidades, tiempos de despacho, condiciones de pago, cantidades, y exhibición de productos; y supervisar el comportamiento de stocks para la toma oportuna de decisiones en cuanto a compras futuras.Abastecimiento: Supervisar la llegada de los productos y abastecimiento hacia las tiendas.¿Cuáles son los requisitos para tu postulación?🎯Ingeniería Comercial con orientación a Ventas y Marketing (Excluyente)Deseable experiencia 0-1 año en compras consumo masivo o retailManejo de Microsoft Office Intermedio-Avanzado (Excluyente)Ser proactivo, enérgico y dinámico¿Por qué trabajar en Ripley?Pensamos en el bienestar de nuestros colaboradores, es por esto que contamos con atractivos beneficios corporativos como:Capacitaciones y entrenamiento enfocado a tu desarrollo de carrera.Tasa Preferencial en Productos Banco Ripley.Seguro Complementario Gratuito.Descuento en Tiendas Ripley.Desarrollo Profesional.Entre otros.¡Postula para ser parte de nuestro equipo!En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Favor No postular si no cumple lo requerido.</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>SurChile SPA</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Presencial Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56084/product-manager-ing-comercial-lampa-valle-grande-1-3-liquidos</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>1</v>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" t="n">
+        <v>0</v>
+      </c>
+      <c r="K284" t="n">
+        <v>1</v>
+      </c>
+      <c r="L284" t="n">
+        <v>1</v>
+      </c>
+      <c r="M284" t="n">
+        <v>0</v>
+      </c>
+      <c r="N284" t="n">
+        <v>0</v>
+      </c>
+      <c r="O284" t="n">
+        <v>0</v>
+      </c>
+      <c r="P284" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>Vacante para Ingenieros Comerciales - EXCLUYENTEEXPERIENCIA PRICING Y ESTRATEGIA COMERCIAL - EXCLUYENTE  1 AÑOHombre por características del cargo - ExcluyenteFavor No postular si no cumple lo requerido.Muchas gracias por su comprensión.EnSurChile SPAbuscamos un/aProduct Managercon visión estratégica, orientación a resultados y pasión por el desarrollo de negocios, para liderar la gestión integral de nuestras líneas de productos y potenciar su crecimiento en el mercado.Esta posición es clave para impulsar la rentabilidad, posicionamiento y expansión del portafolio, asegurando una ejecución comercial efectiva y alineada a los objetivos de la compañía.🚀 Principales responsabilidadesDiseñar e implementar la estrategia comercial y de posicionamiento del producto.Analizar mercado, competencia y oportunidades de crecimiento.Liderar lanzamientos y planes de desarrollo de nuevos productos.Gestionar indicadores de desempeño (ventas, margen, participación de mercado).Coordinar con áreas internas (ventas, operaciones, logística, marketing).Desarrollar y mantener relaciones estratégicas con clientes y proveedores.Identificar oportunidades de mejora e innovación en el portafolio.🎯 RequisitosTítulo de Ingeniería Comercial o carrera afín.Experiencia previa en gestión de productos, desarrollo comercial o áreas similares.Alta capacidad de análisis y visión estratégica.Habilidades de negociación y gestión de proyectos.Manejo de herramientas de análisis y reportes comerciales (deseable).🧩 Competencias claveLiderazgo e iniciativa.Orientación a resultados y cumplimiento de metas.Comunicación efectiva y trabajo colaborativo.Proactividad y autonomía en la toma de decisiones.BeneficiosCaja Los AndesAguinaldos fiestas patrias y fin de año</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q284"/>
+  <dimension ref="A1:Q285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19674,6 +19674,75 @@
         </is>
       </c>
     </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Analista Tesorería</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Importante Empresa</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56101/analista-tesoreria</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>2</v>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I285" t="n">
+        <v>0</v>
+      </c>
+      <c r="J285" t="n">
+        <v>0</v>
+      </c>
+      <c r="K285" t="n">
+        <v>0</v>
+      </c>
+      <c r="L285" t="n">
+        <v>1</v>
+      </c>
+      <c r="M285" t="n">
+        <v>0</v>
+      </c>
+      <c r="N285" t="n">
+        <v>0</v>
+      </c>
+      <c r="O285" t="n">
+        <v>0</v>
+      </c>
+      <c r="P285" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>¡Únete a Cumplo como nuestro próximo Treasury Analyst – Chile! 👌En Cumplo, buscamos personas que quieran marcar la diferencia 💚. Personas que no solo busquen un trabajo, sino que quieran aportar al crecimiento de miles de pymes y transformar realidades.Queremos impactar. Soñamos con un mundo en el que todas las empresas accedan a los recursos que necesitan para crecer y desplegar su máximo potencial.¿Te identificas con todo esto? Si es así, ¡te estamos buscando!¿Qué te espera? 🎯• Procesar giros de operaciones a solicitantes, incluyendo refinanciamientos, anticipos y pagos finales.• Gestionar la asociación de pagos en el módulo de tesorería y la dispersión de fondos a beneficiarios.• Realizar conciliaciones bancarias, identificando diferencias y proponiendo mejoras al proceso.• Realizar transferencias bancarias y la gestión de devolución de excedentes según las políticas internas.• Apoyar en la automatización de procesos operativos y flujos de trabajo del área de tesorería.• Colaborar en tareas administrativas y operativas del día a día en coordinación con Finanzas y Operaciones.¿Qué necesitas? 🕵️‍♀️• Profesional de las áreas de Finanzas, Administración, Contabilidad o carreras afines.• Al menos 1 año de experiencia demostrable en contabilidad y finanzas.• Manejo de Excel avanzado (tablas dinámicas, macros, fórmulas anidadas).• Conocimientos contables y financieros básicos (asientos contables, definición de ingresos, entre otros).Beneficios¿Qué ofrecemos? 🎁• Personal Days: Día libre por cumpleaños y mudanza.• Más vacaciones: 3 días extra al año + 2 administrativos.• Sistema de vacaciones 5+1• Puntos flexibles• Seguro complementario.• Convenio con Caja Los Andes.• Cultura cercana y colaborativa: Sé parte de un equipo con propósito.Sobre nosotros:En Cumplo, conectamos a empresas que buscan liquidez con personas dispuestas a invertir en sus proyectos. Nuestra misión es democratizar el financiamiento y apoyar el crecimiento de las pymes en Latinoamérica, promoviendo un ecosistema financiero más justo y transparente.Si compartes nuestra visión y deseas ser parte de este cambio, te invitamos a postular.💡 ¡Postula ahora y sé parte de la transformación financiera! 🚀</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q285"/>
+  <dimension ref="A1:Q291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19743,6 +19743,416 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Ejecutivo Comercial</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Cumplo</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Av Apoquindo 5400, Chile</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56134/ejecutivo-comercial</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>1</v>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" t="n">
+        <v>0</v>
+      </c>
+      <c r="K286" t="n">
+        <v>0</v>
+      </c>
+      <c r="L286" t="n">
+        <v>1</v>
+      </c>
+      <c r="M286" t="n">
+        <v>0</v>
+      </c>
+      <c r="N286" t="n">
+        <v>0</v>
+      </c>
+      <c r="O286" t="n">
+        <v>0</v>
+      </c>
+      <c r="P286" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>¡Únete a Cumplo como nuestro próximoBusiness Developer!👌En Cumplo, buscamos personas que quieran marcar la diferencia 💚. Personas que no solo busquen un trabajo, sino que quieran aportar al crecimiento de miles de pymes y transformar realidades.Queremos impactar. Soñamos con un mundo en el que todas las empresas accedan a los recursos que necesitan para crecer y desplegar su máximo potencial.¿Te identificas con todo esto? Si es así, ¡te estamos buscando!¿Qué te espera? 🎯Analizar el mercado y la competencia para identificar oportunidades de negocio.Diseñar e implementar estrategias de ventas que impulsen el crecimiento de Cumplo.Establecer y mantener relaciones con clientes y socios estratégicos.Colaborar con equipos internos para asegurar el alineamiento en la ejecución de estrategias.Monitorear el rendimiento de las estrategias y realizar ajustes según sea necesario.Preparar informes y presentaciones sobre el progreso de las iniciativas estratégicas.Requerimientos¿Qué necesitas? 🕵️‍♀️Al menos 1 año de experiencia previa en ventas o desarrollo de negocio, idealmente en el sector fintech o servicios financieros.Gusto por las ventas y la atención al cliente.Conocimiento financiero y comercial.Familiaridad con herramientas de análisis de mercado y CRM.Capacidad para trabajar por objetivos.Beneficios¿Qué ofrecemos? 🎁Personal Days: Día libre por cumpleaños y mudanza.Más vacaciones: 3 días extra al año + 2 administrativos.Seguro complementario.Convenio con Caja Los Andes.Cultura cercana y colaborativa: Sé parte de un equipo con propósito.Sobre nosotros 🌍En Cumplo, conectamos a empresas que buscan liquidez con personas dispuestas a invertir en sus proyectos. Nuestra misión es democratizar el financiamiento y apoyar el crecimiento de las pymes en Latinoamérica, promoviendo un ecosistema financiero más justo y transparente.Si compartes nuestra visión y deseas ser parte de este cambio, te invitamos a postular.💡 ¡Postula ahora y sé parte de la transformación financiera! 🚀</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Category Manager de Ventas Mayoristas</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Rosen</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56131/category-manager-de-ventas-mayoristas</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>3</v>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I287" t="n">
+        <v>0</v>
+      </c>
+      <c r="J287" t="n">
+        <v>0</v>
+      </c>
+      <c r="K287" t="n">
+        <v>1</v>
+      </c>
+      <c r="L287" t="n">
+        <v>1</v>
+      </c>
+      <c r="M287" t="n">
+        <v>0</v>
+      </c>
+      <c r="N287" t="n">
+        <v>0</v>
+      </c>
+      <c r="O287" t="n">
+        <v>0</v>
+      </c>
+      <c r="P287" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>📢¡Si te gusta la decoración, el mundo del descanso familiar, Rosen es para ti!  Estamos buscando nuevos y nuevas RosenLovers que quieran ser parte de una de las mejores empresas para trabajar en Chile, ranking GPTW 2025. Buscamos el ADN Rosen en cada uno de nuestros/as colaboradores/as, potenciando la Excelencia, Integridad, Compromiso e Innovación.🙌 En Rosen creemos en el valor de las personas y en la riqueza de equipos diversos. Por eso, promovemos procesos de selección inclusivos y si necesitas algún ajuste para participar en el proceso, puedes indicarlo en tu postulación. Esta vacante se enmarca en nuestro compromiso con la inclusión laboral y la Ley 21.015.Actualmente nos encontramos en búsqueda de un/aCategory Managera trabajar para nuestra Gerencia de Ventas Mayoristas en Modalidad Híbrida, en nuestras oficinas ubicadas en la comuna deColina, Región Metropolitana.🔍¿Cuál es la misión de este cargo?:Gestionar el desempeño comercial de las categorías de producto en el canal Mayorista, identificando oportunidades de crecimiento, optimizando el mix y apoyando al equipo KAM con inteligencia de negocio para el cumplimiento de metas.💡¿Qué harás en este cargo?Análisis de Sell-out por categoría para identificar brechas.Propuesta de acciones de surtido o pricing.Seguimiento de KPIs comerciales por cliente.Mantener catálogo de productos en los distintos Ecommerce, buscando mejorar tasa de conversión y ventas.Elaboración de proyecciones de venta de las distintas líneas de negocio(Colchones, Tapizados, Muebles y Textiles), y análisis de la venta para toma de decisiones.Mantener y mejorar constantemente los sistemas y bancos de información de Mayorista.Otros requerimientos propios del cargo.📌¿Cuáles son los requisitos para rol?Titulado de Ingeniería comercial / civil Industrial, que cuente con hasta 2 años de experiencia laboral en el área comercial.Excel y Powerpoint avanzado, para manejo en visualización de datos.Deseable experiencia con Inteligencia Artificial en el manejo de datos, análisis y visualización.Deseable manejo de herramienta SAP y Qlikview.📌Jornada laboral:Lunes a jueves presencial de 8:00 a 16:30 hrs, viernes teletrabajo.¡Te invitamos a ser parte de una compañía comprometida con sus colaboradores y la sustentabilidad!🌱🙌BeneficiosBeneficios de nuestro team Rosen 🎁:Jornada laboral de 40 horas.Bono de vacaciones 🏝Aguinaldos.30% de descuentos en Productos Rosen.Seguro Complementario de Salud (desde contrato indefinido).Día Libre de Cumpleaños 🎈Regalos Corporativos 🎁Casino corporativo 🍝 y Buses de acercamiento.¡Entre muchos otros!</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>INGENIERO EN ENTRENAMIENTO</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Enaex</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Calama, Antofagasta, Chile</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56120/ingeniero-en-entrenamiento</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>0</v>
+      </c>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" t="n">
+        <v>0</v>
+      </c>
+      <c r="K288" t="n">
+        <v>0</v>
+      </c>
+      <c r="L288" t="n">
+        <v>1</v>
+      </c>
+      <c r="M288" t="n">
+        <v>0</v>
+      </c>
+      <c r="N288" t="n">
+        <v>0</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0</v>
+      </c>
+      <c r="P288" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>Nuestra empresa:Enaex es una empresa filial del grupo Sigdo Koppers, con más de 100 años de trayectoria en el mercado de explosivos. Nos hemos consolidado como el tercer productor mundial de Nitrato de Amonio de baja densidad y el principal prestador de servicios integrales de fragmentación de roca para la minería en Chile y Latinoamérica. Queremos invitarte a crecer con nosotros y desafiarte día a día en una compañía cuyo propósito es Humanizar la minería. Si para ti la prioridad es la vida, tu obsesión es la excelencia, tu vocación son los clientes y tienes como fortaleza la innovación y el emprendimiento, ¡este es tu lugar!Misión del cargo:Se requiere de un profesional con experiencia, que contribuya, junto con el equipo, al proyecto T1Descripción del cargo:- Control de Procesos- Control presupuestario- Administracion de proyectos- Administracion de contratos- Colaboración Interdisciplinaria- Cumplimiento Normativo y Documental- Cumplimiento de plazos establecidos en los Proyectos.- Revisión y liberacion de SAPNuestro Candidato Ideal:Ingeniero Instrumentación y Control, Civil Quimico, Civil Electrico o Civil MecanicoDeseable al menos 1 año de experiencia en cargos o proyectos similaresHabilidades de Comunicación y OrganizaciónProceso de selección:El proceso de selección se realiza a través de Aira - plataforma de reclutamiento diseñado para mejorar tu experiencia de postulación.Para postular solo necesitas:1. Postular a la oferta2. Revisar tu email3. Ingresar a Aira y contestar las preguntas y/o pruebas solicitadasLuego, si vemos que tu perfil se ajusta a lo que estamos buscando, te contactaremos por email (a través de Aira) para seguir a la etapa presencial.Beneficios- Seguro médico- Capacitaciones y cursos- Actividades wellness- Gimnasio- Subsidio escolar para hijos- Subsidio escolar para hijos- Préstamos financieros- Vacaciones extras</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Category Manager Textil</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Rosen</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56132/category-manager-textil</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>2</v>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I289" t="n">
+        <v>1</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0</v>
+      </c>
+      <c r="K289" t="n">
+        <v>1</v>
+      </c>
+      <c r="L289" t="n">
+        <v>1</v>
+      </c>
+      <c r="M289" t="n">
+        <v>0</v>
+      </c>
+      <c r="N289" t="n">
+        <v>0</v>
+      </c>
+      <c r="O289" t="n">
+        <v>0</v>
+      </c>
+      <c r="P289" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>📢¡Si te gusta la decoración, el mundo del descanso familiar, Rosen es para ti!  Estamos buscando nuevos y nuevas RosenLovers que quieran ser parte de una de las mejores empresas para trabajar en Chile, ranking GPTW 2025. Buscamos el ADN Rosen en cada uno de nuestros/as colaboradores/as, potenciando la Excelencia, Integridad, Compromiso e Innovación.🙌 En Rosen creemos en el valor de las personas y en la riqueza de equipos diversos. Por eso, promovemos procesos de selección inclusivos y si necesitas algún ajuste para participar en el proceso, puedes indicarlo en tu postulación. Esta vacante se enmarca en nuestro compromiso con la inclusión laboral y la Ley 21.015.Actualmente nos encontramos en búsqueda de un/aCategory Managera trabajar para nuestra Gerencia de Productos en Modalidad Híbrida, en nuestras oficinas ubicadas en la comuna de Colina, Región Metropolitana.🔍¿Cuál es la misión de este rol?Analizar y supervisar las ventas de los productos y su comportamiento en el mercado para los usuarios finales. Adicionalmente, apoyar en el seguimiento del desarrollo de las colecciones de textil.💡¿Qué harás en este cargo?Analizar y monitorear mapas de precios v/s ventas de productos de la línea textil, identificando el margen de contribución, con el fin de aportar información clave en la toma de decisiones y en la estrategia de comercialización de Rosen.Emitir informes periódicos de ventas, con el fin de analizar el performance de cada familia de productos.Participar en el desarrollo de productos nuevos y llevar el correcto seguimiento de las Gantt asociadas, además de generar y actualizar la planilla de BBDD de productos por cada colección.Otros requerimientos propios del cargo.📌¿Cuáles son los requisitos para rol?Titulado/a en Ingeniería Comercial o carrera afín.1 a 2 años de experiencia en cargos similares ideal interés en rubro Retail.Conocimiento en Excel nivel intermedio.Deseable manejo de ingles, oral y escrito.Disponibilidad para trabajar en modalidad híbrida en Colina (4 días presencial, contamos con estacionamiento y buses de acercamiento).¡Te invitamos a ser parte de una compañía comprometida con sus colaboradores y la sustentabilidad!🌱🙌BeneficiosBeneficios de nuestro team Rosen 🎁:Jornada laboral de 40 horas.Bono de vacaciones 🏝Aguinaldos.30% de descuentos en Productos Rosen.Seguro Complementario de Salud (desde contrato indefinido).Día Libre de Cumpleaños 🎈Regalos Corporativos 🎁Casino corporativo 🍝 y Buses de acercamiento.¡Entre muchos otros!</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Ingenieroa de Procesos - Temuco</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Región de la Araucanía, Chile</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56123/ingeniero-a-de-procesos-temuco</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>9</v>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>analisis, excel, power bi, looker studio, looker</t>
+        </is>
+      </c>
+      <c r="I290" t="n">
+        <v>0</v>
+      </c>
+      <c r="J290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K290" t="n">
+        <v>0</v>
+      </c>
+      <c r="L290" t="n">
+        <v>1</v>
+      </c>
+      <c r="M290" t="n">
+        <v>0</v>
+      </c>
+      <c r="N290" t="n">
+        <v>0</v>
+      </c>
+      <c r="O290" t="n">
+        <v>0</v>
+      </c>
+      <c r="P290" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>Estamos buscando a un/aIngeniero/a de Procesospara desempeñarse en nuestra planta enTemuco.Principales funciones:Consolidar y analizar datos provenientes de distintas áreas de la planta.Elaborar reportería y dar seguimiento a indicadores monetarios y de eficiencia.Coordinar con las áreas la entrega oportuna de información y apoyarlas en el análisis de sus datos.Implementar mejoras en terreno en torno al uso y comprensión de los datos entregados.Requisitos:Título de Ingeniería Civil Industrial, o afines.Alrededor de 2 años de experiencia laboral en cargos similares.Manejo de Excel intermedio (excluyente).Manejo de SAP (deseable).Manejo de Looker Studio (deseable).Manejo de Power Bi (deseable).</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Práctica Ciberseguridad - IT Advisory</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>KPMG Chile</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Las Condes, Metropolitana, Chile, Chile</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56124/practica-ciberseguridad-it-advisory</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>11</v>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>analisis, informatica, cloud, gcp, aws, azure</t>
+        </is>
+      </c>
+      <c r="I291" t="n">
+        <v>1</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" t="n">
+        <v>1</v>
+      </c>
+      <c r="L291" t="n">
+        <v>0</v>
+      </c>
+      <c r="M291" t="n">
+        <v>0</v>
+      </c>
+      <c r="N291" t="n">
+        <v>1</v>
+      </c>
+      <c r="O291" t="n">
+        <v>0</v>
+      </c>
+      <c r="P291" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>Buscamos un estudiante proactivo y con gran potencial para unirse a nuestro equipo de IT Advisory en KPMG Chile.RequisitosEstudiante de Ingeniería Informática, Técnico en Informática o carreras afines.Disponibilidad para realizar una práctica de al menos 3 meses.Seguro escolar vigente.Principales responsabilidadesParticipar activamente en proyectos de seguridad de la información y ciberseguridad.Apoyar en el diseño e implementación de revisiones.Participar en la evaluación de riesgos.Desarrollar soluciones de mitigación.Conocimientos y habilidades valoradasCapacidad para analizar y comunicar métricas clave de seguridad.Enfoque en la automatización y mejora continua de procesos.Conocimientos en remediación de vulnerabilidades.Análisis forense.Auditoría de código.Arquitecturas cloud (Azure, GCP, AWS).Familiaridad con frameworks de seguridad como OWASP, ISO27001, NIST, CIS, CSA, PCI, Swift o RAN 20-10.Nivel de inglés intermedio/avanzado (será un plus).¿Qué buscamos?Si buscas un entorno dinámico que fomente el aprendizaje continuo y te brinde la oportunidad de desarrollar tus habilidades en ciberseguridad, ¡esta práctica es para ti!Beneficios¿Qué ganas tú?🌎Ser parte de una de las principales compañías de Auditoría y Consultoría a nivel mundial.🚀 Oportunidades de desarrollo profesional.💻Jornada de trabajo híbrida.🏢Oficinas de primer nivel ubicadas en Las Condes, frente al Parque Araucano.💯Múltiples convenios corporativos.🎉Actividades como fiestas, Meeting Points y encuentros de área para disfrutar con compañeros.🎂Tu día de cumpleaños es completamente libre para que lo disfrutes como desees.💸Remuneración mensual: $400.000 líquidos.En KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas , con un propósito claro, para una mejor sociedad. Valoramos las diversas habilidades y fortalezas, tanto personales como profesionales, que cada persona aporta.En KPMG estamos comprometidos con la Diversidad e inclusión , nuestras ofertas de empleo están disponibles con los ajustes razonables necesarios para tu proceso. Juntos, estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. ¡Anímate y ven a descubrir por qué somos la opción más clara! 🥇</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q291"/>
+  <dimension ref="A1:Q299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20153,6 +20153,558 @@
         </is>
       </c>
     </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>ANALISTA PROYECTOS DE SOSTENIBILIDAD I</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>BCP</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56148/analista-proyectos-de-sostenibilidad-i</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>1</v>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I292" t="n">
+        <v>1</v>
+      </c>
+      <c r="J292" t="n">
+        <v>0</v>
+      </c>
+      <c r="K292" t="n">
+        <v>0</v>
+      </c>
+      <c r="L292" t="n">
+        <v>1</v>
+      </c>
+      <c r="M292" t="n">
+        <v>0</v>
+      </c>
+      <c r="N292" t="n">
+        <v>1</v>
+      </c>
+      <c r="O292" t="n">
+        <v>0</v>
+      </c>
+      <c r="P292" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>Buscamos a los que tienen ganas de transformar el país. A los que quieren llegar lejos. Por qué esto no es solo un trabajo. Esto es desafiarte en grande para impactar en grande. Te estamos buscando para que formes parte de nuestro equipoANALISTA PROYECTOS DE SOSTENIBILIDAD I.¿Cuál es el retoFormar parte del equipo que se tendrá a su cargo la recopilación, análisis y reporte de la data vinculada a las métricas de sostenibilidad.¿Cómo impactarás en grande?Diseñar y mantener el sistema de información de sostenibilidad.Mapear fuentes de información, responsables, metodologías y periodicidades.Definir reglas de trazabilidad y documentación para indicadores de sostenibilidad.Dar soporte a reportería regulatoria local en sostenibilidad, reportes exigidos por banca multilateral, Memoria Integrada, Reporte de Sostenibilidad, TCFD, reportes Credicorp, indicadores estratégicos y cuestionarios ESG¿Qué necesitamos de ti?Eres Bachiller en Ingenierías, Computer Science, Administración o carreras afines.Tienes experiencia en recopilación, análisis, identificación de insights y presentación de data.Deseable experiencia en análisis predictivo, consultas y armado de querys.Mínimo dos años de experiencia laboral, de preferencia en el sector financieroSQL – intermedioPython – intermedioPower Query – intermedioPower bi – básico - intermedioExcel - avanzadoInglés – intermedio – deseableAgente de IA - deseable¿Por qué unirte a nuestro equipo?Ser parte de la empresa #1 en Merco Talento 2025.Convenio de prácticas con el Credicorp desde tu primer día.Accede a incentivos por tu esfuerzo/desempeño.Acompañamiento de líderes expertos y referentes en la banca.Acceso a descuentos en productos financieros.Beneficios corporativos exclusivos por provincia para disfrutar con tu familia.Formarás parte de una cultura constante de reconocimientos.Sí, a ti. Te estamos buscando ¡Únete al equipo BCP!“Somos una organización comprometida con la igualdad de derechos y oportunidades. Nuestros procesos de selección se rigen bajo una política donde nuestras/os postulantes son consideradas/os sin importar su origen, género, raza o cualquier otra característica, condición o preferencia, promoviendo así una cultura de respeto mutuo"</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Analista de Gestión Comercial PYME</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>BCP</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>San Isidro, Perú</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56143/analista-de-gestion-comercial-pyme</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>10</v>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>sql, analisis, estadistica, excel, power bi</t>
+        </is>
+      </c>
+      <c r="I293" t="n">
+        <v>1</v>
+      </c>
+      <c r="J293" t="n">
+        <v>0</v>
+      </c>
+      <c r="K293" t="n">
+        <v>0</v>
+      </c>
+      <c r="L293" t="n">
+        <v>1</v>
+      </c>
+      <c r="M293" t="n">
+        <v>0</v>
+      </c>
+      <c r="N293" t="n">
+        <v>0</v>
+      </c>
+      <c r="O293" t="n">
+        <v>0</v>
+      </c>
+      <c r="P293" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>Buscamos a los que tienen ganas de transformar el país. A los que quieren llegar lejos. Por qué esto no es solo un trabajo. Esto es desafiarte en grande para impactar en grande. Esto es el BCP y te estamos buscando para que formes parte de nuestro equipo comoAnalista de Gestión Comercial PYME¿Cuál es el reto?Asegurar la ejecución, integridad y oportunidad de los procesos comerciales de compensación variable, reconocimientos, y gestión de procesos del segmento PyME, brindando analítica accionable y gobierno de datos para impulsar el cumplimiento de metas, la motivación comercial y la mejora continua.¿Cómo impactarás en grande?Monitorear indicadores comerciales y de planillas, reclamos de ventas y pago de incentivos.Levantar y gestionar flujos comerciales y operativos identificando ineficiencias o reprocesos y proponer mejoras.Análisis comercial PYME, generar insights, evaluar impactos y dar seguimiento.Diseñar iniciativas comerciales/data driven, estructurar planes con kpis, gestionar pilotos y escalar soluciones.Creación de Metodología de Gestión EfectivaAdministrar el ciclo de metas comerciales PYME.¿Qué necesitamos de ti?Egresado, Bachiller universitario de Ingeniería Industrial / Sistemas / Economía / Estadística / Administración o afines.Tiempo en el puesto: mínimo 1 año; Empresas del sector bancario.Excel Avanzado (indispensable).SQL a nivel intermedio.Power BI a nivel intermedio.Conocimientos en análisis de datos, gestión de procesos y operaciones.Deseable conocimiento de Power Apps.Inglés intermedio (deseable).Disponibilidad para laborar de manera presencial, de lunes a viernes, en el horario de 9:00 a.m. a 6:00 p.m.¿Por qué unirte a nuestro equipo?Ser parte de la empresa #1 en Merco Talento 2025.Ingreso a planilla BCP desde tu primer día.Accede a incentivos por tu esfuerzo/desempeñoAcompañamiento de líderes expertos y referentes en la banca.Acceso a descuentos en productos financieros.Beneficios corporativos exclusivos por provincia para disfrutar con tu familia.Formarás parte de una cultura constante de reconocimientosSí, a ti. Te estamos buscando ¡Únete al equipo BCP!“Somos una organización comprometida con la igualdad de derechos y oportunidades. Nuestros procesos de selección se rigen bajo una política donde nuestras/os postulantes son consideradas/os sin importar su origen, género, raza o cualquier otra característica, condición o preferencia, promoviendo así una cultura de respeto mutuo"</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Ejecutivo de Seguros</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Mutucar</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56154/ejecutivo-de-seguros</t>
+        </is>
+      </c>
+      <c r="G294" t="n">
+        <v>2</v>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I294" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" t="n">
+        <v>0</v>
+      </c>
+      <c r="K294" t="n">
+        <v>0</v>
+      </c>
+      <c r="L294" t="n">
+        <v>1</v>
+      </c>
+      <c r="M294" t="n">
+        <v>0</v>
+      </c>
+      <c r="N294" t="n">
+        <v>0</v>
+      </c>
+      <c r="O294" t="n">
+        <v>0</v>
+      </c>
+      <c r="P294" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>Somos una organización financiera sin fines de lucro del rubro del seguro, con el propósito de "Brindar apoyo y seguridad a quienes nos entregan seguridad". Buscamos un Ejecutivo de Seguros que nos ayude a realizar la atención a asegurados, entregando respuestas directas a requerimientos de información, orientando a los usuarios sobre la documentación necesaria para contratar y/o liquidar algún seguro, de acuerdo con protocolos y procedimientos establecidos.Funciones principales:🔵Atender presencialmente a los clientes.🔵Asesorar a los asegurados en materias de seguros.🔵Realizar formalización de seguros.Requisitos:🔵Título Ingeniero Comercial, Administración de Empresas o carrera afín.🔵Especialización y/o conocimientos específicos:💡Cursos sobre Seguros.💡Conceptos básicos de contabilidad aplicada a seguros.💡Curso de Atención al cliente.💡Conocimiento Sisnet.🔵Dominio computacional de Herramientas Office: Word a nivel básico y Excel a nivelintermedio.🔵Experiencia laboral: 2 años en Ventas en compañías de seguros, bancos u organizacionesafines.🔵Deseable experiencia como ejecutivo de seguros de incendio.BeneficiosBeneficios:🟢38 horas y 15 minutos de trabajo semanal.🟢Seguros complementario, vida, salud, dental y catastrófico.🟢20 días hábiles anuales de vacaciones.🟢3 días administrativos.🟢El día del cumpleaños si cae hábil es libre.🟢Clases de acondicionamiento físico y zumba.🟢Viernes Jeans Day.🟢Centros recreacionales.🟢Actividades de integración.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Ingeniero Machine Learning</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56149/ingeniero-machine-learning</t>
+        </is>
+      </c>
+      <c r="G295" t="n">
+        <v>24</v>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>python, sql, machine learning, estadistica, matematica, informatica, cloud, gcp, aws, azure</t>
+        </is>
+      </c>
+      <c r="I295" t="n">
+        <v>0</v>
+      </c>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" t="n">
+        <v>1</v>
+      </c>
+      <c r="L295" t="n">
+        <v>0</v>
+      </c>
+      <c r="M295" t="n">
+        <v>0</v>
+      </c>
+      <c r="N295" t="n">
+        <v>0</v>
+      </c>
+      <c r="O295" t="n">
+        <v>0</v>
+      </c>
+      <c r="P295" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>📢 Estamos buscando un(a)Machine Learning Engineerpara sumarse a nuestro equipo y liderar el desarrollo e implementación de soluciones de Machine Learning que generen impacto real en el negocio.Si te motiva trabajar con datos, modelos predictivos, automatización y tecnologías Cloud, esta oportunidad es para ti.Principales responsabilidades:Diseñar y desarrollar pipelines de datos para analítica avanzada.Construir e implementar pipelines de predicción para modelos de IA.Desplegar modelos de Machine Learning en ambientes productivos.Monitorear el rendimiento y desempeño de modelos en producción.Diseñar procesos automáticos de reentrenamiento y mejora de modelos.Contribuir a la escalabilidad y confiabilidad de las soluciones de inteligencia artificial.Perfil deseadoFormación en: Ingeniería Civil en Computación e Informática, Ingeniería Civil Industrial, Ingeniería Matemática, Ingeniería Estadística o carrera afín.Experiencia: 1 a 2 años en cargos similares.Conocimientos en:Machine Learning y Deep Learning.Python y SQL.Desarrollo de pipelines de datos.TensorFlow, PyTorch y/o Scikit-Learn.Bases de datos SQL y NoSQL.Cloud Computing (AWS, Azure o GCP).Docker y Kubernetes.Monitoreo y mantenimiento de modelos en producción.BeneficiosBeneficios:Seguro complementario de salud, dental, vida y catastrófico cofinanciado.Aguinaldos.Bono anual.Día libre de cumpleaños.Jornada laboral de 40 horas semanales.Modalidad de trabajo híbrida.Creemos en la diversidad y promovemos la igualdad de oportunidades. Esta oferta se enmarca en la Ley 21.015 que incentiva la inclusión laboral de personas con discapacidad.Si te interesa desarrollar soluciones de Machine Learning de alto impacto y ser parte de un equipo innovador, ¡te invitamos a postular!</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Analista de Riesgo de Crédito Empresas</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>BICE</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56160/analista-de-riesgo-de-credito-empresas</t>
+        </is>
+      </c>
+      <c r="G296" t="n">
+        <v>1</v>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I296" t="n">
+        <v>0</v>
+      </c>
+      <c r="J296" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" t="n">
+        <v>1</v>
+      </c>
+      <c r="L296" t="n">
+        <v>1</v>
+      </c>
+      <c r="M296" t="n">
+        <v>0</v>
+      </c>
+      <c r="N296" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" t="n">
+        <v>0</v>
+      </c>
+      <c r="P296" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>En Banco BICE creemos que las personas son el motor de nuestro crecimiento. Impulsamos el desarrollo profesional en un entorno colaborativo, desafiante y con sello humano, donde el aprendizaje continuo y la excelencia son parte de nuestro día a día.¿Te apasiona el análisis financiero y te interesa desarrollar una carrera en riesgo de crédito?Estamos buscando un/a Analista de Riesgo de Crédito Empresas para sumarse a nuestra Gerencia de Riesgo Banca Empresas y Corporaciones.🔍 ¿Qué harás en este rol?✅ Analizar información financiera de empresas para la elaboración de informes de riesgo.✅ Evaluar antecedentes financieros de clientes y apoyar procesos de renovación y otorgamiento de créditos.✅ Participar en reuniones y visitas a clientes para recopilar información relevante para el análisis.✅ Preparar presentaciones y propuestas para comités de crédito.✅ Desempeñarte como contraparte de riesgo para las distintas gerencias comerciales del Banco.✅ Apoyar iniciativas y proyectos del área, contribuyendo a la mejora continua de los procesos.🎓 ¿Qué necesitas para postular?Título profesional de Ingeniería Comercial con magister en finanzas o carrera afín.Entre 0 y 1 año de experiencia laboral. (EXCLUYENTE ESTAR TITULADO)Deseable que hayas realizado tu práctia en áreas de análisis de riesgo o similaresCapacidad analítica, proactividad y orientación al aprendizaje.Si buscas iniciar tu carrera en el mundo financiero y desarrollarte en una de las áreas estratégicas del Banco, este desafío es para ti.¡Te invitamos a postular y ser parte de Banco BICE!Beneficios🏢Modalidad de trabajo según rol: Algunas posiciones acceden a un sistema híbrido, mientras que las áreas comerciales operan 100% de forma presencial.🍽️Almuerzo diario cubierto: Si trabajas en casa matriz, accedes al casino corporativo con almuerzo gratuito. Si estás en una sucursal, se te asigna un monto diario para cubrir este gasto.🛍️Descuentos exclusivos y convenios: Acceso a beneficios con diversas empresas asociadas en áreas como salud, retail, entretenimiento y más.⚽Actividades internas: Participación en torneos deportivos, actividades lúdicas, operativos oftalmológicos y otras instancias que promueven el bienestar.🤝Cultura cercana y participativa: Ser parte activa de un entorno laboral colaborativo, donde se vive la cultura organizacional día a día.🩺Seguros complementarios: Cobertura en salud, dental y de vida, para que cuentes con mayor respaldo y tranquilidad.🐾Seguro para mascotas: Protección adicional para tus compañeros de cuatro patas.🏋️Convenio con gimnasios: Accede a tarifas preferenciales para mantenerte activo y saludable.🎓Formación continua: Convenios y descuentos con instituciones educativas para diplomados, cursos y otros programas de desarrollo profesional.🚲Acceso a bicicletero: Estacionamiento seguro para bicicletas en casa matriz.🅿️Convenio de estacionamientos: Tarifas preferenciales en estacionamientos cercanos.📱Convenio con Entel: Descuentos en planes y equipos móviles.🦷Red de centros odontológicos: Acceso a múltiples convenios para atención dental.🎁Bonos diversos: Incluye bonos por escolaridad, fallecimiento, vacaciones, invierno, excelencia académica, aguinaldos de Fiestas Patrias y Navidad, entre otros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Analista Tienda de Conveniencia Gerencia Ventas</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Arcor</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Las Condes, Chile</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56142/analista-tienda-de-conveniencia-gerencia-ventas</t>
+        </is>
+      </c>
+      <c r="G297" t="n">
+        <v>1</v>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I297" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" t="n">
+        <v>0</v>
+      </c>
+      <c r="K297" t="n">
+        <v>0</v>
+      </c>
+      <c r="L297" t="n">
+        <v>1</v>
+      </c>
+      <c r="M297" t="n">
+        <v>0</v>
+      </c>
+      <c r="N297" t="n">
+        <v>0</v>
+      </c>
+      <c r="O297" t="n">
+        <v>0</v>
+      </c>
+      <c r="P297" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>En Arcor nos encontramos en búsqueda de un Analista Tienda de Conveniencia para trabajar en nuestras oficinas Comerciales en Las Condes:¿Te apasiona el análisis comercial, el trabajo con clientes y la gestión de indicadores que impulsan el negocio?En esta posición tendrás un rol clave en la operación y desarrollo del Canal Tiendas de Conveniencia, asegurando que el proceso de venta se ejecute de manera eficiente, desde la recepción de las órdenes de compra hasta la entrega final al cliente. Además, serás un socio estratégico para el equipo comercial mediante el análisis de información crítica para la toma de decisiones.¿Qué desafíos te esperan?:Gestionar y monitorear órdenes de compra de clientes.Coordinar y validar procesos de abastecimiento, stock y despachos.Analizar indicadores clave del canal como ventas, sell in, sell out y nivel de servicio.Generar reportes e información estratégica para clientes y equipo comercial.Apoyar al equipo de KAMs, contribuyendo al crecimiento y excelencia del canal.Tendrás la oportunidad de impactar directamente en los resultados de uno de los canales más relevantes del negocio, trabajando con equipos comerciales y desarrollando una visión integral de ventas, servicio y operación.¡Te invitamos a dar el siguiente paso en tu carrera y ser parte de este desafío!🚀Perfil deseadoRequisitos:Carreras de Ing. Comercial o a fin.Disfruten trabajar con datos y transformarlos en información valiosa para el negocio.Capacidad de analísis, organización y orientación a resultados.Posean habilidades para relacionarse con distintas áreas y clientes.Tengan motivación por aprender y desarrollarse en un entorno dinámico y desafiante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Analista de Control y Gestión (Cobranzas)</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>HDI Seguros</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56157/analista-de-control-y-gestion-cobranzas</t>
+        </is>
+      </c>
+      <c r="G298" t="n">
+        <v>2</v>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>power bi</t>
+        </is>
+      </c>
+      <c r="I298" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" t="n">
+        <v>0</v>
+      </c>
+      <c r="K298" t="n">
+        <v>1</v>
+      </c>
+      <c r="L298" t="n">
+        <v>0</v>
+      </c>
+      <c r="M298" t="n">
+        <v>0</v>
+      </c>
+      <c r="N298" t="n">
+        <v>0</v>
+      </c>
+      <c r="O298" t="n">
+        <v>0</v>
+      </c>
+      <c r="P298" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>Estamos buscando un(a)Analista de Control y Gestión (Cobranzas)para integrarse a nuestro equipo. Su principal desafío será analizar indicadores, generar reportería y aportar información clave para la toma de decisiones y el seguimiento de la gestión de cobranzas.¿Qué harás?Elaborar reportes e indicadores de gestión del área de cobranzas.Analizar resultados y desempeño de los principales KPI del negocio.Apoyar la preparación de informes de gestión y cierres mensuales.Realizar seguimiento de indicadores de experiencia de clientes (NPS).Monitorear el cumplimiento de SLA y generar alertas ante desviaciones.Participar en iniciativas de mejora continua y optimización de procesos.Apoyar el control interno y la gestión documental del área.Perfil deseadoRecién titulado/a Ingeniería Comercial o Ingeniería Civil Industrial.Conocimientos enExcel nivel intermedio.Power BI.Manejo de indicadores de gestión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Analista de Datos y Gestión Operacional (recién tituladoa)</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>HDI Seguros</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56158/analista-de-datos-y-gestion-operacional-recien-titulado-a</t>
+        </is>
+      </c>
+      <c r="G299" t="n">
+        <v>5</v>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>analisis, excel, power bi</t>
+        </is>
+      </c>
+      <c r="I299" t="n">
+        <v>0</v>
+      </c>
+      <c r="J299" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" t="n">
+        <v>1</v>
+      </c>
+      <c r="L299" t="n">
+        <v>0</v>
+      </c>
+      <c r="M299" t="n">
+        <v>0</v>
+      </c>
+      <c r="N299" t="n">
+        <v>0</v>
+      </c>
+      <c r="O299" t="n">
+        <v>0</v>
+      </c>
+      <c r="P299" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>🚀¿Eres Ingeniero/a Comercial o Ingeniero/a Civil Industrial recién titulado/a y buscas comenzar tu carrera en una empresa líder del mercado asegurador?En HDI Seguros estamos buscando un(a)Analista de Datos y Gestión Operacionalpara integrarse a un equipo dinámico, donde podrás desarrollar tus habilidades analíticas, fortalecer tu manejo de datos y participar activamente en la toma de decisiones del negocio.¿Qué harás en tu día a día?Analizar y controlar información asociada a recuperos judiciales.Monitorear convenios de pago y oportunidades de recupero.Elaborar reportes de gestión e indicadores para apoyar la toma de decisiones.Realizar seguimiento y control de estudios jurídicos externos.Analizar información de siniestros con potencial de recupero.Identificar desviaciones y proponer mejoras en procesos y controles.Perfil deseadoFormación en Ingeniería Comercial o Ingeniería Civil Industrial.Conocimientos:Excel nivel intermedio.Conocimiento en Power BI.BeneficiosSeguro complementario de salud.Aguinaldos.Bono anual.Modalidad híbrida.Jornada laboral de 40 horas semanales.Creemos en la diversidad y fomentamos la igualdad de oportunidades. Esta oferta se enmarca en la Ley 21.015 que promueve la inclusión laboral de personas con discapacidad.Si buscas un nuevo desafío profesional donde puedas potenciar tus habilidades de análisis y gestión, ¡te invitamos a postular!</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q299"/>
+  <dimension ref="A1:Q308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20705,6 +20705,615 @@
         </is>
       </c>
     </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Analista de Inteligencia de Negocio</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Entel Perú</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56171/analista-de-inteligencia-de-negocio</t>
+        </is>
+      </c>
+      <c r="G300" t="n">
+        <v>5</v>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>sql, power bi</t>
+        </is>
+      </c>
+      <c r="I300" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" t="n">
+        <v>0</v>
+      </c>
+      <c r="K300" t="n">
+        <v>0</v>
+      </c>
+      <c r="L300" t="n">
+        <v>1</v>
+      </c>
+      <c r="M300" t="n">
+        <v>0</v>
+      </c>
+      <c r="N300" t="n">
+        <v>1</v>
+      </c>
+      <c r="O300" t="n">
+        <v>0</v>
+      </c>
+      <c r="P300" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>¿Te mueve colaborar, desafiar y crecer con propósito? Conoce que desafíos te esperan como Analista de Inteligencia de NegocioAnalizar el desempeño e impacto de iniciativas a demanda de los canales de retención.Diseñar y mantener dashboards de gestión operativa.Construir procesos, tablas y automatizaciones mediante SQL.Elaborar reportes de resultados y generar insights para entender el performance de las campañas de retención.Identificar buenas prácticas y proponer mejoras replicables.Controlar y dar seguimiento a indicadores propios de la gestión de call center.RequisitosFormación universitaria completa en carreras de Administración, Ing, Industrial o afines.Experiencia de 1 año en gestión comercial, contact center o canales de atención.Manejo de Office a nivel avanzadoManejo de Power BI a nivel intermedioManejo de SQL a nivel intermedio</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>INGENIERO DE SOPORTE Y PROYECTOS IoT</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Clickie</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56189/ingeniero-de-soporte-y-proyectos-iot</t>
+        </is>
+      </c>
+      <c r="G301" t="n">
+        <v>5</v>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>python, excel</t>
+        </is>
+      </c>
+      <c r="I301" t="n">
+        <v>1</v>
+      </c>
+      <c r="J301" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" t="n">
+        <v>1</v>
+      </c>
+      <c r="L301" t="n">
+        <v>1</v>
+      </c>
+      <c r="M301" t="n">
+        <v>0</v>
+      </c>
+      <c r="N301" t="n">
+        <v>0</v>
+      </c>
+      <c r="O301" t="n">
+        <v>0</v>
+      </c>
+      <c r="P301" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>INGENIERO DE SOPORTE Y PROYECTOS IoTClickie | Santiago de Chile | Modalidad mixta oficina/terreno | Jornada 40 horas—SOBRE CLICKIEEn Clickie desarrollamos soluciones de eficiencia energética y telemetría IoT/IIoT para clientes de retail, edificios corporativos e instalaciones industriales y comerciales. Operamos en diferentes países de la región, con plataforma propia de telemetría y una arquitectura agnóstica a la tecnología mediante la integración de dispositivos de diversos tipos.—EL DESAFÍOBuscamos a alguien que conecte el mundo del terreno con el del cliente. En este cargo vas a levantar proyectos nuevos, resolver incidencias técnicas en sitio, participación en labores de montaje de equipos de telemetría y transformar lo que observaste en terreno en una propuesta concreta. Es un rol de ciclo completo: partes en la visita y terminas con la solución operando.—QUÉ VAS A HACERAtender y resolver solicitudes de clientes a través de nuestro sistema de tickets, dando seguimiento hasta el cierre efectivo de cada caso.Realizar visitas técnicas de soporte para diagnóstico y resolución de incidencias en sitio.Ejecutar visitas de levantamiento técnico para nuevos proyectos.Montar, configurar y poner en marcha equipos de telemetría, medición y control en instalaciones de clientes.Elaborar propuestas técnicas y económicas a partir de los levantamientos realizados.Registrar y gestionar información de proyectos e inventario en nuestro ERP.Coordinar de forma directa con las áreas comercial, producto, administración y logística para la ejecución de los proyectos.—REQUISITOS EXCLUYENTESTítulo de Técnico Eléctrico, Ingeniero Eléctrico, Ingeniero Electrónico o Ingeniero en Automatización Industrial.Licencia eléctrica SEC vigente (cualquier clase).Licencia de conducir clase B vigente.Inglés técnico de lectura, suficiente para interpretar datasheets y manuales de equipos.Disponibilidad para viajar dentro de la Región Metropolitana y a regiones de Chile.Disponibilidad para turnos de emergencia asociados a soporte, y para trabajo fuera de horario cuando un proyecto lo requiera.—REQUISITOS DESEABLES3 años de experiencia en roles similares. También evaluamos perfiles junior o recién titulados con ganas reales de aprender.Experiencia en trabajos eléctricos de baja tensión y en montaje de tableros eléctricos.Experiencia en automatización industrial.Conocimiento de protocolos de comunicación industrial: Modbus RTU y Modbus TCP/IP.Conocimiento de LoRaWAN o de otras tecnologías de comunicación inalámbrica para IoT.Conocimientos de redes y direccionamiento IP.Manejo de Excel y Google Workspace.Nociones de Python o disposición a aprender.Examen de altura vigente. Si no lo tienes, la empresa puede gestionarlo.—QUÉ BUSCAMOS EN TIProactividad: que detectes el problema antes de que el cliente lo reporte.Ganas de aprender. Trabajamos con tecnología que cambia rápido y valoramos más la curiosidad que el currículum perfecto.Trabajo en equipo y capacidad de moverte entre tareas distintas dentro de una misma semana.Autonomía en terreno y criterio para resolver con lo que hay.Orden y disciplina en el registro de la información.—CONDICIONESUbicación: Santiago de Chile.Modalidad: Presencial mixta oficina/terrenoJornada: 40 horas semanales.Contrato: plazo fijo con proyección a indefinido.Reporta a: Responsable de Operaciones, dentro de un equipo de 6 personas.—CÓMO POSTULAREnvía tu CV a[email protected]con el asunto "Ingeniero de Soporte y Proyectos IoT".</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Asistente de Adquisición de Talento y ME - Surco</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Ferreyros</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Surco, Perú</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56173/asistente-de-adquisicion-de-talento-y-me-surco</t>
+        </is>
+      </c>
+      <c r="G302" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="n">
+        <v>0</v>
+      </c>
+      <c r="L302" t="n">
+        <v>1</v>
+      </c>
+      <c r="M302" t="n">
+        <v>0</v>
+      </c>
+      <c r="N302" t="n">
+        <v>0</v>
+      </c>
+      <c r="O302" t="n">
+        <v>0</v>
+      </c>
+      <c r="P302" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>Misión del PuestoBrindar soporte operativo integral y ejecutar los procesos de selección alineados a las necesidades de la organización, garantizando la cobertura oportuna de vacantes y fortaleciendo la posición de nuestra Marca Empleadora en cada punto de contacto con el talento.FuncionesEjecutar el reclutamiento y selección de posiciones operativas, mandos medios y convocatorias masivas según el volumen requerido.Proponer, coordinar y ejecutar nuevas fuentes de reclutamiento (activaciones en campo, ferias laborales, redes locales y estrategias digitales) para enriquecer nuestra base de candidatos.Gestionar la programación y seguimiento de evaluaciones psicológicas, procesos tercerizados y exámenes médicos ocupacionales.Mantener actualizadas las matrices de control del área y apoyar en el monitoreo de los principales KPIs del proceso (tiempos de cobertura, rotación inicial, entre otros).Identificar proactivamente eficiencias en el flujo de selección masiva para reducir tiempos de atención asegurando el fit cultural.Brindar soporte presencial en viajes para la evaluación de programas especiales, procesos masivos descentralizados y ferias de empleo.Requisitos:Egresado/a de Psicología (indispensable).1 año de experiencia en procesos de selección end-to-end en sectores industriales, consumo masivo o empresas de consultoría/outsourcing.Manejo de Google Workspace o Microsoft Office a nivel usuario/intermedio.Disponibilidad para laborar de forma resencial en Monterrico, Surco (Lunes a Viernes).Disponibilidad para realizar viajes puntuales a nivel nacional según necesidad de los procesos masivos o ferias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Trainee De SSMA - Op Las Bambas</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Ferreyros</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>APURIMAC, Perú</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56174/trainee-de-ssma-op-las-bambas</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>7</v>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>trainee</t>
+        </is>
+      </c>
+      <c r="I303" t="n">
+        <v>0</v>
+      </c>
+      <c r="J303" t="n">
+        <v>0</v>
+      </c>
+      <c r="K303" t="n">
+        <v>0</v>
+      </c>
+      <c r="L303" t="n">
+        <v>1</v>
+      </c>
+      <c r="M303" t="n">
+        <v>0</v>
+      </c>
+      <c r="N303" t="n">
+        <v>1</v>
+      </c>
+      <c r="O303" t="n">
+        <v>1</v>
+      </c>
+      <c r="P303" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>Misión del puestoBrindar soporte estratégico en el seguimiento y reportabilidad del Plan Anual de SSMA (PASSMA) para nuestra Gerencia de División.FuncionesHacer seguimiento continuo y consolidar reportes periódicos sobre los avances del PASSMA y sus planes de acción.Verificar en campo el cumplimiento de normas, estándares e instructivos de SSMA, tanto para personal propio como contratistas.Impartir capacitaciones y sensibilizar a los equipos en la adopción de comportamientos seguros y buenas prácticas.Asegurar el cumplimiento de requisitos legales y estándares corporativos para la mejora continua del área.RequisitosEgresado/a o Bachiller en Ingeniería Industrial, Minas, Mecánica, Ambiental, Higiene y Seguridad Industrial o afines.1 año de experiencia general en el rubro y 1 año de experiencia certificada en posiciones similares (¡se consideran prácticas pre y profesionales!).Residencia en provincias de la región sur (Arequipa, Cusco, Moquegua u otras zonas cercanas).Para laborar bajo régimen atípico en la operación asignada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Asistente de Ventas Part Time</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Tanner</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56193/asistente-de-ventas-part-time</t>
+        </is>
+      </c>
+      <c r="G304" t="n">
+        <v>0</v>
+      </c>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="n">
+        <v>0</v>
+      </c>
+      <c r="J304" t="n">
+        <v>0</v>
+      </c>
+      <c r="K304" t="n">
+        <v>0</v>
+      </c>
+      <c r="L304" t="n">
+        <v>1</v>
+      </c>
+      <c r="M304" t="n">
+        <v>1</v>
+      </c>
+      <c r="N304" t="n">
+        <v>0</v>
+      </c>
+      <c r="O304" t="n">
+        <v>0</v>
+      </c>
+      <c r="P304" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>En Tanner seguimos creciendo y queremos que tú también seas parte de este equipo.Buscamos a nuestro próximo/aAsistente de Ventas Part Time, quien tendrá la misión de brindar un servicio de excelencia a nuestros clientes en el punto de venta, asesorándolos en productos financieros y seguros automotrices.¿Qué harás?Asesorar y apoyar en la venta de productos financieros y seguros automotrices. Entregar una experiencia de atención cercana y de calidad, ayudando a cada cliente a encontrar la mejor alternativa según sus necesidades.Validar documentación y respaldos asociados a los cierres de financiamiento.Representar a Tanner con una actitud proactiva, empática y orientada al servicio.En Tanner valoramos el compromiso, la cercanía y el trabajo colaborativo, ofreciendo un espacio donde podrás desarrollarte y generar impacto en la experiencia de nuestros clientes.¿Qué buscamos?Deseable contar con estudios técnicos o profesionales en áreas comerciales, administración o afines.Al menos 1 año de experiencia en atención al cliente o ventas (idealmente en retail o servicios financieros).Habilidades comunicacionales y orientación al cliente.Disponibilidad para trabajar en modalidad presencial, 3 días en la semana, incluyendo sábado y domingo de forma fija.¡Te invitamos a postular y ser parte de Tanner!</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Ingenieroa de Productos Vida - Gerencia Comercial Corporativa</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Consorcio</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Las Condes, Chile</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56187/ingeniero-a-de-productos-vida-gerencia-comercial-corporativa</t>
+        </is>
+      </c>
+      <c r="G305" t="n">
+        <v>10</v>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>python, sql, excel, power bi</t>
+        </is>
+      </c>
+      <c r="I305" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" t="n">
+        <v>0</v>
+      </c>
+      <c r="L305" t="n">
+        <v>1</v>
+      </c>
+      <c r="M305" t="n">
+        <v>0</v>
+      </c>
+      <c r="N305" t="n">
+        <v>0</v>
+      </c>
+      <c r="O305" t="n">
+        <v>0</v>
+      </c>
+      <c r="P305" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>En Consorcio creemos en lugares de trabajo inclusivos, donde las diferencias de las personas son respetadas, valoradas y atendidas para que todos nuestros colaboradores puedan desarrollar plenamente sus talentos.Si buscas un lugar de trabajo desafiante y quieres desarrollarte profesionalmente, esta es tu oportunidad. En Consorcio, nos encontramos en la búsqueda de un Ingeniero/a de Productos Vida para la Gerencia Comercial Corporativa, quien será responsable de liderar, planificar y controlar las actividades asociados a la implementación de nuevos seguros de vida y Fondos mutuos y mejoras de los actuales, dada la estrategia de desarrollo de productos de la Compañía, que se adecuen a las necesidades y expectativas de los clientes y canales, sujetos al cumplimiento de la factibilidad técnica, normativa y operacional.💡 ¿Cuáles serán tus principales funciones?Liderar la implementación de los nuevos Seguros de Vida individuales o Fondos mutuos y sus mejoras, asegurando la elaboración de productos que se adecuen a las necesidades y expectativas de los clientes y canales.Analizar los riesgos de cada iniciativa en las distintas áreas de la compañía, asegurando el cumplimiento de la factibilidad técnica, legal y operacional.Diseñar los requerimientos, documentación y contenidos relacionados con los productos, velando por el cumplimiento de la implementación de los productos y sus flujos.Proponer soluciones eficientes basadas en el conocimiento de las potencialidades de los sistemas y procesos, asegurando la correcta implementación de los productos, sus procesos y desarrollos asociados.Mantener estrecha relación con los distintos canales de distribución, colaborando entre áreas para la adecuada implementación de nuevos productos.🔎 ¿Qué buscamos?Profesional de las carreras Ingeniería Civil o Ingeniería Comercial.Poseer al menos 1 año de experiencia profesional en cargos similares.Conocimiento en Diseño, Planificación y Administración de Proyectos.Manejo de Excel avanzado.Dominio de Power BI, SQL y Python.Deseable conocimiento y uso de IA.Esta oferta se rige bajo la Ley N°21.015, que incentiva la inclusión de personas con discapacidad en el mundo laboral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Key Account Specialist (KAS) – Trade Marketing, Logística y COMEX</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Casa Nativa</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56181/key-account-specialist-kas-trade-marketing-logistica-y-comex</t>
+        </is>
+      </c>
+      <c r="G306" t="n">
+        <v>2</v>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I306" t="n">
+        <v>1</v>
+      </c>
+      <c r="J306" t="n">
+        <v>0</v>
+      </c>
+      <c r="K306" t="n">
+        <v>0</v>
+      </c>
+      <c r="L306" t="n">
+        <v>1</v>
+      </c>
+      <c r="M306" t="n">
+        <v>0</v>
+      </c>
+      <c r="N306" t="n">
+        <v>1</v>
+      </c>
+      <c r="O306" t="n">
+        <v>0</v>
+      </c>
+      <c r="P306" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>Somos parte del mundo WildWild Lama. Wild Foods. Wild Labs. Un grupo de marcas chilenas que compartenuna idea simple: se pueden hacer productos de consumo masivo bien hechos,sustentables, y que además compitan de igual a igual con las multinacionalesen la góndola.Wild Labs es la casa de dos de esas marcas. Casa Nativa, de limpiezasustentable. Casa Delfina, de aromatización de hogar. Nuestros productosestán hoy en Jumbo y en Líder, además de marketplaces y canal propio.Llegar ahí no fue fácil. Mantenerlo y crecer es el trabajo que viene.El cargoBuscamos a la persona que se haga cargo de que todo eso funcione: que elproducto llegue, que esté en la góndola, y que se venda.Es un cargo con una particularidad poco común para alguien que está partiendo:vas a ver el negocio completo. Desde una orden de compra a un proveedor enChina hasta la exhibición de ese mismo producto en un Jumbo de Santiago. Enuna multinacional esas tres cosas las hacen tres áreas distintas y tú veríasuna. Acá las ves todas, y en dos años vas a entender de consumo masivo lo queotros entienden en cinco.Trade marketing y ejecución en salaVas a estar en terreno. Recorrer salas, revisar exhibición, precio y presencia.Detectar quiebres y resolverlos con supervisores y jefes de local. Coordinaral equipo de reposición. Ejecutar activaciones y campañas. Analizar el sell-outpor sala y por SKU, y proponer qué hacer con eso.Logística y abastecimientoGestionar las órdenes de compra de las cadenas, agendar despachos, coordinarcon la bodega. Controlar el fill rate y el cumplimiento del manual de proveedorde cada cadena. Cuadrar inventario y anticipar quiebres antes de que ocurran.COMEX e importacionesSeguimiento a las órdenes con proveedores en China e India. Coordinar embarquescon el freight forwarder y el agente de aduanas. Controlar documentación yplazos de cada despacho. Levantar el costeo por SKU.A quién buscamosTitulado o egresado de Ingeniería Comercial o Ingeniería Civil Industrial.Entre 0 y 2 años de experiencia. Práctica en retail o consumo masivo suma,pero no es requisito.Excel intermedio: tablas dinámicas, funciones de búsqueda, cruce de bases.Inglés intermedio, suficiente para escribirle a un proveedor en Asia.Licencia clase B vigente y movilización propia. Este punto es excluyente.Y dos cosas que no se enseñan:Rigurosidad con el detalle. Acá un documento de importación mal emitido o unaficha de producto mal cargada cuesta plata de verdad. El estándar es alto y nolo vamos a bajar.Gusto por el terreno. Este no es un cargo de escritorio. Si tu idea del trabajoideal es un Excel y una pantalla, no eres tú. Buscamos a alguien a quien leguste caminar salas, hablar con la gente del retail, y volver con informaciónque nadie más tiene.Lo que ofrecemosRenta líquida de $1.400.000 más bonos por cumplimiento de indicadores.Contrato plazo fijo 3 meses y luego indefinido.Oficina en Vitacura, con terreno frecuente.Un practicante a tu cargo desde el primer día.Reporte directo a la gerencia general. Vas a estar en las conversaciones dondese toman las decisiones, no leyendo el resumen después.Ruta de crecimiento definida a Key Account Manager o Product Manager, con unhorizonte de 18 a 24 meses.Si buscas un cargo cómodo y acotado, este no es. Si buscas el lugar donde vas aaprender más rápido en los próximos dos años, conversemos.BeneficiosBeneficiosSeguro complementario de salud, vida, dental y catastrófico, financiado100% por la empresa (aplica al pasar a contrato indefinido).Reajuste de sueldo por IPC dos veces al año, en junio y diciembre. Noesperas a la evaluación anual para que tu sueldo no pierda valor.Almuerzo de Desarrollo: te financiamos un almuerzo al mes con alguien detu rubro para que aprendas de su experiencia y construyas red. Cubrimosel 100% del invitado. Es un beneficio pensado para que crezcasprofesionalmente más allá de tu escritorio.40% de descuento en todas las marcas del grupo Wild —Wild Lama, WildFoods— y en Casa Nativa. 30% adicional para tus familiares y amigos.Medio día libre para tu cumpleaños.Aguinaldos de Fiestas Patrias y Navidad.Day &amp; Night Ticket: una salida mensual financiada con el equipo.15% de descuento en Beasty Butchers.Permisos que van más allá de la ley:Un mes adicional de postnatal masculino y femenino, con flexibilidad paratomarlo completo o en jornada parcial.Una semana extra de luna de miel.Cinco días hábiles adicionales por fallecimiento de familiar directo.Un mes de descanso por pérdida gestacional, para madres y padres.Día libre por fallecimiento de tu mascota.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>📊 Paid Media Manager</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Milimetrix</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Callao 2911, Chile</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56185/paid-media-manager</t>
+        </is>
+      </c>
+      <c r="G307" t="n">
+        <v>2</v>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I307" t="n">
+        <v>0</v>
+      </c>
+      <c r="J307" t="n">
+        <v>1</v>
+      </c>
+      <c r="K307" t="n">
+        <v>1</v>
+      </c>
+      <c r="L307" t="n">
+        <v>0</v>
+      </c>
+      <c r="M307" t="n">
+        <v>0</v>
+      </c>
+      <c r="N307" t="n">
+        <v>0</v>
+      </c>
+      <c r="O307" t="n">
+        <v>0</v>
+      </c>
+      <c r="P307" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>¿Te motiva convertir datos en decisiones que disparen las ventas de marcas e-commerce?EnMilimetrix, agencia de performance creada por ex-ejecutivos retail &amp; e-commerce, buscamos a nuestro nuevoPaid Media Manager. Serás parte de un equipo que combina consultoría estratégica y ejecución hands-on para escalar negocios en toda Latam.No nos conformamos con ser una agencia común. Estamos impulsados por la excelencia y la innovación, buscando siempre nuevas formas de hacer crecer los negocios de nuestros clientes. Nuestra visión es convertirnos en la agencia líder en marketing digital de Latinoamérica, y sabemos que esto solo es posible trabajando con los mejores talentos del sector.Lo que harás día a díaAnálisis Ninja:Identificar y traducir métricas complejas en insights estratégicos de alto impacto para el negocio de nuestros clientes. Diagnosticar la salud de las campañas y proponer soluciones de optimización.Growth Hacker en formación:Lanzar, monitorear y optimizar campañas en Google Ads, Meta Ads y LinkedIn Ads para distintos objetivos (ventas, leads, awareness).Control de vuelo diario:Vigilar métricas clave, budgets y pacing; proponer ajustes pro-profit y test A/B.Storyteller de datos:Convertir KPIs en relatos claros para clientes y para el equipo, recomendando próximos pasos que generen impacto real.Lo que necesitas traerFormación:Recién egresada/o deIngeniería Comercial o Ingeniería Civil.ADN Milimetrix:Fuerte orientación a la excelencia y pasión por entender qué hace que un negocio crezca. Buscamos a alguien que aspire a la maestría técnica y estratégica en performance.Conocimientos:Preferentemente conocimientos básicos en Google Ads y Meta Ads (si tienes certificaciones, ¡mejor!). Si no los tienes, entrarás a la mejor empresa para aprender y crecer.Herramientas:Manejo intermedio de Excel/Sheets y pasión por los datos.Soft Skills:Proactividad, gestión del tiempo, comunicación clara y espíritu colaborativo.Lo que ganarásMentoría directa de especialistas top en performance y e-commerce.Plan de entrenamiento en atribución, CRO y AI tools (sí, jugamos con lo último).Ambiente start-up: rápido, meritocrático y con desafíos reales desde el día 1.BeneficiosAlgunos de los beneficios Milimetrix:Modalidad:Híbrida 3x2Días libres por ocasión:Cumpleaños, mudanza, titulaciónFamilia:Licencias maternales y paternales extendidas (15 días adicionales). Los nuevos padres podrán trabajar de manera remota todas las tardes del primer medio año de vida de su nuevo integrante.Work from Anywhere:3 semanas al año para trabajar 100% remoto; dos semanas son fijas (septiembre y Navidad/Año Nuevo) y una semana adicional es de libre elección.Vacaciones Premium:Si programas y te tomas 10 días de vacaciones consecutivos, ¡nosotros te regalamos un 11° día libre!Experiencia Milimetrix:actividades de equipo mensuales para fortalecer la colaboración y cultura interna.Make the dream:Después de cierto tiempo en la empresa, disfruta de hasta 6 meses sin goce de sueldo para perseguir ese sueño pendiente.Luna de miel prolongada:Añade 5 días extra a tu licencia matrimonial.Acompañamiento:Dos semanas libres en caso de pérdida de embarazo. Estamos contigo.Convenio preferencial con MindFit Advanced, centro de entrenamiento ubicado en nuestro mismo edificio.Salud:Seguro complementario de salud y de vida sin costo.Equipamiento:Macbook asignado por la compañía.Detalles del cargoUbicación:Las Condes, Santiago.Horario:Lun-Jue 09:00 - 18:15 hrs; Vie: 8:30 -16:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>🌟 ¡Queremos conocerte! Súmate a FORUS</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Forus</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56192/queremos-conocerte-sumate-a-forus</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>0</v>
+      </c>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" t="n">
+        <v>0</v>
+      </c>
+      <c r="K308" t="n">
+        <v>0</v>
+      </c>
+      <c r="L308" t="n">
+        <v>1</v>
+      </c>
+      <c r="M308" t="n">
+        <v>0</v>
+      </c>
+      <c r="N308" t="n">
+        <v>1</v>
+      </c>
+      <c r="O308" t="n">
+        <v>0</v>
+      </c>
+      <c r="P308" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>EnFORUSqueremos conocerte. 💙Somos una compañía líder en retail, con un portafolio de increíbles marcas internacionales comoVans, Columbia, Hush Puppies, CAT, Merrell y Under Armour, entre otras.Creemos que el talento puede venir de distintos lugares y que las mejores oportunidades comienzan con una conversación. Por eso, abrimos este espacio para que puedasdejarnos tu CV y ser parte de nuestra Base de Talento.🔎 ¿A quiénes buscamos?Esta convocatoria está dirigida a personas que:Estén buscando realizar supráctica profesional.Seanrecién egresados/asy estén buscando su primera experiencia laboral.Estén dando sus primeros pasos profesionales y quieran desarrollarse en una compañía dinámica y desafiante.Buscamos talento de distintas carreras y áreas, porque en FORUS existen oportunidades en múltiples equipos:Marketing, Comercial, Finanzas, Recursos Humanos, Operaciones, Supply Chain, Tecnología, Producto, Diseño, Retail, entre otras.🚀 ¿Por quéFORUS?Porque aquí podrás aprender, aportar y asumir desafíos desde el comienzo.Somos una compañía que valora lacuriosidad, la agilidad, el ownership y la accountability, y que busca personas con ganas de aprender, proponer ideas y hacer que las cosas pasen.Tu primer trabajo o práctica puede ser mucho más que una experiencia en tu CV: puede ser el comienzo de tu desarrollo profesional.📩 ¡Déjanos tu CV!Aunque hoy no tengamos publicada una vacante específica para tu perfil,queremos conocerte y considerar tu perfil para futuras oportunidades de práctica y posiciones junior en FORUS.👉Postula dejando tu CV actualizado y cuéntanos qué tipo de oportunidad estás buscando.¡Quizás tu próximo desafío comienza aquí! 🚀#FORUS #TalentoFORUS #Prácticas #PrimerTrabajo #Empleabilidad #OportunidadesLaboralesBeneficios👟 Trabajar con grandes marcas internacionales🚀 Aprender en una compañía dinámica y en crecimiento🌎 Conocer un negocio con presencia regional💡 Participar en proyectos y desafíos reales🤝 Trabajar junto a equipos multidisciplinarios📚 Desarrollar experiencia y habilidades para tu futuro profesional🛍️ Acceder a beneficios y descuentos en nuestras marcas❤️ Ser parte de iniciativas de bienestar y calidad de vida</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q308"/>
+  <dimension ref="A1:Q312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21314,6 +21314,278 @@
         </is>
       </c>
     </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Práctica Profesional Auditoría (Temporada de Verano)</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>KPMG Chile</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Las Condes, Metropolitana, Chile, Chile</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56218/practica-profesional-auditoria-temporada-de-verano</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>0</v>
+      </c>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" t="n">
+        <v>0</v>
+      </c>
+      <c r="K309" t="n">
+        <v>1</v>
+      </c>
+      <c r="L309" t="n">
+        <v>1</v>
+      </c>
+      <c r="M309" t="n">
+        <v>0</v>
+      </c>
+      <c r="N309" t="n">
+        <v>1</v>
+      </c>
+      <c r="O309" t="n">
+        <v>0</v>
+      </c>
+      <c r="P309" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>**Perfil Ideal: Practicante de Auditoría (Temporada de Verano)** Buscamos estudiantes de último año de Contador Auditor, Ingeniería en Información y Control de Gestión o Ingeniería Comercial para unirse a nuestro equipo de Auditoría durante la temporada de verano. El candidato ideal demostrará un fuerte compromiso, adaptabilidad y una mentalidad colaborativa, prosperando en entornos de alta exigencia. **Competencias Clave:** * **Pensamiento Crítico y Juicio Profesional:** Capacidad para abordar tareas con precisión y criterio técnico. * **Habilidades Analíticas y Metódicas:** Aptitud para diseñar y ejecutar procedimientos de auditoría sustantivos y analíticos. * **Competencia Tecnológica:** Conocimiento y aplicación de herramientas tecnológicas para optimizar procesos. * **Organización y Documentación:** Habilidad para estructurar papeles de trabajo de forma ordenada y documentar evidencia según normas de auditoría. * **Comunicación Efectiva:** Capacidad para interactuar fluidamente con el equipo de trabajo y clientes. * **Proactividad y Aprendizaje Continuo:** Motivación por adquirir nuevos conocimientos y enfrentar desafíos. * **Gestión del Tiempo:** Habilidad para administrar eficazmente el tiempo y cumplir plazos. * **Ética Profesional:** Estricto respeto por las políticas de independencia, confidencialidad y manejo de información sensible. **Requisitos Esenciales:** * Estudiante regular de 4° o 5° año de las carreras mencionadas. * Disponibilidad mínima de 360 horas (full-time). * Disponibilidad para iniciar entre diciembre y enero. * Carta de solicitud de práctica y seguro escolar vigente (excluyentes). * Disponibilidad para modalidad híbrida (oficina en Santiago y visitas a terreno). * Para estudiantes de regiones, posibilidad de residir en SantiagoBeneficios¿Qué ganas tú? 💰 Remuneración mensual: $400.000 CLP. 🌍 Oportunidad de realizar tu práctica en una firma multinacional líder en consultoría, con proyección de desarrollo profesional. 📈 Alta posibilidad de continuidad laboral y desarrollo profesional dentro de la Firma. 🧠 Aprendizaje continuo a través de la plataforma Degreed, donde podrás desarrollar habilidades según tus intereses y línea de carrera. 🕐 Viernes más cortos: horario de salida a las 13:30 hrs. 👔 Vestimenta business casual, para que trabajes con comodidad y profesionalismo. 🎉 Día libre en tu cumpleaños, porque celebrar también es importante. 🤝 Flexibilidad horaria: si necesitas realizar trámites personales, puedes coordinarlo directamente con tu jefatura. 💼 Múltiples convenios en áreas como salud dental, kinesiología, estética, restaurantes y cafeterías. 🚲 Estacionamiento gratuito para bicicletas y scooters, con acceso a camarines y duchas. En KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas , con un propósito claro, para una mejor sociedad. Valoramos las diversas habilidades y fortalezas, tanto personales como profesionales, que cada persona aporta. En KPMG estamos comprometidos con la Diversidad e inclusión , nuestras ofertas de empleo están disponibles con los ajustes razonables necesarios para tu proceso. Juntos, estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. ¡Anímate y ven a descubrir por qué somos la opción más clara! 🥇</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Analista Centro Control Operacional (OTP)</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Polpaico Soluciones</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56219/analista-centro-control-operacional-otp</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>6</v>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>python, analisis, power bi</t>
+        </is>
+      </c>
+      <c r="I310" t="n">
+        <v>0</v>
+      </c>
+      <c r="J310" t="n">
+        <v>0</v>
+      </c>
+      <c r="K310" t="n">
+        <v>0</v>
+      </c>
+      <c r="L310" t="n">
+        <v>1</v>
+      </c>
+      <c r="M310" t="n">
+        <v>0</v>
+      </c>
+      <c r="N310" t="n">
+        <v>0</v>
+      </c>
+      <c r="O310" t="n">
+        <v>0</v>
+      </c>
+      <c r="P310" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>Polpaico Soluciones, es una compañía líder en el mercado nacional de la fabricación y comercialización de cemento, hormigón y áridos. Como empresa estamos convencidos que tener un equipo de trabajo diverso y una cultura inclusiva genera beneficios para las personas y el negocio. No sólo aceptamos la diversidad, sino que la valoramos y promovemos activamente.Actualmente nos encontramos en la búsqueda de unAnalista Centro Control Operacional (OTP)Elobjetivodel cargo es: Recopilar, procesar y analizar los datos operacionales del CCO para construir los indicadores de desempeño que permiten medir la puntualidad, regularidad, estadía, ciclos de camión y productividad de operadores, asegurando continuidad y consistencia en la producción de información. Provee al Jefe de OTP la base analítica para reportar con el desempeño de la operación.¿Cuáles serán tus principales funciones en este cargo?1. Extraer, validar y procesar los datos operacionales desde Command Alkon, GPS, TrackIt y telemetría para la construcción diaria de los indicadores del CCO.2. Calcular y actualizar el OTD (On Time Delivery) con ventana ±10 minutos por carga, obra, cliente, planta y zona geográfica, incluyendo la puntualidad de primera carga como indicador separado.3. Medir el OTP (On Time Performance) frecuencias, regularidad de cargas comprometidas versus ejecutadas y detectar desviaciones que requieran análisis de causa raíz.4. Calcular la estadía y sobre estadía de camiones por obra y cliente, cuantificando el impacto en viajes perdidos equivalentes para el informe mensual al área comercial.5. Analizar los ciclos de camión tiempo de carga en planta, tránsito, descarga y retorno identificando patrones de ineficiencia por zona, planta u operador.6. Actualizar semanalmente el ranking de operadores mediante el driver score multidimensional, integrando las dimensiones de combustible, velocidad, frenadas, G en curvas, puntualidad, tiempo de carga y estadía en obra.7. Medir la productividad de los operadores mixer m³ por turno, viajes completados, tiempo productivo versus improductivo y mantener el histórico para análisis de tendencias.8. Registrar y codificar las causas raíz de atrasos, sobre estadías y contingencias operacionales, manteniendo actualizada la base de datos histórica del CCO.9. Mantener actualizados los dashboards operacionales del CCO, asegurando disponibilidad, calidad visual y consistencia de los datos publicados.10. Apoyar al Jefe de OTP en la preparación de reportes ejecutivos, presentaciones y análisis especiales requeridos por el Gerente CCO o las subgerencias.Formación y Conocimientos-Título profesional de Ingeniería Civil Industrial ó Civil informático.-Conocimientos en Análisis de datos y construcción de indicadores de gestión operacional.-Power BI (Deseable)-SAP (Deseable)-Python (Deseable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Analista Contable Trainee - Las Condes</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>CCU</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56221/analista-contable-trainee-las-condes</t>
+        </is>
+      </c>
+      <c r="G311" t="n">
+        <v>10</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>analisis, trainee, excel</t>
+        </is>
+      </c>
+      <c r="I311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" t="n">
+        <v>0</v>
+      </c>
+      <c r="L311" t="n">
+        <v>1</v>
+      </c>
+      <c r="M311" t="n">
+        <v>0</v>
+      </c>
+      <c r="N311" t="n">
+        <v>0</v>
+      </c>
+      <c r="O311" t="n">
+        <v>1</v>
+      </c>
+      <c r="P311" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>¡En CCU nos apasiona crear experiencias para compartir juntos un mejor vivir!Estamos en búsqueda de un/a Analista Contable Trainee para desempeñarse en nuestro edificio corporativo ubicado en la comuna de Las Condes.Principales Funciones:Revisión de estados financieros mensuales de forma analítica.Registro de provisiones.Contrucción de flujo de efectivo.Presentaciones de estado financieros a los clientes asignados.Realización de encuestas INE.Preparación de análisis de cuentas.Requisitos:Título de Contador AuditorManejo de Excel nivel intermedio (excluyente).Experiencia de 1 año en contabilidad (no excluyente).Maneje SAP (no excluyente).Nuestro SER CCU nos inspira a trabajar con aceptación y respeto a las diferencias de las personas, promoviendo un entorno diverso e integrador, para así contribuir a un mejor vivir. Por esto, te agradecemos que nos compartas si necesitas adaptación en alguna etapa del proceso de postulación.¡Te invitamos a SER CCU!</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Analista de Proyectos de innovación Digital</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56224/analista-de-proyectos-de-innovacion-digital</t>
+        </is>
+      </c>
+      <c r="G312" t="n">
+        <v>12</v>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>analisis, excel, power bi, looker studio, looker, gemini</t>
+        </is>
+      </c>
+      <c r="I312" t="n">
+        <v>0</v>
+      </c>
+      <c r="J312" t="n">
+        <v>0</v>
+      </c>
+      <c r="K312" t="n">
+        <v>1</v>
+      </c>
+      <c r="L312" t="n">
+        <v>0</v>
+      </c>
+      <c r="M312" t="n">
+        <v>0</v>
+      </c>
+      <c r="N312" t="n">
+        <v>1</v>
+      </c>
+      <c r="O312" t="n">
+        <v>0</v>
+      </c>
+      <c r="P312" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>Buscamos a alguien que no solo use tecnología, sino que disfrute descubriendo cómo hacer que otros también quieran usarla.Si eres de las personas que prueba nuevas herramientas de IA, automatiza tareas, analiza cómo se comportan los usuarios y siempre está pensando “esto podría funcionar mejor”, queremos conocerte.Te sumarás al equipo detrás de una plataforma digital con un desafío concreto: aumentar su adopción, mejorar la experiencia de sus usuarios y convertir información, feedback e ideas en iniciativas que generen impacto real.Este rol combinaproducto digital, inteligencia artificial, análisis de datos, experiencia de usuarios y gestión de comunidades. Buscamos a alguien inquieto, creativo y con ganas de experimentar, pero también capaz de implementar, medir resultados y hacer seguimiento.Tu desafío será:🤖Explorar y aplicar herramientas de IApara analizar información, crear contenidos, sistematizar feedback, optimizar procesos y proponer nuevas formas de relacionarnos con los usuarios.🚀Diseñar e implementar iniciativas de adopción digitalque ayuden a incorporar nuevos usuarios y aumentar el uso efectivo de la plataforma.🔍Entender el comportamiento de los usuarios, identificando barreras, necesidades y oportunidades de mejora.📊Construir indicadores y reportesde uso, satisfacción, adopción y crecimiento, transformando datos en recomendaciones concretas.💡Experimentar con nuevas ideas, evaluar sus resultados y escalar aquellas que generen mayor valor.🎓Crear experiencias de incorporación y aprendizaje, incluyendo materiales, capacitaciones y recursos que faciliten el uso de la plataforma.🌐Activar una comunidad de usuarios, generando instancias de colaboración, participación e intercambio de buenas prácticas.🤝Trabajar con usuarios y organizaciones, levantando feedback y convirtiéndolo en mejoras para el producto.Este desafío puede ser para ti si…✔ Tienes entre 1 y 3 años de experiencia en adopción de productos digitales, Product Operations, Customer Success, Growth, implementación tecnológica, innovación o transformación digital.✔ Te interesa genuinamente la inteligencia artificial y ya experimentas con herramientas como ChatGPT, Claude, Gemini, Copilot u otras.✔ Has participado en iniciativas orientadas a aumentar el uso, incorporación o engagement de usuarios de una plataforma.✔ Disfrutas combinando análisis, creatividad y contacto directo con usuarios.✔ Manejas Excel o Google Sheets y tienes experiencia trabajando con indicadores.✔ Te acomoda probar ideas, aprender de los resultados y realizar ajustes rápidamente.✔ Puedes coordinar iniciativas con distintos actores y hacer seguimiento hasta que efectivamente ocurran.⭐Sumas puntos si tienes experiencia en:Diseño de estrategias de adopción digital.Automatización de procesos con IA.UX, investigación o levantamiento de necesidades de usuarios.Gestión o activación de comunidades.Power BI, Looker Studio u otras herramientas de visualización.Relacionamiento con municipios, instituciones u organizaciones.Lo que esperamos encontrar en tiCuriosidad tecnológica real.Mentalidad experimental.Orientación a usuarios y resultados.Creatividad para proponer nuevas soluciones.Capacidad para convertir ideas en acciones.Autonomía, organización y seguimiento.Interés permanente por aprender y probar herramientas emergentes.BeneficiosBonificaciones durante el añoReajuste trimestral según IPCCofinanciamiento de estudiosBeneficios de salud y bienestar:seguro complementario, apoyo actividades recreativas y gimnasia.Beneficios que acompañan tu desarrollo y bienestar:bonificaciones durante el año, reajustes trimestrales según IPC, cofinanciamiento para continuar estudiando, seguros de salud y vida, y distintos permisos para que puedas compatibilizar mejor tu trabajo con tu vida personal.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q312"/>
+  <dimension ref="A1:Q316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21586,6 +21586,282 @@
         </is>
       </c>
     </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Product Manager Loyalty</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Ofi. Alonso De Cordova 5320 - Producto Financiero, Chile</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56247/product-manager-loyalty</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>2</v>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I313" t="n">
+        <v>0</v>
+      </c>
+      <c r="J313" t="n">
+        <v>0</v>
+      </c>
+      <c r="K313" t="n">
+        <v>1</v>
+      </c>
+      <c r="L313" t="n">
+        <v>0</v>
+      </c>
+      <c r="M313" t="n">
+        <v>0</v>
+      </c>
+      <c r="N313" t="n">
+        <v>0</v>
+      </c>
+      <c r="O313" t="n">
+        <v>0</v>
+      </c>
+      <c r="P313" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>¡En Banco Ripley Chile estamos en búsqueda de un/a Product Manager Loyalty! 🛍️💜Sé parte de Banco Ripley, un banco retail en constante crecimiento, donde trabajamos de forma colaborativa para potenciar el uso de nuestros medios de pago y generar mayor valor comercial y financiero para el negocio.¿Cuál será tu principal desafío? 🚀💡 Administrar y rentabilizar la relación comercial entre Retail y Banco Ripley, maximizando el uso de nuestros medios de pago en todos sus formatos.💜 Gestionar y escalar el programa Ripley Puntos Go como palanca de fidelización.📣 Evaluar, diseñar y coordinar campañas con Retail en las principales categorías, impulsando el uso y la facturación del medio de pago.📈 Definir estrategias comerciales, de marketing y CRM orientadas a aumentar la facturación del medio de pago en Retail y la rentabilidad del producto.🧠 Coordinar de forma transversal con distintos equipos de Banco y Retail para asegurar una correcta ejecución, control de gastos y medición de resultados.¿Qué valoramos en tu postulación? 🎯🎓 Profesional titulado/a de Ingeniería Comercial, Ingeniería Civil o carrera afín.💼 Entre 1 y 2 años de experiencia en áreas comerciales, marketing o similares.📊 Manejo de Excel y PowerPoint.🧠 Fuerte sentido comercial, orientación a resultados y capacidad analítica.¿Por qué trabajar en Banco Ripley? 💜Nos importa tu desarrollo y bienestar, por eso ofrecemos:🔹 Oportunidades de aprendizaje y crecimiento profesional.🔹 Trabajo colaborativo con equipos de alto impacto en el negocio.🔹 Tasa preferencial en productos Banco Ripley.🔹 Seguro complementario.🔹 Descuentos en Tiendas Ripley.En Ripley y Banco Ripley promovemos una cultura diversa e inclusiva. En el marco de la Ley 21.015, invitamos a todas las personas a postular y a informarnos si requieren algún ajuste razonable durante el proceso.📢 ¡Postula y sé parte del equipo que impulsa el crecimiento y la rentabilidad del negocio retail en Banco Ripley! 🚀💳BeneficiosDescripción de los beneficios de la vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Analista de Contenido Junior</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Kitchen Center</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56248/analista-de-contenido-junior</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
+        <v>2</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="I314" t="n">
+        <v>0</v>
+      </c>
+      <c r="J314" t="n">
+        <v>0</v>
+      </c>
+      <c r="K314" t="n">
+        <v>1</v>
+      </c>
+      <c r="L314" t="n">
+        <v>0</v>
+      </c>
+      <c r="M314" t="n">
+        <v>0</v>
+      </c>
+      <c r="N314" t="n">
+        <v>1</v>
+      </c>
+      <c r="O314" t="n">
+        <v>0</v>
+      </c>
+      <c r="P314" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>Kitchen Center imporante Empresa del rubro Retail, buscamos a una persona creativa, analítica y con gran interés en el mundo digital, para integrarse a un equipo de trabajo dinámico, donde podrá aportar a la generación de contenidos orientados al posicionamiento orgánico y crecimiento de visibilidad en canales digitales.Principales responsabilidades:Implementación y optimización de mejoras técnicas SEO para RRSS y sitio web.Redacción de textos SEO (blog, notas, descripciones de productos, recetas, comparativas, preguntas frecuentes, entre otros) implementando buenas prácticas del orgánico (html, H1, H2, estructura de textos).Elaboración semanal de un listado de palabras clave para orientar contenido estratégico y definir el calendario de contenido de SEO (según palabras clave y tendencias).Supervisión y actualización de las páginas web de las marcas, asegurando que el contenido esté vigente, alineado con campañas, correctamente vinculado y optimizado con palabras clave relevantes para mejorar su visibilidad.Medición del crecimiento del SEO tanto de Google como Social.Apoyo general en la planificación de RRSS (Redacción de copies para RRSS, CTA, considerando palabras clave relevantes, etc).Planificación y organización de contenido visual (fotos y vídeos) (considera hacer los Briefs para los videos)Apoyo transversal en la revisión y redacción de textos que se requieren en distintas áreas de la empresa.lacionadas con el desempeño del contenido orgánico.Perfil deseadoCarrera: Publicista, Periodista, Relacionador Público, Ingeniería en marketing o afín.Experiencia: al menos 6 meses de experiencia comprobada en SEOBeneficiosTrabajo Híbrido 3x2Casino en Casa MatrizEstacionamientoGimnasio en Casa Matriz</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Customer Success</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Cumplo</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Av Apoquindo 5400, Chile</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55276/customer-success</t>
+        </is>
+      </c>
+      <c r="G315" t="n">
+        <v>2</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I315" t="n">
+        <v>0</v>
+      </c>
+      <c r="J315" t="n">
+        <v>0</v>
+      </c>
+      <c r="K315" t="n">
+        <v>0</v>
+      </c>
+      <c r="L315" t="n">
+        <v>1</v>
+      </c>
+      <c r="M315" t="n">
+        <v>0</v>
+      </c>
+      <c r="N315" t="n">
+        <v>0</v>
+      </c>
+      <c r="O315" t="n">
+        <v>0</v>
+      </c>
+      <c r="P315" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>¡Únete aCumplocomo nuestro próximoCustomer Success!👌En Cumplo, buscamos personas que quieran marcar la diferencia 💚. Personas que no solo busquen un trabajo, sino que quieran aportar al crecimiento de miles de pymes y transformar realidades.Queremos impactar. Soñamos con un mundo en el que todas las empresas accedan a los recursos que necesitan para crecer y desplegar su máximo potencial.¿Te identificas con todo esto? Si es así, ¡te estamos buscando!¿Qué te espera? 🎯Identificar y contactar empresas potenciales para generar nuevas oportunidades de negocio.Calificar prospectos y asegurar su conexión al sistema interno.Realizar prospección activa vía correo, teléfono y CRM.Investigar mercados e industrias para mejorar la estrategia comercial.Colaborar con los equipos de ventas, marketing y operaciones para asegurar un traspaso fluido de leads.Participar en iniciativas para aumentar la visibilidad y conversión de Cumplo.¿Qué necesitas? 🕵️‍♀️Deseable experiencia previa en ventas, prospección o desarrollo comercial.Al menos 1 año en roles comerciales, desarrollo de mercado o ventas (idealmente en servicios financieros o Fintech)Manejo de Excel y herramientas de gestión de bases de datos.Conocimientos en prospección digital e investigación de mercado.Familiaridad con plataformas CRM como Salesforce, HubSpot, entre otras.Disponibilidad para trabajar presencial en Las Condes.Beneficios¿Qué ofrecemos? 🎁Personal Days: Día libre por cumpleaños y mudanza.Más vacaciones: 3 días extra al año + 2 administrativos.2 Semanas de WFASeguro complementario.Convenio con Caja Los Andes.Cultura cercana y colaborativa: Sé parte de un equipo con propósito.Sobre nosotros 🌍En Cumplo, conectamos a empresas que buscan liquidez con personas dispuestas a invertir en sus proyectos. Nuestra misión es democratizar el financiamiento y apoyar el crecimiento de las pymes en Latinoamérica, promoviendo un ecosistema financiero más justo y transparente.Si compartes nuestra visión y deseas ser parte de este cambio, te invitamos a postular.💡 ¡Postula ahora y sé parte de la transformación financiera! 🚀</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Ingenieroa de Planificación (Distribución) - Quilicura</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>CCU</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56242/ingeniero-a-de-planificacion-distribucion-quilicura</t>
+        </is>
+      </c>
+      <c r="G316" t="n">
+        <v>11</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>sql, excel, power bi, looker studio, looker</t>
+        </is>
+      </c>
+      <c r="I316" t="n">
+        <v>0</v>
+      </c>
+      <c r="J316" t="n">
+        <v>0</v>
+      </c>
+      <c r="K316" t="n">
+        <v>0</v>
+      </c>
+      <c r="L316" t="n">
+        <v>1</v>
+      </c>
+      <c r="M316" t="n">
+        <v>0</v>
+      </c>
+      <c r="N316" t="n">
+        <v>0</v>
+      </c>
+      <c r="O316" t="n">
+        <v>0</v>
+      </c>
+      <c r="P316" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>¡En CCU nos apasiona crear experiencias para compartir juntos un mejor vivir!Nos encontramos en búsqueda de unIngeniero/a de Planificación (Distribución)para desempeñarse en nuestra Planta Cervecera ubicada enQuilicura.Principales funciones:Gestionar indicadores operativos del área, diseñando herramientas de visualización y control para asegurar el cumplimiento de metas y desplegar acciones de mejora.Liderar iniciativas y proyectos de eficiencia en los procesos de distribución bajo metodología y políticas de la organización, promoviendo una operación sostenible.Monitorear los gastos y ahorros del área, identificando causas de desviaciones y generando alertas preventivas.Trabajar en conjunto con empresas de transporte y proveedores internos, para así monitorear y mejorar nivel de servicio esperado.Requisitos:Título de Ingeniería Civil, Comercial o carrera afín.0-6 meses de experiencia laboral.Manejo de Excel intermedio-avanzado.Deseable manejo de Looker Studio o Power BI.Deseable manejo de SQL o herramientas de programación.Disponibilidad para trabajar en modalidad 100% presencial en Quilicura.Nuestro SER CCU nos inspira a trabajar con aceptación y respeto a las diferencias de las personas, promoviendo un entorno diverso e integrador, para así contribuir a un mejor vivir. Por esto, te agradecemos que nos compartas si necesitas adaptación en alguna etapa del proceso de postulación.¡Te invitamos a SER CCU!</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q316"/>
+  <dimension ref="A1:Q319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21862,6 +21862,213 @@
         </is>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Analista de Inventarios</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56280/analista-de-inventarios</t>
+        </is>
+      </c>
+      <c r="G317" t="n">
+        <v>3</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I317" t="n">
+        <v>0</v>
+      </c>
+      <c r="J317" t="n">
+        <v>0</v>
+      </c>
+      <c r="K317" t="n">
+        <v>1</v>
+      </c>
+      <c r="L317" t="n">
+        <v>0</v>
+      </c>
+      <c r="M317" t="n">
+        <v>0</v>
+      </c>
+      <c r="N317" t="n">
+        <v>1</v>
+      </c>
+      <c r="O317" t="n">
+        <v>0</v>
+      </c>
+      <c r="P317" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>¡Buscamos a nuestro próximo Analista de Inventarios!Reconocida multinacional del rubro deconsumo masivose encuentra en la búsqueda de unAnalista de Inventariospara integrarse a su equipo. Si te apasiona la gestión de inventarios, el análisis de información y la optimización de procesos, ¡esta oportunidad es para ti!Desafío principal:Asegurar el correcto control y gestión de los inventarios de la compañía, generando información clave para la toma de decisiones y velando por el cumplimiento de los procedimientos y controles internos.Principales funciones:Liderar y supervisar inventarios generales.Realizar seguimiento y control de inventarios, diferencias, obsolescencias, tránsitos y regularizaciones.Supervisar solicitudes y recepción de mercadería, realizando movimientos y ajustes de inventario en SAP según corresponda.Generar reportes y estadísticas mensuales de inventarios.Coordinar y auditar procesos de destrucción de productos.Realizar auditorías de buenas prácticas de almacenamiento y asegurar el cumplimiento de controles internos.Coordinar inventarios con auditores internos y externos, asegurando la trazabilidad y respaldo de los controles establecidos.Buscamos:Experiencia en gestión y control de inventarios.Formación profesional relacionada con Administración, Logística, Contador Auditor, Ingeniería o carreras afines.Manejo de Excel nivel intermedio–avanzado.Conocimientos de SAP.Capacidad analítica y orientación al detalle.Habilidades de coordinación y seguimiento con distintas áreas.Disponibilidad para desempeñarse en modalidad de trabajo híbrida.BeneficiosModalidad híbrida de trabajoEarly fridayCelebraciones de eventos corporativos</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Especialista Riesgo Financiero y Liquidez</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Tanner</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56277/especialista-riesgo-financiero-y-liquidez</t>
+        </is>
+      </c>
+      <c r="G318" t="n">
+        <v>7</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>python, sql, analisis</t>
+        </is>
+      </c>
+      <c r="I318" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" t="n">
+        <v>0</v>
+      </c>
+      <c r="K318" t="n">
+        <v>1</v>
+      </c>
+      <c r="L318" t="n">
+        <v>0</v>
+      </c>
+      <c r="M318" t="n">
+        <v>0</v>
+      </c>
+      <c r="N318" t="n">
+        <v>0</v>
+      </c>
+      <c r="O318" t="n">
+        <v>0</v>
+      </c>
+      <c r="P318" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>En Tanner estamos buscando Especialista de Riesgo Financiero y LiquidezSi te interesa el mundo financiero, disfrutas el análisis y quieres seguir desarrollándote en riesgos, esta oportunidad puede ser para ti.Buscamos incorporar a nuestro equipo deRiesgo Financieroa una persona que contribuya al análisis, cálculo y seguimiento de las métricas de riesgo de liquidez, apoyando una gestión financiera sólida y el cumplimiento de la normativa vigente.¿Cuáles serán tus principales desafíos?• Calcular y analizar métricas de liquidez internas y normativas.• Analizar movimientos del balance y explicar las principales variaciones de las métricas.• Realizar seguimiento de reportes normativos CMF (C46, C47 y C49).• Coordinar y revisar modelos asociados al cálculo de Riesgo de Liquidez.• Desarrollar y controlar indicadores de Alerta Temprana del Plan de Contingencia de Liquidez.• Participar en la revisión y actualización de políticas, procedimientos y guías de Riesgo de Liquidez.¿Qué buscamos?• Profesionales de Ingeniería Comercial, Ingeniería Civil Industrial o formación afín al ámbito financiero/económico.• Entre 1 y 3 años de experiencia profesional.• Conocimientos en finanzas cuantitativas, mercado de valores y análisis financiero.• Conocimientos de modelos matemáticos, estadísticos y econométricos.• Manejo de bases de datos y herramientas como SQL, R y/o Python.• Conocimientos de normativa bancaria, contabilidad financiera y cálculos de flujo de caja.• Capacidad analítica, orientación a resultados, adaptación y disposición para trabajar colaborativamente.¿Te interesa asumir nuevos desafíos y seguir desarrollando tu carrera en el mundo financiero?¡Postula y sé parte de Tanner!#SomosTanner #Tanner #OportunidadLaboral #RiesgoFinanciero #RiesgoDeLiquidez #Finanzas #EmpleosChile</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Analista de Selección y Desarrollo</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56275/analista-de-seleccion-y-desarrollo</t>
+        </is>
+      </c>
+      <c r="G319" t="n">
+        <v>3</v>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I319" t="n">
+        <v>0</v>
+      </c>
+      <c r="J319" t="n">
+        <v>0</v>
+      </c>
+      <c r="K319" t="n">
+        <v>1</v>
+      </c>
+      <c r="L319" t="n">
+        <v>0</v>
+      </c>
+      <c r="M319" t="n">
+        <v>0</v>
+      </c>
+      <c r="N319" t="n">
+        <v>0</v>
+      </c>
+      <c r="O319" t="n">
+        <v>0</v>
+      </c>
+      <c r="P319" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>Estamos buscando unAnalista de Selección y Desarrollo Organizacionalpara integrarse a una empresa líder del rubro consumo masivo. Buscamos una persona cercana, proactiva y con una fuerte orientación al cliente interno, que disfrute trabajando con personas y generando impacto en toda la experiencia del colaborador.¿Cuál será tu desafío?Serás responsable de acompañar distintos procesos de gestión de personas, participando activamente en:✅Reclutamiento y selección de personal para distintos cargos de la organización.✅ Coordinación y ejecución de procesos de onboarding.✅ Identificación y desarrollo de talento interno.✅ Seguimiento y análisis de indicadores de gestión del área.✅ Coordinación con líderes y clientes internos para detectar necesidades de personas y desarrollo.✅ Participación en iniciativas de capacitación, desempeño, clima y experiencia de los colaboradores de la empresa.✅ Visitas periódicas a distintas sucursales y locaciones de la empresa para mantener cercanía con los equipos.¿Qué buscamos?Título profesional afín al área de Recursos Humanos, Psicología, Ingeniería Comercial y/o similar.Al menos 2 años de experiencia en reclutamiento, selección y/o desarrollo organizacional.Manejo de Excel nivel intermedio (excluyente).Capacidad analítica para interpretar indicadores y generar propuestas de mejora.Excelente comunicación y habilidades de relacionamiento.Orientación al cliente interno y vocación de servicio.Capacidad de organización y seguimiento de múltiples procesos.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q151"/>
+  <dimension ref="A1:Q159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,40 +506,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Consumer Strategy &amp; Intelligence Manager</t>
+          <t>Auxiliar de Servicios Transaccionales (Temporal)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Mibanco</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Lima, Perú</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55748/consumer-strategy-intelligence-manager</t>
+          <t>https://firstjob.me/oferta/55765/auxiliar-de-servicios-transaccionales-temporal</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>analisis</t>
+          <t>python, excel</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -549,26 +549,26 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>¿Te apasiona entender al consumidor a partir de los datos y transformar ese conocimiento en estrategias de alto impacto? Buscamos un/aConsumer Strategy &amp; Intelligence Managerque lidere la evolución de la inteligencia de clientes y contribuya a fortalecer la relación entre nuestras marcas y millones de consumidores en Latinoamérica.En este rol tendrás la oportunidad de impulsar iniciativas regionales, trabajar con equipos multidisciplinarios y convertir los datos en decisiones que generen valor para el negocio y una mejor experiencia para nuestros clientes.Desafío:Serás responsable de liderar la estrategia de inteligencia de clientes y gestión de CRM, potenciando el conocimiento del consumidor para apoyar la toma de decisiones comerciales y de marketing. Tu foco estará en desarrollar estrategias de segmentación, fidelización y automatización que permitan construir relaciones de largo plazo con nuestros clientes en los distintos mercados donde operamos.Principales responsabilidades:Liderar la estrategia de segmentación de clientes y gestión de su ciclo de vida, utilizando metodologías como RFM y nuevas fuentes de información.Diseñar y coordinar campañas de captación, retención y fidelización junto a las distintas marcas y equipos regionales.Administrar y optimizar la plataforma CRM, asegurando la correcta implementación de automatizaciones y flujos de comunicación.Generar análisis e insights estratégicos que apoyen la planificación de campañas, promociones y comunicaciones orientadas al cliente.Promover el uso de herramientas de inteligencia de clientes dentro de la organización, capacitando y acompañando a los equipos internos en su adopción.Trabajar de manera transversal con Marketing, Comercial, Atención al Cliente, Tecnología y otras áreas clave para asegurar una visión integral del consumidor.Compartir aprendizajes y mejores prácticas entre los distintos países, impulsando la mejora continua de las estrategias de relacionamiento.</t>
+          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAuxiliar de Servicios Transaccionales (Temporal).¿Cuáles serían tus principales responsabilidades?Atender requerimientos de regularizaciones creados en el JIRA.Verifica que el expediente se encuentre creado en Onbase.Validar el contenido del expediente creado en Onbase.Seguimiento a la subsanación de las observaciones encontradas.Informa a Negocios sobre las observaciones encontradas diariamente por correo electrónico.¿Qué necesitamos?Estudiante o Egresado en Administración, Ing. Industrial o Sistemas, afines.Al menos 6 meses de experiencia en gestión de información.Capacidad para trabajo bajo presión por la importancia de los plazos de entrega.Consultas y creación de querys en PLSQL a nivel intermedio.Excel nivel avanzado (Macros) (deseable)Creación y mantenimiento de Dashboards en PowerBI nivel básico/intermedio.Python, Powerplatform nivel Intermedio (deseable).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Auxiliar de Servicios Transaccionales (Temporal)</t>
+          <t>Analista de Monitoreo (Fraudes)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -600,15 +600,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55765/auxiliar-de-servicios-transaccionales-temporal</t>
+          <t>https://firstjob.me/oferta/55764/analista-de-monitoreo-fraudes</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>python, excel</t>
+          <t>excel, cloud</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -633,11 +633,11 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAuxiliar de Servicios Transaccionales (Temporal).¿Cuáles serían tus principales responsabilidades?Atender requerimientos de regularizaciones creados en el JIRA.Verifica que el expediente se encuentre creado en Onbase.Validar el contenido del expediente creado en Onbase.Seguimiento a la subsanación de las observaciones encontradas.Informa a Negocios sobre las observaciones encontradas diariamente por correo electrónico.¿Qué necesitamos?Estudiante o Egresado en Administración, Ing. Industrial o Sistemas, afines.Al menos 6 meses de experiencia en gestión de información.Capacidad para trabajo bajo presión por la importancia de los plazos de entrega.Consultas y creación de querys en PLSQL a nivel intermedio.Excel nivel avanzado (Macros) (deseable)Creación y mantenimiento de Dashboards en PowerBI nivel básico/intermedio.Python, Powerplatform nivel Intermedio (deseable).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
+          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAnalista de Monitoreo.¿Cuáles serían tus principales responsabilidades?Realizar el monitoreo continuo de las herramientas de prevención del fraudeAnalizar, coordinar, comunicar y realizar el seguimiento a los eventos reportados.Gestionar los eventos y alertas de las herramientas de monitoreo y el contacto con el cliente.Consolidar información y emitir el reporte de la gestión realizada por durante el monitoreo.Evaluar el cumplimiento los indicadores de monitoreo y brindar retroalimentación para la mejora de las herramientas.¿Qué necesitamos?Bachiller o Titulado en Administración bancaria o empresas, Economía, Derecho, Ingenierías.Mínimo 1 año de experiencia en el área de monitoreo en los sectores de banca, retail, seguros o telcoms.Creacción de reportes en Excel nivel Intermedio (Graficos) (Indispensable)Herramientas de Monitoreo nivel intermedio (Orion, CGR, PRTG, Monitor Plus, entre otros) (Indispensable).Conocimiento de MS Office a nivel Intermedio (Deseable).Creación de tickets Smart Cloud o JIRA nivel Intermedio (Deseable)Conocimientos en estructura de Red de Agencias y/o del sector financiero.Herramientas de Automatización - nivel Intermedio (Deseable).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Analista de Monitoreo (Fraudes)</t>
+          <t>Analista de Alianzas Estratégicas y Growth</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -664,20 +664,20 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55764/analista-de-monitoreo-fraudes</t>
+          <t>https://firstjob.me/oferta/55762/analista-de-alianzas-estrategicas-y-growth</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>excel, cloud</t>
+          <t>python, sql, modelo, analisis, tableu</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -706,7 +706,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAnalista de Monitoreo.¿Cuáles serían tus principales responsabilidades?Realizar el monitoreo continuo de las herramientas de prevención del fraudeAnalizar, coordinar, comunicar y realizar el seguimiento a los eventos reportados.Gestionar los eventos y alertas de las herramientas de monitoreo y el contacto con el cliente.Consolidar información y emitir el reporte de la gestión realizada por durante el monitoreo.Evaluar el cumplimiento los indicadores de monitoreo y brindar retroalimentación para la mejora de las herramientas.¿Qué necesitamos?Bachiller o Titulado en Administración bancaria o empresas, Economía, Derecho, Ingenierías.Mínimo 1 año de experiencia en el área de monitoreo en los sectores de banca, retail, seguros o telcoms.Creacción de reportes en Excel nivel Intermedio (Graficos) (Indispensable)Herramientas de Monitoreo nivel intermedio (Orion, CGR, PRTG, Monitor Plus, entre otros) (Indispensable).Conocimiento de MS Office a nivel Intermedio (Deseable).Creación de tickets Smart Cloud o JIRA nivel Intermedio (Deseable)Conocimientos en estructura de Red de Agencias y/o del sector financiero.Herramientas de Automatización - nivel Intermedio (Deseable).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
+          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAnalista de Alianzas Estratégicas y Growth.¿Cuáles serían tus principales responsabilidades?Construir y mantener reportes de performance comercial de alianzas y growth (leads, funnel, conversión, desembolsos, rentabilidad).Analizar data comercial y operativa con foco en crecimiento, eficiencia y rentabilidad, incorporando contexto de negocio.Generar insights accionables orientados a impacto (qué escalar, qué corregir, qué optimizar).Realizar seguimiento end‑to‑end al desempeño del funnel de prospectos provenientes de alianzas estratégicas y growth.Automatización de reportería generada para la generación más rápida y eficiente de insightsEjecutar y apoyar en tareas de soporte al modelo de alianzas (presentaciones, comunicaciones,validación de documentos, control de comisiones, atención de consultas de aliados y canales de venta).¿Qué necesitamos?Bachiller de Administración, Ing Industrial, Marketing, Economía, Ing Sistemas o afines.Experiencia mínima de 1-2 años en análisis comercial, reporting, producto o negocioExperiencia trabajando con data de ventas, canales o alianzas (deseable). De 1 a 2 añosExcel Avanzado (tablas dinámicas, programación de macros)SQL (consulta, cruce y análisis de datos, construcción de queries para reportería –Intermedio/Avanzado) (Indispensable).Herramientas de BI, visualización y automatización de datos.Power BI – Avanzado (Indispensable).Power Automate – básico (Deseable).Tableu – básico (Deseable).Python básico (automatización y análisis de datos) (Deseable).Conocimiento básico de framework ágil Scrum (Deseable).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
         </is>
       </c>
     </row>
@@ -718,12 +718,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Analista de Alianzas Estratégicas y Growth</t>
+          <t>WHOLESALE RISK ANALYST I</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mibanco</t>
+          <t>BBVA Perú</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -738,15 +738,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55762/analista-de-alianzas-estrategicas-y-growth</t>
+          <t>https://firstjob.me/oferta/55761/wholesale-risk-analyst-i</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>python, sql, modelo, analisis, tableu</t>
+          <t>analisis</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -756,7 +756,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -771,11 +771,11 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAnalista de Alianzas Estratégicas y Growth.¿Cuáles serían tus principales responsabilidades?Construir y mantener reportes de performance comercial de alianzas y growth (leads, funnel, conversión, desembolsos, rentabilidad).Analizar data comercial y operativa con foco en crecimiento, eficiencia y rentabilidad, incorporando contexto de negocio.Generar insights accionables orientados a impacto (qué escalar, qué corregir, qué optimizar).Realizar seguimiento end‑to‑end al desempeño del funnel de prospectos provenientes de alianzas estratégicas y growth.Automatización de reportería generada para la generación más rápida y eficiente de insightsEjecutar y apoyar en tareas de soporte al modelo de alianzas (presentaciones, comunicaciones,validación de documentos, control de comisiones, atención de consultas de aliados y canales de venta).¿Qué necesitamos?Bachiller de Administración, Ing Industrial, Marketing, Economía, Ing Sistemas o afines.Experiencia mínima de 1-2 años en análisis comercial, reporting, producto o negocioExperiencia trabajando con data de ventas, canales o alianzas (deseable). De 1 a 2 añosExcel Avanzado (tablas dinámicas, programación de macros)SQL (consulta, cruce y análisis de datos, construcción de queries para reportería –Intermedio/Avanzado) (Indispensable).Herramientas de BI, visualización y automatización de datos.Power BI – Avanzado (Indispensable).Power Automate – básico (Deseable).Tableu – básico (Deseable).Python básico (automatización y análisis de datos) (Deseable).Conocimiento básico de framework ágil Scrum (Deseable).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
+          <t>¿Qué estamos buscando?Funciones:Elaborar programas financieros (informes de riesgo de crédito) y evaluación técnica de líneas de crédito y reestructuraciones de deuda, mediante bilaterales/sindicados de mediana empresa, gran empresa o empresas corporativasPresentar el Programa Financiero u Operación puntual, a las Jefaturas o comités de crédito.Visitar a clientes y dar soporte a la estructuración de las transacciones y programas financieros.Atender y asesorar a los Gerentes de Oficinas, Ejecutivos y Gestores sobre las operaciones presentadas y por presentarse.Cumplir los tiempo de respuesta en la evaluación de operaciones de acuerdo a ANS establecidoValidar correctamente el Rating , para poder ejercer delegación o refrendar las propuestas con jefes directos o comitesCumplir las normativas y procedimientos internos( facilidades crediticias, delegaciones y protocolos de Admisión)Presentar Propuestas para ingresos de clientes en Comite WLRequisitos:Profesional de las carreras de Economía, Administración, Ing. Industrial y/o afines.2 años de experiencia en análisis de estados financieros, evaluación de riesgos crediticios de grandes empresas , evaluación de créditos de medianos plazos.Experiencia en el sector de Banca.</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>WHOLESALE RISK ANALYST I</t>
+          <t>Analista de Control de Gestión y Presupuesto</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BBVA Perú</t>
+          <t>Mibanco</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -807,15 +807,15 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55761/wholesale-risk-analyst-i</t>
+          <t>https://firstjob.me/oferta/55763/analista-de-control-de-gestion-y-presupuesto</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>analisis</t>
+          <t>python, sql, analisis, excel</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -825,7 +825,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -844,51 +844,47 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>¿Qué estamos buscando?Funciones:Elaborar programas financieros (informes de riesgo de crédito) y evaluación técnica de líneas de crédito y reestructuraciones de deuda, mediante bilaterales/sindicados de mediana empresa, gran empresa o empresas corporativasPresentar el Programa Financiero u Operación puntual, a las Jefaturas o comités de crédito.Visitar a clientes y dar soporte a la estructuración de las transacciones y programas financieros.Atender y asesorar a los Gerentes de Oficinas, Ejecutivos y Gestores sobre las operaciones presentadas y por presentarse.Cumplir los tiempo de respuesta en la evaluación de operaciones de acuerdo a ANS establecidoValidar correctamente el Rating , para poder ejercer delegación o refrendar las propuestas con jefes directos o comitesCumplir las normativas y procedimientos internos( facilidades crediticias, delegaciones y protocolos de Admisión)Presentar Propuestas para ingresos de clientes en Comite WLRequisitos:Profesional de las carreras de Economía, Administración, Ing. Industrial y/o afines.2 años de experiencia en análisis de estados financieros, evaluación de riesgos crediticios de grandes empresas , evaluación de créditos de medianos plazos.Experiencia en el sector de Banca.</t>
+          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAnalista de Control de Gestión y Presupuesto.¿Cuáles serían tus principales responsabilidades?Participa en el proceso de planeamiento financiero y proyecciones durante el año, retando analíticamente a los equipos responsables de las principales líneas del GyP del banco.Mensualmente elabora presentaciones a los foros más senior de la organización (Comité Ejecutivo y Directorio), incorporando información de diferentes líneas del GyP mediante una buena dinámica con equipos del banco para su consolidación.Propone y desarrolla modelos financieros eficientes y automatizados, que nutran el análisis más granular de los drivers de crecimiento del negocio y que sirva como input tanto para el entendimiento de la ejecución real como insight looking forward hacia las proyecciones.¿Qué necesitamos?Bachiller en Economía, Administración, Ingeniería Industrial, Ingeniería de Sistemas, o a fines.Experiencia de mínimo 1 año en prácticas pre-profesionales en equipos de planeamiento financiero, planeamiento estratégico, tesorería o pricing.Excel Avanzado (Tablas Dinámicas y Macros) (Indispensable).Conocimiento Intermedio de PowerPoint (Indispensable).Conocimiento de nivel intermedio de lenguajes de programación para manejo de data (SQL, Power Query, Python u otros) (Indispensable al menos 1).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Analista de Control de Gestión y Presupuesto</t>
+          <t>Project Manager Office (PMO)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mibanco</t>
+          <t>Murex Chile</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Lima, Perú</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Presencial Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55763/analista-de-control-de-gestion-y-presupuesto</t>
+          <t>https://firstjob.me/oferta/55792/project-manager-office-pmo</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>python, sql, analisis, excel</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -913,7 +909,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAnalista de Control de Gestión y Presupuesto.¿Cuáles serían tus principales responsabilidades?Participa en el proceso de planeamiento financiero y proyecciones durante el año, retando analíticamente a los equipos responsables de las principales líneas del GyP del banco.Mensualmente elabora presentaciones a los foros más senior de la organización (Comité Ejecutivo y Directorio), incorporando información de diferentes líneas del GyP mediante una buena dinámica con equipos del banco para su consolidación.Propone y desarrolla modelos financieros eficientes y automatizados, que nutran el análisis más granular de los drivers de crecimiento del negocio y que sirva como input tanto para el entendimiento de la ejecución real como insight looking forward hacia las proyecciones.¿Qué necesitamos?Bachiller en Economía, Administración, Ingeniería Industrial, Ingeniería de Sistemas, o a fines.Experiencia de mínimo 1 año en prácticas pre-profesionales en equipos de planeamiento financiero, planeamiento estratégico, tesorería o pricing.Excel Avanzado (Tablas Dinámicas y Macros) (Indispensable).Conocimiento Intermedio de PowerPoint (Indispensable).Conocimiento de nivel intermedio de lenguajes de programación para manejo de data (SQL, Power Query, Python u otros) (Indispensable al menos 1).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
+          <t>🌍 ¿Quiénes somos?Somos Murex, líder global en tecnología financiera (fintech) especializada en soluciones de trading, gestión de riesgo y procesamiento para mercados de capitales.Con presencia en 19 oficinas alrededor del mundo y más de 3.500 colaboradores de más de 60 nacionalidades, desarrollamos, implementamos y damos soporte a una plataforma utilizada por bancos, asset managers, corporaciones y utilities a nivel global.En Murex trabajarás en una industria que está a la vanguardia de la innovación, en un entorno centrado en las personas, donde podrás crecer rápidamente sin dejar de ser tú mismo/a. Formarás parte de un equipo global, diverso y altamente colaborativo.👥 El equipoEl área deProject Managementes responsable de la implementación y entrega de las soluciones de Murex. Gestionamos a los clientes desde la firma de los acuerdos contractuales hasta la puesta en marcha (go-live) del producto. ElProject Manageres el responsable integral del proyecto de implementación de Murex, liderando al equipo hacia una entrega exitosa del alcance y los servicios acordados, siguiendo los estándares de Murex, respetando las restricciones del proyecto y consolidando una sólida relación de largo plazo con el cliente🚀 ¿Qué harás?Liderar al equipo del proyecto hacia el cumplimiento de los objetivos, contribuyendo al desarrollo y la motivación a largo plazo de sus miembros, en colaboración con sus respectivos gerentes.Comunicar y reportar el estado del proyecto, proporcionando una visión clara y compartida a la dirección de Murex y al equipo del proyecto (incluidos los integradores).Definir el plan del proyecto: estimar esfuerzos, elaborar planes de alto nivel y detallados, incluyendo dotación de personal y aspectos logísticos (perfil de recursos, gobierno y organización).Coordinar con clientes e integradores, asegurando su preparación para el proyecto y construyendo una relación basada en el respeto y la confianza mutua.Identificar riesgos e incidencias del proyecto y garantizar la implementación de planes de mitigación.Asegurar el cumplimiento del cronograma, alcance, presupuesto y expectativas de calidad, gestionando además el proceso de solicitudes de cambio y monitoreando los KPI asociados.Adoptar y promover las metodologías, herramientas y mejores prácticas de gestión de proyectos de Murex, alineándolas con clientes e integradores.Contribuir a la definición y mantenimiento de metodologías.Preparar y ejecutar el cierre del proyecto y la transferencia de responsabilidades.Documentar y compartir las lecciones aprendidas.Reportar al Director de Proyecto y colaborar estrechamente con las distintas áreas de Murex (Client Services, departamentos de Producto y Administración de Proyectos).Asegurar que el espíritu de colaboración entre los distintos departamentos de Murex se promueva y difunda dentro de todo el equipo del proyecto.🎯 ¿Qué buscamos?Entre 6 y 10 años de experiencia relevante en gestión de proyectos dentro de los sectores de software, tecnología o banca.Experiencia previa en mercados de inversión o mercados financieros.Experiencia previa en actividades de cara al cliente.Se valorará el conocimiento de la industria y las soluciones de software de Murex.Capacidad para trabajar en múltiples tareas simultáneamente y manejar situaciones de presión.Enfoque demostrado, organizado, analítico y metodológico.Certificación PMI deseable.Nivel avanzado de inglés.</t>
         </is>
       </c>
     </row>
@@ -925,12 +921,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Project Manager Office (PMO)</t>
+          <t>Directora de arte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Murex Chile</t>
+          <t>KiosClub</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -940,12 +936,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Presencial Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55792/project-manager-office-pmo</t>
+          <t>https://firstjob.me/oferta/55777/director-a-de-arte</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -953,13 +949,13 @@
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -968,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -978,7 +974,7 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>🌍 ¿Quiénes somos?Somos Murex, líder global en tecnología financiera (fintech) especializada en soluciones de trading, gestión de riesgo y procesamiento para mercados de capitales.Con presencia en 19 oficinas alrededor del mundo y más de 3.500 colaboradores de más de 60 nacionalidades, desarrollamos, implementamos y damos soporte a una plataforma utilizada por bancos, asset managers, corporaciones y utilities a nivel global.En Murex trabajarás en una industria que está a la vanguardia de la innovación, en un entorno centrado en las personas, donde podrás crecer rápidamente sin dejar de ser tú mismo/a. Formarás parte de un equipo global, diverso y altamente colaborativo.👥 El equipoEl área deProject Managementes responsable de la implementación y entrega de las soluciones de Murex. Gestionamos a los clientes desde la firma de los acuerdos contractuales hasta la puesta en marcha (go-live) del producto. ElProject Manageres el responsable integral del proyecto de implementación de Murex, liderando al equipo hacia una entrega exitosa del alcance y los servicios acordados, siguiendo los estándares de Murex, respetando las restricciones del proyecto y consolidando una sólida relación de largo plazo con el cliente🚀 ¿Qué harás?Liderar al equipo del proyecto hacia el cumplimiento de los objetivos, contribuyendo al desarrollo y la motivación a largo plazo de sus miembros, en colaboración con sus respectivos gerentes.Comunicar y reportar el estado del proyecto, proporcionando una visión clara y compartida a la dirección de Murex y al equipo del proyecto (incluidos los integradores).Definir el plan del proyecto: estimar esfuerzos, elaborar planes de alto nivel y detallados, incluyendo dotación de personal y aspectos logísticos (perfil de recursos, gobierno y organización).Coordinar con clientes e integradores, asegurando su preparación para el proyecto y construyendo una relación basada en el respeto y la confianza mutua.Identificar riesgos e incidencias del proyecto y garantizar la implementación de planes de mitigación.Asegurar el cumplimiento del cronograma, alcance, presupuesto y expectativas de calidad, gestionando además el proceso de solicitudes de cambio y monitoreando los KPI asociados.Adoptar y promover las metodologías, herramientas y mejores prácticas de gestión de proyectos de Murex, alineándolas con clientes e integradores.Contribuir a la definición y mantenimiento de metodologías.Preparar y ejecutar el cierre del proyecto y la transferencia de responsabilidades.Documentar y compartir las lecciones aprendidas.Reportar al Director de Proyecto y colaborar estrechamente con las distintas áreas de Murex (Client Services, departamentos de Producto y Administración de Proyectos).Asegurar que el espíritu de colaboración entre los distintos departamentos de Murex se promueva y difunda dentro de todo el equipo del proyecto.🎯 ¿Qué buscamos?Entre 6 y 10 años de experiencia relevante en gestión de proyectos dentro de los sectores de software, tecnología o banca.Experiencia previa en mercados de inversión o mercados financieros.Experiencia previa en actividades de cara al cliente.Se valorará el conocimiento de la industria y las soluciones de software de Murex.Capacidad para trabajar en múltiples tareas simultáneamente y manejar situaciones de presión.Enfoque demostrado, organizado, analítico y metodológico.Certificación PMI deseable.Nivel avanzado de inglés.</t>
+          <t>KiosClub American SupermarketSomos una empresa que surge en 2017 con el propósito de acercar productos internacionales al mercado chileno, con una propuesta diferenciada basada en marcas norteamericanas. Nuestro foco está en la variedad, la innovación y un servicio cercano.Hoy contamos con más de 50 tiendas a lo largo de todo el país y seguimos creciendo. Nuestra misión es ofrecer una experiencia de compra dinámica y entretenida, manteniendo estándares claros en nuestros productos y en la forma en que operamos.¡Estamos buscando a nuestro/a próximo/aDirector/a de Arte!Si te apasiona el mundo del diseño y quieres desarrollarte en el área de Marketing dentro de una empresa en crecimiento, esta oportunidad es para ti.Tus principales responsabilidades serán:Diseñar, desarrollar y liderar propuestas de diseño gráfico e integral desde una perspectiva de branding 360°, fortaleciendo la identidad visual de la marca en todos sus puntos de contacto.Revisar, y entregar feedback sobre las piezas desarrolladas por el equipo creativo, asegurando el cumplimiento de los estándares de diseño y comunicación.Diseñar y Desarrollar piezas gráficas de alta complejidad  para distintos proyectos y canales de la compañíaConceptualizar, coordinar y participar activamente en sesiones fotográficas y producciones audiovisuales para campañas, e-commerce, redes sociales y otros canales.Realizar fotografías de productos, ambientes y contenido de marca, asegurando material visual de alta calidad para el sitio web, campañas y comunicaciones.Supervisar y optimizar la calidad visual del sitio web, proponiendo mejoras en imágenes, banners, recursos gráficos y presentación de productos para fortalecer la experiencia de compra.Apoyar al equipo de Visual Merchandising en terreno, levantando oportunidades y desarrollando materiales gráficos para una correcta implementación en tienda.Administrar y mantener actualizados los recursos gráficos, bibliotecas de imágenes, plantillas y activos visuales de la marca.Requisitos para postular:Formación en Diseño Gráfico o carrera afin1 año de experiencia en dirección de arte, branding y campañas creativasManejo avanzado de Adobe Creative Suite (Photoshop, Illustrator, InDesign, etc.).Experiencia en producción fotográfica y audiovisual (dirección de arte en shoots)Experiencia en dirección de arte, planificación y ejecución de sesiones fotográficas y producciones audiovisuales.Conocimiento en fotografía de producto, composición, iluminación y criterios visuales para e-commerce y redes sociales.Conocimiento en branding, identidad visual, desarrollo de key visuals y aplicación de brandbooks.Deseable experiencia en retail, visual merchandising y desarrollo de materiales para punto de venta.BeneficiosDías libres adicionales, sin límite anual, orientados a la flexibilidad laboral, sin goce de sueldo y previa coordinación con el equipo y la jefatura.Acceso a beneficios de la Asociación Chilena de Seguridad y Caja Los Andes.Seguro de salud complementario, aplicable a partir de la contratación indefinida.Beneficios para el hogar, con descuentos preferenciales en productos y servicios.</t>
         </is>
       </c>
     </row>
@@ -990,27 +986,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Directora de arte</t>
+          <t>💼  Finance &amp; Administration Specialist</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KiosClub</t>
+          <t>Milimetrix</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Callao 2911, Las Condes, Chile</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55777/director-a-de-arte</t>
+          <t>https://firstjob.me/oferta/53554/finance-administration-specialist</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1021,13 +1017,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1043,29 +1039,29 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>KiosClub American SupermarketSomos una empresa que surge en 2017 con el propósito de acercar productos internacionales al mercado chileno, con una propuesta diferenciada basada en marcas norteamericanas. Nuestro foco está en la variedad, la innovación y un servicio cercano.Hoy contamos con más de 50 tiendas a lo largo de todo el país y seguimos creciendo. Nuestra misión es ofrecer una experiencia de compra dinámica y entretenida, manteniendo estándares claros en nuestros productos y en la forma en que operamos.¡Estamos buscando a nuestro/a próximo/aDirector/a de Arte!Si te apasiona el mundo del diseño y quieres desarrollarte en el área de Marketing dentro de una empresa en crecimiento, esta oportunidad es para ti.Tus principales responsabilidades serán:Diseñar, desarrollar y liderar propuestas de diseño gráfico e integral desde una perspectiva de branding 360°, fortaleciendo la identidad visual de la marca en todos sus puntos de contacto.Revisar, y entregar feedback sobre las piezas desarrolladas por el equipo creativo, asegurando el cumplimiento de los estándares de diseño y comunicación.Diseñar y Desarrollar piezas gráficas de alta complejidad  para distintos proyectos y canales de la compañíaConceptualizar, coordinar y participar activamente en sesiones fotográficas y producciones audiovisuales para campañas, e-commerce, redes sociales y otros canales.Realizar fotografías de productos, ambientes y contenido de marca, asegurando material visual de alta calidad para el sitio web, campañas y comunicaciones.Supervisar y optimizar la calidad visual del sitio web, proponiendo mejoras en imágenes, banners, recursos gráficos y presentación de productos para fortalecer la experiencia de compra.Apoyar al equipo de Visual Merchandising en terreno, levantando oportunidades y desarrollando materiales gráficos para una correcta implementación en tienda.Administrar y mantener actualizados los recursos gráficos, bibliotecas de imágenes, plantillas y activos visuales de la marca.Requisitos para postular:Formación en Diseño Gráfico o carrera afin1 año de experiencia en dirección de arte, branding y campañas creativasManejo avanzado de Adobe Creative Suite (Photoshop, Illustrator, InDesign, etc.).Experiencia en producción fotográfica y audiovisual (dirección de arte en shoots)Experiencia en dirección de arte, planificación y ejecución de sesiones fotográficas y producciones audiovisuales.Conocimiento en fotografía de producto, composición, iluminación y criterios visuales para e-commerce y redes sociales.Conocimiento en branding, identidad visual, desarrollo de key visuals y aplicación de brandbooks.Deseable experiencia en retail, visual merchandising y desarrollo de materiales para punto de venta.BeneficiosDías libres adicionales, sin límite anual, orientados a la flexibilidad laboral, sin goce de sueldo y previa coordinación con el equipo y la jefatura.Acceso a beneficios de la Asociación Chilena de Seguridad y Caja Los Andes.Seguro de salud complementario, aplicable a partir de la contratación indefinida.Beneficios para el hogar, con descuentos preferenciales en productos y servicios.</t>
+          <t>Buscamos a nuestro/a próximo/aAnalista de Administración y Finanzaspara sumarse al equipo y apoyar el orden y control financiero de una empresa en etapa de crecimiento.Somos una consultora del rubromarketing digital &amp; e-commerce, que trabaja con marcas reconocidas a nivel nacional e internacional. Este rol será clave para asegurar una operación ordenada y mantener claridad en la información financiera para la toma de decisiones.Buscamos un perfil ordenado, confiable y con ganas de aprender, que quiera involucrarse en el día a día del área y entender cómo funciona la gestión financiera de una empresa dinámica.💼Principales responsabilidadesApoyar la gestión y control de contratos (clientes y proveedores)Llevar seguimiento del flujo de caja y apoyar en proyeccionesEjecutar y coordinar pagosApoyar la relación con contabilidad externa y procesos de cierrePreparar reportes básicos para el Gerente GeneralMantener orden y control de procesos administrativos internosApoyar en tareas financieras y operativas del día a día💡Lo que buscamosFormación en Contabilidad o carrera afínAl menos 1 año de experiencia en áreas de administración y/o finanzasAlto nivel de orden, responsabilidad y atención al detalleGanas de aprender y crecer en el áreaBuen manejo de ExcelCapacidad para trabajar de forma autónoma y organizadaBeneficiosModalidad: Híbrida 3x2 (Lunes, Miércoles y Jueves en oficina / Martes y Viernes remoto).Días libres por ocasión: Cumpleaños, mudanza, titulaciónFamilia: Licencias maternales y paternales extendidas (15 días adicionales). Los nuevos padres podrán trabajar de manera remota todas las tardes del primer medio año de vida de su nuevo integrante.Work from Anywhere: 3 semanas al año para trabajar 100% remoto; dos semanas son fijas (septiembre y Navidad/Año Nuevo) y una semana adicional es de libre elección.Vacaciones Premium: Si programas y te tomas 10 días de vacaciones consecutivos, ¡nosotros te regalamos un 11° día libre!Experiencia de equipo: actividades de equipo mensuales para fortalecer la colaboración y cultura interna.Make the dream: Después de cierto tiempo en la empresa, disfruta de hasta 6 meses sin goce de sueldo para perseguir ese sueño pendiente.Luna de miel prolongada: Añade 5 días extra a tu licencia matrimonial.Acompañamiento: Dos semanas libres en caso de pérdida de embarazo. Estamos contigo.Salud: Seguro complementario de salud, catastrófico y de vida sin costo.Convenio preferencial con MindFit Advanced, centro de entrenamiento ubicado en nuestro mismo edificio.Detalles del cargoUbicación: Las Condes, Santiago.Horario: Lun-Jue 09:00 - 18:15 hrs; Vie: 8:30 -16:30</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>💼  Finance &amp; Administration Specialist</t>
+          <t>Práctica Riesgo de Crédito (Perfil Computacional) - Advisory</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Milimetrix</t>
+          <t>KPMG Chile</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Callao 2911, Las Condes, Chile</t>
+          <t>Las Condes, Metropolitana, Chile, Chile</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1075,18 +1071,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/53554/finance-administration-specialist</t>
+          <t>https://firstjob.me/oferta/55808/practica-riesgo-de-credito-perfil-computacional-advisory</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>machine learning, estadistica, matematica, informatica</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -1098,17 +1098,17 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>Buscamos a nuestro/a próximo/aAnalista de Administración y Finanzaspara sumarse al equipo y apoyar el orden y control financiero de una empresa en etapa de crecimiento.Somos una consultora del rubromarketing digital &amp; e-commerce, que trabaja con marcas reconocidas a nivel nacional e internacional. Este rol será clave para asegurar una operación ordenada y mantener claridad en la información financiera para la toma de decisiones.Buscamos un perfil ordenado, confiable y con ganas de aprender, que quiera involucrarse en el día a día del área y entender cómo funciona la gestión financiera de una empresa dinámica.💼Principales responsabilidadesApoyar la gestión y control de contratos (clientes y proveedores)Llevar seguimiento del flujo de caja y apoyar en proyeccionesEjecutar y coordinar pagosApoyar la relación con contabilidad externa y procesos de cierrePreparar reportes básicos para el Gerente GeneralMantener orden y control de procesos administrativos internosApoyar en tareas financieras y operativas del día a día💡Lo que buscamosFormación en Contabilidad o carrera afínAl menos 1 año de experiencia en áreas de administración y/o finanzasAlto nivel de orden, responsabilidad y atención al detalleGanas de aprender y crecer en el áreaBuen manejo de ExcelCapacidad para trabajar de forma autónoma y organizadaBeneficiosModalidad: Híbrida 3x2 (Lunes, Miércoles y Jueves en oficina / Martes y Viernes remoto).Días libres por ocasión: Cumpleaños, mudanza, titulaciónFamilia: Licencias maternales y paternales extendidas (15 días adicionales). Los nuevos padres podrán trabajar de manera remota todas las tardes del primer medio año de vida de su nuevo integrante.Work from Anywhere: 3 semanas al año para trabajar 100% remoto; dos semanas son fijas (septiembre y Navidad/Año Nuevo) y una semana adicional es de libre elección.Vacaciones Premium: Si programas y te tomas 10 días de vacaciones consecutivos, ¡nosotros te regalamos un 11° día libre!Experiencia de equipo: actividades de equipo mensuales para fortalecer la colaboración y cultura interna.Make the dream: Después de cierto tiempo en la empresa, disfruta de hasta 6 meses sin goce de sueldo para perseguir ese sueño pendiente.Luna de miel prolongada: Añade 5 días extra a tu licencia matrimonial.Acompañamiento: Dos semanas libres en caso de pérdida de embarazo. Estamos contigo.Salud: Seguro complementario de salud, catastrófico y de vida sin costo.Convenio preferencial con MindFit Advanced, centro de entrenamiento ubicado en nuestro mismo edificio.Detalles del cargoUbicación: Las Condes, Santiago.Horario: Lun-Jue 09:00 - 18:15 hrs; Vie: 8:30 -16:30</t>
+          <t>¿A quién buscamos?Buscamos un/a estudiante proactivo/a y con marcada orientación tecnológica para unirse a nuestro equipo de Riesgo de Crédito en KPMG.El rol se enfoca en la automatización de procesos, scripting y manejo de datos, siendo fundamental para el desarrollo tecnológico y la optimización de flujos de trabajo.Formación AcadémicaEstudiantes de:Ingeniería Informática.Ingeniería en Computación.Ingeniería Matemática.Estadística.Ingeniería Industrial con fuerte orientación tecnológica.Habilidades TécnicasConocimientos prácticos enPython y/o Rpara desarrollo de scripts.Conocimiento enSQL(valorado).Interés y conocimientos básicos enautomatización, data pipelines y scripting.Conocimientos básicos enmachine learning(deseable).Competencias PersonalesProactividad.Curiosidad técnica.Capacidad de aprendizaje.Habilidad para resolver problemas.IdiomasInglés intermedio (deseable).¿Qué ofrecemos?Este puesto ofrece la oportunidad de aplicar y expandir tus habilidades en un entorno dinámico, contribuyendo a la mejora continua de procesos y al desarrollo de soluciones innovadoras en el área de Riesgo de Crédito.BeneficiosAprendizaje técnico avanzado y práctico.Exposición a herramientas de riesgo, automatización y analítica.Mentores y profesionales experimentados que te guiarán durante tu práctica.Desarrollar competencias tanto técnicas como interpersonales.Pertenecer a una organización de prestigio y trayectoria internacional. Ambiente laboral grato y profesional.Práctica Profesional remunerada.También podrás asistir a los “Meetings Point KPMG”, el cual es un encuentro exclusivo para profesionales de KPMG diseñado para pasarlo bien después del horario de oficina.🔎 Detalles de la práctica:Ubicación:Las Condes, Santiago Modalidad híbrida Horario: Lun–Jue: 9:00 a 18:00 Viernes: 9:00 a 13:30</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Práctica Riesgo de Crédito (Perfil Computacional) - Advisory</t>
+          <t>Práctica Riesgo de Crédito (Perfil Analítico) - Advisory</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1140,15 +1140,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55808/practica-riesgo-de-credito-perfil-computacional-advisory</t>
+          <t>https://firstjob.me/oferta/55807/practica-riesgo-de-credito-perfil-analitico-advisory</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>machine learning, estadistica, matematica, informatica</t>
+          <t>python, analisis, excel</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1173,11 +1173,11 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>¿A quién buscamos?Buscamos un/a estudiante proactivo/a y con marcada orientación tecnológica para unirse a nuestro equipo de Riesgo de Crédito en KPMG.El rol se enfoca en la automatización de procesos, scripting y manejo de datos, siendo fundamental para el desarrollo tecnológico y la optimización de flujos de trabajo.Formación AcadémicaEstudiantes de:Ingeniería Informática.Ingeniería en Computación.Ingeniería Matemática.Estadística.Ingeniería Industrial con fuerte orientación tecnológica.Habilidades TécnicasConocimientos prácticos enPython y/o Rpara desarrollo de scripts.Conocimiento enSQL(valorado).Interés y conocimientos básicos enautomatización, data pipelines y scripting.Conocimientos básicos enmachine learning(deseable).Competencias PersonalesProactividad.Curiosidad técnica.Capacidad de aprendizaje.Habilidad para resolver problemas.IdiomasInglés intermedio (deseable).¿Qué ofrecemos?Este puesto ofrece la oportunidad de aplicar y expandir tus habilidades en un entorno dinámico, contribuyendo a la mejora continua de procesos y al desarrollo de soluciones innovadoras en el área de Riesgo de Crédito.BeneficiosAprendizaje técnico avanzado y práctico.Exposición a herramientas de riesgo, automatización y analítica.Mentores y profesionales experimentados que te guiarán durante tu práctica.Desarrollar competencias tanto técnicas como interpersonales.Pertenecer a una organización de prestigio y trayectoria internacional. Ambiente laboral grato y profesional.Práctica Profesional remunerada.También podrás asistir a los “Meetings Point KPMG”, el cual es un encuentro exclusivo para profesionales de KPMG diseñado para pasarlo bien después del horario de oficina.🔎 Detalles de la práctica:Ubicación:Las Condes, Santiago Modalidad híbrida Horario: Lun–Jue: 9:00 a 18:00 Viernes: 9:00 a 13:30</t>
+          <t>¿A quién buscamos?Buscamos un/a estudiante proactivo/a y con un marcado interés por el análisis cuantitativo para unirse a nuestro equipo de Riesgo de Crédito en KPMG Chile.El/la candidato/a ideal será estudiante de:Ingeniería MatemáticaEstadísticaIngeniería IndustrialEconomíaIngeniería Comercial mención cuantitativaCarreras afinesCon un fuerte enfoque en la interpretación de datos y el entendimiento del negocio financiero.Principales responsabilidadesLas responsabilidades principales incluirán:Apoyo en análisis estadísticos.Exploración de datos.Preparación de bases para validación de modelos de riesgo.Participación en análisis macroeconómicos.Colaboración en proyectos de provisiones normativas (CMF, Basilea III, IFRS 9).Conocimientos deseablesSe valorará:Conocimiento básico en Python, R o software estadístico.Manejo intermedio de Excel.Competencias claveHabilidades analíticas sólidas.Capacidad de aprendizaje continuo.Motivación por el trabajo en equipo.Se considerará un nivel intermedio de inglés como un plus.¿Qué ofrecemos?Esta es una excelente oportunidad para desarrollar experiencia práctica en un entorno desafiante y de aprendizaje constante.BeneficiosOportunidad de trabajar en un entorno empresarial dinámico y colaborativo.Mentores y profesionales experimentados que te guiarán durante tu práctica.Desarrollar competencias tanto técnicas como interpersonales.Pertenecer a una organización de prestigio y trayectoria internacional. Ambiente laboral grato y profesional.Práctica Profesional remunerada.También podrás asistir a los “Meetings Point KPMG”, el cual es un encuentro exclusivo para profesionales de KPMG diseñado para pasarlo bien después del horario de oficina.🔎 Detalles de la práctica:Ubicación: Las Condes, Santiago Modalidad híbrida Horario: Lun–Jue: 9:00 a 18:00 Viernes: 9:00 a 13:30</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Práctica Riesgo de Crédito (Perfil Analítico) - Advisory</t>
+          <t>Práctica Profesional - Estudios y Clientes Marketing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KPMG Chile</t>
+          <t>Ripley chile</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Las Condes, Metropolitana, Chile, Chile</t>
+          <t>Ofi Cerro Colorado 5240 - Comercial, Chile</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1209,19 +1209,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55807/practica-riesgo-de-credito-perfil-analitico-advisory</t>
+          <t>https://firstjob.me/oferta/55813/practica-profesional-estudios-y-clientes-marketing</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>python, analisis, excel</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>¿A quién buscamos?Buscamos un/a estudiante proactivo/a y con un marcado interés por el análisis cuantitativo para unirse a nuestro equipo de Riesgo de Crédito en KPMG Chile.El/la candidato/a ideal será estudiante de:Ingeniería MatemáticaEstadísticaIngeniería IndustrialEconomíaIngeniería Comercial mención cuantitativaCarreras afinesCon un fuerte enfoque en la interpretación de datos y el entendimiento del negocio financiero.Principales responsabilidadesLas responsabilidades principales incluirán:Apoyo en análisis estadísticos.Exploración de datos.Preparación de bases para validación de modelos de riesgo.Participación en análisis macroeconómicos.Colaboración en proyectos de provisiones normativas (CMF, Basilea III, IFRS 9).Conocimientos deseablesSe valorará:Conocimiento básico en Python, R o software estadístico.Manejo intermedio de Excel.Competencias claveHabilidades analíticas sólidas.Capacidad de aprendizaje continuo.Motivación por el trabajo en equipo.Se considerará un nivel intermedio de inglés como un plus.¿Qué ofrecemos?Esta es una excelente oportunidad para desarrollar experiencia práctica en un entorno desafiante y de aprendizaje constante.BeneficiosOportunidad de trabajar en un entorno empresarial dinámico y colaborativo.Mentores y profesionales experimentados que te guiarán durante tu práctica.Desarrollar competencias tanto técnicas como interpersonales.Pertenecer a una organización de prestigio y trayectoria internacional. Ambiente laboral grato y profesional.Práctica Profesional remunerada.También podrás asistir a los “Meetings Point KPMG”, el cual es un encuentro exclusivo para profesionales de KPMG diseñado para pasarlo bien después del horario de oficina.🔎 Detalles de la práctica:Ubicación: Las Condes, Santiago Modalidad híbrida Horario: Lun–Jue: 9:00 a 18:00 Viernes: 9:00 a 13:30</t>
+          <t>Práctica Profesional - Estudios y Clientes Marketing🚀 ¡Buscamos a nuestro/a próximo/a practicante de Estudios y Clientes Marketing en la Gerencia de Marketing de Ripley!Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro.Ser parte de Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te motiva ser parte de un negocio desafiante y que tu práctica tenga impacto real? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Entender las necesidades, preferencias y comportamiento de los clientes de retail, permitiendo de esta forma segmentar y personalizar la experiencia, a la vez de levantar insights que permitan la toma de decisiones basadas en datos sólidos y actualizados para perfeccionar la oferta de valor, la propuesta comercial y la imagen de la marca.Funciones: 🤩Recopilar, limpiar, analizar e interpretar datos, para transformarlos en información de valor.Preparar instrumentos de medición (pautas) y supervisar terrenos de estudios de mercado, para que se ejecuten en calidad y tiempos esperados (cualitativos y cuantitativos)Levantar información de clientes al cierre de cada campaña (perfil de clientes, clientes nuevos, fuga, recurrentes, dormidos, etc).¿Qué estamos buscando? 💡Estudiante de Estudiante de Ingeniería Comercial, Estadístico, Civil o carrera afínContar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)Disponibilidad de 6 meses. (deseable posibilidad de extensión)Conocimiento en Excel.¿Por qué trabajar en Ripley? 🩷Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
         </is>
       </c>
     </row>
@@ -1258,17 +1258,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Práctica Profesional - Estudios y Clientes Marketing</t>
+          <t>Administrador de Catálogo Web - Colina (Híbrido)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ripley chile</t>
+          <t>Rosen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ofi Cerro Colorado 5240 - Comercial, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55813/practica-profesional-estudios-y-clientes-marketing</t>
+          <t>https://firstjob.me/oferta/55802/administrador-de-catalogo-web-colina-hibrido</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1299,13 +1299,13 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1315,47 +1315,47 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>Práctica Profesional - Estudios y Clientes Marketing🚀 ¡Buscamos a nuestro/a próximo/a practicante de Estudios y Clientes Marketing en la Gerencia de Marketing de Ripley!Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro.Ser parte de Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te motiva ser parte de un negocio desafiante y que tu práctica tenga impacto real? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Entender las necesidades, preferencias y comportamiento de los clientes de retail, permitiendo de esta forma segmentar y personalizar la experiencia, a la vez de levantar insights que permitan la toma de decisiones basadas en datos sólidos y actualizados para perfeccionar la oferta de valor, la propuesta comercial y la imagen de la marca.Funciones: 🤩Recopilar, limpiar, analizar e interpretar datos, para transformarlos en información de valor.Preparar instrumentos de medición (pautas) y supervisar terrenos de estudios de mercado, para que se ejecuten en calidad y tiempos esperados (cualitativos y cuantitativos)Levantar información de clientes al cierre de cada campaña (perfil de clientes, clientes nuevos, fuga, recurrentes, dormidos, etc).¿Qué estamos buscando? 💡Estudiante de Estudiante de Ingeniería Comercial, Estadístico, Civil o carrera afínContar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)Disponibilidad de 6 meses. (deseable posibilidad de extensión)Conocimiento en Excel.¿Por qué trabajar en Ripley? 🩷Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
+          <t>📢¡Si te gusta la decoración, el mundo del descanso familiar, Rosen es para ti!Estamos buscando nuevos y nuevas RosenLovers que quieran ser parte de una de las mejores empresas para trabajar en Chile, ranking GPTW 2024. Buscamos el ADN Rosen en cada uno de nuestros/as colaboradores/as, potenciando la Excelencia, Integridad, Compromiso e Innovación.En Rosen creemos en el valor de las personas y en la riqueza de equipos diversos. Por eso, promovemos procesos de selección inclusivos y si necesitas algún ajuste para participar en el proceso, puedes indicarlo en tu postulación. Esta vacante se enmarca en nuestro compromiso con la inclusión laboral y la Ley 21.015.Actualmente nos encontramos en búsqueda de un/aAdministrador(a) de Catálogosa trabajar para nuestraGerencia de E-commerceen Modalidad Híbrida, en nuestras oficinas ubicadas en la comuna de Colina, Región Metropolitana.🔍¿Cuál es la misión de este rol?Gestionar la creación, actualización y publicación de productos y contenido comercial en los canales digitales de la compañía, velando por la calidad de la información y la correcta exhibición de la oferta de productos Rosen.💡¿Qué harás en este cargo?Gestionar la creación, actualización y publicación de productos y contenido comercial en los canales digitales de la compañía.Mantener actualizado el catálogo online, asegurando la correcta exhibición de productos, fichas técnicas, imágenes y categorías.Coordinar la actualización de contenidos y publicaciones con distintas áreas internas para garantizar una experiencia de compra consistente.Monitorear la correcta visualización y disponibilidad de los productos en el sitio web, realizando ajustes y mejoras cuando sea necesario.Detectar, reportar y dar seguimiento a incidencias del sitio web, contribuyendo a su correcto funcionamiento y a una óptima experiencia de usuario.📌¿Cuáles son los requisitos para rol?Título Técnico Profesional o estudios/cursos relacionados con canales digitales, eCommerce o gestión de contenidos web.Deseable experiencia en funciones relacionadas con canales digitales, eCommerce, administración de contenidos o gestión de información.Manejo de Excel nivel intermedio.Disponibilidad para trabajar en modalidad híbrida en Colina (4 días presencial, contamos con estacionamiento y buses de acercamiento).¡Te invitamos a ser parte de una compañía comprometida con sus colaboradores y la sustentabilidad!🌱🙌BeneficiosJornada laboral de 40 horas.Bono de vacaciones 🏝Aguinaldos.30% de descuentos en Productos Rosen.Seguro Complementario de Salud (desde contrato indefinido).Día Libre de Cumpleaños 🎈Regalos Corporativos 🎁Casino corporativo 🍝 y Buses de acercamiento.¡Entre muchos otros!</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Administrador de Catálogo Web - Colina (Híbrido)</t>
+          <t>ANALISTA DE EVALUACION DELITOS FINANCIEROS – PROYECTO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rosen</t>
+          <t>BCP</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Lima, Perú</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55802/administrador-de-catalogo-web-colina-hibrido</t>
+          <t>https://firstjob.me/oferta/55823/analista-de-evaluacion-delitos-financieros-proyecto</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>excel</t>
+          <t>sql, excel, power bi</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1365,7 +1365,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>📢¡Si te gusta la decoración, el mundo del descanso familiar, Rosen es para ti!Estamos buscando nuevos y nuevas RosenLovers que quieran ser parte de una de las mejores empresas para trabajar en Chile, ranking GPTW 2024. Buscamos el ADN Rosen en cada uno de nuestros/as colaboradores/as, potenciando la Excelencia, Integridad, Compromiso e Innovación.En Rosen creemos en el valor de las personas y en la riqueza de equipos diversos. Por eso, promovemos procesos de selección inclusivos y si necesitas algún ajuste para participar en el proceso, puedes indicarlo en tu postulación. Esta vacante se enmarca en nuestro compromiso con la inclusión laboral y la Ley 21.015.Actualmente nos encontramos en búsqueda de un/aAdministrador(a) de Catálogosa trabajar para nuestraGerencia de E-commerceen Modalidad Híbrida, en nuestras oficinas ubicadas en la comuna de Colina, Región Metropolitana.🔍¿Cuál es la misión de este rol?Gestionar la creación, actualización y publicación de productos y contenido comercial en los canales digitales de la compañía, velando por la calidad de la información y la correcta exhibición de la oferta de productos Rosen.💡¿Qué harás en este cargo?Gestionar la creación, actualización y publicación de productos y contenido comercial en los canales digitales de la compañía.Mantener actualizado el catálogo online, asegurando la correcta exhibición de productos, fichas técnicas, imágenes y categorías.Coordinar la actualización de contenidos y publicaciones con distintas áreas internas para garantizar una experiencia de compra consistente.Monitorear la correcta visualización y disponibilidad de los productos en el sitio web, realizando ajustes y mejoras cuando sea necesario.Detectar, reportar y dar seguimiento a incidencias del sitio web, contribuyendo a su correcto funcionamiento y a una óptima experiencia de usuario.📌¿Cuáles son los requisitos para rol?Título Técnico Profesional o estudios/cursos relacionados con canales digitales, eCommerce o gestión de contenidos web.Deseable experiencia en funciones relacionadas con canales digitales, eCommerce, administración de contenidos o gestión de información.Manejo de Excel nivel intermedio.Disponibilidad para trabajar en modalidad híbrida en Colina (4 días presencial, contamos con estacionamiento y buses de acercamiento).¡Te invitamos a ser parte de una compañía comprometida con sus colaboradores y la sustentabilidad!🌱🙌BeneficiosJornada laboral de 40 horas.Bono de vacaciones 🏝Aguinaldos.30% de descuentos en Productos Rosen.Seguro Complementario de Salud (desde contrato indefinido).Día Libre de Cumpleaños 🎈Regalos Corporativos 🎁Casino corporativo 🍝 y Buses de acercamiento.¡Entre muchos otros!</t>
+          <t>En el BCP todo lo hacemos distinto, lo hacemos al #ModoBCP. Por eso buscamos personas con tengan ganas de transformar el país y que disfruten desafiarse en grande para impactar en grande. Si eres una de ellas, podría ser nuestro siguienteANALISTA DE EVA. DELITOS FINANCIEROS.¿Cuál es el reto?Analizar las alertas de clientes BCP en base a un enfoque de riesgos considerando la normativa vigente en materia de Prevención de Lavado de Activos y Financiamiento del Terrorismo (PLAFT).¿Cómo impactarás en grande?Descartar e identificar nuevas señales de alertas de operaciones y transacciones monetarias inusuales de clientes, obtenidas mediante los sistemas automáticos o reportes de oficinas a nivel nacional, identificando patrones de comportamiento que se encuentran fuera del perfil habitual del cliente, teniendo en cuenta las autonomías del puesto.Evaluar las operaciones de clientes realizadas en cuentas y ventanilla, elaborando un informe que sustente la evaluación realizada.Consultar a clientes, funcionarios de negocios y otras áreas de la organización sobre operaciones inusuales de clientes con el objetivo de obtener información adicional y sustento documentario sobre las transacciones realizas a través de la institución.Revisar la documentación proporcionada por el cliente con el objetivo de hacer la debida diligencia y descartar la alerta generada.Administración a nivel usuario de aplicativos que contiene información de los clientes y las operaciones/transacciones bancarias que estos han realizado, como mecanismo o herramienta de consulta para la obtención de información relevante.¿Qué necesitamos de ti?Egresados(as) de las carreras de Administración, Economía, Contabilidad, a fines.Experiencia mínima de 1 año, como Asistentes o Analistas del equipo de PLAFT, Fraudes, Gestión Operativa, Auditoría y/o Riesgos.Conocimiento de Plaft, y herramientas de gestión de data.Manejo de Office Intermedio (Excel y Outlook).Manejo de Power BI, u otra herramienta de gestión de datos (SQL u otras)Beneficios¿Por qué unirte a nuestro equipo?Sé parte de la empresa #1 en Merco Talento 2026.Ambiente de trabajo retador: Únete a un entorno de trabajo donde tu voz importa y tus ideas impulsan el cambio.Recompensa a la medida: Disfruta de descuentos en productos financieros y +100 beneficios corporativos exclusivos para disfrutar con tu familia.Cultura que inspira: Vive una cultura constante de reconocimiento, donde tu talento impacta en grande desde el primer día.Crecimiento profesional: Disfruta de oportunidades de desarrollo continúo, respaldadas por un equipo comprometido con tu éxito.Accede a incentivos por tu esfuerzo/desempeño.¿Qué esperas? Postula hoy y ¡Únete al equipo BCP!“Somos una organización comprometida con la igualdad de derechos y oportunidades. Nuestros procesos de selección se rigen bajo una política donde nuestras/os postulantes son consideradas/os sin importar su origen, género, raza o cualquier otra característica, condición o preferencia, promoviendo así una cultura de respeto mutuo.</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ANALISTA DE EVALUACION DELITOS FINANCIEROS – PROYECTO</t>
+          <t>Abogado</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1416,15 +1416,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55823/analista-de-evaluacion-delitos-financieros-proyecto</t>
+          <t>https://firstjob.me/oferta/55822/abogado</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>sql, excel, power bi</t>
+          <t>analisis</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1449,11 +1449,11 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>En el BCP todo lo hacemos distinto, lo hacemos al #ModoBCP. Por eso buscamos personas con tengan ganas de transformar el país y que disfruten desafiarse en grande para impactar en grande. Si eres una de ellas, podría ser nuestro siguienteANALISTA DE EVA. DELITOS FINANCIEROS.¿Cuál es el reto?Analizar las alertas de clientes BCP en base a un enfoque de riesgos considerando la normativa vigente en materia de Prevención de Lavado de Activos y Financiamiento del Terrorismo (PLAFT).¿Cómo impactarás en grande?Descartar e identificar nuevas señales de alertas de operaciones y transacciones monetarias inusuales de clientes, obtenidas mediante los sistemas automáticos o reportes de oficinas a nivel nacional, identificando patrones de comportamiento que se encuentran fuera del perfil habitual del cliente, teniendo en cuenta las autonomías del puesto.Evaluar las operaciones de clientes realizadas en cuentas y ventanilla, elaborando un informe que sustente la evaluación realizada.Consultar a clientes, funcionarios de negocios y otras áreas de la organización sobre operaciones inusuales de clientes con el objetivo de obtener información adicional y sustento documentario sobre las transacciones realizas a través de la institución.Revisar la documentación proporcionada por el cliente con el objetivo de hacer la debida diligencia y descartar la alerta generada.Administración a nivel usuario de aplicativos que contiene información de los clientes y las operaciones/transacciones bancarias que estos han realizado, como mecanismo o herramienta de consulta para la obtención de información relevante.¿Qué necesitamos de ti?Egresados(as) de las carreras de Administración, Economía, Contabilidad, a fines.Experiencia mínima de 1 año, como Asistentes o Analistas del equipo de PLAFT, Fraudes, Gestión Operativa, Auditoría y/o Riesgos.Conocimiento de Plaft, y herramientas de gestión de data.Manejo de Office Intermedio (Excel y Outlook).Manejo de Power BI, u otra herramienta de gestión de datos (SQL u otras)Beneficios¿Por qué unirte a nuestro equipo?Sé parte de la empresa #1 en Merco Talento 2026.Ambiente de trabajo retador: Únete a un entorno de trabajo donde tu voz importa y tus ideas impulsan el cambio.Recompensa a la medida: Disfruta de descuentos en productos financieros y +100 beneficios corporativos exclusivos para disfrutar con tu familia.Cultura que inspira: Vive una cultura constante de reconocimiento, donde tu talento impacta en grande desde el primer día.Crecimiento profesional: Disfruta de oportunidades de desarrollo continúo, respaldadas por un equipo comprometido con tu éxito.Accede a incentivos por tu esfuerzo/desempeño.¿Qué esperas? Postula hoy y ¡Únete al equipo BCP!“Somos una organización comprometida con la igualdad de derechos y oportunidades. Nuestros procesos de selección se rigen bajo una política donde nuestras/os postulantes son consideradas/os sin importar su origen, género, raza o cualquier otra característica, condición o preferencia, promoviendo así una cultura de respeto mutuo.</t>
+          <t>Buscamos a los que tienen ganas de transformar el país. A los que quieren llegar lejos. Por qué esto no es solo un trabajo. Esto es desafiarte en grande para impactar en grande. Esto es el BCP y te estamos buscando para que formes parte de nuestro equipo comoAbogado de la Unidad de Retenciones Judiciales de la Gerencia Procesal¿Cuál es el reto?Analizar y gestionar los requerimientos judiciales vinculados a embargos en forma de retención sobre cuentas y productos del Banco, identificando riesgos legales, definiendo criterios de actuación y proponiendo soluciones que aseguren el adecuado cumplimiento de los mandatos judiciales, protegiendo los intereses de la organización y contribuyendo a la mejora contínua de los procesos de la Unidad.¿Cómo impactarás en grande?Analizar requerimientos judiciales vinculados a medidas cautelares, especialmente embargos en forma de retención, determinando su alcance jurídico y operativo.Identificar, evaluar y mitigar riesgos legales derivados de la atención y ejecución de requerimientos judiciales notificados al Banco.Emitir instrucciones para la correcta ejecución de órdenes judiciales por parte de las áreas operativas involucradas.Absolver consultas especializadas relacionadas con cuentas y productos embargados.Dar soporte legal al equipo de embargos coactivos en temas vinculados a embargos amparados en la Ley de Procedimiento de ejecución coactiva, Código tributario, etc. y/o demanda de revisión judicial de legalidad.Hacer seguimiento al cumplimiento oportuno de los requerimientos judiciales.Contribuir a proyectos de automatización, transformación digital e inteligencia artificial del área¿Qué necesitamos de ti?Universitario Titulado en la carrera de Derecho2 años de experiencia profesionalcomo abogado en materias vinculadas a Derecho Procesal CivilExperiencia en análisis y gestión procesos judiciales civiles, preferentemente relacionados con Obligaciones de Dar Suma de Dinero, Medidas Cautelares y Ejecución de Garantías (incluyendo la elaboración de medidas cautelares, demandas, apelaciones, recurso extraordinario de casación, etc.)Experiencia en interpretación y análisis de resoluciones judiciales, identificación de riesgos legales y emisión de criterios jurídicos para la toma de decisiones.Experiencia en atención de consultas legales.Deseable experiencia en entidades bancarias, estudios de abogados especializados en litigios o área de asesoría legal con componente procesalDeseable experiencia participando en iniciativas de mejora de procesos, automatización y/o transformación digital.Office nivel intermedio o avanzado (deseable)Conocimiento en IA (deseable)Deseable maestría en Derecho Civil y/o Procesal Civil.Beneficios¿Por qué unirte a nuestro equipo?Ser parte de la empresa #1 en Merco Talento 2024.Ingreso a planilla BCP desde tu primer día.Accede a incentivos por tu esfuerzo/desempeñoAcompañamiento de líderes expertos y referentes en la banca.Acceso a descuentos en productos financieros.</t>
         </is>
       </c>
     </row>
@@ -1465,17 +1465,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Abogado</t>
+          <t>Analista Comex (reemplazoplazo fijo)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BCP</t>
+          <t>Arcor</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Lima, Perú</t>
+          <t>Cerrillos, Chile</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1485,15 +1485,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55822/abogado</t>
+          <t>https://firstjob.me/oferta/55820/analista-comex-reemplazo-plazo-fijo</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>analisis</t>
+          <t>analisis, excel</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1518,11 +1518,11 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Buscamos a los que tienen ganas de transformar el país. A los que quieren llegar lejos. Por qué esto no es solo un trabajo. Esto es desafiarte en grande para impactar en grande. Esto es el BCP y te estamos buscando para que formes parte de nuestro equipo comoAbogado de la Unidad de Retenciones Judiciales de la Gerencia Procesal¿Cuál es el reto?Analizar y gestionar los requerimientos judiciales vinculados a embargos en forma de retención sobre cuentas y productos del Banco, identificando riesgos legales, definiendo criterios de actuación y proponiendo soluciones que aseguren el adecuado cumplimiento de los mandatos judiciales, protegiendo los intereses de la organización y contribuyendo a la mejora contínua de los procesos de la Unidad.¿Cómo impactarás en grande?Analizar requerimientos judiciales vinculados a medidas cautelares, especialmente embargos en forma de retención, determinando su alcance jurídico y operativo.Identificar, evaluar y mitigar riesgos legales derivados de la atención y ejecución de requerimientos judiciales notificados al Banco.Emitir instrucciones para la correcta ejecución de órdenes judiciales por parte de las áreas operativas involucradas.Absolver consultas especializadas relacionadas con cuentas y productos embargados.Dar soporte legal al equipo de embargos coactivos en temas vinculados a embargos amparados en la Ley de Procedimiento de ejecución coactiva, Código tributario, etc. y/o demanda de revisión judicial de legalidad.Hacer seguimiento al cumplimiento oportuno de los requerimientos judiciales.Contribuir a proyectos de automatización, transformación digital e inteligencia artificial del área¿Qué necesitamos de ti?Universitario Titulado en la carrera de Derecho2 años de experiencia profesionalcomo abogado en materias vinculadas a Derecho Procesal CivilExperiencia en análisis y gestión procesos judiciales civiles, preferentemente relacionados con Obligaciones de Dar Suma de Dinero, Medidas Cautelares y Ejecución de Garantías (incluyendo la elaboración de medidas cautelares, demandas, apelaciones, recurso extraordinario de casación, etc.)Experiencia en interpretación y análisis de resoluciones judiciales, identificación de riesgos legales y emisión de criterios jurídicos para la toma de decisiones.Experiencia en atención de consultas legales.Deseable experiencia en entidades bancarias, estudios de abogados especializados en litigios o área de asesoría legal con componente procesalDeseable experiencia participando en iniciativas de mejora de procesos, automatización y/o transformación digital.Office nivel intermedio o avanzado (deseable)Conocimiento en IA (deseable)Deseable maestría en Derecho Civil y/o Procesal Civil.Beneficios¿Por qué unirte a nuestro equipo?Ser parte de la empresa #1 en Merco Talento 2024.Ingreso a planilla BCP desde tu primer día.Accede a incentivos por tu esfuerzo/desempeñoAcompañamiento de líderes expertos y referentes en la banca.Acceso a descuentos en productos financieros.</t>
+          <t>¿Te apasiona la logística, la coordinación de operaciones globales y el desafío de conectar mercados a través de una gestión eficiente y estratégica?EnArcorbuscamos unAnalista de Comex, quien será responsable de asegurar la correcta operación de los procesos de importación y exportación, coordinando múltiples actores internos y externos para garantizar el cumplimiento de los plazos, la normativa vigente y los estándares de servicio del negocio. Esta posición se basa en los perfiles de Importaciones y Exportaciones¿Cuál será tu misión?Gestionar integralmente las operaciones de comercio exterior, coordinando embarques, trámites aduaneros, documentación legal y comercial, proveedores logísticos, organismos reguladores y áreas internas, contribuyendo al abastecimiento y distribución internacional de productos de manera eficiente y oportuna.Principales desafíos:Coordinar procesos de importación y exportación, asegurando el cumplimiento de requisitos legales, aduaneros y documentales.Gestionar la emisión, revisión y control de documentación comercial y logística asociada a operaciones internacionales.Coordinar embarques con proveedores, agentes de aduana, navieras, transportistas y clientes internos.Realizar seguimiento de cargas desde origen hasta destino, monitoreando hitos críticos de cada operación.Mantener comunicación permanente con áreas comerciales, logística, programación, calidad y abastecimiento para asegurar el nivel de servicio comprometido.Elaborar reportes de gestión, indicadores y control de operaciones de comercio exterior.Gestionar contingencias operativas, reclamos, siniestros y requerimientos asociados a la cadena logística internacional.Requisitos:Formación en Comercio Exterior, Logística, Negocios Internacionales o carreras afines.Al menos 2 años de experiencia en operaciones de importación, exportación o logística internacional.Manejo de documentación aduanera, embarques marítimos y coordinación con proveedores logísticos.Excel avanzado como herramienta de análisis y control.Capacidad para organizar múltiples procesos simultáneamente y trabajar con un alto nivel de precisión.Orientación al cliente, habilidades de comunicación y capacidad para coordinar distintos stakeholders.</t>
         </is>
       </c>
     </row>
@@ -1534,17 +1534,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Analista Comex (reemplazoplazo fijo)</t>
+          <t>Coordinador(a) de Atracción de Talento y Experiencia de Ingreso</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Arcor</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cerrillos, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1554,15 +1554,15 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55820/analista-comex-reemplazo-plazo-fijo</t>
+          <t>https://firstjob.me/oferta/55835/coordinador-a-de-atraccion-de-talento-y-experiencia-de-ingreso</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>analisis, excel</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1587,11 +1587,11 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>¿Te apasiona la logística, la coordinación de operaciones globales y el desafío de conectar mercados a través de una gestión eficiente y estratégica?EnArcorbuscamos unAnalista de Comex, quien será responsable de asegurar la correcta operación de los procesos de importación y exportación, coordinando múltiples actores internos y externos para garantizar el cumplimiento de los plazos, la normativa vigente y los estándares de servicio del negocio. Esta posición se basa en los perfiles de Importaciones y Exportaciones¿Cuál será tu misión?Gestionar integralmente las operaciones de comercio exterior, coordinando embarques, trámites aduaneros, documentación legal y comercial, proveedores logísticos, organismos reguladores y áreas internas, contribuyendo al abastecimiento y distribución internacional de productos de manera eficiente y oportuna.Principales desafíos:Coordinar procesos de importación y exportación, asegurando el cumplimiento de requisitos legales, aduaneros y documentales.Gestionar la emisión, revisión y control de documentación comercial y logística asociada a operaciones internacionales.Coordinar embarques con proveedores, agentes de aduana, navieras, transportistas y clientes internos.Realizar seguimiento de cargas desde origen hasta destino, monitoreando hitos críticos de cada operación.Mantener comunicación permanente con áreas comerciales, logística, programación, calidad y abastecimiento para asegurar el nivel de servicio comprometido.Elaborar reportes de gestión, indicadores y control de operaciones de comercio exterior.Gestionar contingencias operativas, reclamos, siniestros y requerimientos asociados a la cadena logística internacional.Requisitos:Formación en Comercio Exterior, Logística, Negocios Internacionales o carreras afines.Al menos 2 años de experiencia en operaciones de importación, exportación o logística internacional.Manejo de documentación aduanera, embarques marítimos y coordinación con proveedores logísticos.Excel avanzado como herramienta de análisis y control.Capacidad para organizar múltiples procesos simultáneamente y trabajar con un alto nivel de precisión.Orientación al cliente, habilidades de comunicación y capacidad para coordinar distintos stakeholders.</t>
+          <t>Nos encontramos en búsqueda de un(a) profesional para integrarse al área de Personas de una compañía en constante crecimiento y transformación.La posición tendrá un rol clave en la gestión integral de los procesos de atracción de talento y experiencia de ingreso, asegurando una experiencia positiva para candidatos, nuevos colaboradores y clientes internos.Buscamos una persona autónoma, proactiva y orientada a la mejora continua, capaz de desenvolverse en entornos dinámicos, impulsar iniciativas y coordinar múltiples stakeholders de manera simultánea.Principales responsabilidadesCoordinar procesos de reclutamiento y selección para posiciones operativas y profesionales.Gestionar la relación y seguimiento con proveedores externos de reclutamiento.Asegurar una experiencia de selección ágil y positiva para candidatos y líderes.Coordinar integralmente el proceso de onboarding de nuevos ingresos.Gestionar actividades asociadas a ingresos, inducciones, equipamiento, beneficios y coordinación con áreas de soporte.Desarrollar y ejecutar iniciativas de marca empleadora.Proponer mejoras, automatizaciones y optimizaciones de procesos relacionados con atracción de talento y experiencia colaborador.Generar seguimiento de indicadores y métricas asociadas a los procesos bajo su responsabilidad.¿Qué buscamos?Profesionales titulados de Psicología, Ingeniería Comercial, Ingeniería en Administración o carreras afines.1-2 años de experiencia.Experiencia coordinando procesos de onboarding y gestión de ingresos.Experiencia trabajando con clientes internos y múltiples áreas.Manejo de Excel intermedio o avanzado.Deseable experiencia en iniciativas de marca empleadora, experiencia colaborador o mejora continua.</t>
         </is>
       </c>
     </row>
@@ -1603,17 +1603,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Coordinador(a) de Atracción de Talento y Experiencia de Ingreso</t>
+          <t>Ingeniero(a) de estudios actuariales</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>BNP Paribas Cardif</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Las Condes, Chile</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1623,19 +1623,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55835/coordinador-a-de-atraccion-de-talento-y-experiencia-de-ingreso</t>
+          <t>https://firstjob.me/oferta/55825/ingeniero-a-de-estudios-actuariales</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>excel</t>
+          <t>analisis, estadistica, power bi</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1656,11 +1656,11 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>Nos encontramos en búsqueda de un(a) profesional para integrarse al área de Personas de una compañía en constante crecimiento y transformación.La posición tendrá un rol clave en la gestión integral de los procesos de atracción de talento y experiencia de ingreso, asegurando una experiencia positiva para candidatos, nuevos colaboradores y clientes internos.Buscamos una persona autónoma, proactiva y orientada a la mejora continua, capaz de desenvolverse en entornos dinámicos, impulsar iniciativas y coordinar múltiples stakeholders de manera simultánea.Principales responsabilidadesCoordinar procesos de reclutamiento y selección para posiciones operativas y profesionales.Gestionar la relación y seguimiento con proveedores externos de reclutamiento.Asegurar una experiencia de selección ágil y positiva para candidatos y líderes.Coordinar integralmente el proceso de onboarding de nuevos ingresos.Gestionar actividades asociadas a ingresos, inducciones, equipamiento, beneficios y coordinación con áreas de soporte.Desarrollar y ejecutar iniciativas de marca empleadora.Proponer mejoras, automatizaciones y optimizaciones de procesos relacionados con atracción de talento y experiencia colaborador.Generar seguimiento de indicadores y métricas asociadas a los procesos bajo su responsabilidad.¿Qué buscamos?Profesionales titulados de Psicología, Ingeniería Comercial, Ingeniería en Administración o carreras afines.1-2 años de experiencia.Experiencia coordinando procesos de onboarding y gestión de ingresos.Experiencia trabajando con clientes internos y múltiples áreas.Manejo de Excel intermedio o avanzado.Deseable experiencia en iniciativas de marca empleadora, experiencia colaborador o mejora continua.</t>
+          <t>Hoy BNP Paribas Cardif busca un(a) Ingeniero(a) de estudios actuariales quién será responsable de garantizar la rentabilidad de la compañía mediante análisis de negocios desarrollado en base a análisis económicos, de datos y evaluaciones técnico-financieras, respetando las políticas y procedimientos de la compañía.¿Cuáles son los principales desafíos del cargo?Analizar la rentabilidad de la cartera de productos y generar proyecciones de los diferentes negocios para entregar a la gerencia Comercial y técnico financiera las herramientas e informes para una correcta toma de decisiones.Seguimiento, estudio y control, de los diferentes riesgos que enfrenta la compañíaTarificar los diferentes seguros que vende la compañíaAsegurar, conocer y comprender las normas de cálculos de pasivos y márgenes de solvencia que afectan la rentabilidad de los productosProponer y mejorar las herramientas y modelos utilizados para la tarificación.Responsable de velar por la aplicación de los controles de Seguridad Financiera, establecidos en los diversos procedimientos operacionales del área.Perfil deseado¿Cómo saber si hago match con esta vacante? Buscamos a alguien que:Requisitos:a. Formación:Ingeniería civil industrial o comercial, estadística o afínb. Experiencia RequeridaNo necesita experiencia previac. Conocimientos y HabilidadesIngles avanzadoExcel avanzadoPower BI básico - medioPython medioAlta capacidad de análisis.Beneficios¿Cuáles son los beneficios y ventajas de trabajar con nosotros?Trabajamos eficientemente: 40 horas semanales en horarios flexibles y los viernes salimos a las 14:00.¡Tenemos más vacaciones y días libres! Una semana adicional de vacaciones + 1 día libre considerando tu cumpleaños y quehaceres personales.Apoyamos tu formación profesional: Acceso ilimitado a nuestra plataforma Coursera y dos días libres al año por estudios.Cardif te cuida: Contarás con telemedicina gratis, seguro de vida, de salud y dental.Queremos que seas tú mismo: Contamos con política de vestimenta flexible.Y muchos otros beneficios que podrás conocer al avanzar en nuestro proceso de selección¿Te sumas a la revolución de la industria del seguro?Esperamos tu postulación ¡seguro y con todo!Todas las contrataciones están sujetas a la ley 21015. En BNP Paribas Cardif creemos en lugares de trabajos inclusivos y diversos, donde todas las personas son bienvenidas. En caso de necesitar adaptaciones para ser parte de nuestro proceso de selección, favor comunicarlo en la sección de preguntas.</t>
         </is>
       </c>
     </row>
@@ -1672,17 +1672,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ingeniero(a) de estudios actuariales</t>
+          <t>Analista Suppy Chain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BNP Paribas Cardif</t>
+          <t>Arcor</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Las Condes, Chile</t>
+          <t>Cerrillos, Chile</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1692,19 +1692,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55825/ingeniero-a-de-estudios-actuariales</t>
+          <t>https://firstjob.me/oferta/55819/analista-suppy-chain</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>analisis, estadistica, power bi</t>
+          <t>analisis</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1725,53 +1725,49 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>Hoy BNP Paribas Cardif busca un(a) Ingeniero(a) de estudios actuariales quién será responsable de garantizar la rentabilidad de la compañía mediante análisis de negocios desarrollado en base a análisis económicos, de datos y evaluaciones técnico-financieras, respetando las políticas y procedimientos de la compañía.¿Cuáles son los principales desafíos del cargo?Analizar la rentabilidad de la cartera de productos y generar proyecciones de los diferentes negocios para entregar a la gerencia Comercial y técnico financiera las herramientas e informes para una correcta toma de decisiones.Seguimiento, estudio y control, de los diferentes riesgos que enfrenta la compañíaTarificar los diferentes seguros que vende la compañíaAsegurar, conocer y comprender las normas de cálculos de pasivos y márgenes de solvencia que afectan la rentabilidad de los productosProponer y mejorar las herramientas y modelos utilizados para la tarificación.Responsable de velar por la aplicación de los controles de Seguridad Financiera, establecidos en los diversos procedimientos operacionales del área.Perfil deseado¿Cómo saber si hago match con esta vacante? Buscamos a alguien que:Requisitos:a. Formación:Ingeniería civil industrial o comercial, estadística o afínb. Experiencia RequeridaNo necesita experiencia previac. Conocimientos y HabilidadesIngles avanzadoExcel avanzadoPower BI básico - medioPython medioAlta capacidad de análisis.Beneficios¿Cuáles son los beneficios y ventajas de trabajar con nosotros?Trabajamos eficientemente: 40 horas semanales en horarios flexibles y los viernes salimos a las 14:00.¡Tenemos más vacaciones y días libres! Una semana adicional de vacaciones + 1 día libre considerando tu cumpleaños y quehaceres personales.Apoyamos tu formación profesional: Acceso ilimitado a nuestra plataforma Coursera y dos días libres al año por estudios.Cardif te cuida: Contarás con telemedicina gratis, seguro de vida, de salud y dental.Queremos que seas tú mismo: Contamos con política de vestimenta flexible.Y muchos otros beneficios que podrás conocer al avanzar en nuestro proceso de selección¿Te sumas a la revolución de la industria del seguro?Esperamos tu postulación ¡seguro y con todo!Todas las contrataciones están sujetas a la ley 21015. En BNP Paribas Cardif creemos en lugares de trabajos inclusivos y diversos, donde todas las personas son bienvenidas. En caso de necesitar adaptaciones para ser parte de nuestro proceso de selección, favor comunicarlo en la sección de preguntas.</t>
+          <t>En Arcor buscamos un Analista Supply Chain para trabajar en nuestro Centro de Distribución ubicado en Cerrillos:Objetivo del cargo:El Analista de Supply Chain es responsable de crear, mantener y controlar indicadores clave de desempeño (KPIs) relacionados con logística y planificación, liderando además el proceso de revisión, control y seguimiento de los procesos del área para asegurar la eficiencia operativa y el cumplimiento de los objetivos estratégicos.Responsabilidades:Generar reportes de abastecimiento y gestión logística.Mantener actualizados los estados y maestros de productos.Crear, controlar y dar seguimiento a indicadores de Logística y Planeamiento.Revisar niveles de servicio y caducidad de productos.Calcular y mantener stocks de seguridad.Mantener actualizados los procesos del área.Liderar reuniones de revisión de nivel de servicio.Administración de KPIs de logística y planificación.Análisis de datos operacionales y generación de reportes para la toma de decisiones.Seguimiento de procesos logísticos y de planificación.Coordinación con Compras, Logística, Producción y Ventas.Identificación de oportunidades de mejora continua y automatización.Elaboración de reportes de abastecimiento nacional y comercio exterior.Seguimiento de stock, programación versus fabricación real y movimientos entre bodegas.Perfil deseadoCarreras requeridas:Ingeniería CivilIngeniería IndustrialIngeniería Comercial o carrera afínExperiencia:Entre 0 y 1 año.Competencias técnicasMicrosoft Office: Nivel 5 (avanzado)Manejo ERP: Nivel 3 (intermedio)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Analista Suppy Chain</t>
+          <t>Práctica profesional - Gerencia Riesgo y Cobranza - Área de Diseño Gráfico</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Arcor</t>
+          <t>Ripley chile</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cerrillos, Chile</t>
+          <t>Ofi. Estado 91 - Producto Financiero, Chile</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55819/analista-suppy-chain</t>
+          <t>https://firstjob.me/oferta/55846/practica-profesional-gerencia-riesgo-y-cobranza-area-de-diseno-grafico</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>analisis</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -1779,26 +1775,26 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>En Arcor buscamos un Analista Supply Chain para trabajar en nuestro Centro de Distribución ubicado en Cerrillos:Objetivo del cargo:El Analista de Supply Chain es responsable de crear, mantener y controlar indicadores clave de desempeño (KPIs) relacionados con logística y planificación, liderando además el proceso de revisión, control y seguimiento de los procesos del área para asegurar la eficiencia operativa y el cumplimiento de los objetivos estratégicos.Responsabilidades:Generar reportes de abastecimiento y gestión logística.Mantener actualizados los estados y maestros de productos.Crear, controlar y dar seguimiento a indicadores de Logística y Planeamiento.Revisar niveles de servicio y caducidad de productos.Calcular y mantener stocks de seguridad.Mantener actualizados los procesos del área.Liderar reuniones de revisión de nivel de servicio.Administración de KPIs de logística y planificación.Análisis de datos operacionales y generación de reportes para la toma de decisiones.Seguimiento de procesos logísticos y de planificación.Coordinación con Compras, Logística, Producción y Ventas.Identificación de oportunidades de mejora continua y automatización.Elaboración de reportes de abastecimiento nacional y comercio exterior.Seguimiento de stock, programación versus fabricación real y movimientos entre bodegas.Perfil deseadoCarreras requeridas:Ingeniería CivilIngeniería IndustrialIngeniería Comercial o carrera afínExperiencia:Entre 0 y 1 año.Competencias técnicasMicrosoft Office: Nivel 5 (avanzado)Manejo ERP: Nivel 3 (intermedio)</t>
+          <t>🚀 ¡Buscamos a nuestro/a próximo/a Practicante de Diseño Gráfico para la Gerencia de Riesgo y Cobranzas de Banco Ripley! 💜Si te apasiona el diseño, la creatividad y la comunicación visual, esta es una excelente oportunidad para desarrollar tu talento y aportar a proyectos con impacto organizacional.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo:Apoyar la comunicación de iniciativas, proyectos y resultados de la gerencia mediante el desarrollo de piezas gráficas y materiales visuales que faciliten la comprensión y el impacto de los mensajes.Funciones: 🤩Diseñar propuestas gráficas para presentaciones ejecutivas y proyectos de la gerencia.Crear piezas visuales para comunicaciones digitales internas.Investigar tendencias y buenas prácticas de diseño para incorporar nuevas ideas y formatos.Apoyar la construcción de material visual para iniciativas estratégicas del área.Velar por la calidad gráfica y consistencia visual de las comunicaciones desarrolladas.¿Qué estamos buscando?💡Estudiante de Diseño Gráfico.Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)Disponibilidad mínima de 3 o 6 meses para realizar la práctica.Conocimientos de Adobe Illustrator e InDesign. (Excluyente)Creatividad, atención al detalle y habilidades de comunicación visual.Interés por el diseño corporativo y la presentación efectiva de información.¿Por qué trabajar en Banco Ripley? 💜Porque tendrás la oportunidad de desarrollar proyectos visibles, aportar nuevas ideas y potenciar tu creatividad en un entorno dinámico y colaborativo.En Ripley y Banco Ripley valoramos la diversidad e inclusión. En el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1806,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Práctica profesional - Gerencia Riesgo y Cobranza - Área de Diseño Gráfico</t>
+          <t>Práctica profesional - Gerencia Riesgo Financiero</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1820,7 +1816,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Ofi. Estado 91 - Producto Financiero, Chile</t>
+          <t>Ofi. Alonso De Cordova 5320 - Operaciones, Chile</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1830,13 +1826,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55846/practica-profesional-gerencia-riesgo-y-cobranza-area-de-diseno-grafico</t>
+          <t>https://firstjob.me/oferta/55865/practica-profesional-gerencia-riesgo-financiero</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>python, sql, analisis, estadistica, excel</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -1859,11 +1859,11 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>🚀 ¡Buscamos a nuestro/a próximo/a Practicante de Diseño Gráfico para la Gerencia de Riesgo y Cobranzas de Banco Ripley! 💜Si te apasiona el diseño, la creatividad y la comunicación visual, esta es una excelente oportunidad para desarrollar tu talento y aportar a proyectos con impacto organizacional.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo:Apoyar la comunicación de iniciativas, proyectos y resultados de la gerencia mediante el desarrollo de piezas gráficas y materiales visuales que faciliten la comprensión y el impacto de los mensajes.Funciones: 🤩Diseñar propuestas gráficas para presentaciones ejecutivas y proyectos de la gerencia.Crear piezas visuales para comunicaciones digitales internas.Investigar tendencias y buenas prácticas de diseño para incorporar nuevas ideas y formatos.Apoyar la construcción de material visual para iniciativas estratégicas del área.Velar por la calidad gráfica y consistencia visual de las comunicaciones desarrolladas.¿Qué estamos buscando?💡Estudiante de Diseño Gráfico.Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)Disponibilidad mínima de 3 o 6 meses para realizar la práctica.Conocimientos de Adobe Illustrator e InDesign. (Excluyente)Creatividad, atención al detalle y habilidades de comunicación visual.Interés por el diseño corporativo y la presentación efectiva de información.¿Por qué trabajar en Banco Ripley? 💜Porque tendrás la oportunidad de desarrollar proyectos visibles, aportar nuevas ideas y potenciar tu creatividad en un entorno dinámico y colaborativo.En Ripley y Banco Ripley valoramos la diversidad e inclusión. En el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.</t>
+          <t>🚀 ¡Buscamos a nuestro/a próximo/a Practicante para la Gerencia de Riesgo Financiero de Banco Ripley! 💜Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Banco Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro.Ser parte de Banco Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te interesa desarrollar modelos analíticos, trabajar con información financiera y participar en la gestión de riesgos de una institución financiera? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Apoyar al equipo de Riesgo Financiero en el análisis y monitoreo de riesgos de liquidez y mercado, participando en el desarrollo de metodologías internas, seguimiento de indicadores clave y validación de información regulatoria, contribuyendo a una gestión eficiente de los riesgos y a la sostenibilidad financiera del Banco.Funciones: 🤩• Apoyar en el desarrollo y mejora de metodologías internas para la medición y gestión de riesgos financieros.• Realizar seguimiento y análisis de los Indicadores Clave de Riesgo (KRI), apoyando el monitoreo de la exposición del Banco.• Colaborar en la validación y revisión de informes regulatorios y normativos.• Analizar bases de datos y generar reportes que apoyen la toma de decisiones del área.• Participar en iniciativas de mejora continua, automatización y optimización de procesos relacionados con la gestión de riesgos.¿Qué estamos buscando? 💡• Estudiante de Ingeniería Comercial, Ingeniería Civil, Estadística, Sociología o carrera afín.• Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)• Disponibilidad mínima de 3 meses para realizar la práctica.• Manejo de Excel.• Conocimientos de SQL.• Conocimientos de Python.• Interés por el análisis de datos, riesgo financiero, modelos analíticos y normativa bancaria.• Capacidad analítica, atención al detalle y orientación a la mejora continua.¿Por qué trabajar en Banco Ripley? 💜Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo. 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y, si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Práctica profesional - Gerencia Riesgo Financiero</t>
+          <t>Práctica Profesional - Gerencia Control de Gestión y Medios - Planificación Financiera</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ofi. Alonso De Cordova 5320 - Operaciones, Chile</t>
+          <t>Ofi. Alonso De Cordova 5320 - Gerencia, Chile</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1895,15 +1895,15 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55865/practica-profesional-gerencia-riesgo-financiero</t>
+          <t>https://firstjob.me/oferta/55859/practica-profesional-gerencia-control-de-gestion-y-medios-planificacion-financiera</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>python, sql, analisis, estadistica, excel</t>
+          <t>analisis, excel, power bi</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>🚀 ¡Buscamos a nuestro/a próximo/a Practicante para la Gerencia de Riesgo Financiero de Banco Ripley! 💜Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Banco Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro.Ser parte de Banco Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te interesa desarrollar modelos analíticos, trabajar con información financiera y participar en la gestión de riesgos de una institución financiera? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Apoyar al equipo de Riesgo Financiero en el análisis y monitoreo de riesgos de liquidez y mercado, participando en el desarrollo de metodologías internas, seguimiento de indicadores clave y validación de información regulatoria, contribuyendo a una gestión eficiente de los riesgos y a la sostenibilidad financiera del Banco.Funciones: 🤩• Apoyar en el desarrollo y mejora de metodologías internas para la medición y gestión de riesgos financieros.• Realizar seguimiento y análisis de los Indicadores Clave de Riesgo (KRI), apoyando el monitoreo de la exposición del Banco.• Colaborar en la validación y revisión de informes regulatorios y normativos.• Analizar bases de datos y generar reportes que apoyen la toma de decisiones del área.• Participar en iniciativas de mejora continua, automatización y optimización de procesos relacionados con la gestión de riesgos.¿Qué estamos buscando? 💡• Estudiante de Ingeniería Comercial, Ingeniería Civil, Estadística, Sociología o carrera afín.• Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)• Disponibilidad mínima de 3 meses para realizar la práctica.• Manejo de Excel.• Conocimientos de SQL.• Conocimientos de Python.• Interés por el análisis de datos, riesgo financiero, modelos analíticos y normativa bancaria.• Capacidad analítica, atención al detalle y orientación a la mejora continua.¿Por qué trabajar en Banco Ripley? 💜Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo. 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y, si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
+          <t>🚀 ¡Buscamos a nuestro/a próximo/a Practicante para la Gerencia de Control de Gestión y Medios de Banco Ripley! 💜Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Banco Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro. Ser parte de Banco Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te motiva participar en la planificación financiera de una organización, analizar información clave para la toma de decisiones y generar impacto real en el negocio? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Apoyar al equipo de Control de Gestión y Medios en la planificación y control de costos operativos, participando en la elaboración presupuestaria, el monitoreo de indicadores y la generación de reportes de gestión que contribuyan a optimizar la eficiencia y apoyar la toma de decisiones estratégicas.Funciones: 🤩• Apoyar en la elaboración y consolidación del presupuesto 2027, recopilando, ordenando y analizando información proveniente de distintas áreas.• Realizar seguimiento y análisis de costos de servicios, identificando desviaciones y oportunidades de mejora en la gestión de gastos.• Generar reportes periódicos de gestión, indicadores de desempeño y control presupuestario para apoyar la toma de decisiones.• Colaborar en la automatización y mejora continua de reportes mediante herramientas como Excel y Power BI.• Participar en análisis financieros y en la elaboración de presentaciones de resultados para clientes internos.• Apoyar en el levantamiento, análisis y validación de información relevante para proyectos e iniciativas del área.• Contribuir a la optimización de procesos y generación de eficiencias mediante el análisis de datos y propuestas de mejora.¿Qué estamos buscando? 💡• Estudiante de Ingeniería Comercial, Ingeniería en Control de Gestión, Ingeniería en Administración y Finanzas, Contador Auditor o carrera afín.• Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)• Disponibilidad para realizar una práctica de 3 a 4 meses.• Manejo intermedio de Excel (tablas dinámicas, fórmulas y análisis de datos).• Conocimientos intermedios de Power BI.• Conocimientos en análisis de datos y control de gestión.¿Por qué trabajar en Banco Ripley? 💜Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo. 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y, si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
         </is>
       </c>
     </row>
@@ -1944,17 +1944,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Práctica Profesional - Gerencia Control de Gestión y Medios - Planificación Financiera</t>
+          <t>Head of Sales</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ripley chile</t>
+          <t>eDarkstore</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Ofi. Alonso De Cordova 5320 - Gerencia, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1964,15 +1964,15 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55859/practica-profesional-gerencia-control-de-gestion-y-medios-planificacion-financiera</t>
+          <t>https://firstjob.me/oferta/55858/head-of-sales</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>analisis, excel, power bi</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1991,17 +1991,17 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>🚀 ¡Buscamos a nuestro/a próximo/a Practicante para la Gerencia de Control de Gestión y Medios de Banco Ripley! 💜Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Banco Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro. Ser parte de Banco Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te motiva participar en la planificación financiera de una organización, analizar información clave para la toma de decisiones y generar impacto real en el negocio? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Apoyar al equipo de Control de Gestión y Medios en la planificación y control de costos operativos, participando en la elaboración presupuestaria, el monitoreo de indicadores y la generación de reportes de gestión que contribuyan a optimizar la eficiencia y apoyar la toma de decisiones estratégicas.Funciones: 🤩• Apoyar en la elaboración y consolidación del presupuesto 2027, recopilando, ordenando y analizando información proveniente de distintas áreas.• Realizar seguimiento y análisis de costos de servicios, identificando desviaciones y oportunidades de mejora en la gestión de gastos.• Generar reportes periódicos de gestión, indicadores de desempeño y control presupuestario para apoyar la toma de decisiones.• Colaborar en la automatización y mejora continua de reportes mediante herramientas como Excel y Power BI.• Participar en análisis financieros y en la elaboración de presentaciones de resultados para clientes internos.• Apoyar en el levantamiento, análisis y validación de información relevante para proyectos e iniciativas del área.• Contribuir a la optimización de procesos y generación de eficiencias mediante el análisis de datos y propuestas de mejora.¿Qué estamos buscando? 💡• Estudiante de Ingeniería Comercial, Ingeniería en Control de Gestión, Ingeniería en Administración y Finanzas, Contador Auditor o carrera afín.• Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)• Disponibilidad para realizar una práctica de 3 a 4 meses.• Manejo intermedio de Excel (tablas dinámicas, fórmulas y análisis de datos).• Conocimientos intermedios de Power BI.• Conocimientos en análisis de datos y control de gestión.¿Por qué trabajar en Banco Ripley? 💜Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo. 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y, si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
+          <t>🚀 eDarkstore es una empresa de logística y tecnología que está revolucionando el mercado y la industria. Potenciamos los e-commerce a través de high tech y un equipo joven, entretenido y, por sobre todo, excepcional 🌟. Tenemos una fuerte cultura de innovación, y nos caracterizamos por una constante búsqueda de la excelencia y nuestra pasión por ofrecer un servicio extraordinario 💪. Si quieres tener una experiencia llena de aprendizajes 📚 y la oportunidad de generar cambios, ¡esta es tu oportunidad! 🙌 Súmate a esta empresa rupturista y buena onda 😎. Buscamos a un(a)Head of Salescon liderazgo, visión comercial y pasión por los resultados.🎯FuncionesProspectar y captar nuevos clientes y oportunidades de negocioLiderar y coordinar al equipo comercial para asegurar la ejecución de estrategias de ventaDesarrollar e implementar estrategias comerciales alineadas con los objetivos de la empresaGenerar reportes de cumplimiento de objetivos y rentabilidad de clientesAlinear los objetivos comerciales con las áreas de operaciones y tecnología (TI)Gestionar contratos con proveedores clave y distribuidoresApoyar la toma de decisiones estratégicas e identificar oportunidades de mejora continua✅Serás un buen match si eres/tienesTítulo en Ingeniería Comercial, Ingeniería Civil Industrial o carrera afín5 años de experiencia en roles de venta, liderando equipos comerciales y trabajando con metas.Dominio avanzado de Excel y manejo de CRM (Hubspot)Conocimiento en estrategias comerciales y negociación (deseable)Alta orientación a resultados, liderazgo, pensamiento analítico y proactividadBeneficios🌟 Hasta un 40% de descuento en Wild Lama, Wild Foods y Casa Nativa.🌟 1 día de home office a la semana de libre elección.🌟 Vestimenta informal.🌟 Y muchos más!</t>
         </is>
       </c>
     </row>
@@ -2013,37 +2013,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Head of Sales</t>
+          <t>Recién tituladoa para Coordinador hipotecario (PLAZO FIJO 3 Meses)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>eDarkstore</t>
+          <t>Scotiabank</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Santiago, Chile</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55858/head-of-sales</t>
+          <t>https://firstjob.me/oferta/55863/recien-titulado-a-para-coordinador-hipotecario-plazo-fijo-3-meses</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>excel</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -2051,16 +2047,16 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -2070,7 +2066,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>🚀 eDarkstore es una empresa de logística y tecnología que está revolucionando el mercado y la industria. Potenciamos los e-commerce a través de high tech y un equipo joven, entretenido y, por sobre todo, excepcional 🌟. Tenemos una fuerte cultura de innovación, y nos caracterizamos por una constante búsqueda de la excelencia y nuestra pasión por ofrecer un servicio extraordinario 💪. Si quieres tener una experiencia llena de aprendizajes 📚 y la oportunidad de generar cambios, ¡esta es tu oportunidad! 🙌 Súmate a esta empresa rupturista y buena onda 😎. Buscamos a un(a)Head of Salescon liderazgo, visión comercial y pasión por los resultados.🎯FuncionesProspectar y captar nuevos clientes y oportunidades de negocioLiderar y coordinar al equipo comercial para asegurar la ejecución de estrategias de ventaDesarrollar e implementar estrategias comerciales alineadas con los objetivos de la empresaGenerar reportes de cumplimiento de objetivos y rentabilidad de clientesAlinear los objetivos comerciales con las áreas de operaciones y tecnología (TI)Gestionar contratos con proveedores clave y distribuidoresApoyar la toma de decisiones estratégicas e identificar oportunidades de mejora continua✅Serás un buen match si eres/tienesTítulo en Ingeniería Comercial, Ingeniería Civil Industrial o carrera afín5 años de experiencia en roles de venta, liderando equipos comerciales y trabajando con metas.Dominio avanzado de Excel y manejo de CRM (Hubspot)Conocimiento en estrategias comerciales y negociación (deseable)Alta orientación a resultados, liderazgo, pensamiento analítico y proactividadBeneficios🌟 Hasta un 40% de descuento en Wild Lama, Wild Foods y Casa Nativa.🌟 1 día de home office a la semana de libre elección.🌟 Vestimenta informal.🌟 Y muchos más!</t>
+          <t>Propósito:Ejecutar estrategias comerciales dirigidas a las inmobiliarias con las cuales se generan convenios, con la finalidad de entregar condiciones por volúmenes de operaciones dirigido a los distintos segmentos de negocios Retail Banking del Banco. Implementación, control, mantención, seguimiento y actualización de los convenios efectuados en su zona, administrando y fortaleciendo las relaciones de los convenios con las inmobiliarias. Asegurar la coordinación y calidad de atención de los Canales a las Inmobiliarias en Convenio.Responsabilidades:Apoyar y asesorar en la gestión de venta a los ejecutivos de Red de Sucursales y Fuerza de Ventas, mediante la oportuna entrega de listados de referidos campañables y el direccionamiento y asesoría ante consultas específicas relativas al producto.Seguimiento comercial y operativo de los proyectos financiados por el Banco.Concreción de nuevos convenios inmobiliarios. Coordinación, control y seguimiento de los convenios inmobiliarios vigentes locales como regionales.Coordinación con áreas de curse de las operaciones hipotecarias. (seguimiento para asegurar el correcto curse de las operaciones hipotecarias meta 99 días E2E, desde visado hasta la entrega de la escritura a la inmobiliaria)Trabajo en terreno con las inmobiliarias, visitar proyectos, visualizar sus potencialidades de cruce y calidad del servicio ofrecido sean estos proyectos encadenados y no encadenados, asegurando una atención y nivel de servicio excepcional que incluya las salas de ventas y en permanente coordinación con Sucursales y FFVV.Preparar información para controlar y efectuar el seguimiento de metas de convenios inmobiliarios y proyectos encadenados. Generación de Informes de visita y control de gestión.Analizar periódicamente la competencia regional investigando los productos y servicios que tienen respecto a los nuestros, buscando ofertas, nuevos productos, nuevos atributos y nuevas prácticas que mejoren nuestro servicio (incorporar Bench en las planillas de seguimiento y control de proyectos).Participar en reuniones con los ejecutivos de la banca inmobiliaria.Realizar actividades de capacitación periódicas tanto en canales internos como externos del banco sobre los productos y servicios a cargo.Contribuir al clima laboral dentro de la unidad, aplicando los valores del grupo Scotiabank facilitando el trabajo en equipo y contribuyendo a su desarrollo de carrera.Participar activamente en sesiones de coaching programadas por su jefatura.Participación en ferias inmobiliarias y eventos de la industria, así como en eventos del área con las inmobiliarias.Adecuado manejo del presupuesto y control de gastos de la operación sobre cada convenio.Requisitos:Titulado/a de Ingeniería Comercial o carrera a fin.Interés y motivación por el área comercial en banca.Manejo de Office nivel usuarioBeneficios¿Por qué elegirnos? 👀👀💻 Somos un Banco en proceso de modernización y digitalización.⏱ Equilibrio de vida personal y laboral. ¡Primer banco en reducir la jornada a 39 horas!💡 Grandes oportunidades de movilidad interna. ¡Queremos que crezcas y te desarrolles profesionalmente!📚 Educación y aprendizaje continuo: participa en proyectos, conferencias y eventos para desarrollar nuevas habilidades y conocimientos relevantes.🛫 Posibilidad de trabajar en proyectos con equipos de otros países, ya que potenciamos el intercambio de ideas.🎁 Excelentes beneficios: elige tus días libres, elige cómo distribuir tus bonos, convenios de salud y educación.🌈 Somos diversos e inclusivos.En Scotiabank, la inclusión es parte de nuestra forma de hacer banca 💜. Esta postulación está abierta conforme a la Ley 21.015. Si necesitas algún ajuste razonable para participar en el proceso, cuéntanos 🤝.¡No dudes en postular, únete a este viaje y sé nuestro próximo/a Scotiabanker!</t>
         </is>
       </c>
     </row>
@@ -2082,17 +2078,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Recién tituladoa para Coordinador hipotecario (PLAZO FIJO 3 Meses)</t>
+          <t>Talent &amp; Culture Assistant Retail</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotiabank</t>
+          <t>Belcorp</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>Quilicura, Chile</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2102,13 +2098,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55863/recien-titulado-a-para-coordinador-hipotecario-plazo-fijo-3-meses</t>
+          <t>https://firstjob.me/oferta/55845/talent-culture-assistant-retail</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>Propósito:Ejecutar estrategias comerciales dirigidas a las inmobiliarias con las cuales se generan convenios, con la finalidad de entregar condiciones por volúmenes de operaciones dirigido a los distintos segmentos de negocios Retail Banking del Banco. Implementación, control, mantención, seguimiento y actualización de los convenios efectuados en su zona, administrando y fortaleciendo las relaciones de los convenios con las inmobiliarias. Asegurar la coordinación y calidad de atención de los Canales a las Inmobiliarias en Convenio.Responsabilidades:Apoyar y asesorar en la gestión de venta a los ejecutivos de Red de Sucursales y Fuerza de Ventas, mediante la oportuna entrega de listados de referidos campañables y el direccionamiento y asesoría ante consultas específicas relativas al producto.Seguimiento comercial y operativo de los proyectos financiados por el Banco.Concreción de nuevos convenios inmobiliarios. Coordinación, control y seguimiento de los convenios inmobiliarios vigentes locales como regionales.Coordinación con áreas de curse de las operaciones hipotecarias. (seguimiento para asegurar el correcto curse de las operaciones hipotecarias meta 99 días E2E, desde visado hasta la entrega de la escritura a la inmobiliaria)Trabajo en terreno con las inmobiliarias, visitar proyectos, visualizar sus potencialidades de cruce y calidad del servicio ofrecido sean estos proyectos encadenados y no encadenados, asegurando una atención y nivel de servicio excepcional que incluya las salas de ventas y en permanente coordinación con Sucursales y FFVV.Preparar información para controlar y efectuar el seguimiento de metas de convenios inmobiliarios y proyectos encadenados. Generación de Informes de visita y control de gestión.Analizar periódicamente la competencia regional investigando los productos y servicios que tienen respecto a los nuestros, buscando ofertas, nuevos productos, nuevos atributos y nuevas prácticas que mejoren nuestro servicio (incorporar Bench en las planillas de seguimiento y control de proyectos).Participar en reuniones con los ejecutivos de la banca inmobiliaria.Realizar actividades de capacitación periódicas tanto en canales internos como externos del banco sobre los productos y servicios a cargo.Contribuir al clima laboral dentro de la unidad, aplicando los valores del grupo Scotiabank facilitando el trabajo en equipo y contribuyendo a su desarrollo de carrera.Participar activamente en sesiones de coaching programadas por su jefatura.Participación en ferias inmobiliarias y eventos de la industria, así como en eventos del área con las inmobiliarias.Adecuado manejo del presupuesto y control de gastos de la operación sobre cada convenio.Requisitos:Titulado/a de Ingeniería Comercial o carrera a fin.Interés y motivación por el área comercial en banca.Manejo de Office nivel usuarioBeneficios¿Por qué elegirnos? 👀👀💻 Somos un Banco en proceso de modernización y digitalización.⏱ Equilibrio de vida personal y laboral. ¡Primer banco en reducir la jornada a 39 horas!💡 Grandes oportunidades de movilidad interna. ¡Queremos que crezcas y te desarrolles profesionalmente!📚 Educación y aprendizaje continuo: participa en proyectos, conferencias y eventos para desarrollar nuevas habilidades y conocimientos relevantes.🛫 Posibilidad de trabajar en proyectos con equipos de otros países, ya que potenciamos el intercambio de ideas.🎁 Excelentes beneficios: elige tus días libres, elige cómo distribuir tus bonos, convenios de salud y educación.🌈 Somos diversos e inclusivos.En Scotiabank, la inclusión es parte de nuestra forma de hacer banca 💜. Esta postulación está abierta conforme a la Ley 21.015. Si necesitas algún ajuste razonable para participar en el proceso, cuéntanos 🤝.¡No dudes en postular, únete a este viaje y sé nuestro próximo/a Scotiabanker!</t>
+          <t>¿Buscas un nuevo desafío en el mundo del Retail? ¿Te apasiona la coordinación, el trabajo en equipo y brindar una excelente experiencia a las personas? ¡Entonces esta oportunidad es para ti!Somos una empresa omnicanal y líder en el rubro de la venta directa, con presencia en 14 países de la región. Nos dedicamos a la comercialización de cosméticos a través de nuestras marcasL'BEL, Ésika y Cyzone, presentes en los canales de Venta Directa, E-commerce y Retail.En esta oportunidad buscamos un(a)Asistente Retailpara integrarse a nuestro equipo en unproyecto a plazo fijo de 3 meses, apoyando la gestión administrativa y operacional del área, y contribuyendo al cumplimiento de nuestros objetivos de negocio.Como parte de nuestro equipo de Retail, tendrás un rol clave en el soporte y coordinación de los principales procesos del área. Entre tus principales responsabilidades estarán:Liderar los procesos de reclutamiento, selección y contratación de posiciones de Retail. Apoyar el proceso de incorporación y la gestión administrativa de los nuevos colaboradores de Retail.Gestionar solicitudes administrativasCoordinar y dar seguimiento a la gestión de proveedores, cotizaciones y órdenes de compra.Elaborar, analizar y dar seguimiento a los principales indicadores de gestión del área, tales como rotación, headcount, dotación, vacantes, cobertura de posiciones y otros KPI de Retail, generando reportes que apoyen la toma de decisiones.Perfil deseadoTítulo Técnico o Profesional en Administración de Empresas, Ingeniería en Administración, Ingeniería Comercial o carrera afín.Deseable manejo de Excel nivel intermedio.Deseable experiencia utilizando SAP u otro ERP.Alta capacidad de organización, planificación y seguimiento.Proactividad, orientación al cliente interno y excelentes habilidades de coordinación.</t>
         </is>
       </c>
     </row>
@@ -2147,35 +2147,35 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Talent &amp; Culture Assistant Retail</t>
+          <t>Trainee de Inversiones AFP PlanVital 2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Belcorp</t>
+          <t>AFP Plan Vital</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Quilicura, Chile</t>
+          <t>Las Condes, Metropolitana, Chile</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55845/talent-culture-assistant-retail</t>
+          <t>https://firstjob.me/oferta/55844/trainee-de-inversiones-afp-planvital-2026</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>excel</t>
+          <t>python, sql, analisis, trainee, excel</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -2185,10 +2185,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -2197,54 +2197,54 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>¿Buscas un nuevo desafío en el mundo del Retail? ¿Te apasiona la coordinación, el trabajo en equipo y brindar una excelente experiencia a las personas? ¡Entonces esta oportunidad es para ti!Somos una empresa omnicanal y líder en el rubro de la venta directa, con presencia en 14 países de la región. Nos dedicamos a la comercialización de cosméticos a través de nuestras marcasL'BEL, Ésika y Cyzone, presentes en los canales de Venta Directa, E-commerce y Retail.En esta oportunidad buscamos un(a)Asistente Retailpara integrarse a nuestro equipo en unproyecto a plazo fijo de 3 meses, apoyando la gestión administrativa y operacional del área, y contribuyendo al cumplimiento de nuestros objetivos de negocio.Como parte de nuestro equipo de Retail, tendrás un rol clave en el soporte y coordinación de los principales procesos del área. Entre tus principales responsabilidades estarán:Liderar los procesos de reclutamiento, selección y contratación de posiciones de Retail. Apoyar el proceso de incorporación y la gestión administrativa de los nuevos colaboradores de Retail.Gestionar solicitudes administrativasCoordinar y dar seguimiento a la gestión de proveedores, cotizaciones y órdenes de compra.Elaborar, analizar y dar seguimiento a los principales indicadores de gestión del área, tales como rotación, headcount, dotación, vacantes, cobertura de posiciones y otros KPI de Retail, generando reportes que apoyen la toma de decisiones.Perfil deseadoTítulo Técnico o Profesional en Administración de Empresas, Ingeniería en Administración, Ingeniería Comercial o carrera afín.Deseable manejo de Excel nivel intermedio.Deseable experiencia utilizando SAP u otro ERP.Alta capacidad de organización, planificación y seguimiento.Proactividad, orientación al cliente interno y excelentes habilidades de coordinación.</t>
+          <t>¡Invierte en tu carrera con nosotros!Si eres recién egresado/a y te apasionan los mercados financieros, el análisis y la toma de decisiones basada en datos, queremos ayudarte a explorar tu potencial.En AFP PlanVital estamos buscando a jóvenes profesionales (recién egresados) que quieran desarrollar su carrera en una de las gerencias más estratégicas de nuestro negocio.Diseñamos este programa para acelerar tu aprendizaje, exponerte a desafíos reales y entregarte las herramientas para construir una carrera de largo plazo en inversiones.Durante tus primeros 12 meses conocerás de cerca cómo funciona una de las áreas más desafiantes del negocio, participando en procesos vinculados a Renta Fija y Renta Variable. Aprenderás junto a especialistas del área, conocerás distintas perspectivas del proceso de inversión y desarrollarás habilidades técnicas que te permitirán acelerar tu crecimiento profesional.Más que experiencia previa, buscamos personas con:Curiosidad por entender cómo funcionan los mercadosCapacidad analítica y pensamiento críticoGanas de aprender, desafiarse y crecer profesionalmenteMotivación por construir una carrera en inversiones¡La próxima generación de inversiones comienza aquí!Requisitos Candidato/aIng. Comercial o Civil con mención en economía o finanzasManejo de Office (Word, Excel, Power Point)Ideal conocimientos en programación (Python, SQL u otros)Esta oferta es apta para personas en situación de discapacidad.Beneficios¿Qué hace diferente a este programa?Contrato indefinido desde tu ingresoAprendizaje en procesos de distintas áreasAcompañamiento permanente a través de mentoríaFormación especializada en mercado financiero, Bloomberg, Python y herramientas de análisisParticipación en proyectos reales que están transformando la industria previsionalPosibilidad de especializarte y proyectar tu carrera dentro de la Gerencia de Inversiones</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Trainee de Inversiones AFP PlanVital 2026</t>
+          <t>Analista de Gestión Comercial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AFP Plan Vital</t>
+          <t>Entel Perú</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Las Condes, Metropolitana, Chile</t>
+          <t>Lima, Perú</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55844/trainee-de-inversiones-afp-planvital-2026</t>
+          <t>https://firstjob.me/oferta/55895/analista-de-gestion-comercial</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>python, sql, analisis, trainee, excel</t>
+          <t>modelo, excel</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -2254,10 +2254,10 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -2266,14 +2266,14 @@
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>¡Invierte en tu carrera con nosotros!Si eres recién egresado/a y te apasionan los mercados financieros, el análisis y la toma de decisiones basada en datos, queremos ayudarte a explorar tu potencial.En AFP PlanVital estamos buscando a jóvenes profesionales (recién egresados) que quieran desarrollar su carrera en una de las gerencias más estratégicas de nuestro negocio.Diseñamos este programa para acelerar tu aprendizaje, exponerte a desafíos reales y entregarte las herramientas para construir una carrera de largo plazo en inversiones.Durante tus primeros 12 meses conocerás de cerca cómo funciona una de las áreas más desafiantes del negocio, participando en procesos vinculados a Renta Fija y Renta Variable. Aprenderás junto a especialistas del área, conocerás distintas perspectivas del proceso de inversión y desarrollarás habilidades técnicas que te permitirán acelerar tu crecimiento profesional.Más que experiencia previa, buscamos personas con:Curiosidad por entender cómo funcionan los mercadosCapacidad analítica y pensamiento críticoGanas de aprender, desafiarse y crecer profesionalmenteMotivación por construir una carrera en inversiones¡La próxima generación de inversiones comienza aquí!Requisitos Candidato/aIng. Comercial o Civil con mención en economía o finanzasManejo de Office (Word, Excel, Power Point)Ideal conocimientos en programación (Python, SQL u otros)Esta oferta es apta para personas en situación de discapacidad.Beneficios¿Qué hace diferente a este programa?Contrato indefinido desde tu ingresoAprendizaje en procesos de distintas áreasAcompañamiento permanente a través de mentoríaFormación especializada en mercado financiero, Bloomberg, Python y herramientas de análisisParticipación en proyectos reales que están transformando la industria previsionalPosibilidad de especializarte y proyectar tu carrera dentro de la Gerencia de Inversiones</t>
+          <t>¿Te mueve colaborar, desafiar y crecer con propósito? Conoce que desafíos te esperan como Analista de Gestión ComercialGestión Comercial: Monitorear diariamente el embudo de ventas desde la prospección hasta la conversión (instalación) para identificar oportunidades de mejora en la gestión de los socios de negocio e implementarlas.Soporte y Capacitación al Canal Externo: Ser el punto de contacto para los dueños y supervisores de las fuerzas de ventas terceras, resolviendo dudas sobre el proceso de ventas y modelo de negocio.Optimización y Automatización de Flujos: Implementar soluciones que nos ayuden a optimizar los flujos operacionales con herramientas de tecnología o propuestas de flujos.Control de Gestión (BI): Apoyar y coordinar la elaboración de dashboards para el seguimiento de ventas e instalaciones para optimizar la toma de decisiones en el día a día.Coordinación con las áreas de agendamiento e instalaciones para la correcta conversión de las órdenes de venta.Validación de la actividad comisional de los socios de negocio.Garantizar el cumplimiento del marco normativo de seguridad de la información definido dentro de la organización.Brindar los recursos necesarios para el cumplimiento del modelo de prevención de delitos y facilitar la información requerida para la identificación de riesgos del MPD en su área correspondiente.Cumplir y hacer cumplir, por sus equipos de trabajo, los lineamientos establecidos en los sistemas de gestión implementados y/o certificados.Participar activamente en el desarrollo, implementación y mejora de los sistemas de gestión, y fomentarlo en sus equipos de trabajo.RequisitosBachiller o egresado en Ing. Industrial, Administración o afinesConocimiento de Excel a nivel avanzadoManejo de herramientas de IA generativaExperiencia en áreas comerciales, planeamiento u operaciones (deseable)</t>
         </is>
       </c>
     </row>
@@ -2285,12 +2285,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Analista de Gestión Comercial</t>
+          <t>Ejecutivo de Negocios  Banca Persona</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Entel Perú</t>
+          <t>BCP</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2305,15 +2305,15 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55895/analista-de-gestion-comercial</t>
+          <t>https://firstjob.me/oferta/55891/ejecutivo-de-negocios-banca-persona</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>modelo, excel</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2338,11 +2338,11 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>¿Te mueve colaborar, desafiar y crecer con propósito? Conoce que desafíos te esperan como Analista de Gestión ComercialGestión Comercial: Monitorear diariamente el embudo de ventas desde la prospección hasta la conversión (instalación) para identificar oportunidades de mejora en la gestión de los socios de negocio e implementarlas.Soporte y Capacitación al Canal Externo: Ser el punto de contacto para los dueños y supervisores de las fuerzas de ventas terceras, resolviendo dudas sobre el proceso de ventas y modelo de negocio.Optimización y Automatización de Flujos: Implementar soluciones que nos ayuden a optimizar los flujos operacionales con herramientas de tecnología o propuestas de flujos.Control de Gestión (BI): Apoyar y coordinar la elaboración de dashboards para el seguimiento de ventas e instalaciones para optimizar la toma de decisiones en el día a día.Coordinación con las áreas de agendamiento e instalaciones para la correcta conversión de las órdenes de venta.Validación de la actividad comisional de los socios de negocio.Garantizar el cumplimiento del marco normativo de seguridad de la información definido dentro de la organización.Brindar los recursos necesarios para el cumplimiento del modelo de prevención de delitos y facilitar la información requerida para la identificación de riesgos del MPD en su área correspondiente.Cumplir y hacer cumplir, por sus equipos de trabajo, los lineamientos establecidos en los sistemas de gestión implementados y/o certificados.Participar activamente en el desarrollo, implementación y mejora de los sistemas de gestión, y fomentarlo en sus equipos de trabajo.RequisitosBachiller o egresado en Ing. Industrial, Administración o afinesConocimiento de Excel a nivel avanzadoManejo de herramientas de IA generativaExperiencia en áreas comerciales, planeamiento u operaciones (deseable)</t>
+          <t>Buscamos a los que tienen ganas de transformar el país. A los que quieren llegar lejos. Por qué esto no es solo un trabajo. Esto es desafiarte en grande para impactar en grande. Esto es el BCP y te estamos buscando para que formes parte de nuestro equipo comoEjecutivo de Negocios Bex Digital.¿Cuál es el reto?Construir relaciones a largo plazo con los clientes a través de la efectiva gestión comercial de su cartera. Es responsable de interactuar con los clientes a través del servicio ágil y construir relaciones duraderas.¿Cómo impactarás en grande?Gestionar y desarrollar una cartera de clientes, identificando oportunidades de negocio y fortaleciendo relaciones de largo plazo.Brindar atención y asesoría remota, ofreciendo soluciones financieras de acuerdo con las necesidades de cada cliente.Impulsar la venta cruzada de productos y servicios para incrementar la vinculación y fidelización del clienteRealizar seguimiento permanente a la cartera, asegurando una experiencia ágil, una atención oportuna y altos niveles de satisfacción.Elaborar propuestas comerciales y resolver consultas o requerimientos, cumpliendo las políticas y lineamientos del banco.¿Qué necesitamos de ti?Egresado(a) universitario(a) de carreras afines a Banca, Administración, Economía, Negocios o similares.Experiencia mínima de 1 año en posiciones comerciales dentro de banca, financieras, cajas, seguros, fintech o empresas relacionadas.Experiencia en gestión de cartera de clientes, venta de productos financieros y cumplimiento de metas comerciales.Disponibilidad para laborar de manera presencial en Surquillo o San Isidro, de lunes a viernes de 8:30 a.m. a 6:00 p.m. y sábados de 8:30 a.m. a 1:00 p.mManejo de Excel a nivel intermedio¿Por qué unirte a nuestro equipo?Ser parte de la empresa #1 en Merco Talento 2025.Ingreso a planilla BCP desde tu primer día.Accede a incentivos por tu esfuerzo/desempeñoAcompañamiento de líderes expertos y referentes en la banca.Acceso a descuentos en productos financieros.Beneficios corporativos exclusivos por provincia para disfrutar con tu familia.Formarás parte de una cultura constante de reconocimientosSí, a ti. Te estamos buscando ¡Únete al equipo BCP!“Somos una organización comprometida con la igualdad de derechos y oportunidades. Nuestros procesos de selección se rigen bajo una política donde nuestras/os postulantes son consideradas/os sin importar su origen, género, raza o cualquier otra característica, condición o preferencia, promoviendo así una cultura de respeto mutuo"</t>
         </is>
       </c>
     </row>
@@ -2354,17 +2354,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ejecutivo de Negocios  Banca Persona</t>
+          <t>Ejecutivoa de Gestión y Ahorro UBM</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BCP</t>
+          <t>Clickie</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lima, Perú</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2374,17 +2374,13 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55891/ejecutivo-de-negocios-banca-persona</t>
+          <t>https://firstjob.me/oferta/55897/ejecutivo-a-de-gestion-y-ahorro-ubm</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>excel</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -2411,7 +2407,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Buscamos a los que tienen ganas de transformar el país. A los que quieren llegar lejos. Por qué esto no es solo un trabajo. Esto es desafiarte en grande para impactar en grande. Esto es el BCP y te estamos buscando para que formes parte de nuestro equipo comoEjecutivo de Negocios Bex Digital.¿Cuál es el reto?Construir relaciones a largo plazo con los clientes a través de la efectiva gestión comercial de su cartera. Es responsable de interactuar con los clientes a través del servicio ágil y construir relaciones duraderas.¿Cómo impactarás en grande?Gestionar y desarrollar una cartera de clientes, identificando oportunidades de negocio y fortaleciendo relaciones de largo plazo.Brindar atención y asesoría remota, ofreciendo soluciones financieras de acuerdo con las necesidades de cada cliente.Impulsar la venta cruzada de productos y servicios para incrementar la vinculación y fidelización del clienteRealizar seguimiento permanente a la cartera, asegurando una experiencia ágil, una atención oportuna y altos niveles de satisfacción.Elaborar propuestas comerciales y resolver consultas o requerimientos, cumpliendo las políticas y lineamientos del banco.¿Qué necesitamos de ti?Egresado(a) universitario(a) de carreras afines a Banca, Administración, Economía, Negocios o similares.Experiencia mínima de 1 año en posiciones comerciales dentro de banca, financieras, cajas, seguros, fintech o empresas relacionadas.Experiencia en gestión de cartera de clientes, venta de productos financieros y cumplimiento de metas comerciales.Disponibilidad para laborar de manera presencial en Surquillo o San Isidro, de lunes a viernes de 8:30 a.m. a 6:00 p.m. y sábados de 8:30 a.m. a 1:00 p.mManejo de Excel a nivel intermedio¿Por qué unirte a nuestro equipo?Ser parte de la empresa #1 en Merco Talento 2025.Ingreso a planilla BCP desde tu primer día.Accede a incentivos por tu esfuerzo/desempeñoAcompañamiento de líderes expertos y referentes en la banca.Acceso a descuentos en productos financieros.Beneficios corporativos exclusivos por provincia para disfrutar con tu familia.Formarás parte de una cultura constante de reconocimientosSí, a ti. Te estamos buscando ¡Únete al equipo BCP!“Somos una organización comprometida con la igualdad de derechos y oportunidades. Nuestros procesos de selección se rigen bajo una política donde nuestras/os postulantes son consideradas/os sin importar su origen, género, raza o cualquier otra característica, condición o preferencia, promoviendo así una cultura de respeto mutuo"</t>
+          <t>¡Estamos contratando! Ejecutivo/a de Gestión y Ahorro UBMUbicación:PresencialEquipo:Utility Bill Management (UBM)Tipo de contrato:Jornada completaReporta a:Responsable del Servicio de UBMSobre ClickieEn Clickie ayudamos a nuestros clientes a tomar el control de sus servicios públicos, generando ahorros reales y tangibles a través de la gestión inteligente de sus datos y contratos. Somos un equipo que combina tecnología congestión en terreno de alto impacto— y buscamos sumar a alguien que disfrute salir a resolver, negociar y conseguir resultados concretos cara a cara con los actores que hacen posible el ahorro.El rolBuscamos un/aEjecutivo/a de Gestión y Ahorro UBMpara sumarse a nuestro equipo de Utility Bill Management. Este rol es, ante todo, unrol de campo: la persona será responsable de ejecutar las gestiones administrativas y comerciales —cambios de titularidad, optimización de tarifas y potencia, reclamos, entre otras— mediantepresencia activa y negociación directa in situcon tres actores clave de la operación:Distribuidorasde servicios públicosInmobiliariasMalls y centros comercialesEn Clickie tenemos una convicción clara:los ahorros significativos no se generan desde un escritorio, se generan en terreno.Cada nudo de gestión que se destraba, cada tarifa que se optimiza y cada reclamo que se resuelve es el resultado directo de estar físicamente presentes, construyendo relación y negociando cara a cara con quienes toman las decisiones del otro lado de la mesa.Si te motiva salir a terreno, tienes carácter para negociar en persona y sabes que los resultados se construyen con presencia y persistencia, este rol es para ti.¿Qué harás?Desplegarte activamente en terreno para gestionar directamente condistribuidoras, inmobiliarias y malls/centros comerciales, construyendo relaciones de confianza que faciliten cada negociación.Analizar información de clientes (ya digitalizada y validada por nuestro equipo de Datos) para identificar oportunidades concretas de ahorro y priorizar tu agenda de gestión en terreno.Ejecutar negociaciones cara a cara e in situ ante compañías proveedoras y actores clave, complementando —cuando corresponda— con llamadas, portales de gestión y comunicaciones formales.Dar seguimiento activo y presencial a cada gestión iniciada hasta su cierre efectivo, destrabando nudos operativos que solo se resuelven con presencia física y persistencia en el lugar.Presentar y gestionar reclamos directamente ante proveedores, inmobiliarias y malls cuando se detecten cobros indebidos o incumplimientos contractuales, escalando la conversación en terreno cuando sea necesario.Validar y reportar el ahorro real generado en cada caso cerrado, dejando trazabilidad de cómo la gestión en terreno se tradujo en resultado económico.Mantener actualizado el estado de cada cliente/caso en nuestros sistemas de gestión.Escalar oportunamente casos complejos o bloqueos regulatorios a la Responsable de UBM, con el contexto directo que solo da estar presente en la operación.Colaborar de cerca con el equipo de Digitalización y Calidad de Datos para resolver inconsistencias que puedan frenar una gestión en terreno.Lo que buscamos en tiExperiencia previa en gestión comercial, administrativa o de trámitescon trabajo de campo/terreno: visitas, negociación presencial, relacionamiento con proveedores, inmobiliarias, administraciones de malls o actores similares.Disposición real y disfrute genuino por el trabajo en terreno: esto no es un rol de oficina, es un rol de presencia activa en la operación.Excelente capacidad de negociación presencial y manejo de objeciones cara a cara.Firmeza, proactividad y capacidad de generar y sostener relaciones con contrapartes clave (distribuidoras, inmobiliarias, malls).Organización y capacidad de gestionar múltiples casos y visitas en paralelo sin perder el detalle de cada uno.Comunicación asertiva, tanto en la negociación in situ como en la redacción formal de reclamos y comunicaciones.Orientación a resultados: te motiva cumplir metas y ver el impacto de tu gestión en terreno reflejado en números concretos de ahorro.Persistencia y buena tolerancia a la frustración — las gestiones con proveedores externos no siempre son rápidas, y saber sostener el seguimiento en terreno sin perder el foco.Disponibilidad para desplazamiento frecuenteManejo de herramientas de gestión/CRM (deseable, no excluyente).Deseable (no excluyente):Conocimiento previo del mercado de servicios públicos (tarifas, actores del sector, regulación).Experiencia previa relacionándote en terreno con distribuidoras, inmobiliarias o administraciones de malls/centros comerciales.Experiencia en roles comerciales o de negociación B2B/B2C con componente presencial.¿Te interesa?Envíanos tu CV a[email protected]</t>
         </is>
       </c>
     </row>
@@ -2423,12 +2419,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ejecutivoa de Gestión y Ahorro UBM</t>
+          <t>Product Onboarding Analyst</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Clickie</t>
+          <t>Keirón</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2438,18 +2434,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55897/ejecutivo-a-de-gestion-y-ahorro-ubm</t>
+          <t>https://firstjob.me/oferta/55893/product-onboarding-analyst</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>sql, informatica, excel</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -2457,10 +2457,10 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2472,11 +2472,11 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>¡Estamos contratando! Ejecutivo/a de Gestión y Ahorro UBMUbicación:PresencialEquipo:Utility Bill Management (UBM)Tipo de contrato:Jornada completaReporta a:Responsable del Servicio de UBMSobre ClickieEn Clickie ayudamos a nuestros clientes a tomar el control de sus servicios públicos, generando ahorros reales y tangibles a través de la gestión inteligente de sus datos y contratos. Somos un equipo que combina tecnología congestión en terreno de alto impacto— y buscamos sumar a alguien que disfrute salir a resolver, negociar y conseguir resultados concretos cara a cara con los actores que hacen posible el ahorro.El rolBuscamos un/aEjecutivo/a de Gestión y Ahorro UBMpara sumarse a nuestro equipo de Utility Bill Management. Este rol es, ante todo, unrol de campo: la persona será responsable de ejecutar las gestiones administrativas y comerciales —cambios de titularidad, optimización de tarifas y potencia, reclamos, entre otras— mediantepresencia activa y negociación directa in situcon tres actores clave de la operación:Distribuidorasde servicios públicosInmobiliariasMalls y centros comercialesEn Clickie tenemos una convicción clara:los ahorros significativos no se generan desde un escritorio, se generan en terreno.Cada nudo de gestión que se destraba, cada tarifa que se optimiza y cada reclamo que se resuelve es el resultado directo de estar físicamente presentes, construyendo relación y negociando cara a cara con quienes toman las decisiones del otro lado de la mesa.Si te motiva salir a terreno, tienes carácter para negociar en persona y sabes que los resultados se construyen con presencia y persistencia, este rol es para ti.¿Qué harás?Desplegarte activamente en terreno para gestionar directamente condistribuidoras, inmobiliarias y malls/centros comerciales, construyendo relaciones de confianza que faciliten cada negociación.Analizar información de clientes (ya digitalizada y validada por nuestro equipo de Datos) para identificar oportunidades concretas de ahorro y priorizar tu agenda de gestión en terreno.Ejecutar negociaciones cara a cara e in situ ante compañías proveedoras y actores clave, complementando —cuando corresponda— con llamadas, portales de gestión y comunicaciones formales.Dar seguimiento activo y presencial a cada gestión iniciada hasta su cierre efectivo, destrabando nudos operativos que solo se resuelven con presencia física y persistencia en el lugar.Presentar y gestionar reclamos directamente ante proveedores, inmobiliarias y malls cuando se detecten cobros indebidos o incumplimientos contractuales, escalando la conversación en terreno cuando sea necesario.Validar y reportar el ahorro real generado en cada caso cerrado, dejando trazabilidad de cómo la gestión en terreno se tradujo en resultado económico.Mantener actualizado el estado de cada cliente/caso en nuestros sistemas de gestión.Escalar oportunamente casos complejos o bloqueos regulatorios a la Responsable de UBM, con el contexto directo que solo da estar presente en la operación.Colaborar de cerca con el equipo de Digitalización y Calidad de Datos para resolver inconsistencias que puedan frenar una gestión en terreno.Lo que buscamos en tiExperiencia previa en gestión comercial, administrativa o de trámitescon trabajo de campo/terreno: visitas, negociación presencial, relacionamiento con proveedores, inmobiliarias, administraciones de malls o actores similares.Disposición real y disfrute genuino por el trabajo en terreno: esto no es un rol de oficina, es un rol de presencia activa en la operación.Excelente capacidad de negociación presencial y manejo de objeciones cara a cara.Firmeza, proactividad y capacidad de generar y sostener relaciones con contrapartes clave (distribuidoras, inmobiliarias, malls).Organización y capacidad de gestionar múltiples casos y visitas en paralelo sin perder el detalle de cada uno.Comunicación asertiva, tanto en la negociación in situ como en la redacción formal de reclamos y comunicaciones.Orientación a resultados: te motiva cumplir metas y ver el impacto de tu gestión en terreno reflejado en números concretos de ahorro.Persistencia y buena tolerancia a la frustración — las gestiones con proveedores externos no siempre son rápidas, y saber sostener el seguimiento en terreno sin perder el foco.Disponibilidad para desplazamiento frecuenteManejo de herramientas de gestión/CRM (deseable, no excluyente).Deseable (no excluyente):Conocimiento previo del mercado de servicios públicos (tarifas, actores del sector, regulación).Experiencia previa relacionándote en terreno con distribuidoras, inmobiliarias o administraciones de malls/centros comerciales.Experiencia en roles comerciales o de negociación B2B/B2C con componente presencial.¿Te interesa?Envíanos tu CV a[email protected]</t>
+          <t>Sobre Keirón 🩺En Keirón trabajamos para que ningún paciente se pierda en el sistema de salud. Somos unaHealthTechlatinoamericana que acompaña a clínicas, hospitales y centros de salud en cada etapa del viaje del paciente, desde que agenda una hora hasta que resuelve su problema de salud, reduciendo esperas, errores y desgaste tanto para los pacientes como para los equipos clínicos.Con presencia en Chile, México, Colombia y Perú, y millones de atenciones coordinadas a través de nuestra plataforma. Detrás de cada mejora en un proceso hay algo muy concreto: menos tiempo de espera, más claridad para un paciente, y un equipo clínico que puede enfocarse en dar la mejor atención.Nuestro equipo de OnboardingEn Onboarding traducimos el producto en una implementación exitosa: levantamos los flujos de cada cliente, los configuramos en la plataforma y validamos que funcionen en la operación real.En el equipo estamos buscando a nuestr@ siguienteProduct Onboarding Analyst:  alguien organizado/a, con mirada de proceso completo, cómodo/a manejando varios proyectos en paralelo y conversando tanto con clientes como con equipos de Producto y Tecnología, y con ojo analítico para detectar mejoras y automatizar procesos 🚀.¿Qué tendrás que hacer? 👀Levantar y modelarflujos operativos de nuevos clientes, configurándolos y adaptándolos correctamente en la plataforma.Diseñar y ejecutarel proceso de onboarding end-to-end, asegurando una implementación correcta y oportuna (levantamiento, configuración y capacitación).Detectar, documentar y escalarincidencias y oportunidades de mejora, tanto de implementación como de producto.Comunicaraprendizajes y feedback de clientes hacia los equipos de Producto y Tecnología, contribuyendo a la evolución del producto.Analizar, estandarizar y automatizarinformación y procesos de onboarding, proponiendo mejoras continuas en eficiencia y adopción.Habilidades técnicas deseadas ✨Conocimientos básicos en bases de datos (PostgreSQL, MySQL o similares).Capacidad para realizar consultas SQL simples (SELECT, JOIN, filtros, validaciones).Manejo intermedio de Excel / Google Sheets (tablas dinámicas, fórmulas, filtros).Deseable familiaridad con herramientas de gestión de proyectos y CRM (Jira, HubSpot u otras).Deseable conocimiento en APIs, Webhooks e integraciones con sistemas externos (CRM, ERP, etc.) o interés en aprender y profundizar en estos conceptos.¿Qué esperamos de ti?Formación en Ingeniería Industrial, Informática, Gestión de Proyectos TI o carreras afines (a partir de 1 año de experiencia en roles similares).Deseable experiencia previa enstartupsoentornos de rápido crecimiento.Habilidades decomunicación efectiva,con foco en interacción con clientes y equipos internos.Capacidad deorganización, planificación y gestión del tiempopara manejar múltiples onboardings en paralelo.Perfil analíticoy orientado al detalle, con capacidad para detectar incidencias y oportunidades de mejora.Proactividadyautonomíapara ejecutar tareas y dar seguimiento.Capacidad para trabajarcolaborativamentecon equipos de Producto, Tecnología y Customer Success.BeneficiosAl pasar a contrato indefinido podrás acceder a:Seguro complementario de saludHerramienta de trabajo7 viernes libres al añoMedio día de cumpleaños (más otros detallitos)3 primeros días de licencia pagadosCultura de innovación, impacto y colaboración</t>
         </is>
       </c>
     </row>
@@ -2488,12 +2488,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Product Onboarding Analyst</t>
+          <t>Analista de Normas y Análisis Financiero</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Keirón</t>
+          <t>BICE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2508,15 +2508,15 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55893/product-onboarding-analyst</t>
+          <t>https://firstjob.me/oferta/55886/analista-de-normas-y-analisis-financiero</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>sql, informatica, excel</t>
+          <t>analisis</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2529,7 +2529,7 @@
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2541,61 +2541,61 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>Sobre Keirón 🩺En Keirón trabajamos para que ningún paciente se pierda en el sistema de salud. Somos unaHealthTechlatinoamericana que acompaña a clínicas, hospitales y centros de salud en cada etapa del viaje del paciente, desde que agenda una hora hasta que resuelve su problema de salud, reduciendo esperas, errores y desgaste tanto para los pacientes como para los equipos clínicos.Con presencia en Chile, México, Colombia y Perú, y millones de atenciones coordinadas a través de nuestra plataforma. Detrás de cada mejora en un proceso hay algo muy concreto: menos tiempo de espera, más claridad para un paciente, y un equipo clínico que puede enfocarse en dar la mejor atención.Nuestro equipo de OnboardingEn Onboarding traducimos el producto en una implementación exitosa: levantamos los flujos de cada cliente, los configuramos en la plataforma y validamos que funcionen en la operación real.En el equipo estamos buscando a nuestr@ siguienteProduct Onboarding Analyst:  alguien organizado/a, con mirada de proceso completo, cómodo/a manejando varios proyectos en paralelo y conversando tanto con clientes como con equipos de Producto y Tecnología, y con ojo analítico para detectar mejoras y automatizar procesos 🚀.¿Qué tendrás que hacer? 👀Levantar y modelarflujos operativos de nuevos clientes, configurándolos y adaptándolos correctamente en la plataforma.Diseñar y ejecutarel proceso de onboarding end-to-end, asegurando una implementación correcta y oportuna (levantamiento, configuración y capacitación).Detectar, documentar y escalarincidencias y oportunidades de mejora, tanto de implementación como de producto.Comunicaraprendizajes y feedback de clientes hacia los equipos de Producto y Tecnología, contribuyendo a la evolución del producto.Analizar, estandarizar y automatizarinformación y procesos de onboarding, proponiendo mejoras continuas en eficiencia y adopción.Habilidades técnicas deseadas ✨Conocimientos básicos en bases de datos (PostgreSQL, MySQL o similares).Capacidad para realizar consultas SQL simples (SELECT, JOIN, filtros, validaciones).Manejo intermedio de Excel / Google Sheets (tablas dinámicas, fórmulas, filtros).Deseable familiaridad con herramientas de gestión de proyectos y CRM (Jira, HubSpot u otras).Deseable conocimiento en APIs, Webhooks e integraciones con sistemas externos (CRM, ERP, etc.) o interés en aprender y profundizar en estos conceptos.¿Qué esperamos de ti?Formación en Ingeniería Industrial, Informática, Gestión de Proyectos TI o carreras afines (a partir de 1 año de experiencia en roles similares).Deseable experiencia previa enstartupsoentornos de rápido crecimiento.Habilidades decomunicación efectiva,con foco en interacción con clientes y equipos internos.Capacidad deorganización, planificación y gestión del tiempopara manejar múltiples onboardings en paralelo.Perfil analíticoy orientado al detalle, con capacidad para detectar incidencias y oportunidades de mejora.Proactividadyautonomíapara ejecutar tareas y dar seguimiento.Capacidad para trabajarcolaborativamentecon equipos de Producto, Tecnología y Customer Success.BeneficiosAl pasar a contrato indefinido podrás acceder a:Seguro complementario de saludHerramienta de trabajo7 viernes libres al añoMedio día de cumpleaños (más otros detallitos)3 primeros días de licencia pagadosCultura de innovación, impacto y colaboración</t>
+          <t>¡En BICE te estamos buscando!Creemos firmemente que los colaboradores son nuestro principal activo. Por eso, nos preocupamos de ofrecer oportunidades que potencien su desarrollo integral. Apostamos por profesionales apasionados, innovadores, creativos y con ganas de aprender y crecer.¿Nuestro propósito? Impulsamos tu bienestar creando una experiencia financiera única con sello humano.Te invitamos a ser parte de BICE, donde buscamos a un Analista de Normas y Análisis Financiero para nuestra División de Planificación y Control Financiero.¿Cuáles serán tus principales responsabilidades?Elaborar explicaciones “de negocio” para las principales variaciones de los EEFF, tanto a nivel mensual, trimestral y anual.Comprender y explicar los efectos de mercado (inflación, alzas y bajas de tasas de interés, variaciones del valor razonable de instrumentos financieros, etc).Elaborar presentaciones ejecutivas a requerimiento específicos sobre temas propios del área.Realizar exposiciones internas a la Gerencia de Contabilidad.Analizar y estudiar la estrategia de fondeo e inversión del Banco y sus impactos contables.Apoyar la revisión de EEFF trimestrales y anuales.Elaborar documentos técnicos a requerimiento de la jefatura.¿Qué buscamos?Título de Contador auditor o Ingeniero Comercial, deseable especialización en finanzas corporativas.Ideal experiencia de 1 a 2 años en cargos similares dentro de la industria bancaria (también podría ser recién titulado).Ideal conocimientos en norma IFRS, CMF y del BCCh (deseable).Ideal conocimientos sobre regulación de la industria bancaria como por ejemplo Recopilación Actualizada de Normas, Compendio de Normas Contables para bancos, Basilea III, entre otros. (excluyente)Ideal conocimientos sobre valoración de instrumentos financieros y finanzas corporativas (deseable).Capacidad analítica, trabajo en equipo y bajo presión.Orientación al cumplimiento de tareas y logro de objetivos.Conocimiento SAP (deseable).Postula con nosotros!!Beneficios🏢 Modalidad de trabajo según rol: Algunas posiciones acceden a un sistema híbrido, mientras que las áreas comerciales operan 100% de forma presencial.🍽️ Almuerzo diario cubierto: Si trabajas en casa matriz, accedes al casino corporativo con almuerzo gratuito. Si estás en una sucursal, se te asigna un monto diario para cubrir este gasto.🛍️ Descuentos exclusivos y convenios: Acceso a beneficios con diversas empresas asociadas en áreas como salud, retail, entretenimiento y más.⚽ Actividades internas: Participación en torneos deportivos, actividades lúdicas, operativos oftalmológicos y otras instancias que promueven el bienestar.🤝 Cultura cercana y participativa: Ser parte activa de un entorno laboral colaborativo, donde se vive la cultura organizacional día a día.🩺 Seguros complementarios: Cobertura en salud, dental y de vida, para que cuentes con mayor respaldo y tranquilidad.🐾 Seguro para mascotas: Protección adicional para tus compañeros de cuatro patas.🏋️ Convenio con gimnasios: Accede a tarifas preferenciales para mantenerte activo y saludable.🎓 Formación continua: Convenios y descuentos con instituciones educativas para diplomados, cursos y otros programas de desarrollo profesional.🚲 Acceso a bicicletero: Estacionamiento seguro para bicicletas en casa matriz.🅿️ Convenio de estacionamientos: Tarifas preferenciales en estacionamientos cercanos.📱 Convenio con Entel: Descuentos en planes y equipos móviles.🦷 Red de centros odontológicos: Acceso a múltiples convenios para atención dental.🎁 Bonos diversos: Incluye bonos por escolaridad, fallecimiento, vacaciones, invierno, excelencia académica, aguinaldos de Fiestas Patrias y Navidad, entre otros.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Analista de Normas y Análisis Financiero</t>
+          <t>Ingeniero BI Tecnología Minera</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BICE</t>
+          <t>Ferreyros</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Lima, Perú</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55886/analista-de-normas-y-analisis-financiero</t>
+          <t>https://firstjob.me/oferta/55911/ingeniero-bi-tecnologia-minera</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>analisis</t>
+          <t>python, sql, estadistica, cloud, gcp</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
@@ -2614,7 +2614,7 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>¡En BICE te estamos buscando!Creemos firmemente que los colaboradores son nuestro principal activo. Por eso, nos preocupamos de ofrecer oportunidades que potencien su desarrollo integral. Apostamos por profesionales apasionados, innovadores, creativos y con ganas de aprender y crecer.¿Nuestro propósito? Impulsamos tu bienestar creando una experiencia financiera única con sello humano.Te invitamos a ser parte de BICE, donde buscamos a un Analista de Normas y Análisis Financiero para nuestra División de Planificación y Control Financiero.¿Cuáles serán tus principales responsabilidades?Elaborar explicaciones “de negocio” para las principales variaciones de los EEFF, tanto a nivel mensual, trimestral y anual.Comprender y explicar los efectos de mercado (inflación, alzas y bajas de tasas de interés, variaciones del valor razonable de instrumentos financieros, etc).Elaborar presentaciones ejecutivas a requerimiento específicos sobre temas propios del área.Realizar exposiciones internas a la Gerencia de Contabilidad.Analizar y estudiar la estrategia de fondeo e inversión del Banco y sus impactos contables.Apoyar la revisión de EEFF trimestrales y anuales.Elaborar documentos técnicos a requerimiento de la jefatura.¿Qué buscamos?Título de Contador auditor o Ingeniero Comercial, deseable especialización en finanzas corporativas.Ideal experiencia de 1 a 2 años en cargos similares dentro de la industria bancaria (también podría ser recién titulado).Ideal conocimientos en norma IFRS, CMF y del BCCh (deseable).Ideal conocimientos sobre regulación de la industria bancaria como por ejemplo Recopilación Actualizada de Normas, Compendio de Normas Contables para bancos, Basilea III, entre otros. (excluyente)Ideal conocimientos sobre valoración de instrumentos financieros y finanzas corporativas (deseable).Capacidad analítica, trabajo en equipo y bajo presión.Orientación al cumplimiento de tareas y logro de objetivos.Conocimiento SAP (deseable).Postula con nosotros!!Beneficios🏢 Modalidad de trabajo según rol: Algunas posiciones acceden a un sistema híbrido, mientras que las áreas comerciales operan 100% de forma presencial.🍽️ Almuerzo diario cubierto: Si trabajas en casa matriz, accedes al casino corporativo con almuerzo gratuito. Si estás en una sucursal, se te asigna un monto diario para cubrir este gasto.🛍️ Descuentos exclusivos y convenios: Acceso a beneficios con diversas empresas asociadas en áreas como salud, retail, entretenimiento y más.⚽ Actividades internas: Participación en torneos deportivos, actividades lúdicas, operativos oftalmológicos y otras instancias que promueven el bienestar.🤝 Cultura cercana y participativa: Ser parte activa de un entorno laboral colaborativo, donde se vive la cultura organizacional día a día.🩺 Seguros complementarios: Cobertura en salud, dental y de vida, para que cuentes con mayor respaldo y tranquilidad.🐾 Seguro para mascotas: Protección adicional para tus compañeros de cuatro patas.🏋️ Convenio con gimnasios: Accede a tarifas preferenciales para mantenerte activo y saludable.🎓 Formación continua: Convenios y descuentos con instituciones educativas para diplomados, cursos y otros programas de desarrollo profesional.🚲 Acceso a bicicletero: Estacionamiento seguro para bicicletas en casa matriz.🅿️ Convenio de estacionamientos: Tarifas preferenciales en estacionamientos cercanos.📱 Convenio con Entel: Descuentos en planes y equipos móviles.🦷 Red de centros odontológicos: Acceso a múltiples convenios para atención dental.🎁 Bonos diversos: Incluye bonos por escolaridad, fallecimiento, vacaciones, invierno, excelencia académica, aguinaldos de Fiestas Patrias y Navidad, entre otros.</t>
+          <t>Misión del puestoEjecutar actividades de implementación y soporte a los procesos de flujos y entrega de datos operacionales para facilitar la toma de decisiones, mediante el trabajo coordinado con las áreas operativas y de desarrollo, asegurando siempre los estándares técnicos de la organización.FuncionesGestión de Datos Operacionales: Limpieza, integración y contextualización de datos de campo para garantizar información confiable a Ferreyros y sus clientes.Modelado y Visualización: Analizar la lógica de negocio para implementar flujos de datos y dashboards bajo estándares de la empresa.Diseño y Soporte: Apoyar en el diseño de soluciones de datos, brindando soporte preventivo y correctivo a las herramientas desplegadas para asegurar la continuidad operativa.Capacitación y Adopción: Asistir en la creación y ejecución de capacitaciones técnicas para usuarios finales.Cumplir con la normativa legal y estándares internos en materia de SSMA (Seguridad, Salud y Medio Ambiente).RequisitosBachiller o Titulado/a en Ing. Electrónica, Mecatrónica, Sistemas, Industrial, Minas, Estadística o carreras afines.2 años de experiencia de laboral.Dominio Técnico Sólido en Python para Data Engineering, SQL avanzado y  Power BI u otras herramientas de visualización de Business Intelligence.Conocimiento de Google Cloud Platform (GCP) orientado a arquitectura e integración de datos.Manejo de Inglés (intermedio/avanzado).Disponibilidad para laborar de forma presencial en Cercado de Lima.</t>
         </is>
       </c>
     </row>
@@ -2626,17 +2626,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ingeniero BI Tecnología Minera</t>
+          <t>GESTOR COMERCIAL BANCA EMPRESAS I PER</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ferreyros</t>
+          <t>BBVA Perú</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Lima, Perú</t>
+          <t>Huancayo, Perú</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2646,15 +2646,15 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55911/ingeniero-bi-tecnologia-minera</t>
+          <t>https://firstjob.me/oferta/55910/gestor-comercial-banca-empresas-i-per</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>python, sql, estadistica, cloud, gcp</t>
+          <t>analisis, excel</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>Misión del puestoEjecutar actividades de implementación y soporte a los procesos de flujos y entrega de datos operacionales para facilitar la toma de decisiones, mediante el trabajo coordinado con las áreas operativas y de desarrollo, asegurando siempre los estándares técnicos de la organización.FuncionesGestión de Datos Operacionales: Limpieza, integración y contextualización de datos de campo para garantizar información confiable a Ferreyros y sus clientes.Modelado y Visualización: Analizar la lógica de negocio para implementar flujos de datos y dashboards bajo estándares de la empresa.Diseño y Soporte: Apoyar en el diseño de soluciones de datos, brindando soporte preventivo y correctivo a las herramientas desplegadas para asegurar la continuidad operativa.Capacitación y Adopción: Asistir en la creación y ejecución de capacitaciones técnicas para usuarios finales.Cumplir con la normativa legal y estándares internos en materia de SSMA (Seguridad, Salud y Medio Ambiente).RequisitosBachiller o Titulado/a en Ing. Electrónica, Mecatrónica, Sistemas, Industrial, Minas, Estadística o carreras afines.2 años de experiencia de laboral.Dominio Técnico Sólido en Python para Data Engineering, SQL avanzado y  Power BI u otras herramientas de visualización de Business Intelligence.Conocimiento de Google Cloud Platform (GCP) orientado a arquitectura e integración de datos.Manejo de Inglés (intermedio/avanzado).Disponibilidad para laborar de forma presencial en Cercado de Lima.</t>
+          <t>¿Quieres desarrollar tu carrera profesional?BBVA es una empresa global con más de 160 años de historia que opera en más de 25 países en los que damos servicio a más de 80 millones de clientes. Somos más de 121.000 profesionales que trabajamos en equipos multidisciplinares y de perfiles tan diversos como financieros, expertos jurídicos, científicos de datos, desarrolladores, ingenieros o diseñadores.Nuestra gente marca la diferencia en nuestro éxito.Tipo de Contrato:Regular (Indefinido)¿Qué estamos buscando?Lo que harás:Solicitar información actualizada de los balances, estados de pérdidas y ganancias, conformación de la empresa, accionistas, ejecutivos, y otros documentos a los clientes para la posterior evaluación de riesgos.Obtener información sobre la competencia, proveedores, formas de pago, créditos, etc.Efectuar el análisis del mercado, proyecciones, comportamiento productivo, ventas, créditos otorgados, etc.Efectuar el análisis de su posición en el sistema financiero, responsabilidad con el Banco, etc.Presentar al Ejecutivo de Cuenta el Programa Financiero preliminar, para su respectivo contraste.Gestión de firmas y poderes para la apertura de cuentas corrientes de personas jurídicas.Mantener actualizado y en orden el file comercial, contactos y base de datos.Gestionar y hacer seguimiento de la evolución de tarifas preferenciales (tasas y comisiones).Apoyo en el análisis de oportunidades y gestión del portafolio de clientes del segmento Banca Empresa y Corporativa.Otras funciones asignadas por su jefe inmediato.Requisitos:Nivel de Estudios: Egresado o Bachiller en Administración, Ingeniería Industrial, Ingeniería de Sistemas, Economía o afines.Experiencia previa como analista comercial en los rubros de banca, financieras o afines.MS Excel (avanzado), MS Visio y MS Word (Intermedio), MS Access, MS Power Point y MS Project (Básico).Ingles: Avanzado (no indispensable)Competencias: Orientación al cliente, comunicación asertiva, proactividad y dinamismo.</t>
         </is>
       </c>
     </row>
@@ -2695,17 +2695,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GESTOR COMERCIAL BANCA EMPRESAS I PER</t>
+          <t>Analista de Datos de Desarrollo del Emprendedor</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BBVA Perú</t>
+          <t>Mibanco</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Huancayo, Perú</t>
+          <t>Lima, Perú</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2715,25 +2715,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55910/gestor-comercial-banca-empresas-i-per</t>
+          <t>https://firstjob.me/oferta/55909/analista-de-datos-de-desarrollo-del-emprendedor</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>analisis, excel</t>
+          <t>python, sql, analisis, excel, power bi</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>1</v>
@@ -2742,7 +2742,7 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>¿Quieres desarrollar tu carrera profesional?BBVA es una empresa global con más de 160 años de historia que opera en más de 25 países en los que damos servicio a más de 80 millones de clientes. Somos más de 121.000 profesionales que trabajamos en equipos multidisciplinares y de perfiles tan diversos como financieros, expertos jurídicos, científicos de datos, desarrolladores, ingenieros o diseñadores.Nuestra gente marca la diferencia en nuestro éxito.Tipo de Contrato:Regular (Indefinido)¿Qué estamos buscando?Lo que harás:Solicitar información actualizada de los balances, estados de pérdidas y ganancias, conformación de la empresa, accionistas, ejecutivos, y otros documentos a los clientes para la posterior evaluación de riesgos.Obtener información sobre la competencia, proveedores, formas de pago, créditos, etc.Efectuar el análisis del mercado, proyecciones, comportamiento productivo, ventas, créditos otorgados, etc.Efectuar el análisis de su posición en el sistema financiero, responsabilidad con el Banco, etc.Presentar al Ejecutivo de Cuenta el Programa Financiero preliminar, para su respectivo contraste.Gestión de firmas y poderes para la apertura de cuentas corrientes de personas jurídicas.Mantener actualizado y en orden el file comercial, contactos y base de datos.Gestionar y hacer seguimiento de la evolución de tarifas preferenciales (tasas y comisiones).Apoyo en el análisis de oportunidades y gestión del portafolio de clientes del segmento Banca Empresa y Corporativa.Otras funciones asignadas por su jefe inmediato.Requisitos:Nivel de Estudios: Egresado o Bachiller en Administración, Ingeniería Industrial, Ingeniería de Sistemas, Economía o afines.Experiencia previa como analista comercial en los rubros de banca, financieras o afines.MS Excel (avanzado), MS Visio y MS Word (Intermedio), MS Access, MS Power Point y MS Project (Básico).Ingles: Avanzado (no indispensable)Competencias: Orientación al cliente, comunicación asertiva, proactividad y dinamismo.</t>
+          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAnalista de Datos de Desarrollo del Emprendedor.¿Cuáles serían tus principales responsabilidades?Organizar, recopilar y gestionar la información de los distintos canales y su consolidación en un solo repositorio.Analizar los indicadores de performance de cada canal de difusión de contenidos en cada etapa del funnel.Elaborar reportería que ayude a medir alcance, impacto y satisfacción de los canales y contenido.Proponer mejoras o nuevas iniciativas en función al análisis de la información.Identificar la correlación de la capacitación y su impacto en el negocio.Generar reportería y rankings continuos para la red de agencia.Perfilar a los clientes que reciben los programa por cada canal.Proporcionar información de los clientes que son captados a través de las alianzas.¿Qué necesitamos?Bachiller en Administración, Economía, Ingeniería industrial o afines.Estudios de postgrado Gestión de proyectos, Análisis de datos, Metodologías ágiles, Innovación (deseable no excluyente).01 año de experiencia en la gestión de información y análisis de datos (incluyendo prácticas).Experiencia en elaboración de análisis predictivos, dashboards y reportería.Conocimiento de indicadores de medición de plataformas digitales (intermedio).Excel avanzado (Tablas Dinámicas, macros no excluyentes).Power BI (Dashboards intermedio).SQL/PL-SQL (intermedio).Python básico (deseable).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
         </is>
       </c>
     </row>
@@ -2764,35 +2764,35 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Analista de Datos de Desarrollo del Emprendedor</t>
+          <t>Asistente TAX Compliance</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mibanco</t>
+          <t>Forvis Mazars</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Lima, Perú</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55909/analista-de-datos-de-desarrollo-del-emprendedor</t>
+          <t>https://firstjob.me/oferta/55922/asistente-tax-compliance</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>python, sql, analisis, excel, power bi</t>
+          <t>analisis, excel</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2805,13 +2805,13 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAnalista de Datos de Desarrollo del Emprendedor.¿Cuáles serían tus principales responsabilidades?Organizar, recopilar y gestionar la información de los distintos canales y su consolidación en un solo repositorio.Analizar los indicadores de performance de cada canal de difusión de contenidos en cada etapa del funnel.Elaborar reportería que ayude a medir alcance, impacto y satisfacción de los canales y contenido.Proponer mejoras o nuevas iniciativas en función al análisis de la información.Identificar la correlación de la capacitación y su impacto en el negocio.Generar reportería y rankings continuos para la red de agencia.Perfilar a los clientes que reciben los programa por cada canal.Proporcionar información de los clientes que son captados a través de las alianzas.¿Qué necesitamos?Bachiller en Administración, Economía, Ingeniería industrial o afines.Estudios de postgrado Gestión de proyectos, Análisis de datos, Metodologías ágiles, Innovación (deseable no excluyente).01 año de experiencia en la gestión de información y análisis de datos (incluyendo prácticas).Experiencia en elaboración de análisis predictivos, dashboards y reportería.Conocimiento de indicadores de medición de plataformas digitales (intermedio).Excel avanzado (Tablas Dinámicas, macros no excluyentes).Power BI (Dashboards intermedio).SQL/PL-SQL (intermedio).Python básico (deseable).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
+          <t>Acerca del empleoCon nosotros tienes la oportunidad de pertenecer a una firma internacional con un importante potencial de crecimiento y un equipo de más de 40.000 profesionales altamente capacitados, que brinda servicios profesionales generando alto impacto en todos nuestros clientes en más de 100 países en los cinco continentes.Podrás formar parte de un equipo que valorará tus ideas, apoyará tus ambiciones y celebrará tus éxitos. En Forvis Mazars nos proponemos impulsar la colaboración y la flexibilidad, las diversas perspectivas de nuestros colaboradores y el progreso.Hoy nuestro equipo de TAX Compliance está buscando un (a) Asistente, el cual tiene como principal objetivo apoyar la correcta gestión y cumplimiento de las obligaciones tributarias de las empresas en su cartera asignada, asegurando la precisión, oportunidad y veracidad en los procesos de declaración y presentación de impuestos, así como el resguardo del cumplimiento normativo vigente.Principales ResponsabilidadesPreparar y recopilar la documentación necesaria para la presentación de declaraciones de impuestos mensuales y anuales.Colaborar en la revisión y análisis de los registros contables relacionados con impuestos, verificando su correcta imputación y clasificación.Apoyar en la elaboración de informes tributarios y reportes solicitados por su jefatura.Realizar seguimiento a las actualizaciones normativas y cambios en la legislación tributaria que puedan afectar a la empresa.Gestionar la comunicación y coordinación con entidades externas, como el Servicio de Impuestos Internos (SII) y asesores fiscales.Mantener actualizada la documentación y archivos vinculados a los procesos de TAX Compliances.Perfil RequeridoTítulo universitario en Contabilidad, Auditoría, Administración o carrera afín.Experiencia de 1 año lo menos en cargos similares o en áreas de cumplimiento tributario.Conocimiento actualizado de la normativa tributaria chilena y manejo de plataformas digitales del SII.Manejo de herramientas ofimáticas, especialmente Excel.Capacidad analítica, organización, atención al detalle y orientación al cumplimiento de plazos.Habilidades de comunicación y trabajo en equipo.Este cargo es compatible para personas con discapacidad, se enmarca en la ley 21.015, que incentiva la inclusión de personas con discapacidad al mundo laboral.BeneficiosOfrecemosPaquete de compensaciones de mercadoSeguro Complementarios de salud y Dental, además de seguro de VidaUna experiencia dinámica, diversa e inclusiva, en una Firma con orientación en las personas, desarrollo y crecimientoEducación continua, tanto de programas internos, corporativos y externosDías adicionales de vacaciones.</t>
         </is>
       </c>
     </row>
@@ -2833,35 +2833,35 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Asistente TAX Compliance</t>
+          <t>Analista Experto área de Rezagos Gerencia de Operaciones</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Forvis Mazars</t>
+          <t>AFP Modelo</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Avda de valle 614 Huechuraba, Chile, Chile</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55922/asistente-tax-compliance</t>
+          <t>https://firstjob.me/oferta/55914/analista-experto-area-de-rezagos-gerencia-de-operaciones</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>analisis, excel</t>
+          <t>sql, excel</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2871,10 +2871,10 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>Acerca del empleoCon nosotros tienes la oportunidad de pertenecer a una firma internacional con un importante potencial de crecimiento y un equipo de más de 40.000 profesionales altamente capacitados, que brinda servicios profesionales generando alto impacto en todos nuestros clientes en más de 100 países en los cinco continentes.Podrás formar parte de un equipo que valorará tus ideas, apoyará tus ambiciones y celebrará tus éxitos. En Forvis Mazars nos proponemos impulsar la colaboración y la flexibilidad, las diversas perspectivas de nuestros colaboradores y el progreso.Hoy nuestro equipo de TAX Compliance está buscando un (a) Asistente, el cual tiene como principal objetivo apoyar la correcta gestión y cumplimiento de las obligaciones tributarias de las empresas en su cartera asignada, asegurando la precisión, oportunidad y veracidad en los procesos de declaración y presentación de impuestos, así como el resguardo del cumplimiento normativo vigente.Principales ResponsabilidadesPreparar y recopilar la documentación necesaria para la presentación de declaraciones de impuestos mensuales y anuales.Colaborar en la revisión y análisis de los registros contables relacionados con impuestos, verificando su correcta imputación y clasificación.Apoyar en la elaboración de informes tributarios y reportes solicitados por su jefatura.Realizar seguimiento a las actualizaciones normativas y cambios en la legislación tributaria que puedan afectar a la empresa.Gestionar la comunicación y coordinación con entidades externas, como el Servicio de Impuestos Internos (SII) y asesores fiscales.Mantener actualizada la documentación y archivos vinculados a los procesos de TAX Compliances.Perfil RequeridoTítulo universitario en Contabilidad, Auditoría, Administración o carrera afín.Experiencia de 1 año lo menos en cargos similares o en áreas de cumplimiento tributario.Conocimiento actualizado de la normativa tributaria chilena y manejo de plataformas digitales del SII.Manejo de herramientas ofimáticas, especialmente Excel.Capacidad analítica, organización, atención al detalle y orientación al cumplimiento de plazos.Habilidades de comunicación y trabajo en equipo.Este cargo es compatible para personas con discapacidad, se enmarca en la ley 21.015, que incentiva la inclusión de personas con discapacidad al mundo laboral.BeneficiosOfrecemosPaquete de compensaciones de mercadoSeguro Complementarios de salud y Dental, además de seguro de VidaUna experiencia dinámica, diversa e inclusiva, en una Firma con orientación en las personas, desarrollo y crecimientoEducación continua, tanto de programas internos, corporativos y externosDías adicionales de vacaciones.</t>
+          <t>¿Quiénes somos?Somos una AFP orientada a las personas, comprometida con su bienestar presente y futuro. Destacamos que, en línea con nuestra cultura organizacional, nuestras búsquedas se enmarcan bajo la ley 21.015, la cual promueve la inclusión laboral de las personas con discapacidad.¿Quieres sumarte a cientos de profesionales que buscan contribuir con entusiasmo y responsabilidad al bienestar de las personas? ¡Esta es tu oportunidad!¿Cuáles serán los desafíos del cargo?Ejecutar los procesos necesarios del área de rezagos, a fin, de aportar a la gestión operacional de la misma, teniendo una visión crítica de los procesos que maneja, ideando e implementando soluciones orientadas a la mejora continua siempre de acuerdo a los protocolos y procedimientos vigentes, así como también políticas externas relacionadas al rubro, con el fin de dar cumplimiento al plan de operaciones, a la normativa vigente y a los estándares de servicio al cliente establecidos.¿Qué buscamos?Formación Académica: Egresado o Titulado de carrera Profesional o Técnico de carreras de ingenierías, administración, finanzas, marketing y demás carreras afines.Conocimientos técnicos:Manejo de Excel avanzado, SQL intermedio.Experiencia mínima/deseable: 1 año de experiencia en cargos similares.BeneficiosBus de acercamientoDía de CumpleañosSeguro complementarioy muchos beneficios más¡Te esperamos!</t>
         </is>
       </c>
     </row>
@@ -2902,35 +2902,35 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Analista Experto área de Rezagos Gerencia de Operaciones</t>
+          <t>Práctica Profesional - Gerencia Analytics y BI - Data Science</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AFP Modelo</t>
+          <t>Ripley chile</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Avda de valle 614 Huechuraba, Chile, Chile</t>
+          <t>Ofi. Alonso De Cordova 5320 - Producto Financiero, Chile</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55914/analista-experto-area-de-rezagos-gerencia-de-operaciones</t>
+          <t>https://firstjob.me/oferta/55913/practica-profesional-gerencia-analytics-y-bi-data-science</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>sql, excel</t>
+          <t>python, sql, machine learning, estadistica, informatica, cloud, aws</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2940,26 +2940,26 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>¿Quiénes somos?Somos una AFP orientada a las personas, comprometida con su bienestar presente y futuro. Destacamos que, en línea con nuestra cultura organizacional, nuestras búsquedas se enmarcan bajo la ley 21.015, la cual promueve la inclusión laboral de las personas con discapacidad.¿Quieres sumarte a cientos de profesionales que buscan contribuir con entusiasmo y responsabilidad al bienestar de las personas? ¡Esta es tu oportunidad!¿Cuáles serán los desafíos del cargo?Ejecutar los procesos necesarios del área de rezagos, a fin, de aportar a la gestión operacional de la misma, teniendo una visión crítica de los procesos que maneja, ideando e implementando soluciones orientadas a la mejora continua siempre de acuerdo a los protocolos y procedimientos vigentes, así como también políticas externas relacionadas al rubro, con el fin de dar cumplimiento al plan de operaciones, a la normativa vigente y a los estándares de servicio al cliente establecidos.¿Qué buscamos?Formación Académica: Egresado o Titulado de carrera Profesional o Técnico de carreras de ingenierías, administración, finanzas, marketing y demás carreras afines.Conocimientos técnicos:Manejo de Excel avanzado, SQL intermedio.Experiencia mínima/deseable: 1 año de experiencia en cargos similares.BeneficiosBus de acercamientoDía de CumpleañosSeguro complementarioy muchos beneficios más¡Te esperamos!</t>
+          <t>🚀 ¡Buscamos a nuestro/a próximo/a Practicante de Analítica y Automatización para la Gerencia de Analytics y BI en Banco Ripley! 💜Si estás buscando un lugar donde puedas aprender, desarrollar tus habilidades técnicas y participar en proyectos con impacto real en el negocio, llegaste al lugar indicado. En Banco Ripley te integrarás a un equipo dinámico, donde los datos, la innovación y la mejora continua son parte del día a día.Ser parte de Banco Ripley es vivir una cultura que impulsa el desarrollo, la colaboración y el aprendizaje constante, en un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te apasiona la programación, la analítica de datos y la automatización de procesos? ¿Te gustaría trabajar con modelos analíticos y contribuir a hacer más eficientes los procesos del negocio? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Apoyar la ejecución, monitoreo y optimización de los procesos analíticos de la gerencia, participando en el diseño e implementación de soluciones que permitan automatizar, calendarizar y mejorar los flujos de trabajo actuales, contribuyendo a una operación más eficiente y escalable.Funciones: 🤩• Ejecutar y monitorear los procesos analíticos vigentes para asegurar la continuidad operacional.• Garantizar la entrega oportuna de información y resultados generados por los procesos actuales.• Identificar oportunidades de automatización y mejora en procesos manuales.• Diseñar e implementar soluciones para automatizar y calendarizar procesos analíticos.• Revisar y optimizar el código de modelos analíticos, proponiendo mejoras en su estructura y eficiencia.• Validar el desempeño de modelos y procedimientos almacenados (Stored Procedures) en entornos AWS.• Colaborar en iniciativas de mejora continua que fortalezcan la eficiencia de los procesos del área.¿Qué estamos buscando? 💡• Estudiante de Ingeniería Civil, Ingeniería Informática, Ingeniería Industrial, Estadística, Ciencia de Datos o carrera afín.• Contar con seguro escolar vigente otorgado por la casa de estudios. (Excluyente).• Disponibilidad inmediata para realizar la práctica.• Conocimientos de programación en Python, R y SQL.• Conocimientos en estadística, machine learning y técnicas de clusterización.• Deseable conocimiento de entornos cloud, especialmente AWS SageMaker.• Interés por la analítica, la automatización de procesos y la optimización continua.• Capacidad analítica, proactividad y ganas de aprender en un entorno desafiante.¿Por qué trabajar en Banco Ripley? 💜Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo. 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y, si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
         </is>
       </c>
     </row>
@@ -2971,35 +2971,35 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Práctica Profesional - Gerencia Analytics y BI - Data Science</t>
+          <t>Profesional de Proyectos de Packaging</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ripley chile</t>
+          <t>Difem Laboratorios S.A.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ofi. Alonso De Cordova 5320 - Producto Financiero, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55913/practica-profesional-gerencia-analytics-y-bi-data-science</t>
+          <t>https://firstjob.me/oferta/55908/profesional-de-proyectos-de-packaging</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>python, sql, machine learning, estadistica, informatica, cloud, aws</t>
+          <t>analisis, excel, power bi</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -3009,26 +3009,26 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>🚀 ¡Buscamos a nuestro/a próximo/a Practicante de Analítica y Automatización para la Gerencia de Analytics y BI en Banco Ripley! 💜Si estás buscando un lugar donde puedas aprender, desarrollar tus habilidades técnicas y participar en proyectos con impacto real en el negocio, llegaste al lugar indicado. En Banco Ripley te integrarás a un equipo dinámico, donde los datos, la innovación y la mejora continua son parte del día a día.Ser parte de Banco Ripley es vivir una cultura que impulsa el desarrollo, la colaboración y el aprendizaje constante, en un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te apasiona la programación, la analítica de datos y la automatización de procesos? ¿Te gustaría trabajar con modelos analíticos y contribuir a hacer más eficientes los procesos del negocio? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Apoyar la ejecución, monitoreo y optimización de los procesos analíticos de la gerencia, participando en el diseño e implementación de soluciones que permitan automatizar, calendarizar y mejorar los flujos de trabajo actuales, contribuyendo a una operación más eficiente y escalable.Funciones: 🤩• Ejecutar y monitorear los procesos analíticos vigentes para asegurar la continuidad operacional.• Garantizar la entrega oportuna de información y resultados generados por los procesos actuales.• Identificar oportunidades de automatización y mejora en procesos manuales.• Diseñar e implementar soluciones para automatizar y calendarizar procesos analíticos.• Revisar y optimizar el código de modelos analíticos, proponiendo mejoras en su estructura y eficiencia.• Validar el desempeño de modelos y procedimientos almacenados (Stored Procedures) en entornos AWS.• Colaborar en iniciativas de mejora continua que fortalezcan la eficiencia de los procesos del área.¿Qué estamos buscando? 💡• Estudiante de Ingeniería Civil, Ingeniería Informática, Ingeniería Industrial, Estadística, Ciencia de Datos o carrera afín.• Contar con seguro escolar vigente otorgado por la casa de estudios. (Excluyente).• Disponibilidad inmediata para realizar la práctica.• Conocimientos de programación en Python, R y SQL.• Conocimientos en estadística, machine learning y técnicas de clusterización.• Deseable conocimiento de entornos cloud, especialmente AWS SageMaker.• Interés por la analítica, la automatización de procesos y la optimización continua.• Capacidad analítica, proactividad y ganas de aprender en un entorno desafiante.¿Por qué trabajar en Banco Ripley? 💜Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo. 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y, si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
+          <t>EnDifem Laboratoriosbuscamos un/a profesional para liderar un proyecto de optimización de cajas de embalaje, participando en el análisis, diseño y desarrollo de soluciones que contribuyan a mejorar nuestros procesos y estandarizar el portafolio de packaging.¿Cuáles serán tus principales desafios?Analizar y optimizar el portafolio de cajas de embalaje.Desarrollar y validar propuestas de packaging mediante maquetas y troqueles.Elaborar fichas técnicas de productos y materiales de marketing.Crear instructivos y documentación técnica para la estandarización de procesos.Coordinar pruebas e implementación de mejoras, trabajando de manera transversal con distintas áreas de la compañía.Buscamos a un profesional con:Título de Diseño Industrial, Ingeniería Civil Industrial, Ingeniería en Packaging o carrera afín.Experiencia en desarrollo de packaging, mejora de procesos o gestión de proyectos.Manejo avanzado de Excel.Power BI (deseable).Perfil analítico, organizado y orientado a resultados.Te ofrecemos:Participar en un proyecto estratégico con impacto directo en la organización.🤝 Trabajo colaborativo con equipos multidisciplinarios.📅 Contrato por proyecto.</t>
         </is>
       </c>
     </row>
@@ -3040,27 +3040,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Profesional de Proyectos de Packaging</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Difem Laboratorios S.A.</t>
+          <t>KPMG Chile</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Las Condes, Metropolitana, Chile, Chile</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55908/profesional-de-proyectos-de-packaging</t>
+          <t>https://firstjob.me/oferta/55912/data-analyst</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>analisis, excel, power bi</t>
+          <t>analisis, estadistica, excel</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -3078,10 +3078,10 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -3097,49 +3097,45 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>EnDifem Laboratoriosbuscamos un/a profesional para liderar un proyecto de optimización de cajas de embalaje, participando en el análisis, diseño y desarrollo de soluciones que contribuyan a mejorar nuestros procesos y estandarizar el portafolio de packaging.¿Cuáles serán tus principales desafios?Analizar y optimizar el portafolio de cajas de embalaje.Desarrollar y validar propuestas de packaging mediante maquetas y troqueles.Elaborar fichas técnicas de productos y materiales de marketing.Crear instructivos y documentación técnica para la estandarización de procesos.Coordinar pruebas e implementación de mejoras, trabajando de manera transversal con distintas áreas de la compañía.Buscamos a un profesional con:Título de Diseño Industrial, Ingeniería Civil Industrial, Ingeniería en Packaging o carrera afín.Experiencia en desarrollo de packaging, mejora de procesos o gestión de proyectos.Manejo avanzado de Excel.Power BI (deseable).Perfil analítico, organizado y orientado a resultados.Te ofrecemos:Participar en un proyecto estratégico con impacto directo en la organización.🤝 Trabajo colaborativo con equipos multidisciplinarios.📅 Contrato por proyecto.</t>
+          <t>Perfil Ideal: Analista de DatosBuscamos un profesional proactivo y analítico para unirse a nuestro equipo en KPMG Chile. El candidato ideal poseerá una sólida orientación hacia la gestión y calidad de datos, con el objetivo de optimizar la información y respaldar la toma de decisiones estratégicas.Responsabilidades Clave:Administración y manejo de sistemas CRM, con énfasis en Salesforce.Ejecución de procesos de segmentación de datos para diversas iniciativas de negocio.Apoyo en la gestión, mantenimiento y aseguramiento de la calidad de bases de datos.Monitoreo y seguimiento riguroso de la calidad de la información registrada.Gestión y control de la calidad del pipeline de datos.Requisitos Fundamentales:Título profesional en Ingeniería Comercial, Ingeniería Civil Industrial, Ingeniería en Información y Control de Gestión, Estadística, Administración o carreras afines.Experiencia demostrable en gestión y calidad de datos.Manejo de CRM, preferentemente Salesforce.Conocimientos sólidos en segmentación, administración y análisis de bases de datos.Dominio de Excel a nivel intermedio o avanzado. Este rol es ideal para profesionales que buscan un entorno dinámico donde aplicar sus habilidades analíticas y contribuir directamente al éxito de la organización.Beneficios¿Qué ganas tú?:🚑Seguro complementario de Salud🌎Ser parte de una de las principales compañías de Auditoría y Consultoría a nivel mundial.🚀 Oportunidades de desarrollo profesional.💻Jornada de trabajo Hibrida (flexible según el cliente y el equipo con que se esté trabajando)🏢Oficinas de primer nivel ubicadas en Las Condes, frente al Parque Araucano💯Múltiples convenios corporativos🎉Actividades como fiestas, Meeting Points y encuentros de área para disfrutar con compañerosEn KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas, con un propósito claro, para una mejor sociedad. Valoramos las diversas habilidades y fortalezas, tanto personales como profesionales, que cada persona aporta. En KPMG estamos comprometidos con la Diversidad e inclusión, nuestras ofertas de empleo están disponibles con los ajustes razonables necesarios para tu proceso . Juntos, estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. ¡Anímate y ven a descubrir por qué somos la opción más clara! 🥇</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Asesor de Financiamiento Automotriz Temuco</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KPMG Chile</t>
+          <t>Tanner</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Las Condes, Metropolitana, Chile, Chile</t>
+          <t>Región de la Araucanía, Chile</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55912/data-analyst</t>
+          <t>https://firstjob.me/oferta/55939/asesor-de-financiamiento-automotriz-temuco</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>5</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>analisis, estadistica, excel</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -3147,10 +3143,10 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -3166,7 +3162,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>Perfil Ideal: Analista de DatosBuscamos un profesional proactivo y analítico para unirse a nuestro equipo en KPMG Chile. El candidato ideal poseerá una sólida orientación hacia la gestión y calidad de datos, con el objetivo de optimizar la información y respaldar la toma de decisiones estratégicas.Responsabilidades Clave:Administración y manejo de sistemas CRM, con énfasis en Salesforce.Ejecución de procesos de segmentación de datos para diversas iniciativas de negocio.Apoyo en la gestión, mantenimiento y aseguramiento de la calidad de bases de datos.Monitoreo y seguimiento riguroso de la calidad de la información registrada.Gestión y control de la calidad del pipeline de datos.Requisitos Fundamentales:Título profesional en Ingeniería Comercial, Ingeniería Civil Industrial, Ingeniería en Información y Control de Gestión, Estadística, Administración o carreras afines.Experiencia demostrable en gestión y calidad de datos.Manejo de CRM, preferentemente Salesforce.Conocimientos sólidos en segmentación, administración y análisis de bases de datos.Dominio de Excel a nivel intermedio o avanzado. Este rol es ideal para profesionales que buscan un entorno dinámico donde aplicar sus habilidades analíticas y contribuir directamente al éxito de la organización.Beneficios¿Qué ganas tú?:🚑Seguro complementario de Salud🌎Ser parte de una de las principales compañías de Auditoría y Consultoría a nivel mundial.🚀 Oportunidades de desarrollo profesional.💻Jornada de trabajo Hibrida (flexible según el cliente y el equipo con que se esté trabajando)🏢Oficinas de primer nivel ubicadas en Las Condes, frente al Parque Araucano💯Múltiples convenios corporativos🎉Actividades como fiestas, Meeting Points y encuentros de área para disfrutar con compañerosEn KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas, con un propósito claro, para una mejor sociedad. Valoramos las diversas habilidades y fortalezas, tanto personales como profesionales, que cada persona aporta. En KPMG estamos comprometidos con la Diversidad e inclusión, nuestras ofertas de empleo están disponibles con los ajustes razonables necesarios para tu proceso . Juntos, estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. ¡Anímate y ven a descubrir por qué somos la opción más clara! 🥇</t>
+          <t>Asesor de Financiamiento Automotriz TemucoTanner Servicios FinancierosEn Tanner buscamos personas con energía comercial, foco en resultados y pasión por el mundo automotriz. Si te motiva el contacto con clientes y quieres potenciar tu desarrollo en una compañía del rubro financiero, esta oportunidad es para ti.¿Cuál será tu desafío?Serás responsable de gestionar la venta y refinanciamiento de créditos automotrices y productos asociados, contribuyendo directamente al cumplimiento de metas comerciales de la unidadEn el día a día esto implica:Venta de financiamiento automotriz en distintos canales (especialmente telefónicos)Comercialización de productos asociados (principalmente seguros)Gestión de cartera de clientes y seguimiento comercialCumplimiento de metas y presupuesto comercial¿Por qué Tanner?Aquí no solo vendes productos,generas soluciones reales para los clientesy eres protagonista de su proceso de financiamiento. Trabajarás en un entorno cercano, con foco en resultados y donde tu desempeño impacta directamente en tu crecimiento.Compromiso con la Inclusión:Nuestras ofertas están bajo el marco contextual de laLey 21.015, que incentiva la inclusión laboral de personas con discapacidad. En Tanner, valoramos el talento único de cada persona.Requisitos¿Qué buscamos?Recién titulados o personas con1 año de experiencia en ventas, idealmente en seguros, créditos o rubro automotrizOrientación comercial y foco en resultadosHabilidades de comunicación y cercanía con clientesProactividad y autonomíaDisponibilidad para trabajarfull presencial en Temuco.</t>
         </is>
       </c>
     </row>
@@ -3178,17 +3174,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Asesor de Financiamiento Automotriz Temuco</t>
+          <t>Analista Capacity Planning (1 a 2 años de experiencia)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tanner</t>
+          <t>Polpaico Soluciones</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Región de la Araucanía, Chile</t>
+          <t>san bernardo, Chile</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3198,13 +3194,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55939/asesor-de-financiamiento-automotriz-temuco</t>
+          <t>https://firstjob.me/oferta/55942/analista-capacity-planning-1-a-2-anos-de-experiencia</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>python, analisis, excel, power bi</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>Asesor de Financiamiento Automotriz TemucoTanner Servicios FinancierosEn Tanner buscamos personas con energía comercial, foco en resultados y pasión por el mundo automotriz. Si te motiva el contacto con clientes y quieres potenciar tu desarrollo en una compañía del rubro financiero, esta oportunidad es para ti.¿Cuál será tu desafío?Serás responsable de gestionar la venta y refinanciamiento de créditos automotrices y productos asociados, contribuyendo directamente al cumplimiento de metas comerciales de la unidadEn el día a día esto implica:Venta de financiamiento automotriz en distintos canales (especialmente telefónicos)Comercialización de productos asociados (principalmente seguros)Gestión de cartera de clientes y seguimiento comercialCumplimiento de metas y presupuesto comercial¿Por qué Tanner?Aquí no solo vendes productos,generas soluciones reales para los clientesy eres protagonista de su proceso de financiamiento. Trabajarás en un entorno cercano, con foco en resultados y donde tu desempeño impacta directamente en tu crecimiento.Compromiso con la Inclusión:Nuestras ofertas están bajo el marco contextual de laLey 21.015, que incentiva la inclusión laboral de personas con discapacidad. En Tanner, valoramos el talento único de cada persona.Requisitos¿Qué buscamos?Recién titulados o personas con1 año de experiencia en ventas, idealmente en seguros, créditos o rubro automotrizOrientación comercial y foco en resultadosHabilidades de comunicación y cercanía con clientesProactividad y autonomíaDisponibilidad para trabajarfull presencial en Temuco.</t>
+          <t>Polpaico Soluciones, es una compañía líder en el mercado nacional de la fabricación y comercialización de cemento, hormigón y áridos. Como empresa estamos convencidos que tener un equipo de trabajo diverso y una cultura inclusiva genera beneficios para las personas y el negocio. No sólo aceptamos la diversidad, sino que la valoramos y promovemos activamente.Actualmente nos encontramos en la búsqueda deAnalista de capacity Planningcuyo propósito es la planificación de Capacity en la producción de los análisis, modelos y reportes que sustentan las decisiones de planificación de flota y operadores mixer. Procesa los datos del rolling forecast, construye los modelos de capacity por zona, elabora el calendario de turnos y la asignación de camiones, y monitorea las desviaciones entre la demanda proyectada y la real.¿Cuáles serán tus principales funciones en este cargo?1. Procesar los datos del rolling forecast mensual y construir los modelos de proyección de demanda por zona geográfica y planta, como insumo para el plan de capacity.2. Calcular los requerimientos de flota y operadores necesarios para cubrir la demanda proyectada, identificando brechas de capacidad por zona y período.3. Elaborar y mantener actualizado el calendario mensual de turnos de operadores mixer por planta y zona.4. Construir la propuesta de asignación mensual de camiones por planta y zona, integrando la disponibilidad de flota confirmada por el área de mantenimiento.5. Monitorear mensualmente la evolución de la demanda real versus la proyectada, identificando desviaciones y alertando al superar los umbrales definidos.6. Mantener actualizadas las bases de datos de capacity, demanda histórica, flota, disponibilidad de flota, dotación de operadores,eficiencia de operadores y asegurando calidad e integridad de los datos.7. Preparar los reportes y presentaciones del plan de capacity para la reunión mensual de rolling forecast con Planificación Comercial y el Área Comercial de Hormigones.8. Prepararse analizando distintos escenarios ante variaciones de demanda, disponibilidad de flota u otra variable que pueda afectar la correcta planificación de la operaciónRequisitos:Título profesional en Ingeniería Civil Industrial, Ingeniería Comercial o carrera afínAl menos un año de experiencia en el áreaConocimiento en Forecast de demandas, Proyecciones, Supply chain y/o Gestión de flota.Excel avanzado (Excluyente)Power Bi / Python (Deseable)Formación en metodologías de planificación de operaciones o supply chain (deseable).Polpaico Soluciones garantiza igualdad de condiciones en el acceso al empleo, es decir, esta oferta de trabajo es consciente con el medio y las diversas realidades, por lo que se enmarca en la ley de inclusión laboral N°21.015.Si tu objetivo es asumir nuevos desafíos en una compañía líder del mercado, ¡Postula con nosotros!BeneficiosComo colaborador/a de Polpaico Soluciones, te ofrecemos:Seguro de vida 100% financiado por la compañía.Seguro complementario de salud, dental y catastrófico.Oportunidades de crecimiento y desarrollo profesional a través de becas de estudio.Excelente ambiente de trabajo.Alguna de nuestras principales alianzas son: Caja compensación los Andes y FALP (Fundación Arturo López Perez).</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Analista Capacity Planning (1 a 2 años de experiencia)</t>
+          <t>Analista Operaciones Logística</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3253,25 +3253,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>san bernardo, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Presencial Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55942/analista-capacity-planning-1-a-2-anos-de-experiencia</t>
+          <t>https://firstjob.me/oferta/55941/analista-operaciones-logistica</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>python, analisis, excel, power bi</t>
+          <t>analisis, informatica, excel, power bi</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -3281,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>1</v>
@@ -3296,11 +3296,11 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>Polpaico Soluciones, es una compañía líder en el mercado nacional de la fabricación y comercialización de cemento, hormigón y áridos. Como empresa estamos convencidos que tener un equipo de trabajo diverso y una cultura inclusiva genera beneficios para las personas y el negocio. No sólo aceptamos la diversidad, sino que la valoramos y promovemos activamente.Actualmente nos encontramos en la búsqueda deAnalista de capacity Planningcuyo propósito es la planificación de Capacity en la producción de los análisis, modelos y reportes que sustentan las decisiones de planificación de flota y operadores mixer. Procesa los datos del rolling forecast, construye los modelos de capacity por zona, elabora el calendario de turnos y la asignación de camiones, y monitorea las desviaciones entre la demanda proyectada y la real.¿Cuáles serán tus principales funciones en este cargo?1. Procesar los datos del rolling forecast mensual y construir los modelos de proyección de demanda por zona geográfica y planta, como insumo para el plan de capacity.2. Calcular los requerimientos de flota y operadores necesarios para cubrir la demanda proyectada, identificando brechas de capacidad por zona y período.3. Elaborar y mantener actualizado el calendario mensual de turnos de operadores mixer por planta y zona.4. Construir la propuesta de asignación mensual de camiones por planta y zona, integrando la disponibilidad de flota confirmada por el área de mantenimiento.5. Monitorear mensualmente la evolución de la demanda real versus la proyectada, identificando desviaciones y alertando al superar los umbrales definidos.6. Mantener actualizadas las bases de datos de capacity, demanda histórica, flota, disponibilidad de flota, dotación de operadores,eficiencia de operadores y asegurando calidad e integridad de los datos.7. Preparar los reportes y presentaciones del plan de capacity para la reunión mensual de rolling forecast con Planificación Comercial y el Área Comercial de Hormigones.8. Prepararse analizando distintos escenarios ante variaciones de demanda, disponibilidad de flota u otra variable que pueda afectar la correcta planificación de la operaciónRequisitos:Título profesional en Ingeniería Civil Industrial, Ingeniería Comercial o carrera afínAl menos un año de experiencia en el áreaConocimiento en Forecast de demandas, Proyecciones, Supply chain y/o Gestión de flota.Excel avanzado (Excluyente)Power Bi / Python (Deseable)Formación en metodologías de planificación de operaciones o supply chain (deseable).Polpaico Soluciones garantiza igualdad de condiciones en el acceso al empleo, es decir, esta oferta de trabajo es consciente con el medio y las diversas realidades, por lo que se enmarca en la ley de inclusión laboral N°21.015.Si tu objetivo es asumir nuevos desafíos en una compañía líder del mercado, ¡Postula con nosotros!BeneficiosComo colaborador/a de Polpaico Soluciones, te ofrecemos:Seguro de vida 100% financiado por la compañía.Seguro complementario de salud, dental y catastrófico.Oportunidades de crecimiento y desarrollo profesional a través de becas de estudio.Excelente ambiente de trabajo.Alguna de nuestras principales alianzas son: Caja compensación los Andes y FALP (Fundación Arturo López Perez).</t>
+          <t>Polpaico Soluciones,es una compañía líder en el mercado nacional de la fabricación y comercialización de cemento, hormigón y áridos. Como empresa estamos convencidos que tener un equipo de trabajo diverso y una cultura inclusiva genera beneficios para las personas y el negocio.Actualmente nos encontramos en búsqueda de:Analista de operaciones Logísticas.Objetivo Principal:Proveer inteligencia analítica y de gestión a la Red Logística de Polpaico, liderando la reportabilidad de cierres de mes, el análisis de desviaciones en costos de distribución y el desarrollo de paneles de control en Power BI para la toma de decisiones operativas y estratégicas. Apoya el proceso S&amp;OP garantizando visibilidad end-to-end del desempeño logístico mediante datos confiables, oportunos y accionables.Principales Responsabilidades:1.- Preparar y consolidar el cierre de mes logístico: costos de distribución, volúmenes despachados, rendimientos de flota y cumplimiento de servicio en toda la Red Logística de Chile.2.- Analizar desviaciones de costos de distribución versus presupuesto y forecast, identificando causas raíz y proponiendo acciones correctivas a la jefatura.3.- Diseñar, desarrollar y mantener paneles de Power BI con indicadores clave para la gestión diaria (KPIs de costo, servicio, eficiencia de flota, fill rate, OTIF, cobertura de stock).4.- Gestionar y validar la información proveniente de SAP para asegurar consistencia y calidad de datos en los reportes logísticos.5.- Apoyar el proceso S&amp;OP mensual con análisis de demanda, capacidad logística y alertas de riesgo en el cumplimiento del plan.6.- Automatizar reportes recurrentes mediante Excel avanzado (Power Query, tablas dinámicas, macros) y conectores de datos para reducir tiempos de cierre.7.- Elaborar presentaciones ejecutivas con análisis de resultados logísticos para reuniones de gerencia y comités de gestión.8.- Colaborar con las áreas de Finanzas, Operaciones y Comercial en la validación de información y la alineación de definiciones de KPIs.RequisitosFormación:Ingeniería en Logística, Ingeniería Industrial, Ingeniería en informática ó carrera afín.Experiencia:- 2 años de experiencia en roles de control de gestión logística, planificación, S&amp;OP o analítica de operaciones en industrias de consumo masivo, cemento, materiales de construcción o afines.- Experiencia comprobable en desarrollo de reportes de cierre de mes y análisis de desviaciones de costos.- Historial demostrable en diseño e implementación de dashboards de gestión en Power BI con impacto real en la toma de decisiones operativas.-Deseable experiencia trabajando con datos de SAP en entornos logísticos o de supply chain.Conocimientos:Procesos logísticos y operacionales (transporte, distribución).Excluyente: Manejo de sistemas ERP (SAP), Excel avanzado, Power BI.BeneficiosComo colaborador/a de Polpaico Soluciones, te ofrecemos:Seguro de vida 100% financiado por la compañía.Seguro complementario de salud, dental y catastrófico.Oportunidades de crecimiento y desarrollo profesional a través de becas de estudio.Excelente ambiente de trabajo.Alguna de nuestras principales alianzas son: Caja compensación los Andes y FALP (Fundación Arturo López Pérez).</t>
         </is>
       </c>
     </row>
@@ -3312,37 +3312,33 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Analista Operaciones Logística</t>
+          <t>Asesor de Financiamiento Automotriz Concepción</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Polpaico Soluciones</t>
+          <t>Tanner</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Región del Biobío, Chile</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Presencial Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55941/analista-operaciones-logistica</t>
+          <t>https://firstjob.me/oferta/55940/asesor-de-financiamiento-automotriz-concepcion</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>7</v>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>analisis, informatica, excel, power bi</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -3350,7 +3346,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>1</v>
@@ -3365,11 +3361,11 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>Polpaico Soluciones,es una compañía líder en el mercado nacional de la fabricación y comercialización de cemento, hormigón y áridos. Como empresa estamos convencidos que tener un equipo de trabajo diverso y una cultura inclusiva genera beneficios para las personas y el negocio.Actualmente nos encontramos en búsqueda de:Analista de operaciones Logísticas.Objetivo Principal:Proveer inteligencia analítica y de gestión a la Red Logística de Polpaico, liderando la reportabilidad de cierres de mes, el análisis de desviaciones en costos de distribución y el desarrollo de paneles de control en Power BI para la toma de decisiones operativas y estratégicas. Apoya el proceso S&amp;OP garantizando visibilidad end-to-end del desempeño logístico mediante datos confiables, oportunos y accionables.Principales Responsabilidades:1.- Preparar y consolidar el cierre de mes logístico: costos de distribución, volúmenes despachados, rendimientos de flota y cumplimiento de servicio en toda la Red Logística de Chile.2.- Analizar desviaciones de costos de distribución versus presupuesto y forecast, identificando causas raíz y proponiendo acciones correctivas a la jefatura.3.- Diseñar, desarrollar y mantener paneles de Power BI con indicadores clave para la gestión diaria (KPIs de costo, servicio, eficiencia de flota, fill rate, OTIF, cobertura de stock).4.- Gestionar y validar la información proveniente de SAP para asegurar consistencia y calidad de datos en los reportes logísticos.5.- Apoyar el proceso S&amp;OP mensual con análisis de demanda, capacidad logística y alertas de riesgo en el cumplimiento del plan.6.- Automatizar reportes recurrentes mediante Excel avanzado (Power Query, tablas dinámicas, macros) y conectores de datos para reducir tiempos de cierre.7.- Elaborar presentaciones ejecutivas con análisis de resultados logísticos para reuniones de gerencia y comités de gestión.8.- Colaborar con las áreas de Finanzas, Operaciones y Comercial en la validación de información y la alineación de definiciones de KPIs.RequisitosFormación:Ingeniería en Logística, Ingeniería Industrial, Ingeniería en informática ó carrera afín.Experiencia:- 2 años de experiencia en roles de control de gestión logística, planificación, S&amp;OP o analítica de operaciones en industrias de consumo masivo, cemento, materiales de construcción o afines.- Experiencia comprobable en desarrollo de reportes de cierre de mes y análisis de desviaciones de costos.- Historial demostrable en diseño e implementación de dashboards de gestión en Power BI con impacto real en la toma de decisiones operativas.-Deseable experiencia trabajando con datos de SAP en entornos logísticos o de supply chain.Conocimientos:Procesos logísticos y operacionales (transporte, distribución).Excluyente: Manejo de sistemas ERP (SAP), Excel avanzado, Power BI.BeneficiosComo colaborador/a de Polpaico Soluciones, te ofrecemos:Seguro de vida 100% financiado por la compañía.Seguro complementario de salud, dental y catastrófico.Oportunidades de crecimiento y desarrollo profesional a través de becas de estudio.Excelente ambiente de trabajo.Alguna de nuestras principales alianzas son: Caja compensación los Andes y FALP (Fundación Arturo López Pérez).</t>
+          <t>Asesor de Financiamiento Automotriz TemucoTanner Servicios FinancierosEn Tanner buscamos personas con energía comercial, foco en resultados y pasión por el mundo automotriz. Si te motiva el contacto con clientes y quieres potenciar tu desarrollo en una compañía del rubro financiero, esta oportunidad es para ti.¿Cuál será tu desafío?Serás responsable de gestionar la venta y refinanciamiento de créditos automotrices y productos asociados, contribuyendo directamente al cumplimiento de metas comerciales de la unidadEn el día a día esto implica:Venta de financiamiento automotriz en distintos canales (especialmente telefónicos)Comercialización de productos asociados (principalmente seguros)Gestión de cartera de clientes y seguimiento comercialCumplimiento de metas y presupuesto comercial¿Por qué Tanner?Aquí no solo vendes productos,generas soluciones reales para los clientesy eres protagonista de su proceso de financiamiento. Trabajarás en un entorno cercano, con foco en resultados y donde tu desempeño impacta directamente en tu crecimiento.Compromiso con la Inclusión:Nuestras ofertas están bajo el marco contextual de laLey 21.015, que incentiva la inclusión laboral de personas con discapacidad. En Tanner, valoramos el talento único de cada persona.Requisitos¿Qué buscamos?Recién titulados o personas con1 año de experiencia en ventas, idealmente en seguros, créditos o rubro automotrizOrientación comercial y foco en resultadosHabilidades de comunicación y cercanía con clientesProactividad y autonomíaDisponibilidad para trabajarfull presencial en Temuco.</t>
         </is>
       </c>
     </row>
@@ -3381,27 +3377,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Asesor de Financiamiento Automotriz Concepción</t>
+          <t>Customer Success Manager – TGP</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tanner</t>
+          <t>TGP</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Región del Biobío, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55940/asesor-de-financiamiento-automotriz-concepcion</t>
+          <t>https://firstjob.me/oferta/55926/customer-success-manager-tgp</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -3415,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -3434,7 +3430,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>Asesor de Financiamiento Automotriz TemucoTanner Servicios FinancierosEn Tanner buscamos personas con energía comercial, foco en resultados y pasión por el mundo automotriz. Si te motiva el contacto con clientes y quieres potenciar tu desarrollo en una compañía del rubro financiero, esta oportunidad es para ti.¿Cuál será tu desafío?Serás responsable de gestionar la venta y refinanciamiento de créditos automotrices y productos asociados, contribuyendo directamente al cumplimiento de metas comerciales de la unidadEn el día a día esto implica:Venta de financiamiento automotriz en distintos canales (especialmente telefónicos)Comercialización de productos asociados (principalmente seguros)Gestión de cartera de clientes y seguimiento comercialCumplimiento de metas y presupuesto comercial¿Por qué Tanner?Aquí no solo vendes productos,generas soluciones reales para los clientesy eres protagonista de su proceso de financiamiento. Trabajarás en un entorno cercano, con foco en resultados y donde tu desempeño impacta directamente en tu crecimiento.Compromiso con la Inclusión:Nuestras ofertas están bajo el marco contextual de laLey 21.015, que incentiva la inclusión laboral de personas con discapacidad. En Tanner, valoramos el talento único de cada persona.Requisitos¿Qué buscamos?Recién titulados o personas con1 año de experiencia en ventas, idealmente en seguros, créditos o rubro automotrizOrientación comercial y foco en resultadosHabilidades de comunicación y cercanía con clientesProactividad y autonomíaDisponibilidad para trabajarfull presencial en Temuco.</t>
+          <t>En TGP estamos buscando a nuestro/a próximo/a Customer Success ManagerBuscamos a una persona con experiencia en gestión de clientes B2B que quiera convertirse en un socio estratégico para las cuentas de su cartera. Si te motiva construir relaciones de largo plazo, analizar métricas, detectar oportunidades de crecimiento y generar un impacto directo en la retención y expansión de clientes, esta oportunidad puede ser para ti.¿Cuál será tu foco?Gestionar la relación comercial con una cartera de clientes activos.Analizar métricas de desempeño para identificar oportunidades de mejora y riesgos de churn.Reportar al Customer Success Lead el estado de cada cliente y diseñar en conjunto acciones operativas para mejorar el rendimiento.Diseñar estrategias de retención y expansión junto al Business Partner.Detectar oportunidades de cross-sell y upsell dentro de las cuentas.Liderar reuniones con clientes, presentar reportes y proponer acciones estratégicas.Coordinar con los equipos internos la correcta ejecución de los planes definidos para cada cliente.Buscamos personas que:Cuenten con experiencia en Customer Success, Account Management, KAM o gestión de clientes B2B.Tengan una fuerte orientación comercial y disfruten construir relaciones de largo plazo.Sean analíticas y capaces de interpretar métricas para tomar decisiones.Sean proactivas, organizadas y orientadas a resultados. Disfruten trabajar de forma autónoma y colaborativa con equipos multidisciplinarios.Modalidad: Híbrida (3 días presencial, 2 online)Ubicación:Las Condes, SantiagoSi te interesa esta oportunidad o conoces a alguien que pueda encajar, ¡nos encantaría conversar contigo!Beneficios¿Qué hace atractiva esta oportunidad?Tendrás autonomía para liderar la estrategia comercial de una cartera de clientes. Trabajarás directamente con clientes estratégicos, convirtiéndote en su principal socio comercial dentro de TGP.Serás protagonista en la retención y expansión de cuentas, generando un impacto directo en el crecimiento de la empresa.Contarás con oportunidades reales de crecimiento y desarrollo profesional dentro de TGP.Tendrás un esquema de incentivos asociado a oportunidades de upsell y expansión comercial.</t>
         </is>
       </c>
     </row>
@@ -3446,12 +3442,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Customer Success Manager – TGP</t>
+          <t>Coordinador Planificación y Abastecimiento Repuestos</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TGP</t>
+          <t>Polpaico Soluciones</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3461,12 +3457,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55926/customer-success-manager-tgp</t>
+          <t>https://firstjob.me/oferta/55925/coordinador-planificacion-y-abastecimiento-repuestos</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -3480,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>1</v>
@@ -3499,7 +3495,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>En TGP estamos buscando a nuestro/a próximo/a Customer Success ManagerBuscamos a una persona con experiencia en gestión de clientes B2B que quiera convertirse en un socio estratégico para las cuentas de su cartera. Si te motiva construir relaciones de largo plazo, analizar métricas, detectar oportunidades de crecimiento y generar un impacto directo en la retención y expansión de clientes, esta oportunidad puede ser para ti.¿Cuál será tu foco?Gestionar la relación comercial con una cartera de clientes activos.Analizar métricas de desempeño para identificar oportunidades de mejora y riesgos de churn.Reportar al Customer Success Lead el estado de cada cliente y diseñar en conjunto acciones operativas para mejorar el rendimiento.Diseñar estrategias de retención y expansión junto al Business Partner.Detectar oportunidades de cross-sell y upsell dentro de las cuentas.Liderar reuniones con clientes, presentar reportes y proponer acciones estratégicas.Coordinar con los equipos internos la correcta ejecución de los planes definidos para cada cliente.Buscamos personas que:Cuenten con experiencia en Customer Success, Account Management, KAM o gestión de clientes B2B.Tengan una fuerte orientación comercial y disfruten construir relaciones de largo plazo.Sean analíticas y capaces de interpretar métricas para tomar decisiones.Sean proactivas, organizadas y orientadas a resultados. Disfruten trabajar de forma autónoma y colaborativa con equipos multidisciplinarios.Modalidad: Híbrida (3 días presencial, 2 online)Ubicación:Las Condes, SantiagoSi te interesa esta oportunidad o conoces a alguien que pueda encajar, ¡nos encantaría conversar contigo!Beneficios¿Qué hace atractiva esta oportunidad?Tendrás autonomía para liderar la estrategia comercial de una cartera de clientes. Trabajarás directamente con clientes estratégicos, convirtiéndote en su principal socio comercial dentro de TGP.Serás protagonista en la retención y expansión de cuentas, generando un impacto directo en el crecimiento de la empresa.Contarás con oportunidades reales de crecimiento y desarrollo profesional dentro de TGP.Tendrás un esquema de incentivos asociado a oportunidades de upsell y expansión comercial.</t>
+          <t>Polpaico Soluciones, es una compañía líder en el mercado nacional de la fabricación y comercialización de cemento, hormigón y áridos. Como empresa estamos convencidos que tener un equipo de trabajo diverso y una cultura inclusiva genera beneficios para las personas y el negocio. No sólo aceptamos la diversidad, sino que la valoramos y promovemos activamente.Actualmente nos encontramos en la búsqueda de un/unaCoordinador(a) de Planificación y Abastecimiento de RepuestosObjetivo:Liderar la planificación de la demanda y la gestión técnica del inventario de repuestos para camiones y plantas. Es responsable de asegurar que el negocio cuente con las definiciones de stock necesarias (mínimos, máximos y criticidad) para garantizar la disponibilidad y continuidad operativa, entregando requerimientos validados al área de abastecimiento para las posterior búsqueda y negociación.Además, debe asegurar la gobernanza integral del ciclo de vida de materiales y repuestos, mediante la creación, estandarización y mantención de códigos maestros, la planificación eficiente de repuestos y el control del abastecimiento, articulando de manera coordinada las necesidades del área de Mantenimiento Planta con los procesos del área de Compras, con el fin de garantizar continuidad operacional, optimizar niveles de inventario y contribuir a la toma de decisiones confiables y oportunas para la operación.Funciones:1.- Analizar consumos históricos, criticidad de equipos y planes de mantenimiento para planificar el abastecimiento de repuestos, definiendo parámetros MRP, stocks de seguridad y puntos de reposición.2.- Administrar y asegurar la calidad de los datos maestros de materiales en SAP, garantizando información estandarizada, actualizada y confiable.3.- Coordinar requerimientos entre Mantenimiento, Operaciones, Compras y Bodega, realizando seguimiento al proceso de abastecimiento y apoyando la resolución de desviaciones, devoluciones y diferencias de compras.4.- Gestionar y optimizar los niveles de inventario, identificando sobrestock, obsolescencia y oportunidades de mejora para asegurar la disponibilidad de repuestos críticos.5.- Elaborar reportes e indicadores de planificación, inventarios y abastecimiento, detectando desviaciones y proponiendo acciones de mejora para apoyar la toma de decisiones.BeneficiosSeguro de vida 100% financiado por la compañía.Seguro complementario de salud, dental y catastrófico.Oportunidades de crecimiento y desarrollo profesional a través de becas de estudio.Excelente ambiente de trabajo.Alguna de nuestras principales alianzas son: Caja compensación los Andes y FALP (Fundación Arturo López Pérez).</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3507,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Coordinador Planificación y Abastecimiento Repuestos</t>
+          <t>Analista Planificación Comercial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3531,13 +3527,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55925/coordinador-planificacion-y-abastecimiento-repuestos</t>
+          <t>https://firstjob.me/oferta/55927/analista-planificacion-comercial</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>Polpaico Soluciones, es una compañía líder en el mercado nacional de la fabricación y comercialización de cemento, hormigón y áridos. Como empresa estamos convencidos que tener un equipo de trabajo diverso y una cultura inclusiva genera beneficios para las personas y el negocio. No sólo aceptamos la diversidad, sino que la valoramos y promovemos activamente.Actualmente nos encontramos en la búsqueda de un/unaCoordinador(a) de Planificación y Abastecimiento de RepuestosObjetivo:Liderar la planificación de la demanda y la gestión técnica del inventario de repuestos para camiones y plantas. Es responsable de asegurar que el negocio cuente con las definiciones de stock necesarias (mínimos, máximos y criticidad) para garantizar la disponibilidad y continuidad operativa, entregando requerimientos validados al área de abastecimiento para las posterior búsqueda y negociación.Además, debe asegurar la gobernanza integral del ciclo de vida de materiales y repuestos, mediante la creación, estandarización y mantención de códigos maestros, la planificación eficiente de repuestos y el control del abastecimiento, articulando de manera coordinada las necesidades del área de Mantenimiento Planta con los procesos del área de Compras, con el fin de garantizar continuidad operacional, optimizar niveles de inventario y contribuir a la toma de decisiones confiables y oportunas para la operación.Funciones:1.- Analizar consumos históricos, criticidad de equipos y planes de mantenimiento para planificar el abastecimiento de repuestos, definiendo parámetros MRP, stocks de seguridad y puntos de reposición.2.- Administrar y asegurar la calidad de los datos maestros de materiales en SAP, garantizando información estandarizada, actualizada y confiable.3.- Coordinar requerimientos entre Mantenimiento, Operaciones, Compras y Bodega, realizando seguimiento al proceso de abastecimiento y apoyando la resolución de desviaciones, devoluciones y diferencias de compras.4.- Gestionar y optimizar los niveles de inventario, identificando sobrestock, obsolescencia y oportunidades de mejora para asegurar la disponibilidad de repuestos críticos.5.- Elaborar reportes e indicadores de planificación, inventarios y abastecimiento, detectando desviaciones y proponiendo acciones de mejora para apoyar la toma de decisiones.BeneficiosSeguro de vida 100% financiado por la compañía.Seguro complementario de salud, dental y catastrófico.Oportunidades de crecimiento y desarrollo profesional a través de becas de estudio.Excelente ambiente de trabajo.Alguna de nuestras principales alianzas son: Caja compensación los Andes y FALP (Fundación Arturo López Pérez).</t>
+          <t>Polpaico Soluciones,es una compañía líder en el mercado nacional de la fabricación y comercialización de cemento, hormigón y áridos. Como empresa estamos convencidos que tener un equipo de trabajo diverso y una cultura inclusiva genera beneficios para las personas y el negocio. Actualmente nos encontramos en búsqueda de:Analista de Planificación Comercial.La persona que ocupa el cargo, deberá generar análisis, proyecciones y reportes estratégicos que permitan optimizar la planificación comercial, apoyar la toma de decisiones y contribuir al cumplimiento de metas de venta, rentabilidad y eficiencia operativa.Entre sus principales funciones se encuentran:Elaborar reportes de gestión comercial, análisis de ventas, márgenes, mix de productos y canales.Proyectar demanda y planificar escenarios comerciales.Monitorear KPIs (ventas, forecast accuracy, fill rate, rotación, etc.).Apoyar la definición de presupuestos y metas comerciales.Coordinar con áreas de ventas, marketing, operaciones y finanzas.Identificar oportunidades de mejora en procesos comerciales.Participar en comités de planificación y revisión de resultados.Mantener actualizados los tableros de control y bases de datos comerciales.BeneficiosComo colaborador/a de Polpaico Soluciones, te ofrecemos los siguientes beneficios:- Seguro de vida 100% financiado por la compañía.- Seguro complementario de salud, dental y catastrófico.- Oportunidades de crecimiento y desarrollo profesional a través de becas de estudio.- Excelente ambiente de trabajo.- Algunas de nuestras principales alianzas son: Caja compensación los Andes y FALP (Fundación Arturo López Pérez).</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3576,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Analista Planificación Comercial</t>
+          <t>Ingenieroa de Planificación Demanda - Las Condes</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Polpaico Soluciones</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3596,15 +3596,15 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55927/analista-planificacion-comercial</t>
+          <t>https://firstjob.me/oferta/55928/ingeniero-a-de-planificacion-demanda-las-condes</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>analisis</t>
+          <t>sql, excel</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -3633,29 +3633,29 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>Polpaico Soluciones,es una compañía líder en el mercado nacional de la fabricación y comercialización de cemento, hormigón y áridos. Como empresa estamos convencidos que tener un equipo de trabajo diverso y una cultura inclusiva genera beneficios para las personas y el negocio. Actualmente nos encontramos en búsqueda de:Analista de Planificación Comercial.La persona que ocupa el cargo, deberá generar análisis, proyecciones y reportes estratégicos que permitan optimizar la planificación comercial, apoyar la toma de decisiones y contribuir al cumplimiento de metas de venta, rentabilidad y eficiencia operativa.Entre sus principales funciones se encuentran:Elaborar reportes de gestión comercial, análisis de ventas, márgenes, mix de productos y canales.Proyectar demanda y planificar escenarios comerciales.Monitorear KPIs (ventas, forecast accuracy, fill rate, rotación, etc.).Apoyar la definición de presupuestos y metas comerciales.Coordinar con áreas de ventas, marketing, operaciones y finanzas.Identificar oportunidades de mejora en procesos comerciales.Participar en comités de planificación y revisión de resultados.Mantener actualizados los tableros de control y bases de datos comerciales.BeneficiosComo colaborador/a de Polpaico Soluciones, te ofrecemos los siguientes beneficios:- Seguro de vida 100% financiado por la compañía.- Seguro complementario de salud, dental y catastrófico.- Oportunidades de crecimiento y desarrollo profesional a través de becas de estudio.- Excelente ambiente de trabajo.- Algunas de nuestras principales alianzas son: Caja compensación los Andes y FALP (Fundación Arturo López Pérez).</t>
+          <t>¡En CCU nos apasiona crear experiencias para compartir juntos un mejor vivir!Estamos buscando a nuestro/a próximo/aIngeniero/a de Planificación Demandapara nuestra Gerencia de Planificación Integrada (PPI) en el Edificio Corporativo deLas Condes.Principales funciones:Planificar la demanda de los Centros de Distribución (CDs) para la categoría asignada (Analcoholes), con el objetivo de contar con stock para Canal Tradicional (almacenes y botillerías).Monitorear y analizar KPIs de forecast accuracy, generando reportería para la toma de decisiones.Desarrollar el proceso de planificación de la demanda a fin de generar información para el área de producción, logística, aprovisionamiento, etc.Relacionarse con el área de ventas para recopilar la información de los distintos distritos comerciales con el objetivo de entregar input al equipo de Demanda.Requisitos:Título de Ingeniería Civil Industrial, Ingeniería Comercial o carrera afín.0 - 6 meses de experiencia.Manejo de Excel nivel intermedio y herramientas de Google.Manejo de BBDD SQL deseable.Disponibilidad para trabajar en modalidad presencial en Las Condes y disponibilidad para ir a ruta.Nuestro SER CCU nos inspira a trabajar con aceptación y respeto a las diferencias de las personas, promoviendo un entorno diverso e integrador, para así contribuir a un mejor vivir. Por esto, te agradecemos que nos compartas si necesitas adaptación en alguna etapa del proceso de postulación.¡Te invitamos a SER CCU!</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ingenieroa de Planificación Demanda - Las Condes</t>
+          <t>Ingenieroa Proyectos Innovación y Desarrollo de Productos</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>Enaex</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Las Condes, Metropolitana, Chile</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3665,19 +3665,15 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55928/ingeniero-a-de-planificacion-demanda-las-condes</t>
+          <t>https://firstjob.me/oferta/55982/ingeniero-a-proyectos-innovacion-y-desarrollo-de-productos</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>5</v>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>sql, excel</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -3702,7 +3698,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>¡En CCU nos apasiona crear experiencias para compartir juntos un mejor vivir!Estamos buscando a nuestro/a próximo/aIngeniero/a de Planificación Demandapara nuestra Gerencia de Planificación Integrada (PPI) en el Edificio Corporativo deLas Condes.Principales funciones:Planificar la demanda de los Centros de Distribución (CDs) para la categoría asignada (Analcoholes), con el objetivo de contar con stock para Canal Tradicional (almacenes y botillerías).Monitorear y analizar KPIs de forecast accuracy, generando reportería para la toma de decisiones.Desarrollar el proceso de planificación de la demanda a fin de generar información para el área de producción, logística, aprovisionamiento, etc.Relacionarse con el área de ventas para recopilar la información de los distintos distritos comerciales con el objetivo de entregar input al equipo de Demanda.Requisitos:Título de Ingeniería Civil Industrial, Ingeniería Comercial o carrera afín.0 - 6 meses de experiencia.Manejo de Excel nivel intermedio y herramientas de Google.Manejo de BBDD SQL deseable.Disponibilidad para trabajar en modalidad presencial en Las Condes y disponibilidad para ir a ruta.Nuestro SER CCU nos inspira a trabajar con aceptación y respeto a las diferencias de las personas, promoviendo un entorno diverso e integrador, para así contribuir a un mejor vivir. Por esto, te agradecemos que nos compartas si necesitas adaptación en alguna etapa del proceso de postulación.¡Te invitamos a SER CCU!</t>
+          <t>Nuestra empresa:Enaex es una empresa filial del grupo Sigdo Koppers, con más de 105 años de trayectoria en el mercado de explosivos. Nos hemos consolidado como el tercer productor mundial de Nitrato de Amonio de baja densidad y el principal prestador de servicios integrales de fragmentación de roca para la minería en Chile y Latinoamérica.Queremos invitarte a crecer con nosotros y desafiarte día a día en una compañía cuyo propósito es Humanizar la minería. Si para ti la prioridad es la vida, tu obsesión es la excelencia, tu vocación son los clientes y tienes como fortaleza la innovación y el emprendimiento, ¡este es tu lugar!Misión del cargo:Asegurar la validación en terreno de soluciones innovadoras, conectando la necesidad del cliente con el desarrollo de productos.Descripción del cargo:Propósito del cargo: Asegurar la validación en terreno de soluciones innovadoras, conectando la necesidad del cliente con el desarrollo de productos, para garantizar implementaciones exitosas que generen valor y continuidad operacional.Principales responsabilidades:- Definir pruebas de pilotaje de proyectos de Innovación para ejecutarlas en ambiente controlado y en terreno con clientes.- Articular pruebas de terreno de proyectos de Innovación con diferentes áreas involucradas.- Construir protocolos y reportes de pruebas.- Elaborar documentación de pilotaje y escalamiento de proyectos.- Hacer la conexión de la demanda del usuário y visión del cliente hacia el equipo de desarrollo de productos para articular modificaciones, generando un producto conforme la expectativa y que cumpla con la necesidad del cliente.- Garantizar que la implementación de un nuevo producto alcance continuidad operacional y agregue valor al cliente.- Organizar la primera implementación de productos en escalamiento, y sus posibles adaptaciones, en filiales (otros países) de Enaex.Responde las preguntas en Aira y carga tu currículum actualizado. ¡Esperamos contar contigo!Nuestro Candidato Ideal:Título Ingeniero Civil en Minas o EjecuciónAl menos 2 años de Experiencia en operaciones Mineras implementando nuevos productos; SIE, EMTSDisponibilidad para viajarTurnos 5x2Contar con residencia en Santiago, en Calama o Antofagasta (Deseable)Inglés IntermedioDiscapacidad: Esta vacante es apta para personas con discapacidad.Proceso de selección:El proceso de selección se realiza a través de Aira - plataforma de reclutamiento diseñado para mejorar tu experiencia de postulación.Para postular solo necesitas:1. Postular a la oferta2. Revisar tu email3. Ingresar a Aira y contestar las preguntas y/o pruebas solicitadasLuego, si vemos que tu perfil se ajusta a lo que estamos buscando, te contactaremos por email (a través de Aira) para seguir a la etapa presencial.BeneficiosBeneficios generales</t>
         </is>
       </c>
     </row>
@@ -3714,27 +3710,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ingenieroa Proyectos Innovación y Desarrollo de Productos</t>
+          <t>Supervisora de Oficina en Castro</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Enaex</t>
+          <t>Fondo Esperanza</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Las Condes, Metropolitana, Chile</t>
+          <t>Región de Los Lagos, Chile</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55982/ingeniero-a-proyectos-innovacion-y-desarrollo-de-productos</t>
+          <t>https://firstjob.me/oferta/55981/supervisor-a-de-oficina-en-castro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -3742,13 +3738,13 @@
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
         <v>1</v>
@@ -3767,7 +3763,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>Nuestra empresa:Enaex es una empresa filial del grupo Sigdo Koppers, con más de 105 años de trayectoria en el mercado de explosivos. Nos hemos consolidado como el tercer productor mundial de Nitrato de Amonio de baja densidad y el principal prestador de servicios integrales de fragmentación de roca para la minería en Chile y Latinoamérica.Queremos invitarte a crecer con nosotros y desafiarte día a día en una compañía cuyo propósito es Humanizar la minería. Si para ti la prioridad es la vida, tu obsesión es la excelencia, tu vocación son los clientes y tienes como fortaleza la innovación y el emprendimiento, ¡este es tu lugar!Misión del cargo:Asegurar la validación en terreno de soluciones innovadoras, conectando la necesidad del cliente con el desarrollo de productos.Descripción del cargo:Propósito del cargo: Asegurar la validación en terreno de soluciones innovadoras, conectando la necesidad del cliente con el desarrollo de productos, para garantizar implementaciones exitosas que generen valor y continuidad operacional.Principales responsabilidades:- Definir pruebas de pilotaje de proyectos de Innovación para ejecutarlas en ambiente controlado y en terreno con clientes.- Articular pruebas de terreno de proyectos de Innovación con diferentes áreas involucradas.- Construir protocolos y reportes de pruebas.- Elaborar documentación de pilotaje y escalamiento de proyectos.- Hacer la conexión de la demanda del usuário y visión del cliente hacia el equipo de desarrollo de productos para articular modificaciones, generando un producto conforme la expectativa y que cumpla con la necesidad del cliente.- Garantizar que la implementación de un nuevo producto alcance continuidad operacional y agregue valor al cliente.- Organizar la primera implementación de productos en escalamiento, y sus posibles adaptaciones, en filiales (otros países) de Enaex.Responde las preguntas en Aira y carga tu currículum actualizado. ¡Esperamos contar contigo!Nuestro Candidato Ideal:Título Ingeniero Civil en Minas o EjecuciónAl menos 2 años de Experiencia en operaciones Mineras implementando nuevos productos; SIE, EMTSDisponibilidad para viajarTurnos 5x2Contar con residencia en Santiago, en Calama o Antofagasta (Deseable)Inglés IntermedioDiscapacidad: Esta vacante es apta para personas con discapacidad.Proceso de selección:El proceso de selección se realiza a través de Aira - plataforma de reclutamiento diseñado para mejorar tu experiencia de postulación.Para postular solo necesitas:1. Postular a la oferta2. Revisar tu email3. Ingresar a Aira y contestar las preguntas y/o pruebas solicitadasLuego, si vemos que tu perfil se ajusta a lo que estamos buscando, te contactaremos por email (a través de Aira) para seguir a la etapa presencial.BeneficiosBeneficios generales</t>
+          <t>Impulsa tu talento en un lugar donde la inclusión laboral es prioridadTe proyectas trabajando en una organización apasionada por la superación de la pobreza, donde el foco está en inspirar el desarrollo social de emprendedores de sectores vulnerables, sus familias y comunidades, ampliando sus oportunidades mediante servicios financieros, capacitación y redes.En Fondo Esperanza nos encontramos en búsqueda de un/aSupervisor/a de Oficina(Trabajador/a Social) para integrarse en nuestra oficina ubicada enCastro. Su principal objetivo será supervisar la gestión de los colaboradores de la oficina en coordinación con la jefatura, para el mejoramiento de las condiciones de vida de emprendedores vulnerables, sus familias y comunidades, asegurando la entrega del servicio microfinanciero integral alineado con los valores, misión y visión de Fondo Esperanza🌍 Compromiso con la inclusiónEn Fondo Esperanza valoramos profundamente ladiversidad y la equidadcomo pilares fundamentales de nuestro quehacer. Esta vacante se publica en el marco de laLey 21.015, que promueve la inclusión laboral de personas con discapacidad. Queremos que cada persona encuentre un espacio donde pueda aportar sus talentos y desarrollarse plenamente.Si durante el proceso de postulación o en tu futura experiencia laboral necesitasajustes razonables, te invitamos a informarlo con toda confianza. Promovemos un ambiente derespeto, colaboración y reconocimiento, donde cada persona es valorada por lo que aporta.🎯Principales responsabilidades:Asegurar la entrega del servicio integral de Fondo Esperanza, supervisando la gestión del equipo de acuerdo a los estándares establecidos.Promover en el equipo de trabajo la adecuada utilización de los recursos de la oficina (materiales. humanos, tecnológicos y financieros).Apoyar el cumplimiento de las metas de la oficina y los lineamientos estratégicos de la organización (visión, misión y valores), a través del acompañamiento de los colaboradores y la revisión permanente de los indicadoresCondiciones del cargo:Modalidad semi presencial (Oficina, Terreno y Teletrabajo).Flexibilidad horaria. (Artículo 22, inciso 2)💡Buscamos personas con:Orientación al servicio y trabajo en terreno.Compromiso con la transformación social.Capacidad de planificación, gestión y autonomía.Disponibilidad de viaje.Flexibilidad horaria (se recomienda)Reuniones y Gestiones dentro y fuera de la Oficina¿Y los beneficios?En esta organización, ¡tu bienestar también importa!Te compartimos algunos de los beneficios que entregamos a nuestro equipo:🎁Beneficios:Días administrativosAlianza con Caja de Compensación Los AndesDía libre por cumpleañosConvenio con clínica dentalConvenio con centro de salud mentalConvenio con gimnasioAguinaldos en Fiestas Patrias y Fin de Año🛡Y una vez con contrato indefinido, también accedes a:Seguro complementario Vida CámaraExtensión de vacacionesGift Cards de Escolaridad y NavidadReconocimiento por excelencia académicaReincorporación gradual para mamás y papásFondo de apoyo a la vivienda🌟¿Por qué postular a Fondo Esperanza?Porque trabajamos con propósito, en un entorno colaborativo, transparente y flexible, generando impacto social real. Queremos que tu talento y compromiso sean parte de este camino.BeneficiosTítulo:Trabajador Social y/o Profesional del Área Social.Experiencia:2 años de experiencia laboral:-      Ojalá liderando equipos de personas.-      Gestionando metodologías grupales de intervención  comunitariaFormación:Deseable curso o diplomado en Gestión de PersonasConocimientos Específicos-      Educación de Adultos.-      Conocimiento de gestión de redes.-      Administración de personas.-      Office Intermedio.</t>
         </is>
       </c>
     </row>
@@ -3779,7 +3775,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Supervisora de Oficina en Castro</t>
+          <t>Especialista de Estudios e Impacto</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3789,7 +3785,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Región de Los Lagos, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3799,13 +3795,17 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55981/supervisor-a-de-oficina-en-castro</t>
+          <t>https://firstjob.me/oferta/55980/especialista-de-estudios-e-impacto</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>python, analisis</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -3816,7 +3816,7 @@
         <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>Impulsa tu talento en un lugar donde la inclusión laboral es prioridadTe proyectas trabajando en una organización apasionada por la superación de la pobreza, donde el foco está en inspirar el desarrollo social de emprendedores de sectores vulnerables, sus familias y comunidades, ampliando sus oportunidades mediante servicios financieros, capacitación y redes.En Fondo Esperanza nos encontramos en búsqueda de un/aSupervisor/a de Oficina(Trabajador/a Social) para integrarse en nuestra oficina ubicada enCastro. Su principal objetivo será supervisar la gestión de los colaboradores de la oficina en coordinación con la jefatura, para el mejoramiento de las condiciones de vida de emprendedores vulnerables, sus familias y comunidades, asegurando la entrega del servicio microfinanciero integral alineado con los valores, misión y visión de Fondo Esperanza🌍 Compromiso con la inclusiónEn Fondo Esperanza valoramos profundamente ladiversidad y la equidadcomo pilares fundamentales de nuestro quehacer. Esta vacante se publica en el marco de laLey 21.015, que promueve la inclusión laboral de personas con discapacidad. Queremos que cada persona encuentre un espacio donde pueda aportar sus talentos y desarrollarse plenamente.Si durante el proceso de postulación o en tu futura experiencia laboral necesitasajustes razonables, te invitamos a informarlo con toda confianza. Promovemos un ambiente derespeto, colaboración y reconocimiento, donde cada persona es valorada por lo que aporta.🎯Principales responsabilidades:Asegurar la entrega del servicio integral de Fondo Esperanza, supervisando la gestión del equipo de acuerdo a los estándares establecidos.Promover en el equipo de trabajo la adecuada utilización de los recursos de la oficina (materiales. humanos, tecnológicos y financieros).Apoyar el cumplimiento de las metas de la oficina y los lineamientos estratégicos de la organización (visión, misión y valores), a través del acompañamiento de los colaboradores y la revisión permanente de los indicadoresCondiciones del cargo:Modalidad semi presencial (Oficina, Terreno y Teletrabajo).Flexibilidad horaria. (Artículo 22, inciso 2)💡Buscamos personas con:Orientación al servicio y trabajo en terreno.Compromiso con la transformación social.Capacidad de planificación, gestión y autonomía.Disponibilidad de viaje.Flexibilidad horaria (se recomienda)Reuniones y Gestiones dentro y fuera de la Oficina¿Y los beneficios?En esta organización, ¡tu bienestar también importa!Te compartimos algunos de los beneficios que entregamos a nuestro equipo:🎁Beneficios:Días administrativosAlianza con Caja de Compensación Los AndesDía libre por cumpleañosConvenio con clínica dentalConvenio con centro de salud mentalConvenio con gimnasioAguinaldos en Fiestas Patrias y Fin de Año🛡Y una vez con contrato indefinido, también accedes a:Seguro complementario Vida CámaraExtensión de vacacionesGift Cards de Escolaridad y NavidadReconocimiento por excelencia académicaReincorporación gradual para mamás y papásFondo de apoyo a la vivienda🌟¿Por qué postular a Fondo Esperanza?Porque trabajamos con propósito, en un entorno colaborativo, transparente y flexible, generando impacto social real. Queremos que tu talento y compromiso sean parte de este camino.BeneficiosTítulo:Trabajador Social y/o Profesional del Área Social.Experiencia:2 años de experiencia laboral:-      Ojalá liderando equipos de personas.-      Gestionando metodologías grupales de intervención  comunitariaFormación:Deseable curso o diplomado en Gestión de PersonasConocimientos Específicos-      Educación de Adultos.-      Conocimiento de gestión de redes.-      Administración de personas.-      Office Intermedio.</t>
+          <t>Impulsa tu talento en un lugar donde la inclusión laboral es prioridadTe proyectas trabajando en una organización apasionada por la superación de la pobreza, donde el foco está en inspirar el desarrollo social de emprendedores de sectores vulnerables, sus familias y comunidades, ampliando sus oportunidades mediante servicios financieros, capacitación y redes.En Fondo Esperanza nos encontramos en búsqueda de un/aEspecialista de Estudios e Impactopara sumarse a la Gerencia Comercial y Social. Su principal objetivo será impulsar y desarrollar estudios de diversa índole, colaborando con universidades y otras instituciones para generar conocimiento útil. La finalidad es aportar evidencia sólida que fortalezca la toma de decisiones estratégicas, la incidencia pública y la creación de valor para nuestras socias y la industria de las microfinanzas.🌍 Compromiso con la inclusiónEn Fondo Esperanza valoramos profundamente ladiversidad y la equidadcomo pilares fundamentales de nuestro quehacer. Esta vacante se publica en el marco de laLey 21.015, que promueve la inclusión laboral de personas con discapacidad. Queremos que cada persona encuentre un espacio donde pueda aportar sus talentos y desarrollarse plenamente.Si durante el proceso de postulación o en tu futura experiencia laboral necesitasajustes razonables, te invitamos a informarlo con toda confianza. Promovemos un ambiente derespeto, colaboración y reconocimiento, donde cada persona es valorada por lo que aporta.¿Te proyectas trabajando en una organización apasionada por la superación de la pobreza? En Fondo Esperanza, nuestro foco está en inspirar el desarrollo social de emprendedores de sectores vulnerables, sus familias y comunidades, ampliando sus oportunidades mediante servicios financieros, capacitación y redes.🎯 Principales responsabilidades:Impulsar, coordinar y desarrollar estudios de evaluación de impacto e innovación metodológica a partir del análisis de datos internos y externos.Definir y validar metodologías, instrumentos y modelos de análisis, asegurando su calidad técnica para medir el impacto de los productos y servicios de Fondo Esperanza.Gestionar y asegurar la calidad y robustez de los datos utilizados en los estudios, proponiendo mejoras continuas en su generación y administración.Acompañar a las distintas áreas en la interpretación de hallazgos y en la incorporación de evidencia para la toma de decisiones.Articular y supervisar el trabajo con actores externos como consultores, universidades y centros de investigación, asegurando la alineación con los objetivos institucionales.Proponer nuevas líneas de investigación y mejoras en la gestión de indicadores sociales para identificar oportunidades de innovación.🧠 Requisitos:Formación académica:Sociología, Economía, Ingeniería Comercial, Políticas Públicas, Ciencias Políticas u otras carreras afines.Experiencia laboral:Al menos 3 años en estudios o evaluación de impacto dentro de las políticas públicas, investigación ampliada.Conocimientos técnicos específicos:Métodos avanzados de análisis cuantitativo y cualitativo. (Se requiere cuantitativo)Programación en R, Python o STATA.Manejo de bases de datos relacionales y herramientas de visualización.Conocimiento en evaluación de programas y políticas públicas.Competencias:Pensamiento estratégico y analítico.Capacidad de generar incidencia con evidencia.Comunicación clara de hallazgos a públicos técnicos y no técnicos.Liderazgo técnico y trabajo colaborativo.Innovación metodológica.Condiciones del cargo:Modalidad:Híbrida.Ubicación:Oficina Central.🎁 Beneficios:Días administrativos.Alianza con Caja de Compensación Los Andes.Día libre por cumpleaños.Convenio con clínica dental.Convenio con centro de salud mental.Convenio con gimnasio.Aguinaldos en Fiestas Patrias y Fin de Año.🛡Y una vez con contrato indefinido, también accedes a:Seguro complementario Vida Cámara.Gift Cards de Escolaridad y Navidad.Reconocimiento por excelencia académica.Reincorporación gradual para mamás y papás.Fondo de apoyo a la vivienda.🌟 ¿Por qué postular a Fondo Esperanza?Porque trabajamos con propósito y vivimos nuestros valores día a día. Ponemos a la socia en el centro, enfocándonos en su desarrollo. Creemos que somos un equipo, por eso fomentamos un ambiente colaborativo, positivo y flexible. Promovemos relaciones transparentes, con comunicación abierta y retroalimentación constante. Generamos impacto social real a través de nuestro trabajo ético y comprometido, y siempre aspiramos a más, innovando para llegar más lejos.BeneficiosFormación académica:Sociología, Economía, Ingeniería Comercial, Políticas Públicas, Ciencias Políticas u otras carreras afines.Experiencia laboral:Al menos 3 años en estudios o evaluación de impacto dentro de las políticas públicas, investigación ampliada.Conocimientos técnicos específicos:Métodos avanzados de análisis cuantitativo y cualitativo. (Se requiere cuantitativo)Programación en R, Python o STATA.Manejo de bases de datos relacionales y herramientas de visualización.Conocimiento en evaluación de programas y políticas públicas.Competencias:Pensamiento estratégico y analítico.Capacidad de generar incidencia con evidencia.Comunicación clara de hallazgos a públicos técnicos y no técnicos.Liderazgo técnico y trabajo colaborativo.Innovación metodológica.</t>
         </is>
       </c>
     </row>
@@ -3844,37 +3844,33 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Especialista de Estudios e Impacto</t>
+          <t>Químico Farmacéutico Full Time, Santiago</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Fondo Esperanza</t>
+          <t>Cencosud</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Santiago, Chile</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55980/especialista-de-estudios-e-impacto</t>
+          <t>https://firstjob.me/oferta/55970/quimico-farmaceutico-full-time-santiago</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>4</v>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>python, analisis</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -3882,10 +3878,10 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -3901,7 +3897,7 @@
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>Impulsa tu talento en un lugar donde la inclusión laboral es prioridadTe proyectas trabajando en una organización apasionada por la superación de la pobreza, donde el foco está en inspirar el desarrollo social de emprendedores de sectores vulnerables, sus familias y comunidades, ampliando sus oportunidades mediante servicios financieros, capacitación y redes.En Fondo Esperanza nos encontramos en búsqueda de un/aEspecialista de Estudios e Impactopara sumarse a la Gerencia Comercial y Social. Su principal objetivo será impulsar y desarrollar estudios de diversa índole, colaborando con universidades y otras instituciones para generar conocimiento útil. La finalidad es aportar evidencia sólida que fortalezca la toma de decisiones estratégicas, la incidencia pública y la creación de valor para nuestras socias y la industria de las microfinanzas.🌍 Compromiso con la inclusiónEn Fondo Esperanza valoramos profundamente ladiversidad y la equidadcomo pilares fundamentales de nuestro quehacer. Esta vacante se publica en el marco de laLey 21.015, que promueve la inclusión laboral de personas con discapacidad. Queremos que cada persona encuentre un espacio donde pueda aportar sus talentos y desarrollarse plenamente.Si durante el proceso de postulación o en tu futura experiencia laboral necesitasajustes razonables, te invitamos a informarlo con toda confianza. Promovemos un ambiente derespeto, colaboración y reconocimiento, donde cada persona es valorada por lo que aporta.¿Te proyectas trabajando en una organización apasionada por la superación de la pobreza? En Fondo Esperanza, nuestro foco está en inspirar el desarrollo social de emprendedores de sectores vulnerables, sus familias y comunidades, ampliando sus oportunidades mediante servicios financieros, capacitación y redes.🎯 Principales responsabilidades:Impulsar, coordinar y desarrollar estudios de evaluación de impacto e innovación metodológica a partir del análisis de datos internos y externos.Definir y validar metodologías, instrumentos y modelos de análisis, asegurando su calidad técnica para medir el impacto de los productos y servicios de Fondo Esperanza.Gestionar y asegurar la calidad y robustez de los datos utilizados en los estudios, proponiendo mejoras continuas en su generación y administración.Acompañar a las distintas áreas en la interpretación de hallazgos y en la incorporación de evidencia para la toma de decisiones.Articular y supervisar el trabajo con actores externos como consultores, universidades y centros de investigación, asegurando la alineación con los objetivos institucionales.Proponer nuevas líneas de investigación y mejoras en la gestión de indicadores sociales para identificar oportunidades de innovación.🧠 Requisitos:Formación académica:Sociología, Economía, Ingeniería Comercial, Políticas Públicas, Ciencias Políticas u otras carreras afines.Experiencia laboral:Al menos 3 años en estudios o evaluación de impacto dentro de las políticas públicas, investigación ampliada.Conocimientos técnicos específicos:Métodos avanzados de análisis cuantitativo y cualitativo. (Se requiere cuantitativo)Programación en R, Python o STATA.Manejo de bases de datos relacionales y herramientas de visualización.Conocimiento en evaluación de programas y políticas públicas.Competencias:Pensamiento estratégico y analítico.Capacidad de generar incidencia con evidencia.Comunicación clara de hallazgos a públicos técnicos y no técnicos.Liderazgo técnico y trabajo colaborativo.Innovación metodológica.Condiciones del cargo:Modalidad:Híbrida.Ubicación:Oficina Central.🎁 Beneficios:Días administrativos.Alianza con Caja de Compensación Los Andes.Día libre por cumpleaños.Convenio con clínica dental.Convenio con centro de salud mental.Convenio con gimnasio.Aguinaldos en Fiestas Patrias y Fin de Año.🛡Y una vez con contrato indefinido, también accedes a:Seguro complementario Vida Cámara.Gift Cards de Escolaridad y Navidad.Reconocimiento por excelencia académica.Reincorporación gradual para mamás y papás.Fondo de apoyo a la vivienda.🌟 ¿Por qué postular a Fondo Esperanza?Porque trabajamos con propósito y vivimos nuestros valores día a día. Ponemos a la socia en el centro, enfocándonos en su desarrollo. Creemos que somos un equipo, por eso fomentamos un ambiente colaborativo, positivo y flexible. Promovemos relaciones transparentes, con comunicación abierta y retroalimentación constante. Generamos impacto social real a través de nuestro trabajo ético y comprometido, y siempre aspiramos a más, innovando para llegar más lejos.BeneficiosFormación académica:Sociología, Economía, Ingeniería Comercial, Políticas Públicas, Ciencias Políticas u otras carreras afines.Experiencia laboral:Al menos 3 años en estudios o evaluación de impacto dentro de las políticas públicas, investigación ampliada.Conocimientos técnicos específicos:Métodos avanzados de análisis cuantitativo y cualitativo. (Se requiere cuantitativo)Programación en R, Python o STATA.Manejo de bases de datos relacionales y herramientas de visualización.Conocimiento en evaluación de programas y políticas públicas.Competencias:Pensamiento estratégico y analítico.Capacidad de generar incidencia con evidencia.Comunicación clara de hallazgos a públicos técnicos y no técnicos.Liderazgo técnico y trabajo colaborativo.Innovación metodológica.</t>
+          <t>Si piensas como nosotros que las funciones y el rol del Químico Farmacéutico debe tener estrecha relación con su formación profesional, poniendo como eje central la atención… Entonces este desafío laboral y profesional es para ti!!😀Nos encontramos en búsqueda del mejor Químico Farmacéutico Full Time para nuestra Farmacia Jumbo en nuestro local ubicado en Santiago. Todas las funciones tienen estrecha relación con la formación académica y profesional del Químico Farmacéutico, respetando al 100% la normativa legal y profesional¿Qué esperamos de ti?Elevada ética profesional en el ejercicio de tus funciones.Que te apasione y disfrutes de la atención de clientesTítulo profesional de Químico Farmacéutico (excluyente)Registro al día en la Superintendencia de SaludDisponibilidad para trabajar en turnos rotativosRequisitos de PostulaciónTítulo profesional de Químico Farmacéutico(excluyente)Registro al día en la Superintendencia de SaludDisponibilidad para trabajar Sábado, Domingo y Festivos en turnos rotativosBeneficios¿Qué otras cosas puedes obtener con nosotros?Descuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Seguridad y tranquilidad: todas nuestras Farmacias se encuentran en el interior de nuestros SupermercadosAguinaldo de navidad y fiestas patrias.ColaciónEl mejor lugar para trabajar y estabilidad a toda pruebaY podrás optar a muchos otros beneficios !!¡¡No lo pienses más y sé parte de nuestras Farmacias Jumbo 🐘💚!!</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3909,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Químico Farmacéutico Full Time, Santiago</t>
+          <t>Químico Farmacéutico Full time, Jumbo Rancagua</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3923,7 +3919,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>Loc Jumbo 504- Rancagua (Mall), Chile</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3933,7 +3929,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55970/quimico-farmaceutico-full-time-santiago</t>
+          <t>https://firstjob.me/oferta/55960/quimico-farmaceutico-full-time-jumbo-rancagua</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -3966,7 +3962,7 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>Si piensas como nosotros que las funciones y el rol del Químico Farmacéutico debe tener estrecha relación con su formación profesional, poniendo como eje central la atención… Entonces este desafío laboral y profesional es para ti!!😀Nos encontramos en búsqueda del mejor Químico Farmacéutico Full Time para nuestra Farmacia Jumbo en nuestro local ubicado en Santiago. Todas las funciones tienen estrecha relación con la formación académica y profesional del Químico Farmacéutico, respetando al 100% la normativa legal y profesional¿Qué esperamos de ti?Elevada ética profesional en el ejercicio de tus funciones.Que te apasione y disfrutes de la atención de clientesTítulo profesional de Químico Farmacéutico (excluyente)Registro al día en la Superintendencia de SaludDisponibilidad para trabajar en turnos rotativosRequisitos de PostulaciónTítulo profesional de Químico Farmacéutico(excluyente)Registro al día en la Superintendencia de SaludDisponibilidad para trabajar Sábado, Domingo y Festivos en turnos rotativosBeneficios¿Qué otras cosas puedes obtener con nosotros?Descuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Seguridad y tranquilidad: todas nuestras Farmacias se encuentran en el interior de nuestros SupermercadosAguinaldo de navidad y fiestas patrias.ColaciónEl mejor lugar para trabajar y estabilidad a toda pruebaY podrás optar a muchos otros beneficios !!¡¡No lo pienses más y sé parte de nuestras Farmacias Jumbo 🐘💚!!</t>
+          <t>Si piensas como nosotros que las funciones y el rol del Químico Farmacéutico debe tener estrecha relación con su formación profesional, poniendo como eje central la atención… Entonces este desafío laboral y profesional es para ti!!😀Nos encontramos en búsqueda del mejor Químico Farmacéutico Full Time para nuestra Farmacia Jumbo en nuestro local ubicado en Rancagua. Todas las funciones tienen estrecha relación con la formación académica y profesional del Químico Farmacéutico, respetando al 100% la normativa legal y profesional¿Qué esperamos de ti?Elevada ética profesional en el ejercicio de tus funciones.Que te apasione y disfrutes de la atención de clientesTítulo profesional de Químico Farmacéutico (excluyente)Registro al día en la Superintendencia de SaludDisponibilidad para trabajar en turnos rotativosRequisitos de PostulaciónTítulo profesional de Químico Farmacéutico(excluyente)Registro al dia en la Superintendencia de SaludDisponibilidad para trabajar Sábado, Domingo y Festivos en turnos rotativosBeneficios¿Qué otras cosas puedes obtener con nosotros?Descuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Seguridad y tranquilidad: todas nuestras Farmacias se encuentran en el interior de nuestros SupermercadosAguinaldo de navidad y fiestas patrias.ColaciónEl mejor lugar para trabajar y estabilidad a toda pruebaY podrás optar a muchos otros beneficios !!¡¡No lo pienses más y sé parte de nuestras Farmacias Jumbo 🐘💚!!</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3974,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Químico Farmacéutico Full time, Jumbo Rancagua</t>
+          <t>Químico Farmacéutico Part Time Fines de Semana, Jumbo Rancagua</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3998,7 +3994,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55960/quimico-farmaceutico-full-time-jumbo-rancagua</t>
+          <t>https://firstjob.me/oferta/55959/quimico-farmaceutico-part-time-fines-de-semana-jumbo-rancagua</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -4018,7 +4014,7 @@
         <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
@@ -4031,7 +4027,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>Si piensas como nosotros que las funciones y el rol del Químico Farmacéutico debe tener estrecha relación con su formación profesional, poniendo como eje central la atención… Entonces este desafío laboral y profesional es para ti!!😀Nos encontramos en búsqueda del mejor Químico Farmacéutico Full Time para nuestra Farmacia Jumbo en nuestro local ubicado en Rancagua. Todas las funciones tienen estrecha relación con la formación académica y profesional del Químico Farmacéutico, respetando al 100% la normativa legal y profesional¿Qué esperamos de ti?Elevada ética profesional en el ejercicio de tus funciones.Que te apasione y disfrutes de la atención de clientesTítulo profesional de Químico Farmacéutico (excluyente)Registro al día en la Superintendencia de SaludDisponibilidad para trabajar en turnos rotativosRequisitos de PostulaciónTítulo profesional de Químico Farmacéutico(excluyente)Registro al dia en la Superintendencia de SaludDisponibilidad para trabajar Sábado, Domingo y Festivos en turnos rotativosBeneficios¿Qué otras cosas puedes obtener con nosotros?Descuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Seguridad y tranquilidad: todas nuestras Farmacias se encuentran en el interior de nuestros SupermercadosAguinaldo de navidad y fiestas patrias.ColaciónEl mejor lugar para trabajar y estabilidad a toda pruebaY podrás optar a muchos otros beneficios !!¡¡No lo pienses más y sé parte de nuestras Farmacias Jumbo 🐘💚!!</t>
+          <t>Si piensas como nosotros que las funciones y el rol del Químico Farmacéutico debe tener estrecha relación con su formación profesional, poniendo como eje central la atención… Entonces este desafío laboral y profesional es para ti!!😀Nos encontramos en búsqueda del mejor Químico Farmacéutico Part Time (Fines de semana, 20 horas) para nuestra Farmacia Jumbo Rancagua. Todas las funciones tienen estrecha relación con la formación académica y profesional del Químico Farmacéutico, respetando al 100% la normativa legal y profesionalRequisitos de PostulaciónElevada ética profesional en el ejercicio de tus funciones.Que te apasione y disfrutes de la atención de clientesTítulo profesional de Químico Farmacéutico (excluyente)Registro al día en la Superintendencia de SaludDisponibilidad para trabajar en turnos rotativosBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Seguridad y tranquilidad: todas nuestras Farmacias se encuentran en el interior de nuestros SupermercadosAguinaldo de navidad y fiestas patrias.ColaciónEl mejor lugar para trabajar y estabilidad a toda pruebaY podrás optar a muchos otros beneficios !!¡¡No lo pienses más y sé parte de nuestras Farmacias Jumbo 🐘💚!!</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4039,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Químico Farmacéutico Part Time Fines de Semana, Jumbo Rancagua</t>
+          <t>Quimico Farmacéutico Part Time fines de semana, Santiago</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4053,7 +4049,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Loc Jumbo 504- Rancagua (Mall), Chile</t>
+          <t>Santiago, Chile</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4063,7 +4059,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55959/quimico-farmaceutico-part-time-fines-de-semana-jumbo-rancagua</t>
+          <t>https://firstjob.me/oferta/55958/quimico-farmaceutico-part-time-fines-de-semana-santiago</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -4096,7 +4092,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>Si piensas como nosotros que las funciones y el rol del Químico Farmacéutico debe tener estrecha relación con su formación profesional, poniendo como eje central la atención… Entonces este desafío laboral y profesional es para ti!!😀Nos encontramos en búsqueda del mejor Químico Farmacéutico Part Time (Fines de semana, 20 horas) para nuestra Farmacia Jumbo Rancagua. Todas las funciones tienen estrecha relación con la formación académica y profesional del Químico Farmacéutico, respetando al 100% la normativa legal y profesionalRequisitos de PostulaciónElevada ética profesional en el ejercicio de tus funciones.Que te apasione y disfrutes de la atención de clientesTítulo profesional de Químico Farmacéutico (excluyente)Registro al día en la Superintendencia de SaludDisponibilidad para trabajar en turnos rotativosBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Seguridad y tranquilidad: todas nuestras Farmacias se encuentran en el interior de nuestros SupermercadosAguinaldo de navidad y fiestas patrias.ColaciónEl mejor lugar para trabajar y estabilidad a toda pruebaY podrás optar a muchos otros beneficios !!¡¡No lo pienses más y sé parte de nuestras Farmacias Jumbo 🐘💚!!</t>
+          <t>Si piensas como nosotros que las funciones y el rol del Químico Farmacéutico debe tener estrecha relación con su formación profesional, poniendo como eje central la atención… Entonces este desafío laboral y profesional es para ti!!😀Nos encontramos en búsqueda del mejor Químico Farmacéutico Part Time (Fines de semana, 20 horas) para nuestra Farmacia Jumbo, Santiago. Todas las funciones tienen estrecha relación con la formación académica y profesional del Químico Farmacéutico, respetando al 100% la normativa legal y profesionalRequisitos de PostulaciónElevada ética profesional en el ejercicio de tus funciones.Que te apasione y disfrutes de la atención de clientesTítulo profesional de Químico Farmacéutico (excluyente)Registro al día en la Superintendencia de SaludDisponibilidad para trabajar en turnos rotativosBeneficios¿Qué otras cosas puedes obtener con nosotros?Descuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Seguridad y tranquilidad: todas nuestras Farmacias se encuentran en el interior de nuestros SupermercadosAguinaldo de navidad y fiestas patrias.ColaciónEl mejor lugar para trabajar y estabilidad a toda pruebaY podrás optar a muchos otros beneficios !!¡¡No lo pienses más y sé parte de nuestras Farmacias Jumbo 🐘💚!!</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4104,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Quimico Farmacéutico Part Time fines de semana, Santiago</t>
+          <t>Auxiliar de Farmacia PT 20 hrs. (Fines de semana) - Jumbo El Belloto</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4118,7 +4114,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>Lc Jumbo 781-El Belloto (Mall), Chile</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4128,7 +4124,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55958/quimico-farmaceutico-part-time-fines-de-semana-santiago</t>
+          <t>https://firstjob.me/oferta/55946/auxiliar-de-farmacia-pt-20-hrs-fines-de-semana-jumbo-el-belloto</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -4148,7 +4144,7 @@
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
@@ -4161,7 +4157,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>Si piensas como nosotros que las funciones y el rol del Químico Farmacéutico debe tener estrecha relación con su formación profesional, poniendo como eje central la atención… Entonces este desafío laboral y profesional es para ti!!😀Nos encontramos en búsqueda del mejor Químico Farmacéutico Part Time (Fines de semana, 20 horas) para nuestra Farmacia Jumbo, Santiago. Todas las funciones tienen estrecha relación con la formación académica y profesional del Químico Farmacéutico, respetando al 100% la normativa legal y profesionalRequisitos de PostulaciónElevada ética profesional en el ejercicio de tus funciones.Que te apasione y disfrutes de la atención de clientesTítulo profesional de Químico Farmacéutico (excluyente)Registro al día en la Superintendencia de SaludDisponibilidad para trabajar en turnos rotativosBeneficios¿Qué otras cosas puedes obtener con nosotros?Descuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Seguridad y tranquilidad: todas nuestras Farmacias se encuentran en el interior de nuestros SupermercadosAguinaldo de navidad y fiestas patrias.ColaciónEl mejor lugar para trabajar y estabilidad a toda pruebaY podrás optar a muchos otros beneficios !!¡¡No lo pienses más y sé parte de nuestras Farmacias Jumbo 🐘💚!!</t>
+          <t>¡Porque en Jumbo somos expertos en brindar una buena atención, sabemos que tú eres el indicado para formar parte de nuestro equipo como nuestro nuevo Auxiliar de Farmacia PartTime 20 hrs (FIN DE SEMANA) para apoyar en nuestro Jumbo el Belloto.Las Principales funciones del cargo son colaborar en la dispensación, expendio y/o venta, gestión de almacenamiento, y todo lo concerniente a los medicamentos en la Farmacia.Requisitos de PostulaciónCarnét o Certificado de Auxiliar de Farmacia otorgado por el MINSAL o SEREMI (excluyente)Técnico medio/ colegio técnicoDominio ComputacionalBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Aguinaldo de navidad y fiestas patrias.Bono por vacaciones.Y podrás optar a muchos otros, como un completo Seguro Complementario de Salud, Bono por Escolaridad, Bono por nacimiento de hijo(a), entre otros.Te invitamos a vivir una gran experiencia, donde existen espacios INCLUSIVOS en los que se valoran tus capacidades, convicciones, competencias, experiencia y te desafiamos a desarrollarte constantemente junto a nosotros.</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4169,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Auxiliar de Farmacia PT 20 hrs. (Fines de semana) - Jumbo El Belloto</t>
+          <t>Auxiliar de Farmacia Full Time - Jumbo El Belloto</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4193,7 +4189,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55946/auxiliar-de-farmacia-pt-20-hrs-fines-de-semana-jumbo-el-belloto</t>
+          <t>https://firstjob.me/oferta/55945/auxiliar-de-farmacia-full-time-jumbo-el-belloto</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -4226,7 +4222,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>¡Porque en Jumbo somos expertos en brindar una buena atención, sabemos que tú eres el indicado para formar parte de nuestro equipo como nuestro nuevo Auxiliar de Farmacia PartTime 20 hrs (FIN DE SEMANA) para apoyar en nuestro Jumbo el Belloto.Las Principales funciones del cargo son colaborar en la dispensación, expendio y/o venta, gestión de almacenamiento, y todo lo concerniente a los medicamentos en la Farmacia.Requisitos de PostulaciónCarnét o Certificado de Auxiliar de Farmacia otorgado por el MINSAL o SEREMI (excluyente)Técnico medio/ colegio técnicoDominio ComputacionalBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Aguinaldo de navidad y fiestas patrias.Bono por vacaciones.Y podrás optar a muchos otros, como un completo Seguro Complementario de Salud, Bono por Escolaridad, Bono por nacimiento de hijo(a), entre otros.Te invitamos a vivir una gran experiencia, donde existen espacios INCLUSIVOS en los que se valoran tus capacidades, convicciones, competencias, experiencia y te desafiamos a desarrollarte constantemente junto a nosotros.</t>
+          <t>¡Porque en Jumbo somos expertos en brindar una buena atención, sabemos que tú eres el indicado para formar parte de nuestro equipo como nuestro nuevo Auxiliar de Farmacia Full Time para apoyar en nuestro Jumbo El BellotoLas Principales funciones del cargo son colaborar en la dispensación, expendio y/o venta, gestión de almacenamiento, y todo lo concerniente a los medicamentos en la Farmacia.Requisitos de PostulaciónCarnét o Certificado de Auxiliar de Farmacia otorgado por el MINSAL o SEREMI (excluyente)Técnico medio/ colegio técnicoDominio ComputacionalBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Aguinaldo de navidad y fiestas patrias.Bono por vacaciones.Y podrás optar a muchos otros, como un completo Seguro Complementario de Salud, Bono por Escolaridad, Bono por nacimiento de hijo(a), entre otros.Te invitamos a vivir una gran experiencia, donde existen espacios INCLUSIVOS en los que se valoran tus capacidades, convicciones, competencias, experiencia y te desafiamos a desarrollarte constantemente junto a nosotros.</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4234,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Auxiliar de Farmacia Full Time - Jumbo El Belloto</t>
+          <t>Auxiliar de Farmacia Full Time - Jumbo La Reina</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4248,7 +4244,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Lc Jumbo 781-El Belloto (Mall), Chile</t>
+          <t>Loc Jumbo 512-La Reina (Mall), Chile</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4258,7 +4254,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55945/auxiliar-de-farmacia-full-time-jumbo-el-belloto</t>
+          <t>https://firstjob.me/oferta/55944/auxiliar-de-farmacia-full-time-jumbo-la-reina</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -4291,7 +4287,7 @@
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>¡Porque en Jumbo somos expertos en brindar una buena atención, sabemos que tú eres el indicado para formar parte de nuestro equipo como nuestro nuevo Auxiliar de Farmacia Full Time para apoyar en nuestro Jumbo El BellotoLas Principales funciones del cargo son colaborar en la dispensación, expendio y/o venta, gestión de almacenamiento, y todo lo concerniente a los medicamentos en la Farmacia.Requisitos de PostulaciónCarnét o Certificado de Auxiliar de Farmacia otorgado por el MINSAL o SEREMI (excluyente)Técnico medio/ colegio técnicoDominio ComputacionalBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Aguinaldo de navidad y fiestas patrias.Bono por vacaciones.Y podrás optar a muchos otros, como un completo Seguro Complementario de Salud, Bono por Escolaridad, Bono por nacimiento de hijo(a), entre otros.Te invitamos a vivir una gran experiencia, donde existen espacios INCLUSIVOS en los que se valoran tus capacidades, convicciones, competencias, experiencia y te desafiamos a desarrollarte constantemente junto a nosotros.</t>
+          <t>¡Porque en Jumbo somos expertos en brindar una buena atención, sabemos que tú eres el indicado para formar parte de nuestro equipo como nuestro nuevo Auxiliar de Farmacia Full Time para apoyar en nuestro Jumbo La Reina.Las Principales funciones del cargo son colaborar en la dispensación, expendio y/o venta, gestión de almacenamiento, y todo lo concerniente a los medicamentos en la Farmacia.Requisitos de PostulaciónCarnét o Certificado de Auxiliar de Farmacia otorgado por el MINSAL o SEREMI (excluyente)Técnico medio/ colegio técnicoDominio ComputacionalBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Aguinaldo de navidad y fiestas patrias.Bono por vacaciones.Y podrás optar a muchos otros, como un completo Seguro Complementario de Salud, Bono por Escolaridad, Bono por nacimiento de hijo(a), entre otros.Te invitamos a vivir una gran experiencia, donde existen espacios INCLUSIVOS en los que se valoran tus capacidades, convicciones, competencias, experiencia y te desafiamos a desarrollarte constantemente junto a nosotros.</t>
         </is>
       </c>
     </row>
@@ -4303,33 +4299,37 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Auxiliar de Farmacia Full Time - Jumbo La Reina</t>
+          <t>Práctica Profesional - Auditoría TI</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cencosud</t>
+          <t>Ripley chile</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Loc Jumbo 512-La Reina (Mall), Chile</t>
+          <t>Ofi. Alonso De Cordova 5320 - Auditoria, Chile</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55944/auxiliar-de-farmacia-full-time-jumbo-la-reina</t>
+          <t>https://firstjob.me/oferta/55979/practica-profesional-auditoria-ti</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>analisis, informatica</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -4337,26 +4337,26 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>¡Porque en Jumbo somos expertos en brindar una buena atención, sabemos que tú eres el indicado para formar parte de nuestro equipo como nuestro nuevo Auxiliar de Farmacia Full Time para apoyar en nuestro Jumbo La Reina.Las Principales funciones del cargo son colaborar en la dispensación, expendio y/o venta, gestión de almacenamiento, y todo lo concerniente a los medicamentos en la Farmacia.Requisitos de PostulaciónCarnét o Certificado de Auxiliar de Farmacia otorgado por el MINSAL o SEREMI (excluyente)Técnico medio/ colegio técnicoDominio ComputacionalBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Aguinaldo de navidad y fiestas patrias.Bono por vacaciones.Y podrás optar a muchos otros, como un completo Seguro Complementario de Salud, Bono por Escolaridad, Bono por nacimiento de hijo(a), entre otros.Te invitamos a vivir una gran experiencia, donde existen espacios INCLUSIVOS en los que se valoran tus capacidades, convicciones, competencias, experiencia y te desafiamos a desarrollarte constantemente junto a nosotros.</t>
+          <t>🚀 ¡Buscamos a nuestro/a próximo/a Practicante para Auditoría TI en la Gerencia de Contraloría de Banco Ripley! 💜Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Banco Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro.Ser parte de Banco Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te motiva ser parte de un negocio desafiante y que tu práctica tenga impacto real? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Apoyar al equipo de Auditoría TI en la evaluación independiente y objetiva de los controles tecnológicos, la gestión de riesgos y el cumplimiento normativo del Banco, contribuyendo al fortalecimiento del sistema de control interno, la seguridad de la información y la protección de los activos tecnológicos mediante el uso de herramientas innovadoras y tecnologías emergentes.Funciones: 🤩• Apoyar en la revisión y evaluación de controles de seguridad tecnológica, identificando oportunidades de mejora y fortalecimiento del ambiente de control.• Colaborar en la creación y desarrollo de agentes y soluciones basadas en Inteligencia Artificial para optimizar procesos de auditoría y análisis.• Participar en el seguimiento de planes de acción derivados de auditorías, asegurando la correcta implementación de medidas correctivas.• Apoyar en la evaluación de controles generales de tecnología (ITGC) y prácticas relacionadas con ciberseguridad.• Colaborar en iniciativas de mejora continua relacionadas con auditoría tecnológica, gestión de riesgos y control interno.¿Qué estamos buscando? 💡• Estudiante de Ingeniería en Informática, Ingeniería en Ciberseguridad, Auditoría en Sistemas de Información o carrera afín.• Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)• Disponibilidad de 3 a 6 meses para realizar la práctica.• Conocimientos en estándares de seguridad de la información y ciberseguridad.• Conocimientos de controles generales de tecnología (ITGC).• Interés por auditoría tecnológica, gestión de riesgos, seguridad de la información e Inteligencia Artificial.• Deseable conocimiento o experiencia en herramientas de IA y automatización.• Capacidad analítica, curiosidad tecnológica y orientación al aprendizaje continuo.¿Por qué trabajar en Banco Ripley? 💜Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
         </is>
       </c>
     </row>
@@ -4368,37 +4368,33 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Práctica Profesional - Auditoría TI</t>
+          <t>Auxiliar de farmacia Full Time Jumbo Santiago</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ripley chile</t>
+          <t>Cencosud</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ofi. Alonso De Cordova 5320 - Auditoria, Chile</t>
+          <t>Santiago, Chile</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55979/practica-profesional-auditoria-ti</t>
+          <t>https://firstjob.me/oferta/55969/auxiliar-de-farmacia-full-time-jumbo-santiago</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>analisis, informatica</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -4406,26 +4402,26 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>🚀 ¡Buscamos a nuestro/a próximo/a Practicante para Auditoría TI en la Gerencia de Contraloría de Banco Ripley! 💜Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Banco Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro.Ser parte de Banco Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te motiva ser parte de un negocio desafiante y que tu práctica tenga impacto real? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Apoyar al equipo de Auditoría TI en la evaluación independiente y objetiva de los controles tecnológicos, la gestión de riesgos y el cumplimiento normativo del Banco, contribuyendo al fortalecimiento del sistema de control interno, la seguridad de la información y la protección de los activos tecnológicos mediante el uso de herramientas innovadoras y tecnologías emergentes.Funciones: 🤩• Apoyar en la revisión y evaluación de controles de seguridad tecnológica, identificando oportunidades de mejora y fortalecimiento del ambiente de control.• Colaborar en la creación y desarrollo de agentes y soluciones basadas en Inteligencia Artificial para optimizar procesos de auditoría y análisis.• Participar en el seguimiento de planes de acción derivados de auditorías, asegurando la correcta implementación de medidas correctivas.• Apoyar en la evaluación de controles generales de tecnología (ITGC) y prácticas relacionadas con ciberseguridad.• Colaborar en iniciativas de mejora continua relacionadas con auditoría tecnológica, gestión de riesgos y control interno.¿Qué estamos buscando? 💡• Estudiante de Ingeniería en Informática, Ingeniería en Ciberseguridad, Auditoría en Sistemas de Información o carrera afín.• Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)• Disponibilidad de 3 a 6 meses para realizar la práctica.• Conocimientos en estándares de seguridad de la información y ciberseguridad.• Conocimientos de controles generales de tecnología (ITGC).• Interés por auditoría tecnológica, gestión de riesgos, seguridad de la información e Inteligencia Artificial.• Deseable conocimiento o experiencia en herramientas de IA y automatización.• Capacidad analítica, curiosidad tecnológica y orientación al aprendizaje continuo.¿Por qué trabajar en Banco Ripley? 💜Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
+          <t>¡Porque en Jumbo somos expertos en brindar una buena atención, sabemos que tú eres el indicado para formar parte de nuestro equipo como nuestro nuevo Auxiliar de Farmacia Full Time para apoyar en nuestro Jumbo Santiago.Las Principales funciones del cargo son colaborar en la dispensación, expendio y/o venta, gestión de almacenamiento, y todo lo concerniente a los medicamentos en la Farmacia.Requisitos de PostulaciónCarnét o Certificado de Auxiliar de Farmacia otorgado por el MINSAL o SEREMI (excluyente)Técnico medio/ colegio técnicoDominio ComputacionalBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Aguinaldo de navidad y fiestas patrias.Bono por vacaciones.Y podrás optar a muchos otros, como un completo Seguro Complementario de Salud, Bono por Escolaridad, Bono por nacimiento de hijo(a), entre otros.Te invitamos a vivir una gran experiencia, donde existen espacios INCLUSIVOS en los que se valoran tus capacidades, convicciones, competencias, experiencia y te desafiamos a desarrollarte constantemente junto a nosotros.</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4433,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Auxiliar de farmacia Full Time Jumbo Santiago</t>
+          <t>Auxiliar de Farmacia PT 20 hrs. (Fines de semana) - Jumbo Santiago</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4457,7 +4453,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55969/auxiliar-de-farmacia-full-time-jumbo-santiago</t>
+          <t>https://firstjob.me/oferta/55948/auxiliar-de-farmacia-pt-20-hrs-fines-de-semana-jumbo-santiago</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -4490,29 +4486,29 @@
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>¡Porque en Jumbo somos expertos en brindar una buena atención, sabemos que tú eres el indicado para formar parte de nuestro equipo como nuestro nuevo Auxiliar de Farmacia Full Time para apoyar en nuestro Jumbo Santiago.Las Principales funciones del cargo son colaborar en la dispensación, expendio y/o venta, gestión de almacenamiento, y todo lo concerniente a los medicamentos en la Farmacia.Requisitos de PostulaciónCarnét o Certificado de Auxiliar de Farmacia otorgado por el MINSAL o SEREMI (excluyente)Técnico medio/ colegio técnicoDominio ComputacionalBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Aguinaldo de navidad y fiestas patrias.Bono por vacaciones.Y podrás optar a muchos otros, como un completo Seguro Complementario de Salud, Bono por Escolaridad, Bono por nacimiento de hijo(a), entre otros.Te invitamos a vivir una gran experiencia, donde existen espacios INCLUSIVOS en los que se valoran tus capacidades, convicciones, competencias, experiencia y te desafiamos a desarrollarte constantemente junto a nosotros.</t>
+          <t>¡Porque en Jumbo somos expertos en brindar una buena atención, sabemos que tú eres el indicado para formar parte de nuestro equipo como nuestro nuevo Auxiliar de Farmacia PartTime 20 hrs (FIN DE SEMANA) para apoyar en un Jumbo en Santiago.Las Principales funciones del cargo son colaborar en la dispensación, expendio y/o venta, gestión de almacenamiento, y todo lo concerniente a los medicamentos en la Farmacia.Requisitos de PostulaciónCarnét o Certificado de Auxiliar de Farmacia otorgado por el MINSAL o SEREMI (excluyente)Técnico medio/ colegio técnicoDominio ComputacionalBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Aguinaldo de navidad y fiestas patrias.Bono por vacaciones.Y podrás optar a muchos otros, como un completo Seguro Complementario de Salud, Bono por Escolaridad, Bono por nacimiento de hijo(a), entre otros.Te invitamos a vivir una gran experiencia, donde existen espacios INCLUSIVOS en los que se valoran tus capacidades, convicciones, competencias, experiencia y te desafiamos a desarrollarte constantemente junto a nosotros.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Auxiliar de Farmacia PT 20 hrs. (Fines de semana) - Jumbo Santiago</t>
+          <t>Analista Jr Calidad Plantas</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cencosud</t>
+          <t>Alsea Colombia</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Santiago, Chile</t>
+          <t>Medellín, Colombia</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4522,13 +4518,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55948/auxiliar-de-farmacia-pt-20-hrs-fines-de-semana-jumbo-santiago</t>
+          <t>https://firstjob.me/oferta/56010/analista-jr-calidad-plantas</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>¡Porque en Jumbo somos expertos en brindar una buena atención, sabemos que tú eres el indicado para formar parte de nuestro equipo como nuestro nuevo Auxiliar de Farmacia PartTime 20 hrs (FIN DE SEMANA) para apoyar en un Jumbo en Santiago.Las Principales funciones del cargo son colaborar en la dispensación, expendio y/o venta, gestión de almacenamiento, y todo lo concerniente a los medicamentos en la Farmacia.Requisitos de PostulaciónCarnét o Certificado de Auxiliar de Farmacia otorgado por el MINSAL o SEREMI (excluyente)Técnico medio/ colegio técnicoDominio ComputacionalBeneficiosDescuentos Cruzados: Podrás comprar con descuentos no solo en Jumbo, sino que también en las distintas unidades de negocio de Cencosud: Easy, Santa Isabel, y Paris.Aguinaldo de navidad y fiestas patrias.Bono por vacaciones.Y podrás optar a muchos otros, como un completo Seguro Complementario de Salud, Bono por Escolaridad, Bono por nacimiento de hijo(a), entre otros.Te invitamos a vivir una gran experiencia, donde existen espacios INCLUSIVOS en los que se valoran tus capacidades, convicciones, competencias, experiencia y te desafiamos a desarrollarte constantemente junto a nosotros.</t>
+          <t>💥¿Quieres ser parte de nuestro equipo?Nos encontramos en busqueda de nuestro proximo/a Analista de Calidad Plantas que quiera ser parte de una compañía líder en el sector de restaurantes y food service, aportando al fortalecimiento de nuestros estándares de calidad e inocuidad alimentaria.Si te apasiona la mejora continua, los procesos productivos y el desarrollo de culturas de calidad, esta oportunidad es para ti.¿Cuál será tu proposito?Asegurar el cumplimiento de los estándares de calidad e inocuidad alimentaria en nuestras plantas de producción, contribuyendo a la implementación, mantenimiento y mejora continua de los sistemas de gestión, garantizando productos seguros y procesos alineados con la normativa vigente.📍 Medellín / Bello, Colombia🌟 Responsabilidades:Velar por el cumplimiento de los estándares de calidad e inocuidad en las plantas de producción.Implementar y fortalecer los sistemas de gestión de calidad y seguridad alimentaria.Realizar seguimiento a indicadores, auditorías y planes de acción asociados a la mejora continua.Capacitar y acompañar a los equipos operativos en materias de calidad e inocuidad.Promover una cultura de calidad, colaborando transversalmente con las distintas áreas de la operación.Capacitar y acompañar a los equipos de planta en materias de seguridad alimentaria.Promover el fortalecimiento de la cultura de calidad dentro de la operación.Coordinar acciones con áreas de Producción, Mantenimiento, Compras, SST, Logística y Recursos Humanos.Identificar oportunidades de mejora y proponer cambios que fortalezcan los procesos productivos y el sistema de gestión.RequisitosProfesional en Ingeniería en Alimentos, Microbiología o carreras afines.Al menos 2 años de experiencia en calidad dentro de plantas de producción de alimentos.Conocimiento de BPM, HACCP y sistemas de gestión de inocuidad alimentaria.Experiencia en auditorías y seguimiento de planes de acción.Manejo de Excel intermedio.Beneficios👪 En nuestro equipo:👉 Demostramos pasión por la excelencia y buscamos superar cada desafío.👉 Impulsamos una cultura de reconocimiento y gratitud en todo lo que hacemos.👉 Creamos experiencias únicas, llenas de sabor y cercanía.👉 Somos impacto positivo, comprometidos con el negocio, las personas y el entorno.¿Cuál es nuestro compromiso? Te sumas a una compañía con una cultura diversa e inclusiva, donde promovemos un ambiente de respeto, colaboración y oportunidades de desarrollo, valorando el aporte único de cada persona.❤️ En Alsea somos la suma de experiencias únicas y espacios para ser felices. ¿Te unes? 😎</t>
         </is>
       </c>
     </row>
@@ -4567,37 +4567,33 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Analista Jr Calidad Plantas</t>
+          <t>Asistente contable (Outsourcing)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Alsea Colombia</t>
+          <t>Forvis Mazars</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Medellín, Colombia</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56010/analista-jr-calidad-plantas</t>
+          <t>https://firstjob.me/oferta/56003/asistente-contable-outsourcing</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>2</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>excel</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -4605,10 +4601,10 @@
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
         <v>0</v>
@@ -4624,7 +4620,7 @@
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>💥¿Quieres ser parte de nuestro equipo?Nos encontramos en busqueda de nuestro proximo/a Analista de Calidad Plantas que quiera ser parte de una compañía líder en el sector de restaurantes y food service, aportando al fortalecimiento de nuestros estándares de calidad e inocuidad alimentaria.Si te apasiona la mejora continua, los procesos productivos y el desarrollo de culturas de calidad, esta oportunidad es para ti.¿Cuál será tu proposito?Asegurar el cumplimiento de los estándares de calidad e inocuidad alimentaria en nuestras plantas de producción, contribuyendo a la implementación, mantenimiento y mejora continua de los sistemas de gestión, garantizando productos seguros y procesos alineados con la normativa vigente.📍 Medellín / Bello, Colombia🌟 Responsabilidades:Velar por el cumplimiento de los estándares de calidad e inocuidad en las plantas de producción.Implementar y fortalecer los sistemas de gestión de calidad y seguridad alimentaria.Realizar seguimiento a indicadores, auditorías y planes de acción asociados a la mejora continua.Capacitar y acompañar a los equipos operativos en materias de calidad e inocuidad.Promover una cultura de calidad, colaborando transversalmente con las distintas áreas de la operación.Capacitar y acompañar a los equipos de planta en materias de seguridad alimentaria.Promover el fortalecimiento de la cultura de calidad dentro de la operación.Coordinar acciones con áreas de Producción, Mantenimiento, Compras, SST, Logística y Recursos Humanos.Identificar oportunidades de mejora y proponer cambios que fortalezcan los procesos productivos y el sistema de gestión.RequisitosProfesional en Ingeniería en Alimentos, Microbiología o carreras afines.Al menos 2 años de experiencia en calidad dentro de plantas de producción de alimentos.Conocimiento de BPM, HACCP y sistemas de gestión de inocuidad alimentaria.Experiencia en auditorías y seguimiento de planes de acción.Manejo de Excel intermedio.Beneficios👪 En nuestro equipo:👉 Demostramos pasión por la excelencia y buscamos superar cada desafío.👉 Impulsamos una cultura de reconocimiento y gratitud en todo lo que hacemos.👉 Creamos experiencias únicas, llenas de sabor y cercanía.👉 Somos impacto positivo, comprometidos con el negocio, las personas y el entorno.¿Cuál es nuestro compromiso? Te sumas a una compañía con una cultura diversa e inclusiva, donde promovemos un ambiente de respeto, colaboración y oportunidades de desarrollo, valorando el aporte único de cada persona.❤️ En Alsea somos la suma de experiencias únicas y espacios para ser felices. ¿Te unes? 😎</t>
+          <t>Con nosotros tienes la oportunidad de pertenecer a una firma internacional con un importante potencial de crecimiento y un equipo de más de 40.000 profesionales altamente capacitados, que brinda servicios profesionales generando alto impacto en todos nuestros clientes en más de 100 países en los cinco continentes.Podrás formar parte de un equipo que valorará tus ideas, apoyará tus ambiciones y celebrará tus éxitos. En Forvis Mazars nos proponemos impulsar la colaboración y la flexibilidad, las diversas perspectivas de nuestros colaboradores y el progreso.Hoy buscamos un/aAsistente Contablepara integrarse a nuestro equipo de Outsourcing. La persona será responsable de apoyar la gestión contable y administrativa de una cartera de clientes, asegurando el registro oportuno y correcto de la información financiera, el cumplimiento de procedimientos internos y el apoyo en procesos tributarios y administrativos.Tareas y ResponsabilidadesRegistrar transacciones contables de clientes en los sistemas definidos.Preparar y mantener actualizados los registros contables de la cartera de clientes asignada.Gestionar y mantener la documentación contable y administrativa, tanto física como digital.Revisar y actualizar información contable en ERP y sistemas de gestión.Apoyar en la elaboración de reportes e informes requeridos por clientes y la jefatura.Cumplir con los procedimientos, políticas internas y estándares de calidad establecidos para el servicio.RequisitosTécnico de Nivel Superior en Contabilidad General, Contador Auditor o carrera afín.Hasta 2 años de experiencia.Deseable experiencia en funciones administrativas y/o contables.Manejo de Microsoft Office.Conocimientos de ERP contables.Conocimientos básicos de normativa contable y tributaria.Capacidad de organización y atención al detalle.Deseable experiencia trabajando con carteras de clientes o servicios de outsourcing.OfrecemosPaquete de compensaciones de mercadoSeguro Complementarios de salud y Dental, además de seguro de VidaUna experiencia dinámica, diversa e inclusiva, en una Firma con orientación en las personas, desarrollo y crecimientoEducación continua, tanto de programas internos, corporativos y externosDías adicionales de vacaciones.Este cargo es compatible para personas con discapacidad, se enmarca en la ley 21.015, que incentiva la inclusión de personas con discapacidad al mundo laboral.</t>
         </is>
       </c>
     </row>
@@ -4636,17 +4632,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Asistente contable (Outsourcing)</t>
+          <t>Analista Actuarial</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Forvis Mazars</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4656,15 +4652,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56003/asistente-contable-outsourcing</t>
+          <t>https://firstjob.me/oferta/56011/analista-actuarial</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>python, analisis, estadistica, matematica</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -4685,33 +4685,33 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>Con nosotros tienes la oportunidad de pertenecer a una firma internacional con un importante potencial de crecimiento y un equipo de más de 40.000 profesionales altamente capacitados, que brinda servicios profesionales generando alto impacto en todos nuestros clientes en más de 100 países en los cinco continentes.Podrás formar parte de un equipo que valorará tus ideas, apoyará tus ambiciones y celebrará tus éxitos. En Forvis Mazars nos proponemos impulsar la colaboración y la flexibilidad, las diversas perspectivas de nuestros colaboradores y el progreso.Hoy buscamos un/aAsistente Contablepara integrarse a nuestro equipo de Outsourcing. La persona será responsable de apoyar la gestión contable y administrativa de una cartera de clientes, asegurando el registro oportuno y correcto de la información financiera, el cumplimiento de procedimientos internos y el apoyo en procesos tributarios y administrativos.Tareas y ResponsabilidadesRegistrar transacciones contables de clientes en los sistemas definidos.Preparar y mantener actualizados los registros contables de la cartera de clientes asignada.Gestionar y mantener la documentación contable y administrativa, tanto física como digital.Revisar y actualizar información contable en ERP y sistemas de gestión.Apoyar en la elaboración de reportes e informes requeridos por clientes y la jefatura.Cumplir con los procedimientos, políticas internas y estándares de calidad establecidos para el servicio.RequisitosTécnico de Nivel Superior en Contabilidad General, Contador Auditor o carrera afín.Hasta 2 años de experiencia.Deseable experiencia en funciones administrativas y/o contables.Manejo de Microsoft Office.Conocimientos de ERP contables.Conocimientos básicos de normativa contable y tributaria.Capacidad de organización y atención al detalle.Deseable experiencia trabajando con carteras de clientes o servicios de outsourcing.OfrecemosPaquete de compensaciones de mercadoSeguro Complementarios de salud y Dental, además de seguro de VidaUna experiencia dinámica, diversa e inclusiva, en una Firma con orientación en las personas, desarrollo y crecimientoEducación continua, tanto de programas internos, corporativos y externosDías adicionales de vacaciones.Este cargo es compatible para personas con discapacidad, se enmarca en la ley 21.015, que incentiva la inclusión de personas con discapacidad al mundo laboral.</t>
+          <t>Importante empresa de servicios financieros se encuentra en búsqueda de un Analista Actuarial Junior, que será responsable de contribuir a la generación de análisis estratégicos, desarrollo de modelos y proyecciones financieras, apoyando la toma de decisiones en una organización líder del sector financiero.Principales responsabilidades:Apoyar el desarrollo, actualización y validación de modelos actuariales utilizados para análisis, medición y proyecciones del negocio.Crear análisis y reportes que contribuyan a la evaluación de resultados, tendencias y desempeño de productos.Supervisar la calidad, consistencia e integridad de la información utilizada en los procesos actuariales.Gestionar análisis relacionados con tarifas, reservas, rentabilidad, experiencia de siniestralidad y métricas de riesgo.Desarrollar proyecciones financieras y escenarios de negocio para apoyar la planificación y la toma de decisiones.Coordinar con áreas de Finanzas, Riesgos, Productos, Operaciones y otras funciones relacionadas para asegurar una adecuada implementación de modelos y análisis.Requisitos:Título profesional en Ingeniería Matemática o Ingeniería Estadística.Un año de experiencia en funciones similares y/o interés en desarrollarte en esta área.Inglés avanzado o fluido, tanto oral como escrito.Experiencia en programación y análisis de datos utilizando Python.Interés o experiencia en herramientas de inteligencia artificial generativa y automatización (Copilot u otras soluciones similares).Competencias que buscamos:Sólida capacidad analítica y estadística.Orientado a resultadosAutonomíaRelacionamientoComunicación a todo nivelBeneficiosTe ofrecemos:Trabajo colaborativo con equipos multidisciplinarios.Acceso a tecnologías, herramientas analíticas e iniciativas de innovación.Oportunidades de desarrollo profesional en un entorno desafiante.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Analista Actuarial</t>
+          <t>Consultor de Proyecto | Matrix Consulting</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Matrix Consulting</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Av. presidente Riesco 5435, Multipaís</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4721,15 +4721,15 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56011/analista-actuarial</t>
+          <t>https://firstjob.me/oferta/56058/consultor-de-proyecto-matrix-consulting</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>python, analisis, estadistica, matematica</t>
+          <t>analisis</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -4748,17 +4748,17 @@
         <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>Importante empresa de servicios financieros se encuentra en búsqueda de un Analista Actuarial Junior, que será responsable de contribuir a la generación de análisis estratégicos, desarrollo de modelos y proyecciones financieras, apoyando la toma de decisiones en una organización líder del sector financiero.Principales responsabilidades:Apoyar el desarrollo, actualización y validación de modelos actuariales utilizados para análisis, medición y proyecciones del negocio.Crear análisis y reportes que contribuyan a la evaluación de resultados, tendencias y desempeño de productos.Supervisar la calidad, consistencia e integridad de la información utilizada en los procesos actuariales.Gestionar análisis relacionados con tarifas, reservas, rentabilidad, experiencia de siniestralidad y métricas de riesgo.Desarrollar proyecciones financieras y escenarios de negocio para apoyar la planificación y la toma de decisiones.Coordinar con áreas de Finanzas, Riesgos, Productos, Operaciones y otras funciones relacionadas para asegurar una adecuada implementación de modelos y análisis.Requisitos:Título profesional en Ingeniería Matemática o Ingeniería Estadística.Un año de experiencia en funciones similares y/o interés en desarrollarte en esta área.Inglés avanzado o fluido, tanto oral como escrito.Experiencia en programación y análisis de datos utilizando Python.Interés o experiencia en herramientas de inteligencia artificial generativa y automatización (Copilot u otras soluciones similares).Competencias que buscamos:Sólida capacidad analítica y estadística.Orientado a resultadosAutonomíaRelacionamientoComunicación a todo nivelBeneficiosTe ofrecemos:Trabajo colaborativo con equipos multidisciplinarios.Acceso a tecnologías, herramientas analíticas e iniciativas de innovación.Oportunidades de desarrollo profesional en un entorno desafiante.</t>
+          <t>¡¡Te invitamos a formar parte de nuestro equipo de Matrixianos!! Estamos buscando personas como tú, apasionadas, enfocadas y con todas las ganas de crecer.Misión del cargoComo Consultor, podrá desarrollar junto al equipo de consultoría de proyectos labores de investigación y análisis, colaborando en el desarrollo de soluciones y recomendaciones de negocio para los clientes. El consultor deberá profundizar sus conocimientos en distintas industrias, clientes y áreas de práctica (estrategia, organización, operaciones, finanzas corporativas, transformación digital etc.) creando valor mediante la entrega de propuestas que se ajusten a las necesidades de los clientes.FuncionesDesarrollar diagnósticos y propuestas, acordes a los desafíos y problemáticas planteadas por los clientes.Realizar investigación y búsqueda de información relevante para el proyecto; estructurando y ejecutando los análisis de información.Anticipar requerimientos del proyecto, proponer lineamientos y objetivos para la generación de material de apoyo.Preparar presentaciones y otros documentos para clientes, liderando algunas reuniones en entornos de bajo riesgo.Ejecutar estrategia y planes diseñados, con foco en la mejora continua.RequisitosProfesión: Ing. Civil Industrial, Ing. Comercial, Ing. Industrial o Economista; Administración de Empresas o similaresIdioma: Inglés avanzado (oral y escrito) - B2/C1Experiencia laboral: 0 a 2 años - Entry levelExperiencia valorada: Experiencia relacionada con la consultoría como finanzas, control de gestión, estudios, evaluación de proyectos, desarrollo, nuevos negocios o similar (deseable, no excluyente).Otros: Participación en actividades que demuestran compromiso y liderazgo como: centro de alumnos, organizaciones sin fines de lucro, deportes, etc.Esta vacante tendrá como base Chile, Colombia o Perú (con viajes incluidos) y Argentina con posibilidad de traslado.BeneficiosDías adicionales de vacacionesDesarrollo profesional aceleradoTrabajar en una firma líder en consultoría.Ambiente de trabajo colaborativo y dinámicoCofinanciamiento con Wellhub para que puedas hacer deporte¡Celebramos todo! nuestros logros, cumpleaños, festividades y más</t>
         </is>
       </c>
     </row>
@@ -4770,45 +4770,45 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Consultor de Proyecto | Matrix Consulting</t>
+          <t>Desarrollador(a) de Automatización e Inteligencia Artificial</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Matrix Consulting</t>
+          <t>Postedin</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Av. presidente Riesco 5435, Multipaís</t>
+          <t>Multipaís</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Remoto Trabajo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56058/consultor-de-proyecto-matrix-consulting</t>
+          <t>https://firstjob.me/oferta/56051/desarrollador-a-de-automatizacion-e-inteligencia-artificial</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>analisis</t>
+          <t>python, analisis, informatica, javascript, gemini, zapier, n8n</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -4823,11 +4823,11 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>¡¡Te invitamos a formar parte de nuestro equipo de Matrixianos!! Estamos buscando personas como tú, apasionadas, enfocadas y con todas las ganas de crecer.Misión del cargoComo Consultor, podrá desarrollar junto al equipo de consultoría de proyectos labores de investigación y análisis, colaborando en el desarrollo de soluciones y recomendaciones de negocio para los clientes. El consultor deberá profundizar sus conocimientos en distintas industrias, clientes y áreas de práctica (estrategia, organización, operaciones, finanzas corporativas, transformación digital etc.) creando valor mediante la entrega de propuestas que se ajusten a las necesidades de los clientes.FuncionesDesarrollar diagnósticos y propuestas, acordes a los desafíos y problemáticas planteadas por los clientes.Realizar investigación y búsqueda de información relevante para el proyecto; estructurando y ejecutando los análisis de información.Anticipar requerimientos del proyecto, proponer lineamientos y objetivos para la generación de material de apoyo.Preparar presentaciones y otros documentos para clientes, liderando algunas reuniones en entornos de bajo riesgo.Ejecutar estrategia y planes diseñados, con foco en la mejora continua.RequisitosProfesión: Ing. Civil Industrial, Ing. Comercial, Ing. Industrial o Economista; Administración de Empresas o similaresIdioma: Inglés avanzado (oral y escrito) - B2/C1Experiencia laboral: 0 a 2 años - Entry levelExperiencia valorada: Experiencia relacionada con la consultoría como finanzas, control de gestión, estudios, evaluación de proyectos, desarrollo, nuevos negocios o similar (deseable, no excluyente).Otros: Participación en actividades que demuestran compromiso y liderazgo como: centro de alumnos, organizaciones sin fines de lucro, deportes, etc.Esta vacante tendrá como base Chile, Colombia o Perú (con viajes incluidos) y Argentina con posibilidad de traslado.BeneficiosDías adicionales de vacacionesDesarrollo profesional aceleradoTrabajar en una firma líder en consultoría.Ambiente de trabajo colaborativo y dinámicoCofinanciamiento con Wellhub para que puedas hacer deporte¡Celebramos todo! nuestros logros, cumpleaños, festividades y más</t>
+          <t>Modalidad:RemotoTipo de contrato:A convenirUbicación:LATAMSobre PostedinEn Postedin ayudamos a marcas líderes de Latinoamérica a mejorar su visibilidad orgánica en buscadores, asistentes de inteligencia artificial y plataformas digitales. Combinamos estrategia, tecnología, datos y automatización para entender cómo las personas encuentran información y cómo las marcas pueden ser relevantes dentro de ese proceso.Hoy estamos buscando una persona para integrarse a nuestro equipo de Desarrollo e Inteligencia Artificial, donde trabajará en la creación de automatizaciones, herramientas internas, análisis de datos y proyectos de investigación relacionados con el funcionamiento de los modelos de IA y los motores de búsqueda.¿Qué harás?Diseñar e implementar automatizaciones utilizando herramientas low-code y desarrollo personalizado.Crear integraciones entre plataformas mediante APIs.Participar en el desarrollo de herramientas internas impulsadas por inteligencia artificial.Construir dashboards y sistemas de visualización para equipos técnicos, ejecutivos y clientes.Investigar cómo los motores de búsqueda y los modelos de IA descubren, interpretan y priorizan información.Analizar patrones de visibilidad de marcas, conceptos y contenidos en Google, ChatGPT, Gemini, Claude y otras plataformas de IA.Apoyar el desarrollo de procesos de captura, transformación y análisis de datos.Colaborar con equipos de SEO, contenido, estrategia y analítica para convertir hallazgos en soluciones escalables.Experimentar constantemente con nuevas tecnologías, frameworks y herramientas impulsadas por IA.Lo que buscamosMás que un especialista en marketing digital, buscamos una persona con mentalidad técnica, curiosidad y ganas de aprender.Nos interesa alguien que:Disfrute investigando cómo funcionan las cosas.Tenga interés genuino por la inteligencia artificial y sus aplicaciones.Utilice herramientas de IA dentro de su flujo diario de trabajo.Se sienta cómodo construyendo soluciones, automatizando procesos y conectando sistemas.Tenga iniciativa para aprender tecnologías nuevas de manera autónoma.RequisitosFormación en Ingeniería Informática, Desarrollo de Software, Ciencia de Datos o carrera afín.Experiencia desarrollando software o automatizaciones.Conocimientos de programación en al menos un lenguaje moderno (Python, JavaScript, TypeScript u otro equivalente).Experiencia consumiendo e integrando APIs.Familiaridad con herramientas como N8N, Make, Zapier o similares.Manejo de bases de datos y procesamiento de información.Capacidad para analizar problemas y proponer soluciones técnicas.DeseablesConocimientos sobre LLMs (Large Language Models) y técnicas de prompting.Experiencia utilizando APIs de modelos de IA.Conocimientos de scraping, extracción y procesamiento de datos.Experiencia en herramientas de visualización y dashboards.Familiaridad con Google Analytics, Google Search Console, Ahrefs, Semrush o plataformas similares.Interés por SEO, GEO (Generative Engine Optimization), AEO (Answer Engine Optimization) y búsqueda impulsada por IA.Lo que aprenderásCómo funcionan los motores de búsqueda modernos y los asistentes de IA.Técnicas para analizar y mejorar la visibilidad de marcas en entornos de inteligencia artificial.Desarrollo de herramientas basadas en LLMs.Automatización avanzada de procesos de marketing y análisis de datos.Construcción de sistemas de monitoreo, dashboards e inteligencia de negocio.Aplicación práctica de IA en proyectos reales para empresas líderes de Latinoamérica.Lo que valoramos especialmenteNo esperamos que llegues sabiendo todo.Valoramos más la capacidad de aprender rápido, la curiosidad técnica, la pasión por construir soluciones y el interés por entender uno de los desafíos más interesantes de la industria hoy: descubrir cómo los motores de búsqueda y los modelos de inteligencia artificial encuentran, interpretan y recomiendan información.Si te entusiasma investigar, experimentar y construir herramientas que ayuden a entender las nuevas reglas de Internet, nos gustaría conocerte.BeneficiosAfiliación a Caja Los Andes.Acceso a Seguro de Salud Complementario al pasar a contrato indefinido.Previsión según topes legales.Tipo de trabajo: remotoSeguro de salud.Día de cumpleaños libre.Oportunidades de desarrollo y crecimiento profesional.Ambiente de trabajo dinámico y colaborativo.Acceso a capacitaciones continuas en marketing digital y SEO.</t>
         </is>
       </c>
     </row>
@@ -4839,64 +4839,60 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Desarrollador(a) de Automatización e Inteligencia Artificial</t>
+          <t>Asistente de Ventas Full Time – Tanner Servicios Financieros</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Postedin</t>
+          <t>Tanner</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Multipaís</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Remoto Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56051/desarrollador-a-de-automatizacion-e-inteligencia-artificial</t>
+          <t>https://firstjob.me/oferta/56079/asistente-de-ventas-full-time-tanner-servicios-financieros</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>17</v>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>python, analisis, informatica, javascript, gemini, zapier, n8n</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
         <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>Modalidad:RemotoTipo de contrato:A convenirUbicación:LATAMSobre PostedinEn Postedin ayudamos a marcas líderes de Latinoamérica a mejorar su visibilidad orgánica en buscadores, asistentes de inteligencia artificial y plataformas digitales. Combinamos estrategia, tecnología, datos y automatización para entender cómo las personas encuentran información y cómo las marcas pueden ser relevantes dentro de ese proceso.Hoy estamos buscando una persona para integrarse a nuestro equipo de Desarrollo e Inteligencia Artificial, donde trabajará en la creación de automatizaciones, herramientas internas, análisis de datos y proyectos de investigación relacionados con el funcionamiento de los modelos de IA y los motores de búsqueda.¿Qué harás?Diseñar e implementar automatizaciones utilizando herramientas low-code y desarrollo personalizado.Crear integraciones entre plataformas mediante APIs.Participar en el desarrollo de herramientas internas impulsadas por inteligencia artificial.Construir dashboards y sistemas de visualización para equipos técnicos, ejecutivos y clientes.Investigar cómo los motores de búsqueda y los modelos de IA descubren, interpretan y priorizan información.Analizar patrones de visibilidad de marcas, conceptos y contenidos en Google, ChatGPT, Gemini, Claude y otras plataformas de IA.Apoyar el desarrollo de procesos de captura, transformación y análisis de datos.Colaborar con equipos de SEO, contenido, estrategia y analítica para convertir hallazgos en soluciones escalables.Experimentar constantemente con nuevas tecnologías, frameworks y herramientas impulsadas por IA.Lo que buscamosMás que un especialista en marketing digital, buscamos una persona con mentalidad técnica, curiosidad y ganas de aprender.Nos interesa alguien que:Disfrute investigando cómo funcionan las cosas.Tenga interés genuino por la inteligencia artificial y sus aplicaciones.Utilice herramientas de IA dentro de su flujo diario de trabajo.Se sienta cómodo construyendo soluciones, automatizando procesos y conectando sistemas.Tenga iniciativa para aprender tecnologías nuevas de manera autónoma.RequisitosFormación en Ingeniería Informática, Desarrollo de Software, Ciencia de Datos o carrera afín.Experiencia desarrollando software o automatizaciones.Conocimientos de programación en al menos un lenguaje moderno (Python, JavaScript, TypeScript u otro equivalente).Experiencia consumiendo e integrando APIs.Familiaridad con herramientas como N8N, Make, Zapier o similares.Manejo de bases de datos y procesamiento de información.Capacidad para analizar problemas y proponer soluciones técnicas.DeseablesConocimientos sobre LLMs (Large Language Models) y técnicas de prompting.Experiencia utilizando APIs de modelos de IA.Conocimientos de scraping, extracción y procesamiento de datos.Experiencia en herramientas de visualización y dashboards.Familiaridad con Google Analytics, Google Search Console, Ahrefs, Semrush o plataformas similares.Interés por SEO, GEO (Generative Engine Optimization), AEO (Answer Engine Optimization) y búsqueda impulsada por IA.Lo que aprenderásCómo funcionan los motores de búsqueda modernos y los asistentes de IA.Técnicas para analizar y mejorar la visibilidad de marcas en entornos de inteligencia artificial.Desarrollo de herramientas basadas en LLMs.Automatización avanzada de procesos de marketing y análisis de datos.Construcción de sistemas de monitoreo, dashboards e inteligencia de negocio.Aplicación práctica de IA en proyectos reales para empresas líderes de Latinoamérica.Lo que valoramos especialmenteNo esperamos que llegues sabiendo todo.Valoramos más la capacidad de aprender rápido, la curiosidad técnica, la pasión por construir soluciones y el interés por entender uno de los desafíos más interesantes de la industria hoy: descubrir cómo los motores de búsqueda y los modelos de inteligencia artificial encuentran, interpretan y recomiendan información.Si te entusiasma investigar, experimentar y construir herramientas que ayuden a entender las nuevas reglas de Internet, nos gustaría conocerte.BeneficiosAfiliación a Caja Los Andes.Acceso a Seguro de Salud Complementario al pasar a contrato indefinido.Previsión según topes legales.Tipo de trabajo: remotoSeguro de salud.Día de cumpleaños libre.Oportunidades de desarrollo y crecimiento profesional.Ambiente de trabajo dinámico y colaborativo.Acceso a capacitaciones continuas en marketing digital y SEO.</t>
+          <t>En Tanner seguimos creciendo y queremos que tú también seas parte de este equipo.Buscamos a nuestro próximo/aAsistente de Ventas Full Time, quien tendrá la misión de brindar un servicio de excelencia a nuestros clientes en el punto de venta, asesorándolos en productos financieros y seguros automotrices.¿Qué harás?Asesorar y apoyar en la venta de productos financieros y seguros automotrices.Entregar una experiencia de atención cercana y de calidad, ayudando a cada cliente a encontrar la mejor alternativa según sus necesidades.Validar documentación y respaldos asociados a los cierres de financiamiento.Representar a Tanner con una actitud proactiva, empática y orientada al servicio.En Tanner valoramos el compromiso, la cercanía y el trabajo colaborativo, ofreciendo un espacio donde podrás desarrollarte y generar impacto en la experiencia de nuestros clientes.¡Te invitamos a postular y ser parte de Tanner!Requisitos🔎 ¿Qué buscamos?Deseable contar con estudios técnicos o profesionales en áreas comerciales, administración o afines.Al menos 1 año de experiencia en atención al cliente o ventas (idealmente en retail o servicios financieros).Habilidades comunicacionales y orientación al cliente.Disponibilidad para trabajar en modalidad presencial 5x2, 3 días en la semana, incluyendo sábado y domingo de forma fija</t>
         </is>
       </c>
     </row>
@@ -4908,12 +4904,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Asistente de Ventas Full Time – Tanner Servicios Financieros</t>
+          <t>Práctica profesional - Comunicaciones internas</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tanner</t>
+          <t>Ripley chile</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4923,12 +4919,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56079/asistente-de-ventas-full-time-tanner-servicios-financieros</t>
+          <t>https://firstjob.me/oferta/56047/practica-profesional-comunicaciones-internas</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -4942,16 +4938,16 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -4961,7 +4957,7 @@
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>En Tanner seguimos creciendo y queremos que tú también seas parte de este equipo.Buscamos a nuestro próximo/aAsistente de Ventas Full Time, quien tendrá la misión de brindar un servicio de excelencia a nuestros clientes en el punto de venta, asesorándolos en productos financieros y seguros automotrices.¿Qué harás?Asesorar y apoyar en la venta de productos financieros y seguros automotrices.Entregar una experiencia de atención cercana y de calidad, ayudando a cada cliente a encontrar la mejor alternativa según sus necesidades.Validar documentación y respaldos asociados a los cierres de financiamiento.Representar a Tanner con una actitud proactiva, empática y orientada al servicio.En Tanner valoramos el compromiso, la cercanía y el trabajo colaborativo, ofreciendo un espacio donde podrás desarrollarte y generar impacto en la experiencia de nuestros clientes.¡Te invitamos a postular y ser parte de Tanner!Requisitos🔎 ¿Qué buscamos?Deseable contar con estudios técnicos o profesionales en áreas comerciales, administración o afines.Al menos 1 año de experiencia en atención al cliente o ventas (idealmente en retail o servicios financieros).Habilidades comunicacionales y orientación al cliente.Disponibilidad para trabajar en modalidad presencial 5x2, 3 días en la semana, incluyendo sábado y domingo de forma fija</t>
+          <t>Práctica profesional - Comunicaciones internas 🚀 ¡Buscamos a nuestro/a próximo/a practicante para el Área de Comunicaciones Internas y Eventos Estratégicos en la Gerencia Corporativa de Personas de Ripley!Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Ripley/Banco Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro.Ser parte de Ripley/Banco Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te motiva ser parte de un negocio desafiante y que tu práctica tenga impacto real? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Ser parte activa de distintos proyectos del área, apoyando su coordinación, seguimiento y visibilidad comunicacional.Funciones: 🤩Ser parte activa de distintos proyectos del área, apoyando su coordinación, seguimiento y visibilidad comunicacional.Crear, proponer y ejecutar contenido para nuestro Instagram interno, potenciando iniciativas, cultura y experiencias de marca interna.¿Qué estamos buscando? 💡Estudiante de Publicidad o Periodismo.Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)Disponibilidad de 6 meses. (deseable posibilidad de extensión)Conocimiento en canva y suite de adobe, además de conocimiento de edición de videos.¿Por qué trabajar en Ripley/Banco Ripley? 💗Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.   ¡TRABAJA CON NOSOTROS!BeneficiosDescripción de los beneficios de la vacante</t>
         </is>
       </c>
     </row>
@@ -4973,7 +4969,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Práctica profesional - Comunicaciones internas</t>
+          <t>Practica profesional - Desarrollo Organizacional</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4983,7 +4979,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Ofi. Alonso De Cordova 5320 - RECURSOS HUMANO, Chile</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4993,13 +4989,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56047/practica-profesional-comunicaciones-internas</t>
+          <t>https://firstjob.me/oferta/56044/practica-profesional-desarrollo-organizacional</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>Práctica profesional - Comunicaciones internas 🚀 ¡Buscamos a nuestro/a próximo/a practicante para el Área de Comunicaciones Internas y Eventos Estratégicos en la Gerencia Corporativa de Personas de Ripley!Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Ripley/Banco Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro.Ser parte de Ripley/Banco Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te motiva ser parte de un negocio desafiante y que tu práctica tenga impacto real? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Ser parte activa de distintos proyectos del área, apoyando su coordinación, seguimiento y visibilidad comunicacional.Funciones: 🤩Ser parte activa de distintos proyectos del área, apoyando su coordinación, seguimiento y visibilidad comunicacional.Crear, proponer y ejecutar contenido para nuestro Instagram interno, potenciando iniciativas, cultura y experiencias de marca interna.¿Qué estamos buscando? 💡Estudiante de Publicidad o Periodismo.Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)Disponibilidad de 6 meses. (deseable posibilidad de extensión)Conocimiento en canva y suite de adobe, además de conocimiento de edición de videos.¿Por qué trabajar en Ripley/Banco Ripley? 💗Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.   ¡TRABAJA CON NOSOTROS!BeneficiosDescripción de los beneficios de la vacante</t>
+          <t>Practica profesional - Desarrollo Organizacional 🚀 ¡Buscamos a nuestro/a próximo/a practicante para el Área de Desarrollo Organizacional en la Gerencia de Gestión de personas de Ripley!Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Ripley/Banco Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro.Ser parte de Ripley/Banco Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te motiva ser parte de un negocio desafiante y que tu práctica tenga impacto real? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Impulsar el desarrollo del talento interno y acompañar a cada colaborador en su viaje profesional, mediante iniciativas y procesos que fortalezcan su crecimiento, fomenten su compromiso y estén alineados con nuestra cultura corporativa. Buscamos crear experiencias significativas, simples y humanas que potencien el valor de las personas dentro de Ripley.Funciones: 🤩Levantar y mapear los procesos del área de Desarrollo Organizacional desde la perspectiva del colaborador, identificando puntos de fricción y oportunidades de mejora.Analizar la experiencia de usuario en los distintos procesos de desarrollo de talento, mediante herramientas de diagnóstico como entrevistas, encuestas u observación directa.Diseñar propuestas de mejora centradas en el usuario, que simplifiquen la experiencia y estén alineadas con la cultura organizacional.Trabajar en conjunto con el área de Datos y el equipo de desarrollo de la plataforma externa para crear, diseñar y realizar las modificaciones necesarias en los procesos definidos.¿Qué estamos buscando? 💡Estudiante de último año de la carrera de Psicología, Ingeniería/Técnico en administración de empresas, ingeniería comercial.Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)Disponibilidad de 6 meses. (deseable posibilidad de extensión)Conocimiento en Excel.¿Por qué trabajar en Ripley/Banco Ripley? 💗Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.   ¡TRABAJA CON NOSOTROS!BeneficiosDescripción de los beneficios de la vacante</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Practica profesional - Desarrollo Organizacional</t>
+          <t>Category Manager Tecno</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Ofi. Alonso De Cordova 5320 - RECURSOS HUMANO, Chile</t>
+          <t>Ofi Cerro Colorado 5240 - Comercial, Chile</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5058,19 +5058,19 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56044/practica-profesional-desarrollo-organizacional</t>
+          <t>https://firstjob.me/oferta/56032/category-manager-tecno</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>excel</t>
+          <t>analisis</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -5085,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -5095,7 +5095,7 @@
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>Practica profesional - Desarrollo Organizacional 🚀 ¡Buscamos a nuestro/a próximo/a practicante para el Área de Desarrollo Organizacional en la Gerencia de Gestión de personas de Ripley!Si estás buscando un lugar donde puedas aprender, crecer y aportar desde el primer día, llegaste al lugar indicado. En Ripley/Banco Ripley te unirás a un equipo diverso, dinámico y lleno de desafíos, donde el cliente está siempre en el centro.Ser parte de Ripley/Banco Ripley es vivir una cultura que impulsa el desarrollo, la innovación y el trabajo colaborativo, con un ambiente de confianza, cercanía y equilibrio entre lo laboral y lo personal.¿Te motiva ser parte de un negocio desafiante y que tu práctica tenga impacto real? Entonces esta oportunidad es para ti.✨ ¡Súmate a la experiencia Ripley Pro y crece con nosotros!Objetivo: 🚀Impulsar el desarrollo del talento interno y acompañar a cada colaborador en su viaje profesional, mediante iniciativas y procesos que fortalezcan su crecimiento, fomenten su compromiso y estén alineados con nuestra cultura corporativa. Buscamos crear experiencias significativas, simples y humanas que potencien el valor de las personas dentro de Ripley.Funciones: 🤩Levantar y mapear los procesos del área de Desarrollo Organizacional desde la perspectiva del colaborador, identificando puntos de fricción y oportunidades de mejora.Analizar la experiencia de usuario en los distintos procesos de desarrollo de talento, mediante herramientas de diagnóstico como entrevistas, encuestas u observación directa.Diseñar propuestas de mejora centradas en el usuario, que simplifiquen la experiencia y estén alineadas con la cultura organizacional.Trabajar en conjunto con el área de Datos y el equipo de desarrollo de la plataforma externa para crear, diseñar y realizar las modificaciones necesarias en los procesos definidos.¿Qué estamos buscando? 💡Estudiante de último año de la carrera de Psicología, Ingeniería/Técnico en administración de empresas, ingeniería comercial.Contar con seguro escolar vigente otorgado por casa de estudios. (Excluyente)Disponibilidad de 6 meses. (deseable posibilidad de extensión)Conocimiento en Excel.¿Por qué trabajar en Ripley/Banco Ripley? 💗Porque aquí el trabajo se adapta a ti. Creemos en la flexibilidad como parte de una vida más equilibrada, por eso impulsamos beneficios que se ajustan a tu ritmo. Nos conectamos desde donde estés y contamos con espacios colaborativos que inspiran creatividad, conexión y trabajo en equipo 🌟En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.   ¡TRABAJA CON NOSOTROS!BeneficiosDescripción de los beneficios de la vacante</t>
+          <t>Category Manager Tecno¡En Ripley Chile, lo tenemos todo! ¡Solo nos falta tu talento! 🤩🩷Somos un equipo diverso, ágil y colaborativo, enfocado en mejorar constantemente la experiencia de nuestros clientes a través de la innovación y una sólida cultura de servicio. Si te apasiona el análisis de datos, el trabajo en equipo y enfrentar nuevos desafíos, esta oportunidad es para ti.¡Postula para ser parte de nuestro equipo!Estamos en búsqueda de nuestro/a nuevo/a Category Manager Tecno - Electro Menor y Audio para nuestra Gerencia Comercial.¿Cuáles serán tus principales desafíos? 🚀Apoyar la definición de estrategia comercial del departamento: Electro menor y AudioGenerar órdenes de compra.Ejecutar cambio de precios y costos.Realizar la gestión operacional del departamento.Apoyar al área en negociaciones con las marcas involucradas.Ser el contacto directo entre Product Manager y las tiendas¿Qué valoramos en tu postulación? 🎯Título Profesional en Ingeniería Comercial/Civil Industrial (Excluyente)Microsoft Office Avanzado (Excluyente)Dominio Inglés IntermedioExperiencia de al menos 1 año en cargos similares o áreas comerciales.Deseable experiencia en retail.¿Por qué trabajar en Ripley?🩷Pensamos en el bienestar de nuestros colaboradores, es por esto que contamos con atractivos beneficios corporativos como:Capacitaciones y entrenamiento enfocado a tu desarrollo de carrera.Tasa Preferencial en Productos Banco Ripley.Seguro Complementario Gratuito.Descuento en Tiendas Ripley.Desarrollo Profesional.Entre otros.En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarloBeneficiosDescripción de los beneficios de la vacante</t>
         </is>
       </c>
     </row>
@@ -5107,17 +5107,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Category Manager Tecno</t>
+          <t>Analista de riesgo financiero (foco quant)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ripley chile</t>
+          <t>AFP Modelo</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Ofi Cerro Colorado 5240 - Comercial, Chile</t>
+          <t>Avda de valle 614 Huechuraba, Chile, Chile</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5127,19 +5127,19 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56032/category-manager-tecno</t>
+          <t>https://firstjob.me/oferta/56049/analista-de-riesgo-financiero-foco-quant</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>analisis</t>
+          <t>python, sql, estadistica, matematica</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -5164,29 +5164,29 @@
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>Category Manager Tecno¡En Ripley Chile, lo tenemos todo! ¡Solo nos falta tu talento! 🤩🩷Somos un equipo diverso, ágil y colaborativo, enfocado en mejorar constantemente la experiencia de nuestros clientes a través de la innovación y una sólida cultura de servicio. Si te apasiona el análisis de datos, el trabajo en equipo y enfrentar nuevos desafíos, esta oportunidad es para ti.¡Postula para ser parte de nuestro equipo!Estamos en búsqueda de nuestro/a nuevo/a Category Manager Tecno - Electro Menor y Audio para nuestra Gerencia Comercial.¿Cuáles serán tus principales desafíos? 🚀Apoyar la definición de estrategia comercial del departamento: Electro menor y AudioGenerar órdenes de compra.Ejecutar cambio de precios y costos.Realizar la gestión operacional del departamento.Apoyar al área en negociaciones con las marcas involucradas.Ser el contacto directo entre Product Manager y las tiendas¿Qué valoramos en tu postulación? 🎯Título Profesional en Ingeniería Comercial/Civil Industrial (Excluyente)Microsoft Office Avanzado (Excluyente)Dominio Inglés IntermedioExperiencia de al menos 1 año en cargos similares o áreas comerciales.Deseable experiencia en retail.¿Por qué trabajar en Ripley?🩷Pensamos en el bienestar de nuestros colaboradores, es por esto que contamos con atractivos beneficios corporativos como:Capacitaciones y entrenamiento enfocado a tu desarrollo de carrera.Tasa Preferencial en Productos Banco Ripley.Seguro Complementario Gratuito.Descuento en Tiendas Ripley.Desarrollo Profesional.Entre otros.En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarloBeneficiosDescripción de los beneficios de la vacante</t>
+          <t>¿Quiénes somos?Somos una AFP orientada a las personas, comprometida con su bienestar presente y futuro. Destacamos que, en línea con nuestra cultura organizacional, nuestras búsquedas se enmarcan bajo la ley 21.015, la cual promueve la inclusión laboral de las personas con discapacidad.¿Quieres sumarte a cientos de profesionales que buscan contribuir con entusiasmo y responsabilidad al bienestar de las personas? ¡Esta es tu oportunidad!¿Cuáles serán los desafíos del cargo?Analizar, desarrollar e implementar herramientas tecnológicas y financieras, usando modelos con enfoques principalmente matemáticos y estadísticos que permitan monitorear y aportar información relevante para la toma de decisiones y el control de riesgos financieros. Lo anterior, acorde a la normativa vigente y futuros cambios relevantes de la industria.Funciones principales:Analizar, desarrollar e implementar herramientas y modelos que complementen los vigentes y mejoren en sistema de control de riesgos financieros.Aportar información relevante para la toma de decisiones de inversiones y el control de riesgos financieros, particularmente riesgos de mercado y liquidez.Desarrollo de nuevas herramientas tecnológicas que apunten a hacer más eficiente y eficaz el control de riesgos financieros.¿Qué buscamos?Profesionales de Ingeniería Civil Matemática, en Computación, Estadística o carreras afines con fuerte base cuantitativa.Interés y/o conocimiento en mercados financieros, métricas y modelos de riesgos financieros.Manejo de SQL y Python excluyenteExperiencia: Deseable 1 año en cargos similares.¡Te esperamos!BeneficiosBus de acercamientoDía de CumpleañosSeguro complementarioy muchos beneficios más</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Analista de riesgo financiero (foco quant)</t>
+          <t>Auditor Tributario - Tax &amp; Legal</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AFP Modelo</t>
+          <t>KPMG Chile</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Avda de valle 614 Huechuraba, Chile, Chile</t>
+          <t>Las Condes, Metropolitana, Chile, Chile</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5196,19 +5196,15 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56049/analista-de-riesgo-financiero-foco-quant</t>
+          <t>https://firstjob.me/oferta/56087/auditor-tributario-tax-legal</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>10</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>python, sql, estadistica, matematica</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -5233,7 +5229,7 @@
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>¿Quiénes somos?Somos una AFP orientada a las personas, comprometida con su bienestar presente y futuro. Destacamos que, en línea con nuestra cultura organizacional, nuestras búsquedas se enmarcan bajo la ley 21.015, la cual promueve la inclusión laboral de las personas con discapacidad.¿Quieres sumarte a cientos de profesionales que buscan contribuir con entusiasmo y responsabilidad al bienestar de las personas? ¡Esta es tu oportunidad!¿Cuáles serán los desafíos del cargo?Analizar, desarrollar e implementar herramientas tecnológicas y financieras, usando modelos con enfoques principalmente matemáticos y estadísticos que permitan monitorear y aportar información relevante para la toma de decisiones y el control de riesgos financieros. Lo anterior, acorde a la normativa vigente y futuros cambios relevantes de la industria.Funciones principales:Analizar, desarrollar e implementar herramientas y modelos que complementen los vigentes y mejoren en sistema de control de riesgos financieros.Aportar información relevante para la toma de decisiones de inversiones y el control de riesgos financieros, particularmente riesgos de mercado y liquidez.Desarrollo de nuevas herramientas tecnológicas que apunten a hacer más eficiente y eficaz el control de riesgos financieros.¿Qué buscamos?Profesionales de Ingeniería Civil Matemática, en Computación, Estadística o carreras afines con fuerte base cuantitativa.Interés y/o conocimiento en mercados financieros, métricas y modelos de riesgos financieros.Manejo de SQL y Python excluyenteExperiencia: Deseable 1 año en cargos similares.¡Te esperamos!BeneficiosBus de acercamientoDía de CumpleañosSeguro complementarioy muchos beneficios más</t>
+          <t>**Perfil Ideal: Auditor Tributario - Tax &amp; Legal** Buscamos un **Auditor Tributario** con un mínimo de **2 años de experiencia** en cumplimiento tributario, para unirse a nuestro equipo de Tax &amp; Legal. El candidato ideal poseerá un título universitario en **Contador Auditor** (titulado o egresado) y un sólido interés en los procesos contables, financieros y tributarios. Las responsabilidades clave incluirán la preparación y presentación de impuestos mensuales (IVA e Impuesto Adicional), la determinación de Renta Líquida Imponible y Capital Propio Tributario, la elaboración de Registros de Rentas Empresariales para grandes empresas, y la determinación de provisiones de impuesto a la Renta e Impuestos Diferidos. Se espera un profundo conocimiento y aplicación de la normativa tributaria vigente. Se valorará el dominio **básico-intermedio de Microsoft Office** y, deseablemente, un nivel **intermedio-avanzado de inglés**. Este rol, de nivel **Junior**, es una excelente oportunidad para profesionales que buscan crecer en una de las cuatro consultoras auditoras más grandes del mundo y contribuir activamente al futuro de los negocios.Beneficios¿Qué ganas tú? 🌎Ser parte de una de las principales compañías de Auditoría y Consultoría a nivel mundial. 🚀 Oportunidades de desarrollo profesional. 🚑 Seguro de salud complementario con contrato indefinido. 💻 Jornada de trabajo híbrida. 🏢 Oficinas de primer nivel ubicadas en Las Condes, frente al Parque Araucano. 💯 Múltiples convenios corporativos. 🎉 Actividades como fiestas, Meeting Points y encuentros de área para disfrutar con compañeros. 🎂 16 horas anuales a libre disposición y tu día de cumpleaños es completamente libre para que lo disfrutes como desees. En KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas , con un propósito claro, para una mejor sociedad. Valoramos las diversas habilidades y fortalezas, tanto personales como profesionales, que cada persona aporta. En KPMG estamos comprometidos con la Diversidad e inclusión , nuestras ofertas de empleo están disponibles con los ajustes razonables necesarios para tu proceso. Juntos, estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. ¡Anímate y ven a descubrir por qué somos la opción más clara! 🥇</t>
         </is>
       </c>
     </row>
@@ -5245,17 +5241,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Auditor Tributario - Tax &amp; Legal</t>
+          <t>Analista Siniestros RV</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KPMG Chile</t>
+          <t>Fid seguros</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Las Condes, Metropolitana, Chile, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5265,7 +5261,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56087/auditor-tributario-tax-legal</t>
+          <t>https://firstjob.me/oferta/56096/analista-siniestros-rv</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -5273,7 +5269,7 @@
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -5298,7 +5294,7 @@
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>**Perfil Ideal: Auditor Tributario - Tax &amp; Legal** Buscamos un **Auditor Tributario** con un mínimo de **2 años de experiencia** en cumplimiento tributario, para unirse a nuestro equipo de Tax &amp; Legal. El candidato ideal poseerá un título universitario en **Contador Auditor** (titulado o egresado) y un sólido interés en los procesos contables, financieros y tributarios. Las responsabilidades clave incluirán la preparación y presentación de impuestos mensuales (IVA e Impuesto Adicional), la determinación de Renta Líquida Imponible y Capital Propio Tributario, la elaboración de Registros de Rentas Empresariales para grandes empresas, y la determinación de provisiones de impuesto a la Renta e Impuestos Diferidos. Se espera un profundo conocimiento y aplicación de la normativa tributaria vigente. Se valorará el dominio **básico-intermedio de Microsoft Office** y, deseablemente, un nivel **intermedio-avanzado de inglés**. Este rol, de nivel **Junior**, es una excelente oportunidad para profesionales que buscan crecer en una de las cuatro consultoras auditoras más grandes del mundo y contribuir activamente al futuro de los negocios.Beneficios¿Qué ganas tú? 🌎Ser parte de una de las principales compañías de Auditoría y Consultoría a nivel mundial. 🚀 Oportunidades de desarrollo profesional. 🚑 Seguro de salud complementario con contrato indefinido. 💻 Jornada de trabajo híbrida. 🏢 Oficinas de primer nivel ubicadas en Las Condes, frente al Parque Araucano. 💯 Múltiples convenios corporativos. 🎉 Actividades como fiestas, Meeting Points y encuentros de área para disfrutar con compañeros. 🎂 16 horas anuales a libre disposición y tu día de cumpleaños es completamente libre para que lo disfrutes como desees. En KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas , con un propósito claro, para una mejor sociedad. Valoramos las diversas habilidades y fortalezas, tanto personales como profesionales, que cada persona aporta. En KPMG estamos comprometidos con la Diversidad e inclusión , nuestras ofertas de empleo están disponibles con los ajustes razonables necesarios para tu proceso. Juntos, estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. ¡Anímate y ven a descubrir por qué somos la opción más clara! 🥇</t>
+          <t>FID Seguros es una compañía diseñada para integrar la tecnología como base de la experiencia de corredores y clientes. Nos definimos como una insurtech de seguros generales, que utiliza la digitalización para ofrecer experiencias simples, ágiles y transparentes, apalancado en la innovación, en el uso de la tecnología, en el trabajo en equipo y el compromiso.Actualmente nos encontramos en búsqueda de un/a Analista de Siniestros RV.¿Qué harás en este rol?Controlar y gestionar el ingreso de pérdidas probables en el plazo establecido en el procedimiento.Analizar y gestionar, según corresponda, requerimientos contenidos en pre-informes de liquidación emitido por liquidadores oficiales de seguros.Analizar la propuesta contenida en el informe de liquidación y gestionar, pago, rechazo o impugnación según corresponda. Para liquidadores oficiales a nivel nacionalVelar por el correcto pago al beneficiario en el plazo establecido en el procedimiento de la Compañía y en la norma.Gestionar el cobro y controlar el estado de pago de siniestros que afecten a pólizas con cláusula de libre pacto.Administrar y controlar la gestión de recupero legal y material.Mantener al día nómina de profesionales externos con la respectiva tabla de honorarios y comunicar su aplicación a nivel nacional.Desarrollar y mantener versión vigente de Manuales.Liquidar en forma directa.Participar en el desarrollo e implementación del sistema informático del área y de las modificaciones o cambios futuros.Desarrollar procedimiento de mejora continua.Desarrollar y comunicar sistemáticamente informes de gestión del área.¿Qué buscamos en ti?Titulado/a de Ingeniería en Construcción, Contador Auditor, Derecho, Ing Comercial, Civil Industrial.Experiencia de 1 año en roles similares.BeneficiosLo que ofrecemosModalidad de trabajo híbrida.Horario flexibleBeneficios como bono por desempeño, ajustes semestrales por IPC, seguro complementario y de vida, días administrativos, acuerdos de descuentos varios, entre otros.Esta oferta laboral se rige bajo la Ley Nº 21.015 que incentiva la inclusión de personas con discapacidad al mundo laboral.</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5306,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Analista Siniestros RV</t>
+          <t>Analista de Coordinación Siniestros (técnicoingeniería en administración o carrera afín)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5330,13 +5326,17 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56096/analista-siniestros-rv</t>
+          <t>https://firstjob.me/oferta/56095/analista-de-coordinacion-siniestros-tecnico-ingenieria-en-administracion-o-carrera-afin</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>FID Seguros es una compañía diseñada para integrar la tecnología como base de la experiencia de corredores y clientes. Nos definimos como una insurtech de seguros generales, que utiliza la digitalización para ofrecer experiencias simples, ágiles y transparentes, apalancado en la innovación, en el uso de la tecnología, en el trabajo en equipo y el compromiso.Actualmente nos encontramos en búsqueda de un/a Analista de Siniestros RV.¿Qué harás en este rol?Controlar y gestionar el ingreso de pérdidas probables en el plazo establecido en el procedimiento.Analizar y gestionar, según corresponda, requerimientos contenidos en pre-informes de liquidación emitido por liquidadores oficiales de seguros.Analizar la propuesta contenida en el informe de liquidación y gestionar, pago, rechazo o impugnación según corresponda. Para liquidadores oficiales a nivel nacionalVelar por el correcto pago al beneficiario en el plazo establecido en el procedimiento de la Compañía y en la norma.Gestionar el cobro y controlar el estado de pago de siniestros que afecten a pólizas con cláusula de libre pacto.Administrar y controlar la gestión de recupero legal y material.Mantener al día nómina de profesionales externos con la respectiva tabla de honorarios y comunicar su aplicación a nivel nacional.Desarrollar y mantener versión vigente de Manuales.Liquidar en forma directa.Participar en el desarrollo e implementación del sistema informático del área y de las modificaciones o cambios futuros.Desarrollar procedimiento de mejora continua.Desarrollar y comunicar sistemáticamente informes de gestión del área.¿Qué buscamos en ti?Titulado/a de Ingeniería en Construcción, Contador Auditor, Derecho, Ing Comercial, Civil Industrial.Experiencia de 1 año en roles similares.BeneficiosLo que ofrecemosModalidad de trabajo híbrida.Horario flexibleBeneficios como bono por desempeño, ajustes semestrales por IPC, seguro complementario y de vida, días administrativos, acuerdos de descuentos varios, entre otros.Esta oferta laboral se rige bajo la Ley Nº 21.015 que incentiva la inclusión de personas con discapacidad al mundo laboral.</t>
+          <t>EnFID Seguros, no solo somos una compañía de seguros generales; Somos el equipo que construye confianza, innova en servicio y transforma desafíos en soluciones. Buscamos a aquellos apasionados por aprender, crecer y contribuir desde el primer día.Actualmente nos encontramos en búsqueda Analista de Coordinación Siniestros a plazo fijo 3 meses,¿Qué harás en este rol?Realizar el ingreso de información/documentación relevante en sistemas para agilizar el proceso de liquidación de siniestros.Realizar la Cargar de documentación (CAV, Inspección de Riesgo, entre otros) en el sistema de siniestros para facilitar el análisis en el proceso de liquidación por parte de liquidador y analista de siniestros.Realizar la Validación e ingreso de denuncios de compañías coaseguradoras en sistema de siniestros para lograr registrar el siniestro en sistema de siniestros con su debida reserva.Coordinar y realizar reuniones con contrapartes internas y externas  para proveer de información sobre desempeño de gestión Intercompañía, coaseguro y carga de documentación.Realizar reportes de control y gestión en área de siniestros para contribuir el cumplimiento de indicadores de servicio y realizar feedback.RequisitosConocimientos de:  Técnico y/o Ingeniero en Administración, carrera afín. Normativa de seguros Manejo de office intermedioExperiencia en gestión y control de Información.Beneficios- Modalidad híbrida</t>
         </is>
       </c>
     </row>
@@ -5375,17 +5375,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Analista de Coordinación Siniestros (técnicoingeniería en administración o carrera afín)</t>
+          <t>Category Manager Nuevos Negocios</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fid seguros</t>
+          <t>Ripley chile</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Ofi Cerro Colorado 5240 - Comercial, Chile</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56095/analista-de-coordinacion-siniestros-tecnico-ingenieria-en-administracion-o-carrera-afin</t>
+          <t>https://firstjob.me/oferta/56091/category-manager-nuevos-negocios</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -5422,7 +5422,7 @@
         <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -5432,7 +5432,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>EnFID Seguros, no solo somos una compañía de seguros generales; Somos el equipo que construye confianza, innova en servicio y transforma desafíos en soluciones. Buscamos a aquellos apasionados por aprender, crecer y contribuir desde el primer día.Actualmente nos encontramos en búsqueda Analista de Coordinación Siniestros a plazo fijo 3 meses,¿Qué harás en este rol?Realizar el ingreso de información/documentación relevante en sistemas para agilizar el proceso de liquidación de siniestros.Realizar la Cargar de documentación (CAV, Inspección de Riesgo, entre otros) en el sistema de siniestros para facilitar el análisis en el proceso de liquidación por parte de liquidador y analista de siniestros.Realizar la Validación e ingreso de denuncios de compañías coaseguradoras en sistema de siniestros para lograr registrar el siniestro en sistema de siniestros con su debida reserva.Coordinar y realizar reuniones con contrapartes internas y externas  para proveer de información sobre desempeño de gestión Intercompañía, coaseguro y carga de documentación.Realizar reportes de control y gestión en área de siniestros para contribuir el cumplimiento de indicadores de servicio y realizar feedback.RequisitosConocimientos de:  Técnico y/o Ingeniero en Administración, carrera afín. Normativa de seguros Manejo de office intermedioExperiencia en gestión y control de Información.Beneficios- Modalidad híbrida</t>
+          <t>Category Manager Nuevos NegociosEn Ripley Chile, lo tenemos todo ¡Solo nos falta tu talento! 🤩Promovemos equipos diversos y colaborativos, buscando mejorar la experiencia de nuestros clientes a través de la innovación y la cultura de servicio. ¡Súmate a una industria ágil y desafiante!¡Postula para ser parte de nuestro equipo!Estamos en búsqueda de nuestro nuevo Category Manager para la Gerencia de Nuevos Negocios, de nuestra Gerencia Comercial.¿Cuáles serán tus principales desafíos?Encargado de apoyar al comprador en rentabilizar las categorías de Garantía y Rphone de todas las tiendas Ripley y Ripley.com. Para ello deberá poner en práctica todos sus conocimientos comerciales, venta y de marketing para poder crear acciones que generen el crecimiento del negocio. Parte de su responsabilidad será reunirse con proveedores (marcas), buscar nuevos productos, rentabilizar los actuales, visitar tiendas. Si eres una persona que se apasiona por el trabajo dinámico y el desafío constante ¡Esta es tu oportunidad de hacer que las cosas pasen!Tus principales funciones:🚀Estrategias Comerciales: Crear estrategias comerciales y de precios para llegar a las metas de venta y contribución presupuestadas por temporada.Mix de Compra: Presupuestar la compra de marcas y productos nacionales e importados, y en base a ello, generar el mix adecuado de productos y definir la carga de estos, en tiendas de cuerdo a capacidades, de manera de rentabilizar el metro cuadrado.Administrar la Compra: Revisar los abiertos de compra con los Planificadores de Compras, y seguir el comportamiento de las ventas, a fin de mantener volumen y stock suficientes para asegurar el óptimo desarrollo comercial por categoría y ubicación, y/o definir liquidaciones.Análisis de Tendencias de Mercado: Analizar e investigar los mercados internos y externos en cuanto a sus tendencias, competencia y cambios en la moda para así generar atractivas colecciones.Administración de Inventario: Negociar y coordinar constantemente con proveedores para definir precios, calidades, tiempos de despacho, condiciones de pago, cantidades, y exhibición de productos; y supervisar el comportamiento de stocks para la toma oportuna de decisiones en cuanto a compras futuras.Abastecimiento: Supervisar la llegada de los productos y abastecimiento hacia las tiendas.¿Cuáles son los requisitos para tu postulación?🎯Ingeniería Comercial con orientación a Ventas y Marketing (Excluyente)Deseable experiencia 0-1 año en compras consumo masivo o retailManejo de Microsoft Office Intermedio-Avanzado (Excluyente)Ser proactivo, enérgico y dinámico¿Por qué trabajar en Ripley?Pensamos en el bienestar de nuestros colaboradores, es por esto que contamos con atractivos beneficios corporativos como:Capacitaciones y entrenamiento enfocado a tu desarrollo de carrera.Tasa Preferencial en Productos Banco Ripley.Seguro Complementario Gratuito.Descuento en Tiendas Ripley.Desarrollo Profesional.Entre otros.¡Postula para ser parte de nuestro equipo!En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
         </is>
       </c>
     </row>
@@ -5444,27 +5444,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Category Manager Nuevos Negocios</t>
+          <t>Favor No postular si no cumple lo requerido.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ripley chile</t>
+          <t>SurChile SPA</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Ofi Cerro Colorado 5240 - Comercial, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56091/category-manager-nuevos-negocios</t>
+          <t>https://firstjob.me/oferta/56084/product-manager-ing-comercial-lampa-valle-grande-1-3-liquidos</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -5485,13 +5485,13 @@
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -5501,24 +5501,24 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>Category Manager Nuevos NegociosEn Ripley Chile, lo tenemos todo ¡Solo nos falta tu talento! 🤩Promovemos equipos diversos y colaborativos, buscando mejorar la experiencia de nuestros clientes a través de la innovación y la cultura de servicio. ¡Súmate a una industria ágil y desafiante!¡Postula para ser parte de nuestro equipo!Estamos en búsqueda de nuestro nuevo Category Manager para la Gerencia de Nuevos Negocios, de nuestra Gerencia Comercial.¿Cuáles serán tus principales desafíos?Encargado de apoyar al comprador en rentabilizar las categorías de Garantía y Rphone de todas las tiendas Ripley y Ripley.com. Para ello deberá poner en práctica todos sus conocimientos comerciales, venta y de marketing para poder crear acciones que generen el crecimiento del negocio. Parte de su responsabilidad será reunirse con proveedores (marcas), buscar nuevos productos, rentabilizar los actuales, visitar tiendas. Si eres una persona que se apasiona por el trabajo dinámico y el desafío constante ¡Esta es tu oportunidad de hacer que las cosas pasen!Tus principales funciones:🚀Estrategias Comerciales: Crear estrategias comerciales y de precios para llegar a las metas de venta y contribución presupuestadas por temporada.Mix de Compra: Presupuestar la compra de marcas y productos nacionales e importados, y en base a ello, generar el mix adecuado de productos y definir la carga de estos, en tiendas de cuerdo a capacidades, de manera de rentabilizar el metro cuadrado.Administrar la Compra: Revisar los abiertos de compra con los Planificadores de Compras, y seguir el comportamiento de las ventas, a fin de mantener volumen y stock suficientes para asegurar el óptimo desarrollo comercial por categoría y ubicación, y/o definir liquidaciones.Análisis de Tendencias de Mercado: Analizar e investigar los mercados internos y externos en cuanto a sus tendencias, competencia y cambios en la moda para así generar atractivas colecciones.Administración de Inventario: Negociar y coordinar constantemente con proveedores para definir precios, calidades, tiempos de despacho, condiciones de pago, cantidades, y exhibición de productos; y supervisar el comportamiento de stocks para la toma oportuna de decisiones en cuanto a compras futuras.Abastecimiento: Supervisar la llegada de los productos y abastecimiento hacia las tiendas.¿Cuáles son los requisitos para tu postulación?🎯Ingeniería Comercial con orientación a Ventas y Marketing (Excluyente)Deseable experiencia 0-1 año en compras consumo masivo o retailManejo de Microsoft Office Intermedio-Avanzado (Excluyente)Ser proactivo, enérgico y dinámico¿Por qué trabajar en Ripley?Pensamos en el bienestar de nuestros colaboradores, es por esto que contamos con atractivos beneficios corporativos como:Capacitaciones y entrenamiento enfocado a tu desarrollo de carrera.Tasa Preferencial en Productos Banco Ripley.Seguro Complementario Gratuito.Descuento en Tiendas Ripley.Desarrollo Profesional.Entre otros.¡Postula para ser parte de nuestro equipo!En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
+          <t>Vacante para Ingenieros Comerciales - EXCLUYENTEEXPERIENCIA PRICING Y ESTRATEGIA COMERCIAL - EXCLUYENTE  1 AÑOHombre por características del cargo - ExcluyenteFavor No postular si no cumple lo requerido.Muchas gracias por su comprensión.EnSurChile SPAbuscamos un/aProduct Managercon visión estratégica, orientación a resultados y pasión por el desarrollo de negocios, para liderar la gestión integral de nuestras líneas de productos y potenciar su crecimiento en el mercado.Esta posición es clave para impulsar la rentabilidad, posicionamiento y expansión del portafolio, asegurando una ejecución comercial efectiva y alineada a los objetivos de la compañía.🚀 Principales responsabilidadesDiseñar e implementar la estrategia comercial y de posicionamiento del producto.Analizar mercado, competencia y oportunidades de crecimiento.Liderar lanzamientos y planes de desarrollo de nuevos productos.Gestionar indicadores de desempeño (ventas, margen, participación de mercado).Coordinar con áreas internas (ventas, operaciones, logística, marketing).Desarrollar y mantener relaciones estratégicas con clientes y proveedores.Identificar oportunidades de mejora e innovación en el portafolio.🎯 RequisitosTítulo de Ingeniería Comercial o carrera afín.Experiencia previa en gestión de productos, desarrollo comercial o áreas similares.Alta capacidad de análisis y visión estratégica.Habilidades de negociación y gestión de proyectos.Manejo de herramientas de análisis y reportes comerciales (deseable).🧩 Competencias claveLiderazgo e iniciativa.Orientación a resultados y cumplimiento de metas.Comunicación efectiva y trabajo colaborativo.Proactividad y autonomía en la toma de decisiones.BeneficiosCaja Los AndesAguinaldos fiestas patrias y fin de año</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Favor No postular si no cumple lo requerido.</t>
+          <t>Analista Tesorería</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SurChile SPA</t>
+          <t>Importante Empresa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5528,20 +5528,20 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Presencial Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56084/product-manager-ing-comercial-lampa-valle-grande-1-3-liquidos</t>
+          <t>https://firstjob.me/oferta/56101/analista-tesoreria</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>analisis</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -5551,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
         <v>1</v>
@@ -5566,33 +5566,33 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>Vacante para Ingenieros Comerciales - EXCLUYENTEEXPERIENCIA PRICING Y ESTRATEGIA COMERCIAL - EXCLUYENTE  1 AÑOHombre por características del cargo - ExcluyenteFavor No postular si no cumple lo requerido.Muchas gracias por su comprensión.EnSurChile SPAbuscamos un/aProduct Managercon visión estratégica, orientación a resultados y pasión por el desarrollo de negocios, para liderar la gestión integral de nuestras líneas de productos y potenciar su crecimiento en el mercado.Esta posición es clave para impulsar la rentabilidad, posicionamiento y expansión del portafolio, asegurando una ejecución comercial efectiva y alineada a los objetivos de la compañía.🚀 Principales responsabilidadesDiseñar e implementar la estrategia comercial y de posicionamiento del producto.Analizar mercado, competencia y oportunidades de crecimiento.Liderar lanzamientos y planes de desarrollo de nuevos productos.Gestionar indicadores de desempeño (ventas, margen, participación de mercado).Coordinar con áreas internas (ventas, operaciones, logística, marketing).Desarrollar y mantener relaciones estratégicas con clientes y proveedores.Identificar oportunidades de mejora e innovación en el portafolio.🎯 RequisitosTítulo de Ingeniería Comercial o carrera afín.Experiencia previa en gestión de productos, desarrollo comercial o áreas similares.Alta capacidad de análisis y visión estratégica.Habilidades de negociación y gestión de proyectos.Manejo de herramientas de análisis y reportes comerciales (deseable).🧩 Competencias claveLiderazgo e iniciativa.Orientación a resultados y cumplimiento de metas.Comunicación efectiva y trabajo colaborativo.Proactividad y autonomía en la toma de decisiones.BeneficiosCaja Los AndesAguinaldos fiestas patrias y fin de año</t>
+          <t>¡Únete a Cumplo como nuestro próximo Treasury Analyst – Chile! 👌En Cumplo, buscamos personas que quieran marcar la diferencia 💚. Personas que no solo busquen un trabajo, sino que quieran aportar al crecimiento de miles de pymes y transformar realidades.Queremos impactar. Soñamos con un mundo en el que todas las empresas accedan a los recursos que necesitan para crecer y desplegar su máximo potencial.¿Te identificas con todo esto? Si es así, ¡te estamos buscando!¿Qué te espera? 🎯• Procesar giros de operaciones a solicitantes, incluyendo refinanciamientos, anticipos y pagos finales.• Gestionar la asociación de pagos en el módulo de tesorería y la dispersión de fondos a beneficiarios.• Realizar conciliaciones bancarias, identificando diferencias y proponiendo mejoras al proceso.• Realizar transferencias bancarias y la gestión de devolución de excedentes según las políticas internas.• Apoyar en la automatización de procesos operativos y flujos de trabajo del área de tesorería.• Colaborar en tareas administrativas y operativas del día a día en coordinación con Finanzas y Operaciones.¿Qué necesitas? 🕵️‍♀️• Profesional de las áreas de Finanzas, Administración, Contabilidad o carreras afines.• Al menos 1 año de experiencia demostrable en contabilidad y finanzas.• Manejo de Excel avanzado (tablas dinámicas, macros, fórmulas anidadas).• Conocimientos contables y financieros básicos (asientos contables, definición de ingresos, entre otros).Beneficios¿Qué ofrecemos? 🎁• Personal Days: Día libre por cumpleaños y mudanza.• Más vacaciones: 3 días extra al año + 2 administrativos.• Sistema de vacaciones 5+1• Puntos flexibles• Seguro complementario.• Convenio con Caja Los Andes.• Cultura cercana y colaborativa: Sé parte de un equipo con propósito.Sobre nosotros:En Cumplo, conectamos a empresas que buscan liquidez con personas dispuestas a invertir en sus proyectos. Nuestra misión es democratizar el financiamiento y apoyar el crecimiento de las pymes en Latinoamérica, promoviendo un ecosistema financiero más justo y transparente.Si compartes nuestra visión y deseas ser parte de este cambio, te invitamos a postular.💡 ¡Postula ahora y sé parte de la transformación financiera! 🚀</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Analista Tesorería</t>
+          <t>Ejecutivo Comercial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Importante Empresa</t>
+          <t>Cumplo</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Av Apoquindo 5400, Chile</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5602,15 +5602,15 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56101/analista-tesoreria</t>
+          <t>https://firstjob.me/oferta/56134/ejecutivo-comercial</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>excel</t>
+          <t>analisis</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -5635,11 +5635,11 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>¡Únete a Cumplo como nuestro próximo Treasury Analyst – Chile! 👌En Cumplo, buscamos personas que quieran marcar la diferencia 💚. Personas que no solo busquen un trabajo, sino que quieran aportar al crecimiento de miles de pymes y transformar realidades.Queremos impactar. Soñamos con un mundo en el que todas las empresas accedan a los recursos que necesitan para crecer y desplegar su máximo potencial.¿Te identificas con todo esto? Si es así, ¡te estamos buscando!¿Qué te espera? 🎯• Procesar giros de operaciones a solicitantes, incluyendo refinanciamientos, anticipos y pagos finales.• Gestionar la asociación de pagos en el módulo de tesorería y la dispersión de fondos a beneficiarios.• Realizar conciliaciones bancarias, identificando diferencias y proponiendo mejoras al proceso.• Realizar transferencias bancarias y la gestión de devolución de excedentes según las políticas internas.• Apoyar en la automatización de procesos operativos y flujos de trabajo del área de tesorería.• Colaborar en tareas administrativas y operativas del día a día en coordinación con Finanzas y Operaciones.¿Qué necesitas? 🕵️‍♀️• Profesional de las áreas de Finanzas, Administración, Contabilidad o carreras afines.• Al menos 1 año de experiencia demostrable en contabilidad y finanzas.• Manejo de Excel avanzado (tablas dinámicas, macros, fórmulas anidadas).• Conocimientos contables y financieros básicos (asientos contables, definición de ingresos, entre otros).Beneficios¿Qué ofrecemos? 🎁• Personal Days: Día libre por cumpleaños y mudanza.• Más vacaciones: 3 días extra al año + 2 administrativos.• Sistema de vacaciones 5+1• Puntos flexibles• Seguro complementario.• Convenio con Caja Los Andes.• Cultura cercana y colaborativa: Sé parte de un equipo con propósito.Sobre nosotros:En Cumplo, conectamos a empresas que buscan liquidez con personas dispuestas a invertir en sus proyectos. Nuestra misión es democratizar el financiamiento y apoyar el crecimiento de las pymes en Latinoamérica, promoviendo un ecosistema financiero más justo y transparente.Si compartes nuestra visión y deseas ser parte de este cambio, te invitamos a postular.💡 ¡Postula ahora y sé parte de la transformación financiera! 🚀</t>
+          <t>¡Únete a Cumplo como nuestro próximoBusiness Developer!👌En Cumplo, buscamos personas que quieran marcar la diferencia 💚. Personas que no solo busquen un trabajo, sino que quieran aportar al crecimiento de miles de pymes y transformar realidades.Queremos impactar. Soñamos con un mundo en el que todas las empresas accedan a los recursos que necesitan para crecer y desplegar su máximo potencial.¿Te identificas con todo esto? Si es así, ¡te estamos buscando!¿Qué te espera? 🎯Analizar el mercado y la competencia para identificar oportunidades de negocio.Diseñar e implementar estrategias de ventas que impulsen el crecimiento de Cumplo.Establecer y mantener relaciones con clientes y socios estratégicos.Colaborar con equipos internos para asegurar el alineamiento en la ejecución de estrategias.Monitorear el rendimiento de las estrategias y realizar ajustes según sea necesario.Preparar informes y presentaciones sobre el progreso de las iniciativas estratégicas.Requerimientos¿Qué necesitas? 🕵️‍♀️Al menos 1 año de experiencia previa en ventas o desarrollo de negocio, idealmente en el sector fintech o servicios financieros.Gusto por las ventas y la atención al cliente.Conocimiento financiero y comercial.Familiaridad con herramientas de análisis de mercado y CRM.Capacidad para trabajar por objetivos.Beneficios¿Qué ofrecemos? 🎁Personal Days: Día libre por cumpleaños y mudanza.Más vacaciones: 3 días extra al año + 2 administrativos.Seguro complementario.Convenio con Caja Los Andes.Cultura cercana y colaborativa: Sé parte de un equipo con propósito.Sobre nosotros 🌍En Cumplo, conectamos a empresas que buscan liquidez con personas dispuestas a invertir en sus proyectos. Nuestra misión es democratizar el financiamiento y apoyar el crecimiento de las pymes en Latinoamérica, promoviendo un ecosistema financiero más justo y transparente.Si compartes nuestra visión y deseas ser parte de este cambio, te invitamos a postular.💡 ¡Postula ahora y sé parte de la transformación financiera! 🚀</t>
         </is>
       </c>
     </row>
@@ -5651,35 +5651,35 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Ejecutivo Comercial</t>
+          <t>Category Manager de Ventas Mayoristas</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cumplo</t>
+          <t>Rosen</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Av Apoquindo 5400, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56134/ejecutivo-comercial</t>
+          <t>https://firstjob.me/oferta/56131/category-manager-de-ventas-mayoristas</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>analisis</t>
+          <t>analisis, excel</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -5689,7 +5689,7 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" t="n">
         <v>1</v>
@@ -5708,7 +5708,7 @@
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>¡Únete a Cumplo como nuestro próximoBusiness Developer!👌En Cumplo, buscamos personas que quieran marcar la diferencia 💚. Personas que no solo busquen un trabajo, sino que quieran aportar al crecimiento de miles de pymes y transformar realidades.Queremos impactar. Soñamos con un mundo en el que todas las empresas accedan a los recursos que necesitan para crecer y desplegar su máximo potencial.¿Te identificas con todo esto? Si es así, ¡te estamos buscando!¿Qué te espera? 🎯Analizar el mercado y la competencia para identificar oportunidades de negocio.Diseñar e implementar estrategias de ventas que impulsen el crecimiento de Cumplo.Establecer y mantener relaciones con clientes y socios estratégicos.Colaborar con equipos internos para asegurar el alineamiento en la ejecución de estrategias.Monitorear el rendimiento de las estrategias y realizar ajustes según sea necesario.Preparar informes y presentaciones sobre el progreso de las iniciativas estratégicas.Requerimientos¿Qué necesitas? 🕵️‍♀️Al menos 1 año de experiencia previa en ventas o desarrollo de negocio, idealmente en el sector fintech o servicios financieros.Gusto por las ventas y la atención al cliente.Conocimiento financiero y comercial.Familiaridad con herramientas de análisis de mercado y CRM.Capacidad para trabajar por objetivos.Beneficios¿Qué ofrecemos? 🎁Personal Days: Día libre por cumpleaños y mudanza.Más vacaciones: 3 días extra al año + 2 administrativos.Seguro complementario.Convenio con Caja Los Andes.Cultura cercana y colaborativa: Sé parte de un equipo con propósito.Sobre nosotros 🌍En Cumplo, conectamos a empresas que buscan liquidez con personas dispuestas a invertir en sus proyectos. Nuestra misión es democratizar el financiamiento y apoyar el crecimiento de las pymes en Latinoamérica, promoviendo un ecosistema financiero más justo y transparente.Si compartes nuestra visión y deseas ser parte de este cambio, te invitamos a postular.💡 ¡Postula ahora y sé parte de la transformación financiera! 🚀</t>
+          <t>📢¡Si te gusta la decoración, el mundo del descanso familiar, Rosen es para ti!  Estamos buscando nuevos y nuevas RosenLovers que quieran ser parte de una de las mejores empresas para trabajar en Chile, ranking GPTW 2025. Buscamos el ADN Rosen en cada uno de nuestros/as colaboradores/as, potenciando la Excelencia, Integridad, Compromiso e Innovación.🙌 En Rosen creemos en el valor de las personas y en la riqueza de equipos diversos. Por eso, promovemos procesos de selección inclusivos y si necesitas algún ajuste para participar en el proceso, puedes indicarlo en tu postulación. Esta vacante se enmarca en nuestro compromiso con la inclusión laboral y la Ley 21.015.Actualmente nos encontramos en búsqueda de un/aCategory Managera trabajar para nuestra Gerencia de Ventas Mayoristas en Modalidad Híbrida, en nuestras oficinas ubicadas en la comuna deColina, Región Metropolitana.🔍¿Cuál es la misión de este cargo?:Gestionar el desempeño comercial de las categorías de producto en el canal Mayorista, identificando oportunidades de crecimiento, optimizando el mix y apoyando al equipo KAM con inteligencia de negocio para el cumplimiento de metas.💡¿Qué harás en este cargo?Análisis de Sell-out por categoría para identificar brechas.Propuesta de acciones de surtido o pricing.Seguimiento de KPIs comerciales por cliente.Mantener catálogo de productos en los distintos Ecommerce, buscando mejorar tasa de conversión y ventas.Elaboración de proyecciones de venta de las distintas líneas de negocio(Colchones, Tapizados, Muebles y Textiles), y análisis de la venta para toma de decisiones.Mantener y mejorar constantemente los sistemas y bancos de información de Mayorista.Otros requerimientos propios del cargo.📌¿Cuáles son los requisitos para rol?Titulado de Ingeniería comercial / civil Industrial, que cuente con hasta 2 años de experiencia laboral en el área comercial.Excel y Powerpoint avanzado, para manejo en visualización de datos.Deseable experiencia con Inteligencia Artificial en el manejo de datos, análisis y visualización.Deseable manejo de herramienta SAP y Qlikview.📌Jornada laboral:Lunes a jueves presencial de 8:00 a 16:30 hrs, viernes teletrabajo.¡Te invitamos a ser parte de una compañía comprometida con sus colaboradores y la sustentabilidad!🌱🙌BeneficiosBeneficios de nuestro team Rosen 🎁:Jornada laboral de 40 horas.Bono de vacaciones 🏝Aguinaldos.30% de descuentos en Productos Rosen.Seguro Complementario de Salud (desde contrato indefinido).Día Libre de Cumpleaños 🎈Regalos Corporativos 🎁Casino corporativo 🍝 y Buses de acercamiento.¡Entre muchos otros!</t>
         </is>
       </c>
     </row>
@@ -5720,37 +5720,33 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Category Manager de Ventas Mayoristas</t>
+          <t>INGENIERO EN ENTRENAMIENTO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Rosen</t>
+          <t>Enaex</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Calama, Antofagasta, Chile</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56131/category-manager-de-ventas-mayoristas</t>
+          <t>https://firstjob.me/oferta/56120/ingeniero-en-entrenamiento</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>3</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>analisis, excel</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -5758,7 +5754,7 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
         <v>1</v>
@@ -5777,7 +5773,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>📢¡Si te gusta la decoración, el mundo del descanso familiar, Rosen es para ti!  Estamos buscando nuevos y nuevas RosenLovers que quieran ser parte de una de las mejores empresas para trabajar en Chile, ranking GPTW 2025. Buscamos el ADN Rosen en cada uno de nuestros/as colaboradores/as, potenciando la Excelencia, Integridad, Compromiso e Innovación.🙌 En Rosen creemos en el valor de las personas y en la riqueza de equipos diversos. Por eso, promovemos procesos de selección inclusivos y si necesitas algún ajuste para participar en el proceso, puedes indicarlo en tu postulación. Esta vacante se enmarca en nuestro compromiso con la inclusión laboral y la Ley 21.015.Actualmente nos encontramos en búsqueda de un/aCategory Managera trabajar para nuestra Gerencia de Ventas Mayoristas en Modalidad Híbrida, en nuestras oficinas ubicadas en la comuna deColina, Región Metropolitana.🔍¿Cuál es la misión de este cargo?:Gestionar el desempeño comercial de las categorías de producto en el canal Mayorista, identificando oportunidades de crecimiento, optimizando el mix y apoyando al equipo KAM con inteligencia de negocio para el cumplimiento de metas.💡¿Qué harás en este cargo?Análisis de Sell-out por categoría para identificar brechas.Propuesta de acciones de surtido o pricing.Seguimiento de KPIs comerciales por cliente.Mantener catálogo de productos en los distintos Ecommerce, buscando mejorar tasa de conversión y ventas.Elaboración de proyecciones de venta de las distintas líneas de negocio(Colchones, Tapizados, Muebles y Textiles), y análisis de la venta para toma de decisiones.Mantener y mejorar constantemente los sistemas y bancos de información de Mayorista.Otros requerimientos propios del cargo.📌¿Cuáles son los requisitos para rol?Titulado de Ingeniería comercial / civil Industrial, que cuente con hasta 2 años de experiencia laboral en el área comercial.Excel y Powerpoint avanzado, para manejo en visualización de datos.Deseable experiencia con Inteligencia Artificial en el manejo de datos, análisis y visualización.Deseable manejo de herramienta SAP y Qlikview.📌Jornada laboral:Lunes a jueves presencial de 8:00 a 16:30 hrs, viernes teletrabajo.¡Te invitamos a ser parte de una compañía comprometida con sus colaboradores y la sustentabilidad!🌱🙌BeneficiosBeneficios de nuestro team Rosen 🎁:Jornada laboral de 40 horas.Bono de vacaciones 🏝Aguinaldos.30% de descuentos en Productos Rosen.Seguro Complementario de Salud (desde contrato indefinido).Día Libre de Cumpleaños 🎈Regalos Corporativos 🎁Casino corporativo 🍝 y Buses de acercamiento.¡Entre muchos otros!</t>
+          <t>Nuestra empresa:Enaex es una empresa filial del grupo Sigdo Koppers, con más de 100 años de trayectoria en el mercado de explosivos. Nos hemos consolidado como el tercer productor mundial de Nitrato de Amonio de baja densidad y el principal prestador de servicios integrales de fragmentación de roca para la minería en Chile y Latinoamérica. Queremos invitarte a crecer con nosotros y desafiarte día a día en una compañía cuyo propósito es Humanizar la minería. Si para ti la prioridad es la vida, tu obsesión es la excelencia, tu vocación son los clientes y tienes como fortaleza la innovación y el emprendimiento, ¡este es tu lugar!Misión del cargo:Se requiere de un profesional con experiencia, que contribuya, junto con el equipo, al proyecto T1Descripción del cargo:- Control de Procesos- Control presupuestario- Administracion de proyectos- Administracion de contratos- Colaboración Interdisciplinaria- Cumplimiento Normativo y Documental- Cumplimiento de plazos establecidos en los Proyectos.- Revisión y liberacion de SAPNuestro Candidato Ideal:Ingeniero Instrumentación y Control, Civil Quimico, Civil Electrico o Civil MecanicoDeseable al menos 1 año de experiencia en cargos o proyectos similaresHabilidades de Comunicación y OrganizaciónProceso de selección:El proceso de selección se realiza a través de Aira - plataforma de reclutamiento diseñado para mejorar tu experiencia de postulación.Para postular solo necesitas:1. Postular a la oferta2. Revisar tu email3. Ingresar a Aira y contestar las preguntas y/o pruebas solicitadasLuego, si vemos que tu perfil se ajusta a lo que estamos buscando, te contactaremos por email (a través de Aira) para seguir a la etapa presencial.Beneficios- Seguro médico- Capacitaciones y cursos- Actividades wellness- Gimnasio- Subsidio escolar para hijos- Subsidio escolar para hijos- Préstamos financieros- Vacaciones extras</t>
         </is>
       </c>
     </row>
@@ -5789,41 +5785,45 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>INGENIERO EN ENTRENAMIENTO</t>
+          <t>Category Manager Textil</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Enaex</t>
+          <t>Rosen</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Calama, Antofagasta, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56120/ingeniero-en-entrenamiento</t>
+          <t>https://firstjob.me/oferta/56132/category-manager-textil</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
-      </c>
-      <c r="H80" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -5842,7 +5842,7 @@
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>Nuestra empresa:Enaex es una empresa filial del grupo Sigdo Koppers, con más de 100 años de trayectoria en el mercado de explosivos. Nos hemos consolidado como el tercer productor mundial de Nitrato de Amonio de baja densidad y el principal prestador de servicios integrales de fragmentación de roca para la minería en Chile y Latinoamérica. Queremos invitarte a crecer con nosotros y desafiarte día a día en una compañía cuyo propósito es Humanizar la minería. Si para ti la prioridad es la vida, tu obsesión es la excelencia, tu vocación son los clientes y tienes como fortaleza la innovación y el emprendimiento, ¡este es tu lugar!Misión del cargo:Se requiere de un profesional con experiencia, que contribuya, junto con el equipo, al proyecto T1Descripción del cargo:- Control de Procesos- Control presupuestario- Administracion de proyectos- Administracion de contratos- Colaboración Interdisciplinaria- Cumplimiento Normativo y Documental- Cumplimiento de plazos establecidos en los Proyectos.- Revisión y liberacion de SAPNuestro Candidato Ideal:Ingeniero Instrumentación y Control, Civil Quimico, Civil Electrico o Civil MecanicoDeseable al menos 1 año de experiencia en cargos o proyectos similaresHabilidades de Comunicación y OrganizaciónProceso de selección:El proceso de selección se realiza a través de Aira - plataforma de reclutamiento diseñado para mejorar tu experiencia de postulación.Para postular solo necesitas:1. Postular a la oferta2. Revisar tu email3. Ingresar a Aira y contestar las preguntas y/o pruebas solicitadasLuego, si vemos que tu perfil se ajusta a lo que estamos buscando, te contactaremos por email (a través de Aira) para seguir a la etapa presencial.Beneficios- Seguro médico- Capacitaciones y cursos- Actividades wellness- Gimnasio- Subsidio escolar para hijos- Subsidio escolar para hijos- Préstamos financieros- Vacaciones extras</t>
+          <t>📢¡Si te gusta la decoración, el mundo del descanso familiar, Rosen es para ti!  Estamos buscando nuevos y nuevas RosenLovers que quieran ser parte de una de las mejores empresas para trabajar en Chile, ranking GPTW 2025. Buscamos el ADN Rosen en cada uno de nuestros/as colaboradores/as, potenciando la Excelencia, Integridad, Compromiso e Innovación.🙌 En Rosen creemos en el valor de las personas y en la riqueza de equipos diversos. Por eso, promovemos procesos de selección inclusivos y si necesitas algún ajuste para participar en el proceso, puedes indicarlo en tu postulación. Esta vacante se enmarca en nuestro compromiso con la inclusión laboral y la Ley 21.015.Actualmente nos encontramos en búsqueda de un/aCategory Managera trabajar para nuestra Gerencia de Productos en Modalidad Híbrida, en nuestras oficinas ubicadas en la comuna de Colina, Región Metropolitana.🔍¿Cuál es la misión de este rol?Analizar y supervisar las ventas de los productos y su comportamiento en el mercado para los usuarios finales. Adicionalmente, apoyar en el seguimiento del desarrollo de las colecciones de textil.💡¿Qué harás en este cargo?Analizar y monitorear mapas de precios v/s ventas de productos de la línea textil, identificando el margen de contribución, con el fin de aportar información clave en la toma de decisiones y en la estrategia de comercialización de Rosen.Emitir informes periódicos de ventas, con el fin de analizar el performance de cada familia de productos.Participar en el desarrollo de productos nuevos y llevar el correcto seguimiento de las Gantt asociadas, además de generar y actualizar la planilla de BBDD de productos por cada colección.Otros requerimientos propios del cargo.📌¿Cuáles son los requisitos para rol?Titulado/a en Ingeniería Comercial o carrera afín.1 a 2 años de experiencia en cargos similares ideal interés en rubro Retail.Conocimiento en Excel nivel intermedio.Deseable manejo de ingles, oral y escrito.Disponibilidad para trabajar en modalidad híbrida en Colina (4 días presencial, contamos con estacionamiento y buses de acercamiento).¡Te invitamos a ser parte de una compañía comprometida con sus colaboradores y la sustentabilidad!🌱🙌BeneficiosBeneficios de nuestro team Rosen 🎁:Jornada laboral de 40 horas.Bono de vacaciones 🏝Aguinaldos.30% de descuentos en Productos Rosen.Seguro Complementario de Salud (desde contrato indefinido).Día Libre de Cumpleaños 🎈Regalos Corporativos 🎁Casino corporativo 🍝 y Buses de acercamiento.¡Entre muchos otros!</t>
         </is>
       </c>
     </row>
@@ -5854,45 +5854,45 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Category Manager Textil</t>
+          <t>Ingenieroa de Procesos - Temuco</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rosen</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Región de la Araucanía, Chile</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56132/category-manager-textil</t>
+          <t>https://firstjob.me/oferta/56123/ingeniero-a-de-procesos-temuco</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>excel</t>
+          <t>analisis, excel, power bi, looker studio, looker</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
         <v>1</v>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>📢¡Si te gusta la decoración, el mundo del descanso familiar, Rosen es para ti!  Estamos buscando nuevos y nuevas RosenLovers que quieran ser parte de una de las mejores empresas para trabajar en Chile, ranking GPTW 2025. Buscamos el ADN Rosen en cada uno de nuestros/as colaboradores/as, potenciando la Excelencia, Integridad, Compromiso e Innovación.🙌 En Rosen creemos en el valor de las personas y en la riqueza de equipos diversos. Por eso, promovemos procesos de selección inclusivos y si necesitas algún ajuste para participar en el proceso, puedes indicarlo en tu postulación. Esta vacante se enmarca en nuestro compromiso con la inclusión laboral y la Ley 21.015.Actualmente nos encontramos en búsqueda de un/aCategory Managera trabajar para nuestra Gerencia de Productos en Modalidad Híbrida, en nuestras oficinas ubicadas en la comuna de Colina, Región Metropolitana.🔍¿Cuál es la misión de este rol?Analizar y supervisar las ventas de los productos y su comportamiento en el mercado para los usuarios finales. Adicionalmente, apoyar en el seguimiento del desarrollo de las colecciones de textil.💡¿Qué harás en este cargo?Analizar y monitorear mapas de precios v/s ventas de productos de la línea textil, identificando el margen de contribución, con el fin de aportar información clave en la toma de decisiones y en la estrategia de comercialización de Rosen.Emitir informes periódicos de ventas, con el fin de analizar el performance de cada familia de productos.Participar en el desarrollo de productos nuevos y llevar el correcto seguimiento de las Gantt asociadas, además de generar y actualizar la planilla de BBDD de productos por cada colección.Otros requerimientos propios del cargo.📌¿Cuáles son los requisitos para rol?Titulado/a en Ingeniería Comercial o carrera afín.1 a 2 años de experiencia en cargos similares ideal interés en rubro Retail.Conocimiento en Excel nivel intermedio.Deseable manejo de ingles, oral y escrito.Disponibilidad para trabajar en modalidad híbrida en Colina (4 días presencial, contamos con estacionamiento y buses de acercamiento).¡Te invitamos a ser parte de una compañía comprometida con sus colaboradores y la sustentabilidad!🌱🙌BeneficiosBeneficios de nuestro team Rosen 🎁:Jornada laboral de 40 horas.Bono de vacaciones 🏝Aguinaldos.30% de descuentos en Productos Rosen.Seguro Complementario de Salud (desde contrato indefinido).Día Libre de Cumpleaños 🎈Regalos Corporativos 🎁Casino corporativo 🍝 y Buses de acercamiento.¡Entre muchos otros!</t>
+          <t>Estamos buscando a un/aIngeniero/a de Procesospara desempeñarse en nuestra planta enTemuco.Principales funciones:Consolidar y analizar datos provenientes de distintas áreas de la planta.Elaborar reportería y dar seguimiento a indicadores monetarios y de eficiencia.Coordinar con las áreas la entrega oportuna de información y apoyarlas en el análisis de sus datos.Implementar mejoras en terreno en torno al uso y comprensión de los datos entregados.Requisitos:Título de Ingeniería Civil Industrial, o afines.Alrededor de 2 años de experiencia laboral en cargos similares.Manejo de Excel intermedio (excluyente).Manejo de SAP (deseable).Manejo de Looker Studio (deseable).Manejo de Power Bi (deseable).</t>
         </is>
       </c>
     </row>
@@ -5923,104 +5923,104 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ingenieroa de Procesos - Temuco</t>
+          <t>Práctica Ciberseguridad - IT Advisory</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>KPMG Chile</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Región de la Araucanía, Chile</t>
+          <t>Las Condes, Metropolitana, Chile, Chile</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56123/ingeniero-a-de-procesos-temuco</t>
+          <t>https://firstjob.me/oferta/56124/practica-ciberseguridad-it-advisory</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>analisis, excel, power bi, looker studio, looker</t>
+          <t>analisis, informatica, cloud, gcp, aws, azure</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>Estamos buscando a un/aIngeniero/a de Procesospara desempeñarse en nuestra planta enTemuco.Principales funciones:Consolidar y analizar datos provenientes de distintas áreas de la planta.Elaborar reportería y dar seguimiento a indicadores monetarios y de eficiencia.Coordinar con las áreas la entrega oportuna de información y apoyarlas en el análisis de sus datos.Implementar mejoras en terreno en torno al uso y comprensión de los datos entregados.Requisitos:Título de Ingeniería Civil Industrial, o afines.Alrededor de 2 años de experiencia laboral en cargos similares.Manejo de Excel intermedio (excluyente).Manejo de SAP (deseable).Manejo de Looker Studio (deseable).Manejo de Power Bi (deseable).</t>
+          <t>Buscamos un estudiante proactivo y con gran potencial para unirse a nuestro equipo de IT Advisory en KPMG Chile.RequisitosEstudiante de Ingeniería Informática, Técnico en Informática o carreras afines.Disponibilidad para realizar una práctica de al menos 3 meses.Seguro escolar vigente.Principales responsabilidadesParticipar activamente en proyectos de seguridad de la información y ciberseguridad.Apoyar en el diseño e implementación de revisiones.Participar en la evaluación de riesgos.Desarrollar soluciones de mitigación.Conocimientos y habilidades valoradasCapacidad para analizar y comunicar métricas clave de seguridad.Enfoque en la automatización y mejora continua de procesos.Conocimientos en remediación de vulnerabilidades.Análisis forense.Auditoría de código.Arquitecturas cloud (Azure, GCP, AWS).Familiaridad con frameworks de seguridad como OWASP, ISO27001, NIST, CIS, CSA, PCI, Swift o RAN 20-10.Nivel de inglés intermedio/avanzado (será un plus).¿Qué buscamos?Si buscas un entorno dinámico que fomente el aprendizaje continuo y te brinde la oportunidad de desarrollar tus habilidades en ciberseguridad, ¡esta práctica es para ti!Beneficios¿Qué ganas tú?🌎Ser parte de una de las principales compañías de Auditoría y Consultoría a nivel mundial.🚀 Oportunidades de desarrollo profesional.💻Jornada de trabajo híbrida.🏢Oficinas de primer nivel ubicadas en Las Condes, frente al Parque Araucano.💯Múltiples convenios corporativos.🎉Actividades como fiestas, Meeting Points y encuentros de área para disfrutar con compañeros.🎂Tu día de cumpleaños es completamente libre para que lo disfrutes como desees.💸Remuneración mensual: $400.000 líquidos.En KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas , con un propósito claro, para una mejor sociedad. Valoramos las diversas habilidades y fortalezas, tanto personales como profesionales, que cada persona aporta.En KPMG estamos comprometidos con la Diversidad e inclusión , nuestras ofertas de empleo están disponibles con los ajustes razonables necesarios para tu proceso. Juntos, estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. ¡Anímate y ven a descubrir por qué somos la opción más clara! 🥇</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Práctica Ciberseguridad - IT Advisory</t>
+          <t>ANALISTA PROYECTOS DE SOSTENIBILIDAD I</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>KPMG Chile</t>
+          <t>BCP</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Las Condes, Metropolitana, Chile, Chile</t>
+          <t>Lima, Perú</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56124/practica-ciberseguridad-it-advisory</t>
+          <t>https://firstjob.me/oferta/56148/analista-proyectos-de-sostenibilidad-i</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>analisis, informatica, cloud, gcp, aws, azure</t>
+          <t>analisis</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -6030,10 +6030,10 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -6045,11 +6045,11 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>Buscamos un estudiante proactivo y con gran potencial para unirse a nuestro equipo de IT Advisory en KPMG Chile.RequisitosEstudiante de Ingeniería Informática, Técnico en Informática o carreras afines.Disponibilidad para realizar una práctica de al menos 3 meses.Seguro escolar vigente.Principales responsabilidadesParticipar activamente en proyectos de seguridad de la información y ciberseguridad.Apoyar en el diseño e implementación de revisiones.Participar en la evaluación de riesgos.Desarrollar soluciones de mitigación.Conocimientos y habilidades valoradasCapacidad para analizar y comunicar métricas clave de seguridad.Enfoque en la automatización y mejora continua de procesos.Conocimientos en remediación de vulnerabilidades.Análisis forense.Auditoría de código.Arquitecturas cloud (Azure, GCP, AWS).Familiaridad con frameworks de seguridad como OWASP, ISO27001, NIST, CIS, CSA, PCI, Swift o RAN 20-10.Nivel de inglés intermedio/avanzado (será un plus).¿Qué buscamos?Si buscas un entorno dinámico que fomente el aprendizaje continuo y te brinde la oportunidad de desarrollar tus habilidades en ciberseguridad, ¡esta práctica es para ti!Beneficios¿Qué ganas tú?🌎Ser parte de una de las principales compañías de Auditoría y Consultoría a nivel mundial.🚀 Oportunidades de desarrollo profesional.💻Jornada de trabajo híbrida.🏢Oficinas de primer nivel ubicadas en Las Condes, frente al Parque Araucano.💯Múltiples convenios corporativos.🎉Actividades como fiestas, Meeting Points y encuentros de área para disfrutar con compañeros.🎂Tu día de cumpleaños es completamente libre para que lo disfrutes como desees.💸Remuneración mensual: $400.000 líquidos.En KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas , con un propósito claro, para una mejor sociedad. Valoramos las diversas habilidades y fortalezas, tanto personales como profesionales, que cada persona aporta.En KPMG estamos comprometidos con la Diversidad e inclusión , nuestras ofertas de empleo están disponibles con los ajustes razonables necesarios para tu proceso. Juntos, estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. ¡Anímate y ven a descubrir por qué somos la opción más clara! 🥇</t>
+          <t>Buscamos a los que tienen ganas de transformar el país. A los que quieren llegar lejos. Por qué esto no es solo un trabajo. Esto es desafiarte en grande para impactar en grande. Te estamos buscando para que formes parte de nuestro equipoANALISTA PROYECTOS DE SOSTENIBILIDAD I.¿Cuál es el retoFormar parte del equipo que se tendrá a su cargo la recopilación, análisis y reporte de la data vinculada a las métricas de sostenibilidad.¿Cómo impactarás en grande?Diseñar y mantener el sistema de información de sostenibilidad.Mapear fuentes de información, responsables, metodologías y periodicidades.Definir reglas de trazabilidad y documentación para indicadores de sostenibilidad.Dar soporte a reportería regulatoria local en sostenibilidad, reportes exigidos por banca multilateral, Memoria Integrada, Reporte de Sostenibilidad, TCFD, reportes Credicorp, indicadores estratégicos y cuestionarios ESG¿Qué necesitamos de ti?Eres Bachiller en Ingenierías, Computer Science, Administración o carreras afines.Tienes experiencia en recopilación, análisis, identificación de insights y presentación de data.Deseable experiencia en análisis predictivo, consultas y armado de querys.Mínimo dos años de experiencia laboral, de preferencia en el sector financieroSQL – intermedioPython – intermedioPower Query – intermedioPower bi – básico - intermedioExcel - avanzadoInglés – intermedio – deseableAgente de IA - deseable¿Por qué unirte a nuestro equipo?Ser parte de la empresa #1 en Merco Talento 2025.Convenio de prácticas con el Credicorp desde tu primer día.Accede a incentivos por tu esfuerzo/desempeño.Acompañamiento de líderes expertos y referentes en la banca.Acceso a descuentos en productos financieros.Beneficios corporativos exclusivos por provincia para disfrutar con tu familia.Formarás parte de una cultura constante de reconocimientos.Sí, a ti. Te estamos buscando ¡Únete al equipo BCP!“Somos una organización comprometida con la igualdad de derechos y oportunidades. Nuestros procesos de selección se rigen bajo una política donde nuestras/os postulantes son consideradas/os sin importar su origen, género, raza o cualquier otra característica, condición o preferencia, promoviendo así una cultura de respeto mutuo"</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ANALISTA PROYECTOS DE SOSTENIBILIDAD I</t>
+          <t>Analista de Gestión Comercial PYME</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Lima, Perú</t>
+          <t>San Isidro, Perú</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -6081,15 +6081,15 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56148/analista-proyectos-de-sostenibilidad-i</t>
+          <t>https://firstjob.me/oferta/56143/analista-de-gestion-comercial-pyme</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>analisis</t>
+          <t>sql, analisis, estadistica, excel, power bi</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -6108,7 +6108,7 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>Buscamos a los que tienen ganas de transformar el país. A los que quieren llegar lejos. Por qué esto no es solo un trabajo. Esto es desafiarte en grande para impactar en grande. Te estamos buscando para que formes parte de nuestro equipoANALISTA PROYECTOS DE SOSTENIBILIDAD I.¿Cuál es el retoFormar parte del equipo que se tendrá a su cargo la recopilación, análisis y reporte de la data vinculada a las métricas de sostenibilidad.¿Cómo impactarás en grande?Diseñar y mantener el sistema de información de sostenibilidad.Mapear fuentes de información, responsables, metodologías y periodicidades.Definir reglas de trazabilidad y documentación para indicadores de sostenibilidad.Dar soporte a reportería regulatoria local en sostenibilidad, reportes exigidos por banca multilateral, Memoria Integrada, Reporte de Sostenibilidad, TCFD, reportes Credicorp, indicadores estratégicos y cuestionarios ESG¿Qué necesitamos de ti?Eres Bachiller en Ingenierías, Computer Science, Administración o carreras afines.Tienes experiencia en recopilación, análisis, identificación de insights y presentación de data.Deseable experiencia en análisis predictivo, consultas y armado de querys.Mínimo dos años de experiencia laboral, de preferencia en el sector financieroSQL – intermedioPython – intermedioPower Query – intermedioPower bi – básico - intermedioExcel - avanzadoInglés – intermedio – deseableAgente de IA - deseable¿Por qué unirte a nuestro equipo?Ser parte de la empresa #1 en Merco Talento 2025.Convenio de prácticas con el Credicorp desde tu primer día.Accede a incentivos por tu esfuerzo/desempeño.Acompañamiento de líderes expertos y referentes en la banca.Acceso a descuentos en productos financieros.Beneficios corporativos exclusivos por provincia para disfrutar con tu familia.Formarás parte de una cultura constante de reconocimientos.Sí, a ti. Te estamos buscando ¡Únete al equipo BCP!“Somos una organización comprometida con la igualdad de derechos y oportunidades. Nuestros procesos de selección se rigen bajo una política donde nuestras/os postulantes son consideradas/os sin importar su origen, género, raza o cualquier otra característica, condición o preferencia, promoviendo así una cultura de respeto mutuo"</t>
+          <t>Buscamos a los que tienen ganas de transformar el país. A los que quieren llegar lejos. Por qué esto no es solo un trabajo. Esto es desafiarte en grande para impactar en grande. Esto es el BCP y te estamos buscando para que formes parte de nuestro equipo comoAnalista de Gestión Comercial PYME¿Cuál es el reto?Asegurar la ejecución, integridad y oportunidad de los procesos comerciales de compensación variable, reconocimientos, y gestión de procesos del segmento PyME, brindando analítica accionable y gobierno de datos para impulsar el cumplimiento de metas, la motivación comercial y la mejora continua.¿Cómo impactarás en grande?Monitorear indicadores comerciales y de planillas, reclamos de ventas y pago de incentivos.Levantar y gestionar flujos comerciales y operativos identificando ineficiencias o reprocesos y proponer mejoras.Análisis comercial PYME, generar insights, evaluar impactos y dar seguimiento.Diseñar iniciativas comerciales/data driven, estructurar planes con kpis, gestionar pilotos y escalar soluciones.Creación de Metodología de Gestión EfectivaAdministrar el ciclo de metas comerciales PYME.¿Qué necesitamos de ti?Egresado, Bachiller universitario de Ingeniería Industrial / Sistemas / Economía / Estadística / Administración o afines.Tiempo en el puesto: mínimo 1 año; Empresas del sector bancario.Excel Avanzado (indispensable).SQL a nivel intermedio.Power BI a nivel intermedio.Conocimientos en análisis de datos, gestión de procesos y operaciones.Deseable conocimiento de Power Apps.Inglés intermedio (deseable).Disponibilidad para laborar de manera presencial, de lunes a viernes, en el horario de 9:00 a.m. a 6:00 p.m.¿Por qué unirte a nuestro equipo?Ser parte de la empresa #1 en Merco Talento 2025.Ingreso a planilla BCP desde tu primer día.Accede a incentivos por tu esfuerzo/desempeñoAcompañamiento de líderes expertos y referentes en la banca.Acceso a descuentos en productos financieros.Beneficios corporativos exclusivos por provincia para disfrutar con tu familia.Formarás parte de una cultura constante de reconocimientosSí, a ti. Te estamos buscando ¡Únete al equipo BCP!“Somos una organización comprometida con la igualdad de derechos y oportunidades. Nuestros procesos de selección se rigen bajo una política donde nuestras/os postulantes son consideradas/os sin importar su origen, género, raza o cualquier otra característica, condición o preferencia, promoviendo así una cultura de respeto mutuo"</t>
         </is>
       </c>
     </row>
@@ -6130,17 +6130,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Analista de Gestión Comercial PYME</t>
+          <t>Ejecutivo de Seguros</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BCP</t>
+          <t>Mutucar</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>San Isidro, Perú</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56143/analista-de-gestion-comercial-pyme</t>
+          <t>https://firstjob.me/oferta/56154/ejecutivo-de-seguros</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>sql, analisis, estadistica, excel, power bi</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>Buscamos a los que tienen ganas de transformar el país. A los que quieren llegar lejos. Por qué esto no es solo un trabajo. Esto es desafiarte en grande para impactar en grande. Esto es el BCP y te estamos buscando para que formes parte de nuestro equipo comoAnalista de Gestión Comercial PYME¿Cuál es el reto?Asegurar la ejecución, integridad y oportunidad de los procesos comerciales de compensación variable, reconocimientos, y gestión de procesos del segmento PyME, brindando analítica accionable y gobierno de datos para impulsar el cumplimiento de metas, la motivación comercial y la mejora continua.¿Cómo impactarás en grande?Monitorear indicadores comerciales y de planillas, reclamos de ventas y pago de incentivos.Levantar y gestionar flujos comerciales y operativos identificando ineficiencias o reprocesos y proponer mejoras.Análisis comercial PYME, generar insights, evaluar impactos y dar seguimiento.Diseñar iniciativas comerciales/data driven, estructurar planes con kpis, gestionar pilotos y escalar soluciones.Creación de Metodología de Gestión EfectivaAdministrar el ciclo de metas comerciales PYME.¿Qué necesitamos de ti?Egresado, Bachiller universitario de Ingeniería Industrial / Sistemas / Economía / Estadística / Administración o afines.Tiempo en el puesto: mínimo 1 año; Empresas del sector bancario.Excel Avanzado (indispensable).SQL a nivel intermedio.Power BI a nivel intermedio.Conocimientos en análisis de datos, gestión de procesos y operaciones.Deseable conocimiento de Power Apps.Inglés intermedio (deseable).Disponibilidad para laborar de manera presencial, de lunes a viernes, en el horario de 9:00 a.m. a 6:00 p.m.¿Por qué unirte a nuestro equipo?Ser parte de la empresa #1 en Merco Talento 2025.Ingreso a planilla BCP desde tu primer día.Accede a incentivos por tu esfuerzo/desempeñoAcompañamiento de líderes expertos y referentes en la banca.Acceso a descuentos en productos financieros.Beneficios corporativos exclusivos por provincia para disfrutar con tu familia.Formarás parte de una cultura constante de reconocimientosSí, a ti. Te estamos buscando ¡Únete al equipo BCP!“Somos una organización comprometida con la igualdad de derechos y oportunidades. Nuestros procesos de selección se rigen bajo una política donde nuestras/os postulantes son consideradas/os sin importar su origen, género, raza o cualquier otra característica, condición o preferencia, promoviendo así una cultura de respeto mutuo"</t>
+          <t>Somos una organización financiera sin fines de lucro del rubro del seguro, con el propósito de "Brindar apoyo y seguridad a quienes nos entregan seguridad". Buscamos un Ejecutivo de Seguros que nos ayude a realizar la atención a asegurados, entregando respuestas directas a requerimientos de información, orientando a los usuarios sobre la documentación necesaria para contratar y/o liquidar algún seguro, de acuerdo con protocolos y procedimientos establecidos.Funciones principales:🔵Atender presencialmente a los clientes.🔵Asesorar a los asegurados en materias de seguros.🔵Realizar formalización de seguros.Requisitos:🔵Título Ingeniero Comercial, Administración de Empresas o carrera afín.🔵Especialización y/o conocimientos específicos:💡Cursos sobre Seguros.💡Conceptos básicos de contabilidad aplicada a seguros.💡Curso de Atención al cliente.💡Conocimiento Sisnet.🔵Dominio computacional de Herramientas Office: Word a nivel básico y Excel a nivelintermedio.🔵Experiencia laboral: 2 años en Ventas en compañías de seguros, bancos u organizacionesafines.🔵Deseable experiencia como ejecutivo de seguros de incendio.BeneficiosBeneficios:🟢38 horas y 15 minutos de trabajo semanal.🟢Seguros complementario, vida, salud, dental y catastrófico.🟢20 días hábiles anuales de vacaciones.🟢3 días administrativos.🟢El día del cumpleaños si cae hábil es libre.🟢Clases de acondicionamiento físico y zumba.🟢Viernes Jeans Day.🟢Centros recreacionales.🟢Actividades de integración.</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ejecutivo de Seguros</t>
+          <t>Ingeniero Machine Learning</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Mutucar</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6214,20 +6214,20 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56154/ejecutivo-de-seguros</t>
+          <t>https://firstjob.me/oferta/56149/ingeniero-machine-learning</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>excel</t>
+          <t>python, sql, machine learning, estadistica, matematica, informatica, cloud, gcp, aws, azure</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -6237,10 +6237,10 @@
         <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -6252,11 +6252,11 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>Somos una organización financiera sin fines de lucro del rubro del seguro, con el propósito de "Brindar apoyo y seguridad a quienes nos entregan seguridad". Buscamos un Ejecutivo de Seguros que nos ayude a realizar la atención a asegurados, entregando respuestas directas a requerimientos de información, orientando a los usuarios sobre la documentación necesaria para contratar y/o liquidar algún seguro, de acuerdo con protocolos y procedimientos establecidos.Funciones principales:🔵Atender presencialmente a los clientes.🔵Asesorar a los asegurados en materias de seguros.🔵Realizar formalización de seguros.Requisitos:🔵Título Ingeniero Comercial, Administración de Empresas o carrera afín.🔵Especialización y/o conocimientos específicos:💡Cursos sobre Seguros.💡Conceptos básicos de contabilidad aplicada a seguros.💡Curso de Atención al cliente.💡Conocimiento Sisnet.🔵Dominio computacional de Herramientas Office: Word a nivel básico y Excel a nivelintermedio.🔵Experiencia laboral: 2 años en Ventas en compañías de seguros, bancos u organizacionesafines.🔵Deseable experiencia como ejecutivo de seguros de incendio.BeneficiosBeneficios:🟢38 horas y 15 minutos de trabajo semanal.🟢Seguros complementario, vida, salud, dental y catastrófico.🟢20 días hábiles anuales de vacaciones.🟢3 días administrativos.🟢El día del cumpleaños si cae hábil es libre.🟢Clases de acondicionamiento físico y zumba.🟢Viernes Jeans Day.🟢Centros recreacionales.🟢Actividades de integración.</t>
+          <t>📢 Estamos buscando un(a)Machine Learning Engineerpara sumarse a nuestro equipo y liderar el desarrollo e implementación de soluciones de Machine Learning que generen impacto real en el negocio.Si te motiva trabajar con datos, modelos predictivos, automatización y tecnologías Cloud, esta oportunidad es para ti.Principales responsabilidades:Diseñar y desarrollar pipelines de datos para analítica avanzada.Construir e implementar pipelines de predicción para modelos de IA.Desplegar modelos de Machine Learning en ambientes productivos.Monitorear el rendimiento y desempeño de modelos en producción.Diseñar procesos automáticos de reentrenamiento y mejora de modelos.Contribuir a la escalabilidad y confiabilidad de las soluciones de inteligencia artificial.Perfil deseadoFormación en: Ingeniería Civil en Computación e Informática, Ingeniería Civil Industrial, Ingeniería Matemática, Ingeniería Estadística o carrera afín.Experiencia: 1 a 2 años en cargos similares.Conocimientos en:Machine Learning y Deep Learning.Python y SQL.Desarrollo de pipelines de datos.TensorFlow, PyTorch y/o Scikit-Learn.Bases de datos SQL y NoSQL.Cloud Computing (AWS, Azure o GCP).Docker y Kubernetes.Monitoreo y mantenimiento de modelos en producción.BeneficiosBeneficios:Seguro complementario de salud, dental, vida y catastrófico cofinanciado.Aguinaldos.Bono anual.Día libre de cumpleaños.Jornada laboral de 40 horas semanales.Modalidad de trabajo híbrida.Creemos en la diversidad y promovemos la igualdad de oportunidades. Esta oferta se enmarca en la Ley 21.015 que incentiva la inclusión laboral de personas con discapacidad.Si te interesa desarrollar soluciones de Machine Learning de alto impacto y ser parte de un equipo innovador, ¡te invitamos a postular!</t>
         </is>
       </c>
     </row>
@@ -6268,12 +6268,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ingeniero Machine Learning</t>
+          <t>Analista de Riesgo de Crédito Empresas</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>BICE</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6283,20 +6283,20 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56149/ingeniero-machine-learning</t>
+          <t>https://firstjob.me/oferta/56160/analista-de-riesgo-de-credito-empresas</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>python, sql, machine learning, estadistica, matematica, informatica, cloud, gcp, aws, azure</t>
+          <t>analisis</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -6309,7 +6309,7 @@
         <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -6321,11 +6321,11 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>📢 Estamos buscando un(a)Machine Learning Engineerpara sumarse a nuestro equipo y liderar el desarrollo e implementación de soluciones de Machine Learning que generen impacto real en el negocio.Si te motiva trabajar con datos, modelos predictivos, automatización y tecnologías Cloud, esta oportunidad es para ti.Principales responsabilidades:Diseñar y desarrollar pipelines de datos para analítica avanzada.Construir e implementar pipelines de predicción para modelos de IA.Desplegar modelos de Machine Learning en ambientes productivos.Monitorear el rendimiento y desempeño de modelos en producción.Diseñar procesos automáticos de reentrenamiento y mejora de modelos.Contribuir a la escalabilidad y confiabilidad de las soluciones de inteligencia artificial.Perfil deseadoFormación en: Ingeniería Civil en Computación e Informática, Ingeniería Civil Industrial, Ingeniería Matemática, Ingeniería Estadística o carrera afín.Experiencia: 1 a 2 años en cargos similares.Conocimientos en:Machine Learning y Deep Learning.Python y SQL.Desarrollo de pipelines de datos.TensorFlow, PyTorch y/o Scikit-Learn.Bases de datos SQL y NoSQL.Cloud Computing (AWS, Azure o GCP).Docker y Kubernetes.Monitoreo y mantenimiento de modelos en producción.BeneficiosBeneficios:Seguro complementario de salud, dental, vida y catastrófico cofinanciado.Aguinaldos.Bono anual.Día libre de cumpleaños.Jornada laboral de 40 horas semanales.Modalidad de trabajo híbrida.Creemos en la diversidad y promovemos la igualdad de oportunidades. Esta oferta se enmarca en la Ley 21.015 que incentiva la inclusión laboral de personas con discapacidad.Si te interesa desarrollar soluciones de Machine Learning de alto impacto y ser parte de un equipo innovador, ¡te invitamos a postular!</t>
+          <t>En Banco BICE creemos que las personas son el motor de nuestro crecimiento. Impulsamos el desarrollo profesional en un entorno colaborativo, desafiante y con sello humano, donde el aprendizaje continuo y la excelencia son parte de nuestro día a día.¿Te apasiona el análisis financiero y te interesa desarrollar una carrera en riesgo de crédito?Estamos buscando un/a Analista de Riesgo de Crédito Empresas para sumarse a nuestra Gerencia de Riesgo Banca Empresas y Corporaciones.🔍 ¿Qué harás en este rol?✅ Analizar información financiera de empresas para la elaboración de informes de riesgo.✅ Evaluar antecedentes financieros de clientes y apoyar procesos de renovación y otorgamiento de créditos.✅ Participar en reuniones y visitas a clientes para recopilar información relevante para el análisis.✅ Preparar presentaciones y propuestas para comités de crédito.✅ Desempeñarte como contraparte de riesgo para las distintas gerencias comerciales del Banco.✅ Apoyar iniciativas y proyectos del área, contribuyendo a la mejora continua de los procesos.🎓 ¿Qué necesitas para postular?Título profesional de Ingeniería Comercial con magister en finanzas o carrera afín.Entre 0 y 1 año de experiencia laboral. (EXCLUYENTE ESTAR TITULADO)Deseable que hayas realizado tu práctia en áreas de análisis de riesgo o similaresCapacidad analítica, proactividad y orientación al aprendizaje.Si buscas iniciar tu carrera en el mundo financiero y desarrollarte en una de las áreas estratégicas del Banco, este desafío es para ti.¡Te invitamos a postular y ser parte de Banco BICE!Beneficios🏢Modalidad de trabajo según rol: Algunas posiciones acceden a un sistema híbrido, mientras que las áreas comerciales operan 100% de forma presencial.🍽️Almuerzo diario cubierto: Si trabajas en casa matriz, accedes al casino corporativo con almuerzo gratuito. Si estás en una sucursal, se te asigna un monto diario para cubrir este gasto.🛍️Descuentos exclusivos y convenios: Acceso a beneficios con diversas empresas asociadas en áreas como salud, retail, entretenimiento y más.⚽Actividades internas: Participación en torneos deportivos, actividades lúdicas, operativos oftalmológicos y otras instancias que promueven el bienestar.🤝Cultura cercana y participativa: Ser parte activa de un entorno laboral colaborativo, donde se vive la cultura organizacional día a día.🩺Seguros complementarios: Cobertura en salud, dental y de vida, para que cuentes con mayor respaldo y tranquilidad.🐾Seguro para mascotas: Protección adicional para tus compañeros de cuatro patas.🏋️Convenio con gimnasios: Accede a tarifas preferenciales para mantenerte activo y saludable.🎓Formación continua: Convenios y descuentos con instituciones educativas para diplomados, cursos y otros programas de desarrollo profesional.🚲Acceso a bicicletero: Estacionamiento seguro para bicicletas en casa matriz.🅿️Convenio de estacionamientos: Tarifas preferenciales en estacionamientos cercanos.📱Convenio con Entel: Descuentos en planes y equipos móviles.🦷Red de centros odontológicos: Acceso a múltiples convenios para atención dental.🎁Bonos diversos: Incluye bonos por escolaridad, fallecimiento, vacaciones, invierno, excelencia académica, aguinaldos de Fiestas Patrias y Navidad, entre otros.</t>
         </is>
       </c>
     </row>
@@ -6337,17 +6337,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Analista de Riesgo de Crédito Empresas</t>
+          <t>Analista Tienda de Conveniencia Gerencia Ventas</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BICE</t>
+          <t>Arcor</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Las Condes, Chile</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56160/analista-de-riesgo-de-credito-empresas</t>
+          <t>https://firstjob.me/oferta/56142/analista-tienda-de-conveniencia-gerencia-ventas</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -6375,7 +6375,7 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
         <v>1</v>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>En Banco BICE creemos que las personas son el motor de nuestro crecimiento. Impulsamos el desarrollo profesional en un entorno colaborativo, desafiante y con sello humano, donde el aprendizaje continuo y la excelencia son parte de nuestro día a día.¿Te apasiona el análisis financiero y te interesa desarrollar una carrera en riesgo de crédito?Estamos buscando un/a Analista de Riesgo de Crédito Empresas para sumarse a nuestra Gerencia de Riesgo Banca Empresas y Corporaciones.🔍 ¿Qué harás en este rol?✅ Analizar información financiera de empresas para la elaboración de informes de riesgo.✅ Evaluar antecedentes financieros de clientes y apoyar procesos de renovación y otorgamiento de créditos.✅ Participar en reuniones y visitas a clientes para recopilar información relevante para el análisis.✅ Preparar presentaciones y propuestas para comités de crédito.✅ Desempeñarte como contraparte de riesgo para las distintas gerencias comerciales del Banco.✅ Apoyar iniciativas y proyectos del área, contribuyendo a la mejora continua de los procesos.🎓 ¿Qué necesitas para postular?Título profesional de Ingeniería Comercial con magister en finanzas o carrera afín.Entre 0 y 1 año de experiencia laboral. (EXCLUYENTE ESTAR TITULADO)Deseable que hayas realizado tu práctia en áreas de análisis de riesgo o similaresCapacidad analítica, proactividad y orientación al aprendizaje.Si buscas iniciar tu carrera en el mundo financiero y desarrollarte en una de las áreas estratégicas del Banco, este desafío es para ti.¡Te invitamos a postular y ser parte de Banco BICE!Beneficios🏢Modalidad de trabajo según rol: Algunas posiciones acceden a un sistema híbrido, mientras que las áreas comerciales operan 100% de forma presencial.🍽️Almuerzo diario cubierto: Si trabajas en casa matriz, accedes al casino corporativo con almuerzo gratuito. Si estás en una sucursal, se te asigna un monto diario para cubrir este gasto.🛍️Descuentos exclusivos y convenios: Acceso a beneficios con diversas empresas asociadas en áreas como salud, retail, entretenimiento y más.⚽Actividades internas: Participación en torneos deportivos, actividades lúdicas, operativos oftalmológicos y otras instancias que promueven el bienestar.🤝Cultura cercana y participativa: Ser parte activa de un entorno laboral colaborativo, donde se vive la cultura organizacional día a día.🩺Seguros complementarios: Cobertura en salud, dental y de vida, para que cuentes con mayor respaldo y tranquilidad.🐾Seguro para mascotas: Protección adicional para tus compañeros de cuatro patas.🏋️Convenio con gimnasios: Accede a tarifas preferenciales para mantenerte activo y saludable.🎓Formación continua: Convenios y descuentos con instituciones educativas para diplomados, cursos y otros programas de desarrollo profesional.🚲Acceso a bicicletero: Estacionamiento seguro para bicicletas en casa matriz.🅿️Convenio de estacionamientos: Tarifas preferenciales en estacionamientos cercanos.📱Convenio con Entel: Descuentos en planes y equipos móviles.🦷Red de centros odontológicos: Acceso a múltiples convenios para atención dental.🎁Bonos diversos: Incluye bonos por escolaridad, fallecimiento, vacaciones, invierno, excelencia académica, aguinaldos de Fiestas Patrias y Navidad, entre otros.</t>
+          <t>En Arcor nos encontramos en búsqueda de un Analista Tienda de Conveniencia para trabajar en nuestras oficinas Comerciales en Las Condes:¿Te apasiona el análisis comercial, el trabajo con clientes y la gestión de indicadores que impulsan el negocio?En esta posición tendrás un rol clave en la operación y desarrollo del Canal Tiendas de Conveniencia, asegurando que el proceso de venta se ejecute de manera eficiente, desde la recepción de las órdenes de compra hasta la entrega final al cliente. Además, serás un socio estratégico para el equipo comercial mediante el análisis de información crítica para la toma de decisiones.¿Qué desafíos te esperan?:Gestionar y monitorear órdenes de compra de clientes.Coordinar y validar procesos de abastecimiento, stock y despachos.Analizar indicadores clave del canal como ventas, sell in, sell out y nivel de servicio.Generar reportes e información estratégica para clientes y equipo comercial.Apoyar al equipo de KAMs, contribuyendo al crecimiento y excelencia del canal.Tendrás la oportunidad de impactar directamente en los resultados de uno de los canales más relevantes del negocio, trabajando con equipos comerciales y desarrollando una visión integral de ventas, servicio y operación.¡Te invitamos a dar el siguiente paso en tu carrera y ser parte de este desafío!🚀Perfil deseadoRequisitos:Carreras de Ing. Comercial o a fin.Disfruten trabajar con datos y transformarlos en información valiosa para el negocio.Capacidad de analísis, organización y orientación a resultados.Posean habilidades para relacionarse con distintas áreas y clientes.Tengan motivación por aprender y desarrollarse en un entorno dinámico y desafiante.</t>
         </is>
       </c>
     </row>
@@ -6406,35 +6406,35 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Analista Tienda de Conveniencia Gerencia Ventas</t>
+          <t>Analista de Control y Gestión (Cobranzas)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Arcor</t>
+          <t>HDI Seguros</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Las Condes, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56142/analista-tienda-de-conveniencia-gerencia-ventas</t>
+          <t>https://firstjob.me/oferta/56157/analista-de-control-y-gestion-cobranzas</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>analisis</t>
+          <t>power bi</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -6444,10 +6444,10 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>En Arcor nos encontramos en búsqueda de un Analista Tienda de Conveniencia para trabajar en nuestras oficinas Comerciales en Las Condes:¿Te apasiona el análisis comercial, el trabajo con clientes y la gestión de indicadores que impulsan el negocio?En esta posición tendrás un rol clave en la operación y desarrollo del Canal Tiendas de Conveniencia, asegurando que el proceso de venta se ejecute de manera eficiente, desde la recepción de las órdenes de compra hasta la entrega final al cliente. Además, serás un socio estratégico para el equipo comercial mediante el análisis de información crítica para la toma de decisiones.¿Qué desafíos te esperan?:Gestionar y monitorear órdenes de compra de clientes.Coordinar y validar procesos de abastecimiento, stock y despachos.Analizar indicadores clave del canal como ventas, sell in, sell out y nivel de servicio.Generar reportes e información estratégica para clientes y equipo comercial.Apoyar al equipo de KAMs, contribuyendo al crecimiento y excelencia del canal.Tendrás la oportunidad de impactar directamente en los resultados de uno de los canales más relevantes del negocio, trabajando con equipos comerciales y desarrollando una visión integral de ventas, servicio y operación.¡Te invitamos a dar el siguiente paso en tu carrera y ser parte de este desafío!🚀Perfil deseadoRequisitos:Carreras de Ing. Comercial o a fin.Disfruten trabajar con datos y transformarlos en información valiosa para el negocio.Capacidad de analísis, organización y orientación a resultados.Posean habilidades para relacionarse con distintas áreas y clientes.Tengan motivación por aprender y desarrollarse en un entorno dinámico y desafiante.</t>
+          <t>Estamos buscando un(a)Analista de Control y Gestión (Cobranzas)para integrarse a nuestro equipo. Su principal desafío será analizar indicadores, generar reportería y aportar información clave para la toma de decisiones y el seguimiento de la gestión de cobranzas.¿Qué harás?Elaborar reportes e indicadores de gestión del área de cobranzas.Analizar resultados y desempeño de los principales KPI del negocio.Apoyar la preparación de informes de gestión y cierres mensuales.Realizar seguimiento de indicadores de experiencia de clientes (NPS).Monitorear el cumplimiento de SLA y generar alertas ante desviaciones.Participar en iniciativas de mejora continua y optimización de procesos.Apoyar el control interno y la gestión documental del área.Perfil deseadoRecién titulado/a Ingeniería Comercial o Ingeniería Civil Industrial.Conocimientos enExcel nivel intermedio.Power BI.Manejo de indicadores de gestión.</t>
         </is>
       </c>
     </row>
@@ -6475,7 +6475,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Analista de Control y Gestión (Cobranzas)</t>
+          <t>Analista de Datos y Gestión Operacional (recién tituladoa)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6495,15 +6495,15 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56157/analista-de-control-y-gestion-cobranzas</t>
+          <t>https://firstjob.me/oferta/56158/analista-de-datos-y-gestion-operacional-recien-titulado-a</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>power bi</t>
+          <t>analisis, excel, power bi</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -6532,39 +6532,39 @@
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>Estamos buscando un(a)Analista de Control y Gestión (Cobranzas)para integrarse a nuestro equipo. Su principal desafío será analizar indicadores, generar reportería y aportar información clave para la toma de decisiones y el seguimiento de la gestión de cobranzas.¿Qué harás?Elaborar reportes e indicadores de gestión del área de cobranzas.Analizar resultados y desempeño de los principales KPI del negocio.Apoyar la preparación de informes de gestión y cierres mensuales.Realizar seguimiento de indicadores de experiencia de clientes (NPS).Monitorear el cumplimiento de SLA y generar alertas ante desviaciones.Participar en iniciativas de mejora continua y optimización de procesos.Apoyar el control interno y la gestión documental del área.Perfil deseadoRecién titulado/a Ingeniería Comercial o Ingeniería Civil Industrial.Conocimientos enExcel nivel intermedio.Power BI.Manejo de indicadores de gestión.</t>
+          <t>🚀¿Eres Ingeniero/a Comercial o Ingeniero/a Civil Industrial recién titulado/a y buscas comenzar tu carrera en una empresa líder del mercado asegurador?En HDI Seguros estamos buscando un(a)Analista de Datos y Gestión Operacionalpara integrarse a un equipo dinámico, donde podrás desarrollar tus habilidades analíticas, fortalecer tu manejo de datos y participar activamente en la toma de decisiones del negocio.¿Qué harás en tu día a día?Analizar y controlar información asociada a recuperos judiciales.Monitorear convenios de pago y oportunidades de recupero.Elaborar reportes de gestión e indicadores para apoyar la toma de decisiones.Realizar seguimiento y control de estudios jurídicos externos.Analizar información de siniestros con potencial de recupero.Identificar desviaciones y proponer mejoras en procesos y controles.Perfil deseadoFormación en Ingeniería Comercial o Ingeniería Civil Industrial.Conocimientos:Excel nivel intermedio.Conocimiento en Power BI.BeneficiosSeguro complementario de salud.Aguinaldos.Bono anual.Modalidad híbrida.Jornada laboral de 40 horas semanales.Creemos en la diversidad y fomentamos la igualdad de oportunidades. Esta oferta se enmarca en la Ley 21.015 que promueve la inclusión laboral de personas con discapacidad.Si buscas un nuevo desafío profesional donde puedas potenciar tus habilidades de análisis y gestión, ¡te invitamos a postular!</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Analista de Datos y Gestión Operacional (recién tituladoa)</t>
+          <t>Analista de Inteligencia de Negocio</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HDI Seguros</t>
+          <t>Entel Perú</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Lima, Perú</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56158/analista-de-datos-y-gestion-operacional-recien-titulado-a</t>
+          <t>https://firstjob.me/oferta/56171/analista-de-inteligencia-de-negocio</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>analisis, excel, power bi</t>
+          <t>sql, power bi</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -6582,26 +6582,26 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>🚀¿Eres Ingeniero/a Comercial o Ingeniero/a Civil Industrial recién titulado/a y buscas comenzar tu carrera en una empresa líder del mercado asegurador?En HDI Seguros estamos buscando un(a)Analista de Datos y Gestión Operacionalpara integrarse a un equipo dinámico, donde podrás desarrollar tus habilidades analíticas, fortalecer tu manejo de datos y participar activamente en la toma de decisiones del negocio.¿Qué harás en tu día a día?Analizar y controlar información asociada a recuperos judiciales.Monitorear convenios de pago y oportunidades de recupero.Elaborar reportes de gestión e indicadores para apoyar la toma de decisiones.Realizar seguimiento y control de estudios jurídicos externos.Analizar información de siniestros con potencial de recupero.Identificar desviaciones y proponer mejoras en procesos y controles.Perfil deseadoFormación en Ingeniería Comercial o Ingeniería Civil Industrial.Conocimientos:Excel nivel intermedio.Conocimiento en Power BI.BeneficiosSeguro complementario de salud.Aguinaldos.Bono anual.Modalidad híbrida.Jornada laboral de 40 horas semanales.Creemos en la diversidad y fomentamos la igualdad de oportunidades. Esta oferta se enmarca en la Ley 21.015 que promueve la inclusión laboral de personas con discapacidad.Si buscas un nuevo desafío profesional donde puedas potenciar tus habilidades de análisis y gestión, ¡te invitamos a postular!</t>
+          <t>¿Te mueve colaborar, desafiar y crecer con propósito? Conoce que desafíos te esperan como Analista de Inteligencia de NegocioAnalizar el desempeño e impacto de iniciativas a demanda de los canales de retención.Diseñar y mantener dashboards de gestión operativa.Construir procesos, tablas y automatizaciones mediante SQL.Elaborar reportes de resultados y generar insights para entender el performance de las campañas de retención.Identificar buenas prácticas y proponer mejoras replicables.Controlar y dar seguimiento a indicadores propios de la gestión de call center.RequisitosFormación universitaria completa en carreras de Administración, Ing, Industrial o afines.Experiencia de 1 año en gestión comercial, contact center o canales de atención.Manejo de Office a nivel avanzadoManejo de Power BI a nivel intermedioManejo de SQL a nivel intermedio</t>
         </is>
       </c>
     </row>
@@ -6613,27 +6613,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Analista de Inteligencia de Negocio</t>
+          <t>INGENIERO DE SOPORTE Y PROYECTOS IoT</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Entel Perú</t>
+          <t>Clickie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Lima, Perú</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56171/analista-de-inteligencia-de-negocio</t>
+          <t>https://firstjob.me/oferta/56189/ingeniero-de-soporte-y-proyectos-iot</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -6641,17 +6641,17 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>sql, power bi</t>
+          <t>python, excel</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
@@ -6660,7 +6660,7 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>¿Te mueve colaborar, desafiar y crecer con propósito? Conoce que desafíos te esperan como Analista de Inteligencia de NegocioAnalizar el desempeño e impacto de iniciativas a demanda de los canales de retención.Diseñar y mantener dashboards de gestión operativa.Construir procesos, tablas y automatizaciones mediante SQL.Elaborar reportes de resultados y generar insights para entender el performance de las campañas de retención.Identificar buenas prácticas y proponer mejoras replicables.Controlar y dar seguimiento a indicadores propios de la gestión de call center.RequisitosFormación universitaria completa en carreras de Administración, Ing, Industrial o afines.Experiencia de 1 año en gestión comercial, contact center o canales de atención.Manejo de Office a nivel avanzadoManejo de Power BI a nivel intermedioManejo de SQL a nivel intermedio</t>
+          <t>INGENIERO DE SOPORTE Y PROYECTOS IoTClickie | Santiago de Chile | Modalidad mixta oficina/terreno | Jornada 40 horas—SOBRE CLICKIEEn Clickie desarrollamos soluciones de eficiencia energética y telemetría IoT/IIoT para clientes de retail, edificios corporativos e instalaciones industriales y comerciales. Operamos en diferentes países de la región, con plataforma propia de telemetría y una arquitectura agnóstica a la tecnología mediante la integración de dispositivos de diversos tipos.—EL DESAFÍOBuscamos a alguien que conecte el mundo del terreno con el del cliente. En este cargo vas a levantar proyectos nuevos, resolver incidencias técnicas en sitio, participación en labores de montaje de equipos de telemetría y transformar lo que observaste en terreno en una propuesta concreta. Es un rol de ciclo completo: partes en la visita y terminas con la solución operando.—QUÉ VAS A HACERAtender y resolver solicitudes de clientes a través de nuestro sistema de tickets, dando seguimiento hasta el cierre efectivo de cada caso.Realizar visitas técnicas de soporte para diagnóstico y resolución de incidencias en sitio.Ejecutar visitas de levantamiento técnico para nuevos proyectos.Montar, configurar y poner en marcha equipos de telemetría, medición y control en instalaciones de clientes.Elaborar propuestas técnicas y económicas a partir de los levantamientos realizados.Registrar y gestionar información de proyectos e inventario en nuestro ERP.Coordinar de forma directa con las áreas comercial, producto, administración y logística para la ejecución de los proyectos.—REQUISITOS EXCLUYENTESTítulo de Técnico Eléctrico, Ingeniero Eléctrico, Ingeniero Electrónico o Ingeniero en Automatización Industrial.Licencia eléctrica SEC vigente (cualquier clase).Licencia de conducir clase B vigente.Inglés técnico de lectura, suficiente para interpretar datasheets y manuales de equipos.Disponibilidad para viajar dentro de la Región Metropolitana y a regiones de Chile.Disponibilidad para turnos de emergencia asociados a soporte, y para trabajo fuera de horario cuando un proyecto lo requiera.—REQUISITOS DESEABLES3 años de experiencia en roles similares. También evaluamos perfiles junior o recién titulados con ganas reales de aprender.Experiencia en trabajos eléctricos de baja tensión y en montaje de tableros eléctricos.Experiencia en automatización industrial.Conocimiento de protocolos de comunicación industrial: Modbus RTU y Modbus TCP/IP.Conocimiento de LoRaWAN o de otras tecnologías de comunicación inalámbrica para IoT.Conocimientos de redes y direccionamiento IP.Manejo de Excel y Google Workspace.Nociones de Python o disposición a aprender.Examen de altura vigente. Si no lo tienes, la empresa puede gestionarlo.—QUÉ BUSCAMOS EN TIProactividad: que detectes el problema antes de que el cliente lo reporte.Ganas de aprender. Trabajamos con tecnología que cambia rápido y valoramos más la curiosidad que el currículum perfecto.Trabajo en equipo y capacidad de moverte entre tareas distintas dentro de una misma semana.Autonomía en terreno y criterio para resolver con lo que hay.Orden y disciplina en el registro de la información.—CONDICIONESUbicación: Santiago de Chile.Modalidad: Presencial mixta oficina/terrenoJornada: 40 horas semanales.Contrato: plazo fijo con proyección a indefinido.Reporta a: Responsable de Operaciones, dentro de un equipo de 6 personas.—CÓMO POSTULAREnvía tu CV a[email protected]con el asunto "Ingeniero de Soporte y Proyectos IoT".</t>
         </is>
       </c>
     </row>
@@ -6682,45 +6682,41 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>INGENIERO DE SOPORTE Y PROYECTOS IoT</t>
+          <t>Asistente de Adquisición de Talento y ME - Surco</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Clickie</t>
+          <t>Ferreyros</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Surco, Perú</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56189/ingeniero-de-soporte-y-proyectos-iot</t>
+          <t>https://firstjob.me/oferta/56173/asistente-de-adquisicion-de-talento-y-me-surco</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>5</v>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>python, excel</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
         <v>1</v>
@@ -6735,11 +6731,11 @@
         <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>INGENIERO DE SOPORTE Y PROYECTOS IoTClickie | Santiago de Chile | Modalidad mixta oficina/terreno | Jornada 40 horas—SOBRE CLICKIEEn Clickie desarrollamos soluciones de eficiencia energética y telemetría IoT/IIoT para clientes de retail, edificios corporativos e instalaciones industriales y comerciales. Operamos en diferentes países de la región, con plataforma propia de telemetría y una arquitectura agnóstica a la tecnología mediante la integración de dispositivos de diversos tipos.—EL DESAFÍOBuscamos a alguien que conecte el mundo del terreno con el del cliente. En este cargo vas a levantar proyectos nuevos, resolver incidencias técnicas en sitio, participación en labores de montaje de equipos de telemetría y transformar lo que observaste en terreno en una propuesta concreta. Es un rol de ciclo completo: partes en la visita y terminas con la solución operando.—QUÉ VAS A HACERAtender y resolver solicitudes de clientes a través de nuestro sistema de tickets, dando seguimiento hasta el cierre efectivo de cada caso.Realizar visitas técnicas de soporte para diagnóstico y resolución de incidencias en sitio.Ejecutar visitas de levantamiento técnico para nuevos proyectos.Montar, configurar y poner en marcha equipos de telemetría, medición y control en instalaciones de clientes.Elaborar propuestas técnicas y económicas a partir de los levantamientos realizados.Registrar y gestionar información de proyectos e inventario en nuestro ERP.Coordinar de forma directa con las áreas comercial, producto, administración y logística para la ejecución de los proyectos.—REQUISITOS EXCLUYENTESTítulo de Técnico Eléctrico, Ingeniero Eléctrico, Ingeniero Electrónico o Ingeniero en Automatización Industrial.Licencia eléctrica SEC vigente (cualquier clase).Licencia de conducir clase B vigente.Inglés técnico de lectura, suficiente para interpretar datasheets y manuales de equipos.Disponibilidad para viajar dentro de la Región Metropolitana y a regiones de Chile.Disponibilidad para turnos de emergencia asociados a soporte, y para trabajo fuera de horario cuando un proyecto lo requiera.—REQUISITOS DESEABLES3 años de experiencia en roles similares. También evaluamos perfiles junior o recién titulados con ganas reales de aprender.Experiencia en trabajos eléctricos de baja tensión y en montaje de tableros eléctricos.Experiencia en automatización industrial.Conocimiento de protocolos de comunicación industrial: Modbus RTU y Modbus TCP/IP.Conocimiento de LoRaWAN o de otras tecnologías de comunicación inalámbrica para IoT.Conocimientos de redes y direccionamiento IP.Manejo de Excel y Google Workspace.Nociones de Python o disposición a aprender.Examen de altura vigente. Si no lo tienes, la empresa puede gestionarlo.—QUÉ BUSCAMOS EN TIProactividad: que detectes el problema antes de que el cliente lo reporte.Ganas de aprender. Trabajamos con tecnología que cambia rápido y valoramos más la curiosidad que el currículum perfecto.Trabajo en equipo y capacidad de moverte entre tareas distintas dentro de una misma semana.Autonomía en terreno y criterio para resolver con lo que hay.Orden y disciplina en el registro de la información.—CONDICIONESUbicación: Santiago de Chile.Modalidad: Presencial mixta oficina/terrenoJornada: 40 horas semanales.Contrato: plazo fijo con proyección a indefinido.Reporta a: Responsable de Operaciones, dentro de un equipo de 6 personas.—CÓMO POSTULAREnvía tu CV a[email protected]con el asunto "Ingeniero de Soporte y Proyectos IoT".</t>
+          <t>Misión del PuestoBrindar soporte operativo integral y ejecutar los procesos de selección alineados a las necesidades de la organización, garantizando la cobertura oportuna de vacantes y fortaleciendo la posición de nuestra Marca Empleadora en cada punto de contacto con el talento.FuncionesEjecutar el reclutamiento y selección de posiciones operativas, mandos medios y convocatorias masivas según el volumen requerido.Proponer, coordinar y ejecutar nuevas fuentes de reclutamiento (activaciones en campo, ferias laborales, redes locales y estrategias digitales) para enriquecer nuestra base de candidatos.Gestionar la programación y seguimiento de evaluaciones psicológicas, procesos tercerizados y exámenes médicos ocupacionales.Mantener actualizadas las matrices de control del área y apoyar en el monitoreo de los principales KPIs del proceso (tiempos de cobertura, rotación inicial, entre otros).Identificar proactivamente eficiencias en el flujo de selección masiva para reducir tiempos de atención asegurando el fit cultural.Brindar soporte presencial en viajes para la evaluación de programas especiales, procesos masivos descentralizados y ferias de empleo.Requisitos:Egresado/a de Psicología (indispensable).1 año de experiencia en procesos de selección end-to-end en sectores industriales, consumo masivo o empresas de consultoría/outsourcing.Manejo de Google Workspace o Microsoft Office a nivel usuario/intermedio.Disponibilidad para laborar de forma resencial en Monterrico, Surco (Lunes a Viernes).Disponibilidad para realizar viajes puntuales a nivel nacional según necesidad de los procesos masivos o ferias.</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6747,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Asistente de Adquisición de Talento y ME - Surco</t>
+          <t>Trainee De SSMA - Op Las Bambas</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6761,7 +6757,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Surco, Perú</t>
+          <t>APURIMAC, Perú</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6771,13 +6767,17 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56173/asistente-de-adquisicion-de-talento-y-me-surco</t>
+          <t>https://firstjob.me/oferta/56174/trainee-de-ssma-op-las-bambas</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>trainee</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -6794,17 +6794,17 @@
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P94" t="n">
         <v>0</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>Misión del PuestoBrindar soporte operativo integral y ejecutar los procesos de selección alineados a las necesidades de la organización, garantizando la cobertura oportuna de vacantes y fortaleciendo la posición de nuestra Marca Empleadora en cada punto de contacto con el talento.FuncionesEjecutar el reclutamiento y selección de posiciones operativas, mandos medios y convocatorias masivas según el volumen requerido.Proponer, coordinar y ejecutar nuevas fuentes de reclutamiento (activaciones en campo, ferias laborales, redes locales y estrategias digitales) para enriquecer nuestra base de candidatos.Gestionar la programación y seguimiento de evaluaciones psicológicas, procesos tercerizados y exámenes médicos ocupacionales.Mantener actualizadas las matrices de control del área y apoyar en el monitoreo de los principales KPIs del proceso (tiempos de cobertura, rotación inicial, entre otros).Identificar proactivamente eficiencias en el flujo de selección masiva para reducir tiempos de atención asegurando el fit cultural.Brindar soporte presencial en viajes para la evaluación de programas especiales, procesos masivos descentralizados y ferias de empleo.Requisitos:Egresado/a de Psicología (indispensable).1 año de experiencia en procesos de selección end-to-end en sectores industriales, consumo masivo o empresas de consultoría/outsourcing.Manejo de Google Workspace o Microsoft Office a nivel usuario/intermedio.Disponibilidad para laborar de forma resencial en Monterrico, Surco (Lunes a Viernes).Disponibilidad para realizar viajes puntuales a nivel nacional según necesidad de los procesos masivos o ferias.</t>
+          <t>Misión del puestoBrindar soporte estratégico en el seguimiento y reportabilidad del Plan Anual de SSMA (PASSMA) para nuestra Gerencia de División.FuncionesHacer seguimiento continuo y consolidar reportes periódicos sobre los avances del PASSMA y sus planes de acción.Verificar en campo el cumplimiento de normas, estándares e instructivos de SSMA, tanto para personal propio como contratistas.Impartir capacitaciones y sensibilizar a los equipos en la adopción de comportamientos seguros y buenas prácticas.Asegurar el cumplimiento de requisitos legales y estándares corporativos para la mejora continua del área.RequisitosEgresado/a o Bachiller en Ingeniería Industrial, Minas, Mecánica, Ambiental, Higiene y Seguridad Industrial o afines.1 año de experiencia general en el rubro y 1 año de experiencia certificada en posiciones similares (¡se consideran prácticas pre y profesionales!).Residencia en provincias de la región sur (Arequipa, Cusco, Moquegua u otras zonas cercanas).Para laborar bajo régimen atípico en la operación asignada.</t>
         </is>
       </c>
     </row>
@@ -6816,17 +6816,17 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Trainee De SSMA - Op Las Bambas</t>
+          <t>Asistente de Ventas Part Time</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ferreyros</t>
+          <t>Tanner</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>APURIMAC, Perú</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6836,17 +6836,13 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56174/trainee-de-ssma-op-las-bambas</t>
+          <t>https://firstjob.me/oferta/56193/asistente-de-ventas-part-time</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>7</v>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>trainee</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -6860,20 +6856,20 @@
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P95" t="n">
         <v>0</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>Misión del puestoBrindar soporte estratégico en el seguimiento y reportabilidad del Plan Anual de SSMA (PASSMA) para nuestra Gerencia de División.FuncionesHacer seguimiento continuo y consolidar reportes periódicos sobre los avances del PASSMA y sus planes de acción.Verificar en campo el cumplimiento de normas, estándares e instructivos de SSMA, tanto para personal propio como contratistas.Impartir capacitaciones y sensibilizar a los equipos en la adopción de comportamientos seguros y buenas prácticas.Asegurar el cumplimiento de requisitos legales y estándares corporativos para la mejora continua del área.RequisitosEgresado/a o Bachiller en Ingeniería Industrial, Minas, Mecánica, Ambiental, Higiene y Seguridad Industrial o afines.1 año de experiencia general en el rubro y 1 año de experiencia certificada en posiciones similares (¡se consideran prácticas pre y profesionales!).Residencia en provincias de la región sur (Arequipa, Cusco, Moquegua u otras zonas cercanas).Para laborar bajo régimen atípico en la operación asignada.</t>
+          <t>En Tanner seguimos creciendo y queremos que tú también seas parte de este equipo.Buscamos a nuestro próximo/aAsistente de Ventas Part Time, quien tendrá la misión de brindar un servicio de excelencia a nuestros clientes en el punto de venta, asesorándolos en productos financieros y seguros automotrices.¿Qué harás?Asesorar y apoyar en la venta de productos financieros y seguros automotrices. Entregar una experiencia de atención cercana y de calidad, ayudando a cada cliente a encontrar la mejor alternativa según sus necesidades.Validar documentación y respaldos asociados a los cierres de financiamiento.Representar a Tanner con una actitud proactiva, empática y orientada al servicio.En Tanner valoramos el compromiso, la cercanía y el trabajo colaborativo, ofreciendo un espacio donde podrás desarrollarte y generar impacto en la experiencia de nuestros clientes.¿Qué buscamos?Deseable contar con estudios técnicos o profesionales en áreas comerciales, administración o afines.Al menos 1 año de experiencia en atención al cliente o ventas (idealmente en retail o servicios financieros).Habilidades comunicacionales y orientación al cliente.Disponibilidad para trabajar en modalidad presencial, 3 días en la semana, incluyendo sábado y domingo de forma fija.¡Te invitamos a postular y ser parte de Tanner!</t>
         </is>
       </c>
     </row>
@@ -6885,17 +6881,17 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Asistente de Ventas Part Time</t>
+          <t>Ingenieroa de Productos Vida - Gerencia Comercial Corporativa</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Tanner</t>
+          <t>Consorcio</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Las Condes, Chile</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6905,13 +6901,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56193/asistente-de-ventas-part-time</t>
+          <t>https://firstjob.me/oferta/56187/ingeniero-a-de-productos-vida-gerencia-comercial-corporativa</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>python, sql, excel, power bi</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>En Tanner seguimos creciendo y queremos que tú también seas parte de este equipo.Buscamos a nuestro próximo/aAsistente de Ventas Part Time, quien tendrá la misión de brindar un servicio de excelencia a nuestros clientes en el punto de venta, asesorándolos en productos financieros y seguros automotrices.¿Qué harás?Asesorar y apoyar en la venta de productos financieros y seguros automotrices. Entregar una experiencia de atención cercana y de calidad, ayudando a cada cliente a encontrar la mejor alternativa según sus necesidades.Validar documentación y respaldos asociados a los cierres de financiamiento.Representar a Tanner con una actitud proactiva, empática y orientada al servicio.En Tanner valoramos el compromiso, la cercanía y el trabajo colaborativo, ofreciendo un espacio donde podrás desarrollarte y generar impacto en la experiencia de nuestros clientes.¿Qué buscamos?Deseable contar con estudios técnicos o profesionales en áreas comerciales, administración o afines.Al menos 1 año de experiencia en atención al cliente o ventas (idealmente en retail o servicios financieros).Habilidades comunicacionales y orientación al cliente.Disponibilidad para trabajar en modalidad presencial, 3 días en la semana, incluyendo sábado y domingo de forma fija.¡Te invitamos a postular y ser parte de Tanner!</t>
+          <t>En Consorcio creemos en lugares de trabajo inclusivos, donde las diferencias de las personas son respetadas, valoradas y atendidas para que todos nuestros colaboradores puedan desarrollar plenamente sus talentos.Si buscas un lugar de trabajo desafiante y quieres desarrollarte profesionalmente, esta es tu oportunidad. En Consorcio, nos encontramos en la búsqueda de un Ingeniero/a de Productos Vida para la Gerencia Comercial Corporativa, quien será responsable de liderar, planificar y controlar las actividades asociados a la implementación de nuevos seguros de vida y Fondos mutuos y mejoras de los actuales, dada la estrategia de desarrollo de productos de la Compañía, que se adecuen a las necesidades y expectativas de los clientes y canales, sujetos al cumplimiento de la factibilidad técnica, normativa y operacional.💡 ¿Cuáles serán tus principales funciones?Liderar la implementación de los nuevos Seguros de Vida individuales o Fondos mutuos y sus mejoras, asegurando la elaboración de productos que se adecuen a las necesidades y expectativas de los clientes y canales.Analizar los riesgos de cada iniciativa en las distintas áreas de la compañía, asegurando el cumplimiento de la factibilidad técnica, legal y operacional.Diseñar los requerimientos, documentación y contenidos relacionados con los productos, velando por el cumplimiento de la implementación de los productos y sus flujos.Proponer soluciones eficientes basadas en el conocimiento de las potencialidades de los sistemas y procesos, asegurando la correcta implementación de los productos, sus procesos y desarrollos asociados.Mantener estrecha relación con los distintos canales de distribución, colaborando entre áreas para la adecuada implementación de nuevos productos.🔎 ¿Qué buscamos?Profesional de las carreras Ingeniería Civil o Ingeniería Comercial.Poseer al menos 1 año de experiencia profesional en cargos similares.Conocimiento en Diseño, Planificación y Administración de Proyectos.Manejo de Excel avanzado.Dominio de Power BI, SQL y Python.Deseable conocimiento y uso de IA.Esta oferta se rige bajo la Ley N°21.015, que incentiva la inclusión de personas con discapacidad en el mundo laboral.</t>
         </is>
       </c>
     </row>
@@ -6950,17 +6950,17 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ingenieroa de Productos Vida - Gerencia Comercial Corporativa</t>
+          <t>Key Account Specialist (KAS) – Trade Marketing, Logística y COMEX</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Consorcio</t>
+          <t>Casa Nativa</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Las Condes, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6970,19 +6970,19 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56187/ingeniero-a-de-productos-vida-gerencia-comercial-corporativa</t>
+          <t>https://firstjob.me/oferta/56181/key-account-specialist-kas-trade-marketing-logistica-y-comex</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>python, sql, excel, power bi</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -6997,7 +6997,7 @@
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>En Consorcio creemos en lugares de trabajo inclusivos, donde las diferencias de las personas son respetadas, valoradas y atendidas para que todos nuestros colaboradores puedan desarrollar plenamente sus talentos.Si buscas un lugar de trabajo desafiante y quieres desarrollarte profesionalmente, esta es tu oportunidad. En Consorcio, nos encontramos en la búsqueda de un Ingeniero/a de Productos Vida para la Gerencia Comercial Corporativa, quien será responsable de liderar, planificar y controlar las actividades asociados a la implementación de nuevos seguros de vida y Fondos mutuos y mejoras de los actuales, dada la estrategia de desarrollo de productos de la Compañía, que se adecuen a las necesidades y expectativas de los clientes y canales, sujetos al cumplimiento de la factibilidad técnica, normativa y operacional.💡 ¿Cuáles serán tus principales funciones?Liderar la implementación de los nuevos Seguros de Vida individuales o Fondos mutuos y sus mejoras, asegurando la elaboración de productos que se adecuen a las necesidades y expectativas de los clientes y canales.Analizar los riesgos de cada iniciativa en las distintas áreas de la compañía, asegurando el cumplimiento de la factibilidad técnica, legal y operacional.Diseñar los requerimientos, documentación y contenidos relacionados con los productos, velando por el cumplimiento de la implementación de los productos y sus flujos.Proponer soluciones eficientes basadas en el conocimiento de las potencialidades de los sistemas y procesos, asegurando la correcta implementación de los productos, sus procesos y desarrollos asociados.Mantener estrecha relación con los distintos canales de distribución, colaborando entre áreas para la adecuada implementación de nuevos productos.🔎 ¿Qué buscamos?Profesional de las carreras Ingeniería Civil o Ingeniería Comercial.Poseer al menos 1 año de experiencia profesional en cargos similares.Conocimiento en Diseño, Planificación y Administración de Proyectos.Manejo de Excel avanzado.Dominio de Power BI, SQL y Python.Deseable conocimiento y uso de IA.Esta oferta se rige bajo la Ley N°21.015, que incentiva la inclusión de personas con discapacidad en el mundo laboral.</t>
+          <t>Somos parte del mundo WildWild Lama. Wild Foods. Wild Labs. Un grupo de marcas chilenas que compartenuna idea simple: se pueden hacer productos de consumo masivo bien hechos,sustentables, y que además compitan de igual a igual con las multinacionalesen la góndola.Wild Labs es la casa de dos de esas marcas. Casa Nativa, de limpiezasustentable. Casa Delfina, de aromatización de hogar. Nuestros productosestán hoy en Jumbo y en Líder, además de marketplaces y canal propio.Llegar ahí no fue fácil. Mantenerlo y crecer es el trabajo que viene.El cargoBuscamos a la persona que se haga cargo de que todo eso funcione: que elproducto llegue, que esté en la góndola, y que se venda.Es un cargo con una particularidad poco común para alguien que está partiendo:vas a ver el negocio completo. Desde una orden de compra a un proveedor enChina hasta la exhibición de ese mismo producto en un Jumbo de Santiago. Enuna multinacional esas tres cosas las hacen tres áreas distintas y tú veríasuna. Acá las ves todas, y en dos años vas a entender de consumo masivo lo queotros entienden en cinco.Trade marketing y ejecución en salaVas a estar en terreno. Recorrer salas, revisar exhibición, precio y presencia.Detectar quiebres y resolverlos con supervisores y jefes de local. Coordinaral equipo de reposición. Ejecutar activaciones y campañas. Analizar el sell-outpor sala y por SKU, y proponer qué hacer con eso.Logística y abastecimientoGestionar las órdenes de compra de las cadenas, agendar despachos, coordinarcon la bodega. Controlar el fill rate y el cumplimiento del manual de proveedorde cada cadena. Cuadrar inventario y anticipar quiebres antes de que ocurran.COMEX e importacionesSeguimiento a las órdenes con proveedores en China e India. Coordinar embarquescon el freight forwarder y el agente de aduanas. Controlar documentación yplazos de cada despacho. Levantar el costeo por SKU.A quién buscamosTitulado o egresado de Ingeniería Comercial o Ingeniería Civil Industrial.Entre 0 y 2 años de experiencia. Práctica en retail o consumo masivo suma,pero no es requisito.Excel intermedio: tablas dinámicas, funciones de búsqueda, cruce de bases.Inglés intermedio, suficiente para escribirle a un proveedor en Asia.Licencia clase B vigente y movilización propia. Este punto es excluyente.Y dos cosas que no se enseñan:Rigurosidad con el detalle. Acá un documento de importación mal emitido o unaficha de producto mal cargada cuesta plata de verdad. El estándar es alto y nolo vamos a bajar.Gusto por el terreno. Este no es un cargo de escritorio. Si tu idea del trabajoideal es un Excel y una pantalla, no eres tú. Buscamos a alguien a quien leguste caminar salas, hablar con la gente del retail, y volver con informaciónque nadie más tiene.Lo que ofrecemosRenta líquida de $1.400.000 más bonos por cumplimiento de indicadores.Contrato plazo fijo 3 meses y luego indefinido.Oficina en Vitacura, con terreno frecuente.Un practicante a tu cargo desde el primer día.Reporte directo a la gerencia general. Vas a estar en las conversaciones dondese toman las decisiones, no leyendo el resumen después.Ruta de crecimiento definida a Key Account Manager o Product Manager, con unhorizonte de 18 a 24 meses.Si buscas un cargo cómodo y acotado, este no es. Si buscas el lugar donde vas aaprender más rápido en los próximos dos años, conversemos.BeneficiosBeneficiosSeguro complementario de salud, vida, dental y catastrófico, financiado100% por la empresa (aplica al pasar a contrato indefinido).Reajuste de sueldo por IPC dos veces al año, en junio y diciembre. Noesperas a la evaluación anual para que tu sueldo no pierda valor.Almuerzo de Desarrollo: te financiamos un almuerzo al mes con alguien detu rubro para que aprendas de su experiencia y construyas red. Cubrimosel 100% del invitado. Es un beneficio pensado para que crezcasprofesionalmente más allá de tu escritorio.40% de descuento en todas las marcas del grupo Wild —Wild Lama, WildFoods— y en Casa Nativa. 30% adicional para tus familiares y amigos.Medio día libre para tu cumpleaños.Aguinaldos de Fiestas Patrias y Navidad.Day &amp; Night Ticket: una salida mensual financiada con el equipo.15% de descuento en Beasty Butchers.Permisos que van más allá de la ley:Un mes adicional de postnatal masculino y femenino, con flexibilidad paratomarlo completo o en jornada parcial.Una semana extra de luna de miel.Cinco días hábiles adicionales por fallecimiento de familiar directo.Un mes de descanso por pérdida gestacional, para madres y padres.Día libre por fallecimiento de tu mascota.</t>
         </is>
       </c>
     </row>
@@ -7019,27 +7019,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Key Account Specialist (KAS) – Trade Marketing, Logística y COMEX</t>
+          <t>📊 Paid Media Manager</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Casa Nativa</t>
+          <t>Milimetrix</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Callao 2911, Chile</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56181/key-account-specialist-kas-trade-marketing-logistica-y-comex</t>
+          <t>https://firstjob.me/oferta/56185/paid-media-manager</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -7051,22 +7051,22 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>Somos parte del mundo WildWild Lama. Wild Foods. Wild Labs. Un grupo de marcas chilenas que compartenuna idea simple: se pueden hacer productos de consumo masivo bien hechos,sustentables, y que además compitan de igual a igual con las multinacionalesen la góndola.Wild Labs es la casa de dos de esas marcas. Casa Nativa, de limpiezasustentable. Casa Delfina, de aromatización de hogar. Nuestros productosestán hoy en Jumbo y en Líder, además de marketplaces y canal propio.Llegar ahí no fue fácil. Mantenerlo y crecer es el trabajo que viene.El cargoBuscamos a la persona que se haga cargo de que todo eso funcione: que elproducto llegue, que esté en la góndola, y que se venda.Es un cargo con una particularidad poco común para alguien que está partiendo:vas a ver el negocio completo. Desde una orden de compra a un proveedor enChina hasta la exhibición de ese mismo producto en un Jumbo de Santiago. Enuna multinacional esas tres cosas las hacen tres áreas distintas y tú veríasuna. Acá las ves todas, y en dos años vas a entender de consumo masivo lo queotros entienden en cinco.Trade marketing y ejecución en salaVas a estar en terreno. Recorrer salas, revisar exhibición, precio y presencia.Detectar quiebres y resolverlos con supervisores y jefes de local. Coordinaral equipo de reposición. Ejecutar activaciones y campañas. Analizar el sell-outpor sala y por SKU, y proponer qué hacer con eso.Logística y abastecimientoGestionar las órdenes de compra de las cadenas, agendar despachos, coordinarcon la bodega. Controlar el fill rate y el cumplimiento del manual de proveedorde cada cadena. Cuadrar inventario y anticipar quiebres antes de que ocurran.COMEX e importacionesSeguimiento a las órdenes con proveedores en China e India. Coordinar embarquescon el freight forwarder y el agente de aduanas. Controlar documentación yplazos de cada despacho. Levantar el costeo por SKU.A quién buscamosTitulado o egresado de Ingeniería Comercial o Ingeniería Civil Industrial.Entre 0 y 2 años de experiencia. Práctica en retail o consumo masivo suma,pero no es requisito.Excel intermedio: tablas dinámicas, funciones de búsqueda, cruce de bases.Inglés intermedio, suficiente para escribirle a un proveedor en Asia.Licencia clase B vigente y movilización propia. Este punto es excluyente.Y dos cosas que no se enseñan:Rigurosidad con el detalle. Acá un documento de importación mal emitido o unaficha de producto mal cargada cuesta plata de verdad. El estándar es alto y nolo vamos a bajar.Gusto por el terreno. Este no es un cargo de escritorio. Si tu idea del trabajoideal es un Excel y una pantalla, no eres tú. Buscamos a alguien a quien leguste caminar salas, hablar con la gente del retail, y volver con informaciónque nadie más tiene.Lo que ofrecemosRenta líquida de $1.400.000 más bonos por cumplimiento de indicadores.Contrato plazo fijo 3 meses y luego indefinido.Oficina en Vitacura, con terreno frecuente.Un practicante a tu cargo desde el primer día.Reporte directo a la gerencia general. Vas a estar en las conversaciones dondese toman las decisiones, no leyendo el resumen después.Ruta de crecimiento definida a Key Account Manager o Product Manager, con unhorizonte de 18 a 24 meses.Si buscas un cargo cómodo y acotado, este no es. Si buscas el lugar donde vas aaprender más rápido en los próximos dos años, conversemos.BeneficiosBeneficiosSeguro complementario de salud, vida, dental y catastrófico, financiado100% por la empresa (aplica al pasar a contrato indefinido).Reajuste de sueldo por IPC dos veces al año, en junio y diciembre. Noesperas a la evaluación anual para que tu sueldo no pierda valor.Almuerzo de Desarrollo: te financiamos un almuerzo al mes con alguien detu rubro para que aprendas de su experiencia y construyas red. Cubrimosel 100% del invitado. Es un beneficio pensado para que crezcasprofesionalmente más allá de tu escritorio.40% de descuento en todas las marcas del grupo Wild —Wild Lama, WildFoods— y en Casa Nativa. 30% adicional para tus familiares y amigos.Medio día libre para tu cumpleaños.Aguinaldos de Fiestas Patrias y Navidad.Day &amp; Night Ticket: una salida mensual financiada con el equipo.15% de descuento en Beasty Butchers.Permisos que van más allá de la ley:Un mes adicional de postnatal masculino y femenino, con flexibilidad paratomarlo completo o en jornada parcial.Una semana extra de luna de miel.Cinco días hábiles adicionales por fallecimiento de familiar directo.Un mes de descanso por pérdida gestacional, para madres y padres.Día libre por fallecimiento de tu mascota.</t>
+          <t>¿Te motiva convertir datos en decisiones que disparen las ventas de marcas e-commerce?EnMilimetrix, agencia de performance creada por ex-ejecutivos retail &amp; e-commerce, buscamos a nuestro nuevoPaid Media Manager. Serás parte de un equipo que combina consultoría estratégica y ejecución hands-on para escalar negocios en toda Latam.No nos conformamos con ser una agencia común. Estamos impulsados por la excelencia y la innovación, buscando siempre nuevas formas de hacer crecer los negocios de nuestros clientes. Nuestra visión es convertirnos en la agencia líder en marketing digital de Latinoamérica, y sabemos que esto solo es posible trabajando con los mejores talentos del sector.Lo que harás día a díaAnálisis Ninja:Identificar y traducir métricas complejas en insights estratégicos de alto impacto para el negocio de nuestros clientes. Diagnosticar la salud de las campañas y proponer soluciones de optimización.Growth Hacker en formación:Lanzar, monitorear y optimizar campañas en Google Ads, Meta Ads y LinkedIn Ads para distintos objetivos (ventas, leads, awareness).Control de vuelo diario:Vigilar métricas clave, budgets y pacing; proponer ajustes pro-profit y test A/B.Storyteller de datos:Convertir KPIs en relatos claros para clientes y para el equipo, recomendando próximos pasos que generen impacto real.Lo que necesitas traerFormación:Recién egresada/o deIngeniería Comercial o Ingeniería Civil.ADN Milimetrix:Fuerte orientación a la excelencia y pasión por entender qué hace que un negocio crezca. Buscamos a alguien que aspire a la maestría técnica y estratégica en performance.Conocimientos:Preferentemente conocimientos básicos en Google Ads y Meta Ads (si tienes certificaciones, ¡mejor!). Si no los tienes, entrarás a la mejor empresa para aprender y crecer.Herramientas:Manejo intermedio de Excel/Sheets y pasión por los datos.Soft Skills:Proactividad, gestión del tiempo, comunicación clara y espíritu colaborativo.Lo que ganarásMentoría directa de especialistas top en performance y e-commerce.Plan de entrenamiento en atribución, CRO y AI tools (sí, jugamos con lo último).Ambiente start-up: rápido, meritocrático y con desafíos reales desde el día 1.BeneficiosAlgunos de los beneficios Milimetrix:Modalidad:Híbrida 3x2Días libres por ocasión:Cumpleaños, mudanza, titulaciónFamilia:Licencias maternales y paternales extendidas (15 días adicionales). Los nuevos padres podrán trabajar de manera remota todas las tardes del primer medio año de vida de su nuevo integrante.Work from Anywhere:3 semanas al año para trabajar 100% remoto; dos semanas son fijas (septiembre y Navidad/Año Nuevo) y una semana adicional es de libre elección.Vacaciones Premium:Si programas y te tomas 10 días de vacaciones consecutivos, ¡nosotros te regalamos un 11° día libre!Experiencia Milimetrix:actividades de equipo mensuales para fortalecer la colaboración y cultura interna.Make the dream:Después de cierto tiempo en la empresa, disfruta de hasta 6 meses sin goce de sueldo para perseguir ese sueño pendiente.Luna de miel prolongada:Añade 5 días extra a tu licencia matrimonial.Acompañamiento:Dos semanas libres en caso de pérdida de embarazo. Estamos contigo.Convenio preferencial con MindFit Advanced, centro de entrenamiento ubicado en nuestro mismo edificio.Salud:Seguro complementario de salud y de vida sin costo.Equipamiento:Macbook asignado por la compañía.Detalles del cargoUbicación:Las Condes, Santiago.Horario:Lun-Jue 09:00 - 18:15 hrs; Vie: 8:30 -16:30</t>
         </is>
       </c>
     </row>
@@ -7088,54 +7088,50 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>📊 Paid Media Manager</t>
+          <t>🌟 ¡Queremos conocerte! Súmate a FORUS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Milimetrix</t>
+          <t>Forus</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Callao 2911, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56185/paid-media-manager</t>
+          <t>https://firstjob.me/oferta/56192/queremos-conocerte-sumate-a-forus</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>excel</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="n">
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -7145,29 +7141,29 @@
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>¿Te motiva convertir datos en decisiones que disparen las ventas de marcas e-commerce?EnMilimetrix, agencia de performance creada por ex-ejecutivos retail &amp; e-commerce, buscamos a nuestro nuevoPaid Media Manager. Serás parte de un equipo que combina consultoría estratégica y ejecución hands-on para escalar negocios en toda Latam.No nos conformamos con ser una agencia común. Estamos impulsados por la excelencia y la innovación, buscando siempre nuevas formas de hacer crecer los negocios de nuestros clientes. Nuestra visión es convertirnos en la agencia líder en marketing digital de Latinoamérica, y sabemos que esto solo es posible trabajando con los mejores talentos del sector.Lo que harás día a díaAnálisis Ninja:Identificar y traducir métricas complejas en insights estratégicos de alto impacto para el negocio de nuestros clientes. Diagnosticar la salud de las campañas y proponer soluciones de optimización.Growth Hacker en formación:Lanzar, monitorear y optimizar campañas en Google Ads, Meta Ads y LinkedIn Ads para distintos objetivos (ventas, leads, awareness).Control de vuelo diario:Vigilar métricas clave, budgets y pacing; proponer ajustes pro-profit y test A/B.Storyteller de datos:Convertir KPIs en relatos claros para clientes y para el equipo, recomendando próximos pasos que generen impacto real.Lo que necesitas traerFormación:Recién egresada/o deIngeniería Comercial o Ingeniería Civil.ADN Milimetrix:Fuerte orientación a la excelencia y pasión por entender qué hace que un negocio crezca. Buscamos a alguien que aspire a la maestría técnica y estratégica en performance.Conocimientos:Preferentemente conocimientos básicos en Google Ads y Meta Ads (si tienes certificaciones, ¡mejor!). Si no los tienes, entrarás a la mejor empresa para aprender y crecer.Herramientas:Manejo intermedio de Excel/Sheets y pasión por los datos.Soft Skills:Proactividad, gestión del tiempo, comunicación clara y espíritu colaborativo.Lo que ganarásMentoría directa de especialistas top en performance y e-commerce.Plan de entrenamiento en atribución, CRO y AI tools (sí, jugamos con lo último).Ambiente start-up: rápido, meritocrático y con desafíos reales desde el día 1.BeneficiosAlgunos de los beneficios Milimetrix:Modalidad:Híbrida 3x2Días libres por ocasión:Cumpleaños, mudanza, titulaciónFamilia:Licencias maternales y paternales extendidas (15 días adicionales). Los nuevos padres podrán trabajar de manera remota todas las tardes del primer medio año de vida de su nuevo integrante.Work from Anywhere:3 semanas al año para trabajar 100% remoto; dos semanas son fijas (septiembre y Navidad/Año Nuevo) y una semana adicional es de libre elección.Vacaciones Premium:Si programas y te tomas 10 días de vacaciones consecutivos, ¡nosotros te regalamos un 11° día libre!Experiencia Milimetrix:actividades de equipo mensuales para fortalecer la colaboración y cultura interna.Make the dream:Después de cierto tiempo en la empresa, disfruta de hasta 6 meses sin goce de sueldo para perseguir ese sueño pendiente.Luna de miel prolongada:Añade 5 días extra a tu licencia matrimonial.Acompañamiento:Dos semanas libres en caso de pérdida de embarazo. Estamos contigo.Convenio preferencial con MindFit Advanced, centro de entrenamiento ubicado en nuestro mismo edificio.Salud:Seguro complementario de salud y de vida sin costo.Equipamiento:Macbook asignado por la compañía.Detalles del cargoUbicación:Las Condes, Santiago.Horario:Lun-Jue 09:00 - 18:15 hrs; Vie: 8:30 -16:30</t>
+          <t>EnFORUSqueremos conocerte. 💙Somos una compañía líder en retail, con un portafolio de increíbles marcas internacionales comoVans, Columbia, Hush Puppies, CAT, Merrell y Under Armour, entre otras.Creemos que el talento puede venir de distintos lugares y que las mejores oportunidades comienzan con una conversación. Por eso, abrimos este espacio para que puedasdejarnos tu CV y ser parte de nuestra Base de Talento.🔎 ¿A quiénes buscamos?Esta convocatoria está dirigida a personas que:Estén buscando realizar supráctica profesional.Seanrecién egresados/asy estén buscando su primera experiencia laboral.Estén dando sus primeros pasos profesionales y quieran desarrollarse en una compañía dinámica y desafiante.Buscamos talento de distintas carreras y áreas, porque en FORUS existen oportunidades en múltiples equipos:Marketing, Comercial, Finanzas, Recursos Humanos, Operaciones, Supply Chain, Tecnología, Producto, Diseño, Retail, entre otras.🚀 ¿Por quéFORUS?Porque aquí podrás aprender, aportar y asumir desafíos desde el comienzo.Somos una compañía que valora lacuriosidad, la agilidad, el ownership y la accountability, y que busca personas con ganas de aprender, proponer ideas y hacer que las cosas pasen.Tu primer trabajo o práctica puede ser mucho más que una experiencia en tu CV: puede ser el comienzo de tu desarrollo profesional.📩 ¡Déjanos tu CV!Aunque hoy no tengamos publicada una vacante específica para tu perfil,queremos conocerte y considerar tu perfil para futuras oportunidades de práctica y posiciones junior en FORUS.👉Postula dejando tu CV actualizado y cuéntanos qué tipo de oportunidad estás buscando.¡Quizás tu próximo desafío comienza aquí! 🚀#FORUS #TalentoFORUS #Prácticas #PrimerTrabajo #Empleabilidad #OportunidadesLaboralesBeneficios👟 Trabajar con grandes marcas internacionales🚀 Aprender en una compañía dinámica y en crecimiento🌎 Conocer un negocio con presencia regional💡 Participar en proyectos y desafíos reales🤝 Trabajar junto a equipos multidisciplinarios📚 Desarrollar experiencia y habilidades para tu futuro profesional🛍️ Acceder a beneficios y descuentos en nuestras marcas❤️ Ser parte de iniciativas de bienestar y calidad de vida</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>🌟 ¡Queremos conocerte! Súmate a FORUS</t>
+          <t>Práctica Profesional Auditoría (Temporada de Verano)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Forus</t>
+          <t>KPMG Chile</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Las Condes, Metropolitana, Chile, Chile</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -7177,7 +7173,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56192/queremos-conocerte-sumate-a-forus</t>
+          <t>https://firstjob.me/oferta/56218/practica-profesional-auditoria-temporada-de-verano</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -7191,7 +7187,7 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
         <v>1</v>
@@ -7210,7 +7206,7 @@
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>EnFORUSqueremos conocerte. 💙Somos una compañía líder en retail, con un portafolio de increíbles marcas internacionales comoVans, Columbia, Hush Puppies, CAT, Merrell y Under Armour, entre otras.Creemos que el talento puede venir de distintos lugares y que las mejores oportunidades comienzan con una conversación. Por eso, abrimos este espacio para que puedasdejarnos tu CV y ser parte de nuestra Base de Talento.🔎 ¿A quiénes buscamos?Esta convocatoria está dirigida a personas que:Estén buscando realizar supráctica profesional.Seanrecién egresados/asy estén buscando su primera experiencia laboral.Estén dando sus primeros pasos profesionales y quieran desarrollarse en una compañía dinámica y desafiante.Buscamos talento de distintas carreras y áreas, porque en FORUS existen oportunidades en múltiples equipos:Marketing, Comercial, Finanzas, Recursos Humanos, Operaciones, Supply Chain, Tecnología, Producto, Diseño, Retail, entre otras.🚀 ¿Por quéFORUS?Porque aquí podrás aprender, aportar y asumir desafíos desde el comienzo.Somos una compañía que valora lacuriosidad, la agilidad, el ownership y la accountability, y que busca personas con ganas de aprender, proponer ideas y hacer que las cosas pasen.Tu primer trabajo o práctica puede ser mucho más que una experiencia en tu CV: puede ser el comienzo de tu desarrollo profesional.📩 ¡Déjanos tu CV!Aunque hoy no tengamos publicada una vacante específica para tu perfil,queremos conocerte y considerar tu perfil para futuras oportunidades de práctica y posiciones junior en FORUS.👉Postula dejando tu CV actualizado y cuéntanos qué tipo de oportunidad estás buscando.¡Quizás tu próximo desafío comienza aquí! 🚀#FORUS #TalentoFORUS #Prácticas #PrimerTrabajo #Empleabilidad #OportunidadesLaboralesBeneficios👟 Trabajar con grandes marcas internacionales🚀 Aprender en una compañía dinámica y en crecimiento🌎 Conocer un negocio con presencia regional💡 Participar en proyectos y desafíos reales🤝 Trabajar junto a equipos multidisciplinarios📚 Desarrollar experiencia y habilidades para tu futuro profesional🛍️ Acceder a beneficios y descuentos en nuestras marcas❤️ Ser parte de iniciativas de bienestar y calidad de vida</t>
+          <t>**Perfil Ideal: Practicante de Auditoría (Temporada de Verano)** Buscamos estudiantes de último año de Contador Auditor, Ingeniería en Información y Control de Gestión o Ingeniería Comercial para unirse a nuestro equipo de Auditoría durante la temporada de verano. El candidato ideal demostrará un fuerte compromiso, adaptabilidad y una mentalidad colaborativa, prosperando en entornos de alta exigencia. **Competencias Clave:** * **Pensamiento Crítico y Juicio Profesional:** Capacidad para abordar tareas con precisión y criterio técnico. * **Habilidades Analíticas y Metódicas:** Aptitud para diseñar y ejecutar procedimientos de auditoría sustantivos y analíticos. * **Competencia Tecnológica:** Conocimiento y aplicación de herramientas tecnológicas para optimizar procesos. * **Organización y Documentación:** Habilidad para estructurar papeles de trabajo de forma ordenada y documentar evidencia según normas de auditoría. * **Comunicación Efectiva:** Capacidad para interactuar fluidamente con el equipo de trabajo y clientes. * **Proactividad y Aprendizaje Continuo:** Motivación por adquirir nuevos conocimientos y enfrentar desafíos. * **Gestión del Tiempo:** Habilidad para administrar eficazmente el tiempo y cumplir plazos. * **Ética Profesional:** Estricto respeto por las políticas de independencia, confidencialidad y manejo de información sensible. **Requisitos Esenciales:** * Estudiante regular de 4° o 5° año de las carreras mencionadas. * Disponibilidad mínima de 360 horas (full-time). * Disponibilidad para iniciar entre diciembre y enero. * Carta de solicitud de práctica y seguro escolar vigente (excluyentes). * Disponibilidad para modalidad híbrida (oficina en Santiago y visitas a terreno). * Para estudiantes de regiones, posibilidad de residir en SantiagoBeneficios¿Qué ganas tú? 💰 Remuneración mensual: $400.000 CLP. 🌍 Oportunidad de realizar tu práctica en una firma multinacional líder en consultoría, con proyección de desarrollo profesional. 📈 Alta posibilidad de continuidad laboral y desarrollo profesional dentro de la Firma. 🧠 Aprendizaje continuo a través de la plataforma Degreed, donde podrás desarrollar habilidades según tus intereses y línea de carrera. 🕐 Viernes más cortos: horario de salida a las 13:30 hrs. 👔 Vestimenta business casual, para que trabajes con comodidad y profesionalismo. 🎉 Día libre en tu cumpleaños, porque celebrar también es importante. 🤝 Flexibilidad horaria: si necesitas realizar trámites personales, puedes coordinarlo directamente con tu jefatura. 💼 Múltiples convenios en áreas como salud dental, kinesiología, estética, restaurantes y cafeterías. 🚲 Estacionamiento gratuito para bicicletas y scooters, con acceso a camarines y duchas. En KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas , con un propósito claro, para una mejor sociedad. Valoramos las diversas habilidades y fortalezas, tanto personales como profesionales, que cada persona aporta. En KPMG estamos comprometidos con la Diversidad e inclusión , nuestras ofertas de empleo están disponibles con los ajustes razonables necesarios para tu proceso. Juntos, estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. ¡Anímate y ven a descubrir por qué somos la opción más clara! 🥇</t>
         </is>
       </c>
     </row>
@@ -7222,17 +7218,17 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Práctica Profesional Auditoría (Temporada de Verano)</t>
+          <t>Analista Centro Control Operacional (OTP)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KPMG Chile</t>
+          <t>Polpaico Soluciones</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Las Condes, Metropolitana, Chile, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -7242,13 +7238,17 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56218/practica-profesional-auditoria-temporada-de-verano</t>
+          <t>https://firstjob.me/oferta/56219/analista-centro-control-operacional-otp</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>python, analisis, power bi</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
@@ -7256,7 +7256,7 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
         <v>1</v>
@@ -7265,7 +7265,7 @@
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>**Perfil Ideal: Practicante de Auditoría (Temporada de Verano)** Buscamos estudiantes de último año de Contador Auditor, Ingeniería en Información y Control de Gestión o Ingeniería Comercial para unirse a nuestro equipo de Auditoría durante la temporada de verano. El candidato ideal demostrará un fuerte compromiso, adaptabilidad y una mentalidad colaborativa, prosperando en entornos de alta exigencia. **Competencias Clave:** * **Pensamiento Crítico y Juicio Profesional:** Capacidad para abordar tareas con precisión y criterio técnico. * **Habilidades Analíticas y Metódicas:** Aptitud para diseñar y ejecutar procedimientos de auditoría sustantivos y analíticos. * **Competencia Tecnológica:** Conocimiento y aplicación de herramientas tecnológicas para optimizar procesos. * **Organización y Documentación:** Habilidad para estructurar papeles de trabajo de forma ordenada y documentar evidencia según normas de auditoría. * **Comunicación Efectiva:** Capacidad para interactuar fluidamente con el equipo de trabajo y clientes. * **Proactividad y Aprendizaje Continuo:** Motivación por adquirir nuevos conocimientos y enfrentar desafíos. * **Gestión del Tiempo:** Habilidad para administrar eficazmente el tiempo y cumplir plazos. * **Ética Profesional:** Estricto respeto por las políticas de independencia, confidencialidad y manejo de información sensible. **Requisitos Esenciales:** * Estudiante regular de 4° o 5° año de las carreras mencionadas. * Disponibilidad mínima de 360 horas (full-time). * Disponibilidad para iniciar entre diciembre y enero. * Carta de solicitud de práctica y seguro escolar vigente (excluyentes). * Disponibilidad para modalidad híbrida (oficina en Santiago y visitas a terreno). * Para estudiantes de regiones, posibilidad de residir en SantiagoBeneficios¿Qué ganas tú? 💰 Remuneración mensual: $400.000 CLP. 🌍 Oportunidad de realizar tu práctica en una firma multinacional líder en consultoría, con proyección de desarrollo profesional. 📈 Alta posibilidad de continuidad laboral y desarrollo profesional dentro de la Firma. 🧠 Aprendizaje continuo a través de la plataforma Degreed, donde podrás desarrollar habilidades según tus intereses y línea de carrera. 🕐 Viernes más cortos: horario de salida a las 13:30 hrs. 👔 Vestimenta business casual, para que trabajes con comodidad y profesionalismo. 🎉 Día libre en tu cumpleaños, porque celebrar también es importante. 🤝 Flexibilidad horaria: si necesitas realizar trámites personales, puedes coordinarlo directamente con tu jefatura. 💼 Múltiples convenios en áreas como salud dental, kinesiología, estética, restaurantes y cafeterías. 🚲 Estacionamiento gratuito para bicicletas y scooters, con acceso a camarines y duchas. En KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas , con un propósito claro, para una mejor sociedad. Valoramos las diversas habilidades y fortalezas, tanto personales como profesionales, que cada persona aporta. En KPMG estamos comprometidos con la Diversidad e inclusión , nuestras ofertas de empleo están disponibles con los ajustes razonables necesarios para tu proceso. Juntos, estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. ¡Anímate y ven a descubrir por qué somos la opción más clara! 🥇</t>
+          <t>Polpaico Soluciones, es una compañía líder en el mercado nacional de la fabricación y comercialización de cemento, hormigón y áridos. Como empresa estamos convencidos que tener un equipo de trabajo diverso y una cultura inclusiva genera beneficios para las personas y el negocio. No sólo aceptamos la diversidad, sino que la valoramos y promovemos activamente.Actualmente nos encontramos en la búsqueda de unAnalista Centro Control Operacional (OTP)Elobjetivodel cargo es: Recopilar, procesar y analizar los datos operacionales del CCO para construir los indicadores de desempeño que permiten medir la puntualidad, regularidad, estadía, ciclos de camión y productividad de operadores, asegurando continuidad y consistencia en la producción de información. Provee al Jefe de OTP la base analítica para reportar con el desempeño de la operación.¿Cuáles serán tus principales funciones en este cargo?1. Extraer, validar y procesar los datos operacionales desde Command Alkon, GPS, TrackIt y telemetría para la construcción diaria de los indicadores del CCO.2. Calcular y actualizar el OTD (On Time Delivery) con ventana ±10 minutos por carga, obra, cliente, planta y zona geográfica, incluyendo la puntualidad de primera carga como indicador separado.3. Medir el OTP (On Time Performance) frecuencias, regularidad de cargas comprometidas versus ejecutadas y detectar desviaciones que requieran análisis de causa raíz.4. Calcular la estadía y sobre estadía de camiones por obra y cliente, cuantificando el impacto en viajes perdidos equivalentes para el informe mensual al área comercial.5. Analizar los ciclos de camión tiempo de carga en planta, tránsito, descarga y retorno identificando patrones de ineficiencia por zona, planta u operador.6. Actualizar semanalmente el ranking de operadores mediante el driver score multidimensional, integrando las dimensiones de combustible, velocidad, frenadas, G en curvas, puntualidad, tiempo de carga y estadía en obra.7. Medir la productividad de los operadores mixer m³ por turno, viajes completados, tiempo productivo versus improductivo y mantener el histórico para análisis de tendencias.8. Registrar y codificar las causas raíz de atrasos, sobre estadías y contingencias operacionales, manteniendo actualizada la base de datos histórica del CCO.9. Mantener actualizados los dashboards operacionales del CCO, asegurando disponibilidad, calidad visual y consistencia de los datos publicados.10. Apoyar al Jefe de OTP en la preparación de reportes ejecutivos, presentaciones y análisis especiales requeridos por el Gerente CCO o las subgerencias.Formación y Conocimientos-Título profesional de Ingeniería Civil Industrial ó Civil informático.-Conocimientos en Análisis de datos y construcción de indicadores de gestión operacional.-Power BI (Deseable)-SAP (Deseable)-Python (Deseable)</t>
         </is>
       </c>
     </row>
@@ -7287,12 +7287,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Analista Centro Control Operacional (OTP)</t>
+          <t>Analista Contable Trainee - Las Condes</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Polpaico Soluciones</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -7307,15 +7307,15 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56219/analista-centro-control-operacional-otp</t>
+          <t>https://firstjob.me/oferta/56221/analista-contable-trainee-las-condes</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>python, analisis, power bi</t>
+          <t>analisis, trainee, excel</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -7337,14 +7337,14 @@
         <v>0</v>
       </c>
       <c r="O102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P102" t="n">
         <v>0</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>Polpaico Soluciones, es una compañía líder en el mercado nacional de la fabricación y comercialización de cemento, hormigón y áridos. Como empresa estamos convencidos que tener un equipo de trabajo diverso y una cultura inclusiva genera beneficios para las personas y el negocio. No sólo aceptamos la diversidad, sino que la valoramos y promovemos activamente.Actualmente nos encontramos en la búsqueda de unAnalista Centro Control Operacional (OTP)Elobjetivodel cargo es: Recopilar, procesar y analizar los datos operacionales del CCO para construir los indicadores de desempeño que permiten medir la puntualidad, regularidad, estadía, ciclos de camión y productividad de operadores, asegurando continuidad y consistencia en la producción de información. Provee al Jefe de OTP la base analítica para reportar con el desempeño de la operación.¿Cuáles serán tus principales funciones en este cargo?1. Extraer, validar y procesar los datos operacionales desde Command Alkon, GPS, TrackIt y telemetría para la construcción diaria de los indicadores del CCO.2. Calcular y actualizar el OTD (On Time Delivery) con ventana ±10 minutos por carga, obra, cliente, planta y zona geográfica, incluyendo la puntualidad de primera carga como indicador separado.3. Medir el OTP (On Time Performance) frecuencias, regularidad de cargas comprometidas versus ejecutadas y detectar desviaciones que requieran análisis de causa raíz.4. Calcular la estadía y sobre estadía de camiones por obra y cliente, cuantificando el impacto en viajes perdidos equivalentes para el informe mensual al área comercial.5. Analizar los ciclos de camión tiempo de carga en planta, tránsito, descarga y retorno identificando patrones de ineficiencia por zona, planta u operador.6. Actualizar semanalmente el ranking de operadores mediante el driver score multidimensional, integrando las dimensiones de combustible, velocidad, frenadas, G en curvas, puntualidad, tiempo de carga y estadía en obra.7. Medir la productividad de los operadores mixer m³ por turno, viajes completados, tiempo productivo versus improductivo y mantener el histórico para análisis de tendencias.8. Registrar y codificar las causas raíz de atrasos, sobre estadías y contingencias operacionales, manteniendo actualizada la base de datos histórica del CCO.9. Mantener actualizados los dashboards operacionales del CCO, asegurando disponibilidad, calidad visual y consistencia de los datos publicados.10. Apoyar al Jefe de OTP en la preparación de reportes ejecutivos, presentaciones y análisis especiales requeridos por el Gerente CCO o las subgerencias.Formación y Conocimientos-Título profesional de Ingeniería Civil Industrial ó Civil informático.-Conocimientos en Análisis de datos y construcción de indicadores de gestión operacional.-Power BI (Deseable)-SAP (Deseable)-Python (Deseable)</t>
+          <t>¡En CCU nos apasiona crear experiencias para compartir juntos un mejor vivir!Estamos en búsqueda de un/a Analista Contable Trainee para desempeñarse en nuestro edificio corporativo ubicado en la comuna de Las Condes.Principales Funciones:Revisión de estados financieros mensuales de forma analítica.Registro de provisiones.Contrucción de flujo de efectivo.Presentaciones de estado financieros a los clientes asignados.Realización de encuestas INE.Preparación de análisis de cuentas.Requisitos:Título de Contador AuditorManejo de Excel nivel intermedio (excluyente).Experiencia de 1 año en contabilidad (no excluyente).Maneje SAP (no excluyente).Nuestro SER CCU nos inspira a trabajar con aceptación y respeto a las diferencias de las personas, promoviendo un entorno diverso e integrador, para así contribuir a un mejor vivir. Por esto, te agradecemos que nos compartas si necesitas adaptación en alguna etapa del proceso de postulación.¡Te invitamos a SER CCU!</t>
         </is>
       </c>
     </row>
@@ -7356,12 +7356,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Analista Contable Trainee - Las Condes</t>
+          <t>Analista de Proyectos de innovación Digital</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -7371,20 +7371,20 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56221/analista-contable-trainee-las-condes</t>
+          <t>https://firstjob.me/oferta/56224/analista-de-proyectos-de-innovacion-digital</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>analisis, trainee, excel</t>
+          <t>analisis, excel, power bi, looker studio, looker, gemini</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -7394,48 +7394,48 @@
         <v>0</v>
       </c>
       <c r="K103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>¡En CCU nos apasiona crear experiencias para compartir juntos un mejor vivir!Estamos en búsqueda de un/a Analista Contable Trainee para desempeñarse en nuestro edificio corporativo ubicado en la comuna de Las Condes.Principales Funciones:Revisión de estados financieros mensuales de forma analítica.Registro de provisiones.Contrucción de flujo de efectivo.Presentaciones de estado financieros a los clientes asignados.Realización de encuestas INE.Preparación de análisis de cuentas.Requisitos:Título de Contador AuditorManejo de Excel nivel intermedio (excluyente).Experiencia de 1 año en contabilidad (no excluyente).Maneje SAP (no excluyente).Nuestro SER CCU nos inspira a trabajar con aceptación y respeto a las diferencias de las personas, promoviendo un entorno diverso e integrador, para así contribuir a un mejor vivir. Por esto, te agradecemos que nos compartas si necesitas adaptación en alguna etapa del proceso de postulación.¡Te invitamos a SER CCU!</t>
+          <t>Buscamos a alguien que no solo use tecnología, sino que disfrute descubriendo cómo hacer que otros también quieran usarla.Si eres de las personas que prueba nuevas herramientas de IA, automatiza tareas, analiza cómo se comportan los usuarios y siempre está pensando “esto podría funcionar mejor”, queremos conocerte.Te sumarás al equipo detrás de una plataforma digital con un desafío concreto: aumentar su adopción, mejorar la experiencia de sus usuarios y convertir información, feedback e ideas en iniciativas que generen impacto real.Este rol combinaproducto digital, inteligencia artificial, análisis de datos, experiencia de usuarios y gestión de comunidades. Buscamos a alguien inquieto, creativo y con ganas de experimentar, pero también capaz de implementar, medir resultados y hacer seguimiento.Tu desafío será:🤖Explorar y aplicar herramientas de IApara analizar información, crear contenidos, sistematizar feedback, optimizar procesos y proponer nuevas formas de relacionarnos con los usuarios.🚀Diseñar e implementar iniciativas de adopción digitalque ayuden a incorporar nuevos usuarios y aumentar el uso efectivo de la plataforma.🔍Entender el comportamiento de los usuarios, identificando barreras, necesidades y oportunidades de mejora.📊Construir indicadores y reportesde uso, satisfacción, adopción y crecimiento, transformando datos en recomendaciones concretas.💡Experimentar con nuevas ideas, evaluar sus resultados y escalar aquellas que generen mayor valor.🎓Crear experiencias de incorporación y aprendizaje, incluyendo materiales, capacitaciones y recursos que faciliten el uso de la plataforma.🌐Activar una comunidad de usuarios, generando instancias de colaboración, participación e intercambio de buenas prácticas.🤝Trabajar con usuarios y organizaciones, levantando feedback y convirtiéndolo en mejoras para el producto.Este desafío puede ser para ti si…✔ Tienes entre 1 y 3 años de experiencia en adopción de productos digitales, Product Operations, Customer Success, Growth, implementación tecnológica, innovación o transformación digital.✔ Te interesa genuinamente la inteligencia artificial y ya experimentas con herramientas como ChatGPT, Claude, Gemini, Copilot u otras.✔ Has participado en iniciativas orientadas a aumentar el uso, incorporación o engagement de usuarios de una plataforma.✔ Disfrutas combinando análisis, creatividad y contacto directo con usuarios.✔ Manejas Excel o Google Sheets y tienes experiencia trabajando con indicadores.✔ Te acomoda probar ideas, aprender de los resultados y realizar ajustes rápidamente.✔ Puedes coordinar iniciativas con distintos actores y hacer seguimiento hasta que efectivamente ocurran.⭐Sumas puntos si tienes experiencia en:Diseño de estrategias de adopción digital.Automatización de procesos con IA.UX, investigación o levantamiento de necesidades de usuarios.Gestión o activación de comunidades.Power BI, Looker Studio u otras herramientas de visualización.Relacionamiento con municipios, instituciones u organizaciones.Lo que esperamos encontrar en tiCuriosidad tecnológica real.Mentalidad experimental.Orientación a usuarios y resultados.Creatividad para proponer nuevas soluciones.Capacidad para convertir ideas en acciones.Autonomía, organización y seguimiento.Interés permanente por aprender y probar herramientas emergentes.BeneficiosBonificaciones durante el añoReajuste trimestral según IPCCofinanciamiento de estudiosBeneficios de salud y bienestar:seguro complementario, apoyo actividades recreativas y gimnasia.Beneficios que acompañan tu desarrollo y bienestar:bonificaciones durante el año, reajustes trimestrales según IPC, cofinanciamiento para continuar estudiando, seguros de salud y vida, y distintos permisos para que puedas compatibilizar mejor tu trabajo con tu vida personal.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Analista de Proyectos de innovación Digital</t>
+          <t>Product Manager Loyalty</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Ripley chile</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Ofi. Alonso De Cordova 5320 - Producto Financiero, Chile</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -7445,15 +7445,15 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56224/analista-de-proyectos-de-innovacion-digital</t>
+          <t>https://firstjob.me/oferta/56247/product-manager-loyalty</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>analisis, excel, power bi, looker studio, looker, gemini</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -7472,17 +7472,17 @@
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
       </c>
       <c r="P104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Buscamos a alguien que no solo use tecnología, sino que disfrute descubriendo cómo hacer que otros también quieran usarla.Si eres de las personas que prueba nuevas herramientas de IA, automatiza tareas, analiza cómo se comportan los usuarios y siempre está pensando “esto podría funcionar mejor”, queremos conocerte.Te sumarás al equipo detrás de una plataforma digital con un desafío concreto: aumentar su adopción, mejorar la experiencia de sus usuarios y convertir información, feedback e ideas en iniciativas que generen impacto real.Este rol combinaproducto digital, inteligencia artificial, análisis de datos, experiencia de usuarios y gestión de comunidades. Buscamos a alguien inquieto, creativo y con ganas de experimentar, pero también capaz de implementar, medir resultados y hacer seguimiento.Tu desafío será:🤖Explorar y aplicar herramientas de IApara analizar información, crear contenidos, sistematizar feedback, optimizar procesos y proponer nuevas formas de relacionarnos con los usuarios.🚀Diseñar e implementar iniciativas de adopción digitalque ayuden a incorporar nuevos usuarios y aumentar el uso efectivo de la plataforma.🔍Entender el comportamiento de los usuarios, identificando barreras, necesidades y oportunidades de mejora.📊Construir indicadores y reportesde uso, satisfacción, adopción y crecimiento, transformando datos en recomendaciones concretas.💡Experimentar con nuevas ideas, evaluar sus resultados y escalar aquellas que generen mayor valor.🎓Crear experiencias de incorporación y aprendizaje, incluyendo materiales, capacitaciones y recursos que faciliten el uso de la plataforma.🌐Activar una comunidad de usuarios, generando instancias de colaboración, participación e intercambio de buenas prácticas.🤝Trabajar con usuarios y organizaciones, levantando feedback y convirtiéndolo en mejoras para el producto.Este desafío puede ser para ti si…✔ Tienes entre 1 y 3 años de experiencia en adopción de productos digitales, Product Operations, Customer Success, Growth, implementación tecnológica, innovación o transformación digital.✔ Te interesa genuinamente la inteligencia artificial y ya experimentas con herramientas como ChatGPT, Claude, Gemini, Copilot u otras.✔ Has participado en iniciativas orientadas a aumentar el uso, incorporación o engagement de usuarios de una plataforma.✔ Disfrutas combinando análisis, creatividad y contacto directo con usuarios.✔ Manejas Excel o Google Sheets y tienes experiencia trabajando con indicadores.✔ Te acomoda probar ideas, aprender de los resultados y realizar ajustes rápidamente.✔ Puedes coordinar iniciativas con distintos actores y hacer seguimiento hasta que efectivamente ocurran.⭐Sumas puntos si tienes experiencia en:Diseño de estrategias de adopción digital.Automatización de procesos con IA.UX, investigación o levantamiento de necesidades de usuarios.Gestión o activación de comunidades.Power BI, Looker Studio u otras herramientas de visualización.Relacionamiento con municipios, instituciones u organizaciones.Lo que esperamos encontrar en tiCuriosidad tecnológica real.Mentalidad experimental.Orientación a usuarios y resultados.Creatividad para proponer nuevas soluciones.Capacidad para convertir ideas en acciones.Autonomía, organización y seguimiento.Interés permanente por aprender y probar herramientas emergentes.BeneficiosBonificaciones durante el añoReajuste trimestral según IPCCofinanciamiento de estudiosBeneficios de salud y bienestar:seguro complementario, apoyo actividades recreativas y gimnasia.Beneficios que acompañan tu desarrollo y bienestar:bonificaciones durante el año, reajustes trimestrales según IPC, cofinanciamiento para continuar estudiando, seguros de salud y vida, y distintos permisos para que puedas compatibilizar mejor tu trabajo con tu vida personal.</t>
+          <t>¡En Banco Ripley Chile estamos en búsqueda de un/a Product Manager Loyalty! 🛍️💜Sé parte de Banco Ripley, un banco retail en constante crecimiento, donde trabajamos de forma colaborativa para potenciar el uso de nuestros medios de pago y generar mayor valor comercial y financiero para el negocio.¿Cuál será tu principal desafío? 🚀💡 Administrar y rentabilizar la relación comercial entre Retail y Banco Ripley, maximizando el uso de nuestros medios de pago en todos sus formatos.💜 Gestionar y escalar el programa Ripley Puntos Go como palanca de fidelización.📣 Evaluar, diseñar y coordinar campañas con Retail en las principales categorías, impulsando el uso y la facturación del medio de pago.📈 Definir estrategias comerciales, de marketing y CRM orientadas a aumentar la facturación del medio de pago en Retail y la rentabilidad del producto.🧠 Coordinar de forma transversal con distintos equipos de Banco y Retail para asegurar una correcta ejecución, control de gastos y medición de resultados.¿Qué valoramos en tu postulación? 🎯🎓 Profesional titulado/a de Ingeniería Comercial, Ingeniería Civil o carrera afín.💼 Entre 1 y 2 años de experiencia en áreas comerciales, marketing o similares.📊 Manejo de Excel y PowerPoint.🧠 Fuerte sentido comercial, orientación a resultados y capacidad analítica.¿Por qué trabajar en Banco Ripley? 💜Nos importa tu desarrollo y bienestar, por eso ofrecemos:🔹 Oportunidades de aprendizaje y crecimiento profesional.🔹 Trabajo colaborativo con equipos de alto impacto en el negocio.🔹 Tasa preferencial en productos Banco Ripley.🔹 Seguro complementario.🔹 Descuentos en Tiendas Ripley.En Ripley y Banco Ripley promovemos una cultura diversa e inclusiva. En el marco de la Ley 21.015, invitamos a todas las personas a postular y a informarnos si requieren algún ajuste razonable durante el proceso.📢 ¡Postula y sé parte del equipo que impulsa el crecimiento y la rentabilidad del negocio retail en Banco Ripley! 🚀💳BeneficiosDescripción de los beneficios de la vacante</t>
         </is>
       </c>
     </row>
@@ -7494,17 +7494,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Product Manager Loyalty</t>
+          <t>Analista de Contenido Junior</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ripley chile</t>
+          <t>Kitchen Center</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Ofi. Alonso De Cordova 5320 - Producto Financiero, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56247/product-manager-loyalty</t>
+          <t>https://firstjob.me/oferta/56248/analista-de-contenido-junior</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>excel</t>
+          <t>html</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -7541,7 +7541,7 @@
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>¡En Banco Ripley Chile estamos en búsqueda de un/a Product Manager Loyalty! 🛍️💜Sé parte de Banco Ripley, un banco retail en constante crecimiento, donde trabajamos de forma colaborativa para potenciar el uso de nuestros medios de pago y generar mayor valor comercial y financiero para el negocio.¿Cuál será tu principal desafío? 🚀💡 Administrar y rentabilizar la relación comercial entre Retail y Banco Ripley, maximizando el uso de nuestros medios de pago en todos sus formatos.💜 Gestionar y escalar el programa Ripley Puntos Go como palanca de fidelización.📣 Evaluar, diseñar y coordinar campañas con Retail en las principales categorías, impulsando el uso y la facturación del medio de pago.📈 Definir estrategias comerciales, de marketing y CRM orientadas a aumentar la facturación del medio de pago en Retail y la rentabilidad del producto.🧠 Coordinar de forma transversal con distintos equipos de Banco y Retail para asegurar una correcta ejecución, control de gastos y medición de resultados.¿Qué valoramos en tu postulación? 🎯🎓 Profesional titulado/a de Ingeniería Comercial, Ingeniería Civil o carrera afín.💼 Entre 1 y 2 años de experiencia en áreas comerciales, marketing o similares.📊 Manejo de Excel y PowerPoint.🧠 Fuerte sentido comercial, orientación a resultados y capacidad analítica.¿Por qué trabajar en Banco Ripley? 💜Nos importa tu desarrollo y bienestar, por eso ofrecemos:🔹 Oportunidades de aprendizaje y crecimiento profesional.🔹 Trabajo colaborativo con equipos de alto impacto en el negocio.🔹 Tasa preferencial en productos Banco Ripley.🔹 Seguro complementario.🔹 Descuentos en Tiendas Ripley.En Ripley y Banco Ripley promovemos una cultura diversa e inclusiva. En el marco de la Ley 21.015, invitamos a todas las personas a postular y a informarnos si requieren algún ajuste razonable durante el proceso.📢 ¡Postula y sé parte del equipo que impulsa el crecimiento y la rentabilidad del negocio retail en Banco Ripley! 🚀💳BeneficiosDescripción de los beneficios de la vacante</t>
+          <t>Kitchen Center imporante Empresa del rubro Retail, buscamos a una persona creativa, analítica y con gran interés en el mundo digital, para integrarse a un equipo de trabajo dinámico, donde podrá aportar a la generación de contenidos orientados al posicionamiento orgánico y crecimiento de visibilidad en canales digitales.Principales responsabilidades:Implementación y optimización de mejoras técnicas SEO para RRSS y sitio web.Redacción de textos SEO (blog, notas, descripciones de productos, recetas, comparativas, preguntas frecuentes, entre otros) implementando buenas prácticas del orgánico (html, H1, H2, estructura de textos).Elaboración semanal de un listado de palabras clave para orientar contenido estratégico y definir el calendario de contenido de SEO (según palabras clave y tendencias).Supervisión y actualización de las páginas web de las marcas, asegurando que el contenido esté vigente, alineado con campañas, correctamente vinculado y optimizado con palabras clave relevantes para mejorar su visibilidad.Medición del crecimiento del SEO tanto de Google como Social.Apoyo general en la planificación de RRSS (Redacción de copies para RRSS, CTA, considerando palabras clave relevantes, etc).Planificación y organización de contenido visual (fotos y vídeos) (considera hacer los Briefs para los videos)Apoyo transversal en la revisión y redacción de textos que se requieren en distintas áreas de la empresa.lacionadas con el desempeño del contenido orgánico.Perfil deseadoCarrera: Publicista, Periodista, Relacionador Público, Ingeniería en marketing o afín.Experiencia: al menos 6 meses de experiencia comprobada en SEOBeneficiosTrabajo Híbrido 3x2Casino en Casa MatrizEstacionamientoGimnasio en Casa Matriz</t>
         </is>
       </c>
     </row>
@@ -7563,27 +7563,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Analista de Contenido Junior</t>
+          <t>Customer Success</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Kitchen Center</t>
+          <t>Cumplo</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Av Apoquindo 5400, Chile</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56248/analista-de-contenido-junior</t>
+          <t>https://firstjob.me/oferta/55276/customer-success</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>html</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -7601,16 +7601,16 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>Kitchen Center imporante Empresa del rubro Retail, buscamos a una persona creativa, analítica y con gran interés en el mundo digital, para integrarse a un equipo de trabajo dinámico, donde podrá aportar a la generación de contenidos orientados al posicionamiento orgánico y crecimiento de visibilidad en canales digitales.Principales responsabilidades:Implementación y optimización de mejoras técnicas SEO para RRSS y sitio web.Redacción de textos SEO (blog, notas, descripciones de productos, recetas, comparativas, preguntas frecuentes, entre otros) implementando buenas prácticas del orgánico (html, H1, H2, estructura de textos).Elaboración semanal de un listado de palabras clave para orientar contenido estratégico y definir el calendario de contenido de SEO (según palabras clave y tendencias).Supervisión y actualización de las páginas web de las marcas, asegurando que el contenido esté vigente, alineado con campañas, correctamente vinculado y optimizado con palabras clave relevantes para mejorar su visibilidad.Medición del crecimiento del SEO tanto de Google como Social.Apoyo general en la planificación de RRSS (Redacción de copies para RRSS, CTA, considerando palabras clave relevantes, etc).Planificación y organización de contenido visual (fotos y vídeos) (considera hacer los Briefs para los videos)Apoyo transversal en la revisión y redacción de textos que se requieren en distintas áreas de la empresa.lacionadas con el desempeño del contenido orgánico.Perfil deseadoCarrera: Publicista, Periodista, Relacionador Público, Ingeniería en marketing o afín.Experiencia: al menos 6 meses de experiencia comprobada en SEOBeneficiosTrabajo Híbrido 3x2Casino en Casa MatrizEstacionamientoGimnasio en Casa Matriz</t>
+          <t>¡Únete aCumplocomo nuestro próximoCustomer Success!👌En Cumplo, buscamos personas que quieran marcar la diferencia 💚. Personas que no solo busquen un trabajo, sino que quieran aportar al crecimiento de miles de pymes y transformar realidades.Queremos impactar. Soñamos con un mundo en el que todas las empresas accedan a los recursos que necesitan para crecer y desplegar su máximo potencial.¿Te identificas con todo esto? Si es así, ¡te estamos buscando!¿Qué te espera? 🎯Identificar y contactar empresas potenciales para generar nuevas oportunidades de negocio.Calificar prospectos y asegurar su conexión al sistema interno.Realizar prospección activa vía correo, teléfono y CRM.Investigar mercados e industrias para mejorar la estrategia comercial.Colaborar con los equipos de ventas, marketing y operaciones para asegurar un traspaso fluido de leads.Participar en iniciativas para aumentar la visibilidad y conversión de Cumplo.¿Qué necesitas? 🕵️‍♀️Deseable experiencia previa en ventas, prospección o desarrollo comercial.Al menos 1 año en roles comerciales, desarrollo de mercado o ventas (idealmente en servicios financieros o Fintech)Manejo de Excel y herramientas de gestión de bases de datos.Conocimientos en prospección digital e investigación de mercado.Familiaridad con plataformas CRM como Salesforce, HubSpot, entre otras.Disponibilidad para trabajar presencial en Las Condes.Beneficios¿Qué ofrecemos? 🎁Personal Days: Día libre por cumpleaños y mudanza.Más vacaciones: 3 días extra al año + 2 administrativos.2 Semanas de WFASeguro complementario.Convenio con Caja Los Andes.Cultura cercana y colaborativa: Sé parte de un equipo con propósito.Sobre nosotros 🌍En Cumplo, conectamos a empresas que buscan liquidez con personas dispuestas a invertir en sus proyectos. Nuestra misión es democratizar el financiamiento y apoyar el crecimiento de las pymes en Latinoamérica, promoviendo un ecosistema financiero más justo y transparente.Si compartes nuestra visión y deseas ser parte de este cambio, te invitamos a postular.💡 ¡Postula ahora y sé parte de la transformación financiera! 🚀</t>
         </is>
       </c>
     </row>
@@ -7632,17 +7632,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Customer Success</t>
+          <t>Ingenieroa de Planificación (Distribución) - Quilicura</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Cumplo</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Av Apoquindo 5400, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -7652,15 +7652,15 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55276/customer-success</t>
+          <t>https://firstjob.me/oferta/56242/ingeniero-a-de-planificacion-distribucion-quilicura</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>excel</t>
+          <t>sql, excel, power bi, looker studio, looker</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -7689,24 +7689,24 @@
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>¡Únete aCumplocomo nuestro próximoCustomer Success!👌En Cumplo, buscamos personas que quieran marcar la diferencia 💚. Personas que no solo busquen un trabajo, sino que quieran aportar al crecimiento de miles de pymes y transformar realidades.Queremos impactar. Soñamos con un mundo en el que todas las empresas accedan a los recursos que necesitan para crecer y desplegar su máximo potencial.¿Te identificas con todo esto? Si es así, ¡te estamos buscando!¿Qué te espera? 🎯Identificar y contactar empresas potenciales para generar nuevas oportunidades de negocio.Calificar prospectos y asegurar su conexión al sistema interno.Realizar prospección activa vía correo, teléfono y CRM.Investigar mercados e industrias para mejorar la estrategia comercial.Colaborar con los equipos de ventas, marketing y operaciones para asegurar un traspaso fluido de leads.Participar en iniciativas para aumentar la visibilidad y conversión de Cumplo.¿Qué necesitas? 🕵️‍♀️Deseable experiencia previa en ventas, prospección o desarrollo comercial.Al menos 1 año en roles comerciales, desarrollo de mercado o ventas (idealmente en servicios financieros o Fintech)Manejo de Excel y herramientas de gestión de bases de datos.Conocimientos en prospección digital e investigación de mercado.Familiaridad con plataformas CRM como Salesforce, HubSpot, entre otras.Disponibilidad para trabajar presencial en Las Condes.Beneficios¿Qué ofrecemos? 🎁Personal Days: Día libre por cumpleaños y mudanza.Más vacaciones: 3 días extra al año + 2 administrativos.2 Semanas de WFASeguro complementario.Convenio con Caja Los Andes.Cultura cercana y colaborativa: Sé parte de un equipo con propósito.Sobre nosotros 🌍En Cumplo, conectamos a empresas que buscan liquidez con personas dispuestas a invertir en sus proyectos. Nuestra misión es democratizar el financiamiento y apoyar el crecimiento de las pymes en Latinoamérica, promoviendo un ecosistema financiero más justo y transparente.Si compartes nuestra visión y deseas ser parte de este cambio, te invitamos a postular.💡 ¡Postula ahora y sé parte de la transformación financiera! 🚀</t>
+          <t>¡En CCU nos apasiona crear experiencias para compartir juntos un mejor vivir!Nos encontramos en búsqueda de unIngeniero/a de Planificación (Distribución)para desempeñarse en nuestra Planta Cervecera ubicada enQuilicura.Principales funciones:Gestionar indicadores operativos del área, diseñando herramientas de visualización y control para asegurar el cumplimiento de metas y desplegar acciones de mejora.Liderar iniciativas y proyectos de eficiencia en los procesos de distribución bajo metodología y políticas de la organización, promoviendo una operación sostenible.Monitorear los gastos y ahorros del área, identificando causas de desviaciones y generando alertas preventivas.Trabajar en conjunto con empresas de transporte y proveedores internos, para así monitorear y mejorar nivel de servicio esperado.Requisitos:Título de Ingeniería Civil, Comercial o carrera afín.0-6 meses de experiencia laboral.Manejo de Excel intermedio-avanzado.Deseable manejo de Looker Studio o Power BI.Deseable manejo de SQL o herramientas de programación.Disponibilidad para trabajar en modalidad 100% presencial en Quilicura.Nuestro SER CCU nos inspira a trabajar con aceptación y respeto a las diferencias de las personas, promoviendo un entorno diverso e integrador, para así contribuir a un mejor vivir. Por esto, te agradecemos que nos compartas si necesitas adaptación en alguna etapa del proceso de postulación.¡Te invitamos a SER CCU!</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ingenieroa de Planificación (Distribución) - Quilicura</t>
+          <t>Analista de Inventarios</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7716,20 +7716,20 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56242/ingeniero-a-de-planificacion-distribucion-quilicura</t>
+          <t>https://firstjob.me/oferta/56280/analista-de-inventarios</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>sql, excel, power bi, looker studio, looker</t>
+          <t>analisis, excel</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -7739,16 +7739,16 @@
         <v>0</v>
       </c>
       <c r="K108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
         <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>¡En CCU nos apasiona crear experiencias para compartir juntos un mejor vivir!Nos encontramos en búsqueda de unIngeniero/a de Planificación (Distribución)para desempeñarse en nuestra Planta Cervecera ubicada enQuilicura.Principales funciones:Gestionar indicadores operativos del área, diseñando herramientas de visualización y control para asegurar el cumplimiento de metas y desplegar acciones de mejora.Liderar iniciativas y proyectos de eficiencia en los procesos de distribución bajo metodología y políticas de la organización, promoviendo una operación sostenible.Monitorear los gastos y ahorros del área, identificando causas de desviaciones y generando alertas preventivas.Trabajar en conjunto con empresas de transporte y proveedores internos, para así monitorear y mejorar nivel de servicio esperado.Requisitos:Título de Ingeniería Civil, Comercial o carrera afín.0-6 meses de experiencia laboral.Manejo de Excel intermedio-avanzado.Deseable manejo de Looker Studio o Power BI.Deseable manejo de SQL o herramientas de programación.Disponibilidad para trabajar en modalidad 100% presencial en Quilicura.Nuestro SER CCU nos inspira a trabajar con aceptación y respeto a las diferencias de las personas, promoviendo un entorno diverso e integrador, para así contribuir a un mejor vivir. Por esto, te agradecemos que nos compartas si necesitas adaptación en alguna etapa del proceso de postulación.¡Te invitamos a SER CCU!</t>
+          <t>¡Buscamos a nuestro próximo Analista de Inventarios!Reconocida multinacional del rubro deconsumo masivose encuentra en la búsqueda de unAnalista de Inventariospara integrarse a su equipo. Si te apasiona la gestión de inventarios, el análisis de información y la optimización de procesos, ¡esta oportunidad es para ti!Desafío principal:Asegurar el correcto control y gestión de los inventarios de la compañía, generando información clave para la toma de decisiones y velando por el cumplimiento de los procedimientos y controles internos.Principales funciones:Liderar y supervisar inventarios generales.Realizar seguimiento y control de inventarios, diferencias, obsolescencias, tránsitos y regularizaciones.Supervisar solicitudes y recepción de mercadería, realizando movimientos y ajustes de inventario en SAP según corresponda.Generar reportes y estadísticas mensuales de inventarios.Coordinar y auditar procesos de destrucción de productos.Realizar auditorías de buenas prácticas de almacenamiento y asegurar el cumplimiento de controles internos.Coordinar inventarios con auditores internos y externos, asegurando la trazabilidad y respaldo de los controles establecidos.Buscamos:Experiencia en gestión y control de inventarios.Formación profesional relacionada con Administración, Logística, Contador Auditor, Ingeniería o carreras afines.Manejo de Excel nivel intermedio–avanzado.Conocimientos de SAP.Capacidad analítica y orientación al detalle.Habilidades de coordinación y seguimiento con distintas áreas.Disponibilidad para desempeñarse en modalidad de trabajo híbrida.BeneficiosModalidad híbrida de trabajoEarly fridayCelebraciones de eventos corporativos</t>
         </is>
       </c>
     </row>
@@ -7770,12 +7770,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Analista de Inventarios</t>
+          <t>Especialista Riesgo Financiero y Liquidez</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Tanner</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7790,15 +7790,15 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56280/analista-de-inventarios</t>
+          <t>https://firstjob.me/oferta/56277/especialista-riesgo-financiero-y-liquidez</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>analisis, excel</t>
+          <t>python, sql, analisis</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -7817,7 +7817,7 @@
         <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>¡Buscamos a nuestro próximo Analista de Inventarios!Reconocida multinacional del rubro deconsumo masivose encuentra en la búsqueda de unAnalista de Inventariospara integrarse a su equipo. Si te apasiona la gestión de inventarios, el análisis de información y la optimización de procesos, ¡esta oportunidad es para ti!Desafío principal:Asegurar el correcto control y gestión de los inventarios de la compañía, generando información clave para la toma de decisiones y velando por el cumplimiento de los procedimientos y controles internos.Principales funciones:Liderar y supervisar inventarios generales.Realizar seguimiento y control de inventarios, diferencias, obsolescencias, tránsitos y regularizaciones.Supervisar solicitudes y recepción de mercadería, realizando movimientos y ajustes de inventario en SAP según corresponda.Generar reportes y estadísticas mensuales de inventarios.Coordinar y auditar procesos de destrucción de productos.Realizar auditorías de buenas prácticas de almacenamiento y asegurar el cumplimiento de controles internos.Coordinar inventarios con auditores internos y externos, asegurando la trazabilidad y respaldo de los controles establecidos.Buscamos:Experiencia en gestión y control de inventarios.Formación profesional relacionada con Administración, Logística, Contador Auditor, Ingeniería o carreras afines.Manejo de Excel nivel intermedio–avanzado.Conocimientos de SAP.Capacidad analítica y orientación al detalle.Habilidades de coordinación y seguimiento con distintas áreas.Disponibilidad para desempeñarse en modalidad de trabajo híbrida.BeneficiosModalidad híbrida de trabajoEarly fridayCelebraciones de eventos corporativos</t>
+          <t>En Tanner estamos buscando Especialista de Riesgo Financiero y LiquidezSi te interesa el mundo financiero, disfrutas el análisis y quieres seguir desarrollándote en riesgos, esta oportunidad puede ser para ti.Buscamos incorporar a nuestro equipo deRiesgo Financieroa una persona que contribuya al análisis, cálculo y seguimiento de las métricas de riesgo de liquidez, apoyando una gestión financiera sólida y el cumplimiento de la normativa vigente.¿Cuáles serán tus principales desafíos?• Calcular y analizar métricas de liquidez internas y normativas.• Analizar movimientos del balance y explicar las principales variaciones de las métricas.• Realizar seguimiento de reportes normativos CMF (C46, C47 y C49).• Coordinar y revisar modelos asociados al cálculo de Riesgo de Liquidez.• Desarrollar y controlar indicadores de Alerta Temprana del Plan de Contingencia de Liquidez.• Participar en la revisión y actualización de políticas, procedimientos y guías de Riesgo de Liquidez.¿Qué buscamos?• Profesionales de Ingeniería Comercial, Ingeniería Civil Industrial o formación afín al ámbito financiero/económico.• Entre 1 y 3 años de experiencia profesional.• Conocimientos en finanzas cuantitativas, mercado de valores y análisis financiero.• Conocimientos de modelos matemáticos, estadísticos y econométricos.• Manejo de bases de datos y herramientas como SQL, R y/o Python.• Conocimientos de normativa bancaria, contabilidad financiera y cálculos de flujo de caja.• Capacidad analítica, orientación a resultados, adaptación y disposición para trabajar colaborativamente.¿Te interesa asumir nuevos desafíos y seguir desarrollando tu carrera en el mundo financiero?¡Postula y sé parte de Tanner!#SomosTanner #Tanner #OportunidadLaboral #RiesgoFinanciero #RiesgoDeLiquidez #Finanzas #EmpleosChile</t>
         </is>
       </c>
     </row>
@@ -7839,12 +7839,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Especialista Riesgo Financiero y Liquidez</t>
+          <t>Analista de Selección y Desarrollo</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tanner</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7859,15 +7859,15 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56277/especialista-riesgo-financiero-y-liquidez</t>
+          <t>https://firstjob.me/oferta/56275/analista-de-seleccion-y-desarrollo</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>python, sql, analisis</t>
+          <t>analisis, excel</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -7896,47 +7896,47 @@
       </c>
       <c r="Q110" t="inlineStr">
         <is>
-          <t>En Tanner estamos buscando Especialista de Riesgo Financiero y LiquidezSi te interesa el mundo financiero, disfrutas el análisis y quieres seguir desarrollándote en riesgos, esta oportunidad puede ser para ti.Buscamos incorporar a nuestro equipo deRiesgo Financieroa una persona que contribuya al análisis, cálculo y seguimiento de las métricas de riesgo de liquidez, apoyando una gestión financiera sólida y el cumplimiento de la normativa vigente.¿Cuáles serán tus principales desafíos?• Calcular y analizar métricas de liquidez internas y normativas.• Analizar movimientos del balance y explicar las principales variaciones de las métricas.• Realizar seguimiento de reportes normativos CMF (C46, C47 y C49).• Coordinar y revisar modelos asociados al cálculo de Riesgo de Liquidez.• Desarrollar y controlar indicadores de Alerta Temprana del Plan de Contingencia de Liquidez.• Participar en la revisión y actualización de políticas, procedimientos y guías de Riesgo de Liquidez.¿Qué buscamos?• Profesionales de Ingeniería Comercial, Ingeniería Civil Industrial o formación afín al ámbito financiero/económico.• Entre 1 y 3 años de experiencia profesional.• Conocimientos en finanzas cuantitativas, mercado de valores y análisis financiero.• Conocimientos de modelos matemáticos, estadísticos y econométricos.• Manejo de bases de datos y herramientas como SQL, R y/o Python.• Conocimientos de normativa bancaria, contabilidad financiera y cálculos de flujo de caja.• Capacidad analítica, orientación a resultados, adaptación y disposición para trabajar colaborativamente.¿Te interesa asumir nuevos desafíos y seguir desarrollando tu carrera en el mundo financiero?¡Postula y sé parte de Tanner!#SomosTanner #Tanner #OportunidadLaboral #RiesgoFinanciero #RiesgoDeLiquidez #Finanzas #EmpleosChile</t>
+          <t>Estamos buscando unAnalista de Selección y Desarrollo Organizacionalpara integrarse a una empresa líder del rubro consumo masivo. Buscamos una persona cercana, proactiva y con una fuerte orientación al cliente interno, que disfrute trabajando con personas y generando impacto en toda la experiencia del colaborador.¿Cuál será tu desafío?Serás responsable de acompañar distintos procesos de gestión de personas, participando activamente en:✅Reclutamiento y selección de personal para distintos cargos de la organización.✅ Coordinación y ejecución de procesos de onboarding.✅ Identificación y desarrollo de talento interno.✅ Seguimiento y análisis de indicadores de gestión del área.✅ Coordinación con líderes y clientes internos para detectar necesidades de personas y desarrollo.✅ Participación en iniciativas de capacitación, desempeño, clima y experiencia de los colaboradores de la empresa.✅ Visitas periódicas a distintas sucursales y locaciones de la empresa para mantener cercanía con los equipos.¿Qué buscamos?Título profesional afín al área de Recursos Humanos, Psicología, Ingeniería Comercial y/o similar.Al menos 2 años de experiencia en reclutamiento, selección y/o desarrollo organizacional.Manejo de Excel nivel intermedio (excluyente).Capacidad analítica para interpretar indicadores y generar propuestas de mejora.Excelente comunicación y habilidades de relacionamiento.Orientación al cliente interno y vocación de servicio.Capacidad de organización y seguimiento de múltiples procesos.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Analista de Selección y Desarrollo</t>
+          <t>Asistente legal - Gestor Hipotecario</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>BCP</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Lima, Perú</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56275/analista-de-seleccion-y-desarrollo</t>
+          <t>https://firstjob.me/oferta/56322/asistente-legal-gestor-hipotecario</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>analisis, excel</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -7946,10 +7946,10 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>Estamos buscando unAnalista de Selección y Desarrollo Organizacionalpara integrarse a una empresa líder del rubro consumo masivo. Buscamos una persona cercana, proactiva y con una fuerte orientación al cliente interno, que disfrute trabajando con personas y generando impacto en toda la experiencia del colaborador.¿Cuál será tu desafío?Serás responsable de acompañar distintos procesos de gestión de personas, participando activamente en:✅Reclutamiento y selección de personal para distintos cargos de la organización.✅ Coordinación y ejecución de procesos de onboarding.✅ Identificación y desarrollo de talento interno.✅ Seguimiento y análisis de indicadores de gestión del área.✅ Coordinación con líderes y clientes internos para detectar necesidades de personas y desarrollo.✅ Participación en iniciativas de capacitación, desempeño, clima y experiencia de los colaboradores de la empresa.✅ Visitas periódicas a distintas sucursales y locaciones de la empresa para mantener cercanía con los equipos.¿Qué buscamos?Título profesional afín al área de Recursos Humanos, Psicología, Ingeniería Comercial y/o similar.Al menos 2 años de experiencia en reclutamiento, selección y/o desarrollo organizacional.Manejo de Excel nivel intermedio (excluyente).Capacidad analítica para interpretar indicadores y generar propuestas de mejora.Excelente comunicación y habilidades de relacionamiento.Orientación al cliente interno y vocación de servicio.Capacidad de organización y seguimiento de múltiples procesos.</t>
+          <t>Buscamos a los que tienen ganas de transformar el país. A los que quieren llegar lejos. Por qué esto no es solo un trabajo. Esto es desafiarte en grande para impactar en grande. Esto es el BCP y te estamos buscando para que formes parte de nuestro equipo comoAsistente Legal - Gestor(a) Hipotecario.¿Cuál es el reto?Seguimiento del proceso de la fase inmobiliaria, coordinando con clientes y asesor de crédito hipotecario y siendo responsable de gestión post venta.¿Cómo impactarás en grande?Gestionar y coordinar el proceso de tasación del inmueble a hipotecarRevisión de documentos y subsanación de observaciones por parte del área legalCoordinación e instrucción para emisión de medio de pago y firma de escritura públicaSeguimiento y asesoría a clientes para levantamiento de observaciones.¿Qué necesitamos de ti?Perfil Diverso: Estudiante desde 7mo de la carrera de Derecho (Indispensable).Experiencias: 1 año de experiencia en funciones administrativas para áreas legales, notarias o inmobiliaria (Indispensable).Primordial el dominio: Excel a nivel intermedio (indispensable).Sede de trabajo: San Isidro¿Por qué unirte a nuestro equipo?Ser parte de la empresa #1 en Merco Talento 2025.Ingreso a planilla de BCP desde tu primer día.Acompañamiento de líderes expertos y referentes en la banca.Acceso a descuentos en productos financieros.Beneficios corporativos exclusivos por provincia para disfrutar con tu familia.Formarás parte de una cultura constante de reconocimientos.“Somos una organización comprometida con la igualdad de derechos y oportunidades. Nuestros procesos de selección se rigen bajo una política donde nuestras/os postulantes son consideradas/os sin importar su origen, género, raza o cualquier otra característica, condición o preferencia, promoviendo así una cultura de respeto mutuo.</t>
         </is>
       </c>
     </row>
@@ -7977,17 +7977,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Asistente legal - Gestor Hipotecario</t>
+          <t>Encargado de Bodega E-Commerce - PUDAHUEL</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>BCP</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Lima, Perú</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7997,7 +7997,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56322/asistente-legal-gestor-hipotecario</t>
+          <t>https://firstjob.me/oferta/56310/encargado-de-bodega-e-commerce-pudahuel</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>Buscamos a los que tienen ganas de transformar el país. A los que quieren llegar lejos. Por qué esto no es solo un trabajo. Esto es desafiarte en grande para impactar en grande. Esto es el BCP y te estamos buscando para que formes parte de nuestro equipo comoAsistente Legal - Gestor(a) Hipotecario.¿Cuál es el reto?Seguimiento del proceso de la fase inmobiliaria, coordinando con clientes y asesor de crédito hipotecario y siendo responsable de gestión post venta.¿Cómo impactarás en grande?Gestionar y coordinar el proceso de tasación del inmueble a hipotecarRevisión de documentos y subsanación de observaciones por parte del área legalCoordinación e instrucción para emisión de medio de pago y firma de escritura públicaSeguimiento y asesoría a clientes para levantamiento de observaciones.¿Qué necesitamos de ti?Perfil Diverso: Estudiante desde 7mo de la carrera de Derecho (Indispensable).Experiencias: 1 año de experiencia en funciones administrativas para áreas legales, notarias o inmobiliaria (Indispensable).Primordial el dominio: Excel a nivel intermedio (indispensable).Sede de trabajo: San Isidro¿Por qué unirte a nuestro equipo?Ser parte de la empresa #1 en Merco Talento 2025.Ingreso a planilla de BCP desde tu primer día.Acompañamiento de líderes expertos y referentes en la banca.Acceso a descuentos en productos financieros.Beneficios corporativos exclusivos por provincia para disfrutar con tu familia.Formarás parte de una cultura constante de reconocimientos.“Somos una organización comprometida con la igualdad de derechos y oportunidades. Nuestros procesos de selección se rigen bajo una política donde nuestras/os postulantes son consideradas/os sin importar su origen, género, raza o cualquier otra característica, condición o preferencia, promoviendo así una cultura de respeto mutuo.</t>
+          <t>Empresa líder en la comercialización de productos para la Gran Minería (Cadenas para la nieve, izaje y amarre de carga, EPP y seguridad vial) busca un profesional del área logística para hacerse cargo de la operación de bodega de su canal e-commerce. El foco del cargo es asegurar que cada pedido salga completo, bien embalado y dentro del plazo comprometido con el cliente.Principales funcionesRecepcionar, revisar y almacenar mercadería, verificando cantidades, códigos y estado de los productos.Preparar los pedidos del canal e-commerce (picking, packing y rotulado) cumpliendo los tiempos de despacho comprometidos.Emitir y controlar la documentación asociada: guías de despacho, notas de venta y respaldos de entrega.Coordinar retiros y despachos con couriers y transportistas, y hacer seguimiento hasta la entrega.Mantener el control de inventario del área: cuadraturas periódicas, control de diferencias y actualización de stock en el sistema.Velar por el orden, limpieza y seguridad de la bodega, aplicando los procedimientos internos y las normas de prevención de riesgos.Reportar indicadores de la operación (pedidos preparados, cumplimiento de plazos, quiebres de stock) a la jefatura.RequisitosFormación técnica o profesional en Logística, Administración o carrera afín.Experiencia mínima de 2 años en bodega, preparación de pedidos o despacho (deseable en e-commerce o retail).Manejo de sistemas ERP/WMS (deseable Softland) y Excel a nivel intermedio.Deseable: licencia de grúa horquilla vigente y conocimiento de productos de izaje o EPP.Proactividad, rigurosidad en el manejo de información y orientación al cliente.OfrecemosContrato directo con la empresa, con proyección de crecimiento.Jornada de lunes a viernes, de 08:00 a 17:00 hrs.Lugar de trabajo: Pudahuel.Incorporación a una empresa consolidada, en una línea de negocio en plena expansión.</t>
         </is>
       </c>
     </row>
@@ -8046,37 +8046,33 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Encargado de Bodega E-Commerce - PUDAHUEL</t>
+          <t>Asistentes Centro de Excelencia Auditoría - Puerto Montt</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>EY Chile</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Región de Los Lagos, Chile</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56310/encargado-de-bodega-e-commerce-pudahuel</t>
+          <t>https://firstjob.me/oferta/56320/asistentes-centro-de-excelencia-auditoria-puerto-montt</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>2</v>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>excel</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
         <v>0</v>
       </c>
@@ -8084,10 +8080,10 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
@@ -8103,7 +8099,7 @@
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>Empresa líder en la comercialización de productos para la Gran Minería (Cadenas para la nieve, izaje y amarre de carga, EPP y seguridad vial) busca un profesional del área logística para hacerse cargo de la operación de bodega de su canal e-commerce. El foco del cargo es asegurar que cada pedido salga completo, bien embalado y dentro del plazo comprometido con el cliente.Principales funcionesRecepcionar, revisar y almacenar mercadería, verificando cantidades, códigos y estado de los productos.Preparar los pedidos del canal e-commerce (picking, packing y rotulado) cumpliendo los tiempos de despacho comprometidos.Emitir y controlar la documentación asociada: guías de despacho, notas de venta y respaldos de entrega.Coordinar retiros y despachos con couriers y transportistas, y hacer seguimiento hasta la entrega.Mantener el control de inventario del área: cuadraturas periódicas, control de diferencias y actualización de stock en el sistema.Velar por el orden, limpieza y seguridad de la bodega, aplicando los procedimientos internos y las normas de prevención de riesgos.Reportar indicadores de la operación (pedidos preparados, cumplimiento de plazos, quiebres de stock) a la jefatura.RequisitosFormación técnica o profesional en Logística, Administración o carrera afín.Experiencia mínima de 2 años en bodega, preparación de pedidos o despacho (deseable en e-commerce o retail).Manejo de sistemas ERP/WMS (deseable Softland) y Excel a nivel intermedio.Deseable: licencia de grúa horquilla vigente y conocimiento de productos de izaje o EPP.Proactividad, rigurosidad en el manejo de información y orientación al cliente.OfrecemosContrato directo con la empresa, con proyección de crecimiento.Jornada de lunes a viernes, de 08:00 a 17:00 hrs.Lugar de trabajo: Pudahuel.Incorporación a una empresa consolidada, en una línea de negocio en plena expansión.</t>
+          <t>En EY Chile, Firma multinacional líder en Consultoría y Auditoría, reconocida como una de las 15 mejores empresas para trabajar en Chile según el ranking Great Place To Work, estamos en búsqueda de profesionales en su último año (4° o 5° año), recién egresados/as o titulados/as de la carrera de Contador Auditor, para integrarse como Asistentes en nuestro Centro de Excelencia de Auditoría a partir de octubre de 2026, en nuestraoficina de Puerto Montt.Funciones:Apoyar en la confección y revisión de informes de Estados financieros.Apoyar en la realización de inventarios en las dependencias de nuestros clientes.Tipo de contrato:Plazo fijo desde octubre hasta el 31 de marzo de 2027.Necesitamos personas proactivas, con clara orientación al logro de metas y objetivos, con excelentes relaciones interpersonales.EY cree en la igualdad de oportunidades. Independientemente del género, edad, raza, color, credo, orientación sexual y discapacidad, todos los candidatos calificados serán considerados en nuestros procesos.¡Te invitamos a nuestro gran equipo!BeneficiosTe ofrecemos adquirir experiencia en una empresa líder a nivel internacional, que ofrece oportunidades de hacer carrera y desarrollarse profesionalmente, además de un grato ambiente laboral.</t>
         </is>
       </c>
     </row>
@@ -8115,17 +8111,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Asistentes Centro de Excelencia Auditoría - Puerto Montt</t>
+          <t>Asistente de Auditoría</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>EY Chile</t>
+          <t>Forvis Mazars</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Región de Los Lagos, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8135,7 +8131,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56320/asistentes-centro-de-excelencia-auditoria-puerto-montt</t>
+          <t>https://firstjob.me/oferta/56303/asistente-de-auditoria</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -8168,7 +8164,7 @@
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>En EY Chile, Firma multinacional líder en Consultoría y Auditoría, reconocida como una de las 15 mejores empresas para trabajar en Chile según el ranking Great Place To Work, estamos en búsqueda de profesionales en su último año (4° o 5° año), recién egresados/as o titulados/as de la carrera de Contador Auditor, para integrarse como Asistentes en nuestro Centro de Excelencia de Auditoría a partir de octubre de 2026, en nuestraoficina de Puerto Montt.Funciones:Apoyar en la confección y revisión de informes de Estados financieros.Apoyar en la realización de inventarios en las dependencias de nuestros clientes.Tipo de contrato:Plazo fijo desde octubre hasta el 31 de marzo de 2027.Necesitamos personas proactivas, con clara orientación al logro de metas y objetivos, con excelentes relaciones interpersonales.EY cree en la igualdad de oportunidades. Independientemente del género, edad, raza, color, credo, orientación sexual y discapacidad, todos los candidatos calificados serán considerados en nuestros procesos.¡Te invitamos a nuestro gran equipo!BeneficiosTe ofrecemos adquirir experiencia en una empresa líder a nivel internacional, que ofrece oportunidades de hacer carrera y desarrollarse profesionalmente, además de un grato ambiente laboral.</t>
+          <t>Con nosotros tienes la oportunidad de pertenecer a una firma internacional con un importante potencial de crecimiento y un equipo de más de 40.000 profesionales altamente capacitados, que brinda servicios profesionales generando alto impacto en todos nuestros clientes en más de 100 países en los cinco continentes.Podrás formar parte de un equipo que valorará tus ideas, apoyará tus ambiciones y celebrará tus éxitos. En Forvis Mazars nos proponemos impulsar la colaboración y la flexibilidad, las diversas perspectivas de nuestros colaboradores y el progreso.Hoy buscamos un Asistente para el área de Auditoría.Tareas/ResponsabilidadesBrindar asesoría y soporte a las distintas áreas de la firma.Analizar, monitorear y optimizar procesos, que apoyen la toma de decisiones.Apoyo en informes de auditoría.Revisión de documentación.RequisitosContador Auditor hasta 2 años de experiencia laboral en firmas de auditoría externa, servicios profesionales o entornos regulados.Manejo de herramientas Microsoft Office.OfrecemosModalidad de trabajo híbrida.Seguro de salud y dental.Entorno joven, dinámico y altamente colaborativo.Oportunidades de aprendizaje continuo y desarrollo profesional en un área estratégica de la firma.Este cargo es compatible para personas con discapacidad, se enmarca en la ley 21.015, que incentiva la inclusión de personas con discapacidad al mundo laboral.</t>
         </is>
       </c>
     </row>
@@ -8180,17 +8176,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Asistente de Auditoría</t>
+          <t>Asistentes Centro de Excelencia Auditoría - Concepción</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Forvis Mazars</t>
+          <t>EY Chile</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Región del Biobío, Chile</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8200,7 +8196,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56303/asistente-de-auditoria</t>
+          <t>https://firstjob.me/oferta/56321/asistentes-centro-de-excelencia-auditoria-concepcion</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -8233,7 +8229,7 @@
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>Con nosotros tienes la oportunidad de pertenecer a una firma internacional con un importante potencial de crecimiento y un equipo de más de 40.000 profesionales altamente capacitados, que brinda servicios profesionales generando alto impacto en todos nuestros clientes en más de 100 países en los cinco continentes.Podrás formar parte de un equipo que valorará tus ideas, apoyará tus ambiciones y celebrará tus éxitos. En Forvis Mazars nos proponemos impulsar la colaboración y la flexibilidad, las diversas perspectivas de nuestros colaboradores y el progreso.Hoy buscamos un Asistente para el área de Auditoría.Tareas/ResponsabilidadesBrindar asesoría y soporte a las distintas áreas de la firma.Analizar, monitorear y optimizar procesos, que apoyen la toma de decisiones.Apoyo en informes de auditoría.Revisión de documentación.RequisitosContador Auditor hasta 2 años de experiencia laboral en firmas de auditoría externa, servicios profesionales o entornos regulados.Manejo de herramientas Microsoft Office.OfrecemosModalidad de trabajo híbrida.Seguro de salud y dental.Entorno joven, dinámico y altamente colaborativo.Oportunidades de aprendizaje continuo y desarrollo profesional en un área estratégica de la firma.Este cargo es compatible para personas con discapacidad, se enmarca en la ley 21.015, que incentiva la inclusión de personas con discapacidad al mundo laboral.</t>
+          <t>En EY Chile, Firma multinacional líder en Consultoría y Auditoría, reconocida como una de las 15 mejores empresas para trabajar en Chile según el ranking Great Place To Work, estamos en búsqueda de profesionales en su último año (4° o 5° año), recién egresados/as o titulados/as de la carrera de Contador Auditor, para integrarse como Asistentes en nuestro Centro de Excelencia de Auditoría a partir de octubre de 2026, en nuestraoficina de Concepción.Funciones:Apoyar en la confección y revisión de informes de Estados financieros.Apoyar en la realización de inventarios en las dependencias de nuestros clientes.Tipo de contrato:Plazo fijo desde octubre hasta el 31 de marzo de 2027.Necesitamos personas proactivas, con clara orientación al logro de metas y objetivos, con excelentes relaciones interpersonales.EY cree en la igualdad de oportunidades. Independientemente del género, edad, raza, color, credo, orientación sexual y discapacidad, todos los candidatos calificados serán considerados en nuestros procesos.¡Te invitamos a nuestro gran equipo!BeneficiosTe ofrecemos adquirir experiencia en una empresa líder a nivel internacional, que ofrece oportunidades de hacer carrera y desarrollarse profesionalmente, además de un grato ambiente laboral.</t>
         </is>
       </c>
     </row>
@@ -8245,17 +8241,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Asistentes Centro de Excelencia Auditoría - Concepción</t>
+          <t>Testing Engineering Consultant</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>EY Chile</t>
+          <t>Murex Chile</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Región del Biobío, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8265,15 +8261,19 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56321/asistentes-centro-de-excelencia-auditoria-concepcion</t>
+          <t>https://firstjob.me/oferta/56317/testing-engineering-consultant</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
-      </c>
-      <c r="H116" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>sql, analisis, informatica</t>
+        </is>
+      </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -8288,17 +8288,17 @@
         <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q116" t="inlineStr">
         <is>
-          <t>En EY Chile, Firma multinacional líder en Consultoría y Auditoría, reconocida como una de las 15 mejores empresas para trabajar en Chile según el ranking Great Place To Work, estamos en búsqueda de profesionales en su último año (4° o 5° año), recién egresados/as o titulados/as de la carrera de Contador Auditor, para integrarse como Asistentes en nuestro Centro de Excelencia de Auditoría a partir de octubre de 2026, en nuestraoficina de Concepción.Funciones:Apoyar en la confección y revisión de informes de Estados financieros.Apoyar en la realización de inventarios en las dependencias de nuestros clientes.Tipo de contrato:Plazo fijo desde octubre hasta el 31 de marzo de 2027.Necesitamos personas proactivas, con clara orientación al logro de metas y objetivos, con excelentes relaciones interpersonales.EY cree en la igualdad de oportunidades. Independientemente del género, edad, raza, color, credo, orientación sexual y discapacidad, todos los candidatos calificados serán considerados en nuestros procesos.¡Te invitamos a nuestro gran equipo!BeneficiosTe ofrecemos adquirir experiencia en una empresa líder a nivel internacional, que ofrece oportunidades de hacer carrera y desarrollarse profesionalmente, además de un grato ambiente laboral.</t>
+          <t>Quiénes somosMurex es un líder global en fintech especializado en soluciones de trading, gestión de riesgo y procesamiento para mercados de capitales. Con presencia en 19 oficinas y más de 3.500 colaboradores de más de 60 nacionalidades, desarrollamos, implementamos y damos soporte a una de las plataformas más utilizadas por bancos, asset managers, corporaciones y utilities a nivel mundial.Únete a Murex y trabaja en los desafíos de una industria a la vanguardia de la innovación, en un entorno centrado en las personas.Serás parte de un equipo global donde podrás aprender rápidamente y desarrollarte profesionalmente ✨🔎 Qué harásComoTest Engineerapoyarás al equipo en la ejecución de la metodología de testing de Murex dentro de distintos proyectos, adquiriendo experiencia práctica en aseguramiento de calidad en entornos tecnológicos y financieros.Responsabilidades:Ejecución de pruebas:Apoyar en la definición, diseño y ejecución de casos de prueba, asegurando la calidad de las soluciones implementadas.Coordinación de actividades de testing:Colaborar en la organización y seguimiento de actividades de testing dentro de proyectos.Análisis de requerimientos:Apoyar en el entendimiento de requerimientos funcionales para diseñar estrategias y planes de prueba.Gestión de calidad:Contribuir a la identificación de riesgos y validación de cobertura de pruebas.Automatización (deseable):Apoyar en la identificación de oportunidades de automatización de pruebas y uso de herramientas.Seguimiento y reporting:Colaborar en el seguimiento de campañas de testing, documentando avances y resultados.Capacitación y aprendizaje:Participar en entrenamientos internos y programas de transferencia de conocimiento en herramientas y metodología Murex.Trabajo en equipo:Apoyar a ingenieros y consultores más senior, contribuyendo a un ambiente colaborativo.🌟 Quién eres🎓 Formación académica:Titulado de Ingeniería Civil Informática, Ingeniería Civil Industrial, Ingeniería en Computación o carrera afín.💻 Conocimientos técnicos: Nociones en entornos tecnológicos como SQL, XML, Unix o Windows.👨‍💻 Programación: Conocimientos básicos en Java o C/C++ (deseable).🧩 Habilidades analíticas: Pensamiento lógico, capacidad analítica y orientación a la resolución de problemas.🗣️ Comunicación: Buenas habilidades comunicacionales y nivel de inglés intermedio/avanzado.🤝 Trabajo en equipo: Capacidad de colaboración y comunicación con equipos multidisciplinarios.🚀 Actitud: Proactividad, atención al detalle, orientación a la calidad y ganas de aprender.</t>
         </is>
       </c>
     </row>
@@ -8310,64 +8310,64 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Testing Engineering Consultant</t>
+          <t>Ingeniero en Control de Gestión (Balance Score Card, Gerencia de Planificación y Control)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Murex Chile</t>
+          <t>AFP Modelo</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Avda de valle 614 Huechuraba, Chile, Chile</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56317/testing-engineering-consultant</t>
+          <t>https://firstjob.me/oferta/56306/ingeniero-en-control-de-gestion-balance-score-card-gerencia-de-planificacion-y-control</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>sql, analisis, informatica</t>
+          <t>python, sql, analisis, power bi</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
       </c>
       <c r="K117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M117" t="n">
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
       </c>
       <c r="P117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>Quiénes somosMurex es un líder global en fintech especializado en soluciones de trading, gestión de riesgo y procesamiento para mercados de capitales. Con presencia en 19 oficinas y más de 3.500 colaboradores de más de 60 nacionalidades, desarrollamos, implementamos y damos soporte a una de las plataformas más utilizadas por bancos, asset managers, corporaciones y utilities a nivel mundial.Únete a Murex y trabaja en los desafíos de una industria a la vanguardia de la innovación, en un entorno centrado en las personas.Serás parte de un equipo global donde podrás aprender rápidamente y desarrollarte profesionalmente ✨🔎 Qué harásComoTest Engineerapoyarás al equipo en la ejecución de la metodología de testing de Murex dentro de distintos proyectos, adquiriendo experiencia práctica en aseguramiento de calidad en entornos tecnológicos y financieros.Responsabilidades:Ejecución de pruebas:Apoyar en la definición, diseño y ejecución de casos de prueba, asegurando la calidad de las soluciones implementadas.Coordinación de actividades de testing:Colaborar en la organización y seguimiento de actividades de testing dentro de proyectos.Análisis de requerimientos:Apoyar en el entendimiento de requerimientos funcionales para diseñar estrategias y planes de prueba.Gestión de calidad:Contribuir a la identificación de riesgos y validación de cobertura de pruebas.Automatización (deseable):Apoyar en la identificación de oportunidades de automatización de pruebas y uso de herramientas.Seguimiento y reporting:Colaborar en el seguimiento de campañas de testing, documentando avances y resultados.Capacitación y aprendizaje:Participar en entrenamientos internos y programas de transferencia de conocimiento en herramientas y metodología Murex.Trabajo en equipo:Apoyar a ingenieros y consultores más senior, contribuyendo a un ambiente colaborativo.🌟 Quién eres🎓 Formación académica:Titulado de Ingeniería Civil Informática, Ingeniería Civil Industrial, Ingeniería en Computación o carrera afín.💻 Conocimientos técnicos: Nociones en entornos tecnológicos como SQL, XML, Unix o Windows.👨‍💻 Programación: Conocimientos básicos en Java o C/C++ (deseable).🧩 Habilidades analíticas: Pensamiento lógico, capacidad analítica y orientación a la resolución de problemas.🗣️ Comunicación: Buenas habilidades comunicacionales y nivel de inglés intermedio/avanzado.🤝 Trabajo en equipo: Capacidad de colaboración y comunicación con equipos multidisciplinarios.🚀 Actitud: Proactividad, atención al detalle, orientación a la calidad y ganas de aprender.</t>
+          <t>El objetivo del cargo es procesar, analizar y generar reportes de información de indicadores de gestión de las distintas áreas, de acuerdo a objetivos estratégicos, protocolos y normativas vigentes relacionadas al rubro. Lo anterior para controlar, analizar y reportar desviaciones en los resultados de indicadores de gestión instaurados dentro de la definición estratégica y de metas organizacionales establecidas.Requisitos:Formación académica: Ingeniería en control de gestión o civil industrial con foco en análisis de datos.Conocimiento Técnico; Manejo de Herramientas de BBDD, Power BI, SQL server (deseable nivel intermedio-avanzado)Control y Gestión de Procesos. Data storytelling (deseable).Python (deseable intermedio).Aplicación de I.A para procesos afines.Experiencia (mínima): 1 año de experiencia en cargos similares</t>
         </is>
       </c>
     </row>
@@ -8379,17 +8379,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ingeniero en Control de Gestión (Balance Score Card, Gerencia de Planificación y Control)</t>
+          <t>HR Specialist - Fresh Graduate</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AFP Modelo</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Avda de valle 614 Huechuraba, Chile, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8399,19 +8399,15 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56306/ingeniero-en-control-de-gestion-balance-score-card-gerencia-de-planificacion-y-control</t>
+          <t>https://firstjob.me/oferta/56299/hr-specialist-fresh-graduate</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>9</v>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>python, sql, analisis, power bi</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -8436,7 +8432,7 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>El objetivo del cargo es procesar, analizar y generar reportes de información de indicadores de gestión de las distintas áreas, de acuerdo a objetivos estratégicos, protocolos y normativas vigentes relacionadas al rubro. Lo anterior para controlar, analizar y reportar desviaciones en los resultados de indicadores de gestión instaurados dentro de la definición estratégica y de metas organizacionales establecidas.Requisitos:Formación académica: Ingeniería en control de gestión o civil industrial con foco en análisis de datos.Conocimiento Técnico; Manejo de Herramientas de BBDD, Power BI, SQL server (deseable nivel intermedio-avanzado)Control y Gestión de Procesos. Data storytelling (deseable).Python (deseable intermedio).Aplicación de I.A para procesos afines.Experiencia (mínima): 1 año de experiencia en cargos similares</t>
+          <t>EnHuawei Chilenos encontramos en búsqueda de unHR Specialist – Fresh Graduatepara incorporarse a nuestro equipo en Santiago, Chile.Buscamos un/a profesional recién egresado/a, altamente motivado/a por desarrollar una carrera a largo plazo en el área deRecursos Humanos, dentro de una compañía global de tecnología.Serás responsable de apoyar diversas actividades y procesos deRecursos Humanos, trabajando de manera cercana con los equipos de negocio y con los equipos de HR locales y regionales. Esta posición permitirá adquirir experiencia en distintos procesos de HR, gestión de colaboradores, operaciones y soporte al negocio.Serás responsable de:Apoyar las actividades y procesos de Recursos Humanos del día a día.Trabajar en conjunto con los equipos de negocio para comprender sus necesidades y entregar el soporte adecuado.Apoyar la implementación de políticas, procesos e iniciativas de HR.Participar en procesos relacionados con los colaboradores a lo largo de su ciclo de vida.Apoyar en reportes, gestión documental y administración de información de HR.Colaborar con equipos de HR locales y regionales en distintos proyectos e iniciativas.Entregar soporte a colaboradores y managers respecto de procesos y políticas de Recursos Humanos.¿Qué buscamos en ti?Título profesional enRecursos Humanos, Administración de Empresas, Psicología o carrera afín.Titulación durante2025 o 2026.Entre0 y 2 años de experiencia profesional.Recién egresados/as son bienvenidos/as a postular.Alto interés por desarrollar una carrera en el área de Recursos Humanos.Excelentes habilidades de organización, comunicación y relacionamiento interpersonal.Dominio avanzado de inglés, tanto oral como escrito.Experiencia previa en la industria de telecomunicaciones o tecnología será valorada, perono es excluyente.</t>
         </is>
       </c>
     </row>
@@ -8448,12 +8444,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>HR Specialist - Fresh Graduate</t>
+          <t>Operador de Traslados AM</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>Achs Servicios</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -8468,7 +8464,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/56299/hr-specialist-fresh-graduate</t>
+          <t>https://firstjob.me/oferta/55530/operador-de-traslados-am</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -8476,7 +8472,7 @@
       </c>
       <c r="H119" t="inlineStr"/>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -8501,7 +8497,7 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>EnHuawei Chilenos encontramos en búsqueda de unHR Specialist – Fresh Graduatepara incorporarse a nuestro equipo en Santiago, Chile.Buscamos un/a profesional recién egresado/a, altamente motivado/a por desarrollar una carrera a largo plazo en el área deRecursos Humanos, dentro de una compañía global de tecnología.Serás responsable de apoyar diversas actividades y procesos deRecursos Humanos, trabajando de manera cercana con los equipos de negocio y con los equipos de HR locales y regionales. Esta posición permitirá adquirir experiencia en distintos procesos de HR, gestión de colaboradores, operaciones y soporte al negocio.Serás responsable de:Apoyar las actividades y procesos de Recursos Humanos del día a día.Trabajar en conjunto con los equipos de negocio para comprender sus necesidades y entregar el soporte adecuado.Apoyar la implementación de políticas, procesos e iniciativas de HR.Participar en procesos relacionados con los colaboradores a lo largo de su ciclo de vida.Apoyar en reportes, gestión documental y administración de información de HR.Colaborar con equipos de HR locales y regionales en distintos proyectos e iniciativas.Entregar soporte a colaboradores y managers respecto de procesos y políticas de Recursos Humanos.¿Qué buscamos en ti?Título profesional enRecursos Humanos, Administración de Empresas, Psicología o carrera afín.Titulación durante2025 o 2026.Entre0 y 2 años de experiencia profesional.Recién egresados/as son bienvenidos/as a postular.Alto interés por desarrollar una carrera en el área de Recursos Humanos.Excelentes habilidades de organización, comunicación y relacionamiento interpersonal.Dominio avanzado de inglés, tanto oral como escrito.Experiencia previa en la industria de telecomunicaciones o tecnología será valorada, perono es excluyente.</t>
+          <t>¡En Achs Servicios te estamos buscando!Somos una Empresa de servicios, que cuenta con el respaldo y trayectoria de la mutualidad líder en Chile. Nuestra misión es entregar confianza, seguridad y cercanía a nuestros colaboradores, pacientes y comunidades. Con un servicio de excelencia y permanente innovación.Queremos que seas nuestro/a próximo/a Operador de Traslados, para trabajar en la Región Metropolitana en jornada de 04:00 a 13:00 horasEl objetivo principal del cargo es monitorear y coordinar la gestión de los traslados de todos los pacientes.Requisitos para ser el candidato ideal:Título técnico nivel superior en Administración, Logística y/o carrera afínExperiencia en áreas logísticas y/o administrativas al menos 2 añosManejo computacionalServicio al clienteIdealmente experiencia en coordinación de transporte.¡Anímate! ¡Y postula con nosotros!</t>
         </is>
       </c>
     </row>
@@ -8513,17 +8509,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Operador de Traslados AM</t>
+          <t>Client Service Associate</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Achs Servicios</t>
+          <t>Dialectica Colombia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Cundinamarca, Colombia</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8533,7 +8529,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55530/operador-de-traslados-am</t>
+          <t>https://firstjob.me/oferta/55509/client-service-associate</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -8541,7 +8537,7 @@
       </c>
       <c r="H120" t="inlineStr"/>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -8566,7 +8562,7 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>¡En Achs Servicios te estamos buscando!Somos una Empresa de servicios, que cuenta con el respaldo y trayectoria de la mutualidad líder en Chile. Nuestra misión es entregar confianza, seguridad y cercanía a nuestros colaboradores, pacientes y comunidades. Con un servicio de excelencia y permanente innovación.Queremos que seas nuestro/a próximo/a Operador de Traslados, para trabajar en la Región Metropolitana en jornada de 04:00 a 13:00 horasEl objetivo principal del cargo es monitorear y coordinar la gestión de los traslados de todos los pacientes.Requisitos para ser el candidato ideal:Título técnico nivel superior en Administración, Logística y/o carrera afínExperiencia en áreas logísticas y/o administrativas al menos 2 añosManejo computacionalServicio al clienteIdealmente experiencia en coordinación de transporte.¡Anímate! ¡Y postula con nosotros!</t>
+          <t>Acerca del puestoComo asociado/a del equipo de atención al cliente, actuarás como enlace entre nuestros clientes y expertos del sector. Tu función será colaborar con ellos para comprender sus lagunas de conocimiento e identificar a los expertos con la experiencia y los conocimientos más relevantes para abordarlas. Un día podrías conectar a una firma de capital privado con expertos para comprender mejor el mercado de las telecomunicaciones en el África subsahariana, y al día siguiente asesorar a una consultora estratégica que analiza las perspectivas de crecimiento de la energía solar en Oriente Medio.Deberás pensar de forma crítica y rápida, realizar investigaciones exhaustivas sobre sectores y empresas, e identificar a los mejores expertos, asegurándote de que cuenten con la experiencia y el conocimiento más relevantes para responder a las preguntas de nuestros clientes. Dedicarás una cantidad considerable de tiempo a contactar con posibles expertos por teléfono y correo electrónico para evaluar su experiencia y conocimientos, antes de ponerlos en contacto con nuestros clientes. Al trabajar en varios proyectos de clientes simultáneamente, desarrollarás rápidamente habilidades clave en ventas, gestión del tiempo y priorización, negociación y comunicación profesional.Sus principales responsabilidades incluirán:Revisar los informes de proyectos de los clientes para comprender sus lagunas de conocimiento y realizar investigaciones de alto nivel sobre la industria y la empresa para identificar a los expertos más relevantes.Utilizar el teléfono, LinkedIn y el correo electrónico para contactar con expertos.Evaluación crítica de expertos para determinar su idoneidad y relevancia para satisfacer las necesidades del cliente, con énfasis en la calidad.El equipo de atención al clienteEl equipo de Atención al Cliente es el principal motor de ingresos de nuestro negocio. Una carrera en el equipo de Atención al Cliente de Dialectica es mucho más que un simple trabajo; es una oportunidad para impulsar tu carrera profesional, acceder a una remuneración competitiva basada en el rendimiento y desarrollar habilidades clave en diversas áreas como ventas, comunicación profesional, gestión de relaciones con clientes, gestión de proyectos, gestión de cuentas y gestión de personal. El esfuerzo, la motivación y el compromiso con la creación de valor te permitirán ascender rápidamente a Gerente.RequisitosNuestro futuro miembro del equipo de Dialectica tiene:0 - 2 años de experiencia laboralLogros académicos obtenidos en cualquier campo de pregrado (licenciatura o superior).Es imprescindible tener fluidez en inglés, tanto oral como escrita.Participación en actividades extracurriculares con historial comprobado de liderazgo.Gran interés y pasión por el mundo empresarial.Una mentalidad de desarrollo que considera los contratiempos y los desafíos a corto plazo como oportunidades de aprendizaje para el crecimiento.Una mentalidad de servicio al cliente, lo que significa que estás comprometido a ir más alláBeneficiosPaquete de compensación competitivoSeguro médico y de vida privadoOportunidades de aprendizaje y desarrolloProgramas de recompensa y reconocimientoEventos de integración de equipos patrocinados por la empresaActividades semanales de salud y bienestar (por ejemplo, baloncesto, fútbol, ​​yoga, correr).Aperitivos y bebidas gratis¡Cultura emprendedora y compañeros de trabajo increíbles!</t>
         </is>
       </c>
     </row>
@@ -8578,27 +8574,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Client Service Associate</t>
+          <t>Asistente de Calidad, Riesgos y Cumplimiento - Forvis Mazars</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dialectica Colombia</t>
+          <t>Forvis Mazars</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Cundinamarca, Colombia</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55509/client-service-associate</t>
+          <t>https://firstjob.me/oferta/55499/asistente-de-calidad-riesgos-y-cumplimiento-forvis-mazars</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -8606,16 +8602,16 @@
       </c>
       <c r="H121" t="inlineStr"/>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
@@ -8631,7 +8627,7 @@
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>Acerca del puestoComo asociado/a del equipo de atención al cliente, actuarás como enlace entre nuestros clientes y expertos del sector. Tu función será colaborar con ellos para comprender sus lagunas de conocimiento e identificar a los expertos con la experiencia y los conocimientos más relevantes para abordarlas. Un día podrías conectar a una firma de capital privado con expertos para comprender mejor el mercado de las telecomunicaciones en el África subsahariana, y al día siguiente asesorar a una consultora estratégica que analiza las perspectivas de crecimiento de la energía solar en Oriente Medio.Deberás pensar de forma crítica y rápida, realizar investigaciones exhaustivas sobre sectores y empresas, e identificar a los mejores expertos, asegurándote de que cuenten con la experiencia y el conocimiento más relevantes para responder a las preguntas de nuestros clientes. Dedicarás una cantidad considerable de tiempo a contactar con posibles expertos por teléfono y correo electrónico para evaluar su experiencia y conocimientos, antes de ponerlos en contacto con nuestros clientes. Al trabajar en varios proyectos de clientes simultáneamente, desarrollarás rápidamente habilidades clave en ventas, gestión del tiempo y priorización, negociación y comunicación profesional.Sus principales responsabilidades incluirán:Revisar los informes de proyectos de los clientes para comprender sus lagunas de conocimiento y realizar investigaciones de alto nivel sobre la industria y la empresa para identificar a los expertos más relevantes.Utilizar el teléfono, LinkedIn y el correo electrónico para contactar con expertos.Evaluación crítica de expertos para determinar su idoneidad y relevancia para satisfacer las necesidades del cliente, con énfasis en la calidad.El equipo de atención al clienteEl equipo de Atención al Cliente es el principal motor de ingresos de nuestro negocio. Una carrera en el equipo de Atención al Cliente de Dialectica es mucho más que un simple trabajo; es una oportunidad para impulsar tu carrera profesional, acceder a una remuneración competitiva basada en el rendimiento y desarrollar habilidades clave en diversas áreas como ventas, comunicación profesional, gestión de relaciones con clientes, gestión de proyectos, gestión de cuentas y gestión de personal. El esfuerzo, la motivación y el compromiso con la creación de valor te permitirán ascender rápidamente a Gerente.RequisitosNuestro futuro miembro del equipo de Dialectica tiene:0 - 2 años de experiencia laboralLogros académicos obtenidos en cualquier campo de pregrado (licenciatura o superior).Es imprescindible tener fluidez en inglés, tanto oral como escrita.Participación en actividades extracurriculares con historial comprobado de liderazgo.Gran interés y pasión por el mundo empresarial.Una mentalidad de desarrollo que considera los contratiempos y los desafíos a corto plazo como oportunidades de aprendizaje para el crecimiento.Una mentalidad de servicio al cliente, lo que significa que estás comprometido a ir más alláBeneficiosPaquete de compensación competitivoSeguro médico y de vida privadoOportunidades de aprendizaje y desarrolloProgramas de recompensa y reconocimientoEventos de integración de equipos patrocinados por la empresaActividades semanales de salud y bienestar (por ejemplo, baloncesto, fútbol, ​​yoga, correr).Aperitivos y bebidas gratis¡Cultura emprendedora y compañeros de trabajo increíbles!</t>
+          <t>Con nosotros tienes la oportunidad de pertenecer a una firma internacional con un equipo de más de 40.000 profesionales altamente capacitados, que brinda servicios profesionales generando alto impacto en todos nuestros clientes en más de 100 países en los cinco continentes.Podrás formar parte de un equipo que valorará tus ideas, apoyará tus ambiciones y celebrará tus éxitos. En Forvis Mazars nos proponemos impulsar la colaboración y la flexibilidad, las diversas perspectivas de nuestros colaboradores y el progreso.Hoy buscamos un Asistente para el área deCalidad, Riesgos y Cumplimiento.Este rol es clave para apoyar el logro de los objetivos del área, especialmente en materias de cumplimiento normativo, ambiente regulatorio de la industria, medidas de control y mejora continua de procesos y procedimientos internos.Tareas/ResponsabilidadesApoyar la implementación, mantención y mejora continua del Programa de Calidad, Riesgos y Cumplimiento.Brindar asesoría y soporte a las distintas áreas de la firma.Analizar, monitorear y optimizar procesos, que apoyen la toma de decisiones.Fortalecer la cultura de riesgos, cumplimiento organizacional.RequisitosContador Auditorhasta 2 años de experiencia laboralen firmas de auditoría externa, servicios profesionales o entornos regulados.Experiencia en gestión de riesgos, cumplimiento normativo, legal, privacidad de información o áreas afines.Deseable conocimiento de normativa regulatoria o marcos globales de compliance.Este cargo es compatible para personas con discapacidad, se enmarca en la ley 21.015, que incentiva la inclusión de personas con discapacidad al mundo laboral.BeneficiosOfrecemosModalidad de trabajo híbrida.Seguro de salud y dental.Entorno joven, dinámico y altamente colaborativo.Oportunidades de aprendizaje continuo y desarrollo profesional en un área estratégica de la firma.</t>
         </is>
       </c>
     </row>
@@ -8643,12 +8639,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Asistente de Calidad, Riesgos y Cumplimiento - Forvis Mazars</t>
+          <t>PAC (Productions Architect Consultant)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Forvis Mazars</t>
+          <t>Murex Chile</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -8663,15 +8659,19 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55499/asistente-de-calidad-riesgos-y-cumplimiento-forvis-mazars</t>
+          <t>https://firstjob.me/oferta/55487/pac-productions-architect-consultant</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
-      </c>
-      <c r="H122" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>python, sql, analisis, cloud, git, javascript</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>Con nosotros tienes la oportunidad de pertenecer a una firma internacional con un equipo de más de 40.000 profesionales altamente capacitados, que brinda servicios profesionales generando alto impacto en todos nuestros clientes en más de 100 países en los cinco continentes.Podrás formar parte de un equipo que valorará tus ideas, apoyará tus ambiciones y celebrará tus éxitos. En Forvis Mazars nos proponemos impulsar la colaboración y la flexibilidad, las diversas perspectivas de nuestros colaboradores y el progreso.Hoy buscamos un Asistente para el área deCalidad, Riesgos y Cumplimiento.Este rol es clave para apoyar el logro de los objetivos del área, especialmente en materias de cumplimiento normativo, ambiente regulatorio de la industria, medidas de control y mejora continua de procesos y procedimientos internos.Tareas/ResponsabilidadesApoyar la implementación, mantención y mejora continua del Programa de Calidad, Riesgos y Cumplimiento.Brindar asesoría y soporte a las distintas áreas de la firma.Analizar, monitorear y optimizar procesos, que apoyen la toma de decisiones.Fortalecer la cultura de riesgos, cumplimiento organizacional.RequisitosContador Auditorhasta 2 años de experiencia laboralen firmas de auditoría externa, servicios profesionales o entornos regulados.Experiencia en gestión de riesgos, cumplimiento normativo, legal, privacidad de información o áreas afines.Deseable conocimiento de normativa regulatoria o marcos globales de compliance.Este cargo es compatible para personas con discapacidad, se enmarca en la ley 21.015, que incentiva la inclusión de personas con discapacidad al mundo laboral.BeneficiosOfrecemosModalidad de trabajo híbrida.Seguro de salud y dental.Entorno joven, dinámico y altamente colaborativo.Oportunidades de aprendizaje continuo y desarrollo profesional en un área estratégica de la firma.</t>
+          <t>Quiénes somosMurex es un líder global en fintech especializado en soluciones de trading, gestión de riesgo y procesamiento para mercados de capitales. Con presencia en 19 oficinas y más de 3.500 colaboradores de más de 60 nacionalidades, desarrollamos, implementamos y damos soporte a una de las plataformas más utilizadas por bancos, asset managers, corporaciones y utilities a nivel mundial.Únete a Murex y trabaja en los desafíos de una industria a la vanguardia de la innovación, en un entorno centrado en las personas.Serás parte de un equipo global donde podrás aprender rápidamente y desarrollarte profesionalmente ✨💻 Qué harásFormarás parte de un equipo global donde podrás aprender rápidamente y mantenerte fiel a ti mismo.Las personas son nuestro activo más importante. Para apoyar las necesidades del mercado, tenemos una oportunidad para que profesionales talentosos se unan a nuestro equipo deProduction and Architecture Consulting (PAC)con base en Chile comoConsultores de Producción y Arquitectura.Esta persona será responsable de proporcionarsoporte técnico, apoyo en implementaciones, pruebas y medición de rendimiento (benchmarks), consultoría de infraestructura y arquitectura, así como capacitacióna nuestros clientes y equipos.Responsabilidades principales de este rol:Diseñar y apoyar el despliegue de las soluciones de nuestros clientes en infraestructuras de producción (tantoon-premisecomo en la nube), adaptándolas a su ámbito de actividad.Proporcionar soporte técnico diario para garantizar la satisfacción técnica de los clientes de Murex.Desarrollar y ejecutar pruebas de rendimiento (performance testing) para asegurar el mejor desempeño de las aplicaciones.Utilizar herramientas estándar de monitoreo y análisis de rendimiento para identificar cuellos de botella, proponiendo y construyendo soluciones en colaboración con el equipo de desarrollo de producto cuando sea necesario.Impartir capacitaciones técnicas y de arquitectura a los clientes de Murex, con el fin de fortalecer sus capacidades de soporte.Desarrollar experiencia en distintas áreas técnicas, incluyendo sistemas operativos, diseño e implementación de aplicaciones, infraestructura de hardware y nube, redes y servidores de bases de datos.🌟 Quién eres🎓 Formación académicaBuscamos un experto técnico apasionado y con potencial de crecimiento para unirse a nuestro equipo en Chile:Título de Licenciatura o Magíster en Ciencias de la Computación, Ingeniería, Matemáticas o carreras afines,Experiencia: entre 0 y 2 años  en áreas relacionadas.Conocimientos en scripting conUnix Shell, Java, C/C++, SQL/RDBMS y Python.Se valorarán conocimientos en las siguientes tecnologías y conceptos: soluciones en la nube (Cloud Solutions) y arquitecturas multinivel (Multitier Architecture).Se considerará una ventaja contar con conocimientos en XML/XSLT, JSON, Terraform, Ansible, Perl, expresiones regulares (Regex), JavaScript, Java JDK/JRE y Git/BitBucket.Sólidas habilidades de programación y resolución de problemas, con orientación al cliente y una fuerte motivación por alcanzar la excelencia.Dominio avanzado del inglés(oral, escrito y lectura) es indispensable, junto con excelentes habilidades de comunicación.Beneficios🌍 Por qué unirte a nosotrosSer parte de una empresa líder con más de 35 años en una industria dinámica.Formar parte de un equipo inclusivo y centrado en las personas.Aprender en un entorno internacional y altamente colaborativo.Desarrollarte en tecnologías de integración, sistemas financieros y soluciones fintech.Oportunidades de crecimiento profesional y posible continuidad en la compañía.🌈 Diversidad e inclusiónEn Murex creemos en la igualdad de oportunidades para todos los colaboradores y postulantes. No se permite ningún tipo de discriminación o acoso por motivos de raza, género, religión, orientación sexual, discapacidad u otras características protegidas por la ley.Nuestro compromiso con la equidad e inclusión es parte fundamental de nuestra cultura.</t>
         </is>
       </c>
     </row>
@@ -8708,17 +8708,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PAC (Productions Architect Consultant)</t>
+          <t>Operador de Traslados Coordinación Operativa Providencia 5X2</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Murex Chile</t>
+          <t>Achs Servicios</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Providencia, Chile</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -8728,19 +8728,15 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55487/pac-productions-architect-consultant</t>
+          <t>https://firstjob.me/oferta/55531/operador-de-traslados-coordinacion-operativa-providencia-5x2</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>13</v>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>python, sql, analisis, cloud, git, javascript</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -8765,7 +8761,7 @@
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>Quiénes somosMurex es un líder global en fintech especializado en soluciones de trading, gestión de riesgo y procesamiento para mercados de capitales. Con presencia en 19 oficinas y más de 3.500 colaboradores de más de 60 nacionalidades, desarrollamos, implementamos y damos soporte a una de las plataformas más utilizadas por bancos, asset managers, corporaciones y utilities a nivel mundial.Únete a Murex y trabaja en los desafíos de una industria a la vanguardia de la innovación, en un entorno centrado en las personas.Serás parte de un equipo global donde podrás aprender rápidamente y desarrollarte profesionalmente ✨💻 Qué harásFormarás parte de un equipo global donde podrás aprender rápidamente y mantenerte fiel a ti mismo.Las personas son nuestro activo más importante. Para apoyar las necesidades del mercado, tenemos una oportunidad para que profesionales talentosos se unan a nuestro equipo deProduction and Architecture Consulting (PAC)con base en Chile comoConsultores de Producción y Arquitectura.Esta persona será responsable de proporcionarsoporte técnico, apoyo en implementaciones, pruebas y medición de rendimiento (benchmarks), consultoría de infraestructura y arquitectura, así como capacitacióna nuestros clientes y equipos.Responsabilidades principales de este rol:Diseñar y apoyar el despliegue de las soluciones de nuestros clientes en infraestructuras de producción (tantoon-premisecomo en la nube), adaptándolas a su ámbito de actividad.Proporcionar soporte técnico diario para garantizar la satisfacción técnica de los clientes de Murex.Desarrollar y ejecutar pruebas de rendimiento (performance testing) para asegurar el mejor desempeño de las aplicaciones.Utilizar herramientas estándar de monitoreo y análisis de rendimiento para identificar cuellos de botella, proponiendo y construyendo soluciones en colaboración con el equipo de desarrollo de producto cuando sea necesario.Impartir capacitaciones técnicas y de arquitectura a los clientes de Murex, con el fin de fortalecer sus capacidades de soporte.Desarrollar experiencia en distintas áreas técnicas, incluyendo sistemas operativos, diseño e implementación de aplicaciones, infraestructura de hardware y nube, redes y servidores de bases de datos.🌟 Quién eres🎓 Formación académicaBuscamos un experto técnico apasionado y con potencial de crecimiento para unirse a nuestro equipo en Chile:Título de Licenciatura o Magíster en Ciencias de la Computación, Ingeniería, Matemáticas o carreras afines,Experiencia: entre 0 y 2 años  en áreas relacionadas.Conocimientos en scripting conUnix Shell, Java, C/C++, SQL/RDBMS y Python.Se valorarán conocimientos en las siguientes tecnologías y conceptos: soluciones en la nube (Cloud Solutions) y arquitecturas multinivel (Multitier Architecture).Se considerará una ventaja contar con conocimientos en XML/XSLT, JSON, Terraform, Ansible, Perl, expresiones regulares (Regex), JavaScript, Java JDK/JRE y Git/BitBucket.Sólidas habilidades de programación y resolución de problemas, con orientación al cliente y una fuerte motivación por alcanzar la excelencia.Dominio avanzado del inglés(oral, escrito y lectura) es indispensable, junto con excelentes habilidades de comunicación.Beneficios🌍 Por qué unirte a nosotrosSer parte de una empresa líder con más de 35 años en una industria dinámica.Formar parte de un equipo inclusivo y centrado en las personas.Aprender en un entorno internacional y altamente colaborativo.Desarrollarte en tecnologías de integración, sistemas financieros y soluciones fintech.Oportunidades de crecimiento profesional y posible continuidad en la compañía.🌈 Diversidad e inclusiónEn Murex creemos en la igualdad de oportunidades para todos los colaboradores y postulantes. No se permite ningún tipo de discriminación o acoso por motivos de raza, género, religión, orientación sexual, discapacidad u otras características protegidas por la ley.Nuestro compromiso con la equidad e inclusión es parte fundamental de nuestra cultura.</t>
+          <t>¡En ACHS Servicios te estamos buscando!Somos una Empresa de servicios filial de la Asociación Chilena de Seguridad (ACHS), que cuenta con el respaldo y trayectoria de la mutualidad líder en Chile.Nuestra misiónes entregar confianza, seguridad y cercanía a nuestros colaboradores, pacientes y comunidades. Con un servicio de excelencia y permanente innovación.Queremos que seas nuestro/a próximo/a Operador de Traslado, para trabajar en la Región Metropolitana en turnos L-V Diurno.El objetivo principal del cargoes planificar y coordinar la operación de la empresa en los distintos tipos de móviles.Principales funciones del cargo:Planificar, gestionar y dar seguimiento a los traslados de todos los pacientes de baja, mediana y alta complejidad con el fin de responder a los protocolos de la empresa.Requisitos para ser el candidato ideal:Contar con título técnico nivel superior en administración, logística y/o carrera afínExperiencia en áreas logísticas y/o administrativas al menos 1 añoManejo computacionalServicio al clienteAspiramos a ser los mejores entregando soluciones en salud y logística para el cuidado de los trabajadores y sus familias¡Anímate! ¡Y postula con nosotros!</t>
         </is>
       </c>
     </row>
@@ -8777,27 +8773,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Operador de Traslados Coordinación Operativa Providencia 5X2</t>
+          <t>Asistente de Ventas Part Time Región Metropolitana</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Achs Servicios</t>
+          <t>Tanner</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Providencia, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55531/operador-de-traslados-coordinacion-operativa-providencia-5x2</t>
+          <t>https://firstjob.me/oferta/55350/asistente-de-ventas-part-time-region-metropolitana</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -8811,13 +8807,13 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N124" t="n">
         <v>0</v>
@@ -8830,7 +8826,7 @@
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>¡En ACHS Servicios te estamos buscando!Somos una Empresa de servicios filial de la Asociación Chilena de Seguridad (ACHS), que cuenta con el respaldo y trayectoria de la mutualidad líder en Chile.Nuestra misiónes entregar confianza, seguridad y cercanía a nuestros colaboradores, pacientes y comunidades. Con un servicio de excelencia y permanente innovación.Queremos que seas nuestro/a próximo/a Operador de Traslado, para trabajar en la Región Metropolitana en turnos L-V Diurno.El objetivo principal del cargoes planificar y coordinar la operación de la empresa en los distintos tipos de móviles.Principales funciones del cargo:Planificar, gestionar y dar seguimiento a los traslados de todos los pacientes de baja, mediana y alta complejidad con el fin de responder a los protocolos de la empresa.Requisitos para ser el candidato ideal:Contar con título técnico nivel superior en administración, logística y/o carrera afínExperiencia en áreas logísticas y/o administrativas al menos 1 añoManejo computacionalServicio al clienteAspiramos a ser los mejores entregando soluciones en salud y logística para el cuidado de los trabajadores y sus familias¡Anímate! ¡Y postula con nosotros!</t>
+          <t>Asistente de Ventas Part Time Región MetropolitanaEn Tanner seguimos creciendo y queremos que tú también seas parte de este equipo.Buscamos a nuestro próximo/aAsistente de Ventas Part Time, quien tendrá la misión de brindar un servicio de excelencia a nuestros clientes en el punto de venta, asesorándolos en productos financieros y seguros automotrices.¿Qué harás?Asesorar y apoyar en la venta de productos financieros y seguros automotrices.Entregar una experiencia de atención cercana y de calidad, ayudando a cada cliente a encontrar la mejor alternativa según sus necesidades.Validar documentación y respaldos asociados a los cierres de financiamiento.Representar a Tanner con una actitud proactiva, empática y orientada al servicio.Lugar de trabajoDeberás realizar cobertura principalmente en distintos puntos de la Región Metropolitana:Mall Vespucio, Mall Plaza Oeste, Mall Los Dominicos, Autopark y Mall Alameda.🕒 JornadaModalidad Part Time de 27 horas semanales.Horario: 10:30 a 19:00 hrs.Distribución: sábado y domingo + 1 día a la semana (a coordinar según disponibilidad y necesidades del equipo).Se consideran al menos2 domingos libres al mes.RequisitosDeseable formación técnica o profesional en áreas comerciales o afines.Experiencia en atención al cliente o ventas (idealmente en retail o servicios financieros).Habilidades comunicacionales y orientación al cliente.Proactividad, responsabilidad y capacidad para trabajar en equipo.Disponibilidad para trabajar en modalidad Part Time según la jornada indicada.En Tanner valoramos el compromiso, la cercanía y el trabajo colaborativo, ofreciendo un espacio donde podrás desarrollarte y generar impacto en la experiencia de nuestros clientes.¡Te invitamos a postular y ser parte de Tanner!</t>
         </is>
       </c>
     </row>
@@ -8842,7 +8838,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Asistente de Ventas Part Time Región Metropolitana</t>
+          <t>Especialista de Riesgo de Mercado</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8857,32 +8853,36 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Remoto Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55350/asistente-de-ventas-part-time-region-metropolitana</t>
+          <t>https://firstjob.me/oferta/55653/especialista-de-riesgo-de-mercado</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>python, sql, matematica, excel</t>
+        </is>
+      </c>
       <c r="I125" t="n">
         <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>Asistente de Ventas Part Time Región MetropolitanaEn Tanner seguimos creciendo y queremos que tú también seas parte de este equipo.Buscamos a nuestro próximo/aAsistente de Ventas Part Time, quien tendrá la misión de brindar un servicio de excelencia a nuestros clientes en el punto de venta, asesorándolos en productos financieros y seguros automotrices.¿Qué harás?Asesorar y apoyar en la venta de productos financieros y seguros automotrices.Entregar una experiencia de atención cercana y de calidad, ayudando a cada cliente a encontrar la mejor alternativa según sus necesidades.Validar documentación y respaldos asociados a los cierres de financiamiento.Representar a Tanner con una actitud proactiva, empática y orientada al servicio.Lugar de trabajoDeberás realizar cobertura principalmente en distintos puntos de la Región Metropolitana:Mall Vespucio, Mall Plaza Oeste, Mall Los Dominicos, Autopark y Mall Alameda.🕒 JornadaModalidad Part Time de 27 horas semanales.Horario: 10:30 a 19:00 hrs.Distribución: sábado y domingo + 1 día a la semana (a coordinar según disponibilidad y necesidades del equipo).Se consideran al menos2 domingos libres al mes.RequisitosDeseable formación técnica o profesional en áreas comerciales o afines.Experiencia en atención al cliente o ventas (idealmente en retail o servicios financieros).Habilidades comunicacionales y orientación al cliente.Proactividad, responsabilidad y capacidad para trabajar en equipo.Disponibilidad para trabajar en modalidad Part Time según la jornada indicada.En Tanner valoramos el compromiso, la cercanía y el trabajo colaborativo, ofreciendo un espacio donde podrás desarrollarte y generar impacto en la experiencia de nuestros clientes.¡Te invitamos a postular y ser parte de Tanner!</t>
+          <t>En Tanner estamos buscando a profesionales que quieran potenciar su carrera en riesgo financiero, participando en la gestión de riesgos de mercado y contraparte en un entorno dinámico y desafiante.¿Qué harás en este rol?Apoyar y liderar procesos de valorización de instrumentos financieros.Participar en la reportería regulatoria hacia la CMF.Monitorear riesgos de cartera, P&amp;L y exposiciones.Trabajar directamente con mesas de dinero y áreas clave del negocio.¿A quién buscamos?Profesionales con 2 a 4 años de experiencia en áreas financieras o cuantitativas.Carreras como Ingeniería Comercial, Civil Industrial, Matemática o afines.Interés y conocimientos en instrumentos financieros y derivados.Manejo de herramientas como Excel, SQL o Python.¿Te interesa este desafío? Postula y sé parte de un equipo que impulsa decisiones clave en el negocio financiero.Beneficios- Seguro Complementario de salud- Día Administrativo- Bono vacaciones- Bono fiestas patrias</t>
         </is>
       </c>
     </row>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Especialista de Riesgo de Mercado</t>
+          <t>Asistente de Ventas 5x2</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8922,33 +8922,29 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Remoto Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55653/especialista-de-riesgo-de-mercado</t>
+          <t>https://firstjob.me/oferta/55352/asistente-de-ventas-5x2</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>10</v>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>python, sql, matematica, excel</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="n">
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M126" t="n">
         <v>0</v>
@@ -8964,7 +8960,7 @@
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>En Tanner estamos buscando a profesionales que quieran potenciar su carrera en riesgo financiero, participando en la gestión de riesgos de mercado y contraparte en un entorno dinámico y desafiante.¿Qué harás en este rol?Apoyar y liderar procesos de valorización de instrumentos financieros.Participar en la reportería regulatoria hacia la CMF.Monitorear riesgos de cartera, P&amp;L y exposiciones.Trabajar directamente con mesas de dinero y áreas clave del negocio.¿A quién buscamos?Profesionales con 2 a 4 años de experiencia en áreas financieras o cuantitativas.Carreras como Ingeniería Comercial, Civil Industrial, Matemática o afines.Interés y conocimientos en instrumentos financieros y derivados.Manejo de herramientas como Excel, SQL o Python.¿Te interesa este desafío? Postula y sé parte de un equipo que impulsa decisiones clave en el negocio financiero.Beneficios- Seguro Complementario de salud- Día Administrativo- Bono vacaciones- Bono fiestas patrias</t>
+          <t>Asistente de Ventas Full Time (5x2) Región Metropolitana – Tanner Servicios FinancierosEn Tanner seguimos creciendo y queremos que tú también seas parte de este equipo.Buscamos a nuestro próximo/aAsistente de Ventas Full Time, quien tendrá la misión de brindar un servicio de excelencia a nuestros clientes en el punto de venta, asesorándolos en productos financieros y seguros automotrices.¿Qué harás?Asesorar y apoyar en la venta de productos financieros y seguros automotrices.Entregar una experiencia de atención cercana y de calidad, ayudando a cada cliente a encontrar la mejor alternativa según sus necesidades.Validar documentación y respaldos asociados a los cierres de financiamiento.Representar a Tanner con una actitud proactiva, empática y orientada al servicio.¿Qué buscamos?Deseable contar con estudios técnicos o profesionales en áreas comerciales, administración o afines.Al menos 1 año de experiencia en atención al cliente o ventas (idealmente en retail o servicios financieros).Habilidades comunicacionales y orientación al cliente.Disponibilidad para trabajar en modalidad presencial 5x2En Tanner valoramos el compromiso, la cercanía y el trabajo colaborativo, ofreciendo un espacio donde podrás desarrollarte y generar impacto en la experiencia de nuestros clientes.¡Te invitamos a postular y ser parte de Tanner!</t>
         </is>
       </c>
     </row>
@@ -8976,12 +8972,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Asistente de Ventas 5x2</t>
+          <t>Retail Visual Merchandising</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Tanner</t>
+          <t>Belcorp</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8991,12 +8987,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55352/asistente-de-ventas-5x2</t>
+          <t>https://firstjob.me/oferta/55623/retail-visual-merchandising</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -9004,16 +9000,16 @@
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
       </c>
       <c r="K127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
         <v>0</v>
@@ -9029,7 +9025,7 @@
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>Asistente de Ventas Full Time (5x2) Región Metropolitana – Tanner Servicios FinancierosEn Tanner seguimos creciendo y queremos que tú también seas parte de este equipo.Buscamos a nuestro próximo/aAsistente de Ventas Full Time, quien tendrá la misión de brindar un servicio de excelencia a nuestros clientes en el punto de venta, asesorándolos en productos financieros y seguros automotrices.¿Qué harás?Asesorar y apoyar en la venta de productos financieros y seguros automotrices.Entregar una experiencia de atención cercana y de calidad, ayudando a cada cliente a encontrar la mejor alternativa según sus necesidades.Validar documentación y respaldos asociados a los cierres de financiamiento.Representar a Tanner con una actitud proactiva, empática y orientada al servicio.¿Qué buscamos?Deseable contar con estudios técnicos o profesionales en áreas comerciales, administración o afines.Al menos 1 año de experiencia en atención al cliente o ventas (idealmente en retail o servicios financieros).Habilidades comunicacionales y orientación al cliente.Disponibilidad para trabajar en modalidad presencial 5x2En Tanner valoramos el compromiso, la cercanía y el trabajo colaborativo, ofreciendo un espacio donde podrás desarrollarte y generar impacto en la experiencia de nuestros clientes.¡Te invitamos a postular y ser parte de Tanner!</t>
+          <t>¿Estás buscando tu próximo desafío en Retail Visual Merchandising?¿Te apasiona crear experiencias visuales que conecten a los consumidores con las marcas? ¿Disfrutas transformar ideas en exhibiciones de alto impacto y colaborar con equipos regionales? ¿Quieres desarrollarte en un rol donde el diseño, la estrategia comercial y la experiencia del cliente se unan? ¡Entonces esta oportunidad es para ti!Somos una empresa omnicanal y líder en el rubro de la venta directa, con presencia en 14 países de la región. Comercializamos nuestras marcasL'BEL, Ésika y Cyzonea través de los canales de Venta Directa, E-commerce y Retail.Buscamos profesionales creativos, analíticos y orientados a resultados, con pasión por el diseño y el visual merchandising. Queremos incorporar a una persona que disfrute trabajando con equipos multidisciplinarios, gestionando múltiples proyectos simultáneamente y asegurando que cada punto de venta entregue una experiencia de marca consistente e inspiradora.¿Cuál será tu principal desafío?Serás responsable de desarrollar e implementar todas las piezas visuales de las campañas comerciales para Chile, colaborando además con proyectos para Centroamérica y México. Tu misión será asegurar una ejecución impecable de la identidad visual de nuestras marcas, coordinando con proveedores y equipos internos para generar una experiencia de compra atractiva, consistente y alineada con la estrategia comercial.Además, analizarás el impacto de las implementaciones en tienda, identificando oportunidades de mejora e impulsando iniciativas que fortalezcan la experiencia de nuestros consumidores.Algunas de las responsabilidades del cargo:Desarrollar piezas gráficas y material visual para campañas comerciales, vitrinas, exhibidores, material POP y comunicación en punto de venta.Coordinar la implementación de proyectos con proveedores, realizando seguimiento a la producción y ejecución de cada iniciativa.Diseñar material digital para tiendas, incluyendo comunicaciones internas, mailings y otros recursos visuales.Analizar indicadores y resultados de las implementaciones para identificar insights y oportunidades de mejora.Colaborar con equipos comerciales y de Visual Merchandising para asegurar una correcta implementación de la identidad de marca.Investigar tendencias de retail, diseño y comportamiento del consumidor para proponer nuevas iniciativas que potencien la experiencia en tienda.Lo que necesitamos de tiTítulo profesional en Diseño Gráfico, Diseño Visual, Comunicación Visual, Publicidad o carrera afín.Desde1 año de experienciaen Visual Merchandising, diseño gráfico para retail o desarrollo de material POP.Experiencia idealmente en empresas de consumo masivo.Dominio deAdobe PhotoshopyAdobe Illustrator.Manejo de inglés intermedio.Capacidad para gestionar múltiples proyectos simultáneamente y coordinar con distintos stakeholders.Pensamiento estratégico, habilidades analíticas, autonomía y excelentes habilidades interpersonales.BeneficiosJornada laboral híbridaAsignación de alimentaciónAguinaldos en Septiembre y en Diciembre.Seguro complementario de salud.Convenios dentales, oftalmológicos y oncológicos.Entre otros más!</t>
         </is>
       </c>
     </row>
@@ -9041,12 +9037,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Retail Visual Merchandising</t>
+          <t>Consultor Financiero Contable</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Belcorp</t>
+          <t>Murex Chile</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -9061,13 +9057,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55623/retail-visual-merchandising</t>
+          <t>https://firstjob.me/oferta/55209/consultor-financiero-contable</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>sql</t>
+        </is>
+      </c>
       <c r="I128" t="n">
         <v>1</v>
       </c>
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>¿Estás buscando tu próximo desafío en Retail Visual Merchandising?¿Te apasiona crear experiencias visuales que conecten a los consumidores con las marcas? ¿Disfrutas transformar ideas en exhibiciones de alto impacto y colaborar con equipos regionales? ¿Quieres desarrollarte en un rol donde el diseño, la estrategia comercial y la experiencia del cliente se unan? ¡Entonces esta oportunidad es para ti!Somos una empresa omnicanal y líder en el rubro de la venta directa, con presencia en 14 países de la región. Comercializamos nuestras marcasL'BEL, Ésika y Cyzonea través de los canales de Venta Directa, E-commerce y Retail.Buscamos profesionales creativos, analíticos y orientados a resultados, con pasión por el diseño y el visual merchandising. Queremos incorporar a una persona que disfrute trabajando con equipos multidisciplinarios, gestionando múltiples proyectos simultáneamente y asegurando que cada punto de venta entregue una experiencia de marca consistente e inspiradora.¿Cuál será tu principal desafío?Serás responsable de desarrollar e implementar todas las piezas visuales de las campañas comerciales para Chile, colaborando además con proyectos para Centroamérica y México. Tu misión será asegurar una ejecución impecable de la identidad visual de nuestras marcas, coordinando con proveedores y equipos internos para generar una experiencia de compra atractiva, consistente y alineada con la estrategia comercial.Además, analizarás el impacto de las implementaciones en tienda, identificando oportunidades de mejora e impulsando iniciativas que fortalezcan la experiencia de nuestros consumidores.Algunas de las responsabilidades del cargo:Desarrollar piezas gráficas y material visual para campañas comerciales, vitrinas, exhibidores, material POP y comunicación en punto de venta.Coordinar la implementación de proyectos con proveedores, realizando seguimiento a la producción y ejecución de cada iniciativa.Diseñar material digital para tiendas, incluyendo comunicaciones internas, mailings y otros recursos visuales.Analizar indicadores y resultados de las implementaciones para identificar insights y oportunidades de mejora.Colaborar con equipos comerciales y de Visual Merchandising para asegurar una correcta implementación de la identidad de marca.Investigar tendencias de retail, diseño y comportamiento del consumidor para proponer nuevas iniciativas que potencien la experiencia en tienda.Lo que necesitamos de tiTítulo profesional en Diseño Gráfico, Diseño Visual, Comunicación Visual, Publicidad o carrera afín.Desde1 año de experienciaen Visual Merchandising, diseño gráfico para retail o desarrollo de material POP.Experiencia idealmente en empresas de consumo masivo.Dominio deAdobe PhotoshopyAdobe Illustrator.Manejo de inglés intermedio.Capacidad para gestionar múltiples proyectos simultáneamente y coordinar con distintos stakeholders.Pensamiento estratégico, habilidades analíticas, autonomía y excelentes habilidades interpersonales.BeneficiosJornada laboral híbridaAsignación de alimentaciónAguinaldos en Septiembre y en Diciembre.Seguro complementario de salud.Convenios dentales, oftalmológicos y oncológicos.Entre otros más!</t>
+          <t>🌍 ¿Quiénes somos?Somos Murex, líder global en tecnología financiera (fintech) especializada en soluciones de trading, gestión de riesgo y procesamiento para mercados de capitales.Con presencia en 19 oficinas alrededor del mundo y más de 3.500 colaboradores de más de 60 nacionalidades, desarrollamos, implementamos y damos soporte a una plataforma utilizada por bancos, asset managers, corporaciones y utilities a nivel global.En Murex trabajarás en una industria que está a la vanguardia de la innovación, en un entorno centrado en las personas, donde podrás crecer rápidamente sin dejar de ser tú mismo/a. Formarás parte de un equipo global, diverso y altamente colaborativo.🚀 ¿Qué harás?Como Consultor Contable en el equipo de Finance &amp; P&amp;L de Murex, trabajarás en estrecha colaboración con nuestros clientes, incluyendo grandes bancos, hedge funds, gestores de activos, compañías de seguros, corporaciones y otros participantes del mercado de capitales.Asesoría en mejores prácticas:Proporcionar orientación sobre las mejores prácticas de Murex en procesos de P&amp;L, contabilidad, contabilidad de coberturas (hedge accounting), gestión de posiciones y reportes financieros.Implementaciones en cliente:Soporte a los trading designers durante implementaciones o upgrades, participando en las fases de levantamiento de requerimientos, diseño, construcción, pruebas y despliegue; incluyendo workshops, preparación de documentación, configuración de requerimientos del cliente y ejecución de pruebas de calidad.Soporte a clientes:Gestionar incidencias abiertas y apoyar en actividades de upgrade.Comunicación:Gestionar la relación con el equipo de producto en un área de especialización y apoyar en la construcción del roadmap del producto para la región.Documentación y capacitación:Proporcionar documentación y formación tanto interna como externa.🎯 ¿Qué buscamos?Formación académica:Título profesional en carrera afín.  Contabilidad, Ingeniería comercial, Ingeniería en control de gestiónExperiencia:1 a 2 añosConocimientos técnicos:Fuerte interés o conocimientos en Tesorería y Mercados de CapitalesIdiomas:Inglés avanzado (excluyente).Habilidades técnicas(no excluyentes): Conocimientos en sistemas operativos Unix/Linux, SQL y programación básicaDisponibilidad para viajar.</t>
         </is>
       </c>
     </row>
@@ -9106,17 +9106,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Consultor Financiero Contable</t>
+          <t>Ejecutivo de Operaciones Comerciales - Bogotá, Colombia</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Murex Chile</t>
+          <t>Wherex Colombia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Cundinamarca, Colombia</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -9126,19 +9126,15 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55209/consultor-financiero-contable</t>
+          <t>https://firstjob.me/oferta/55177/ejecutivo-de-operaciones-comerciales-bogota-colombia</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>3</v>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>sql</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -9153,7 +9149,7 @@
         <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -9163,7 +9159,7 @@
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>🌍 ¿Quiénes somos?Somos Murex, líder global en tecnología financiera (fintech) especializada en soluciones de trading, gestión de riesgo y procesamiento para mercados de capitales.Con presencia en 19 oficinas alrededor del mundo y más de 3.500 colaboradores de más de 60 nacionalidades, desarrollamos, implementamos y damos soporte a una plataforma utilizada por bancos, asset managers, corporaciones y utilities a nivel global.En Murex trabajarás en una industria que está a la vanguardia de la innovación, en un entorno centrado en las personas, donde podrás crecer rápidamente sin dejar de ser tú mismo/a. Formarás parte de un equipo global, diverso y altamente colaborativo.🚀 ¿Qué harás?Como Consultor Contable en el equipo de Finance &amp; P&amp;L de Murex, trabajarás en estrecha colaboración con nuestros clientes, incluyendo grandes bancos, hedge funds, gestores de activos, compañías de seguros, corporaciones y otros participantes del mercado de capitales.Asesoría en mejores prácticas:Proporcionar orientación sobre las mejores prácticas de Murex en procesos de P&amp;L, contabilidad, contabilidad de coberturas (hedge accounting), gestión de posiciones y reportes financieros.Implementaciones en cliente:Soporte a los trading designers durante implementaciones o upgrades, participando en las fases de levantamiento de requerimientos, diseño, construcción, pruebas y despliegue; incluyendo workshops, preparación de documentación, configuración de requerimientos del cliente y ejecución de pruebas de calidad.Soporte a clientes:Gestionar incidencias abiertas y apoyar en actividades de upgrade.Comunicación:Gestionar la relación con el equipo de producto en un área de especialización y apoyar en la construcción del roadmap del producto para la región.Documentación y capacitación:Proporcionar documentación y formación tanto interna como externa.🎯 ¿Qué buscamos?Formación académica:Título profesional en carrera afín.  Contabilidad, Ingeniería comercial, Ingeniería en control de gestiónExperiencia:1 a 2 añosConocimientos técnicos:Fuerte interés o conocimientos en Tesorería y Mercados de CapitalesIdiomas:Inglés avanzado (excluyente).Habilidades técnicas(no excluyentes): Conocimientos en sistemas operativos Unix/Linux, SQL y programación básicaDisponibilidad para viajar.</t>
+          <t>¡En Wherex buscamos a nuestro/a próximo/a Ejecutivo/a de Operaciones Comerciales!Estarás a cargo de la gestión diaria de licitaciones que generan nuestros clientes y que son el corazón de nuestro negocio, para esto te apoyarás en nuestros sistemas con IA y de nuestra base de datos de más de 70 mil proveedores.¿Qué harás?- Gestionar de forma diaria las licitaciones asignadas, asegurando su correcta ejecución de principio a fin.- Identificar y activar a los proveedores más adecuados para cada proceso, maximizando la probabilidad de adjudicación.- Captar e incorporar nuevos proveedores según los requerimientos de cada licitación.- Detectar oportunidades de mejora en la operación y proponer soluciones que aumenten la eficiencia y calidad del proceso.- Mantener la información de gestión actualizada, asegurando orden y trazabilidad en las herramientas de la compañía.¿Qué harás?¿Qué estamos buscando?- Titulados de Administración de Empresas, Comercio Exterior, Negocios Internacionales o carreras afines.- 1 a 2 años de experiencia laboral.- Interés por desarrollarte en un rol que combina comercial con la operación.- Perfil dinámico, ordenado y orientado a resultados.📍 Ubicación:Bogotá, Colombia. - Modalidad Hibrida.**Para completar tu postulación, recuerda realizar los test de Genomaworks que miden competencias y habilidades, en el link que se encuentra adjunto en esta publicación.Beneficios¿Por qué trabajar en Wherex?- Medicina Prepagada.- 25 días libres al año para descansar y recargar energías.- Impacto en el corazón del negocio: Serás parte directa de la operación que mueve nuestra plataforma, gestionando licitaciones reales y generando valor concreto para clientes y proveedores en la región.- Aprendizaje acelerado: Trabajarás con grandes volúmenes de información, herramientas tecnológicas e inteligencia artificial, desarrollando una mirada analítica y operativa clave para tu crecimiento profesional.- Cultura de alto desempeño: Formarás parte de un equipo que combina exigencia, colaboración y foco en resultados, donde el aprendizaje continuo y el feedback son parte del día a día.- Desafíos constantes: No es un rol rutinario. Tendrás que tomar decisiones, priorizar y proponer mejoras en procesos que impactan directamente la eficiencia del negocio.</t>
         </is>
       </c>
     </row>
@@ -9175,17 +9171,17 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Ejecutivo de Operaciones Comerciales - Bogotá, Colombia</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Wherex Colombia</t>
+          <t>Murex Chile</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Cundinamarca, Colombia</t>
+          <t>Av. Apoquindo 2730, Chile</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -9195,15 +9191,19 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55177/ejecutivo-de-operaciones-comerciales-bogota-colombia</t>
+          <t>https://firstjob.me/oferta/55395/devops-engineer</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>informatica, cloud, aws</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -9218,17 +9218,17 @@
         <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>¡En Wherex buscamos a nuestro/a próximo/a Ejecutivo/a de Operaciones Comerciales!Estarás a cargo de la gestión diaria de licitaciones que generan nuestros clientes y que son el corazón de nuestro negocio, para esto te apoyarás en nuestros sistemas con IA y de nuestra base de datos de más de 70 mil proveedores.¿Qué harás?- Gestionar de forma diaria las licitaciones asignadas, asegurando su correcta ejecución de principio a fin.- Identificar y activar a los proveedores más adecuados para cada proceso, maximizando la probabilidad de adjudicación.- Captar e incorporar nuevos proveedores según los requerimientos de cada licitación.- Detectar oportunidades de mejora en la operación y proponer soluciones que aumenten la eficiencia y calidad del proceso.- Mantener la información de gestión actualizada, asegurando orden y trazabilidad en las herramientas de la compañía.¿Qué harás?¿Qué estamos buscando?- Titulados de Administración de Empresas, Comercio Exterior, Negocios Internacionales o carreras afines.- 1 a 2 años de experiencia laboral.- Interés por desarrollarte en un rol que combina comercial con la operación.- Perfil dinámico, ordenado y orientado a resultados.📍 Ubicación:Bogotá, Colombia. - Modalidad Hibrida.**Para completar tu postulación, recuerda realizar los test de Genomaworks que miden competencias y habilidades, en el link que se encuentra adjunto en esta publicación.Beneficios¿Por qué trabajar en Wherex?- Medicina Prepagada.- 25 días libres al año para descansar y recargar energías.- Impacto en el corazón del negocio: Serás parte directa de la operación que mueve nuestra plataforma, gestionando licitaciones reales y generando valor concreto para clientes y proveedores en la región.- Aprendizaje acelerado: Trabajarás con grandes volúmenes de información, herramientas tecnológicas e inteligencia artificial, desarrollando una mirada analítica y operativa clave para tu crecimiento profesional.- Cultura de alto desempeño: Formarás parte de un equipo que combina exigencia, colaboración y foco en resultados, donde el aprendizaje continuo y el feedback son parte del día a día.- Desafíos constantes: No es un rol rutinario. Tendrás que tomar decisiones, priorizar y proponer mejoras en procesos que impactan directamente la eficiencia del negocio.</t>
+          <t>Quienes somos:Murex es una empresa fintech líder mundial en soluciones de trading, gestión de riesgos y procesamiento para los mercados de capitales. Desde nuestras 19 oficinas, 3500 Murexianos de más de 60 nacionalidades diferentes garantizan el desarrollo, la implementación y el soporte de nuestra plataforma, utilizada por bancos, gestores de activos, corporaciones y empresas de servicios públicos de todo el mundo.Únase a Murex y trabaje en los desafíos de una industria a la vanguardia de la innovación y prospere en un entorno centrado en las personas.Serás parte de un equipo global donde podrás aprender rápido y mantenerte fiel a ti mismo.El equipo:El equipo de DevOps tiene como objetivo brindar la experiencia que ayuda a los clientes de Murex en la región, brindando una variedad de servicios, que incluyen soporte, capacitación, evolución de la plataforma e implementación de nuevos módulos.Lo que harás:Como Consultor de Implementación Técnica en la oficina de Murex Chile, trabajarás en estrecha colaboración con nuestros clientes, entre los que se encuentran importantes bancos, fondos de cobertura, gestoras de activos, aseguradoras, empresas y otros actores del mercado de capitales. Tus responsabilidades incluirán:Trabajar en la implementación técnica de la plataforma MX.3 en modo SaaSGestionar los requisitos no funcionales (NFR), las pruebas no funcionales (NFT) y todos los temas relacionados con el rendimiento de MX.3Trabajar en estrecha colaboración con el flujo de integración para gestionar el desarrollo y la adaptación de interfaces entre los sistemas de información del cliente y Murex MX.3Garantizar la calidad y estabilidad de la plataforma MX.3Diseñar e implementar herramientas necesarias para la operación y gestión de MX.3 en SaaS (monitoreo, automatización, etc.)Trabajar en modelos de integración continua utilizando Jenkins, Ansible y GITActuar como contacto técnico para los clientes de SaaS y como escalador en todos los incidentes técnicos.Trabajar en propuestas para clientes potenciales de Murex interesados ​​en la oferta SaaS (proporcionar la capacidad de hardware necesaria para implementar los módulos de Murex, responder RFP sobre la arquitectura técnica de Murex, la red, la seguridad, etc.)Quién eres:Si te gusta resolver problemas complejos, pensar críticamente y tienes los siguientes conocimientos:Educación: Título de licenciatura en ingeniería, ingeniería informática, ciencias de la computación o equivalente1 a 2 años de experiencia en TI.Debe tener una buena experiencia trabajando en lenguajes de programación: a saber, Java y Groovy.Apasionado por aprender y trabajar con nuevas tecnologías y prácticas conocidas (agile, DevOps, herramientas de automatización)Conocimiento de scripts de Shell y sistemas UnixConocimiento de bases de datosSe requiere una habilidad excepcional para resolver los problemas del cliente.Capacidad para explicar la arquitectura técnica en términos no técnicos para comunicarse con una audiencia amplia de diferentes orígenes.La exposición a cualquiera de las siguientes aplicaciones/entornos de Cloud Core es una ventajaCitrix, AWS, Jenkins. La exposición a modelos como servicio es una ventaja: IaaS, BPaaS y SaaS.Es necesario tener inglés fluido escrito y oral.Es necesario tener español fluido escrito y oral.BeneficiosÚnase a un líder del mercado con más de 35 años de trayectoria en una industria en crecimiento y dinámica.Sea parte de un equipo inclusivo con un fuerte enfoque en las personas.Colaboración ágil con colegas de diferentes orígenes.Un entorno internacional que ofrece perspectivas de trabajo global.El mejor seguro médico, dental y de vida.En Murex, creemos en la igualdad de oportunidades para todos los empleados y solicitantes de empleo. Queda estrictamente prohibida la discriminación o el acoso por motivos de raza, color, religión, edad, sexo, nacionalidad, discapacidad, genética, condición de veterano protegido, orientación sexual, identidad o expresión de género o cualquier otra característica protegida por las leyes federales, estatales o locales.Esta política se aplica a todos los aspectos del empleo, incluyendo el reclutamiento, la contratación, la colocación, los ascensos, el despido, el despido temporal, la reincorporación, el traslado, las licencias, la compensación y la capacitación. Nuestro compromiso con la equidad y la inclusión es la base de todo lo que hacemos.</t>
         </is>
       </c>
     </row>
@@ -9240,7 +9240,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Operations Consultant</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Av. Apoquindo 2730, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -9260,15 +9260,15 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55395/devops-engineer</t>
+          <t>https://firstjob.me/oferta/55396/operations-consultant</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>informatica, cloud, aws</t>
+          <t>sql</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -9293,11 +9293,11 @@
         <v>0</v>
       </c>
       <c r="P131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>Quienes somos:Murex es una empresa fintech líder mundial en soluciones de trading, gestión de riesgos y procesamiento para los mercados de capitales. Desde nuestras 19 oficinas, 3500 Murexianos de más de 60 nacionalidades diferentes garantizan el desarrollo, la implementación y el soporte de nuestra plataforma, utilizada por bancos, gestores de activos, corporaciones y empresas de servicios públicos de todo el mundo.Únase a Murex y trabaje en los desafíos de una industria a la vanguardia de la innovación y prospere en un entorno centrado en las personas.Serás parte de un equipo global donde podrás aprender rápido y mantenerte fiel a ti mismo.El equipo:El equipo de DevOps tiene como objetivo brindar la experiencia que ayuda a los clientes de Murex en la región, brindando una variedad de servicios, que incluyen soporte, capacitación, evolución de la plataforma e implementación de nuevos módulos.Lo que harás:Como Consultor de Implementación Técnica en la oficina de Murex Chile, trabajarás en estrecha colaboración con nuestros clientes, entre los que se encuentran importantes bancos, fondos de cobertura, gestoras de activos, aseguradoras, empresas y otros actores del mercado de capitales. Tus responsabilidades incluirán:Trabajar en la implementación técnica de la plataforma MX.3 en modo SaaSGestionar los requisitos no funcionales (NFR), las pruebas no funcionales (NFT) y todos los temas relacionados con el rendimiento de MX.3Trabajar en estrecha colaboración con el flujo de integración para gestionar el desarrollo y la adaptación de interfaces entre los sistemas de información del cliente y Murex MX.3Garantizar la calidad y estabilidad de la plataforma MX.3Diseñar e implementar herramientas necesarias para la operación y gestión de MX.3 en SaaS (monitoreo, automatización, etc.)Trabajar en modelos de integración continua utilizando Jenkins, Ansible y GITActuar como contacto técnico para los clientes de SaaS y como escalador en todos los incidentes técnicos.Trabajar en propuestas para clientes potenciales de Murex interesados ​​en la oferta SaaS (proporcionar la capacidad de hardware necesaria para implementar los módulos de Murex, responder RFP sobre la arquitectura técnica de Murex, la red, la seguridad, etc.)Quién eres:Si te gusta resolver problemas complejos, pensar críticamente y tienes los siguientes conocimientos:Educación: Título de licenciatura en ingeniería, ingeniería informática, ciencias de la computación o equivalente1 a 2 años de experiencia en TI.Debe tener una buena experiencia trabajando en lenguajes de programación: a saber, Java y Groovy.Apasionado por aprender y trabajar con nuevas tecnologías y prácticas conocidas (agile, DevOps, herramientas de automatización)Conocimiento de scripts de Shell y sistemas UnixConocimiento de bases de datosSe requiere una habilidad excepcional para resolver los problemas del cliente.Capacidad para explicar la arquitectura técnica en términos no técnicos para comunicarse con una audiencia amplia de diferentes orígenes.La exposición a cualquiera de las siguientes aplicaciones/entornos de Cloud Core es una ventajaCitrix, AWS, Jenkins. La exposición a modelos como servicio es una ventaja: IaaS, BPaaS y SaaS.Es necesario tener inglés fluido escrito y oral.Es necesario tener español fluido escrito y oral.BeneficiosÚnase a un líder del mercado con más de 35 años de trayectoria en una industria en crecimiento y dinámica.Sea parte de un equipo inclusivo con un fuerte enfoque en las personas.Colaboración ágil con colegas de diferentes orígenes.Un entorno internacional que ofrece perspectivas de trabajo global.El mejor seguro médico, dental y de vida.En Murex, creemos en la igualdad de oportunidades para todos los empleados y solicitantes de empleo. Queda estrictamente prohibida la discriminación o el acoso por motivos de raza, color, religión, edad, sexo, nacionalidad, discapacidad, genética, condición de veterano protegido, orientación sexual, identidad o expresión de género o cualquier otra característica protegida por las leyes federales, estatales o locales.Esta política se aplica a todos los aspectos del empleo, incluyendo el reclutamiento, la contratación, la colocación, los ascensos, el despido, el despido temporal, la reincorporación, el traslado, las licencias, la compensación y la capacitación. Nuestro compromiso con la equidad y la inclusión es la base de todo lo que hacemos.</t>
+          <t>🌍 ¿Quiénes somos?Somos Murex, líder global en tecnología financiera (fintech) especializada en soluciones de trading, gestión de riesgo y procesamiento para mercados de capitales.Con presencia en 19 oficinas alrededor del mundo y más de 3.500 colaboradores de más de 60 nacionalidades, desarrollamos, implementamos y damos soporte a una plataforma utilizada por bancos, asset managers, corporaciones y utilities a nivel global.En Murex trabajarás en una industria que está a la vanguardia de la innovación, en un entorno centrado en las personas, donde podrás crecer rápidamente sin dejar de ser tú mismo/a. Formarás parte de un equipo global, diverso y altamente colaborativo.👥 El equipoComoAnalista Técnico Junior de Operacionesen el equipo deOperaciones y Finanzasde la oficina de Murex Chile, trabajarás estrechamente con nuestros clientes, incluyendo importantes bancos, fondos de cobertura (hedge funds), administradoras de activos, compañías de seguros, corporaciones y otros participantes de los mercados de capitales.Tus responsabilidades incluirán:Asesorar a los clientes sobre las mejores prácticas de Murex en el modelado organizacional dentro de MX.3, la gestión del ciclo de vida de las transacciones, la confirmación y conciliación de operaciones, las liquidaciones, la contabilidad y la gestión de posiciones.Participar en implementaciones de MX.3 en las instalaciones de los clientes durante las fases de levantamiento de requerimientos, diseño, construcción, pruebas y despliegue; participando en talleres, preparando documentación, configurando requerimientos de negocio y realizando pruebas de aseguramiento de calidad (QA).Brindar soporte a clientes, incluyendo la gestión de incidencias abiertas y el apoyo en actividades de actualización (upgrades) del sistema.Comunicar necesidades de desarrollo al equipo de desarrollo de producto de Murex.Impartir capacitaciones tanto internas como externas.Adicionalmente, podrás participar como experto funcional en actividades de preventa y apoyo al proceso comercial.🎯 ¿Qué buscamos?Recién graduado(a) o con entre1 y 3 años de experienciaen la industria tecnológica o bancaria.Sólida formación académica ennegocios, finanzas, ingeniería o tecnología.Conocimientos deUnix/Linux, SQL, XSL y programación básicason un plus.Familiaridad con elciclo de vida de las operaciones (trade lifecycle)de productos financieros.Conocimientos decontabilidad financierason un plus.Nivelavanzado de inglés, tanto escrito como hablado, es indispensable.Beneficios🌟 ¿Por qué unirte a Murex?Empresa líder con más de 35 años de trayectoria en una industria dinámica y en constante crecimiento.Cultura inclusiva con enfoque people-first.Trabajo ágil y colaborativo con equipos multiculturales.Ambiente internacional con oportunidades de proyección global.20 días de vacacionescontrato indefinidoSeguro médico, dental y de vida de primer nivel.🤝 Nuestro compromisoEn Murex promovemos la igualdad de oportunidades. No toleramos ningún tipo de discriminación o acoso. Nuestra cultura está basada en la equidad, la inclusión y el respeto en todas las etapas del empleo.Si buscas impulsar tu carrera en mercados financieros, en un entorno internacional y altamente innovador, ¡esta es tu oportunidad! 🚀</t>
         </is>
       </c>
     </row>
@@ -9309,12 +9309,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Operations Consultant</t>
+          <t>Asistentes Centro de Excelencia Auditoría</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Murex Chile</t>
+          <t>EY Chile</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -9329,19 +9329,15 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55396/operations-consultant</t>
+          <t>https://firstjob.me/oferta/55206/asistentes-centro-de-excelencia-auditoria</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>3</v>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>sql</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -9356,7 +9352,7 @@
         <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -9366,7 +9362,7 @@
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>🌍 ¿Quiénes somos?Somos Murex, líder global en tecnología financiera (fintech) especializada en soluciones de trading, gestión de riesgo y procesamiento para mercados de capitales.Con presencia en 19 oficinas alrededor del mundo y más de 3.500 colaboradores de más de 60 nacionalidades, desarrollamos, implementamos y damos soporte a una plataforma utilizada por bancos, asset managers, corporaciones y utilities a nivel global.En Murex trabajarás en una industria que está a la vanguardia de la innovación, en un entorno centrado en las personas, donde podrás crecer rápidamente sin dejar de ser tú mismo/a. Formarás parte de un equipo global, diverso y altamente colaborativo.👥 El equipoComoAnalista Técnico Junior de Operacionesen el equipo deOperaciones y Finanzasde la oficina de Murex Chile, trabajarás estrechamente con nuestros clientes, incluyendo importantes bancos, fondos de cobertura (hedge funds), administradoras de activos, compañías de seguros, corporaciones y otros participantes de los mercados de capitales.Tus responsabilidades incluirán:Asesorar a los clientes sobre las mejores prácticas de Murex en el modelado organizacional dentro de MX.3, la gestión del ciclo de vida de las transacciones, la confirmación y conciliación de operaciones, las liquidaciones, la contabilidad y la gestión de posiciones.Participar en implementaciones de MX.3 en las instalaciones de los clientes durante las fases de levantamiento de requerimientos, diseño, construcción, pruebas y despliegue; participando en talleres, preparando documentación, configurando requerimientos de negocio y realizando pruebas de aseguramiento de calidad (QA).Brindar soporte a clientes, incluyendo la gestión de incidencias abiertas y el apoyo en actividades de actualización (upgrades) del sistema.Comunicar necesidades de desarrollo al equipo de desarrollo de producto de Murex.Impartir capacitaciones tanto internas como externas.Adicionalmente, podrás participar como experto funcional en actividades de preventa y apoyo al proceso comercial.🎯 ¿Qué buscamos?Recién graduado(a) o con entre1 y 3 años de experienciaen la industria tecnológica o bancaria.Sólida formación académica ennegocios, finanzas, ingeniería o tecnología.Conocimientos deUnix/Linux, SQL, XSL y programación básicason un plus.Familiaridad con elciclo de vida de las operaciones (trade lifecycle)de productos financieros.Conocimientos decontabilidad financierason un plus.Nivelavanzado de inglés, tanto escrito como hablado, es indispensable.Beneficios🌟 ¿Por qué unirte a Murex?Empresa líder con más de 35 años de trayectoria en una industria dinámica y en constante crecimiento.Cultura inclusiva con enfoque people-first.Trabajo ágil y colaborativo con equipos multiculturales.Ambiente internacional con oportunidades de proyección global.20 días de vacacionescontrato indefinidoSeguro médico, dental y de vida de primer nivel.🤝 Nuestro compromisoEn Murex promovemos la igualdad de oportunidades. No toleramos ningún tipo de discriminación o acoso. Nuestra cultura está basada en la equidad, la inclusión y el respeto en todas las etapas del empleo.Si buscas impulsar tu carrera en mercados financieros, en un entorno internacional y altamente innovador, ¡esta es tu oportunidad! 🚀</t>
+          <t>En EY Chile, Firma multinacional líder en Consultoría y Auditoría, reconocida como una de las 15 mejores empresas para trabajar en Chile, estamos en búsqueda de profesionales en su último año (4° o 5° año), recién egresados/as o titulados/as de la carrera deContador Auditor, para integrarse como Asistentes en nuestro Centro de Excelencia de Auditoría, a partir de octubre de 2026.Funciones:Apoyar en la confección y revisión de informes de Estados financieros.Apoyar en la realización de inventarios en las dependencias de nuestros clientes.Tipo de contrato:Plazo fijo desde octubre hasta el 31 de marzo de 2027.Necesitamos personas proactivas, con clara orientación al logro de metas y objetivos, con excelentes relaciones interpersonales.EY cree en la igualdad de oportunidades. Independientemente del género, edad, raza, color, credo, orientación sexual y discapacidad, todos los candidatos calificados serán considerados en nuestros procesos.¡Te invitamos a nuestro gran equipo!BeneficiosTe ofrecemos adquirir experiencia en una empresa líder a nivel internacional, que ofrece oportunidades de hacer carrera y desarrollarse profesionalmente, además de un grato ambiente laboral.</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9374,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Asistentes Centro de Excelencia Auditoría</t>
+          <t>Testing Engineering Consultant</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>EY Chile</t>
+          <t>Murex Chile</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -9398,15 +9394,19 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55206/asistentes-centro-de-excelencia-auditoria</t>
+          <t>https://firstjob.me/oferta/55384/testing-engineering-consultant</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>sql, analisis, informatica</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -9421,17 +9421,17 @@
         <v>0</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>En EY Chile, Firma multinacional líder en Consultoría y Auditoría, reconocida como una de las 15 mejores empresas para trabajar en Chile, estamos en búsqueda de profesionales en su último año (4° o 5° año), recién egresados/as o titulados/as de la carrera deContador Auditor, para integrarse como Asistentes en nuestro Centro de Excelencia de Auditoría, a partir de octubre de 2026.Funciones:Apoyar en la confección y revisión de informes de Estados financieros.Apoyar en la realización de inventarios en las dependencias de nuestros clientes.Tipo de contrato:Plazo fijo desde octubre hasta el 31 de marzo de 2027.Necesitamos personas proactivas, con clara orientación al logro de metas y objetivos, con excelentes relaciones interpersonales.EY cree en la igualdad de oportunidades. Independientemente del género, edad, raza, color, credo, orientación sexual y discapacidad, todos los candidatos calificados serán considerados en nuestros procesos.¡Te invitamos a nuestro gran equipo!BeneficiosTe ofrecemos adquirir experiencia en una empresa líder a nivel internacional, que ofrece oportunidades de hacer carrera y desarrollarse profesionalmente, además de un grato ambiente laboral.</t>
+          <t>Quiénes somosMurex es un líder global en fintech especializado en soluciones de trading, gestión de riesgo y procesamiento para mercados de capitales. Con presencia en 19 oficinas y más de 3.500 colaboradores de más de 60 nacionalidades, desarrollamos, implementamos y damos soporte a una de las plataformas más utilizadas por bancos, asset managers, corporaciones y utilities a nivel mundial.Únete a Murex y trabaja en los desafíos de una industria a la vanguardia de la innovación, en un entorno centrado en las personas.Serás parte de un equipo global donde podrás aprender rápidamente y desarrollarte profesionalmente ✨🔎 Qué harásComoTest Engineerapoyarás al equipo en la ejecución de la metodología de testing de Murex dentro de distintos proyectos, adquiriendo experiencia práctica en aseguramiento de calidad en entornos tecnológicos y financieros.Responsabilidades:Ejecución de pruebas:Apoyar en la definición, diseño y ejecución de casos de prueba, asegurando la calidad de las soluciones implementadas.Coordinación de actividades de testing:Colaborar en la organización y seguimiento de actividades de testing dentro de proyectos.Análisis de requerimientos:Apoyar en el entendimiento de requerimientos funcionales para diseñar estrategias y planes de prueba.Gestión de calidad:Contribuir a la identificación de riesgos y validación de cobertura de pruebas.Automatización (deseable):Apoyar en la identificación de oportunidades de automatización de pruebas y uso de herramientas.Seguimiento y reporting:Colaborar en el seguimiento de campañas de testing, documentando avances y resultados.Capacitación y aprendizaje:Participar en entrenamientos internos y programas de transferencia de conocimiento en herramientas y metodología Murex.Trabajo en equipo:Apoyar a ingenieros y consultores más senior, contribuyendo a un ambiente colaborativo.🌟 Quién eres🎓 Formación académica:Titulado de Ingeniería Civil Informática, Ingeniería Civil Industrial, Ingeniería en Computación o carrera afín.💻 Conocimientos técnicos: Nociones en entornos tecnológicos como SQL, XML, Unix o Windows.👨‍💻 Programación: Conocimientos básicos en Java o C/C++ (deseable).🧩 Habilidades analíticas: Pensamiento lógico, capacidad analítica y orientación a la resolución de problemas.🗣️ Comunicación: Buenas habilidades comunicacionales y nivel de inglés intermedio/avanzado.🤝 Trabajo en equipo: Capacidad de colaboración y comunicación con equipos multidisciplinarios.🚀 Actitud: Proactividad, atención al detalle, orientación a la calidad y ganas de aprender.</t>
         </is>
       </c>
     </row>
@@ -9443,64 +9443,64 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Testing Engineering Consultant</t>
+          <t>Analista Contable Jr.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Murex Chile</t>
+          <t>KiosClub</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Las Condes, Chile</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55384/testing-engineering-consultant</t>
+          <t>https://firstjob.me/oferta/55157/analista-contable-jr</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>sql, analisis, informatica</t>
+          <t>analisis, excel</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
       </c>
       <c r="K134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
       </c>
       <c r="N134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
         <v>0</v>
       </c>
       <c r="P134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="inlineStr">
         <is>
-          <t>Quiénes somosMurex es un líder global en fintech especializado en soluciones de trading, gestión de riesgo y procesamiento para mercados de capitales. Con presencia en 19 oficinas y más de 3.500 colaboradores de más de 60 nacionalidades, desarrollamos, implementamos y damos soporte a una de las plataformas más utilizadas por bancos, asset managers, corporaciones y utilities a nivel mundial.Únete a Murex y trabaja en los desafíos de una industria a la vanguardia de la innovación, en un entorno centrado en las personas.Serás parte de un equipo global donde podrás aprender rápidamente y desarrollarte profesionalmente ✨🔎 Qué harásComoTest Engineerapoyarás al equipo en la ejecución de la metodología de testing de Murex dentro de distintos proyectos, adquiriendo experiencia práctica en aseguramiento de calidad en entornos tecnológicos y financieros.Responsabilidades:Ejecución de pruebas:Apoyar en la definición, diseño y ejecución de casos de prueba, asegurando la calidad de las soluciones implementadas.Coordinación de actividades de testing:Colaborar en la organización y seguimiento de actividades de testing dentro de proyectos.Análisis de requerimientos:Apoyar en el entendimiento de requerimientos funcionales para diseñar estrategias y planes de prueba.Gestión de calidad:Contribuir a la identificación de riesgos y validación de cobertura de pruebas.Automatización (deseable):Apoyar en la identificación de oportunidades de automatización de pruebas y uso de herramientas.Seguimiento y reporting:Colaborar en el seguimiento de campañas de testing, documentando avances y resultados.Capacitación y aprendizaje:Participar en entrenamientos internos y programas de transferencia de conocimiento en herramientas y metodología Murex.Trabajo en equipo:Apoyar a ingenieros y consultores más senior, contribuyendo a un ambiente colaborativo.🌟 Quién eres🎓 Formación académica:Titulado de Ingeniería Civil Informática, Ingeniería Civil Industrial, Ingeniería en Computación o carrera afín.💻 Conocimientos técnicos: Nociones en entornos tecnológicos como SQL, XML, Unix o Windows.👨‍💻 Programación: Conocimientos básicos en Java o C/C++ (deseable).🧩 Habilidades analíticas: Pensamiento lógico, capacidad analítica y orientación a la resolución de problemas.🗣️ Comunicación: Buenas habilidades comunicacionales y nivel de inglés intermedio/avanzado.🤝 Trabajo en equipo: Capacidad de colaboración y comunicación con equipos multidisciplinarios.🚀 Actitud: Proactividad, atención al detalle, orientación a la calidad y ganas de aprender.</t>
+          <t>KiosClub American SupermarketSomos una empresa que surge en 2017 con el propósito de acercar productos internacionales al mercado chileno, con una propuesta diferenciada basada en marcas norteamericanas. Nuestro foco está en la variedad, la innovación y un servicio cercano.Hoy contamos con más de 50 tiendas a lo largo de todo el país y seguimos creciendo. Nuestra misión es ofrecer una experiencia de compra dinámica y entretenida, manteniendo estándares claros en nuestros productos y en la forma en que operamos.¡Estamos buscando a nuestro/a próximo/a Analista Contable Jr.!Si te apasiona el mundo de las finanzas y quieres desarrollarte en el área contable dentro de una empresa en crecimiento,esta oportunidad es para ti.Buscamos a una personaresponsable, organizada y con ganas de aprender, que quiera aportar al registro, análisis y conciliación de transacciones contables, asegurando una gestión financiera eficiente y ordenada.Tus principales responsabilidades serán:Registrar y analizar transacciones contables, asegurando la precisión de la información financiera.Apoyar en la preparación de informes y reportes de gestión contable.Colaborar en conciliaciones bancarias y contables.Participar en el análisis y seguimiento del flujo de efectivo.Asistir en el cumplimiento de normas y regulaciones contables vigentes.Mantener registros organizados y actualizados.Colaborar en procesos de auditoría interna y externa.Revisar y controlar documentos contables, garantizando su correcta validación y archivo.Apoyar a otras áreas en temas financieros y administrativos.Requisitos para postular:Título técnico o universitario enContabilidad, Auditoría o carrera afín.Entre 0 y 2 años de experiencia en funciones contables y financieras (ideal en empresas medianas o grandes).Conocimientos de principios contables y normativas vigentes.Manejo intermedio de Excel.Uso de software contable o sistemas ERP (deseable).Experiencia en conciliaciones bancarias y gestión de flujo de caja.Si estás buscando una oportunidad para crecer profesionalmente y ser parte de un equipo dinámico, ¡te invitamos a postular!BeneficiosDías de teletrabajo disponibles durante el año (10), para favorecer la flexibilidad y conciliación laboral.Días libres adicionales, sin límite anual, orientados a la flexibilidad laboral, sin goce de sueldo y previa coordinación con el equipo y la jefatura.Beneficio de salida anticipada los días viernes, lo que significa que podrás finalizar tu jornada laboral a las 14:00 horas.Acceso a beneficios de la Asociación Chilena de Seguridad y Caja Los Andes.Seguro de salud complementario, aplicable a partir de la contratación indefinida.Beneficios para el hogar, con descuentos preferenciales en productos y servicios.</t>
         </is>
       </c>
     </row>
@@ -9512,17 +9512,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Analista Contable Jr.</t>
+          <t>Analista de Planificación Financiera</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>KiosClub</t>
+          <t>CGE</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Las Condes, Chile</t>
+          <t>las condes, Chile</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -9532,15 +9532,15 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55157/analista-contable-jr</t>
+          <t>https://firstjob.me/oferta/55606/analista-de-planificacion-financiera</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>analisis, excel</t>
+          <t>analisis</t>
         </is>
       </c>
       <c r="I135" t="n">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="Q135" t="inlineStr">
         <is>
-          <t>KiosClub American SupermarketSomos una empresa que surge en 2017 con el propósito de acercar productos internacionales al mercado chileno, con una propuesta diferenciada basada en marcas norteamericanas. Nuestro foco está en la variedad, la innovación y un servicio cercano.Hoy contamos con más de 50 tiendas a lo largo de todo el país y seguimos creciendo. Nuestra misión es ofrecer una experiencia de compra dinámica y entretenida, manteniendo estándares claros en nuestros productos y en la forma en que operamos.¡Estamos buscando a nuestro/a próximo/a Analista Contable Jr.!Si te apasiona el mundo de las finanzas y quieres desarrollarte en el área contable dentro de una empresa en crecimiento,esta oportunidad es para ti.Buscamos a una personaresponsable, organizada y con ganas de aprender, que quiera aportar al registro, análisis y conciliación de transacciones contables, asegurando una gestión financiera eficiente y ordenada.Tus principales responsabilidades serán:Registrar y analizar transacciones contables, asegurando la precisión de la información financiera.Apoyar en la preparación de informes y reportes de gestión contable.Colaborar en conciliaciones bancarias y contables.Participar en el análisis y seguimiento del flujo de efectivo.Asistir en el cumplimiento de normas y regulaciones contables vigentes.Mantener registros organizados y actualizados.Colaborar en procesos de auditoría interna y externa.Revisar y controlar documentos contables, garantizando su correcta validación y archivo.Apoyar a otras áreas en temas financieros y administrativos.Requisitos para postular:Título técnico o universitario enContabilidad, Auditoría o carrera afín.Entre 0 y 2 años de experiencia en funciones contables y financieras (ideal en empresas medianas o grandes).Conocimientos de principios contables y normativas vigentes.Manejo intermedio de Excel.Uso de software contable o sistemas ERP (deseable).Experiencia en conciliaciones bancarias y gestión de flujo de caja.Si estás buscando una oportunidad para crecer profesionalmente y ser parte de un equipo dinámico, ¡te invitamos a postular!BeneficiosDías de teletrabajo disponibles durante el año (10), para favorecer la flexibilidad y conciliación laboral.Días libres adicionales, sin límite anual, orientados a la flexibilidad laboral, sin goce de sueldo y previa coordinación con el equipo y la jefatura.Beneficio de salida anticipada los días viernes, lo que significa que podrás finalizar tu jornada laboral a las 14:00 horas.Acceso a beneficios de la Asociación Chilena de Seguridad y Caja Los Andes.Seguro de salud complementario, aplicable a partir de la contratación indefinida.Beneficios para el hogar, con descuentos preferenciales en productos y servicios.</t>
+          <t>¡Te invitamos a formar parte de CGE, uno de los conglomerados energéticos más importantes del país!, donde podrás encontrar un ambiente dinámico y desafiante, para desarrollar tus habilidades y contribuir a continuar entregando a Chile la energía que necesita.Buscamos al próximoAnalista Planificación Financierapara desempeñarse enLas CondesSus funciones principales serán:Analizar la financiación del Grupo CGE.Evaluar la estructura de financiamiento, incluyendo créditos bancarios, bonos y otros instrumentos.Elaborar y dar seguimiento al flujo de caja del Grupo CGE.Analizar y ejecutar instrumentos de cobertura y derivados financieros.Mantener relación con bancos e instituciones financieras.Participar en procesos de clasificación de riesgo con agencias locales e internacionales.Preparar análisis financieros, notas de riesgo y análisis razonado de estados financieros.Elaborar el presupuesto anual financiero y forecast.Utilizar modelos de proyecciones financieras para apoyar la toma de decisiones estratégicas.BeneficiosBono anual por Gestión de DesempeñoSeguro de Salud ComplementarioDía libre para el cumpleaños, 24 diciembre y 31 de diciembre.Entre otros atractivos beneficios</t>
         </is>
       </c>
     </row>
@@ -9581,64 +9581,64 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Analista de Planificación Financiera</t>
+          <t>Customer Success Associate</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CGE</t>
+          <t>Wherex</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>las condes, Chile</t>
+          <t>Región Metropolitana de Santiago, Chile</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55606/analista-de-planificacion-financiera</t>
+          <t>https://firstjob.me/oferta/55682/customer-success-associate</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>analisis</t>
+          <t>modelo, analisis, excel, power bi</t>
         </is>
       </c>
       <c r="I136" t="n">
         <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
         <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>¡Te invitamos a formar parte de CGE, uno de los conglomerados energéticos más importantes del país!, donde podrás encontrar un ambiente dinámico y desafiante, para desarrollar tus habilidades y contribuir a continuar entregando a Chile la energía que necesita.Buscamos al próximoAnalista Planificación Financierapara desempeñarse enLas CondesSus funciones principales serán:Analizar la financiación del Grupo CGE.Evaluar la estructura de financiamiento, incluyendo créditos bancarios, bonos y otros instrumentos.Elaborar y dar seguimiento al flujo de caja del Grupo CGE.Analizar y ejecutar instrumentos de cobertura y derivados financieros.Mantener relación con bancos e instituciones financieras.Participar en procesos de clasificación de riesgo con agencias locales e internacionales.Preparar análisis financieros, notas de riesgo y análisis razonado de estados financieros.Elaborar el presupuesto anual financiero y forecast.Utilizar modelos de proyecciones financieras para apoyar la toma de decisiones estratégicas.BeneficiosBono anual por Gestión de DesempeñoSeguro de Salud ComplementarioDía libre para el cumpleaños, 24 diciembre y 31 de diciembre.Entre otros atractivos beneficios</t>
+          <t>En Wherex buscamos a nuestro/a próximo/aCustomer Success Associate– Santiago, ChileEstamos enfocados en transformar el comercio B2B con la aplicación de tecnología de vanguardia para optimizar la toma de decisiones en el abastecimiento industrial, teniendo como pilares fundamentales la competencia, transparencia y eficiencia en las compras industriales.Buscamos a un Customer Success Associate para integrarse al equipo de Chile y fortalecer la ejecución operativa y analítica del área, habilitando a los CSMs a enfocarse en la gestión estratégica de clientes. Este rol es clave para escalar el modelo de Customer Success, combinando ejecución operativa, análisis de datos y soporte directo a cuentas, con alta exposición al funcionamiento real del negocio.Funciones:🎯 Atención y soporte a usuarios compradores: Entregar soluciones ágiles y de calidad a los requerimientos del día a día: conocer el producto de Wherex y la relevancia de su buen uso, gestionar cambios solicitados por los clientes (fechas, precios, estados), acompañar a los usuarios en sus primeros pasos con capacitaciones y asesoría continua, atender solicitudes en tiempo y forma, y sugerir mejoras en procesos que puedan automatizarse.🔗 Apoyo en gestión de licitaciones (COE): Ser el punto de contacto principal entre el usuario y el área de operaciones comerciales, solicitar asignación y prioridad entregando contexto oportuno del cliente al COE, coordinar con proveedores (incluyendo su inscripción y resolución de problemas), garantizar que la información relevante llegue a los usuarios de forma ordenada y eficiente, y buscar constantemente eficiencias para mejorar el proceso.📊 Reportería y análisis de valor: Usar Power BI como base principal para el armado de reportería en conjunto con el Manager, preparar y enviar el Reporte de Gestión Mensual, y dar seguimiento a los KPIs clave: GTV, GMV, Comisiones, WAU y clientes críticos.🤝 Gestión de portafolio junto al Manager: Gestionar licitaciones mal adjudicadas y en evaluación buscando adjudicaciones en el menor tiempo posible, preparar materiales para reuniones (reportes, avances, pendientes), dar seguimiento a compromisos post-reunión, y proponer eficiencias y mejoras continuas sobre la gestión de la cartera.Lo que buscamos en ti:Experiencia: 0–2 años (prácticas o primeros roles en operaciones, análisis o clientes).Perfil analítico: Alta capacidad analítica y manejo de Excel / Google Sheets. Power BI es un plus.Orden y detalle: Atención al detalle y capacidad de seguimiento riguroso.Proactividad: Disposición a aprender rápido y trabajar en entornos dinámicos y poco estructurados.Comunicación: Buenas habilidades para comunicar información de forma clara y oportuna.Valoramos: Interés en Customer Success, tecnología o modelos SaaS, y experiencia previa en roles operativos o analíticos.Beneficios🏖️ Días adicionales de descanso🏥 Seguro complementario de Salud⌚ Flexibilidad horaria😷 Licencia médica pagada durante dos días😎 Trabajo híbrido (oficina en Las Condes + remoto)</t>
         </is>
       </c>
     </row>
@@ -9650,12 +9650,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Customer Success Associate</t>
+          <t>ANALISTA DE DESARROLLO OPERACIONAL</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Wherex</t>
+          <t>BL CAPITAL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -9665,12 +9665,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55682/customer-success-associate</t>
+          <t>https://firstjob.me/oferta/55706/analista-de-desarrollo-operacional</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -9678,26 +9678,26 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>modelo, analisis, excel, power bi</t>
+          <t>sql, analisis, excel, power bi</t>
         </is>
       </c>
       <c r="I137" t="n">
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -9707,7 +9707,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>En Wherex buscamos a nuestro/a próximo/aCustomer Success Associate– Santiago, ChileEstamos enfocados en transformar el comercio B2B con la aplicación de tecnología de vanguardia para optimizar la toma de decisiones en el abastecimiento industrial, teniendo como pilares fundamentales la competencia, transparencia y eficiencia en las compras industriales.Buscamos a un Customer Success Associate para integrarse al equipo de Chile y fortalecer la ejecución operativa y analítica del área, habilitando a los CSMs a enfocarse en la gestión estratégica de clientes. Este rol es clave para escalar el modelo de Customer Success, combinando ejecución operativa, análisis de datos y soporte directo a cuentas, con alta exposición al funcionamiento real del negocio.Funciones:🎯 Atención y soporte a usuarios compradores: Entregar soluciones ágiles y de calidad a los requerimientos del día a día: conocer el producto de Wherex y la relevancia de su buen uso, gestionar cambios solicitados por los clientes (fechas, precios, estados), acompañar a los usuarios en sus primeros pasos con capacitaciones y asesoría continua, atender solicitudes en tiempo y forma, y sugerir mejoras en procesos que puedan automatizarse.🔗 Apoyo en gestión de licitaciones (COE): Ser el punto de contacto principal entre el usuario y el área de operaciones comerciales, solicitar asignación y prioridad entregando contexto oportuno del cliente al COE, coordinar con proveedores (incluyendo su inscripción y resolución de problemas), garantizar que la información relevante llegue a los usuarios de forma ordenada y eficiente, y buscar constantemente eficiencias para mejorar el proceso.📊 Reportería y análisis de valor: Usar Power BI como base principal para el armado de reportería en conjunto con el Manager, preparar y enviar el Reporte de Gestión Mensual, y dar seguimiento a los KPIs clave: GTV, GMV, Comisiones, WAU y clientes críticos.🤝 Gestión de portafolio junto al Manager: Gestionar licitaciones mal adjudicadas y en evaluación buscando adjudicaciones en el menor tiempo posible, preparar materiales para reuniones (reportes, avances, pendientes), dar seguimiento a compromisos post-reunión, y proponer eficiencias y mejoras continuas sobre la gestión de la cartera.Lo que buscamos en ti:Experiencia: 0–2 años (prácticas o primeros roles en operaciones, análisis o clientes).Perfil analítico: Alta capacidad analítica y manejo de Excel / Google Sheets. Power BI es un plus.Orden y detalle: Atención al detalle y capacidad de seguimiento riguroso.Proactividad: Disposición a aprender rápido y trabajar en entornos dinámicos y poco estructurados.Comunicación: Buenas habilidades para comunicar información de forma clara y oportuna.Valoramos: Interés en Customer Success, tecnología o modelos SaaS, y experiencia previa en roles operativos o analíticos.Beneficios🏖️ Días adicionales de descanso🏥 Seguro complementario de Salud⌚ Flexibilidad horaria😷 Licencia médica pagada durante dos días😎 Trabajo híbrido (oficina en Las Condes + remoto)</t>
+          <t>¿Quieres comenzar tu carrera entendiendo cómo funciona realmente una empresa financiera?En BL Capital, empresa de Factoring, líder en el mercado financiero, buscamos incorporar a un/aAnalista de Desarrollo Operacional, un rol diseñado para profesionales que quieran aprender el negocio desde su base y desarrollar una mirada integral de la organización.Creemos que las mejores ideas nacen de quienes conocen profundamente cómo trabajan las personas y cómo operan los procesos. Por eso, durante tus primeros meses participarás activamente en distintas áreas de la empresa, apoyando la operación diaria y conociendo de primera fuente el funcionamiento del negocio.Una vez adquirida esa experiencia, comenzarás a participar en proyectos de mejora continua, automatización, análisis de información y optimización de procesos, aportando soluciones con impacto real.¿QUE HARAS?Integrarte temporalmente a distintas áreas para conocer y apoyar la operación.Comprender el funcionamiento de los procesos y su impacto en nuestros clientes.Detectar oportunidades de mejora, simplificación y eficiencia.Participar en proyectos de automatización, análisis de datos e implementación de indicadores de gestión.Colaborar con diferentes equipos para impulsar mejoras operacionales.¿QUE BUSCAMOS?Más que experiencia, buscamos personas con potencial. Nos interesa alguien que sea curioso, analítico y observador; que disfrute entendiendo cómo funcionan las cosas antes de proponer cambios; que tenga iniciativa, capacidad para relacionarse con distintas áreas y ganas de aprender constantemente.ALGUNOS REQUISITOSRecién egresado/a o recién titulado/a de Ingeniería Civil Industrial.Interés por procesos, mejora continua y análisis de información.Manejo de Excel.Deseable conocimiento en Power BI, SQL y herramientas de análisis de datos.Interés por utilizar herramientas de Inteligencia Artificial para analizar información, automatizar tareas y optimizar procesos.Disponibilidad para trabajar presencialmente.Beneficios¿QUE TE OFRECEMOS?Una experiencia única para conocer el negocio financiero desde su operación.Un plan de aprendizaje que te permitirá comprender la empresa de manera integral.Participación en proyectos de mejora y transformación de procesos.Trabajo colaborativo con distintas áreas de la organización.Aprendizaje continuo, desafíos reales y oportunidades de desarrollo profesional.Un ambiente cercano, dinámico y orientado al crecimiento.Si te motiva aprender, hacer preguntas, entender cómo funciona un negocio y dejar las cosas mejor de como las encontraste, nos gustaría conocerte.</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ANALISTA DE DESARROLLO OPERACIONAL</t>
+          <t>Category Manager de E-commerce - Colina (Híbrido)</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BL CAPITAL</t>
+          <t>Rosen</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -9734,20 +9734,20 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55706/analista-de-desarrollo-operacional</t>
+          <t>https://firstjob.me/oferta/55152/category-manager-de-e-commerce-colina-hibrido</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>sql, analisis, excel, power bi</t>
+          <t>analisis, excel</t>
         </is>
       </c>
       <c r="I138" t="n">
@@ -9757,7 +9757,7 @@
         <v>0</v>
       </c>
       <c r="K138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138" t="n">
         <v>1</v>
@@ -9766,17 +9766,17 @@
         <v>0</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O138" t="n">
         <v>0</v>
       </c>
       <c r="P138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="inlineStr">
         <is>
-          <t>¿Quieres comenzar tu carrera entendiendo cómo funciona realmente una empresa financiera?En BL Capital, empresa de Factoring, líder en el mercado financiero, buscamos incorporar a un/aAnalista de Desarrollo Operacional, un rol diseñado para profesionales que quieran aprender el negocio desde su base y desarrollar una mirada integral de la organización.Creemos que las mejores ideas nacen de quienes conocen profundamente cómo trabajan las personas y cómo operan los procesos. Por eso, durante tus primeros meses participarás activamente en distintas áreas de la empresa, apoyando la operación diaria y conociendo de primera fuente el funcionamiento del negocio.Una vez adquirida esa experiencia, comenzarás a participar en proyectos de mejora continua, automatización, análisis de información y optimización de procesos, aportando soluciones con impacto real.¿QUE HARAS?Integrarte temporalmente a distintas áreas para conocer y apoyar la operación.Comprender el funcionamiento de los procesos y su impacto en nuestros clientes.Detectar oportunidades de mejora, simplificación y eficiencia.Participar en proyectos de automatización, análisis de datos e implementación de indicadores de gestión.Colaborar con diferentes equipos para impulsar mejoras operacionales.¿QUE BUSCAMOS?Más que experiencia, buscamos personas con potencial. Nos interesa alguien que sea curioso, analítico y observador; que disfrute entendiendo cómo funcionan las cosas antes de proponer cambios; que tenga iniciativa, capacidad para relacionarse con distintas áreas y ganas de aprender constantemente.ALGUNOS REQUISITOSRecién egresado/a o recién titulado/a de Ingeniería Civil Industrial.Interés por procesos, mejora continua y análisis de información.Manejo de Excel.Deseable conocimiento en Power BI, SQL y herramientas de análisis de datos.Interés por utilizar herramientas de Inteligencia Artificial para analizar información, automatizar tareas y optimizar procesos.Disponibilidad para trabajar presencialmente.Beneficios¿QUE TE OFRECEMOS?Una experiencia única para conocer el negocio financiero desde su operación.Un plan de aprendizaje que te permitirá comprender la empresa de manera integral.Participación en proyectos de mejora y transformación de procesos.Trabajo colaborativo con distintas áreas de la organización.Aprendizaje continuo, desafíos reales y oportunidades de desarrollo profesional.Un ambiente cercano, dinámico y orientado al crecimiento.Si te motiva aprender, hacer preguntas, entender cómo funciona un negocio y dejar las cosas mejor de como las encontraste, nos gustaría conocerte.</t>
+          <t>📢¡Si te gusta la decoración, el mundo del descanso familiar, Rosen es para ti!Estamos buscando nuevos y nuevas RosenLovers que quieran ser parte de una de las mejores empresas para trabajar en Chile, ranking GPTW 2024. Buscamos el ADN Rosen en cada uno de nuestros/as colaboradores/as, potenciando la Excelencia, Integridad, Compromiso e Innovación.En Rosen creemos en el valor de las personas y en la riqueza de equipos diversos. Por eso, promovemos procesos de selección inclusivos y si necesitas algún ajuste para participar en el proceso, puedes indicarlo en tu postulación. Esta vacante se enmarca en nuestro compromiso con la inclusión laboral y la Ley 21.015.Actualmente nos encontramos en búsqueda de un/aCategory Managera trabajar para nuestra Gerencia de E-commerce en Modalidad Híbrida, en nuestras oficinas ubicadas en la comuna de Colina, Región Metropolitana.🔍¿Cuál es la misión de este rol?Ejecutar, implementar y controlar de forma permanente el desarrollo de la estrategia definida por la Gerencia de E-Commerce, a través del análisis de variables de venta (conversión, contribución, margen, entre otros), con el fin de alcanzar las metas y objetivos definidos en la planificación.💡¿Qué harás en este cargo?Apoyar la gestión comercial del canal eCommerce, realizando seguimiento a ventas, contribución y margen para asegurar el cumplimiento de los objetivos del negocio.Diseñar e implementar campañas, estrategias de venta cruzada y acciones de optimización orientadas a mejorar la conversión y la experiencia de compra.Gestionar la operación diaria del canal en Magento, asegurando la correcta publicación de productos, el ordenamiento de categorías (PLP) y la actualización permanente del sitio.Analizar indicadores de negocio, elaborar reportería de gestión y monitorear tendencias de mercado y competencia para identificar oportunidades de crecimiento y apoyar la toma de decisiones.Gestionar el surtido y monitorear la disponibilidad de stock, asegurando una propuesta comercial alineada con la demanda y los objetivos del canal.📌¿Cuáles son los requisitos para rol?Titulado/a en Ingeniería Comercial.Desde práctica profesional hasta 1 año de experiencia laboral idealmente áreas comerciales, marketing, e-commerce o gestión de categoríasManejo de excel intermedio.Disponibilidad para trabajar en modalidad híbrida en Colina (4 días presencial, contamos con estacionamiento y buses de acercamiento).¡Te invitamos a ser parte de una compañía comprometida con sus colaboradores y la sustentabilidad!🌱🙌BeneficiosBeneficios de nuestro team Rosen 🎁:Jornada laboral de 40 horas.Bono de vacaciones 🏝Aguinaldos.30% de descuentos en Productos Rosen.Seguro Complementario de Salud (desde contrato indefinido).Día Libre de Cumpleaños 🎈Regalos Corporativos 🎁Casino corporativo 🍝 y Buses de acercamiento.¡Entre muchos otros!</t>
         </is>
       </c>
     </row>
@@ -9788,12 +9788,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Category Manager de E-commerce - Colina (Híbrido)</t>
+          <t>Ejecutivo Cliente Banca Personas - Región Metropolitana</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Rosen</t>
+          <t>Itaú</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -9803,22 +9803,18 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55152/category-manager-de-e-commerce-colina-hibrido</t>
+          <t>https://firstjob.me/oferta/55596/ejecutivo-cliente-banca-personas-region-metropolitana</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>3</v>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>analisis, excel</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H139" t="inlineStr"/>
       <c r="I139" t="n">
         <v>0</v>
       </c>
@@ -9845,7 +9841,7 @@
       </c>
       <c r="Q139" t="inlineStr">
         <is>
-          <t>📢¡Si te gusta la decoración, el mundo del descanso familiar, Rosen es para ti!Estamos buscando nuevos y nuevas RosenLovers que quieran ser parte de una de las mejores empresas para trabajar en Chile, ranking GPTW 2024. Buscamos el ADN Rosen en cada uno de nuestros/as colaboradores/as, potenciando la Excelencia, Integridad, Compromiso e Innovación.En Rosen creemos en el valor de las personas y en la riqueza de equipos diversos. Por eso, promovemos procesos de selección inclusivos y si necesitas algún ajuste para participar en el proceso, puedes indicarlo en tu postulación. Esta vacante se enmarca en nuestro compromiso con la inclusión laboral y la Ley 21.015.Actualmente nos encontramos en búsqueda de un/aCategory Managera trabajar para nuestra Gerencia de E-commerce en Modalidad Híbrida, en nuestras oficinas ubicadas en la comuna de Colina, Región Metropolitana.🔍¿Cuál es la misión de este rol?Ejecutar, implementar y controlar de forma permanente el desarrollo de la estrategia definida por la Gerencia de E-Commerce, a través del análisis de variables de venta (conversión, contribución, margen, entre otros), con el fin de alcanzar las metas y objetivos definidos en la planificación.💡¿Qué harás en este cargo?Apoyar la gestión comercial del canal eCommerce, realizando seguimiento a ventas, contribución y margen para asegurar el cumplimiento de los objetivos del negocio.Diseñar e implementar campañas, estrategias de venta cruzada y acciones de optimización orientadas a mejorar la conversión y la experiencia de compra.Gestionar la operación diaria del canal en Magento, asegurando la correcta publicación de productos, el ordenamiento de categorías (PLP) y la actualización permanente del sitio.Analizar indicadores de negocio, elaborar reportería de gestión y monitorear tendencias de mercado y competencia para identificar oportunidades de crecimiento y apoyar la toma de decisiones.Gestionar el surtido y monitorear la disponibilidad de stock, asegurando una propuesta comercial alineada con la demanda y los objetivos del canal.📌¿Cuáles son los requisitos para rol?Titulado/a en Ingeniería Comercial.Desde práctica profesional hasta 1 año de experiencia laboral idealmente áreas comerciales, marketing, e-commerce o gestión de categoríasManejo de excel intermedio.Disponibilidad para trabajar en modalidad híbrida en Colina (4 días presencial, contamos con estacionamiento y buses de acercamiento).¡Te invitamos a ser parte de una compañía comprometida con sus colaboradores y la sustentabilidad!🌱🙌BeneficiosBeneficios de nuestro team Rosen 🎁:Jornada laboral de 40 horas.Bono de vacaciones 🏝Aguinaldos.30% de descuentos en Productos Rosen.Seguro Complementario de Salud (desde contrato indefinido).Día Libre de Cumpleaños 🎈Regalos Corporativos 🎁Casino corporativo 🍝 y Buses de acercamiento.¡Entre muchos otros!</t>
+          <t>¡¡En Itaú Chile buscamos talentos con ganas de desafiarse y ser protagonistas!!, postula comoEjecutivo de Cuentas para nuestra red de sucursales en la Región Metropolitana, tenemos presencia en todas las comunas del país.  Donde tú misión como Ejecutivo será: administrar una cartera de clientes, con foco en generar un relacionamiento continuo a través de la comunicación oportuna, preocupándose de la mantención de sus productos, atención de necesidades y oferta de nuevos negocios.Principales funciones:Administración de cartera y venta de productos financieros (seguros, ctas ctes, créditos, etc).Captación de nuevos clientesProporcionar una atención personalizada y diferenciadora que implica la fidelización de sus clientes mediante un servicio de excelenciaRequisitos deseados:Idealmente haber realizado tu práctica profesional en la Banca en un rol similar.Contar con experiencia en ventas y atención de clientes.Ser titulado de Ingeniería Comercial, Administración, Financiero o carrera afín.Beneficios¡Ofrecemos una propuesta de beneficios integrales para ti, enfocados en tu tiempo, familia, salud, desarrollo de carrera, momentos especiales, y mucho más!Jornada laboral de 40 horasModelo de trabajo hibrido (dependiendo de tus funciones).32 horas o 4 días libres al año que puedes usarlos como quieras.Voy y vuelvo: Disfruta de 3 meses sin goce de sueldo para cumplir tus sueños.Medio día libre por tu cumpleaños.Seguro complementario de salud, catastrófico y dental, además de seguro de vida.Beneficios de conciliación y equilibrio de vida laboral y personal.Acceso a oportunidades que potencien tu formación y desarrollo profesional.Bonos de navidad, fiestas patrias, vacaciones, matrimonio, entre otros y mucho más.Encuentra el detalle en: https://trabajaenitau.cl/content/Beneficios/?locale=es_ESValoramos el talento diverso, equidad e inclusión.Nos preocupamos por el valor de las personas y sus ideas. Somos por segundo año consecutivo certificados por Equidad.CL como uno de los mejores lugares para trabajar para el talento LGBTIQ+ y tenemos una estrategia de equidad de género, siendo reconocidos como la 4ta empresa de GPTW mujeres. También, reforzamos nuestro compromiso con la inclusión laboral de las personas en situación de discapacidad. Por ello, te invitamos a participar en nuestras búsquedas.¿Y tú? Estás listo para ser un Itubers, ¡te esperamos!¡Postula!</t>
         </is>
       </c>
     </row>
@@ -9857,12 +9853,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ejecutivo Cliente Banca Personas - Región Metropolitana</t>
+          <t>Trainee Operativo Marine - 01 año</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Itaú</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -9872,20 +9868,24 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55596/ejecutivo-cliente-banca-personas-region-metropolitana</t>
+          <t>https://firstjob.me/oferta/55578/trainee-operativo-marine-01-ano</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
-      </c>
-      <c r="H140" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>analisis, trainee, excel</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -9894,7 +9894,7 @@
         <v>1</v>
       </c>
       <c r="L140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
@@ -9903,14 +9903,14 @@
         <v>1</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P140" t="n">
         <v>0</v>
       </c>
       <c r="Q140" t="inlineStr">
         <is>
-          <t>¡¡En Itaú Chile buscamos talentos con ganas de desafiarse y ser protagonistas!!, postula comoEjecutivo de Cuentas para nuestra red de sucursales en la Región Metropolitana, tenemos presencia en todas las comunas del país.  Donde tú misión como Ejecutivo será: administrar una cartera de clientes, con foco en generar un relacionamiento continuo a través de la comunicación oportuna, preocupándose de la mantención de sus productos, atención de necesidades y oferta de nuevos negocios.Principales funciones:Administración de cartera y venta de productos financieros (seguros, ctas ctes, créditos, etc).Captación de nuevos clientesProporcionar una atención personalizada y diferenciadora que implica la fidelización de sus clientes mediante un servicio de excelenciaRequisitos deseados:Idealmente haber realizado tu práctica profesional en la Banca en un rol similar.Contar con experiencia en ventas y atención de clientes.Ser titulado de Ingeniería Comercial, Administración, Financiero o carrera afín.Beneficios¡Ofrecemos una propuesta de beneficios integrales para ti, enfocados en tu tiempo, familia, salud, desarrollo de carrera, momentos especiales, y mucho más!Jornada laboral de 40 horasModelo de trabajo hibrido (dependiendo de tus funciones).32 horas o 4 días libres al año que puedes usarlos como quieras.Voy y vuelvo: Disfruta de 3 meses sin goce de sueldo para cumplir tus sueños.Medio día libre por tu cumpleaños.Seguro complementario de salud, catastrófico y dental, además de seguro de vida.Beneficios de conciliación y equilibrio de vida laboral y personal.Acceso a oportunidades que potencien tu formación y desarrollo profesional.Bonos de navidad, fiestas patrias, vacaciones, matrimonio, entre otros y mucho más.Encuentra el detalle en: https://trabajaenitau.cl/content/Beneficios/?locale=es_ESValoramos el talento diverso, equidad e inclusión.Nos preocupamos por el valor de las personas y sus ideas. Somos por segundo año consecutivo certificados por Equidad.CL como uno de los mejores lugares para trabajar para el talento LGBTIQ+ y tenemos una estrategia de equidad de género, siendo reconocidos como la 4ta empresa de GPTW mujeres. También, reforzamos nuestro compromiso con la inclusión laboral de las personas en situación de discapacidad. Por ello, te invitamos a participar en nuestras búsquedas.¿Y tú? Estás listo para ser un Itubers, ¡te esperamos!¡Postula!</t>
+          <t>La posición es responsable de gestionar y ser vínculo entre línea de negocios y departamento de operaciones a través del envío a emisión de diferentes documentos tales como pólizas, endosos, declaraciones y/o cualquier otro documento necesario para el funcionamiento natural de poliza de seguros.Mantener contacto con intermediarios de pólizas de seguros con el fin de resolver distintas consultas propias de la línea de negocios de seguro de transporte/contenedores.Además, dentro de sus responsabilidades, estará el ser el administrador de portfolio de carga y contenedores, monitorear los cierres mensuales para la línea y preparar información para planificación anual.Realizar cierres mensuales y cuadraturas con los distintos puntos de venta de programa contenedores.Realizar capacitaciones (internas o externas) en el uso de nuestras plataformas de emisión.MAJOR DUTIES &amp; RESPONSIBILITIES:Está a cargo de revisar, ordenar y completar la documentación, así como de las planillas de seguimiento y control de gestión de producción mensual, de sus actividades.Gestión y mantención de negocios.Atención comercial a corredores (servicio rápido con correos y telefónicamente, y asistir a las reuniones con corredores que establezca con su jefatura).Emisión de pólizas, endosos y certificados.Correcta y completa generación de reportes mensuales, locales y regionales.Verificar que las propuestas de emisión de las cuentas a su cargo estén acordes a las cotizaciones que entregó de modo de poder emitir las pólizas en forma correcta.Gestionar de forma correcta y completa la información de los negocios a su cargo.Planilla de control mensual y reportes de indicadores de gestión del área.Apoya a su Jefatura en las gestiones de Cobranzas, tanto en las reuniones periódicas establecidas como contactando a los corredores para actualizar los pagos.Envío de informes semanales con la producción de contenedores.Enviar detalle de producción mensual a las distintas navieras por el producto contenedores.Calcular y cuadrar producción para su posterior factura de producto contenedores.Parametrizar gastos en programa internoRealizar capacitaciones de nuestra plataforma a distintos usuarios.Liderar algunos proyectos internos asociados a plataformas utilizadas.CalificacionesAdministrador de Empresas, Comercio Exterior u otra afín*Dominio avanzado de office (Excel -Word- PP).Muy buen nivel de redacción y ortografía.Inglés deseable.Excelente actitud de servicio, proactividad, responsabilidad, dinamismo y autogestión.Contar con habilidad para poder manejar situaciones de presión ante los cierres de mes, así como inmediatez para responder a pedidos de informe urgente.Habilidades interpersonales para relacionarse con todos los niveles de la organización.Capacidad de asesoría a clientes internos.Capacidad de análisis para toma de decisiones.Deseable Experiencia en seguros en prácticas o trabajos de 1 año.Conocimiento del mercado asegurador local.</t>
         </is>
       </c>
     </row>
@@ -9922,12 +9922,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Trainee Operativo Marine - 01 año</t>
+          <t>Moneda Patria Academy - Trainee Program 2027</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>Moneda Patria Investments</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -9937,20 +9937,20 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55578/trainee-operativo-marine-01-ano</t>
+          <t>https://firstjob.me/oferta/55527/moneda-patria-academy-trainee-program-2027</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>analisis, trainee, excel</t>
+          <t>trainee</t>
         </is>
       </c>
       <c r="I141" t="n">
@@ -9960,16 +9960,16 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
       </c>
       <c r="N141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O141" t="n">
         <v>1</v>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>La posición es responsable de gestionar y ser vínculo entre línea de negocios y departamento de operaciones a través del envío a emisión de diferentes documentos tales como pólizas, endosos, declaraciones y/o cualquier otro documento necesario para el funcionamiento natural de poliza de seguros.Mantener contacto con intermediarios de pólizas de seguros con el fin de resolver distintas consultas propias de la línea de negocios de seguro de transporte/contenedores.Además, dentro de sus responsabilidades, estará el ser el administrador de portfolio de carga y contenedores, monitorear los cierres mensuales para la línea y preparar información para planificación anual.Realizar cierres mensuales y cuadraturas con los distintos puntos de venta de programa contenedores.Realizar capacitaciones (internas o externas) en el uso de nuestras plataformas de emisión.MAJOR DUTIES &amp; RESPONSIBILITIES:Está a cargo de revisar, ordenar y completar la documentación, así como de las planillas de seguimiento y control de gestión de producción mensual, de sus actividades.Gestión y mantención de negocios.Atención comercial a corredores (servicio rápido con correos y telefónicamente, y asistir a las reuniones con corredores que establezca con su jefatura).Emisión de pólizas, endosos y certificados.Correcta y completa generación de reportes mensuales, locales y regionales.Verificar que las propuestas de emisión de las cuentas a su cargo estén acordes a las cotizaciones que entregó de modo de poder emitir las pólizas en forma correcta.Gestionar de forma correcta y completa la información de los negocios a su cargo.Planilla de control mensual y reportes de indicadores de gestión del área.Apoya a su Jefatura en las gestiones de Cobranzas, tanto en las reuniones periódicas establecidas como contactando a los corredores para actualizar los pagos.Envío de informes semanales con la producción de contenedores.Enviar detalle de producción mensual a las distintas navieras por el producto contenedores.Calcular y cuadrar producción para su posterior factura de producto contenedores.Parametrizar gastos en programa internoRealizar capacitaciones de nuestra plataforma a distintos usuarios.Liderar algunos proyectos internos asociados a plataformas utilizadas.CalificacionesAdministrador de Empresas, Comercio Exterior u otra afín*Dominio avanzado de office (Excel -Word- PP).Muy buen nivel de redacción y ortografía.Inglés deseable.Excelente actitud de servicio, proactividad, responsabilidad, dinamismo y autogestión.Contar con habilidad para poder manejar situaciones de presión ante los cierres de mes, así como inmediatez para responder a pedidos de informe urgente.Habilidades interpersonales para relacionarse con todos los niveles de la organización.Capacidad de asesoría a clientes internos.Capacidad de análisis para toma de decisiones.Deseable Experiencia en seguros en prácticas o trabajos de 1 año.Conocimiento del mercado asegurador local.</t>
+          <t>Moneda Patria Academyes nuestro programa de Trainees, el cual tiene como objetivo convocar a los mejores profesionales de las universidades más prestigiosas del país, quienes busquen desplegar su máximo potencial dentro de un entorno de alto desempeño, permitiéndoles ser parte de una experiencia llena de aprendizaje, conocimiento y colaboración.Diseñamos el programa con el objetivo de fomentar el crecimiento y desarrollo de talento a largo plazo, promoviendo oportunidades de aprendizaje personalizado que permite a los participantes adquirir habilidades específicas y conocimientos relevantes para sus áreas de interés.Moneda Patria Academyincluye un itinerario de desarrollo construido durante 12 meses. El cual tomará lugar entreFebrero de 2027 a Febrero de 2028, donde tendrás la oportunidad de conocer nuestra compañía y comprender el funcionamiento y labores realizadas en las diversas áreas de nuestro negocio, entre ellas:Equities, Fixed Income, Institutional Clients y Wealth Management.Dentro de esos 12 meses, podrás inclusive trabajar de manera aleatoria en 2 de esas 4 áreas ya mencionadas, siendo parte de un programa que te permitirá rotar después de los primeros 6 meses, permitiéndote conocer más de un área en particular.Esta oportunidad, además, te permitirá trabajar a tiempo completo con nosotros, de manera tal que puedas empaparte del día a día de un Moneda Patria Employee.Nuestro objetivo es atraer y retener el talento, brindando un entorno desafiante y oportunidades de desarrollo que promuevan y contribuyan al éxito de nuestra empresa.¡Te invitamos a sumarte a este desafío y formar parte de la tercera edición de nuestro programa Moneda Patria Academy 2027, te esperamos!Link de Postulación Formal:Moneda Patria Academy Chile - Trainee Program 2027 - Patria InvestmentsRequisitos:Profesional recién egresado.Carreras Afin: Ingeniería Comercial / Ingeniería Civil Industrial / Economía.Dominio de Inglés Avanzado.Disponibilidad para trabajar de manera presencial desde nuestra oficina de Santiago.Duración del programa: 12 meses (Febrero 2027 a Febrero 2028).Modalidad Full Time.Etapas del Proceso:Inscripciones abiertas hasta el 25 de septiembre.Test Online (Inicios de Octubre)Focus Group Interview (Mediados de Octubre)Case Study (Inicios Noviembre)Hiring Manager Interview (Mediados de Noviembre)Extensión de Ofertas (Finales de Noviembre)Inicio previsto para Febrero de 2027.BeneficiosSerás parte de un programa de aprendizaje centrado en la excelencia, con la posibilidad de interactuar con equipos de alto desempeño y líderes dedicados a desafiar al máximo el potencial de nuestros Trainees.Tendrás capacitaciones y entrenamientos en temáticas relevantes que te permitirán adquirir herramientas, favoreciendo el buen desempeño a lo largo de todo el programa.</t>
         </is>
       </c>
     </row>
@@ -9991,12 +9991,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Moneda Patria Academy - Trainee Program 2027</t>
+          <t>Ingeniero Desarrollo Organizacional (Ing. Comercial)</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Moneda Patria Investments</t>
+          <t>Confidencial</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -10006,33 +10006,33 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55527/moneda-patria-academy-trainee-program-2027</t>
+          <t>https://firstjob.me/oferta/55456/ingeniero-desarrollo-organizacional-ing-comercial</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>trainee</t>
+          <t>analisis, excel</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
@@ -10041,14 +10041,14 @@
         <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>Moneda Patria Academyes nuestro programa de Trainees, el cual tiene como objetivo convocar a los mejores profesionales de las universidades más prestigiosas del país, quienes busquen desplegar su máximo potencial dentro de un entorno de alto desempeño, permitiéndoles ser parte de una experiencia llena de aprendizaje, conocimiento y colaboración.Diseñamos el programa con el objetivo de fomentar el crecimiento y desarrollo de talento a largo plazo, promoviendo oportunidades de aprendizaje personalizado que permite a los participantes adquirir habilidades específicas y conocimientos relevantes para sus áreas de interés.Moneda Patria Academyincluye un itinerario de desarrollo construido durante 12 meses. El cual tomará lugar entreFebrero de 2027 a Febrero de 2028, donde tendrás la oportunidad de conocer nuestra compañía y comprender el funcionamiento y labores realizadas en las diversas áreas de nuestro negocio, entre ellas:Equities, Fixed Income, Institutional Clients y Wealth Management.Dentro de esos 12 meses, podrás inclusive trabajar de manera aleatoria en 2 de esas 4 áreas ya mencionadas, siendo parte de un programa que te permitirá rotar después de los primeros 6 meses, permitiéndote conocer más de un área en particular.Esta oportunidad, además, te permitirá trabajar a tiempo completo con nosotros, de manera tal que puedas empaparte del día a día de un Moneda Patria Employee.Nuestro objetivo es atraer y retener el talento, brindando un entorno desafiante y oportunidades de desarrollo que promuevan y contribuyan al éxito de nuestra empresa.¡Te invitamos a sumarte a este desafío y formar parte de la tercera edición de nuestro programa Moneda Patria Academy 2027, te esperamos!Link de Postulación Formal:Moneda Patria Academy Chile - Trainee Program 2027 - Patria InvestmentsRequisitos:Profesional recién egresado.Carreras Afin: Ingeniería Comercial / Ingeniería Civil Industrial / Economía.Dominio de Inglés Avanzado.Disponibilidad para trabajar de manera presencial desde nuestra oficina de Santiago.Duración del programa: 12 meses (Febrero 2027 a Febrero 2028).Modalidad Full Time.Etapas del Proceso:Inscripciones abiertas hasta el 25 de septiembre.Test Online (Inicios de Octubre)Focus Group Interview (Mediados de Octubre)Case Study (Inicios Noviembre)Hiring Manager Interview (Mediados de Noviembre)Extensión de Ofertas (Finales de Noviembre)Inicio previsto para Febrero de 2027.BeneficiosSerás parte de un programa de aprendizaje centrado en la excelencia, con la posibilidad de interactuar con equipos de alto desempeño y líderes dedicados a desafiar al máximo el potencial de nuestros Trainees.Tendrás capacitaciones y entrenamientos en temáticas relevantes que te permitirán adquirir herramientas, favoreciendo el buen desempeño a lo largo de todo el programa.</t>
+          <t>Tenemos una oportunidad increíble!Para nuestraGerencia de Personasbuscamos unIngeniero Comercial.El propósito de este rol es apoyar la gestión de la Subgerencia de Desarrollo Organizacional en el proceso de análisis de datos, reportería general, diseño de Encuestas, gestión en las actividades corporativas del área y contribuir a los objetivos de nuestra Gerencia y de la organización.Te Pedimos:Titulo profesional de Ingeniero Comercial.Experiencia de 0 a 2 años máximo.Conocimientos y manejo de herramientas y técnicas de Evaluación.Buen manejo Excel y PBI (Excluyente)Manejo de IA para distintos procesos que faciliten la gestión (Excluyente)Alta capacidad de análisis.Habilidades interpersonales destacadas.¡Te ofrecemosun ambiente laboral de alto nivel profesional, entorno flexible y colaborativo, oportunidades de enfrentar desafíos y atractivos beneficios!Si te gustan los desafíos, quieres pensar fuera de la caja y cumples los requisitos, envíanos tu CV y estarás más cerca de poder integrarte a nuestro equipo.Beneficios- Seguro complementario- Bono vacaciones- Bonos fiestas patrias y navidad- días administrativos</t>
         </is>
       </c>
     </row>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ingeniero Desarrollo Organizacional (Ing. Comercial)</t>
+          <t>Ingeniero de Datos</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Confidencial</t>
+          <t>Tanner</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -10080,15 +10080,15 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55456/ingeniero-desarrollo-organizacional-ing-comercial</t>
+          <t>https://firstjob.me/oferta/55216/ingeniero-de-datos</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>analisis, excel</t>
+          <t>etl, informatica, power bi</t>
         </is>
       </c>
       <c r="I143" t="n">
@@ -10107,7 +10107,7 @@
         <v>0</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O143" t="n">
         <v>0</v>
@@ -10117,7 +10117,7 @@
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>Tenemos una oportunidad increíble!Para nuestraGerencia de Personasbuscamos unIngeniero Comercial.El propósito de este rol es apoyar la gestión de la Subgerencia de Desarrollo Organizacional en el proceso de análisis de datos, reportería general, diseño de Encuestas, gestión en las actividades corporativas del área y contribuir a los objetivos de nuestra Gerencia y de la organización.Te Pedimos:Titulo profesional de Ingeniero Comercial.Experiencia de 0 a 2 años máximo.Conocimientos y manejo de herramientas y técnicas de Evaluación.Buen manejo Excel y PBI (Excluyente)Manejo de IA para distintos procesos que faciliten la gestión (Excluyente)Alta capacidad de análisis.Habilidades interpersonales destacadas.¡Te ofrecemosun ambiente laboral de alto nivel profesional, entorno flexible y colaborativo, oportunidades de enfrentar desafíos y atractivos beneficios!Si te gustan los desafíos, quieres pensar fuera de la caja y cumples los requisitos, envíanos tu CV y estarás más cerca de poder integrarte a nuestro equipo.Beneficios- Seguro complementario- Bono vacaciones- Bonos fiestas patrias y navidad- días administrativos</t>
+          <t>EnTanner Servicios Financierosbuscamos a nuestro/a próximo/aIngeniero(a) de Datos, quien será clave en el desarrollo y evolución de nuestras plataformas de datos, habilitando decisiones estratégicas a través de información confiable, oportuna y segura.Si te motiva trabajar con datos, impulsar la analítica avanzada y ser parte de una organización del mundo financiero en constante transformación, este desafío es para ti.Principales desafíosDiseñar y desarrollar procesos de integración de datos (ETL) desde distintas fuentes.Construir y administrar soluciones como Data Warehouse y Data Lake.Asegurar la calidad, disponibilidad y trazabilidad de la información.Optimizar consultas y estructuras de datos para mejorar rendimiento.Implementar prácticas de gobierno y seguridad de datos.Colaborar con equipos de negocio, analítica y tecnología para levantar requerimientos y entregar soluciones de valor.Desarrollar componentes reutilizables que potencien la gestión de datos en la organización.¿Qué buscamos?Formación en Ingeniería, Informática o carrera afín.Experiencia de1 a 2 años en roles de datosManejo deSQL avanzado.Experiencia en herramientas de integración y modelamiento de datos (ETL, Data Warehouse).Conocimiento en herramientas comoIntegration Services, Analysis Services o Power BI.Capacidad analítica, orientación a resultados y trabajo colaborativo.¿Te interesa?Postula y sé parte de Tanner, donde los datos impulsan decisiones que generan impacto.BeneficiosTrabajarás en un entorno colaborativo, con desafíos reales de negocio.Tendrás espacio para desarrollar tus habilidades y crecer profesionalmente.Seguro complementario de saludBono vacacionesOtros.</t>
         </is>
       </c>
     </row>
@@ -10129,12 +10129,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ingeniero de Datos</t>
+          <t>Asistente Recursos Humanos - Retail</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Tanner</t>
+          <t>Belcorp</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -10149,15 +10149,15 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55216/ingeniero-de-datos</t>
+          <t>https://firstjob.me/oferta/55644/asistente-recursos-humanos-retail</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>etl, informatica, power bi</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="I144" t="n">
@@ -10176,7 +10176,7 @@
         <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>EnTanner Servicios Financierosbuscamos a nuestro/a próximo/aIngeniero(a) de Datos, quien será clave en el desarrollo y evolución de nuestras plataformas de datos, habilitando decisiones estratégicas a través de información confiable, oportuna y segura.Si te motiva trabajar con datos, impulsar la analítica avanzada y ser parte de una organización del mundo financiero en constante transformación, este desafío es para ti.Principales desafíosDiseñar y desarrollar procesos de integración de datos (ETL) desde distintas fuentes.Construir y administrar soluciones como Data Warehouse y Data Lake.Asegurar la calidad, disponibilidad y trazabilidad de la información.Optimizar consultas y estructuras de datos para mejorar rendimiento.Implementar prácticas de gobierno y seguridad de datos.Colaborar con equipos de negocio, analítica y tecnología para levantar requerimientos y entregar soluciones de valor.Desarrollar componentes reutilizables que potencien la gestión de datos en la organización.¿Qué buscamos?Formación en Ingeniería, Informática o carrera afín.Experiencia de1 a 2 años en roles de datosManejo deSQL avanzado.Experiencia en herramientas de integración y modelamiento de datos (ETL, Data Warehouse).Conocimiento en herramientas comoIntegration Services, Analysis Services o Power BI.Capacidad analítica, orientación a resultados y trabajo colaborativo.¿Te interesa?Postula y sé parte de Tanner, donde los datos impulsan decisiones que generan impacto.BeneficiosTrabajarás en un entorno colaborativo, con desafíos reales de negocio.Tendrás espacio para desarrollar tus habilidades y crecer profesionalmente.Seguro complementario de saludBono vacacionesOtros.</t>
+          <t>¿Buscas un nuevo desafío en el mundo del Retail? ¿Te apasiona la coordinación, el trabajo en equipo y brindar una excelente experiencia a las personas? ¡Entonces esta oportunidad es para ti!Somos una empresa omnicanal y líder en el rubro de la venta directa, con presencia en 14 países de la región. Nos dedicamos a la comercialización de cosméticos a través de nuestras marcasL'BEL, Ésika y Cyzone, presentes en los canales de Venta Directa, E-commerce y Retail.En esta oportunidad buscamos un(a)Asistente Retailpara integrarse a nuestro equipo en unproyecto a plazo fijo de 3 meses, apoyando la gestión administrativa y operacional del área, y contribuyendo al cumplimiento de nuestros objetivos de negocio.Principales funciones del cargoBrindar soporte administrativo a las distintas iniciativas y procesos del área de Retail.Coordinar y dar seguimiento a la gestión de proveedores, cotizaciones y órdenes de compra.Gestionar solicitudes administrativas y apoyar procesos de facturación.Coordinar la logística de reuniones, capacitaciones y actividades del equipo.Realizar seguimiento a indicadores, reportes y bases de información del área.Apoyar en la coordinación del proceso de incorporación y gestión administrativa de nuevos colaboradores de Retail.Mantener una comunicación permanente con las tiendas y equipos de terreno para asegurar la correcta ejecución de los procesos.Perfil deseadoTítulo Técnico o Profesional en Administración de Empresas, Ingeniería en Administración, Ingeniería Comercial o carrera afín.Deseable manejo de Excel nivel intermedio.Deseable experiencia utilizando SAP u otro ERP.Alta capacidad de organización, planificación y seguimiento.Proactividad, orientación al cliente interno y excelentes habilidades de coordinación.Beneficios- Asignación de colación por Amipass- Modalidad de Trabajo hibrida- Participación de las actividad y/o eventos del área</t>
         </is>
       </c>
     </row>
@@ -10198,12 +10198,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Asistente Recursos Humanos - Retail</t>
+          <t>Analista de Ventas Industriales</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Belcorp</t>
+          <t>Enex</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -10213,20 +10213,20 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55644/asistente-recursos-humanos-retail</t>
+          <t>https://firstjob.me/oferta/55401/analista-de-ventas-industriales</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>excel</t>
+          <t>analisis</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -10236,10 +10236,10 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>¿Buscas un nuevo desafío en el mundo del Retail? ¿Te apasiona la coordinación, el trabajo en equipo y brindar una excelente experiencia a las personas? ¡Entonces esta oportunidad es para ti!Somos una empresa omnicanal y líder en el rubro de la venta directa, con presencia en 14 países de la región. Nos dedicamos a la comercialización de cosméticos a través de nuestras marcasL'BEL, Ésika y Cyzone, presentes en los canales de Venta Directa, E-commerce y Retail.En esta oportunidad buscamos un(a)Asistente Retailpara integrarse a nuestro equipo en unproyecto a plazo fijo de 3 meses, apoyando la gestión administrativa y operacional del área, y contribuyendo al cumplimiento de nuestros objetivos de negocio.Principales funciones del cargoBrindar soporte administrativo a las distintas iniciativas y procesos del área de Retail.Coordinar y dar seguimiento a la gestión de proveedores, cotizaciones y órdenes de compra.Gestionar solicitudes administrativas y apoyar procesos de facturación.Coordinar la logística de reuniones, capacitaciones y actividades del equipo.Realizar seguimiento a indicadores, reportes y bases de información del área.Apoyar en la coordinación del proceso de incorporación y gestión administrativa de nuevos colaboradores de Retail.Mantener una comunicación permanente con las tiendas y equipos de terreno para asegurar la correcta ejecución de los procesos.Perfil deseadoTítulo Técnico o Profesional en Administración de Empresas, Ingeniería en Administración, Ingeniería Comercial o carrera afín.Deseable manejo de Excel nivel intermedio.Deseable experiencia utilizando SAP u otro ERP.Alta capacidad de organización, planificación y seguimiento.Proactividad, orientación al cliente interno y excelentes habilidades de coordinación.Beneficios- Asignación de colación por Amipass- Modalidad de Trabajo hibrida- Participación de las actividad y/o eventos del área</t>
+          <t>¡Somos la energía que mueve tu mundo!¡Súmate a nuestro equipo y construyamos juntos el futuro de la energía!Buscamos integrar a nuestro equipo un/a Analista de Ventas Industriales. El rol se desempeña en el área de soporte y desarrollo comercial, contribuyendo activamente a la eficiencia de los procesos y a la rentabilidad de las operaciones.Principales funciones:Evaluar proyectos de inversión en clientes, resguardando el cumplimiento de aprobaciones y la adecuada asignación de recursos.Generar y administrar reportes de control de contratos, apoyando el seguimiento de la rentabilidad.Gestionar y mantener información de ventas, asegurando la consistencia y calidad de los datos.Elaborar reportes semanales y mensuales de ventas, incluyendo seguimiento de resultados y proyecciones.Proponer mejoras y ajustes a reportes existentes o desarrollar nuevas herramientas de control, según requerimientos del área.Apoyar en la administración de la cartera de clientes del equipo comercial.Coordinar procesos de cotización, asegurando el cumplimiento de flujos y validaciones correspondientes.Colaborar en la implementación de iniciativas y campañas comerciales.Participar en proyectos de mejora continua del área.Perfil deseadoRequisitos:Formación: Ingeniería Civil Industrial, Ingeniería Comercial o carrera afín.Manejo de herramientas Office nivel intermedio-avanzado.Deseable conocimiento en herramientas de reportería y análisis de datos.No se requiere experiencia laboral previa.</t>
         </is>
       </c>
     </row>
@@ -10267,12 +10267,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Analista de Ventas Industriales</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Enex</t>
+          <t>Kitchen Center</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -10282,12 +10282,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55401/analista-de-ventas-industriales</t>
+          <t>https://firstjob.me/oferta/55171/business-analyst</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -10305,10 +10305,10 @@
         <v>0</v>
       </c>
       <c r="K146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
         <v>0</v>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>¡Somos la energía que mueve tu mundo!¡Súmate a nuestro equipo y construyamos juntos el futuro de la energía!Buscamos integrar a nuestro equipo un/a Analista de Ventas Industriales. El rol se desempeña en el área de soporte y desarrollo comercial, contribuyendo activamente a la eficiencia de los procesos y a la rentabilidad de las operaciones.Principales funciones:Evaluar proyectos de inversión en clientes, resguardando el cumplimiento de aprobaciones y la adecuada asignación de recursos.Generar y administrar reportes de control de contratos, apoyando el seguimiento de la rentabilidad.Gestionar y mantener información de ventas, asegurando la consistencia y calidad de los datos.Elaborar reportes semanales y mensuales de ventas, incluyendo seguimiento de resultados y proyecciones.Proponer mejoras y ajustes a reportes existentes o desarrollar nuevas herramientas de control, según requerimientos del área.Apoyar en la administración de la cartera de clientes del equipo comercial.Coordinar procesos de cotización, asegurando el cumplimiento de flujos y validaciones correspondientes.Colaborar en la implementación de iniciativas y campañas comerciales.Participar en proyectos de mejora continua del área.Perfil deseadoRequisitos:Formación: Ingeniería Civil Industrial, Ingeniería Comercial o carrera afín.Manejo de herramientas Office nivel intermedio-avanzado.Deseable conocimiento en herramientas de reportería y análisis de datos.No se requiere experiencia laboral previa.</t>
+          <t>¡¡Te estamos buscando!!Kitchen Center, empresa Retail, líder en equipamiento de cocina busca Business Analyst que pueda desempeñarse dentro de nuestra Gerencia de Tecnología.Será responsable de brindar apoyo en el desarrollo y mejora continua del e - commerce, participando en el análisis de datos, el seguimiento de proyectos y la coordinación de mejoras y nuevas funcionalidades, velando por el correcto funcionamiento de las plataformas digitales y la implementación de soluciones que respondan a las necesidades del negocio.Principales funciones:Apoyar en la gestión de proyectos de mejora y nuevas funcionalidades del sitio web, participando en las distintas etapas de análisis, desarrollo e implementación.Analizar métricas e indicadores del e-commerce, identificando oportunidades de mejora y contribuyendo en la generación de propuestas basadas en datos.Participar en el levantamiento de requerimientos de las distintas áreas y apoyar la coordinación con agencias externas para la implementación de soluciones digitales.Apoyar en la ejecución de pruebas de nuevos desarrollos y en la revisión de incidencias del sitio web, asegurando su correcto funcionamiento.Realizar seguimiento al estado de proyectos e iniciativas digitales, contribuyendo al cumplimiento de plazos y coordinando acciones con los equipos involucrados.Brindar soporte en la gestión del Seller Center y Marketplace, apoyando en la resolución de requerimientos e incidencias relacionadas con productos, precios, pagos y publicaciones.Apoyar en el monitoreo del sistema de tracking de órdenes, identificando oportunidades de mejora y reportando incidencias para su resolución.Participar activamente en reuniones con las distintas áreas de la empresa, colaborando en el análisis, seguimiento y definición de soluciones que aporten valor al negocio.Ordenar, analizar e interpretar información del ecosistema digital, contribuyendo en la identificación de mejoras y optimizaciones para la experiencia de los clientes y el desempeño del e-commerce.¿Por qué nosotros?Porque somos la empresa líder en equipamiento de cocina para el hogar.Porque somos de las 25 mejores empresas para jóvenes profesionales como tú.Porque estamos en una etapa apasionante de crecimiento donde tu perfil nos conducirá al siguiente nivel.Porque contamos con una gran cantidad de beneficios pensados para ti, que te enumeraríamos aquí pero se volvería un texto enorme y preferimos contártelos en el proceso.En nuestra búsqueda de talento, nos enorgullece afirmar que esta oportunidad laboral está abierta a todas las personas, reafirmando nuestro compromiso en dirección a transformarnos en una empresa diversa e inclusiva. Buscamos personas que quieran formar parte de un equipo comprometido con un entorno laboral respetuoso, colaborativo y apasionado. ¡Esperamos contar contigo!Te invitamos a postular y ser parte de nuestra gran empresa.</t>
         </is>
       </c>
     </row>
@@ -10336,12 +10336,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Analista de Administración y Finanzas - Manantial</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Kitchen Center</t>
+          <t>CCU</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -10351,20 +10351,20 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Presencial Trabajo</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55171/business-analyst</t>
+          <t>https://firstjob.me/oferta/55186/analista-de-administracion-y-finanzas-manantial</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>analisis</t>
+          <t>excel</t>
         </is>
       </c>
       <c r="I147" t="n">
@@ -10374,16 +10374,16 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -10393,7 +10393,7 @@
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>¡¡Te estamos buscando!!Kitchen Center, empresa Retail, líder en equipamiento de cocina busca Business Analyst que pueda desempeñarse dentro de nuestra Gerencia de Tecnología.Será responsable de brindar apoyo en el desarrollo y mejora continua del e - commerce, participando en el análisis de datos, el seguimiento de proyectos y la coordinación de mejoras y nuevas funcionalidades, velando por el correcto funcionamiento de las plataformas digitales y la implementación de soluciones que respondan a las necesidades del negocio.Principales funciones:Apoyar en la gestión de proyectos de mejora y nuevas funcionalidades del sitio web, participando en las distintas etapas de análisis, desarrollo e implementación.Analizar métricas e indicadores del e-commerce, identificando oportunidades de mejora y contribuyendo en la generación de propuestas basadas en datos.Participar en el levantamiento de requerimientos de las distintas áreas y apoyar la coordinación con agencias externas para la implementación de soluciones digitales.Apoyar en la ejecución de pruebas de nuevos desarrollos y en la revisión de incidencias del sitio web, asegurando su correcto funcionamiento.Realizar seguimiento al estado de proyectos e iniciativas digitales, contribuyendo al cumplimiento de plazos y coordinando acciones con los equipos involucrados.Brindar soporte en la gestión del Seller Center y Marketplace, apoyando en la resolución de requerimientos e incidencias relacionadas con productos, precios, pagos y publicaciones.Apoyar en el monitoreo del sistema de tracking de órdenes, identificando oportunidades de mejora y reportando incidencias para su resolución.Participar activamente en reuniones con las distintas áreas de la empresa, colaborando en el análisis, seguimiento y definición de soluciones que aporten valor al negocio.Ordenar, analizar e interpretar información del ecosistema digital, contribuyendo en la identificación de mejoras y optimizaciones para la experiencia de los clientes y el desempeño del e-commerce.¿Por qué nosotros?Porque somos la empresa líder en equipamiento de cocina para el hogar.Porque somos de las 25 mejores empresas para jóvenes profesionales como tú.Porque estamos en una etapa apasionante de crecimiento donde tu perfil nos conducirá al siguiente nivel.Porque contamos con una gran cantidad de beneficios pensados para ti, que te enumeraríamos aquí pero se volvería un texto enorme y preferimos contártelos en el proceso.En nuestra búsqueda de talento, nos enorgullece afirmar que esta oportunidad laboral está abierta a todas las personas, reafirmando nuestro compromiso en dirección a transformarnos en una empresa diversa e inclusiva. Buscamos personas que quieran formar parte de un equipo comprometido con un entorno laboral respetuoso, colaborativo y apasionado. ¡Esperamos contar contigo!Te invitamos a postular y ser parte de nuestra gran empresa.</t>
+          <t>¡En CCU nos apasiona crear experiencias para compartir juntos un mejor vivir!Nos encontramos en búsqueda de un/aAnalista de Administración y Finanzaspara desempeñarse en nuestras oficinas deManantialen Quilicura.El propósito del cargo es ser responsable de registrar y analizar información estratégica relacionada al área financiera respecto al control de gestión, interpretación de índices financieros y evaluación de oportunidades de inversión, identificando desviaciones en los resultados obtenidos respecto a las prácticas implementadas por el departamento.Principales Funciones:Ejecutar y hacer seguimiento al Plan Estratégico determinado por la Gerencia del área, con el fin de gestionar y velar por el cumplimiento de los objetivos e indicadores asociados.Elaborar el presupuesto anual de la compañía, analizando las tendencias de gastos e ingresos con el objetivo de preveer y optimizar la gestión de recursos.Analizar los resultados obtenidos del ejercicio mensual del negocio, elaborando reportería sobre los estados financieros actual y pasados para evaluar la situación de la compañía con el propósito de facilitar la toma de decisiones estratégicas en la Compañía.Elaborar informes tanto de corto como largo plazo, dependiendo de la frecuencia de entrega, y analizar las fluctuaciones de los indicadores asociados al área, con el objetivo de hacer seguimiento y captar las necesidades del área.Generar reportes mensuales, analizando la situación de cada zona en la que está presente Manantial y evaluar las oportunidades en las distintas carteras de clientes.Requisitos:Título de Ingeniería Comercial, Ingeniero Civil Industrial o carrera a fin.De 0 a 6 meses de experiencia.Excel nivel intermedio - avanzado.Disponibilidad para trabajar 100% presencial en Quilicura.Nuestro SER CCU nos inspira a trabajar con aceptación y respeto a las diferencias de las personas, promoviendo un entorno diverso e integrador, para así contribuir a un mejor vivir. Por esto, te agradecemos que nos compartas si necesitas adaptación en alguna etapa del proceso de postulación.¡Te invitamos a SER CCU!</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Analista de Administración y Finanzas - Manantial</t>
+          <t>¡Media Assistant!</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CCU</t>
+          <t>Omnicom Media Chile</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Presencial Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/55186/analista-de-administracion-y-finanzas-manantial</t>
+          <t>https://firstjob.me/oferta/54583/media-assistant</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -10443,16 +10443,16 @@
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
       </c>
       <c r="N148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
         <v>0</v>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>¡En CCU nos apasiona crear experiencias para compartir juntos un mejor vivir!Nos encontramos en búsqueda de un/aAnalista de Administración y Finanzaspara desempeñarse en nuestras oficinas deManantialen Quilicura.El propósito del cargo es ser responsable de registrar y analizar información estratégica relacionada al área financiera respecto al control de gestión, interpretación de índices financieros y evaluación de oportunidades de inversión, identificando desviaciones en los resultados obtenidos respecto a las prácticas implementadas por el departamento.Principales Funciones:Ejecutar y hacer seguimiento al Plan Estratégico determinado por la Gerencia del área, con el fin de gestionar y velar por el cumplimiento de los objetivos e indicadores asociados.Elaborar el presupuesto anual de la compañía, analizando las tendencias de gastos e ingresos con el objetivo de preveer y optimizar la gestión de recursos.Analizar los resultados obtenidos del ejercicio mensual del negocio, elaborando reportería sobre los estados financieros actual y pasados para evaluar la situación de la compañía con el propósito de facilitar la toma de decisiones estratégicas en la Compañía.Elaborar informes tanto de corto como largo plazo, dependiendo de la frecuencia de entrega, y analizar las fluctuaciones de los indicadores asociados al área, con el objetivo de hacer seguimiento y captar las necesidades del área.Generar reportes mensuales, analizando la situación de cada zona en la que está presente Manantial y evaluar las oportunidades en las distintas carteras de clientes.Requisitos:Título de Ingeniería Comercial, Ingeniero Civil Industrial o carrera a fin.De 0 a 6 meses de experiencia.Excel nivel intermedio - avanzado.Disponibilidad para trabajar 100% presencial en Quilicura.Nuestro SER CCU nos inspira a trabajar con aceptación y respeto a las diferencias de las personas, promoviendo un entorno diverso e integrador, para así contribuir a un mejor vivir. Por esto, te agradecemos que nos compartas si necesitas adaptación en alguna etapa del proceso de postulación.¡Te invitamos a SER CCU!</t>
+          <t>¡Súmate a una red global de innovación en medios!En Omnicom Media Chile, parte de una de las redes de agencias más influyentes del mundo, buscamos a un/a Media Assistant (Asistente de Medios) con energía, iniciativa y pasión por los medios, y por sobre todo¡Con muchas ganas de aprender!Tu rol será clavepara que nuestras campañas brillen, estén bien ejecutadas y lleguen a las personas correctas en el momento indicado.¡Te estamos buscando!¿Cuál será tu misión?Apoyar la implementación efectiva de campañas en medios digitales y tradicionales.Gestionar y registrar las órdenes de compra para asegurar una operación fluida.Coordinar con agencias creativas y proveedores de medios.Generar reportes y métricas clave para el seguimiento de resultados.Resolver problemas con agilidad y buena comunicación.¿Qué buscamos en ti?Titulado/a de Publicidad, Ingeniería en Marketing o carrera afín.Experiencia de al menos 6 meses en agencias de medios o cargos similares.Conocimientos en Google Ads, Facebook Ads y plataformas similares.Manejo de Excel a nivel medio y habilidades administrativas.Eres proactivo/a, ordenado/a, con buena comunicación y muchas ganas de aprender.¿Listo/a para dar el próximo paso en tu carrera en medios?Postula y sé parte del grupo que está transformando la industria publicitaria en Chile y el mundo.</t>
         </is>
       </c>
     </row>
@@ -10474,45 +10474,41 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>¡Media Assistant!</t>
+          <t>Beca: Santander Future Talents 🚀  Tu primer paso al mundo laboral</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Omnicom Media Chile</t>
+          <t>Santander Chile</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago, Chile</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Híbrido Trabajo</t>
+          <t>Remoto Trabajo</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/54583/media-assistant</t>
+          <t>https://firstjob.me/oferta/53318/beca-santander-future-talents-tu-primer-paso-al-mundo-laboral</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>2</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>excel</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H149" t="inlineStr"/>
       <c r="I149" t="n">
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -10521,7 +10517,7 @@
         <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O149" t="n">
         <v>0</v>
@@ -10531,7 +10527,7 @@
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>¡Súmate a una red global de innovación en medios!En Omnicom Media Chile, parte de una de las redes de agencias más influyentes del mundo, buscamos a un/a Media Assistant (Asistente de Medios) con energía, iniciativa y pasión por los medios, y por sobre todo¡Con muchas ganas de aprender!Tu rol será clavepara que nuestras campañas brillen, estén bien ejecutadas y lleguen a las personas correctas en el momento indicado.¡Te estamos buscando!¿Cuál será tu misión?Apoyar la implementación efectiva de campañas en medios digitales y tradicionales.Gestionar y registrar las órdenes de compra para asegurar una operación fluida.Coordinar con agencias creativas y proveedores de medios.Generar reportes y métricas clave para el seguimiento de resultados.Resolver problemas con agilidad y buena comunicación.¿Qué buscamos en ti?Titulado/a de Publicidad, Ingeniería en Marketing o carrera afín.Experiencia de al menos 6 meses en agencias de medios o cargos similares.Conocimientos en Google Ads, Facebook Ads y plataformas similares.Manejo de Excel a nivel medio y habilidades administrativas.Eres proactivo/a, ordenado/a, con buena comunicación y muchas ganas de aprender.¿Listo/a para dar el próximo paso en tu carrera en medios?Postula y sé parte del grupo que está transformando la industria publicitaria en Chile y el mundo.</t>
+          <t>¿Estás buscando tu primera experiencia laboral, pero no sabes por dónde empezar?Santander, junto a FirstJob, lanza Future Talents, una beca diseñada para ayudarte a dar el salto desde la sala de clases al mundo laboral con herramientas reales.¿Qué es Future Talents? 🎯Un programa de formación práctica que te prepara para conseguir y destacar en tu primer trabajo.¿Qué aprenderás?Empleabilidad y búsqueda laboral efectivaOptimización de CV y LinkedInHabilidades profesionales claveGestión del tiempoExcel y herramientas digitalesFundamentos de IA aplicada al trabajoSeguridad digital¿A quién está dirigido? 👀Estudiantes de últimos añosRecién egresadosJóvenes profesionales en búsqueda de su primera oportunidad laboral¿Qué incluye? 💡Acceso completo al programa.Certificación al finalizar.Preferencia para futuros roles en Santander.Formación práctica enfocada en el mundo real.📅 Postulaciones abiertas hasta el 19 de Mayo👉 Postula ahora y comienza tu camino laboral con ventaja.</t>
         </is>
       </c>
     </row>
@@ -10543,27 +10539,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Beca: Santander Future Talents 🚀  Tu primer paso al mundo laboral</t>
+          <t>Banco De Talentos - Tituladosas - L'Oréal Chile</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Santander Chile</t>
+          <t>L'Oréal</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Apoquindo 3885, 2do piso, Las Condes, Santiago, Chile, Chile</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Remoto Trabajo</t>
+          <t>Híbrido Trabajo</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/53318/beca-santander-future-talents-tu-primer-paso-al-mundo-laboral</t>
+          <t>https://firstjob.me/oferta/37853/banco-de-talentos-titulados-as-l-oreal-chile</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -10574,10 +10570,10 @@
         <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -10596,29 +10592,29 @@
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>¿Estás buscando tu primera experiencia laboral, pero no sabes por dónde empezar?Santander, junto a FirstJob, lanza Future Talents, una beca diseñada para ayudarte a dar el salto desde la sala de clases al mundo laboral con herramientas reales.¿Qué es Future Talents? 🎯Un programa de formación práctica que te prepara para conseguir y destacar en tu primer trabajo.¿Qué aprenderás?Empleabilidad y búsqueda laboral efectivaOptimización de CV y LinkedInHabilidades profesionales claveGestión del tiempoExcel y herramientas digitalesFundamentos de IA aplicada al trabajoSeguridad digital¿A quién está dirigido? 👀Estudiantes de últimos añosRecién egresadosJóvenes profesionales en búsqueda de su primera oportunidad laboral¿Qué incluye? 💡Acceso completo al programa.Certificación al finalizar.Preferencia para futuros roles en Santander.Formación práctica enfocada en el mundo real.📅 Postulaciones abiertas hasta el 19 de Mayo👉 Postula ahora y comienza tu camino laboral con ventaja.</t>
+          <t>¡Descubre tu camino hacia el éxito con nosotros en L'Oréal Chile!Si eres un apasionado de la innovación y estás listo para mostrar tu talento al mundo, ¡tenemos la oportunidad perfecta para ti!Te invitamos a formar parte de nuestroBanco de Talentos, donde podrás dar a conocer tu experiencia y demostrar por qué eres la pieza clave que estamos buscando.Guardaremos tu información en nuestra base de datos global para así tener la oportunidad de contactarte ante futuras oportunidades dentro de esta comunidad dinámica y emprendedora que es L’Oréal.Esta oferta está enfocada en titulados/as que buscan tener experiencia laboral.Estamos comprometidos con la diversidad, equidad e inclusión en todas sus formas; valoramos la singularidad de cada individuo y creemos en el poder de la belleza para transformar el mundo.¡Tu futuro te está esperando! Postula ahora y déjanos descubrir todo lo que puedes aportar a L'Oréal Chile. Juntos, crearemos la belleza que mueve al mundo.¿Quieres saber un poco más de L’Oréal?Apostamos por las personas desde sus inicios. En 2021, dimos la bienvenida a más de 18.000 colaboradores menores de treinta años, incluidos más de 5.000 practicantes.Los miembros de nuestro equipo son tan diversos como el mundo en sí, con más de 85.000 empleados en 150 países, de más de 162 nacionalidades diferentes.Tenemos una fuerte mentalidad de startup. La asociación de L'Oréal con Station F ha acelerado 32 startups desde el 2018.Fuimos reconocidos el 2022 con la puntuación triple "A" por sexto año por el liderazgo medioambiental en la lucha contra el cambio climático, la seguridad del agua y la protección de los bosques.¡Postula ahora y comienza tu viaje hacia un futuro emocionante con nosotros!</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Banco De Talentos - Tituladosas - L'Oréal Chile</t>
+          <t>Práctica Prevención de Riesgo - Gestión de Personas</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>L'Oréal</t>
+          <t>KPMG Chile</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Apoquindo 3885, 2do piso, Las Condes, Santiago, Chile, Chile</t>
+          <t>Las Condes, Metropolitana, Chile, Chile</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -10628,7 +10624,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>https://firstjob.me/oferta/37853/banco-de-talentos-titulados-as-l-oreal-chile</t>
+          <t>https://firstjob.me/oferta/56347/practica-prevencion-de-riesgo-gestion-de-personas</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -10639,13 +10635,13 @@
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K151" t="n">
         <v>1</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
@@ -10661,7 +10657,551 @@
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>¡Descubre tu camino hacia el éxito con nosotros en L'Oréal Chile!Si eres un apasionado de la innovación y estás listo para mostrar tu talento al mundo, ¡tenemos la oportunidad perfecta para ti!Te invitamos a formar parte de nuestroBanco de Talentos, donde podrás dar a conocer tu experiencia y demostrar por qué eres la pieza clave que estamos buscando.Guardaremos tu información en nuestra base de datos global para así tener la oportunidad de contactarte ante futuras oportunidades dentro de esta comunidad dinámica y emprendedora que es L’Oréal.Esta oferta está enfocada en titulados/as que buscan tener experiencia laboral.Estamos comprometidos con la diversidad, equidad e inclusión en todas sus formas; valoramos la singularidad de cada individuo y creemos en el poder de la belleza para transformar el mundo.¡Tu futuro te está esperando! Postula ahora y déjanos descubrir todo lo que puedes aportar a L'Oréal Chile. Juntos, crearemos la belleza que mueve al mundo.¿Quieres saber un poco más de L’Oréal?Apostamos por las personas desde sus inicios. En 2021, dimos la bienvenida a más de 18.000 colaboradores menores de treinta años, incluidos más de 5.000 practicantes.Los miembros de nuestro equipo son tan diversos como el mundo en sí, con más de 85.000 empleados en 150 países, de más de 162 nacionalidades diferentes.Tenemos una fuerte mentalidad de startup. La asociación de L'Oréal con Station F ha acelerado 32 startups desde el 2018.Fuimos reconocidos el 2022 con la puntuación triple "A" por sexto año por el liderazgo medioambiental en la lucha contra el cambio climático, la seguridad del agua y la protección de los bosques.¡Postula ahora y comienza tu viaje hacia un futuro emocionante con nosotros!</t>
+          <t>**Perfil Ideal: Practicante de Prevención de Riesgos - Gestión de Personas** Buscamos un/a estudiante proactivo/a y comprometido/a para unirse a nuestro equipo de Recursos Humanos y Capacitación en KPMG Chile. El candidato/a ideal cursará estudios en Administración de Empresas, Ingeniería, Técnico en Prevención de Riesgos, Técnico en Administración o Técnico en RRHH, o carreras afines. Este rol ofrece una valiosa oportunidad para desarrollar habilidades prácticas en la coordinación de actividades de prevención de riesgos, difusión de procedimientos de trabajo seguro, y apoyo en la gestión del Comité Paritario de Higiene y Seguridad (CPHS). El/la practicante participará activamente en el seguimiento de programas de capacitación, la coordinación de campañas con organismos administradores, y el apoyo en labores administrativas del área, incluyendo el seguimiento de protocolos MINSAL. Se valorará el conocimiento básico de normativas de seguridad y salud ocupacional, aunque no es excluyente. Es indispensable contar con carta de solicitud de práctica y seguro escolar vigente. Se requiere disponibilidad para iniciar la práctica en noviembre de 2026, con una duración mínima de 3 meses (idealmente 6 meses, conversable). Las competencias clave para este puesto incluyen altas habilidades comunicativas e interpersonales, disposición para aprender y aportar, y manejo de herramientas Office. Esta práctica representa una excelente oportunidad de crecimiento profesional en un entorno dinámico.Beneficios⭐ Beneficios: 🌎Ser parte de una de las principales compañías de Auditoría y Consultoría a nivel mundial. 💻 Modalidad presencial de lunes a jueves y trabajo remoto los días viernes. (Oficina: Av. Presidente Riesco 5685, Las Condes). 💰 Remuneración mensual $400.000 líquidos . 😉 ¡Viernes más cortos! Se trabaja hasta las 13:30 hr. 🚲🛴 Estacionamiento de bicicletas y scooters. 💯 Múltiples convenios corporativos. 🎉 Actividades como fiestas, Meeting Points y encuentros de área para disfrutar con compañeros. 🎂T u día de cumpleaños es completamente libre para que lo disfrutes como desees.   En KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas , con un propósito claro, para una mejor sociedad. Valoramos las diversas habilidades y fortalezas, tanto personales como profesionales, que cada persona aporta. En KPMG estamos comprometidos con la Diversidad e inclusión , nuestras ofertas de empleo están disponibles con los ajustes razonables necesarios para tu proceso. Juntos, estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. ¡Anímate y ven a descubrir por qué somos la opción más clara!</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Asistente Administrativo - La Joya</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Ferreyros</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Arequipa, Perú</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56342/asistente-administrativo-la-joya</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>1</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="P152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Misión del puestoRealizar los diferentes procesos y gestiones relacionados con la administración de recursos humanos y proveedores de servicios al personal a fin de contribuir a la gestión del área y propiciar el buen clima laboral del CRC-La Joya así como garantizar el cumplimiento de los objetivos trazados para esta.FuncionesCoordinar con los colaboradores de la operación las firmas de los diferentes documentos requeridos por el área de Recursos Humanos, así como también, comunicar oportunamente las renuncias y no renovaciones.Coordinación de viajes por capacitación y otros.Generar requerimientos por suministros, uniformes, epps y útiles de oficina para el área administrativa y hacer el seguimiento respectivo hasta la llegada de los mismos. Asegurar que se de buen uso de los suministros.Gestionar las habilitaciones del personal permanente para su ingreso a CRC, solicitar uniforme, alimentación, movilidades en caso requiera.Coordinar los servicios de alimentación y transporte de los colaboradores, con el fin de asegurar el confort y bienestar de los mismos.Gestión con Proveedores: Realizar el seguimiento de los servicios de comedor, lavandería y transporte para brindar el servicio y satisfacción del personal.Asumir otras funciones que le sean asignadas por su jefe inmediato, con el fin de mantener la eficiencia en el área y/o Gerencia.RequisitosEgresado(a) de Carreras: Administración, Ing. Industrial o carreras afinesConocimiento en:Tributación, normas laborales, finanzasManejo de OfficeManejo de SAPExperiencia general y en posiciones similares de 01 a 02 años</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Analista de Alianzas Estratégicas y Growth</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Mibanco</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56340/analista-de-alianzas-estrategicas-y-growth</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>12</v>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>python, sql, modelo, analisis, tableu</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>1</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAnalista de Alianzas Estratégicas y Growth.¿Cuáles serían tus principales responsabilidades?Construir y mantener reportes de performance comercial de alianzas y growth (leads, funnel, conversión, desembolsos, rentabilidad).Analizar data comercial y operativa con foco en crecimiento, eficiencia y rentabilidad, incorporando contexto de negocio.Generar insights accionables orientados a impacto (qué escalar, qué corregir, qué optimizar).Realizar seguimiento end‑to‑end al desempeño del funnel de prospectos provenientes de alianzas estratégicas y growth.Automatización de reportería generada para la generación más rápida y eficiente de insightsEjecutar y apoyar en tareas de soporte al modelo de alianzas (presentaciones, comunicaciones,validación de documentos, control de comisiones, atención de consultas de aliados y canales de venta).¿Qué necesitamos?Bachiller de Administración, Ing Industrial, Marketing, Economía, Ing Sistemas o afines.Experiencia mínima de 1-2 años en análisis comercial, reporting, producto o negocioExperiencia trabajando con data de ventas, canales o alianzas (deseable). De 1 a 2 añosExcel Avanzado (tablas dinámicas, programación de macros)SQL (consulta, cruce y análisis de datos, construcción de queries para reportería –Intermedio/Avanzado) (Indispensable).Herramientas de BI, visualización y automatización de datos.Power BI – Avanzado (Indispensable).Power Automate – básico (Deseable).Tableu – básico (Deseable).Python básico (automatización y análisis de datos) (Deseable).Conocimiento básico de framework ágil Scrum (Deseable).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Analista de Datos</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Entel Perú</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56343/analista-de-datos</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>7</v>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>sql, informatica, excel</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>1</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>¿Te mueve colaborar, desafiar y crecer con propósito? Conoce que desafíos te esperan como Analista de DatosExtraer, generar y procesar información de Base de datos con data interna y externa.Analizar la información y los principales indicadores de gestión de los canales escritos.Planificar y proyectar la demanda de tráfico, identificando variables que puedan generar desviaciones y anticipando las necesidades de capacidad de la operación.Identificar oportunidades de mejora y agregar valor a la información.Elaborar reportes y dashboards de gestión.Participar en iniciativas de mejora y proyectos del área.RequisitosEgresado de Ing. de Sistemas, Informática, Administración o carreras afinesConocimiento de inglés a nivel básicoConocimiento de Excel a nivel avanzadoConocimiento de Access a nivel intermedioConocimiento de SQL a nivel intermedioExperiencia en generación y procesamiento de base de datos, ligado a estrategias comerciales</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Analista de Monitoreo (Fraudes)</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Mibanco</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56341/analista-de-monitoreo-fraudes</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>4</v>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>excel, cloud</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>1</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>En Mibanco, el banco especializado en microfinanzas del Grupo Credicorp, nos encontramos en búsqueda de una persona apasionada, proactiva y con grandes ideas para impactar en la vida de los micro y pequeños empresarios del país incorporándose a nuestro equipo comoAnalista de Monitoreo.¿Cuáles serían tus principales responsabilidades?Realizar el monitoreo continuo de las herramientas de prevención del fraudeAnalizar, coordinar, comunicar y realizar el seguimiento a los eventos reportados.Gestionar los eventos y alertas de las herramientas de monitoreo y el contacto con el cliente.Consolidar información y emitir el reporte de la gestión realizada por durante el monitoreo.Evaluar el cumplimiento los indicadores de monitoreo y brindar retroalimentación para la mejora de las herramientas.¿Qué necesitamos?Bachiller o Titulado en Administración bancaria o empresas, Economía, Derecho, Ingenierías.Mínimo 1 año de experiencia en el área de monitoreo en los sectores de banca, retail, seguros o telcoms.Creacción de reportes en Excel nivel Intermedio (Graficos) (Indispensable)Herramientas de Monitoreo nivel intermedio (Orion, CGR, PRTG, Monitor Plus, entre otros) (Indispensable).Conocimiento de MS Office a nivel Intermedio (Deseable).Creación de tickets Smart Cloud o JIRA nivel Intermedio (Deseable)Conocimientos en estructura de Red de Agencias y/o del sector financiero.Herramientas de Automatización - nivel Intermedio (Deseable).Beneficios¿Qué ofrecemos?Formar parte de uno de los grupos económicos más importantes del país.Oportunidad de línea de carrera en la entidad de Microfinanzas más grande de Latinoamérica.Excelente Clima Laboral.Contrato a plazo indeterminado.EPS cubierta al 70%.Descuentos en entidades educativas, de salud y establecimientos comerciales.Trabajo Híbrido.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra."</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Asistente de Calidad, Riesgos y Cumplimiento - Forvis Mazars</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Forvis Mazars</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56334/asistente-de-calidad-riesgos-y-cumplimiento-forvis-mazars</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>1</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Con nosotros tienes la oportunidad de pertenecer a una firma internacional con un equipo de más de 40.000 profesionales altamente capacitados, que brinda servicios profesionales generando alto impacto en todos nuestros clientes en más de 100 países en los cinco continentes.Podrás formar parte de un equipo que valorará tus ideas, apoyará tus ambiciones y celebrará tus éxitos. En Forvis Mazars nos proponemos impulsar la colaboración y la flexibilidad, las diversas perspectivas de nuestros colaboradores y el progreso.Hoy buscamos un Asistente para el área deCalidad, Riesgos y Cumplimiento.Este rol es clave para apoyar el logro de los objetivos del área, especialmente en materias de cumplimiento normativo, ambiente regulatorio de la industria, medidas de control y mejora continua de procesos y procedimientos internos.Tareas/ResponsabilidadesApoyar la implementación, mantención y mejora continua del Programa de Calidad, Riesgos y Cumplimiento.Brindar asesoría y soporte a las distintas áreas de la firma.Analizar, monitorear y optimizar procesos, que apoyen la toma de decisiones.Fortalecer la cultura de riesgos, cumplimiento organizacional.RequisitosContador Auditor(EXCLUYENTE)conhasta 2 años de experiencia laboralen firmas de auditoría externa, servicios profesionales o entornos regulados.Experiencia en gestión de riesgos, cumplimiento normativo, legal, privacidad de información o áreas afines.Deseable conocimiento de normativa regulatoria o marcos globales de compliance.Este cargo es compatible para personas con discapacidad, se enmarca en la ley 21.015, que incentiva la inclusión de personas con discapacidad al mundo laboral.BeneficiosOfrecemosModalidad de trabajo híbrida.Seguro de salud y dental.Entorno joven, dinámico y altamente colaborativo.Oportunidades de aprendizaje continuo y desarrollo profesional en un área estratégica de la firma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Customer Development Partner</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Wherex</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56331/customer-development-partner</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>2</v>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>1</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="O157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>¿Te apasiona el mundo del financiamiento y el servicio al cliente? ¡Únete a Wherex y sé parte de un equipo que está transformando la forma en que las empresas acceden a financiamiento!¿Qué harás?-Apoyar a los clientes en su registro y onboarding en nuestra plataforma de financiamiento. -Atender requerimientos, generar cotizaciones y cerrar negociaciones.-Registrar las operaciones en nuestro sistema ERP.-Hacer seguimiento a operaciones y procesos en curso.-Fidelizar clientes, asegurando una experiencia óptima y un servicio de excelencia.Lo que buscamos-Recién egresados de las carreras Ing. Comercial, Administración de Servicios y carreras afines.-Manejo de Excel intermedio.Beneficios¿Por qué trabajar en Wherex?-25 días de vacaciones al año.-Seguro complementario (médico y dental)-Un entorno dinámico y desafiante donde podrás aprender y crecer profesionalmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Programa GMT (Graduate Managment Trainee) 2027</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>AB InBev</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56332/programa-gmt-graduate-managment-trainee-2027</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>7</v>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>trainee</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>1</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>1</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>¿Listo/a para acelerar tu carrera?El ProgramaGraduate Management Trainee (GMT) 2027es mucho más que tu primer trabajo. Es una experiencia diseñada para desarrollar a la próxima generación delíderesde nuestro negocio.Durante el programa, tendrás la oportunidad de aprender en terreno, asumir desafíos reales, trabajar con equipos de diferentes áreas y generar impacto desde el primer día.Si te apasiona aprender, buscas salir de tu zona de confort y quieres construir una carrera con propósito, este puede serel comienzo que estabas esperando.⚙️ÁreasSupplySupply es el motor que hace posible que nuestras marcas lleguen a millones de consumidores con la calidad que nos caracteriza.A través de un plan de rotaciones, tendrás una visión integral de nuestra operación y experiencia en áreas clave como:Producción y elaboraciónEnvasado y calidadIngeniería y servicios industrialesLogística y distribuciónProcurementConocerás de cerca cómo la innovación, la tecnología, la sustentabilidad y la mejora continua impulsan nuestro negocio.BusinessBusiness está enfocado en hacer crecer nuestras marcas y conectar con consumidores y clientes a través de estrategias que generan valor e impacto.Durante el programa, rotarás por áreas estratégicas como:VentasMarketingFinanzasAl completar el programa, te integrarás a un rol estratégico acorde a tu desempeño, fortalezas y proyección profesional.✨ Buscamos personas curiosas, que desafíen el status quo, aprendan rápido y se animen a hacer que las cosas pasen.Si tienes sed de crecer y ganas de hacer te invitamos a postular al GMT 2027.Sobre el candidatoEstar cursando o haber finalizado estudios universitarios;Tener unafecha de graduación hasta diciembre de 2026;Tenerdisponibilidadparatrabajar presencialmente en Santiago y de forma temporaria en Buenos Aires.Tener, hasta diciembre de 2026, unmáximo de 2 años de experienciaprofesional a tiempo completo;Tener un nivel deinglés avanzado/fluido.Sobre la empresaEnCervecería AB InBev Chileformamos parte de la cervecera líder a nivel mundial. Somos más de150.000 colaboradoresque compartimos un mismo sueño:crear un futuro con más motivos para brindar.Con más de200 marcaspresentes en más de100 países, nuestras cervezas forman parte de los momentos más importantes alrededor del mundo, incluyendo 8 de las más consumidas a nivel global. EnCervecería AB InBev Chilenos enorgullece ser unaEmpresa B Certificada, lo que reafirma nuestro compromiso de generar un impacto positivo económico, social y ambiental en cada comunidad donde estamos presentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Consumer Strategy &amp; Intelligence Manager</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/55748/consumer-strategy-intelligence-manager</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>1</v>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>1</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>1</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>¿Te apasiona entender al consumidor a partir de los datos y transformar ese conocimiento en estrategias de alto impacto? Buscamos un/aConsumer Strategy &amp; Intelligence Managerque lidere la evolución de la inteligencia de clientes y contribuya a fortalecer la relación entre nuestras marcas y millones de consumidores en Latinoamérica.En este rol tendrás la oportunidad de impulsar iniciativas regionales, trabajar con equipos multidisciplinarios y convertir los datos en decisiones que generen valor para el negocio y una mejor experiencia para nuestros clientes.Desafío:Serás responsable de liderar la estrategia de inteligencia de clientes y gestión de CRM, potenciando el conocimiento del consumidor para apoyar la toma de decisiones comerciales y de marketing. Tu foco estará en desarrollar estrategias de segmentación, fidelización y automatización que permitan construir relaciones de largo plazo con nuestros clientes en los distintos mercados donde operamos.Principales responsabilidades:Liderar la estrategia de segmentación de clientes y gestión de su ciclo de vida, utilizando metodologías como RFM y nuevas fuentes de información.Diseñar y coordinar campañas de captación, retención y fidelización junto a las distintas marcas y equipos regionales.Administrar y optimizar la plataforma CRM, asegurando la correcta implementación de automatizaciones y flujos de comunicación.Generar análisis e insights estratégicos que apoyen la planificación de campañas, promociones y comunicaciones orientadas al cliente.Promover el uso de herramientas de inteligencia de clientes dentro de la organización, capacitando y acompañando a los equipos internos en su adopción.Trabajar de manera transversal con Marketing, Comercial, Atención al Cliente, Tecnología y otras áreas clave para asegurar una visión integral del consumidor.Compartir aprendizajes y mejores prácticas entre los distintos países, impulsando la mejora continua de las estrategias de relacionamiento.</t>
         </is>
       </c>
     </row>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q159"/>
+  <dimension ref="A1:Q170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11205,6 +11205,745 @@
         </is>
       </c>
     </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Prevencionista de Riesgo</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Empresa confidencial</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56374/prevencionista-de-riesgo</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>1</v>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="O160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Planificar, controlar, asesorar y promocionar acciones preventivas y correctivas con el fin de evitar y/o minimizar los riesgos que se traducen en accidentes del trabajo y enfermedades profesionales al interior de Mutualidad y sus empresas contratistas, apoyando en iniciativas que fortalezcan la calidad de vida y la salud laboral de los trabajadores.Principales funciones:Ejecutar el Programa de Prevención de Riesgos y diagnosticar condiciones de riesgo.Investigar incidentes y analizar estadísticas de accidentabilidad.Asesorar y participar en el Comité Paritario.Implementar Protocolos MINSAL y velar por el cumplimiento normativoActualizar RIOHS y Plan de Emergencias.Coordinar capacitaciones en Seguridad y Salud Ocupacional.Gestionar relación con el Organismo Administrador (Ley 16.744). Conocimientos: Normativa legal vigente (Ley 16.744, D.S. 44, D.S. 594, Ley 20.123), Sistema de Gestión SSO, investigación de incidentes, análisis estadístico, matrices de riesgos y manejo de crisis.RequerimientosTítulo de Ingeniero en Prevención de Riesgos.1 años de experiencia laboral.Conocimiento actualizado de normativa legal vigente.Beneficios🕒 38 horas y 15 minutos de trabajo semanal.📃 Seguros complementario, vida, salud, dental y catastrófico.🏖️ 20 días hábiles anuales de vacaciones.🧑‍💼 3 días administrativos.🎂 El día del cumpleaños si cae hábil es libre.🏃‍♀️ Clases de acondicionamiento físico y zumba.👖 Viernes Jeans Day.🏞️ Centros recreacionales.🧡 Actividades de integración.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>JEFE DE BODEGA (Lampa-Valle Grande)</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SurChile SPA</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56369/jefe-de-bodega-lampa-valle-grande</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Horario: Presencial Lunes a jueves 08 a 17:30pm (30m colación debe traer almuerzo)Viernes: 08 a 14pmSueldo Líquidos:  1.350.000Entrevista presencial: Santa Isabel 1262, LAmpa (cerca de CHC)Presentar: Cv actualizado, antecedentes, certificado estudios técnicos, último finiquito (opcional).Empresa: www.surchile.clcorreo:[email protected]Principales FuncionesControl de Inventario:Planificar y ejecutar inventarios cíclicos, rotativos y generales de todas las existencias.Conciliación de Stock:Investigar y resolver de forma inmediata cualquier diferencia o desfase entre las existencias físicas y los registros del sistema de gestión.Gestión de Entradas y Salidas:Supervisar la recepción de insumos (mercaderías, envases, químicos, packaging) validando la documentación correspondiente.Trazabilidad:Asegurar la correcta rotulación, almacenamiento por lotes y FEFO (First Expired, First Out) de las materias primasLiderazgo de Equipo:Dirigir, capacitar y evaluar al personal operativo de bodega (operarios, horquilleros).Seguridad y Normativa:Mantener el orden y limpieza de la bodega bajo las normativas vigentes de seguridad (manejo de sustancias o productos industriales) e ISO de la compañía.Definir, analizar y presentarlos indicadores clave de rendimiento (KPI)Dominio de herramientas de TI: SistemasERP(Softland ) y sistemasWMSFormación y ExperienciaEstudios:Ingeniero en Logística, Industrial o carrera afín.Experiencia:Mínimo1 a 2 añosen roles de inventario en plantas productivas.Habilidades Blandas (Competencias)Alta capacidad de organización y planificación.Orientación a la resolución de problemas bajo presión.Comunicación efectivaAtención al detalle para evitar errores de digitación.BeneficiosAguinaldos, venta interna .Beneficios de la caja Los Andes.Fiesta fin de año</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>COORDINADOR LOGISTICO (Lampa-Valle Grande)</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>SurChile SPA</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56368/coordinador-logistico-lampa-valle-grande</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Horario: Presencial Lunes a jueves 08 a 17:30pm (30m colación debe traer almuerzo)Viernes: 08 a 14pmSueldo Líquidos: 800.000 + horas extrasEntrevista presencial: Santa Isabel 1262, LAmpa (cerca de CHC)Presentar: Cv actualizado, antecedentes, certificado estudios técnicos, último finiquito (opcional).Empresa: www.surchile.clcorreo:[email protected]Planificación y Gestión de Plataformas B2BOptimizar y autorizarlos programas maestros de despacho y picking a través de las plataformas internas, equilibrando la capacidad del CD con la demanda.Liderar y validarla carga estratégica de información en los portales B2B de clientes (agendamientos), asegurando ventanas horarias óptimas y minimizando el riesgo de multas por rechazos.Monitorear y dirigirel ciclo completo de la operación (desde el picking hasta la confirmación de entrega), garantizando el cumplimiento delLead Timey los niveles de servicio (Fill Rate).Definir, analizar y presentarlos indicadores clave de rendimiento (KPI) de la operación (entregas a tiempo, costos de transporte, pendientes), implementando planes de acción correctivos ante desviaciones.Experiencia operativa enCentros de Distribución(procesos de Picking, Packing, consolidación de pallets).Dominio de herramientas de TI: SistemasERP(Softland ) y sistemasWMSFormación y ExperienciaEstudios:Técnico Superior o Ingeniero en Logística, Administración de Empresas, Comercio Exterior o carrera afín.Experiencia:Mínimo1 a 2 añosen roles de coordinación logística, idealmente atendiendo canales de Retail o consumo masivo.Habilidades Blandas (Competencias)Alta capacidad de organización y planificación.Orientación a la resolución de problemas bajo presión.Comunicación efectiva  (con transportistas ).Atención al detalle para evitar errores de digitación o despacho.BeneficiosAguinaldos, venta internaBeneficios de la caja Los Andes.Fiesta fin de año</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>AUXILIAR ADMINISTRATIVO DE DESPACHOS (Lampa-Valle Grande)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>SurChile SPA</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56365/auxiliar-administrativo-de-despachos-lampa-valle-grande</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>1</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>Horario: Presencial Lunes a jueves 08 a 17:30pm (30m colación debe traer almuerzo)Viernes: 08 a 14pmSueldo Líquidos: 600.000 + Bono bruto 150.000 según cumplimiento.Entrevista presencial: Santa Isabel 1262, LAmpa (cerca de CHC)Presentar: Cv actualizado, antecedentes, certificado estudios técnicos, último finiquito (opcional).Postulaciones para Mujeres, con conocimientos contables.correo:[email protected]Funciones principalesGestionar y emitir guías de despacho según procedimientos internos.Archivar y mantener ordenada la documentación de despacho (física y/o digital).Generar programaciones de despacho y picking a través de la plataforma/sistema interno.Dar seguimiento al ciclo completo de despacho hasta su cumplimiento (picking, despacho,confirmación).Realizar cargas de información en las plataformas de clientes (portales de agendamiento, sistemas EDI uotros).Elaborar y mantener actualizados controles e indicadores de la operación (cumplimiento, pendientes,tiempos, etc.).Coordinar con bodega, transporte y otras áreas para asegurar el flujo correcto de despachos.Apoyar en la resolución de incidencias documentales o de programación.BeneficiosAguinaldosBonosVenta interna</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Asistente Comercial Norseg</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Forus</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56381/asistente-comercial-norseg</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>3</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Únete a FORUS como nuestro próximo/a Asistente Comercial División Seguridad Industrial¿Te apasiona el orden, el análisis y ser una pieza clave para que un negocio funcione de manera eficiente? ¿Disfrutas trabajar con datos, coordinar múltiples procesos y aportar a la mejora continua? Entonces esta oportunidad puede ser para ti.En FORUS buscamos un/aAsistente Comercialpara nuestraDivisión de Seguridad Industrial, quien será un apoyo fundamental para el equipo comercial, asegurando el correcto seguimiento de procesos, la coordinación administrativa y el control de gestión que permiten impulsar el crecimiento del negocio.¿Cuál será tu desafío?Serás responsable de apoyar la gestión comercial y administrativa de la división, coordinando procesos, administrando información clave y contribuyendo al control de indicadores, presupuestos y compras, trabajando de manera cercana con distintas áreas del negocio.¿Qué harás en este rol?Apoyar el control de gestión de los procesos de demanda, abastecimiento e importaciones.Dar seguimiento a procesos de compras y órdenes de compra en el ERP.Apoyar la administración de acuerdos comerciales con clientes y proveedores.Coordinar procesos relacionados con certificaciones y control de calidad de productos.Administrar partidas del presupuesto y realizar seguimiento de gastos del área.Coordinar viajes, reuniones y eventos internos y externos.Elaborar, actualizar y optimizar reportes e indicadores en Excel y Google Sheets.Trabajar colaborativamente con Brand Managers, Product Development Managers y distintos equipos internos para asegurar una gestión eficiente.¿Por qué FORUS?En FORUS creemos en las personas que hacen que las cosas pasen. Tendrás la oportunidad de desarrollarte en un equipo colaborativo, participar en proyectos desafiantes y contribuir al crecimiento de una división líder en soluciones de seguridad industrial.Si buscas un rol donde tu organización, análisis y capacidad de coordinación tengan un impacto real en el negocio, ¡queremos conocertePerfil deseado¿Qué buscamos?Formación técnica o profesional afín al cargo.Al menos 1 año de experiencia en funciones similares.Manejo avanzado de Excel y/o Google Sheets.Conocimientos de control de gestión y contabilidad.Inglés nivel básico o intermedio.Nos gustaría que fueras una persona que...Se organiza muy bien y sabe priorizar.Disfruta trabajar con información y mantener el control de múltiples procesos.Tiene iniciativa para proponer mejoras.Se comunica de manera clara y efectiva.Trabaja bien en equipo y genera buenas relaciones.Responde de buena forma en entornos dinámicos y de alta exigencia.BeneficiosDescuentos en marcas Forus.Convenios y beneficios de salud y bienestar.Capacitaciones y oportunidades de desarrollo.Movilidad y crecimiento interno.Actividades y beneficios orientados a la calidad de vida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Sales Development Representative (SDR)</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>DataScope</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56355/sales-development-representative-sdr</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>1</v>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>1</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>🧠 Sales Development Representative – DataScope (SaaS B2B)Si te atrae el cargo, postula directamente desde el link:https://links.datascope.io/yHmR📍 Ubicación: Santiago, Chile🕒 Tipo de posición: Tiempo completo, híbridoDataScope es una Startup de Software Chilena que está cambiando la forma en que las empresas digitalizan sus operaciones en más de 40 países. Actualmente, estamos creciendo nuestro equipo de SDR’s y buscamos a alguien que la rompa, sea competitiv@, y que no se conforme hasta llegar a cada rincón donde nos necesiten¿Eres tú? 💥ResponsabilidadesProspección: Serás el corazón de nuestro negocio 💡. Tu habilidad para identificar y contactar nuevos clientes será clave para expandir la presencia de DataScope. Con un análisis previo y estratégico, conectarás con empresas que realmente necesitan nuestra solución.Contactos en frío (outbound): Dominarás el arte de la comunicación asertiva 📞. Desde distintos canales, lograrás captar la atención de altos cargos con mensajes empáticos y relevantes.Calificación de oportunidades: No solo generarás contactos, sino que identificarás las mejores oportunidades 🎯. Asegurarás que cada reunión agendada sea una verdadera puerta al éxito.Sé creativo:¿Te encanta proponer ideas? ¡Aquí es tu lugar! 🎨 En DataScope, valoramos la innovación y creemos que ningún proceso es intocable. Si amas estudiar, escuchar podcasts y leer, aquí tendrás la libertad de plasmar tus aprendizajes y ejecutarlos.Esperamos que luego de tu proceso de Onboarding estes capacitado de generar como mínimo entre 12 y 14 reuniones calificadas al mes.Competencias/ Habilidades- Habilidad para conectar con las personas y comunicarte de manera asertiva.- Sin miedo al teléfono: sabemos que las grandes oportunidades empiezan con una llamada📞- Pasión por aprender y el deseo de convertir nuevas ideas en realidad.➕ Extras que suman puntosExperiencia en ventas outbound, especialmente SaaS.Al menos 1 año de experiencia en ventas de cualquier tipo.Inglés intermedio o avanzado. 🌍Conocimiento en CRM (usamos Hubspot) y herramientas de prospección.Presencia activa y profesional en LinkedInBeneficios🤘🏼 ¿Qué obtendrás al ser parte del equipo?- Puedes ir a la oficina cuando quieras. Estamos en WeWork Apoquindo, un lugar bacán con buenos espacios colaborativos.- Oportunidades reales de crecimiento profesional 📈- Un equipo que celebra tus logros y te apoya en cada desafío. 🎉- Inversión en tu desarrollo: cursos, libros y mentorías para crecer cada día. 📚- ¡Día libre en tu cumpleaños! 🎂- Work-on-you hour: una hora semanal para enfocarte en ti y en tu desarrollo 🙌- Viajes nacionales e internacionales para conectar con el equipo. ✈- Seguro complementario y licencia de paternidad extendida (en Chile). 💙- Wellhub: entrena, haz yoga, medita o anda al gimnasio que quieras. Tienes acceso gratuito a varias opciones y descuentos exclusivos en planes premium.- MacBook incluido para tu trabajo diario 💻</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Category Manager - División Mujer</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Ofi Cerro Colorado 5240 - Comercial, Chile</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56373/category-manager-division-mujer</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="n">
+        <v>1</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>1</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>Category Manager - División Mujer En Ripley Chile, lo tenemos todo. ¡Sólo nos falta tu talento!Promovemos equipos diversos y colaborativos, buscando mejorar la experiencia de nuestros clientes a través de la innovación y la cultura de servicio. ¡Súmate a una industria ágil y desafiante!¡Postula para ser parte de nuestro equipo!Estamos en búsqueda de nuestro/a nuevo/a Category Manager División Mujer para nuestra Gerencia Comercial.¿Cuáles serán tus principales desafíos? 🚀Apoyar la definición de estrategia comercial del departamento.Generar órdenes de compra.Ejecutar cambio de precios y costos.Realizar la gestión operacional del departamento.Apoyar al área en negociaciones con las marcas involucradas.Ser el contacto directo entre Product Manager y las tiendas¿Qué valoramos en tu postulación? 🎯Título Profesional en Ingeniería Comercial/Civil Industrial o carrera afín (Excluyente)Microsoft Office Avanzado (Excluyente)Dominio Inglés IntermedioDeseable experiencia de 0-1 años en áreas comerciales.¿Por qué trabajar en Ripley? ❤️Pensamos en el bienestar de nuestros colaboradores, es por esto que contamos con atractivos beneficios corporativos como:Capacitaciones y entrenamiento enfocado a tu desarrollo de carrera.Tasa Preferencial en Productos Banco Ripley.Seguro Complementario Gratuito.Descuento en Tiendas Ripley.Desarrollo Profesional.Entre otros.¡Postula para ser parte de nuestro equipo!En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.BeneficiosDescripción de los beneficios de la vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Analista de Beneficios y Comunicaciones – Gestión de Personas</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>KPMG Chile</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Las Condes, Metropolitana, Chile, Chile</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56363/analista-de-beneficios-y-comunicaciones-gestion-de-personas</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>1</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Perfil Ideal: Analista de Beneficios y Comunicaciones – Gestión de PersonasBuscamos un profesional proactivo y creativo para unirse a nuestro equipo de Gestión de Personas en KPMG.Experiencia y conocimientos:Sólida experiencia en Comunicación Interna, Marketing Interno, Employer Branding o Experiencia de Colaboradores, con al menos 1 año de trayectoria.Habilidades demostrables en edición de video, fotografía y producción de contenido audiovisual.Manejo intermedio-avanzado de Microsoft Office y la Suite Adobe (Illustrator, Photoshop, InDesign, Premiere).Se valorará positivamente la experiencia en la gestión de beneficios o programas de bienestar.Responsabilidades y competencias:El rol requiere un profesional con capacidad para diseñar, implementar y comunicar estrategias de beneficios, transformando iniciativas en experiencias de alto impacto.Se espera que el candidato potencie la oferta de beneficios, identifique nuevas alianzas estratégicas y lidere la comunicación interna a través de campañas creativas y contenido innovador.La habilidad para coordinar eventos y gestionar calendarios de comunicación será clave para el éxito en esta posición.Beneficios¿Qué ganas tú?🌎Ser parte de una de las principales compañías de Auditoría y Consultoría a nivel mundial.🚀 Oportunidades de desarrollo profesional.🚑Seguro de salud complementario con contrato indefinido.💻Jornada de trabajo híbrida.🏢Oficinas de primer nivel ubicadas en Las Condes, frente al Parque Araucano.💯Múltiples convenios corporativos.🎉Actividades como fiestas, Meeting Points y encuentros de área para disfrutar con compañeros.🎂16 horas anuales a libre disposición y tu día de cumpleaños es completamente libre para que lo disfrutes como desees.En KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas , con un propósito claro, para una mejor sociedad. Valoramos las diversas habilidades y fortalezas, tanto personales como profesionales, que cada persona aporta. En KPMG estamos comprometidos con la Diversidad e inclusión , nuestras ofertas de empleo están disponibles con los ajustes razonables necesarios para tu proceso. Juntos, estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. ¡Anímate y ven a descubrir por qué somos la opción más clara! 🥇</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Product Manager - Ing Comercial - Lampa Valle Grande - 1.3 líquidos</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SurChile SPA</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Presencial Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56364/product-manager-ing-comercial-lampa-valle-grande-1-3-liquidos</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>1</v>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Vacante para Ingenieros Comerciales - EXCLUYENTEEXPERIENCIA PRICING Y ESTRATEGIA COMERCIAL - EXCLUYENTE  1 AÑOHombre por características del cargo - ExcluyenteFavor No postular si no cumple lo requerido.Muchas gracias por su comprensión.EnSurChile SPAbuscamos un/aProduct Managercon visión estratégica, orientación a resultados y pasión por el desarrollo de negocios, para liderar la gestión integral de nuestras líneas de productos y potenciar su crecimiento en el mercado.Esta posición es clave para impulsar la rentabilidad, posicionamiento y expansión del portafolio, asegurando una ejecución comercial efectiva y alineada a los objetivos de la compañía.🚀 Principales responsabilidadesDiseñar e implementar la estrategia comercial y de posicionamiento del producto.Analizar mercado, competencia y oportunidades de crecimiento.Liderar lanzamientos y planes de desarrollo de nuevos productos.Gestionar indicadores de desempeño (ventas, margen, participación de mercado).Coordinar con áreas internas (ventas, operaciones, logística, marketing).Desarrollar y mantener relaciones estratégicas con clientes y proveedores.Identificar oportunidades de mejora e innovación en el portafolio.🎯 RequisitosTítulo de Ingeniería Comercial o carrera afín.Experiencia previa en gestión de productos, desarrollo comercial o áreas similares.Alta capacidad de análisis y visión estratégica.Habilidades de negociación y gestión de proyectos.Manejo de herramientas de análisis y reportes comerciales (deseable).🧩 Competencias claveLiderazgo e iniciativa.Orientación a resultados y cumplimiento de metas.Comunicación efectiva y trabajo colaborativo.Proactividad y autonomía en la toma de decisiones.BeneficiosCaja Los AndesAguinaldos fiestas patrias y fin de año</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Customer Success</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>DataScope</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56356/customer-success</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>3</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>1</v>
+      </c>
+      <c r="K169" t="n">
+        <v>1</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>DataScope (SaaS B2B)📍 Ubicación: Santiago, Chile🕒 Tipo de posición:Tiempo completo, híbrido en Santiago, remoto fuera de Santiago¡Únete al equipo de DataScope! 🚀¿Te apasiona ayudar a los clientes a crecer y sacar el máximo provecho de sus herramientas? ¿Te encanta construir relaciones a largo plazo y resolver problemas con creatividad? ¡Entonces esta oportunidad es para ti! 🙌En DataScope, somos una empresa chilena de SaaS que está revolucionando la forma en que las empresas gestionan sus operaciones en más de 40 países. Nuestra misión es simplificar procesos y automatizar tareas para que nuestros clientes trabajen de manera más eficiente. 🌎Responsabilidades📈 Garantizar el éxito: Supervisarás los hitos y KPIs de implementación, asegurando que se cumplan los objetivos clave junto al cliente.📅 Gestionar cronogramas: Definirás y coordinarás el calendario de implementación para cumplir con los tiempos establecidos.🎓 Capacitar clientes: Impartirás formaciones prácticas y didácticas para que los usuarios aprovechen al máximo la plataforma.🤝 Colaborar con equipos internos: Trabajarás junto a áreas comerciales y de producto para alinear estrategias y entregar soluciones personalizadas.📊 Analizar y mejorar: Proporcionarás feedback basado en datos para optimizar el proceso de incorporación de clientes.🌱 Impulsar el crecimiento: Detectarás oportunidades de expansión en las cuentas y ayudarás a gestionarlas con éxito.Perfil que buscamos🎓 Recién egresados o profesionales con hasta 2 años de experiencia en cargos de Implementación u Onboarding de carreras comoIngeniería Civil, Ingeniería Industrial o afines.📊 Interés por la gestión de proyectos, optimización de procesos, análisis de datos y trabajo con clientes.Competencias/ Habilidades💬 Habilidades interpersonales: Capacidad para generar confianza, guiar procesos y conectar con los clientes.🛠️ Experiencia en soporte al cliente o roles similares en entornos dinámicos.📊 Excel avanzado y manejo de Google Workspace (Hojas de cálculo, Presentaciones).🎓 Facilidad para enseñar y realizar capacitaciones claras y efectivas.⏳ Organización y gestión del tiempo para manejar múltiples proyectos.🧩 Resolución de problemas de forma rápida y efectiva.📂 Conocimiento en bases de datos y análisis de información.Beneficios🤘🏼 ¿Qué obtendrás al ser parte del equipo?Trabajo home office, también puedes ir a la oficina cuando quieras. Estamos en WeWork Apoquindo, un lugar bacán con buenos espacios colaborativos.Oportunidades reales de crecimiento profesional 📈Un equipo que celebra tus logros y te apoya en cada desafío. 🎉Inversión en tu desarrollo: cursos, libros y mentorías para crecer cada día. 📚¡Día libre en tu cumpleaños para festejar como se debe! 🎂Wellhub y desafíos saludablesWork-on-you hour: una hora semanal para enfocarte en ti y tus proyectos. 🙌Viajes nacionales e internacionales para conectar con el equipo. ✈Seguro complementario y licencia de paternidad extendida (en Chile). 💙MacBook incluido para tu trabajo diario 💻</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Seo Analyst</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Milimetrix</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Callao 2911, Las Condes, Chile</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56360/seo-analyst</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>15</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>analisis, informatica, excel, looker studio, looker, html, css, javascript</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>1</v>
+      </c>
+      <c r="K170" t="n">
+        <v>1</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>1</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Buscamos a nuestro/a próximo/aSEO Analystpara sumarse a nuestro equipo de SEO, aprender y desarrollarse junto a un equipo con experiencia, y apoyar la operación diaria del área a medida que crecen nuestros clientes y proyectos.Somos una consultora especializada enmarketing digital y e-commerce, y trabajamos con marcas reconocidas a nivel nacional e internacional, comoPatagonia, Victorinox, MK, Victoria's Secret, entre otras.Buscamos una personaanalítica, curiosa y con muchas ganas de aprender, que quiera desarrollarse profesionalmente en SEO y ser parte de un equipo en pleno crecimiento.💼Principales responsabilidades• Apoyar la investigación de palabras clave (keyword research) e identificación de oportunidades de posicionamiento orgánico para nuestros clientes.• Colaborar en optimizacioneson-page, incluyendo títulos, meta descripciones, estructura de contenidos, enlazado interno y arquitectura de información.• Participar enauditorías técnicas SEO, identificando oportunidades y problemas relacionados con rastreo, indexación, rendimiento y estructura de los sitios.• Monitorear el posicionamiento, tráfico orgánico y principales indicadores SEO utilizando herramientas comoGoogle Search Console y Google Analytics 4.• Apoyar la creación y optimización de contenidos orientados a SEO, trabajando en conjunto con equipos de contenido y otras áreas de marketing.• Elaborar reportes y análisis de desempeño SEO, tanto para uso interno como para nuestros clientes.• Utilizar herramientas de la industria comoSemrush, Ahrefs, Screaming Frog, entre otras.• Apoyar al equipo en la investigación de nuevas tendencias relacionadas con búsqueda, inteligencia artificial y evolución de los motores de búsqueda.💡Lo que buscamos• Formación enAnalista Programador, Ingeniería Informática, Ingeniería Comercial, Ingeniería Civil, Periodismo, Publicidad, Marketing, Comunicación Digitalo carreras afines.• Entre0 y 2 años de experiencia. La experiencia formal en SEO no es excluyente: también valoramos proyectos personales, prácticas, cursos, certificaciones o experiencia relacionada con marketing digital, analítica, contenido o desarrollo web.• Buena capacidad deanálisis, resolución de problemas y atención al detalle.• Curiosidad genuina, proactividad y ganas de aprender un oficio que combinamarketing, tecnología, datos y contenido.• Capacidad para organizar el trabajo, gestionar tareas y colaborar con distintos perfiles y equipos.• Interés por entender cómo funcionan los sitios web, los motores de búsqueda y el comportamiento de los usuarios.Será un plus contar con conocimientos o experiencia en:• Google Analytics 4 y Google Search Console.• WordPress, Shopify u otros CMS.• Semrush, Ahrefs o Screaming Frog.• Excel, Google Sheets, Looker Studio o herramientas de análisis de datos.• HTML, CSS, JavaScript o conceptos básicos de desarrollo web.• Cursos o certificaciones relacionadas con SEO, analítica o marketing digital.BeneficiosBeneficiosModalidad: Híbrida 2x3 (+2 días adicionales presencial durante el mes)Días libres por ocasión: Cumpleaños, mudanza, titulaciónFamilia: Licencias maternales y paternales extendidas (15 días adicionales). Los nuevos padres podrán trabajar de manera remota todas las tardes del primer medio año de vida de su nuevo integrante.Work from Anywhere: 3 semanas al año para trabajar 100% remoto; dos semanas son fijas (septiembre y Navidad/Año Nuevo) y una semana adicional es de libre elección.Vacaciones Premium: Si programas y te tomas 10 días de vacaciones consecutivos, ¡nosotros te regalamos un 11° día libre!Experiencia de equipo: actividades de equipo mensuales para fortalecer la colaboración y cultura interna.Make the dream: Después de cierto tiempo en la empresa, disfruta de hasta 6 meses sin goce de sueldo para perseguir ese sueño pendiente.Luna de miel prolongada: Añade 5 días extra a tu licencia matrimonial.Acompañamiento: Dos semanas libres en caso de pérdida de embarazo. Estamos contigo.Salud: Seguro complementario de salud, catastrófico y de vida sin costo.Convenio preferencial con MindFit Advanced, centro de entrenamiento ubicado en nuestro mismo edificio.Detalles del cargoUbicación: A pasos de Metro Tobalaba, Las Condes, Santiago.Horario: Lun-Jue 09:00 - 18:15 hrs; Vie: 8:30 -16:30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q167"/>
+  <dimension ref="A1:Q180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11721,6 +11721,875 @@
         </is>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Eléctrico Industrial</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Carozzi</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>San Bernardo, Chile</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56525/electrico-industrial</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>En Carozzi nos mueve hacer las cosas bien, para que todos podamos compartir y disfrutar en un mejor entorno, y es por ello que desde hace más de 127 años estamos presentes en el mercado con más de 100 marcas como Costa, Ambrosoli, Vivo, Trattoria, Master Dog, Bresler y Pancho Villa, entre otras.Somos una Compañía donde vivimos la innovación, la pasión por el trabajo bien hecho y el respeto por las personas, valorando la diversidad e inclusión, porque creemos que nuestras diferencias nos enriquecen como organización.Un nuevo desafío te espera! 🚀😊 El equipo de Mantención de una de nuestras plantas está en busca de su próximoEléctrico IndustrialBuscamos a personas con formación en la carrera de Ingeniería eléctrica / en automatización o Técnico Nivel Superior área eléctrica / electrónica con mínimo 2 años de experiencia en electricidad industrial.¿Qué tienes que hacer?Realizar diagnóstico y reparación de fallas eléctricas de alta complejidad en equipos y maquinarias.Mantener el funcionamiento de los equipos de planta.Contribuir a la operatividad, eficiencia y continuidad productiva de los equipos y maquinarias de la planta.Perfil deseado¿Qué necesitas para desempeñar este cargo?Contar con formación técnico nivel superior área eléctrica / electrónica o Ingeniería eléctrica/ en automatización.Deseable experiencia de 2 años como electricista industrial o cargo similaresEstar dispuesto a trabajar en turnos rotativos (mañana, tarde y noche, de lunes a sábado).Tener disponibilidad para trabajar en San Bernardo.BeneficiosTenemos distintos beneficios que podrás disfrutar, acá te señalamos algunos de ellos:Casino.Buses de acercamiento.Seguro complementario, de vida entre otrosDescuento en productos.Gym.Reajuste por IPC.Estabilidad laboral.Entre muchos más que te invitamos a descubrir.Sí te atraen los desafíos te invitamos a postular y vivir la experiencia Carozzi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Ingeniero BI Tecnología Minera - Arequipa</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Ferreyros</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Arequipa, Perú</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56504/ingeniero-bi-tecnologia-minera-arequipa</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>10</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>python, sql, cloud, gcp</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Misión:Ejecutar actividades de implementación y soporte a los procesos de flujos y entrega de datos operacionales para facilitar la toma de decisiones, mediante el trabajo coordinado con las áreas operativas y de desarrollo, asegurando siempre los estándares técnicos de la organización.Funciones:Gestión de Datos Operacionales: Limpieza, integración y contextualización de datos de campo para garantizar información confiable a Ferreyros y sus clientes.Modelado y Visualización: Analizar la lógica de negocio para implementar flujos de datos y dashboards bajo estándares de la empresa.Diseño y Soporte: Apoyar en el diseño de soluciones de datos, brindando soporte preventivo y correctivo a las herramientas desplegadas para asegurar la continuidad operativa.Capacitación y Adopción: Asistir en la creación y ejecución de capacitaciones técnicas para usuarios finales.Cumplir con la normativa legal y estándares internos en materia de SSMA (Seguridad, Salud y Medio Ambiente).Requisitos:Bachiller o Titulado/a en Ing. Minas, Industrial carreras afines.2 años de experiencia de laboral en funciones similares.Dominio Técnico Sólido en Python para Data Engineering, SQL avanzado y  Power BI u otras herramientas de visualización de Business Intelligence.Conocimiento de Google Cloud Platform (GCP) orientado a arquitectura e integración de datos.Disponibilidad para laborar de forma presencial en la Arequipa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Prevencionista de Riesgos - Salamanca - Temporada de Vendimia 2027</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>CCU</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Coquimbo, Chile</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56494/prevencionista-de-riesgos-salamanca-temporada-de-vendimia-2027</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>¡En CCU nos apasiona crear experiencias para compartir juntos un mejor vivir!Nos encontramos en búsqueda de un/aPrevencionista de Riesgospara sumarse a laCompañía Pisquera de Chiledurante la temporada de vendimia, desempeñándose en nuestra planta deSalamanca.Funciones:Ejecutar los Planes de Acción correspondientes  para cumplir con los objetivos de cero accidente, resguardando y velando por la seguridad de la organización, y bajo las normas y estándares de la compañía.Ejecutar auditorías de seguridad, efectuando levantamiento de brecha y asegurando el correcto cierre de las desviaciones en tiempo y forma.Realizar reuniones de seguridad a todo el equipo de planta, para establecer e identificar de manera preventiva los peligros y, con ello, evaluar los riesgos del programa de operaciones.Efectuar y liderar la reunión semanal de Seguridad (Pilar SSMA).Requisitos:Título en Ingeniería de Prevencion de Riesgos o Técnico de Prevención de Riesgos.Experiencia mínima de 1 año en gestión de seguridad, idealmente con experiencia trabajando en temporada de vendimia.Disponibilidad para trabajar por alrededor de 3 meses en Salamanca, en la cuarta región.Disponibilidad para trabajar en turnos rotativos.BeneficiosCasino en todas las plantas.¡Te invitamos a Ser CCU!Nuestro SER CCU nos inspira a trabajar con aceptación y respeto a las diferencias de las personas, promoviendo un entorno diverso e integrador. Si necesitas alguna adaptación en tu proceso de postulación, no dudes en informárnoslo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Prevencionista de Riesgos - Sotaqui - Temporada de Vendimia 2027</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>CCU</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Coquimbo, Chile</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56493/prevencionista-de-riesgos-sotaqui-temporada-de-vendimia-2027</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>¡En CCU nos apasiona crear experiencias para compartir juntos un mejor vivir!Nos encontramos en búsqueda de un/aPrevencionista de Riesgospara sumarse a laCompañía Pisquera de Chiledurante la temporada de vendimia, desempeñándose en nuestra planta deOvalle (Sotaqui/Monte Patria).Funciones:Ejecutar los Planes de Acción correspondientes  para cumplir con los objetivos de cero accidente, resguardando y velando por la seguridad de la organización, y bajo las normas y estándares de la compañía.Ejecutar auditorías de seguridad, efectuando levantamiento de brecha y asegurando el correcto cierre de las desviaciones en tiempo y forma.Realizar reuniones de seguridad a todo el equipo de planta, para establecer e identificar de manera preventiva los peligros y, con ello, evaluar los riesgos del programa de operaciones.Efectuar y liderar la reunión semanal de Seguridad (Pilar SSMA).Requisitos:Título en Ingeniería de Prevencion de Riesgos o Técnico de Prevención de Riesgos.Experiencia mínima de 1 año en gestión de seguridad, idealmente con experiencia trabajando en temporada de vendimia.Disponibilidad para trabajar por alrededor de 3 meses en Sotaqui o Monte Patria, en la cuarta región.Disponibilidad para trabajar en turnos rotativos.¡Te invitamos a Ser CCU!Nuestro SER CCU nos inspira a trabajar con aceptación y respeto a las diferencias de las personas, promoviendo un entorno diverso e integrador. Si necesitas alguna adaptación en tu proceso de postulación, no dudes en informárnoslo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Prevencionista de Riesgo Temporada Febrero a Mayo 2027- Monte Patria IV Región</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>CCU</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Coquimbo, Chile</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56491/prevencionista-de-riesgo-temporada-febrero-a-mayo-2027-monte-patria-iv-region</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="n">
+        <v>1</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>¿Quieres SER CCU?Estamos en búsqueda de Prevencionistas de Riesgo para trabajar por temporada en la Compañía Pisquera de Chile en Monte Patria durante el periodo de Vendimia.Funciones:Asesorar al equipo de Planta para cumplir con los objetivos de cero accidenteEjecutar auditorías de seguridadRealizar reuniones de seguridad, para identificar peligros de manera preventiva y así, evaluar los riesgos del Programa de OperacionesRequisitos:Título de Ingeniería/Técnico en Prevención de Riesgos2 años de experiencia laboralDisponibilidad para trabajar por temporada y en Monte Patria.Deseables conocimientos en prácticas de excelencia operacional TPMNuestro SER CCU nos inspira a trabajar con aceptación y respeto a las diferencias de las personas, promoviendo un entorno diverso e integrador, para así contribuir a un mejor vivir. Por esto, te agradecemos que nos compartas si necesitas adaptación en alguna etapa del procesode postulación.¡Te invitamos a SER CCU!</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Forus</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56526/analista-de-gestion-comercial-y-operaciones</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>3</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Beneficios👟¿Quiénes somos?EnFORUSsomos líderes en el mercado de vestuario, calzado y accesorios, representando reconocidas marcas internacionales comoCAT, VANS, MERRELL, UNDER ARMOUR y COLUMBIA, entre otras. Estamos presentes enChile, Perú, Colombia y Uruguay, con una amplia red de tiendas y un negocio en constante crecimiento.🎯 ¿Cuál será tu desafío?Serás un partner clave para laGerencia de Retail, combinando análisis, gestión y operación para entender qué está pasando en el negocio y transformar los datos en acciones.🚀 ¿Qué harás?Analizarventas, margen, inventario y principales KPIsde las marcas.Hacer seguimiento alpresupuesto y P&amp;L, identificando desviaciones y oportunidades.Monitorear stock y detectarquiebres, sobrestock y oportunidades de reposición.Analizar el impacto deprecios y promociones.Ser el nexo entreCasa Matriz y las tiendas, dando seguimiento a campañas y requerimientos.Generar reportes y análisis que ayuden a la Gerencia atomar mejores decisiones.Proponer mejoras para hacer más eficientes los procesos de gestión y reportería.🔎 ¿Qué buscamos?Ingeniería Comercial, Civil Industrial, Control de Gestión o carrera afín.Al menos1 año de experienciaen análisis, control de gestión, Retail o Consumo Masivo.Excel Avanzado (excluyente).Capacidad analítica, organización y orientación al detalle.Comunicación efectiva y orientación a resultados.Curiosidad, agilidad, ownership y accountability, alineados a nuestra forma de trabajar.🚀 ¿Por qué FORUS?Porque aquí podrás ser parte de un negocio dinámico, aprender de distintas áreas y asumir desafíos que impactan directamente en el negocio.Tu análisis puede convertirse en una decisión, y una decisión puede mover toda una operación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Líder Producción Turnos rotativos (am, pm noche)</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56488/lider-produccion-turnos-rotativos-am-pm-noche</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" t="n">
+        <v>0</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Importante empresa de consumo masivo se encuentra en búsqueda de su próximo líder de producción.Objetivos del cargo:Analizar, desarrollar e implementar mejoras en los equipos y procesos de planta, liderando equipos de trabajo formados para cada una de éstas. Planificar y llevar a cabo el programa de producción y coordinar a los colaboradores de cada línea inspeccionando el buen desempeño, la calidad del producto y la seguridad de las personas.Responsabilidades:Asistencia a reuniones de planificación desarrollo y seguimiento de mejoras para coordinar y llevar a cabo los grupos de mejora.Capacitaciones internas con el fin de reforzar los conocimientos del personal.Formación y liderazgo de equipo de trabajo para llevar a cabo el mantenimiento autónomo del SGI.Llevar estadísticas de los objetivos industriales para cumplir con las necesidades de producción.Perfil deseadoTécnico en Procesos Industriales.Técnico en Alimentos.Técnico Industrial</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Ingeniero de Planificación</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Watt's</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56527/ingeniero-de-planificacion</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>5</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>modelo, excel</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>1</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="n">
+        <v>1</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>En Watt’s buscamos nuevos talentos!En tu despensa, refrigerador o congelador hay, al menos, un producto elaborado por Watt's. Es por esto que queremos invitarte a ser parte de una de las principales empresas de alimentos del país y ayudarnos a seguir creciendo, diversificándonos e innovando.Estamos en búsqueda de nuestro próximoIngeniero de Planificación,para nuestra gerencia de Planificación y Cadena de Suministro, planta San Bernardo.¿Cuál será tu principal desafío?Serás elCoordinador de Go-to-Market (GTM), liderando y orquestando la implementación del plan GTM para todos los lanzamientos de la compañía. Tu objetivo principal será asegurar que cada área cumpla sus hitos, facilitando la comunicación, el seguimiento y la resolución de desvíos.Principales Responsabilidades:Liderar reuniones GTMy coordinar equipos multidisciplinarios (marketing, ventas, logística, planificación, etc.).Gestionar el cronograma: crear, mantener y monitorear el plan de trabajo.Coordinar interdepartamentalmentepara alinear esfuerzos y tiempos.Gestionar riesgos y desvíos: identificar obstáculos y proponer planes de contingencia.Hacer seguimiento y control: reportar indicadores de avance y entregar informes de estado del proyecto.Documentar el proceso: registrar decisiones clave, cambios y aprendizajes.Dar seguimiento a proyectosde nuevos lanzamientos, cambios de diseño, cambios de línea y productos promocionales.Generar reportes semanalesde proyectos, medición de lanzamientos on time y niveles de servicio.Apoyar la generación de reportes de inventariosde diferentes grupos de negocios y plantas.¿Qué esperamos de ti?Título profesional de Ingeniería Industrial, Ingeniería Industrial mención IT, Ingeniería IT o Ingeniería Comercial, idealmente con perfil industrial y analítico.Ser recién egresado/a, idealmente con experiencia de práctica en áreas relacionadas.Contar con manejo de Excel a nivel básico. Se valorará conocimiento en QlikView y SAP.Tener disponibilidad para trabajar en San Bernardo, bajo un modelo híbrido.BeneficiosOfrecemos:Casino en las plantas de acuerdo a tu jornada de trabajo.Aguinaldo de fiestas patrias y navidad.Días administrativos.Seguro complementario de Salud y Dental.Ropa de trabajo para los cargos que así lo requieran.Sala cuna o bono para trabajadoras con hijos menores de hasta 2 años.Venta de productos con descuentos exclusivos Watt’s.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Analista de Soporte Post Venta Clickie | Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Clickie</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Presencial Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56514/analista-de-soporte-post-venta-clickie-santiago-chile</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>1</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="O176" t="n">
+        <v>0</v>
+      </c>
+      <c r="P176" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Analista de Soporte Post VentaClickie | Santiago, ChilePresencial · Lunes a viernes, 08:30 a 17:30 · Contrato plazo fijo con paso a indefinidoSobre ClickieClickie es una empresa de eficiencia energética y soluciones IoT/IIoT con presencia en Chile, Argentina, Perú, México, El Salvador y Bolivia. Ayudamos a nuestros clientes a monitorear y optimizar sus consumos de energía, agua y gas mediante telemetría, sensórica y automatización, generando ahorros reales y trazables a través de nuestra plataforma de gestión de energía.Misión del cargoSerás el/la responsable de la operación de soporte post venta de Clickie: gestionarás de punta a punta nuestra ticketera, asegurando la resolución de todos los requerimientos de nuestros clientes, la continuidad del servicio y el cumplimiento estricto de los SLA comprometidos.Principales responsabilidadesGestionar la ticketera de soporte de Clickie, haciéndote cargo de la resolución del 100% de los requerimientos que ingresen.Revisar diariamente las alertas generadas en clientes, realizar seguimiento e informar causa y solución de cada incidencia.Coordinar al equipo de terreno, agendando visitas de soporte para los casos que no puedan resolverse de forma remota, con foco en recuperar el servicio de clientes desconectados.Comunicar de manera clara y oportuna el estado de incidencias y resoluciones a clientes, stakeholders y equipo de campo.Reportar directamente al responsable de Operaciones los temas resueltos y pendientes, asegurando el seguimiento hasta la resolución final de cada ticket.Generar reportes diarios, semanales y mensuales de KPI de soporte (tiempos de respuesta, resolución, conectividad de la base instalada, entre otros).Velar por el cumplimiento estricto de los SLA comprometidos con nuestros clientes.RequisitosTítulo técnico o de ingeniería en Electricidad, Electrónica o carrera afín, o experiencia equivalente como analista de soporte.Mínimo 1 año de experiencia en atención de soporte a clientes.Perfil híbrido técnico-administrativo: capacidad para entender el funcionamiento de soluciones y arquitecturas tecnológicas, y a la vez gestionar procesos, registros y reportes con rigurosidad.Excelentes habilidades de comunicación oral y escrita para el traspaso de información con clientes y equipos internos.Capacidad de organización, priorización y seguimiento de múltiples casos en paralelo.DeseableExperiencia en soporte de soluciones de telemetría, IoT, gestión de energía o servicios tecnológicos.Manejo de herramientas de ticketing/CRM y de reportería de indicadores.BeneficiosQué ofrecemosSer pieza clave en la operación de una empresa tecnológica en plena expansión internacional.Contrato a plazo fijo con paso a indefinido.Jornada de lunes a viernes, de 08:30 a 17:30, en nuestras oficinas de Santiago.Renta y beneficios a conversar en la entrevista.¿Te motiva asegurar que el servicio de nuestros clientes funcione siempre? Postula y conversemos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Product Manager Adquisición de Clientes</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Ofi. Alonso De Cordova 5320 - Producto Financiero, Chile</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56518/product-manager-adquisicion-de-clientes</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>8</v>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>sql, analisis, excel, power bi</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>1</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>¡En Banco Ripley Chile estamos buscando un/a Product Manager de Adquisición de Clientes! 💜🚀📊¿Te interesa impulsar el crecimiento de un negocio, entender qué mueve a los clientes y convertir datos en iniciativas comerciales concretas? Esta oportunidad puede ser para ti.🎯 ¿Cuál será tu misión?Impulsar el crecimiento de la base de clientes de Banco Ripley, identificando y desarrollando oportunidades comerciales dentro y fuera del ecosistema Ripley.Serás responsable de gestionar iniciativas orientadas a atraer nuevos clientes, facilitar la contratación de Tarjeta de Crédito Ripley y Cuenta Corriente, y acompañar su incorporación al banco, conectando las necesidades de los clientes con los objetivos del negocio.🚀 ¿Cuál será tu principal desafío?Construir una agenda de crecimiento que permita aumentar la captación de manera sostenible, cuidando no solo el volumen de nuevos clientes, sino también su calidad, el costo de adquisición y su activación inicial.Para lograrlo, deberás entender el comportamiento de los clientes, detectar oportunidades en sus journeys y coordinar mejoras comerciales, digitales y operacionales que reduzcan fricciones y aumenten la conversión.📊 ¿Qué harás en este rol?• Gestionar la hoja de ruta de adquisición y activación de clientes para Tarjeta de Crédito Ripley y Cuenta Corriente, definiendo prioridades, metas e iniciativas comerciales.• Identificar oportunidades de crecimiento a partir del análisis de clientes, segmentos, canales, comportamiento digital y tendencias del mercado.• Diseñar y coordinar campañas de captación en medios digitales, canales propios, sucursales, Tiendas Ripley y otros puntos de contacto relevantes.• Analizar el recorrido de los clientes desde el primer contacto con el banco hasta la contratación y activación de sus productos, detectando oportunidades de mejora.• Impulsar experimentos y mejoras de conversión en comunicaciones, ofertas, contenidos, experiencias digitales y procesos comerciales.• Monitorear indicadores como tráfico, solicitudes, clientes con oferta, aperturas, activación, conversión, costo de adquisición y cumplimiento de metas.• Administrar y hacer seguimiento al presupuesto de adquisición, evaluando la eficiencia y el aporte de cada canal e iniciativa.• Preparar análisis, proyecciones y presentaciones ejecutivas que faciliten la toma de decisiones comerciales.• Coordinar proyectos junto a equipos de Marketing, Riesgo, Productos, Canales, Analytics, Experiencia de Cliente, Tecnología, Legal y Retail.• Desarrollar propuestas de valor, beneficios y acciones segmentadas que aprovechen las oportunidades del ecosistema Ripley y fortalezcan la relación inicial de los clientes con el banco.🎯 ¿Qué buscamos en ti?• Título profesional de Ingeniería Comercial, Ingeniería Civil Industrial o una carrera equivalente vinculada con negocios, estrategia o gestión comercial. 🎓• Entre 1 y 3 años de experiencia profesional en áreas comerciales, marketing, productos, canales, growth, analytics o similares. 💼• Conocimientos de captación de clientes, marketing digital y gestión comercial.• Capacidad para analizar métricas de negocio y journeys de conversión. 📈• Manejo intermedio o avanzado de Excel y PowerPoint. 💻• Deseable conocimiento de herramientas como Google Analytics 4 y Power BI.• Deseable experiencia o interés en productos financieros, medios de pago y negocios digitales. 💳• Conocimientos básicos de metodologías ágiles y gestión de proyectos.• Manejo básico de SQL será considerado un plus.💜 ¿Por qué trabajar en Banco Ripley?🔹 Participarás en iniciativas comerciales y estratégicas con impacto directo en el crecimiento del banco.🔹 Tendrás exposición a distintas áreas del negocio y oportunidades reales de aprendizaje y desarrollo.🔹 Accederás a una tasa preferencial en productos Banco Ripley.🔹 Contarás con seguro complementario.🔹 Tendrás descuentos en Tiendas Ripley.🔹 ¡Y muchos otros beneficios!En Banco Ripley valoramos la diversidad y la inclusión. En el marco de la Ley 21.015, invitamos a todas las personas a postular. Si necesitas algún ajuste razonable durante el proceso de selección, puedes indicarlo al momento de tu postulación.📢 ¡Postula y sé parte del equipo que impulsa el crecimiento de Banco Ripley! 💜🚀BeneficiosDescripción de los beneficios de la vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Analista Contable - Outsourcing</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>KPMG Chile</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Las Condes, Metropolitana, Chile, Chile</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56485/analista-contable-outsourcing</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>3</v>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>1</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Buscamos un profesional proactivo y con gran interés en el área contable y financiera para unirse a nuestro equipo de Outsourcing.El candidato ideal será un Contador Auditor egresado o titulado, con una sólida base académica y la capacidad de aplicar conocimientos en normas IFRS.Se valorará la familiaridad con herramientas ofimáticas (Excel, PowerPoint, Word) y experiencia en el manejo de ERPs como Flexline.Si bien se considera la posibilidad de incorporar talento con 0 a 2 años de experiencia, se priorizará a aquellos con conocimientos prácticos en:Análisis de cuentas de activo y pasivo.Registro de información contable.Confección de F.29.Emisión de facturas.Gestión de activo fijo y su registro.Navegación y uso de la plataforma del Servicio de Impuestos Internos.Este rol ofrece una excelente oportunidad de desarrollo profesional dentro de una consultora líder a nivel mundial, participando activamente en la asesoría y gestión contable de diversos clientes.Beneficios¿Qué ganas tú?🌎Ser parte de una de las principales compañías de Auditoría y Consultoría a nivel mundial.🚀 Oportunidades de desarrollo profesional.🚑Seguro de salud complementario con contrato indefinido.💻Jornada de trabajo híbrida.🏢Oficinas de primer nivel ubicadas en Las Condes, frente al Parque Araucano.💯Múltiples convenios corporativos.🎉Actividades como fiestas, Meeting Points y encuentros de área para disfrutar con compañeros.🎂16 horas anuales a libre disposición y tu día de cumpleaños es completamente libre para que lo disfrutes como desees.En KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas , con un propósito claro, para una mejor sociedad. Valoramos las diversas habilidades y fortalezas, tanto personales como profesionales, que cada persona aporta. En KPMG estamos comprometidos con la Diversidad e inclusión, nuestras ofertas de empleo están disponibles con los ajustes razonables necesarios para tu proceso. Juntos, estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. ¡Anímate y ven a descubrir por qué somos la opción más clara! 🥇</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Programa Profesionales en Entrenamiento Quebrada Blanca</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Teck</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Pica, Tarapacá, Chile</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56503/programa-profesionales-en-entrenamiento-quebrada-blanca</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>2</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>1</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>En Teck, nuestro propósito es proporcionar recursos esenciales con los que el mundo cuenta para mejorar la vida, mientras que cuidamos de las personas, comunidades y la tierra que amamos.En Teck Quebrada Blanca buscamos el mejor talento joven (entre 0 y 2 años de experiencia laboral) de distintas profesiones relacionadas con la industria minera, para ser parte de nuestra nueva generación delPrograma Professionals in Training (PIT)para posiciones en nuestra faena.El programa PIT te permitirá:Ser un o una líder de seguridad, cumplir y promover nuestros principios y procedimientos de seguridad y medio ambiente.Adquirir conocimiento general del negocio minero, y específico en áreas críticas de la compañía.Desarrollar proyectos aplicados al negocio, que agreguen valor y permitan maximizar/optimizar los procesos al interior de la compañía.Procurar, incentivar y mantener un ambiente de trabajo seguro, y estimulante con un real compromiso por la seguridad de las personas y el medio ambiente, cumpliendo con el “Reglamento Interno de Orden Higiene y Seguridad” y “Código de Ética y Conducta”.Desarrollar tu conocimiento y experiencia técnica, y prepararte para ser un/a mejor líder en el futuro.Participar de entrenamientos de competencias adaptativas y técnicas diseñadas para ti.Responsabilidades principalesPromovemos la creación de espacios de trabajo respetuosos e inclusivos para todas las personas.Ofrecemos un paquete de compensaciones competitivo, y beneficios para los trabajadores/as y su grupo familiar, pudiendo optar a préstamos habitacionales, becas de estudios, entrenamiento para desarrollar nuevas competencias, entre otros.Podrás desarrollar tu talento Minera Quebrada Blanca, empresa líder en minería sustentable, que ya se encuentra en fase productiva en la Región de TarapacáNuestro programa tiene una duración aproximada de 18 meses y su objetivo es generar experiencia y habilidades para el trabajo en áreas específicas de la operaciónDurante el programa, los y las participantes contarán con una/a un Supervisor/a de Terreno y un Mentor/a, para acompañar y guiar el proceso de desarrollo e impulsar el crecimiento profesional.RequisitosProfesionales titulados/as de las carreras de Ingeniería Mecánica, Eléctrica, Electrónica, Metalúrgica, Química, Minas, Industrial, Geología o de otras especialidades afines a la industria minera.Sin experiencia laboral o con hasta 2 años de experiencia laboralManejo avanzado de herramientas Office (Excel, Power Point y otros).Deseable el dominio de idioma inglés.Deseable participación en actividades extracurriculares (centro de alumnos, ayudantías, voluntariados, etc.)Disponibilidad para trabajar en turnos 4x3 o 7x7 en Faena Quebrada Blanca (4.400 msnm) o en el puerto, a 60 km de Iquique</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Project Manager de Sostenibilidad</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Ofi Cerro Colorado 5240 - Comercial, Chile</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56487/project-manager-de-sostenibilidad</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>3</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>1</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Project Manager de SostenibilidadEnRipley Chile, lo tenemos todo ¡Solo nos falta tu talento! 🤩🩷Promovemos equipos diversos y colaborativos, buscando mejorar la experiencia de nuestros clientes a través de la innovación y la cultura de servicio. ¡Súmate a una industria ágil y desafiante!¡Postula para ser parte de nuestro equipo!Estamos en búsqueda de nuestro/a nuevo/aProject Manager de Sostenibildadpara nuestra Gerencia Marketing y Sostenibilidad Corp.Tumisiónserá ejecutar los proyectos ambientales y de economía circular de la Gerencia de Sostenibilidad, gestionando de manera eficiente el tratamiento de los residuos generados en las sucursales de Ripley Chile, el cumplimiento de la Ley REP, la medición de la huella de carbono y el levantamiento de los datos ambientales que sustentan la reportabilidad de la compañía, sin afectar la operación y con objetivo de cero multas.¿Cuáles serán tus principales funciones? 🚀Gestión operativa de residuos: gestionar el tratamiento de los residuos de las sucursales, asimilables a domiciliarios, embalajes y cartones, peligrosos y merma textil, entre otros.Cumplimiento Ley REP: preparar y presentar las declaraciones de envases y embalajes; coordinar con el sistema de gestión y asegurar trazabilidad y metas de valorización.Datos ambientales y huella de carbono: levantar y consolidar los datos ambientales de la compañía (residuos, energía, agua, emisiones) asegurando calidad y respaldo auditable, entre otras cosas.Proyectos de economía circular: ejecutar proyectos de circularidad: reciclaje y valorización textil, retiro en tienda, y apoyo a iniciativas de atributos sostenibles y activaciones lideradas por el área.Reportes y seguimiento: comunicar avances con reportes claros y presentaciones ejecutivas; mantener actualizados los KPIs ambientales del cuadro de mando.¿Qué valoramos en tu postulación? 🎯Título de Ingeniería Comercial, Civil o carrera afín.Deseable de 0-2 años de experiencia en gestión, operaciones, residuos, idealmente en retail, consumo masivo u operaciones con múltiples instalaciones.Conocimiento de gestión de proyectos y análisis de datos: Excel avanzado, BI; deseable SAP.Conocimientos de negociación, buenas relaciones interpersonales, capacidad de análisis y síntesis; diseño de presentaciones ejecutivas.¿Por qué trabajar en Ripley?🩷Pensamos en el bienestar de nuestros colaboradores, es por esto que contamos con atractivos beneficios corporativos como:Capacitaciones y entrenamiento enfocado a tu desarrollo de carrera.Tasa Preferencial en Productos Banco Ripley.Seguro Complementario Gratuito.Descuento en Tiendas Ripley.Desarrollo Profesional.Entre otros.En Ripley y Banco Ripley valoramos la diversidad e inclusión. Es por esto que, en el marco de la Ley 21.015, te invitamos a postular y si necesitas algún ajuste razonable durante el proceso, no dudes en indicarlo.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q160"/>
+  <dimension ref="A1:Q170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11266,6 +11266,680 @@
         </is>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Desarrollador de Realidad Virtual - Sede Callao</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Ferreyros</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Callao, Perú</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56603/desarrollador-de-realidad-virtual-sede-callao</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="P161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Misión:Desarrollar experiencias inmersivas de realidad extendida y realidad aumentada, mediante la programación de interacciones virtuales; para transformar digitalmente los entrenamientos en la línea Caterpillar y que permitan contribuir al desarrollo técnico de la compañía de acuerdo a los objetivos establecidos.Funciones:Crear contenido de realidad extendida alineado con los objetivos de capacitación de la empresa.Realizar la programación de aplicaciones interactivas para entornos de realidad extendida.Investigar y adoptar nuevas tecnologías para mejorar la calidad y eficiencia de las experiencias de aprendizaje.Garantizar la usabilidad y accesibilidad de las aplicaciones de realidad extendida, aplicando principios centrados en el usuario.Supervisar la actualización y mantenimiento de las aplicaciones de realidad extendida existentes, identificando oportunidades de mejora.Asumir otras funciones que le sean asignadas por su jefe inmediato, con el fin de mantener la eficiencia en el área y/o GerenciaRequisitos:Egresado(a) de carreras de Diseño de Videojuegos, Simuladores o afines.Experiencia laboral en el área de 1 año a más.DIsponibilidad para laborar de manera presencial en sede Callao (Av. Argentina)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Account Executive</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>DataScope</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56617/account-executive</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>1</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>DataScope.io es una empresa de software chilena que digitaliza operaciones de campo en más de 40 países 🌎. Estamos creciendo rápido en Latinoamérica y buscamos a alguien que tome las oportunidades que genera nuestro equipo SDR y las convierta en clientes, siempre con criterio, método y foco en el largo plazo.💡Lo que buscamos en pocas palabras:Alguien que hace buenas preguntas antes de vender, lleva el proceso con orden y entiende que el cierre es solo el comienzo de la relación con el cliente.📋 Tu día a día🎯 Tomar los leads calificados del equipo SDR y evaluarlos con criterio — entender si realmente podemos resolver su problema antes de avanzar.🖥️ Hacer demos del producto por videollamada, adaptadas a la realidad del cliente y su industria.🤝 Desarrollar propuestas comerciales y llevar negociaciones hasta el cierre — buscando siempre un acuerdo que funcione para ambas partes.📊 Mantener el pipeline ordenado en HubSpot y dar seguimiento consistente a las oportunidades activas.💬 Colaborar con el equipo SDR, Marketing, Customer Success y Producto — compartiendo feedback real del mercado para mejorar el proceso comercial.⚡ Participar activamente en la estrategia comercial del equipo y contribuir al cumplimiento de métricas colectivas.🔍 Perfil que buscamos...💻Experiencia en ventas SaaSAños en roles de cierre, idealmente en ciclos de venta consultivos.🗣️Comunicación clara y efectivaSaber escuchar, hacer las preguntas correctas y transmitir valor con simplicidad.📈Orientación a resultadosTe fijas metas, mides tu avance y buscas mejorar tus números semana a semana.💪Autonomía y proactividadGestionas tu pipeline con orden y no esperas que te empujen para avanzar oportunidades.🌱Mentalidad de crecimientoEres autocrítico, aprendes de cada ciclo de venta y buscas retroalimentación activamente.Beneficios🎁 Beneficios:Porque trabajar bien también significa vivir bien.🏢 Trabajo híbrido: Oficina en WeWork Santiago con horarios flexibles si estás en Santiago📚Fondo para aprendizaje: Apoyo para cursos, libros y desarrollo profesional.⏰Work-on-you hour: Una hora semanal dedicada a tu desarrollo profesional.🌴15 días hábiles de vacaciones: Acumulables y flexibles para que los uses cuando quieras.🤖 Acceso a herramientas de IA pagadas: Contarás con licencias de herramientas de inteligencia artificial para potenciar tu productividad, aprendizaje y trabajo diario🎂Día libre en tu cumpleaños: Porque ese día es tuyo.🍼Licencia de paternidad extendida: Más tiempo para estar presente en los momentos que importan.🏃Wellhub + hábitos saludables: Acceso a gimnasios e iniciativas de bienestar.🛡️Seguro complementario: Cobertura adicional de salud para ti y para los que más quieres.💻MacBook: Equipo de trabajo desde el primer día para uso laboral.✈️Viajes de integración: Nacionales e internacionales con el equipo.📊Evaluación por objetivos: Te medimos por resultados, no por horas conectado.🚀Plan de carrera real: Crecimiento dentro de la empresa con planes de desarrollo concretos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Ejecutivo Comercial</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Wherex</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Nuevo León, México</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56608/ejecutivo-comercial</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>1</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>¡En Wherex buscamos a nuestro/a próximo/a Ejecutivo/a de Operaciones Comerciales!Estarás a cargo de la gestión diaria de licitaciones que generan nuestros clientes y que son el corazón de nuestro negocio, para esto te apoyarás en nuestros sistemas con IA y de nuestra base de datos de más de 70 mil proveedores.¿Qué harás?- Gestionar diariamente licitaciones asignadas por jefatura o área.- Obtener las ofertas de los proveedores correctos, para aumentar la probabilidad de adjudicación de las licitaciones.- Captar e inscribir nuevos proveedores, de acuerdo a los requerimientos solicitados.- Identificar oportunidades en los procesos de la operación para proponer soluciones de mejora.- Mantener información de la gestión realizada actualizada y ordenada en las diferentes herramientas de la compañía.¿Qué estamos buscando?- Titulados de Administración de Empresas, Comercio Exterior, Negocios Internacionales o alguna carrera afín.- 1 a 2 años de experiencia.- Interés por desarrollarte en el mundo de la atención al cliente.- Ser una persona dinámica, orientada a los resultados y ordenada.- Vivir en Monterrey (Aquí están nuestras oficinas).**Para completar tu postulación, no olvides realizar los test de Genomawork del link adjunto en esta publicación.¡Este es tu próximo desafío laboral!BeneficiosNuestros beneficios:- 25 días de vacaciones al año.- Seguro gastos medicos mayores.- Ambiente dinámico.- Ambiente laboral de primera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>QA automation</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>BCP</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56605/qa-automation</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>11</v>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>sql, informatica, azure, git, javascript</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>1</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Queremos que tu talento se sume al del BCP, para seguir siendo el banco que todo el tiempo está innovando, es pionero y digital. Juntos tendremos la posibilidad de generar un impacto positivo en nuestro país, teniendo como objetivo que los peruanos logren transformar sus planes en realidad.“Somos una organización comprometida con la igualdad de oportunidades para hombres y mujeres, y en línea con ello, todos nuestros procesos de selección se rigen bajo una política de igualdad de derechos y oportunidades, donde nuestros postulantes son considerados sin importar su origen, lengua, raza, sexo, idioma, religión, opinión, edad, talla, procedencia educativa, condición económica, social, física, mental o cualquier otra índole, promoviendo así una cultura de respeto mutuo”¡Se parte de nuestro equipo comoQUALITY ENGINEER! #ÚnetealequipoBCP¿Ya sabes que hacemos los QUALITY ENGINEER en el BCP?Es el profesional encargado de asegurar la calidad del producto desarrollado, garantizando que todo funcione correctamente de acuerdo a los estándares definidos por el banco.Nuestras responsabilidades principales son:Analizar los requerimientos del usuario.Elaborar estrategia de pruebas.Estimar, priorizar, planificar actividades de prueba (preparación de data, ejecutar, documentar resultados, etc.)Diseñar e implementar casos de pruebas manuales yautomatizados.Identificar, registrar y asegurar que los defectos encontrados sean corregidos antes de entregar el software al cliente.Ejecutar pruebas funcionales (manuales y/oautomatizados).Verificar los cambios en ambiente de productivo.Debes postular a este rol solo si…Profesional de la carrera de Ingeniería de Sistemas, Computación, Informática, Software, Electrónica o carreras aﬁnes.Experiencia de mínimo 1 año como Quality Engineer realizando pruebas automatizadas.Tienes conocimiento o ya cuentas con la Certificación ISTQB Foundation.Tienes conocimiento del marco de trabajo Agile / Scrum / KanbanTienes conocimiento de las técnicas y estrategias de pruebas.Y sobre todo si:Dominas los lenguajes de programación: Java (indispensable), Javascript, .Net/C#.Manejas SQL (en general) o bases de datos no relacionales.Tienes experiencia práctica con herramientas parapruebas automatizadas(web, móvil, APIs, cliente/servidor-mainframe): Selenium, Serenity BDD, Cucumber, Appium, Karate DSL, Calypso, etc.Manejas herramientas de gestión de pruebas: Jira-XrayCreas y redactas planes de prueba y casos de prueba claros, concisos y completos (Gherkin).Manejas herramientas para pruebas de microservicios, flujos en message broker o mobile: Postman, SoapUI.Manejas herramientas de integración continua: Jenkins, Bitbucket, Git, Gitlab, Maven, Gradle, Artifactory entre otros.Manejas herramientas de pruebas de rendimiento: JMeter, HP Load Runner, Azure Load Testing, etc.Deseable conocimiento de pruebas de seguridad (detección de vulnerabilidades): Owasp zap, Burpsuite.Patrones de diseño: Page Object Model, Screenplay, etcConocimiento medio de prácticas de Testing Continuo (shift left, shift right).BeneficiosSeguirás sumando experiencia y desarrollo profesional gracias al equipo de grandes líderes, una cultura de colaboración que inspira y oportunidades para innovar. Si estás dispuesto a asumir grandes retos, llegó el momento de sumarte al BCP.Pago de Bonos por Desempeño.Flex time.Plan de Salud para ColaboradoresOportunidades de desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Ejecutivo Banca Persona - Exclusiva</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>BCP</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56604/ejecutivo-banca-persona-exclusiva</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="P165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>Buscamos a los que tienen ganas de transformar el país. A los que quieren llegar lejos. Por qué esto no es solo un trabajo. Esto es desafiarte en grande para impactar en grande. Esto es el BCP y te estamos buscando para que formes parte de nuestro equipo comoEjecutivo Banca Persona - Exclusiva¿Cuál es el reto?Construir relaciones a largo plazo con los clientes a través de la efectiva gestión comercial de su cartera.¿Cómo impactarás en grande?Responsable de interactuar con los clientes de manera ágil y construir relaciones duraderas de manera remota (no presencial), manteniendo actualizada la información de la cartera de clientes.Según el tipo de cartera debe priorizar de acuerdo a la metodología establecida, a fin de mantener el relacionamiento, dar soporte operativo y monitorear la satisfacción postventa, a fin de generar percepción de accesibilidad y disponibilidad permanente, traducidas en respuestas rápidas y efectivas.Cumplir con su metodología de trabajo, a fin de detectar las necesidades de su cartera de clientes y promover el logro de los objetivos de planilla de desempeño, así como el relacionamiento con el cliente construyendo relaciones a largo plazo.Elaborar una propuesta comercial de acuerdo con el perfil de riesgo de cada cliente.Según el tipo de cartera debe priorizar de acuerdo a la metodología establecida, a fin de mantener el relacionamiento, dar soporte operativo y monitorear la satisfacción postventa, a fin de generar percepción de accesibilidad y disponibilidad permanente.¿Qué necesitamos de ti?Perfil Diverso: Egresado(a) de la carrera de Ing. Industrial, Economía, Administración, Gestión y Alta dirección o afines al negocio.Experiencia gestionando cartera de clientes y productos de banca personal (de preferencia del sector bancario).Experiencia en banca personal, banca pyme, banca negocio, telemarketing afines.¿Por qué unirte a nuestro equipo?Ser parte de la empresa #1 en Merco Talento 2025Ingreso a planilla BCP desde tu primer día.Accede a incentivos por tu esfuerzo/desempeñoAcompañamiento de líderes expertos y referentes en la banca.Acceso a descuentos en productos financieros.Beneficios corporativos exclusivos por provincia para disfrutar con tu familia.Formarás parte de una cultura constante de reconocimientos.Sí, a ti. Te estamos buscando ¡Únete al equipo BCP!“Somos una organización comprometida con la igualdad de derechos y oportunidades. Nuestros procesos de selección se rigen bajo una política donde nuestras/os postulantes son consideradas/os sin importar su origen, género, raza o cualquier otra característica, condición o preferencia, promoviendo así una cultura de respeto mutuo."</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Investor Analyst</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Cumplo</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56612/investor-analyst</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>3</v>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>1</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>Buscamos a nuestro próximoInstitutional Investors Analystpara liderar la gestión operacional, estructuración y control del flujo de inversión de fondos e inversionistas institucionales en nuestra plataforma. Tu objetivo será asegurar la máxima eficiencia del costo de capital, optimizar la liquidez del portafolio y garantizar una ejecución impecable en cada operación.Principales Desafíos y Responsabilidades 🎯Ejecución y Gestión de Fondos: Liderar la asignación y ejecución del capital de fondos de inversión e inversionistas institucionales sobre las operaciones publicadas en la plataforma.Control Operacional y Liquidez: Administrar la disponibilidad de activos en plataforma, monitoreando el flujo de caja, los niveles de utilización de fondos y ejecutando conciliaciones y controles rigurosos.Gestión de Incidencias y Contingencias: Resolver proactivamente desviaciones operacionales, reprocesos e incidencias, asegurando la continuidad del flujo financiero.Relacionamiento Institucional: Mantener una comunicación fluida y ejecutiva con fondos e inversionistas institucionales mediante el seguimiento periódico de sus portafolios de deuda.Coordinación Transversal: Colaborar directamente con los equipos de Riesgo, Operaciones, Tesorería, Producto y Comercial para asegurar una ejecución continua y eficiente.Eficiencia y Automatización: Proponer e implementar mejoras continuas y automatización de procesos para escalar la administración de fondos.Reportería Ejecutiva: Diseñar e interpretar KPIs e indicadores clave para la toma de decisiones estratégicas de la gerencia.Perfil Buscado 🕵️‍♂️Experiencia: 1 a 2 años gestionando operaciones financieras, fondos de inversión, banca corporativa, mercado de deuda privada o fintechs.Dominio Técnico: Trayectoria comprobable en administración de procesos financieros, conciliaciones de capital, gestión de portafolios y manejo de stakeholders institucionales.Conocimiento de Industria: Comprensión del mercado de deuda privada, instrumentos de capital de trabajo, fondos de inversión y gestión de riesgo operacional.Herramientas de Análisis: Manejo de Excel avanzado (modelación, tablas dinámicas y análisis de datos). Valorable el manejo de herramientas BI (Qlik, Power BI o similares).Idiomas: Nivel de inglés intermedio-alto para negociación e interacción en entornos financieros.BeneficiosBeneficios y Propuesta de Valor 🎁Flexibilidad y Descanso: 3 días extra de vacaciones al año, 2 días administrativos, esquema Vacaciones 5+1 y semanas WFA (Work From Anywhere) en invierno y verano.Personal Days: Días libres asignados para tu cumpleaños y mudanza.Bienestar Integral: Seguro complementario de salud, convenio con Caja Los Andes y sistema flexible de puntos.Cultura y Propósito: Sé parte de la primera fintech certificada como Empresa B en la región, impulsando el crecimiento sustentable de las empresas que mueven la economía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Encargado de Inventarios - Outsourcing</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>KPMG Chile</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56609/encargado-de-inventarios-outsourcing</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>2</v>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>1</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Perfil Ideal: Encargado/a de Inventarios - OutsourcingBuscamos un profesional con formación técnica o universitaria en Logística, Ingeniería en Logística, Administración de Empresas o Ingeniería Industrial, con una sólida experiencia de al menos 1 año en supervisión de inventarios, control de existencias o activos fijos.El candidato ideal poseerá experiencia liderando equipos de trabajo en terreno y un profundo conocimiento en procesos de conciliación y control de inventarios. Se valorará el manejo intermedio o avanzado de Microsoft Excel, así como conocimientos en gestión de activos fijos y deseable experiencia con lectores de códigos de barras o dispositivos de captura de datos.Las competencias clave para este rol incluyen un fuerte liderazgo y capacidad de supervisión, excelentes habilidades de organización y planificación, una marcada orientación al detalle y una sólida capacidad analítica. Asimismo, se espera proactividad, habilidad para la resolución de problemas y destacadas competencias de comunicación y trabajo en equipo. Es indispensable la disponibilidad para viajar dentro del país según los requerimientos de los proyectos.Beneficios¿Qué ganas tú?🌎 Ser parte de una de las principales compañías de Auditoría y Consultoría a nivel mundial. 🚀 Oportunidades de desarrollo profesional y crecimiento de carrera.🚑 Seguro de salud complementario con contrato indefinido.💻 Modalidad de trabajo híbrida.🏢 Oficinas de primer nivel ubicadas en Las Condes, frente al Parque Araucano.💯 Múltiples convenios corporativos.🎉 Actividades de integración, Meeting Points, celebraciones y encuentros de área.🎂 16 horas anuales de libre disposición y día de cumpleaños libre.En KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas , contribuyendo a construir una mejor sociedad. Valoramos las diversas habilidades y fortalezas que cada persona aporta. Estamos comprometidos con la diversidad, equidad e inclusión, por lo que nuestras oportunidades laborales consideran los ajustes razonables necesarios para cada proceso de selección. Juntos estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial.🥇¡Anímate y ven a descubrir por qué somos la opción más clara!</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Asistente de Producto (Retail)</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56613/asistente-de-producto-retail</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>1</v>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="O168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>¿Te apasiona el análisis, la planificación y la gestión de inventarios? ¡Esta oportunidad puede ser para ti!Somos una empresa de retail y buscamos a una persona analítica, organizada y proactiva que quiera sumarse a nuestro equipo para asegurar una gestión eficiente delinventarioy contribuir al crecimiento de nuestras marcas en tiendas. Tendrás un rol clave en la planificación, reposición y distribución deproductos, apoyando la toma de decisiones a través delanálisisde ventas y desempeño de las colecciones.¿Cuáles serán tus principales desafíos?Analizarventas, inventarios y desempeño de productos para asegurar una correcta disponibilidad en tiendasPlanificarygestionarla reposición de productos, considerando niveles de stock, demanda y tiempos de abastecimientoCoordinarla distribución de productos y realizar traspasos entre tiendas para optimizar el inventarioMonitorearel desempeño de las colecciones y proponer acciones que contribuyan al cumplimiento de los objetivos comerciales.Ejecutaractualizacionesde precios y apoyar la implementación de promociones y campañas comerciales.Coordinar con distintas áreas de la compañía y mantener comunicación con las tiendas para asegurar una correcta ejecución de la estrategia comercial.Supervisarlos movimientos de inventario y apoyar procesos de apertura y cierre de tiendas.Si disfrutas trabajar con datos, analizar información y generar impacto en la operación comercial, ¡te invitamos a postular y ser parte de nuestro equipo!</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Asistente de Compras y Suministros</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Forus</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Av. Las Condes 11.281, Chile</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56601/asistente-de-compras-y-suministros</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>3</v>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="O169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Únete a FORUS como nuestro próximo/aAsistente de Compras y Suministros¿Te apasiona el análisis de proveedores, la negociación estratégica y asegurar que la operación nunca se detenga? ¿Disfrutas optimizar recursos, evaluar propuestas y mantener un control riguroso en cada proceso? Entonces esta oportunidad es para ti.En nuestra compañía buscamos un/a Asistente de Compras y Suministros para integrarse a la Gerencia de Administración y Finanzas. Serás una pieza clave en el ciclo de adquisición de bienes y servicios, asegurando la continuidad operativa, el cumplimiento normativo y la máxima eficiencia en cada negociación.¿Cuál será tu desafío?Liderar la gestión estratégica de compras, negociando con proveedores, optimizando presupuestos y garantizando que cada adquisición cumpla con los estándares de calidad, tiempo y compliance requeridos por la organización.¿Qué harás en este rol?- Liderar cotizaciones y licitaciones: Recepcionar requerimientos internos, buscar proveedores y elaborar cuadros comparativos para adjudicaciones técnico-económicas.- Administrar el calendario de negociación: Monitorear el cronograma de contratos y servicios vigentes para anticipar renovaciones o renegociaciones sin afectar la operación.- Evaluar y desarrollar proveedores: Ampliar la red de suministros y mantener relaciones fluidas para garantizar plazos y calidad.- Ejecutar negociaciones estratégicas: Lograr el equilibrio ideal entre costo, calidad y oportunidad de entrega.- Garantizar el control normativo: Asegurar el cumplimiento de las políticas de compliance, auditoría y presupuesto en cada compra.¿Por qué sumarte a nuestro equipo?Ofrecemos un entorno dinámico donde tu rigurosidad y visión analítica impactarán directamente en los resultados del negocio. Trabajarás de forma transversal con distintas áreas, desarrollando tus habilidades de negociación y gestión en un ambiente colaborativo.¿Qué buscamos?- Título profesional en Administración de Empresas, Ingeniería Comercial, Comercio Exterior o carrera afín.- 1 a 2 años de experiencia en compras, abastecimiento o logística.- Manejo de ERP (SAP, Oracle o similares).- Dominio intermedio de Microsoft Excel para análisis de datos.Nos gustaría que fueras una persona que...- Posee una gran capacidad de planificación, orden y metodología.- Trabaja con rigurosidad y orientación al logro.- Tiene facilidades para comunicarse y construir relaciones sólidas con proveedores y clientes internos.Beneficios- Descuentos en marcas Forus.- Convenios y beneficios de salud y bienestar.- Capacitaciones y oportunidades de desarrollo.- Movilidad y crecimiento interno.- Actividades y beneficios orientados a la calidad de vida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Analista de Operaciones</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Tanner</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56615/analista-de-operaciones</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>5</v>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>analisis, excel, power bi</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>1</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>¡En Tanner buscamos a: Analista de Operaciones!🚀Si te interesa entender cómo funcionan los procesos, analizar información, detectar oportunidades de mejora y proponer nuevas formas de hacer las cosas, esta oportunidad puede ser para ti.Buscamos una persona que se integre a nuestraGerencia de Operaciones, aportando una mirada analítica y crítica que nos ayude a fortalecer el control, la eficiencia y la mejora continua de nuestros procesos.¿Cuáles serán tus principales desafíos?Monitorear y dar seguimiento a procesos operativos, identificando desviaciones, riesgos e incidencias.Analizar datos e indicadores para detectar oportunidades de eficiencia y optimización.Investigar causas raíz frente a errores, incidentes o contingencias y apoyar la implementación de soluciones.Proponer mejoras que contribuyan a simplificar y optimizar la operación.Apoyar el control y seguimiento de procesos críticos, resguardando la calidad y el cumplimiento de los procedimientos.Participar en iniciativas deautomatización, transformación digital y mejora continua.Trabajar colaborativamente con distintas áreas de Tanner para gestionar requerimientos y resolver desafíos operacionales.Requisitos:Profesionales deIngeniería Comercial, Ingeniería Civil Industrial, Contador Auditor o carreras afines, con1 a 3 años de experienciaen Operaciones, Procesos, Control de Gestión o áreas similares.Excel:nivel intermedio o avanzado.Conocimientos engestión y análisis de procesos.Experiencia o conocimientos enelaboración y seguimiento de indicadores de gestión.Manejo de herramientas de visualización de datos, comoPower BI o similares.Conocimientos degestión documental y mejora continua.Para este rol será especialmente importante que cuentes con:Capacidad analítica y habilidad para resolver problemas.Proactividad, autonomía e iniciativa.Orientación al detalle y al control.💡 ¿Qué perfil queremos encontrar?Más que alguien que solo ejecute tareas operativas, buscamos una personacuriosa, analítica y con mirada crítica, que se pregunte cómo podemos hacer mejor las cosas, cuestione constructivamente los procesos existentes y transforme sus análisis en propuestas concretas de mejora.🌱 Crece junto a nosotrosEste rol te permitirá conocer transversalmente la operación, relacionarte con distintas áreas y participar en iniciativas de mejora y transformación, desarrollando progresivamente tus capacidades de análisis, gestión operacional y automatización.Si te motiva aprender, analizar y generar mejoras concretas en la forma en que hacemos las cosas, queremos conocerte.👉Postula y sé parte de Tanner.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q170"/>
+  <dimension ref="A1:Q176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11940,6 +11940,412 @@
         </is>
       </c>
     </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Asistente de Auditoría C</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Forvis Mazars</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56649/asistente-de-auditoria-c</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>1</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" t="n">
+        <v>0</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Con nosotros tienes la oportunidad de pertenecer a una firma internacional con un importante potencial de crecimiento y un equipo de más de 40.000 profesionales altamente capacitados, que brinda servicios profesionales generando alto impacto en todos nuestros clientes en más de 100 países en los cinco continentes.Podrás formar parte de un equipo que valorará tus ideas, apoyará tus ambiciones y celebrará tus éxitos. En Forvis Mazars nos proponemos impulsar la colaboración y la flexibilidad, las diversas perspectivas de nuestros colaboradores y el progreso.Hoy buscamos un Asistente para el área de Auditoría.Tareas/ResponsabilidadesBrindar asesoría y soporte a las distintas áreas de la firma.Analizar, monitorear y optimizar procesos, que apoyen la toma de decisiones.Apoyo en informes de auditoría.Revisión de documentación.RequisitosContador Auditor hasta 2 años de experiencia laboral en firmas de auditoría externa, servicios profesionales o entornos regulados.Manejo de herramientas Microsoft Office.OfrecemosModalidad de trabajo híbrida.Seguro de salud y dental.Entorno joven, dinámico y altamente colaborativo.Oportunidades de aprendizaje continuo y desarrollo profesional en un área estratégica de la firma.Este cargo es compatible para personas con discapacidad, se enmarca en la ley 21.015, que incentiva la inclusión de personas con discapacidad al mundo laboral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Auditora Interna</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Fid seguros</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56646/auditor-a-interna</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>1</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="n">
+        <v>1</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>FID Seguros es una compañía diseñada para integrar la tecnología como base de la experiencia de corredores y clientes. Nos definimos como una insurtech de seguros generales, que utiliza la digitalización para ofrecer experiencias simples, ágiles y transparentes, apalancado en la innovación, en el uso de la tecnología, en el trabajo en equipo y el compromiso.Actualmente nos encontramos en búsqueda de un/a practicante para el área de Auditoría.¿Qué harás en este rol?Participar en la implementación de auditorías continuas a distintas áreas de la compañía y ser responsable de su ejecución.Apoyar en el desarrollo del plan anual de auditoría interna, en la revisión de procesos y en la realización de visitas a sucursales.Revisar documentos de respaldo para muestras de auditoría y analizar bases de datos.Documentar papeles de trabajo con la información obtenida de las revisiones.Apoyar en la elaboración de informes de auditoría, en la identificación de debilidades de control interno y redacción de recomendaciones.RequisitosTítulo de Contador Público y Auditor.Conocimiento en Normas Globales de Auditoría Interna.Conocimiento de intermedio o avanzado de Microsoft Office2 años de experiencia en auditoría, interna o externa (Big Four), a Compañías de Seguros.BeneficiosLo que ofrecemos:Oportunidad de desarrollarte en una compañía joven, dinámica y con excelente clima laboral, donde podrás crear y dejar tu impronta en cada proceso.Modalidad de trabajo híbridaHorario flexibleBeneficios como bono por desempeño, ajustes semestrales por IPC, seguro complementario y de vida, días administrativos, acuerdos de descuentos varios, entre otrosEsta oferta laboral se rige bajo la Ley Nº 21.015 que incentiva la inclusión de personas con discapacidad al mundo laboral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Consultor Financiero Contable</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Murex Chile</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56627/consultor-financiero-contable</t>
+        </is>
+      </c>
+      <c r="G173" t="n">
+        <v>3</v>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>sql</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>1</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="n">
+        <v>1</v>
+      </c>
+      <c r="O173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>🌍 ¿Quiénes somos?Somos Murex, líder global en tecnología financiera (fintech) especializada en soluciones de trading, gestión de riesgo y procesamiento para mercados de capitales.Con presencia en 19 oficinas alrededor del mundo y más de 3.500 colaboradores de más de 60 nacionalidades, desarrollamos, implementamos y damos soporte a una plataforma utilizada por bancos, asset managers, corporaciones y utilities a nivel global.En Murex trabajarás en una industria que está a la vanguardia de la innovación, en un entorno centrado en las personas, donde podrás crecer rápidamente sin dejar de ser tú mismo/a. Formarás parte de un equipo global, diverso y altamente colaborativo.🚀 ¿Qué harás?Como Consultor Contable en el equipo de Finance &amp; P&amp;L de Murex, trabajarás en estrecha colaboración con nuestros clientes, incluyendo grandes bancos, hedge funds, gestores de activos, compañías de seguros, corporaciones y otros participantes del mercado de capitales.Asesoría en mejores prácticas:Proporcionar orientación sobre las mejores prácticas de Murex en procesos de P&amp;L, contabilidad, contabilidad de coberturas (hedge accounting), gestión de posiciones y reportes financieros.Implementaciones en cliente:Soporte a los trading designers durante implementaciones o upgrades, participando en las fases de levantamiento de requerimientos, diseño, construcción, pruebas y despliegue; incluyendo workshops, preparación de documentación, configuración de requerimientos del cliente y ejecución de pruebas de calidad.Soporte a clientes:Gestionar incidencias abiertas y apoyar en actividades de upgrade.Comunicación:Gestionar la relación con el equipo de producto en un área de especialización y apoyar en la construcción del roadmap del producto para la región.Documentación y capacitación:Proporcionar documentación y formación tanto interna como externa.🎯 ¿Qué buscamos?Formación académica:Título profesional en carrera afín.  Contabilidad, Ingeniería comercial, Ingeniería en control de gestiónExperiencia:1 a 2 añosConocimientos técnicos:Fuerte interés o conocimientos en Tesorería y Mercados de CapitalesIdiomas:Inglés avanzado (excluyente).Habilidades técnicas(no excluyentes): Conocimientos en sistemas operativos Unix/Linux, SQL y programación básicaDisponibilidad para viajar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Supervisor de Tarjeta Trainee Costanera Center</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Tda Costanera Center (Gesic) - Nuevos Clientes, Chile</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56620/supervisor-de-tarjeta-trainee-costanera-center</t>
+        </is>
+      </c>
+      <c r="G174" t="n">
+        <v>7</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>trainee</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>1</v>
+      </c>
+      <c r="L174" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" t="n">
+        <v>1</v>
+      </c>
+      <c r="O174" t="n">
+        <v>1</v>
+      </c>
+      <c r="P174" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Supervisor de Tarjeta Trainee Costanera CenterEnBanco Ripley Chile,lo tenemos todo ¡Solo nos falta tu talento!Somos un equipo diverso, ágil y colaborativo, enfocado en mejorar la experiencia de nuestros clientes a través de la innovación y una sólida cultura de servicio.Súmate a una industria ágil y desafiante ¡Postula para ser parte de nuestro equipo!Estamos en búsqueda de nuestro/aSupervisor de Tarjeta Trainee.Tu misión 🚀Tu misión será formarse en la supervisión y gestión comercial de la tarjeta y productos asociados del banco, adquiriendo experiencia en liderazgo de equipos, normativas regulatorias y estrategias de colocación, con el fin de prepararse para asumir de manera autónoma la posición de Supervisor de Tarjeta.¿Cuáles serán tus principales desafíos? 🚀Participar en un plan de formación estructurado sobre productos financieros, normativas internas y regulatorias.Apoyar a la jefatura en la supervisión y coordinación del equipo de ejecutivos de tarjeta en sucursal.Colaborar en campañas de captación de clientes, colocación de tarjetas y promoción de beneficios.Acompañar el monitoreo de indicadores de gestión: colocación, activación, mora temprana y uso de tarjeta.Contribuir en la resolución de consultas de clientes y derivar casos complejos bajo supervisión.Apoyar en la capacitación del equipo de ventas, participando en entrenamientos y reforzando buenas prácticas.Asegurar el cumplimiento de políticas de riesgo, seguridad y prevención de fraudes financieros.Desarrollar habilidades de liderazgo, comunicación y gestión comercial a través del acompañamiento de la jefatura.¿Por qué trabajar en Ripley? ❤️💜Entendemos y nos amoldamos a tu estilo de vida, promoviendo beneficios que fomenten la flexibilidad en la manera de trabajar.Gracias a Rworks nos conectamos desde cualquier lugar, y contamos con modernos espacios colaborativos para mantener la cohesión con nuestros equipos.Tendrás acceso a seguros complementarios de salud, convenios con reconocidas universidades y beneficios preferenciales en Banco Ripley.Revisa más detalles sobre vida en la empresa en nuestro LinkedIn “Ripley Chile” y "Banco Ripley Chile". Tipo de Puesto: Plazo Fijo Fecha esperada de Contratación: 18/11/2026 ¡TRABAJA CON NOSOTROS!BeneficiosDescripción de los beneficios de la vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Business Development Representative (BDR)</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Pop Estate Chile SPA</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56630/business-development-representative-bdr</t>
+        </is>
+      </c>
+      <c r="G175" t="n">
+        <v>3</v>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>modelo</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>1</v>
+      </c>
+      <c r="L175" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="n">
+        <v>0</v>
+      </c>
+      <c r="O175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>EnPop Estateestamos creciendo y buscamos incorporar un/aBusiness Development Representative (BDR)para formar parte de nuestro equipo comercial.🔍🚀Mientras muchos hablan de crisis en el sector de software, enPop Estate seguimos celebrando récords de ventas y nuevos clientes.Buscamos a alguien comercial, con mucha motivación y orientado/a a resultados, que quiera desarrollarse en la venta de SaaS y construir relaciones con empresas del sector inmobiliario.💼Desafíos del Rol:Prospectar activamente nuevos clientes a través de canales outbound.Contactar y calificar prospectos provenientes de iniciativas inbound.Detectar necesidades y dolores asociados a la gestión de propiedades en arriendo.Coordinar y realizar reuniones comerciales y demostraciones de Pop Estate.Gestionar oportunidades comerciales y realizar seguimiento hasta el cierre.Mantener actualizado el pipeline y registrar la actividad comercial en HubSpot.Trabajar junto al equipo para mejorar continuamente el proceso comercial y alcanzar los objetivos de venta.¿Qué ofrecemos?Modelo de trabajo con comisiones competitivas.Flujo constante de leads calificados.Apoyo comercial, administrativo, operativo y técnico.Posibilidades reales de crecimiento dentro de un equipo en expansión.Nos interesa sumar a alguien que cumpla con:Experiencia previa en ventas ya sea en el sector inmobiliario o SaaS.Personalidad ágil, proactiva, perseverante, motivada y orientada a los resultados.Enfoque en el cliente y comunicación clara.Capacidad de trabajar de manera autónoma y en equipo.Motivación por aprender y desarrollarse en el mundo SaaS y tecnología.BeneficiosBeneficios:💵Sueldo base + comisiones por cumplimiento de objetivos.💻Modalidad de trabajo mixta, solo 1 día presencial!🛠️Herramientas comerciales y tecnológicas para desarrollar tu gestión.🧠Capacitación y acompañamiento comercial.Si te gusta vender, prospectar, conversar con clientes y quieres desarrollar tu carrera comercial dentro de una empresa tecnológica con foco en el mercado inmobiliario…Queremos conocerte! Postula ahora completando el formulario y crezcamos juntos</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Supervisor de Tarjeta Trainee Costanera Center</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Tda Costanera Center (Gesic) - Nuevos Clientes, Chile</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56621/supervisor-de-tarjeta-trainee-costanera-center</t>
+        </is>
+      </c>
+      <c r="G176" t="n">
+        <v>7</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>trainee</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>1</v>
+      </c>
+      <c r="L176" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="n">
+        <v>1</v>
+      </c>
+      <c r="O176" t="n">
+        <v>1</v>
+      </c>
+      <c r="P176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Supervisor de Tarjeta Trainee Costanera CenterEnBanco Ripley Chile,lo tenemos todo ¡Solo nos falta tu talento!Somos un equipo diverso, ágil y colaborativo, enfocado en mejorar la experiencia de nuestros clientes a través de la innovación y una sólida cultura de servicio.Súmate a una industria ágil y desafiante ¡Postula para ser parte de nuestro equipo!Estamos en búsqueda de nuestro/aSupervisor de Tarjeta Trainee.Tu misión 🚀Tu misión será formarse en la supervisión y gestión comercial de la tarjeta y productos asociados del banco, adquiriendo experiencia en liderazgo de equipos, normativas regulatorias y estrategias de colocación, con el fin de prepararse para asumir de manera autónoma la posición de Supervisor de Tarjeta.¿Cuáles serán tus principales desafíos? 🚀Participar en un plan de formación estructurado sobre productos financieros, normativas internas y regulatorias.Apoyar a la jefatura en la supervisión y coordinación del equipo de ejecutivos de tarjeta en sucursal.Colaborar en campañas de captación de clientes, colocación de tarjetas y promoción de beneficios.Acompañar el monitoreo de indicadores de gestión: colocación, activación, mora temprana y uso de tarjeta.Contribuir en la resolución de consultas de clientes y derivar casos complejos bajo supervisión.Apoyar en la capacitación del equipo de ventas, participando en entrenamientos y reforzando buenas prácticas.Asegurar el cumplimiento de políticas de riesgo, seguridad y prevención de fraudes financieros.Desarrollar habilidades de liderazgo, comunicación y gestión comercial a través del acompañamiento de la jefatura.¿Por qué trabajar en Ripley? ❤️💜Entendemos y nos amoldamos a tu estilo de vida, promoviendo beneficios que fomenten la flexibilidad en la manera de trabajar.Gracias a Rworks nos conectamos desde cualquier lugar, y contamos con modernos espacios colaborativos para mantener la cohesión con nuestros equipos.Tendrás acceso a seguros complementarios de salud, convenios con reconocidas universidades y beneficios preferenciales en Banco Ripley.Revisa más detalles sobre vida en la empresa en nuestro LinkedIn “Ripley Chile” y "Banco Ripley Chile". Tipo de Puesto: Plazo Fijo Fecha esperada de Contratación: 18/11/2026 ¡TRABAJA CON NOSOTROS!BeneficiosDescripción de los beneficios de la vacante</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q176"/>
+  <dimension ref="A1:Q183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12346,6 +12346,477 @@
         </is>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Operador Mantenedor</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>ICB</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56671/operador-mantenedor</t>
+        </is>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="O177" t="n">
+        <v>0</v>
+      </c>
+      <c r="P177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>¿Quiénes somos?JBA, empresa perteneciente al holding ICB y referente en la elaboración de alimentos, se caracteriza por su compromiso con la calidad, la innovación y la excelencia operacional. Contamos con modernas instalaciones productivas, altos estándares de seguridad y una sólida red logística que nos permite llegar a distintos puntos del país, contribuyendo al desarrollo de la industria alimentaria en Chile.Hoy nos encontramos en búsqueda de un Operador Mantenedor para desempeñarse en la comuna de Quilicura.Principales funciones:Ejecutar de manera eficiente y oportuna el programa de producción, de acuerdo con los procedimientos establecidos por JBA, cumpliendo los estándares de calidad, seguridad y medio ambiente.Operar correctamente las máquinas asignadas y aplicar las metodologías de trabajo definidas para asegurar el óptimo funcionamiento de los equipos, promoviendo además la mejora continua de los procesos.Coordinar a su equipo de trabajo para lograr el cumplimiento de los objetivos y programas de producción establecidos.Realizar labores de mantenimiento preventivo y correctivo (básico y avanzado) en las máquinas asignadas, contribuyendo a su correcto funcionamiento y disponibilidad operacional.Requisitos principales:Técnico Electromecánico, Técnico en Mantenimiento Industrial o carrera afín.Mínimo 2 años de experiencia en cargos similares, idealmente en plantas de alimentos.Disponibilidad para trabajar en turnos rotativos (mañana, tarde y noche) en la comuna de Quilicura.¡Te invitamos a ser parte de JBA!</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Planificador y Facturador - Temuco</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>ICB</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Región de la Araucanía, Chile</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56668/planificador-y-facturador-temuco</t>
+        </is>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="O178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>¿Quiénes somos?ICB, holding líder en la industria de alimentos y bebidas en Chile, se destaca por su excelencia en la producción, distribución y comercialización de marcas icónicas como Marco Polo, Cola Cao, TéClub, Inferno, Edra y Don Juan. Además, representamos a 23 marcas internacionales reconocidas a nivel mundial, como Van Camp s, Ferrero Rocher, Nutella y Kellogg s. Con tres grandes plantas productivas ubicadas en el norte de Santiago y una sólida red logística y comercial, estamos presentes en todo el país, consolidándonos como un referente en el mercado.Estamos en busca de un Planificador y Facturador (Regional) para incorporarse a nuestro equipo de Gerencia Logística.Principales Funciones:1.- Coordinar la disponibilidad de los controles de despacho y planificar las rutas de entrega, asegurando la distribución oportuna de los pedidos solicitados por los clientes.2.- Diseñar los circuitos de ruta, priorizando clientes críticos, y realizar seguimiento a los despachos en ruta para asegurar la entrega completa y oportuna de la mercadería.3.- Generar órdenes de transporte y documentación asociada al proceso de despacho y distribución, permitiendo el correcto inicio del picking y salida del stock comprometido.4.- Emitir documentación contable relacionada con la venta de productos y gestionar contingencias operacionales asociadas a la documentación del proceso.5.- Controlar el cumplimiento de la programación de cargas y generar reportes de gestión relacionados con los procesos de despacho y movimientos sistémicos de almacén y facturación.Requisitos Principales:Técnico en Logística o carrera afín.Mínimo 1 año de experiencia en cargos similares.Conocimientos en SAP, módulo WMS, Office nivel intermedio y conocimientos contables.¡Postula con nosotros!</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Supervisor de Ventas - Talca</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>ICB</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Región del Maule, Chile</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56667/supervisor-de-ventas-talca</t>
+        </is>
+      </c>
+      <c r="G179" t="n">
+        <v>2</v>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="O179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>¿Quiénes somos?ICB, holding líder en la industria de alimentos y bebidas en Chile, 🍟🍫🍪 se destaca por su excelencia en laproducción, distribución y comercializaciónde marcas icónicas comoMarco Polo, Cola Cao, Té Club, Inferno, EdrayDon Juan. Además, representamos a 23 marcas internacionales reconocidas a nivel mundial, comoVan Camp s, Ferrero Rocher, NutellayKellogg s. Contres grandes plantas productivasubicadas en el norte de Santiago y una sólida red logística y comercial, estamos presentes en todo el país, consolidándonos como un referente en el mercado🌟.Nos encontramos en búsqueda de un(a) Supervisor (a) de Punto de Venta para Talca. El rol principal del cargo cumplir el objetivo de venta e implementar las acciones comprometidas con los clientes en los puntos de ventas y supervisar el trabajo del personal bajo su responsabilidad.Funciones Principales:Realizar seguimiento directo e indirecto a las rutas bajo su responsabilidad, para identificar las oportunidades de mejora y cumplir las metas de ventas y distribución establecidas.Velar que los acuerdos comprometidos con el Cliente se cumplan bajo los estándares de ejecución definidos por el Grupo ICB en el punto de venta.Evaluar el desempeño del equipo de trabajo a su cargo.Controlar que los inventarios de camiones de transportes se lleven a cabo en virtud de los cambios de gestor o control rutinario.Coordinar la mantención preventiva y/o correctiva de los camiones de transportes, con el Jefe y/o Supervisor de Flota.Cumplir el indicador de devoluciones y/o descuentos a los clientes, previamente informado y autorizado por la Gerencia del Canal Tradicional.Cumplir y controlar el inventario de muebles (Raks y/o Exhibiciones) en los clientes del Grupo ICB.Gestionar y coordinar la cobranza oportuna de ventas realizada a clientes.🔎Requisitos:Carrera: Titulados/as de Técnico en Administración, Ingeniero Comercial o carrera afín.Experiencia: 2 o más años de experiencia en Canal Tradicional.Experiencia liderando equipos en empresas de consumo masivo (deseable).Manejo de Excel nivel intermedio.Licencia de conducir Clase B vigente. (excluyente)Disponibilidad para trabajar en terreno.¡Te invitamos a ser parte de ICB!🚚 🛒 🍫</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Práctica en Investigación de Fraude - Advisory - Forensic</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>KPMG Chile</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Las Condes, Metropolitana, Chile, Chile</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56654/practica-en-investigacion-de-fraude-advisory-forensic</t>
+        </is>
+      </c>
+      <c r="G180" t="n">
+        <v>2</v>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>1</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>1</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="n">
+        <v>1</v>
+      </c>
+      <c r="O180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Buscamos un estudiante proactivo y analítico para unirse a nuestro equipo de Advisory-Forensic en KPMG Chile.El candidato ideal será estudiante de Contador Auditor, Ingeniero Comercial, Ingeniero en Control de Gestión o carreras afines, con disponibilidad para una práctica profesional de al menos 3 meses (se valorará mayor duración).El rol principal consistirá en brindar apoyo en la prevención, detección e investigación de fraudes, abusos y otras formas de mala conducta, así como en la resolución de conflictos para nuestros clientes.Se espera que el practicante ejecute sus tareas con alta calidad, eficiencia y oportunidad, construyendo relaciones profesionales sólidas con el personal del cliente y el equipo interno.Competencias Clave y Requisitos:Formación Académica:Estudiante de carreras como Contador Auditor, Ingeniero Comercial, Ingeniero en Control de Gestión o afines.Habilidades Técnicas:Manejo de Excel a nivel intermedio.Idiomas:Nivel de inglés intermedio (deseable).Disponibilidad:Mínimo 3 meses para la práctica profesional.Documentación:Contar con seguro escolar y carta de solicitud de práctica de la institución educativa.Este puesto ofrece una excelente oportunidad para desarrollar habilidades prácticas en un entorno dinámico y desafiante dentro del área de Forensic.Beneficios¿Qué ganas tú?😎🌎Ser parte de una de las principales compañías de Auditoría y Consultoría a nivel mundial.🚀 Oportunidades de desarrollo profesional.💻Jornada de trabajo híbrida.🏢Oficinas de primer nivel ubicadas en Las Condes, frente al Parque Araucano.💯Múltiples convenios corporativos.🎉Actividades como fiestas, Meeting Points y encuentros de área para disfrutar con compañeros.🎂Tu día de cumpleaños es completamente libre para que lo disfrutes como desees.💸Renumeración mensual: $400.000 líquidos.En KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas , con un propósito claro, para una mejor sociedad. Valoramos las diversas habilidades y fortalezas, tanto personales como profesionales, que cada persona aporta. En KPMG estamos comprometidos con la Diversidad e inclusión , nuestras ofertas de empleo están disponibles con los ajustes razonables necesarios para tu proceso. Juntos, estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. ¡Anímate y ven a descubrir por qué somos la opción más clara! 🥇</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Risk Consultant</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Murex Chile</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Av. Apoquindo 2730, Chile</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56658/risk-consultant</t>
+        </is>
+      </c>
+      <c r="G181" t="n">
+        <v>5</v>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>sql, informatica</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>1</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
+        <v>1</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>¿Quiénes somos?Murex es una empresa global líder en tecnología financiera (fintech), especializada en soluciones de trading, gestión de riesgos y procesamiento para los mercados de capitales.Con presencia en 19 oficinas alrededor del mundo y más de 3.500 colaboradores de más de 60 nacionalidades, desarrollamos, implementamos y damos soporte a nuestra plataforma tecnológica, utilizada por bancos, asset managers, corporaciones y empresas de servicios públicos a nivel global.Si buscas formar parte de una industria innovadora y dinámica, en un entorno colaborativo y centrado en las personas, ¡este es tu lugar!El equipoSerás parte del equipo de Consultoría de Riesgo para la región Américas, entregando soporte proactivo y soluciones personalizadas a clientes del sector de Mercados de Capitales.Nuestros consultores acompañan a los clientes en todas las etapas: preventa, implementación y soporte en producción.Principales responsabilidadesBrindar soporte proactivo y de alta calidad a clientes que utilizan los módulos de Riesgo de la plataforma MX.Validar y analizar productos financieros, modelos asociados y perfiles de riesgo (instrumentos vanilla y exóticos).Diseñar soluciones funcionales y realizar el mapeo técnico para adaptar la plataforma a las necesidades del cliente.Gestionar casos de clientes desde su notificación hasta su resolución y validación final.Levantar requerimientos, configurar el sistema, ejecutar pruebas y acompañar a los clientes durante la implementación.Comprender el negocio del cliente y entregar soluciones de alta calidad dentro de los plazos del proyecto, aplicando mejores prácticas.Realizar capacitaciones y participar en la elaboración de materiales y documentación técnica.Apoyar en demostraciones y workshops durante procesos de preventa.RequisitosTítulo profesional en Ingeniería, Ingeniería en Informática, Ingeniería Financiera, Finanzas Aplicadas, Matemáticas o carreras afines.1 a 2 años de experiencia funcional y/o técnica en áreas relacionadas.Sólidos conocimientos en gestión de riesgos financieros, mercados e instrumentos financieros.Conocimientos en SQL (Oracle y/o Sybase) y comandos Unix (deseable).Alta capacidad analítica y excelentes habilidades comunicacionales.Trabajo en equipo, responsabilidad y orientación a resultados.Disponibilidad para viajar.Beneficios¿Por qué unirte a Murex?Formar parte de una empresa líder con más de 35 años de trayectoria en una industria en constante crecimiento.Integrarte a un equipo inclusivo, colaborativo y centrado en las personas.Trabajar en un entorno internacional con oportunidades de desarrollo global.Seguro médico, dental y de vida de primer nivel.En Murex promovemos la igualdad de oportunidades y la no discriminación en todos los procesos laborales, fomentando un entorno diverso, justo e inclusivo para todas las personas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Ingeniero de Proceso</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>ICB</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56666/ingeniero-de-proceso</t>
+        </is>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="n">
+        <v>1</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="n">
+        <v>0</v>
+      </c>
+      <c r="O182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>¿Quiénes somos?ICB, holding líder en la industria de alimentos y bebidas en Chile, se destaca por su excelencia en la producción, distribución y comercialización de marcas icónicas como Marco Polo, Cola Cao, Té Club, Inferno, Edra y Don Juan. Además, representamos a 23 marcas internacionales reconocidas a nivel mundial, como Van Camp’s, Ferrero Rocher, Nutella y Kellogg’s. Con tres grandes plantas productivas ubicadas en el norte de Santiago y una sólida red logística y comercial, estamos presentes en todo el país, consolidándonos como un referente en el mercado.Estamos en busca de unIngeniero de Procesospara incorporarse a nuestro equipo deGerencia de Operaciones.Principales Funciones:Detectar, analizar e implementar oportunidades de mejora en los procesos productivos, realizando seguimiento a las soluciones implementadas y evaluando sus resultados.Coordinar y controlar periódicamente el balance de masa de las distintas líneas de proceso, identificando oportunidades de optimización.Generar informes de gestión y seguimiento de KPI asociados a las mejoras y desempeño de los procesos productivos.Identificar oportunidades de disminución de costos en las distintas líneas de producción, proponiendo acciones orientadas a optimizar los procesos.Velar por el cumplimiento de los estándares y procedimientos establecidos por la compañía, considerando los requisitos de calidad, inocuidad, seguridad e higiene.Requisitos Principales:Título deIngeniería Civil Mecánica o carrera afín.Mínimo1 año de experiencia en cargos similares, idealmente relacionados con procesos productivos o mejora continua.Conocimientos deOffice nivel intermedio.¡Te invitamos a ser parte de ICB! 🍟BeneficiosSeguro ComplementarioCasinoGimnasioBus de acercamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Analista de comunicaciones</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Watt's</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56655/analista-de-comunicaciones</t>
+        </is>
+      </c>
+      <c r="G183" t="n">
+        <v>2</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>1</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="n">
+        <v>0</v>
+      </c>
+      <c r="O183" t="n">
+        <v>0</v>
+      </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>En Watt’s buscamos nuevos talentos!En tu despensa, refrigerador o congelador hay, al menos, un producto elaborado por Watt's. Es por esto que queremos invitarte a ser parte de una de las principales empresas de alimentos del país y ayudarnos a seguir creciendo, diversificándonos e innovando.Estamos en búsqueda de nuestro próximo Analista de Comunicaciones,para nuestra gerencia de Personas, planta San Bernardo.Tus desafíos serían:Reportear para informar, a través de todos los medios de comunicación disponibles, las actividades, proyectos y temas relevantes de la Compañía.Monitorear los medios informativos y generar informes diarios de prensa.Apoyar comunicacionalmente a todas las áreas de la Compañía.Liderar, coordinar y ejecutar las actividades y campañas del Voluntariado Corporativo.Apoyar en la realización de diversos eventos corporativos de la Compañía.Coordinar y ejecutar visitas de escolares en Planta Lonquén.Gestionar requerimientos administrativos asociados al área.¿Qué esperamos de ti?Movilidad propia (excluyente).Experiencia o interés en comunicaciones internas y corporativas.Habilidades de redacción, generación de contenidos y comunicación con distintos públicos.Manejo de herramientas audiovisuales para la creación y edición de contenidos.Manejo de Excel y conocimientos de SAP serán considerados un plus.Proactividad, organización y capacidad para trabajar de manera colaborativa con distintas áreas de la compañía.BeneficiosOfrecemos:Casino en las plantas de acuerdo a tu jornada de trabajo.Aguinaldo de fiestas patrias y navidad.Días administrativos.Seguro complementario de Salud y Dental.Ropa de trabajo para los cargos que así lo requieran.Sala cuna o bono para trabajadoras con hijos menores de hasta 2 años.Venta de productos con descuentos exclusivos Watt’s.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q183"/>
+  <dimension ref="A1:Q192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12821,6 +12821,599 @@
         </is>
       </c>
     </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Business Specialist Advanced</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>BCP</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56731/business-specialist-advanced</t>
+        </is>
+      </c>
+      <c r="G184" t="n">
+        <v>6</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>sql, analisis, power bi</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>¡Únete al EquipoBCP! Sé parte de una comunidad que no conoce fronteras, con un propósito en común que nos motiva e inspira para impactar en los planes de millones de peruanos, transformándolos en realidad. ¿Quieres pertenecer a algo grande? ¡Aquí Es!¿Qué esperamos de ti?Velar por la productividad y eficiencia de los canales comerciales, generando iniciativas y proyectos que impacten en el performance de los mismos.Diseñar e implementar iniciativas/estrategias que impacten en la productividad de venta de los caneles comerciales.Realizar Pilotos/ control (A/B Test) para determinar el impacto de las iniciativas, entre otros.Manejo de data - Realizar análisis.¿Qué buscamos?Experiencia PreviaExperiencia mínima de 1 año en funciones afines.Conocimiento TécnicoOffice 365 (avanzado).SQL (intermedio/avanzado).Power BI.Formación EsperadaProfesionales universitarios de Ingeniería industrial, Economía, administración o afines.¿Qué Ofrecemos?Ambiente empoderador: Únete a un entorno de trabajo donde tu voz importa y tus ideas impulsan el cambio.Crecimiento profesional: Disfruta de oportunidades de desarrollo continúo, respaldadas por un equipo comprometido con tu éxito.Compensación competitiva: Recibe una compensación atractiva y beneficios flexibles diseñados para adaptarse a tu estilo de vida y metas personales.Beneficios¿Qué beneficios disfrutarás?Ingreso a Planilla.Pago de Bonos por Desempeño.Pago de Utilidades.Oportunidades de desarrollo</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Ejecutivo de Negocios BEX Digital</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>BCP</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56730/ejecutivo-de-negocios-bex-digital</t>
+        </is>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="n">
+        <v>1</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" t="n">
+        <v>0</v>
+      </c>
+      <c r="O185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Buscamos a los que tienen ganas de transformar el país. A los que quieren llegar lejos. Por qué esto no es solo un trabajo. Esto es desafiarte en grande para impactar en grande. Esto es el BCP y te estamos buscando para que formes parte de nuestro equipo comoEjecutivo de Negocios BEX Digital¿Cuál es el reto?Construir relaciones a largo plazo con los clientes a través de la efectiva gestión comercial de su cartera. Es responsable de interactuar con los clientes a través del servicio ágil y construir relaciones duraderas.¿Cómo impactarás en grande?Gestionar estratégicamente una cartera de clientes de banca exclusiva, identificando oportunidades comerciales.Brindar atención remota ágil y personalizada, ofreciendo soluciones financieras.Priorizar y administrar la cartera según metodología establecida, garantizando seguimiento postventa.Disponibilidad para laborar de manera presencial en Surquillo o San Isidro.Disponibilidad para trabajar de lunes a viernes de 8:30 a.m. a 6:00 p.m. y sábados de 8:30 a.m. a 1:00 p.m.¿Qué necesitamos de ti?Egresado(a) universitario(a) de carreras afines a Banca, Administración, Economía, Negocios o similares.Experiencia mínima de 1 año de experiencia con manejo de cartera de clientes, venta multiproducto (tarjetas, seguros, préstamo personal, préstamo vehicular y préstamo hipotecario, este último solo conocimiento básico de preferencia).Experiencia en gestión de cartera de clientes, venta de productos financieros y cumplimiento de metas comerciales.¿Por qué unirte a nuestro equipo?Ser parte de la empresa #1 en Merco Talento 2026.Ingreso a planilla BCP desde tu primer día.Accede a incentivos por tu esfuerzo/desempeño.Acompañamiento de líderes expertos y referentes en la banca.Acceso a descuentos en productos financieros.Beneficios corporativos exclusivos por provincia para disfrutar con tu familia.Formarás parte de una cultura constante de reconocimientos¡Únete al equipo BCP!“Somos una organización comprometida con la igualdad de derechos y oportunidades. Nuestros procesos de selección se rigen bajo una política donde nuestras/os postulantes son consideradas/os sin importar su origen, género, raza o cualquier otra característica, condición o preferencia, promoviendo así una cultura de respeto mutuo"</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Asistente Administrativo - La Joya</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Ferreyros</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Arequipa, Perú</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56729/asistente-administrativo-la-joya</t>
+        </is>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>1</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="n">
+        <v>0</v>
+      </c>
+      <c r="O186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>Misión del puestoRealizar los diferentes procesos y gestiones relacionados con la administración de recursos humanos y proveedores de servicios al personal a fin de contribuir a la gestión del área y propiciar el buen clima laboral del CRC-La Joya así como garantizar el cumplimiento de los objetivos trazados para esta.FuncionesCoordinar con los colaboradores de la operación las firmas de los diferentes documentos requeridos por el área de Recursos Humanos, así como también, comunicar oportunamente las renuncias y no renovaciones.Coordinación de viajes por capacitación y otros.Generar requerimientos por suministros, uniformes, epps y útiles de oficina para el área administrativa y hacer el seguimiento respectivo hasta la llegada de los mismos. Asegurar que se de buen uso de los suministros.Gestionar las habilitaciones del personal permanente para su ingreso a CRC, solicitar uniforme, alimentación, movilidades en caso requiera.Coordinar los servicios de alimentación y transporte de los colaboradores, con el fin de asegurar el confort y bienestar de los mismos.Gestión con Proveedores: Realizar el seguimiento de los servicios de comedor, lavandería y transporte para brindar el servicio y satisfacción del personal.Asumir otras funciones que le sean asignadas por su jefe inmediato, con el fin de mantener la eficiencia en el área y/o Gerencia.RequisitosEgresado(a) de Carreras: Administración, Ing. Industrial o carreras afinesConocimiento en:Tributación, normas laborales, finanzasManejo de OfficeManejo de SAPExperiencia general y en posiciones similares de 01 a 02 años</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Diseñador Gráfico Instruccional</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Ferreyros</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Lima, Perú</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56728/disenador-grafico-instruccional</t>
+        </is>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
+        <v>1</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="n">
+        <v>0</v>
+      </c>
+      <c r="O187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>MisiónCrear contenidos gráficos digitales para el desarrollo de entrenamientos asíncronos y microlearning dentro del proyecto de transformación digital de los entrenamientos técnicos, que permitan contribuir al desarrollo técnico de la compañía de acuerdo con los objetivos establecidos.FuncionesCrear elementos visuales para cursos asíncronos sobre capacitaciones técnicas de equipos de la empresa.Desarrollar recursos visuales efectivos para microlearning, enfocándose en temas específicos Caterpillar.Potenciar nuestros cursos técnicos existentes, a conceptos de diseños gráficos paraentornos de aprendizaje virtuales.Trabajar con equipos multidisciplinarios usando la metodología Scrum.Garantizar la coherencia visual en todos los diseños, manteniendo una identidad gráfica sólida y cumpliendo con altos estándares de calidad.Grabación y fotografía en campo utilizando equipos audiovisuales de la empresa para la generación de insumos de capacitación.Producir contenido en formatos dinámicos enfocados en capacitación técnica y microaprendizaje.RequisitosEgresado(a) técnico en Diseñador Gráfico Digital, Diseño Gráfico o afines.2 años de experiencia en el rubro y/o sector.Dominio y conocimiento en contenido e-learningDisponibilidad para laborar de manera presencial en la Sede Callao (Av. Argentina).</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Ingenieroa de Inteligencia de Negocios y Datos - Manantial - Quilicura</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>CCU</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56742/ingeniero-a-de-inteligencia-de-negocios-y-datos-manantial-quilicura</t>
+        </is>
+      </c>
+      <c r="G188" t="n">
+        <v>13</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>machine learning, analisis, excel, power bi, looker studio, looker</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>1</v>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>¡En CCU nos apasiona crear experiencias para compartir juntos un mejor vivir!Nos encontramos en búsqueda de unIngeniero/a de Inteligencia de Negocios y Datospara desempeñarse en nuestra Unidad de Negocio deManantial, en nuestra planta ubicada enQuilicura.El propósito del cargo es gestionar y controlar el software de análisis de datos de Manantial, siendo parte esencial de la inteligencia del negocio en términos de indicadores y reportería, al disponibilizar información crítica sobre y hacia las diferentes áreas, con el fin de facilitar el seguimiento y gestión del desempeño de los diferentes procesos asociados a Manantial.Principales funciones:Construcción y mantención de modelos de Power BI en base a las distintas necesidades del negocio, apoyando a las áreas en la construcción de indicadores o modelos que ayuden en la gestión diaria de sus procesos internos o externos.Programar los datos dentro de la plataforma de la compañía y entregar reportería de forma amigable y clara, para disponibilizar la información y optimizar y automatizar tareas según corresponda.Realizar controles necesarios para que la gobernanza de los datos esté alineada con la seguridad y los objetivos del negocio, estableciendo controles y aseguramiento de la parametría y calidad de los datos con el fin de resguardar el correcto funcionamiento del negocio a nivel de sistemas.Realizar el levantamiento y la implementación de nuevos modelos de machine learning que permitan crear valor a través de los datos, con la finalidad de impulsar nuevas estrategias e innovaciones. Mantener modelos actuales, asegurando el seguimiento de los indicadores relacionados a las acciones comerciales implementadas, como también realizar reprocesos y actualización de parámetros.Requisitos:Título de Ingeniería en Informacion y Control de Gestión, Ingeniería Civil Industrial, Ingeniería Comercial, o carrera afín.Entre 6 meses y 2 años de experiencia en cargos similares.Manejo de Excel nivel intermedio (excluyente).Manejo de Power Bi y/o Looker Studio (deseable).Manejo de herramientas de Inteligencia Artificial.Conocimientos en Machine Learning (deseable).Disponibilidad de trabajar de manera presencial en nuestra planta de Manantial en Quilicura (1 día de teletrabajo a la semana).Nuestro SER CCU nos inspira a trabajar con aceptación y respeto a las diferencias de las personas, promoviendo un entorno diverso e integrador, para así contribuir a un mejor vivir. Por esto, te agradecemos que nos compartas si necesitas adaptación en alguna etapa del proceso de postulación.¡Te invitamos a SER CCU!</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Administrativoa de Sucursal - Coquimbo</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>CCU</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Coquimbo, Chile</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56733/administrativo-a-de-sucursal-coquimbo</t>
+        </is>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
+        <v>1</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="n">
+        <v>0</v>
+      </c>
+      <c r="O189" t="n">
+        <v>0</v>
+      </c>
+      <c r="P189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>¡En CCU nos apasiona crear experiencias para compartir juntos un mejor vivir!Nos encontramos en búsqueda de un/aAdministrativo/a de Sucursal, para desempeñarse en nuestra unidad de negocio deManantial, en Coquimbo.Principales funciones:Atender requerimientos de clientes internos y externos, entregando una respuesta oportuna y realizando seguimiento a sus solicitudes.Gestionar tickets de postventa y servicio técnico, coordinando su atención con las áreas correspondientes.Contactar a clientes para informar el estado de sus pedidos y coordinar entregas, instalaciones o retiros de equipos.Realizar control de activos de la sucursal y mantener actualizados los registros asociados.Realizar control de caja y liquidación de valores, de acuerdo con los procedimientos establecidos.Requisitos:Enseñanza media completa o formación técnica de nivel medio o superior en Administración o carreras afines.Deseable desde 1 año de experiencia en cargos administrativos similares.Deseable experiencia en atención al cliente, postventa, control de caja y activos.Disponibilidad para trabajar en Coquimbo.Manejo de SAP u otro ERP (deseable).Nuestro SER CCU nos inspira a trabajar con aceptación y respeto a las diferencias de las personas, promoviendo un entorno diverso e integrador, para así contribuir a un mejor vivir. Por esto, te agradecemos que nos compartas si necesitas adaptación en alguna etapa del proceso de postulación.¡Te invitamos a SER CCU!</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Técnico en Automatización</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Laboratorios Maver</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56727/tecnico-en-automatizacion</t>
+        </is>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="n">
+        <v>1</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="O190" t="n">
+        <v>0</v>
+      </c>
+      <c r="P190" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>EnLaboratorios Maver, empresa con más de 100 años de historia en la industria farmacéutica chilena y casa de marcas reconocidas comoTapsin, Dolorub, Armonyl, Disfruta y Crema Lechuga, estamos buscando un/aTécnico de Nivel Superior o Ingeniero(a) en Automatización, Electrónica, Electricidad Industrial o carrera afínpara sumarse al equipo deIngeniería y Mantención.En este rol tendrás la oportunidad de:Ejecutar mantenimiento preventivo, correctivo y predictivo de sistemas de control, instrumentación de campo (transmisores de presión, temperatura, flujo, nivel) y variadores de frecuencia.Diagnosticar y resolver fallas de automatización que afecten la continuidad operacional, priorizando según criticidad para producción.Dar soporte técnico a Producción ante alarmas, fallas de control o desviaciones de proceso.Participar en proyectos de actualización y mejora de sistemas de control (upgrades de PLC/SCADA, integración de nuevos equipos).Apoyar en la calibración y verificación metrológica de instrumentos, en coordinación con las áreas productivas.Mantener actualizada la documentación técnica: planos eléctricos, lógicas de programación y backups de programasTrabajar en un entorno regulado, asegurando el cumplimiento de normativa BPM/GMP e ISP en todas las intervenciones.BeneficiosBuses de acercamiento y Casino Gratis.Día libre por tu cumpleaños🎉*Seguro Complementario**Sujeto a condiciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Analista de Impuestos - Tax Technology</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>KPMG Chile</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Las Condes, Metropolitana, Chile, Chile</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56724/analista-de-impuestos-tax-technology</t>
+        </is>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="n">
+        <v>1</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>1</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" t="n">
+        <v>0</v>
+      </c>
+      <c r="O191" t="n">
+        <v>0</v>
+      </c>
+      <c r="P191" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>**Perfil Ideal: Analista de Impuestos - Tax Technology (Junior)** Buscamos un **Analista de Impuestos** con un fuerte interés en la intersección entre tributación y tecnología para unirse a nuestro equipo de Tax Technology en KPMG Chile. El candidato ideal poseerá hasta 1 año de experiencia en cumplimiento tributario y una genuina motivación por innovar y desarrollarse en un entorno dinámico. Las responsabilidades clave incluyen la aplicación de la normativa tributaria vigente para el desarrollo de herramientas tecnológicas que optimicen el cumplimiento, la preparación de escenarios de prueba, la documentación de trabajos y el soporte a clientes. Se requiere título de **Contador Auditor** y un manejo competente de herramientas **Office e Inteligencia Artificial**. Si bien el inglés intermedio no es excluyente, se valorará. Buscamos profesionales con excelentes habilidades interpersonales, orientación al cliente, capacidad de trabajo en equipo, comunicación efectiva y un deseo constante de aprender y crecer profesionalmente.Beneficios¿Qué ganas tú? 🌎 Ser parte de una de las principales compañías de Auditoría y Consultoría a nivel mundial. 🚀 Oportunidades de desarrollo profesional y crecimiento de carrera. 🚑 Seguro de salud complementario con contrato indefinido. 💻 Modalidad de trabajo híbrida. 🏢 Oficinas de primer nivel ubicadas en Las Condes, frente al Parque Araucano. 💯 Múltiples convenios corporativos. 🎉 Actividades de integración, Meeting Points, celebraciones y encuentros de área. 🎂 16 horas anuales de libre disposición y día de cumpleaños libre.   En KPMG Chile tenemos el orgullo de ayudar a hacer mejores empresas , contribuyendo a construir una mejor sociedad. Valoramos las diversas habilidades y fortalezas que cada persona aporta. Estamos comprometidos con la diversidad, equidad e inclusión, por lo que nuestras oportunidades laborales consideran los ajustes razonables necesarios para cada proceso de selección. Juntos estamos definiendo el estándar de excelencia y marcando la diferencia en el mundo empresarial. 🥇¡Anímate y ven a descubrir por qué somos la opción más clara!</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Técnicoa de Operaciones | Tanner</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Tanner</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56735/tecnico-a-de-operaciones-tanner</t>
+        </is>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>1</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="n">
+        <v>1</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>EnTannerbuscamos un/aTécnico/a de Operacionesque quiera comenzar o seguir desarrollando su carrera en nuestra Gerencia de Operaciones.Serás parte de un equipo donde podrás aportar a la correcta ejecución de los procesos administrativos y operativos, trabajando de manera colaborativa y contribuyendo al cumplimiento de los objetivos del área.¿Cuáles serán tus principales desafíos?Ejecutar y revisar las labores administrativas y operativas del área.Velar por el correcto cumplimiento de los procedimientos y plazos establecidos.Gestionar las solicitudes encomendadas y apoyar la gestión comercial y administrativa.Administrar información y preparar reportes asociados a la operación.Contribuir al cumplimiento de los requerimientos del área, de acuerdo con los procedimientos internos y la normativa vigente.¿Qué buscamos?Estudios técnicos o profesionales.Conocimientos en Finanzas.Manejo de Microsoft Office.Conocimientos de SAP.Proactividad, empatía y disposición para trabajar colaborativamente.Si buscas una oportunidad para poner en práctica tus conocimientos, aprender y desarrollarte en el área de Operaciones,te invitamos a postular y ser parte de Tanner.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/first_job/summary_data.xlsx
+++ b/data/first_job/summary_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q192"/>
+  <dimension ref="A1:Q199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13414,6 +13414,477 @@
         </is>
       </c>
     </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Ejecutivo de Cobranzas Plazo Fijo</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Mutucar</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56762/ejecutivo-de-cobranzas-plazo-fijo</t>
+        </is>
+      </c>
+      <c r="G193" t="n">
+        <v>3</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>analisis, excel</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>1</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>En Mutualidad de Carabineros, organización privada sin fin de lucro del rubro del seguro, buscamos dos Ejecutivos de Cobranzas Plazo Fijo (6 meses) para sumarse a nuestro equipo del Departamento de Seguros. Estamos en un proceso de transformación de negocio y buscamos talentos con ganas de desafiarse y ser protagonistas de este proceso de cambio.El propósito del cargo es contribuir al correcto funcionamiento de la gestión operativa y administrativa del proceso de cobranzas del Departamento de Seguros.Funciones:Realiza análisis básicos de datos relacionados con las cuentas por cobrar, como la identificación de tendencias de pago, el calculo de saldos pendientes y la generación de informes simples.Brinda atención y asistencia a los asegurados en relación con sus pólizas de seguros, tanto presencial como telefónica, resolviendo consultas sobre cobros y pagos y proporcionando información sobre opciones de pago y coberturas.Realiza seguimiento de las primas de seguros vencidas, enviar recordatorios de pago a los asegurados y coordinar con los analistas de cobranzas para el seguimiento y recuperación de las primas pendientes.Negocia acuerdos de pago, planes de financiamiento o reestructuración de deuda con los asegurados para facilitar la regularización de pagos pendientes.Verifica el estado de los reclamos pendientes y coordina la regularización de pagos relacionados con reclamos de seguros.Procesa solicitudes de devoluciones de primas de seguros y coordina la emisión de reembolso según las políticas y procedimientos establecidos.Requisitos:Profesional titulado de técnico en Administración de empresa, Técnico en Contabilidad o carreras a fin.Manejo de Excel Intermedio para registrar, monitorear y gestionar las actividades de cobranza de manera eficiente.1 año de experiencia en entidades financieras, auditoras o similares.Te invitamos a sumarte a una organización con propósito y en proceso de cambio porque "Brindar apoyo y seguridad a quienes nos entregan seguridad" nos orienta a seguir mejorando para nuestros asegurados y sus familias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Analista Tributario (Plazo Fijo)</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Tanner</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56758/analista-tributario-plazo-fijo</t>
+        </is>
+      </c>
+      <c r="G194" t="n">
+        <v>2</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>excel</t>
+        </is>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>1</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>En Tanner estamos en búsqueda de nuestro/a próximo/aAnalista TributarioSi te interesa desarrollarte en el área tributaria y ser parte de un equipo que impacta directamente en la transparencia y cumplimiento financiero de la organización, esta oportunidad es para ti.Modalidad: Híbrida, Santiago Centro /Plazo Fijo (6 mesesEn Tanner estamos en búsqueda de nuestro/a próximo/aAnalista TributarioSi te interesa desarrollarte en el área tributaria y ser parte de un equipo que impacta directamente en la transparencia y cumplimiento tributario de la organización, esta oportunidad es para ti.Modalidad:Híbrida, Santiago Centro /Plazo Fijo (6 meses)¿Cuáles serán tus principales desafíos?Analizar y controlar cuentas contables asociadas a impuestos en procesos de cierre mensual.Apoyar en la preparación de declaraciones tributarias mensuales y anuales (F29, F24, F50, entre otras).Colaborar en el cálculo de impuestos y en la elaboración de reportes tributarios.Revisar el tratamiento tributario de distintas operaciones y productos financieros.Apoyar en procesos de fiscalización y requerimientos de organismos reguladores.Contribuir a la mejora continua de procesos y controles tributarios del área.¿Qué buscamos?Título de Contador/a Auditor/a.Experiencia mínima 1 a 3 años en materia de impuestos.Conocimientos en normativa tributaria vigente (SII) y contable.Manejo de Excel (idealmente nivel intermedio-avanzado).Deseable conocimiento en ERP contable (como SAP) y en temas impositivos de industria financiera.Interés por desarrollarse en el área tributaria.Valoramos especialmenteCapacidad analítica y atención al detalle.Organización y planificación.Trabajo colaborativo y comunicación efectiva.Proactividad y ganas de aprender.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Supervisor de Tarjeta Ripley</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Ripley chile</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Tda Plaza Egaña (Gesic) - Relación Comercial, Chile</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56756/supervisor-de-tarjeta-ripley</t>
+        </is>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>1</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>Supervisor de Tarjeta RipleyEn Ripley Chile, lo tenemos todo ¡Solo nos falta tu talento! 🤩Estamos en búsqueda de nuestro/a nuevo/a Supervisor de Tarjeta para nuestra tienda Ripley ubicada en la Región Metropolitana.Tu misión será ser el responsable del equipo de trabajo, planificando y controlando la gestión del personal a su cargo, con el fin de cumplir los objetivos de venta de productos financieros y la excelencia en el servicio entregado.¿Cuáles serán tus principales desafíos? 🚀Asegurar una atención y solución de problemas hacia los clientes a través de su personal de acuerdo a los estándares exigidos por la empresa.Supervisar a todo el equipo de trabajo en las tareas planificadas para el alcance de los objetivos trazados en el plan de trabajo, entregando retroalimentación oportuna.Asesoría y guia de acción para mejorar la productividad del área, buscando soluciones potenciales o planes de acción positivos.Programación de talleres para el desarrollo de habilidades para persuadir y vender.Manejo acabado de los sistemas y servicios que otorga la tarjeta ripley a sus clientes.Responsable del manejo de la información, de forma que esta se encuentre en las bases lo más clara posible.¿Qué valoramos en tu postulación? 🎯Estudios Universitarios o tecnicos del área de la administración2 años de experiencia en cargo similarOrientación al logroCapacidad de trabajo en equipoManejo de ConflictosDisponibilidad para trabajar con turnos rotativos de Lunes a Domingo.¿Por qué trabajar en Ripley? 💜Pensamos en el bienestar de nuestros colaboradores, es por esto que contamos con atractivos beneficios corporativos como:Capacitaciones y entrenamiento enfocado a tu desarrollo de carrera.Tasa Preferencial en Productos Banco Ripley.Seguro Complementario Gratuito.Descuento en Tiendas Ripley.Desarrollo Profesional.Entre otros.¡En Ripley estamos comprometidos con la Diversidad e Inclusión laboral!¡Postula para ser parte de nuestro equipo! Tipo de Puesto: Plazo Fijo Fecha esperada de Contratación: 22/10/2026 ¡TRABAJA CON NOSOTROS!BeneficiosDescripción de los beneficios de la vacante</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>CHOFER POLVORINERO</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Enaex</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Antofagasta, Antofagasta, Chile</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56749/chofer-polvorinero</t>
+        </is>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
+        <v>1</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>Nuestra empresa:Enaex es una empresa filial del grupo Sigdo Koppers, con más de 100 años de trayectoria en el mercado de explosivos. Nos hemos consolidado como el tercer productor mundial de Nitrato de Amonio de baja densidad y el principal prestador de servicios integrales de fragmentación de roca para la minería en Chile y Latinoamérica. Queremos invitarte a crecer con nosotros y desafiarte día a día en una compañía cuyo propósito es Humanizar la minería. Si para ti la prioridad es la vida, tu obsesión es la excelencia, tu vocación son los clientes y tienes como fortaleza la innovación y el emprendimiento, ¡este es tu lugar!Misión del cargo:Prestar apoyo al proceso de tronadura mediante el uso del Camión Polvorín para realizar el proceso de la manera más eficienteysegura posibleDescripción del cargo:Funciones del cargo:- Revisa el equipo al iniciar y finalizar el turno completando el check list.- Manipular, transportar y controlar los explosivos necesarios para el proceso de tronadura, utilizando el camion polvorin para su traslado- Realiza control de inventarios y cuadratura de polvorines.- Firma vale de retiro de explosivos y lleva registro de los mismos.- Mantiene el orden del Polvorín acorde a la normativa vigente.- Realiza medición, primado, amarre y apoyo en carguío de pozos en caso de ser necesario.- Apoya en el carguío de pozos de precorte en caso de ser requerido.- Apoyar labores de aseo Apoya labores de aseo en la planta, oficina, equipos, polvorín, entre otros.Nuestro Candidato Ideal:1 año de experiencia operando equipos transporte explosivosContar con Licencia de conducir clase A4 y B (excluyente)Proceso de selección:El proceso de selección se realiza a través de Aira - plataforma de reclutamiento diseñado para mejorar tu experiencia de postulación.Para postular solo necesitas:1. Postular a la oferta2. Revisar tu email3. Ingresar a Aira y contestar las preguntas y/o pruebas solicitadasLuego, si vemos que tu perfil se ajusta a lo que estamos buscando, te contactaremos por email (a través de Aira) para seguir a la etapa presencial.Beneficios- Seguro médico- Capacitaciones y cursos- Actividades wellness- Gimnasio- Subsidio escolar para hijos- Subsidio escolar para hijos- Préstamos financieros- Vacaciones extras</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Ingenieroa Entrenamiento III Región</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Enaex</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Copiapó, Atacama, Chile</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Presencial Trabajo</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56752/ingeniero-a-entrenamiento-iii-region</t>
+        </is>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="n">
+        <v>1</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>Nuestra empresa:Enaex es una empresa filial del grupo Sigdo Koppers, con más de 100 años de trayectoria en el mercado de explosivos. Nos hemos consolidado como el tercer productor mundial de Nitrato de Amonio de baja densidad y el principal prestador de servicios integrales de fragmentación de roca para la minería en Chile y Latinoamérica. Queremos invitarte a crecer con nosotros y desafiarte día a día en una compañía cuyo propósito es Humanizar la minería. Si para ti la prioridad es la vida, tu obsesión es la excelencia, tu vocación son los clientes y tienes como fortaleza la innovación y el emprendimiento, ¡este es tu lugar!Misión del cargo:Gestionar procesos y procedimientos del área de manera eficiente y efectiva.Descripción del cargo:En Enaex, Multinacional Proveedora de la Minería, Líder en el Mercado de los Explosivos y fabricación de Nitrato de Amonio, nos encontramos actualmente en búsqueda de un/a Ingeniero/a en Entrenamiento III Región.Te invitamos a iniciar tu carrera profesional con nosotros, donde serás un aporte para cumplir con nuestro propósito de humanizar la minería y tendrás muchas oportunidades para seguir creciendo como profesional.Queremos contar contigo para apoyar en los distintos procedimientos asociados a la gestión del área con el objetivo de que éstos se realicen de la manera más eficiente y efectiva posible.Principales funciones a cumplir en tu día a día:- Apoyar la gestión diaria de procedimientos operacionales, administrativos y proceso de licitación.- Apoyar la gestión de proyectos de su área.- Administrar o generar un proceso base de control sistemático en el área, con el fin de ordenar y facilitar la generación de datos, que permitan tomar las mejores decisiones estratégicas, para dar cumplimiento a los planes de producción.- Realizar reportes periódicos con indicadores, que den cuenta de un control exhaustivo de la gestión requerida.- Proponer proyectos, mejoras y/o alternativas de solución.Nuestro Candidato Ideal:Ingeniera/o Civil, comercial o carreras afinInglés avanzadoMáximo 2 años de experiencia profesionalProceso de selección:El proceso de selección se realiza a través de Aira - plataforma de reclutamiento diseñado para mejorar tu experiencia de postulación.Para postular solo necesitas:1. Postular a la oferta2. Revisar tu email3. Ingresar a Aira y contestar las preguntas y/o pruebas solicitadasLuego, si vemos que tu perfil se ajusta a lo que estamos buscando, te contactaremos por email (a través de Aira) para seguir a la etapa presencial.Beneficios- Seguro médico- Capacitaciones y cursos- Actividades wellness- Gimnasio- Subsidio escolar para hijos- Subsidio escolar para hijos- Préstamos financieros- Vacaciones extras</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Analista Logística - Supply Chain</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>BAT</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Valparaíso, Chile</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Presencial Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56750/analista-logistica-supply-chain</t>
+        </is>
+      </c>
+      <c r="G198" t="n">
+        <v>1</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>analisis</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>1</v>
+      </c>
+      <c r="L198" t="n">
+        <v>1</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="n">
+        <v>0</v>
+      </c>
+      <c r="P198" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>Esta posición pertenece al departamento deSupply Chain, específicamente al área deLogística.La persona será responsable de apoyar la gestión y control de los procesos logísticos mediante el análisis de información, elaboración de reportes, seguimiento de indicadores de desempeño (KPI) y coordinación de actividades operacionales. Su principal objetivo será contribuir a la eficiencia de la cadena de suministro, asegurando la disponibilidad y calidad de la información para la toma de decisiones del negocio.Beneficios• Bus de acercamiento.• Oportunidad de conocer el negocio y distintas operaciones logísticas.• Participación en proyectos de mejora y transformación de Supply Chain.• Desarrollo profesional dentro de una organización líder en su industria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Analista de Contenido Junior</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Kitchen Center</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago, Chile</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Híbrido Trabajo</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://firstjob.me/oferta/56755/analista-de-contenido-junior</t>
+        </is>
+      </c>
+      <c r="G199" t="n">
+        <v>2</v>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>html</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>1</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="n">
+        <v>1</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>Kitchen Center imporante Empresa del rubro Retail, buscamos a una persona creativa, analítica y con gran interés en el mundo digital, para integrarse a un equipo de trabajo dinámico, donde podrá aportar a la generación de contenidos orientados al posicionamiento orgánico y crecimiento de visibilidad en canales digitales.Principales responsabilidades:Implementación y optimización de mejoras técnicas SEO para RRSS y sitio web.Redacción de textos SEO (blog, notas, descripciones de productos, recetas, comparativas, preguntas frecuentes, entre otros) implementando buenas prácticas del orgánico (html, H1, H2, estructura de textos).Elaboración semanal de un listado de palabras clave para orientar contenido estratégico y definir el calendario de contenido de SEO (según palabras clave y tendencias).Supervisión y actualización de las páginas web de las marcas, asegurando que el contenido esté vigente, alineado con campañas, correctamente vinculado y optimizado con palabras clave relevantes para mejorar su visibilidad.Medición del crecimiento del SEO tanto de Google como Social.Apoyo general en la planificación de RRSS (Redacción de copies para RRSS, CTA, considerando palabras clave relevantes, etc).Planificación y organización de contenido visual (fotos y vídeos) (considera hacer los Briefs para los videos)Apoyo transversal en la revisión y redacción de textos que se requieren en distintas áreas de la empresa.lacionadas con el desempeño del contenido orgánico.Perfil deseadoCarrera: Publicista, Periodista, Relacionador Público, Ingeniería en marketing o afín.Experiencia: al menos 6 meses de experiencia comprobada en SEOBeneficiosTrabajo Híbrido 3x2Casino en Casa MatrizEstacionamientoGimnasio en Casa Matriz</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
